--- a/data/Fate-Spreadsheet.xlsx
+++ b/data/Fate-Spreadsheet.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pixel\Downloads\Fate-Wiki-Assets\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pixel\Documents\Projects\Fate-Wiki\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F82F6AE1-4067-484E-A19C-49C0363DFF0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{807CE838-7557-4D17-845B-C213D3F85AAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="2" xr2:uid="{B05E798F-9EF6-4508-A0A4-311D06661AED}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="1" xr2:uid="{B05E798F-9EF6-4508-A0A4-311D06661AED}"/>
   </bookViews>
   <sheets>
     <sheet name="Servants" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="76">
   <si>
     <t>servant_id</t>
   </si>
@@ -268,6 +268,9 @@
   </si>
   <si>
     <t>Common-Golem</t>
+  </si>
+  <si>
+    <t>quantity</t>
   </si>
 </sst>
 </file>
@@ -862,16 +865,16 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D1BC60D8-44F3-478D-BCC0-4752624457AE}">
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="2" max="2" width="19" customWidth="1"/>
     <col min="3" max="3" width="15.1328125" customWidth="1"/>
-    <col min="4" max="4" width="16.46484375" customWidth="1"/>
-    <col min="5" max="5" width="13.53125" customWidth="1"/>
+    <col min="4" max="5" width="16.46484375" customWidth="1"/>
+    <col min="6" max="6" width="13.53125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -885,10 +888,13 @@
         <v>45</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>17</v>
       </c>
@@ -901,8 +907,11 @@
       <c r="D2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="E2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>17</v>
       </c>
@@ -910,80 +919,30 @@
         <v>18</v>
       </c>
       <c r="C3" t="s">
-        <v>47</v>
+        <v>73</v>
       </c>
       <c r="D3" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.45">
+        <v>74</v>
+      </c>
+      <c r="E3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="B4" t="s">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="C4" t="s">
-        <v>73</v>
+        <v>48</v>
       </c>
       <c r="D4" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A5" t="s">
-        <v>17</v>
-      </c>
-      <c r="B5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C5" t="s">
-        <v>73</v>
-      </c>
-      <c r="D5" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A6" t="s">
-        <v>17</v>
-      </c>
-      <c r="B6" t="s">
-        <v>18</v>
-      </c>
-      <c r="C6" t="s">
-        <v>73</v>
-      </c>
-      <c r="D6" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A7" t="s">
-        <v>36</v>
-      </c>
-      <c r="B7" t="s">
-        <v>37</v>
-      </c>
-      <c r="C7" t="s">
         <v>48</v>
       </c>
-      <c r="D7" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A8" t="s">
-        <v>36</v>
-      </c>
-      <c r="B8" t="s">
-        <v>37</v>
-      </c>
-      <c r="C8" t="s">
-        <v>48</v>
-      </c>
-      <c r="D8" t="s">
-        <v>48</v>
+      <c r="E4">
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/data/Fate-Spreadsheet.xlsx
+++ b/data/Fate-Spreadsheet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pixel\Documents\Projects\Fate-Wiki\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{807CE838-7557-4D17-845B-C213D3F85AAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48FB44AB-56B6-46D4-A0D5-481883B29607}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="1" xr2:uid="{B05E798F-9EF6-4508-A0A4-311D06661AED}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{B05E798F-9EF6-4508-A0A4-311D06661AED}"/>
   </bookViews>
   <sheets>
     <sheet name="Servants" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="114">
   <si>
     <t>servant_id</t>
   </si>
@@ -271,6 +271,120 @@
   </si>
   <si>
     <t>quantity</t>
+  </si>
+  <si>
+    <t>S0147</t>
+  </si>
+  <si>
+    <t>Passionlip</t>
+  </si>
+  <si>
+    <t>passionlip</t>
+  </si>
+  <si>
+    <t>Alter Ego</t>
+  </si>
+  <si>
+    <t>2,4,5,5</t>
+  </si>
+  <si>
+    <t>Berserker Strength 7,Berserker Strength 9,Luck,Luck,Surveil</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>Alter Ego Class</t>
+  </si>
+  <si>
+    <t>Durga's Nails</t>
+  </si>
+  <si>
+    <t>Masochistic Nature</t>
+  </si>
+  <si>
+    <t>S0069</t>
+  </si>
+  <si>
+    <t>Euryale</t>
+  </si>
+  <si>
+    <t>euryale</t>
+  </si>
+  <si>
+    <t>Archer</t>
+  </si>
+  <si>
+    <t>Skirmisher</t>
+  </si>
+  <si>
+    <t>2,2,2,3,5</t>
+  </si>
+  <si>
+    <t>Divine Core</t>
+  </si>
+  <si>
+    <t>Divine-Core</t>
+  </si>
+  <si>
+    <t>S0070</t>
+  </si>
+  <si>
+    <t>S0071</t>
+  </si>
+  <si>
+    <t>Archer Class</t>
+  </si>
+  <si>
+    <t>Eye of the Euryale</t>
+  </si>
+  <si>
+    <t>Siren's Song</t>
+  </si>
+  <si>
+    <t>S0108</t>
+  </si>
+  <si>
+    <t>Artoria Avalon</t>
+  </si>
+  <si>
+    <t>artoria-avalon</t>
+  </si>
+  <si>
+    <t>Thrasher</t>
+  </si>
+  <si>
+    <t>2,2,3</t>
+  </si>
+  <si>
+    <t>2,3,3,4,4,5</t>
+  </si>
+  <si>
+    <t>Pilgrim's Call</t>
+  </si>
+  <si>
+    <t>Pilgrim's Respite</t>
+  </si>
+  <si>
+    <t>Pilgrim's Destiny</t>
+  </si>
+  <si>
+    <t>Pilgrims-Call</t>
+  </si>
+  <si>
+    <t>Pilgrims-Respite</t>
+  </si>
+  <si>
+    <t>Pilgrims-Destiny</t>
+  </si>
+  <si>
+    <t>Round of Avalon</t>
+  </si>
+  <si>
+    <t>Around Caliburn</t>
+  </si>
+  <si>
+    <t>Staff of Selection</t>
   </si>
 </sst>
 </file>
@@ -320,11 +434,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -659,7 +774,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E33D7ECC-1EAA-4A40-B4DA-A93E54CBC8B5}">
-  <dimension ref="A1:K6"/>
+  <dimension ref="A1:K9"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="2" max="2" width="17.1328125" customWidth="1"/>
@@ -670,7 +785,7 @@
     <col min="7" max="7" width="13.73046875" style="2" customWidth="1"/>
     <col min="8" max="8" width="11.73046875" style="2" customWidth="1"/>
     <col min="9" max="9" width="11.796875" style="2" customWidth="1"/>
-    <col min="10" max="10" width="43.06640625" style="2" customWidth="1"/>
+    <col min="10" max="10" width="48.796875" style="2" customWidth="1"/>
     <col min="11" max="11" width="12.59765625" customWidth="1"/>
   </cols>
   <sheetData>
@@ -743,25 +858,28 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>17</v>
+        <v>86</v>
       </c>
       <c r="B3" t="s">
-        <v>18</v>
+        <v>87</v>
       </c>
       <c r="C3" t="s">
-        <v>19</v>
+        <v>88</v>
       </c>
       <c r="D3" t="s">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="E3" t="s">
-        <v>8</v>
+        <v>90</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>91</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="K3" t="b">
         <v>1</v>
@@ -769,103 +887,190 @@
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="B4" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="C4" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="D4" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
-      <c r="G4" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>28</v>
+      <c r="I4" s="2" t="s">
+        <v>21</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>70</v>
+        <v>22</v>
       </c>
       <c r="K4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>29</v>
+        <v>99</v>
       </c>
       <c r="B5" t="s">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="C5" t="s">
-        <v>31</v>
+        <v>101</v>
       </c>
       <c r="D5" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="E5" t="s">
-        <v>33</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="H5" s="2">
-        <v>3</v>
+        <v>102</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>103</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="J5" s="2" t="s">
-        <v>35</v>
+        <v>104</v>
       </c>
       <c r="K5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>36</v>
+        <v>76</v>
       </c>
       <c r="B6" t="s">
-        <v>37</v>
+        <v>77</v>
       </c>
       <c r="C6" t="s">
-        <v>38</v>
+        <v>78</v>
       </c>
       <c r="D6" t="s">
-        <v>39</v>
+        <v>79</v>
       </c>
       <c r="E6" t="s">
         <v>40</v>
       </c>
       <c r="G6" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="K6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A7" t="s">
+        <v>23</v>
+      </c>
+      <c r="B7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" t="s">
+        <v>25</v>
+      </c>
+      <c r="D7" t="s">
+        <v>26</v>
+      </c>
+      <c r="E7" t="s">
+        <v>8</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="K7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A8" t="s">
+        <v>29</v>
+      </c>
+      <c r="B8" t="s">
+        <v>30</v>
+      </c>
+      <c r="C8" t="s">
+        <v>31</v>
+      </c>
+      <c r="D8" t="s">
+        <v>32</v>
+      </c>
+      <c r="E8" t="s">
+        <v>33</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H8" s="2">
+        <v>3</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="K8" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A9" t="s">
+        <v>36</v>
+      </c>
+      <c r="B9" t="s">
+        <v>37</v>
+      </c>
+      <c r="C9" t="s">
+        <v>38</v>
+      </c>
+      <c r="D9" t="s">
+        <v>39</v>
+      </c>
+      <c r="E9" t="s">
+        <v>40</v>
+      </c>
+      <c r="G9" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="H6" s="2" t="s">
+      <c r="H9" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="J6" s="2" t="s">
+      <c r="J9" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="K6" t="b">
+      <c r="K9" t="b">
         <v>1</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <ignoredErrors>
+    <ignoredError sqref="I6" numberStoredAsText="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D1BC60D8-44F3-478D-BCC0-4752624457AE}">
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="2" max="2" width="19" customWidth="1"/>
@@ -894,20 +1099,20 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C2" t="s">
-        <v>47</v>
-      </c>
-      <c r="D2" t="s">
-        <v>72</v>
-      </c>
-      <c r="E2">
+    <row r="2" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A2" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="E2" s="4">
         <v>2</v>
       </c>
     </row>
@@ -919,40 +1124,110 @@
         <v>18</v>
       </c>
       <c r="C3" t="s">
-        <v>73</v>
+        <v>47</v>
       </c>
       <c r="D3" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" t="s">
+        <v>73</v>
+      </c>
+      <c r="D4" t="s">
+        <v>74</v>
+      </c>
+      <c r="E4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A5" t="s">
+        <v>99</v>
+      </c>
+      <c r="B5" t="s">
+        <v>100</v>
+      </c>
+      <c r="C5" t="s">
+        <v>105</v>
+      </c>
+      <c r="D5" t="s">
+        <v>108</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A6" t="s">
+        <v>99</v>
+      </c>
+      <c r="B6" t="s">
+        <v>100</v>
+      </c>
+      <c r="C6" t="s">
+        <v>106</v>
+      </c>
+      <c r="D6" t="s">
+        <v>109</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A7" t="s">
+        <v>99</v>
+      </c>
+      <c r="B7" t="s">
+        <v>100</v>
+      </c>
+      <c r="C7" t="s">
+        <v>107</v>
+      </c>
+      <c r="D7" t="s">
+        <v>110</v>
+      </c>
+      <c r="E7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A8" t="s">
         <v>36</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B8" t="s">
         <v>37</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C8" t="s">
         <v>48</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D8" t="s">
         <v>48</v>
       </c>
-      <c r="E4">
+      <c r="E8">
         <v>2</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="0" orientation="portrait" horizontalDpi="0" verticalDpi="0" copies="0"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84E3BB0D-5578-4069-B1C9-C3864EB2A429}">
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="2" max="2" width="20.59765625" customWidth="1"/>
@@ -1035,10 +1310,10 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>17</v>
+        <v>86</v>
       </c>
       <c r="B5" t="s">
-        <v>18</v>
+        <v>87</v>
       </c>
       <c r="C5">
         <v>1</v>
@@ -1047,15 +1322,15 @@
         <v>1</v>
       </c>
       <c r="E5" t="s">
-        <v>58</v>
+        <v>96</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>17</v>
+        <v>94</v>
       </c>
       <c r="B6" t="s">
-        <v>18</v>
+        <v>87</v>
       </c>
       <c r="C6">
         <v>2</v>
@@ -1064,15 +1339,15 @@
         <v>0</v>
       </c>
       <c r="E6" t="s">
-        <v>59</v>
+        <v>97</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
-        <v>17</v>
+        <v>95</v>
       </c>
       <c r="B7" t="s">
-        <v>18</v>
+        <v>87</v>
       </c>
       <c r="C7">
         <v>3</v>
@@ -1081,32 +1356,32 @@
         <v>0</v>
       </c>
       <c r="E7" t="s">
-        <v>60</v>
+        <v>98</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="B8" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="C8">
         <v>1</v>
       </c>
       <c r="D8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E8" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="B9" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="C9">
         <v>2</v>
@@ -1115,15 +1390,15 @@
         <v>0</v>
       </c>
       <c r="E9" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="B10" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="C10">
         <v>3</v>
@@ -1132,15 +1407,15 @@
         <v>0</v>
       </c>
       <c r="E10" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
-        <v>29</v>
+        <v>99</v>
       </c>
       <c r="B11" t="s">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="C11">
         <v>1</v>
@@ -1149,15 +1424,15 @@
         <v>0</v>
       </c>
       <c r="E11" t="s">
-        <v>64</v>
+        <v>111</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
-        <v>29</v>
+        <v>99</v>
       </c>
       <c r="B12" t="s">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="C12">
         <v>2</v>
@@ -1166,15 +1441,15 @@
         <v>0</v>
       </c>
       <c r="E12" t="s">
-        <v>65</v>
+        <v>112</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
-        <v>29</v>
+        <v>99</v>
       </c>
       <c r="B13" t="s">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="C13">
         <v>3</v>
@@ -1183,32 +1458,32 @@
         <v>0</v>
       </c>
       <c r="E13" t="s">
-        <v>66</v>
+        <v>113</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
-        <v>36</v>
+        <v>76</v>
       </c>
       <c r="B14" t="s">
-        <v>37</v>
+        <v>77</v>
       </c>
       <c r="C14">
         <v>1</v>
       </c>
       <c r="D14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E14" t="s">
-        <v>67</v>
+        <v>83</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
-        <v>36</v>
+        <v>76</v>
       </c>
       <c r="B15" t="s">
-        <v>37</v>
+        <v>77</v>
       </c>
       <c r="C15">
         <v>2</v>
@@ -1217,15 +1492,15 @@
         <v>0</v>
       </c>
       <c r="E15" t="s">
-        <v>68</v>
+        <v>84</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
-        <v>36</v>
+        <v>76</v>
       </c>
       <c r="B16" t="s">
-        <v>37</v>
+        <v>77</v>
       </c>
       <c r="C16">
         <v>3</v>
@@ -1234,6 +1509,159 @@
         <v>0</v>
       </c>
       <c r="E16" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A17" t="s">
+        <v>23</v>
+      </c>
+      <c r="B17" t="s">
+        <v>24</v>
+      </c>
+      <c r="C17">
+        <v>1</v>
+      </c>
+      <c r="D17" t="b">
+        <v>0</v>
+      </c>
+      <c r="E17" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A18" t="s">
+        <v>23</v>
+      </c>
+      <c r="B18" t="s">
+        <v>24</v>
+      </c>
+      <c r="C18">
+        <v>2</v>
+      </c>
+      <c r="D18" t="b">
+        <v>0</v>
+      </c>
+      <c r="E18" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A19" t="s">
+        <v>23</v>
+      </c>
+      <c r="B19" t="s">
+        <v>24</v>
+      </c>
+      <c r="C19">
+        <v>3</v>
+      </c>
+      <c r="D19" t="b">
+        <v>0</v>
+      </c>
+      <c r="E19" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A20" t="s">
+        <v>29</v>
+      </c>
+      <c r="B20" t="s">
+        <v>30</v>
+      </c>
+      <c r="C20">
+        <v>1</v>
+      </c>
+      <c r="D20" t="b">
+        <v>0</v>
+      </c>
+      <c r="E20" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A21" t="s">
+        <v>29</v>
+      </c>
+      <c r="B21" t="s">
+        <v>30</v>
+      </c>
+      <c r="C21">
+        <v>2</v>
+      </c>
+      <c r="D21" t="b">
+        <v>0</v>
+      </c>
+      <c r="E21" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A22" t="s">
+        <v>29</v>
+      </c>
+      <c r="B22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C22">
+        <v>3</v>
+      </c>
+      <c r="D22" t="b">
+        <v>0</v>
+      </c>
+      <c r="E22" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A23" t="s">
+        <v>36</v>
+      </c>
+      <c r="B23" t="s">
+        <v>37</v>
+      </c>
+      <c r="C23">
+        <v>1</v>
+      </c>
+      <c r="D23" t="b">
+        <v>0</v>
+      </c>
+      <c r="E23" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A24" t="s">
+        <v>36</v>
+      </c>
+      <c r="B24" t="s">
+        <v>37</v>
+      </c>
+      <c r="C24">
+        <v>2</v>
+      </c>
+      <c r="D24" t="b">
+        <v>0</v>
+      </c>
+      <c r="E24" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A25" t="s">
+        <v>36</v>
+      </c>
+      <c r="B25" t="s">
+        <v>37</v>
+      </c>
+      <c r="C25">
+        <v>3</v>
+      </c>
+      <c r="D25" t="b">
+        <v>0</v>
+      </c>
+      <c r="E25" t="s">
         <v>69</v>
       </c>
     </row>

--- a/data/Fate-Spreadsheet.xlsx
+++ b/data/Fate-Spreadsheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pixel\Documents\Projects\Fate-Wiki\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48FB44AB-56B6-46D4-A0D5-481883B29607}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B852EF1C-3539-407D-ACE6-F57265693E33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{B05E798F-9EF6-4508-A0A4-311D06661AED}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="112">
   <si>
     <t>servant_id</t>
   </si>
@@ -325,12 +325,6 @@
   </si>
   <si>
     <t>Divine-Core</t>
-  </si>
-  <si>
-    <t>S0070</t>
-  </si>
-  <si>
-    <t>S0071</t>
   </si>
   <si>
     <t>Archer Class</t>
@@ -434,12 +428,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -843,8 +836,8 @@
       <c r="G2" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="H2" s="2">
-        <v>3</v>
+      <c r="H2" s="2" t="s">
+        <v>82</v>
       </c>
       <c r="I2" s="2" t="s">
         <v>15</v>
@@ -913,25 +906,25 @@
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
+        <v>97</v>
+      </c>
+      <c r="B5" t="s">
+        <v>98</v>
+      </c>
+      <c r="C5" t="s">
         <v>99</v>
-      </c>
-      <c r="B5" t="s">
-        <v>100</v>
-      </c>
-      <c r="C5" t="s">
-        <v>101</v>
       </c>
       <c r="D5" t="s">
         <v>20</v>
       </c>
       <c r="E5" t="s">
+        <v>100</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="I5" s="2" t="s">
         <v>102</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>104</v>
       </c>
       <c r="K5" t="b">
         <v>1</v>
@@ -1017,8 +1010,8 @@
       <c r="G8" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="H8" s="2">
-        <v>3</v>
+      <c r="H8" s="2" t="s">
+        <v>82</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>34</v>
@@ -1063,7 +1056,7 @@
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="I6" numberStoredAsText="1"/>
+    <ignoredError sqref="I6 H2 H8" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1099,20 +1092,20 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="4" t="s">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A2" t="s">
         <v>86</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" t="s">
         <v>87</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" t="s">
         <v>92</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" t="s">
         <v>93</v>
       </c>
-      <c r="E2" s="4">
+      <c r="E2">
         <v>2</v>
       </c>
     </row>
@@ -1152,16 +1145,16 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B5" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C5" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D5" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E5">
         <v>1</v>
@@ -1169,16 +1162,16 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B6" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C6" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D6" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -1186,16 +1179,16 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B7" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C7" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D7" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E7">
         <v>1</v>
@@ -1322,12 +1315,12 @@
         <v>1</v>
       </c>
       <c r="E5" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="B6" t="s">
         <v>87</v>
@@ -1339,12 +1332,12 @@
         <v>0</v>
       </c>
       <c r="E6" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="B7" t="s">
         <v>87</v>
@@ -1356,7 +1349,7 @@
         <v>0</v>
       </c>
       <c r="E7" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.45">
@@ -1412,10 +1405,10 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B11" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C11">
         <v>1</v>
@@ -1424,15 +1417,15 @@
         <v>0</v>
       </c>
       <c r="E11" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B12" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C12">
         <v>2</v>
@@ -1441,15 +1434,15 @@
         <v>0</v>
       </c>
       <c r="E12" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B13" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C13">
         <v>3</v>
@@ -1458,7 +1451,7 @@
         <v>0</v>
       </c>
       <c r="E13" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.45">

--- a/data/Fate-Spreadsheet.xlsx
+++ b/data/Fate-Spreadsheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pixel\Documents\Projects\Fate-Wiki\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B852EF1C-3539-407D-ACE6-F57265693E33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33239780-26C1-4CA1-BB72-800FD4D65CD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{B05E798F-9EF6-4508-A0A4-311D06661AED}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="590" uniqueCount="265">
   <si>
     <t>servant_id</t>
   </si>
@@ -379,6 +379,465 @@
   </si>
   <si>
     <t>Staff of Selection</t>
+  </si>
+  <si>
+    <t>S0002</t>
+  </si>
+  <si>
+    <t>S0003</t>
+  </si>
+  <si>
+    <t>S0004</t>
+  </si>
+  <si>
+    <t>S0005</t>
+  </si>
+  <si>
+    <t>S0006</t>
+  </si>
+  <si>
+    <t>S0007</t>
+  </si>
+  <si>
+    <t>S0008</t>
+  </si>
+  <si>
+    <t>S0009</t>
+  </si>
+  <si>
+    <t>S0010</t>
+  </si>
+  <si>
+    <t>S0011</t>
+  </si>
+  <si>
+    <t>S0012</t>
+  </si>
+  <si>
+    <t>S0013</t>
+  </si>
+  <si>
+    <t>S0014</t>
+  </si>
+  <si>
+    <t>S0015</t>
+  </si>
+  <si>
+    <t>S0016</t>
+  </si>
+  <si>
+    <t>S0017</t>
+  </si>
+  <si>
+    <t>S0018</t>
+  </si>
+  <si>
+    <t>S0019</t>
+  </si>
+  <si>
+    <t>S0020</t>
+  </si>
+  <si>
+    <t>S0021</t>
+  </si>
+  <si>
+    <t>S0022</t>
+  </si>
+  <si>
+    <t>S0023</t>
+  </si>
+  <si>
+    <t>Nero Claudius</t>
+  </si>
+  <si>
+    <t>nero-claudius</t>
+  </si>
+  <si>
+    <t>Mordred</t>
+  </si>
+  <si>
+    <t>Altera</t>
+  </si>
+  <si>
+    <t>Gawain</t>
+  </si>
+  <si>
+    <t>Bedivere</t>
+  </si>
+  <si>
+    <t>Okita Souji</t>
+  </si>
+  <si>
+    <t>Sigurd</t>
+  </si>
+  <si>
+    <t>Siegfried</t>
+  </si>
+  <si>
+    <t>Chevalier d'Eon</t>
+  </si>
+  <si>
+    <t>Senji Muramasa</t>
+  </si>
+  <si>
+    <t>Miyamoto Musashi</t>
+  </si>
+  <si>
+    <t>Charlemagne</t>
+  </si>
+  <si>
+    <t>Jacques de Molay</t>
+  </si>
+  <si>
+    <t>Arthur Pendragon</t>
+  </si>
+  <si>
+    <t>Jason</t>
+  </si>
+  <si>
+    <t>Barghest</t>
+  </si>
+  <si>
+    <t>Saito Hajime</t>
+  </si>
+  <si>
+    <t>Dioscuri</t>
+  </si>
+  <si>
+    <t>Lakshmibai</t>
+  </si>
+  <si>
+    <t>Suzuka Gozen</t>
+  </si>
+  <si>
+    <t>mordred</t>
+  </si>
+  <si>
+    <t>altera</t>
+  </si>
+  <si>
+    <t>gawain</t>
+  </si>
+  <si>
+    <t>bedivere</t>
+  </si>
+  <si>
+    <t>sigurd</t>
+  </si>
+  <si>
+    <t>siegfried</t>
+  </si>
+  <si>
+    <t>charlemagne</t>
+  </si>
+  <si>
+    <t>jason</t>
+  </si>
+  <si>
+    <t>barghest</t>
+  </si>
+  <si>
+    <t>dioscuri</t>
+  </si>
+  <si>
+    <t>lakshmibai</t>
+  </si>
+  <si>
+    <t>okita-souji</t>
+  </si>
+  <si>
+    <t>senji-muramasa</t>
+  </si>
+  <si>
+    <t>miyamoto-musashi</t>
+  </si>
+  <si>
+    <t>arthur-pendragon</t>
+  </si>
+  <si>
+    <t>saito-hajime</t>
+  </si>
+  <si>
+    <t>suzuka-gozen</t>
+  </si>
+  <si>
+    <t>chevalier-deon</t>
+  </si>
+  <si>
+    <t>artoria-pendragon-alter</t>
+  </si>
+  <si>
+    <t>jacques-de-molay</t>
+  </si>
+  <si>
+    <t>okita-souji-alter</t>
+  </si>
+  <si>
+    <t>2,3,4,5,5</t>
+  </si>
+  <si>
+    <t>2,3,4,5</t>
+  </si>
+  <si>
+    <t>Luck</t>
+  </si>
+  <si>
+    <t>2,3,4,5,5,5</t>
+  </si>
+  <si>
+    <t>Luck,Luck,Surveil</t>
+  </si>
+  <si>
+    <t>2,3,3,5,5</t>
+  </si>
+  <si>
+    <t>Surveil,Luck</t>
+  </si>
+  <si>
+    <t>2,2,3,4,5</t>
+  </si>
+  <si>
+    <t>Luck,Preparation</t>
+  </si>
+  <si>
+    <t>4,4</t>
+  </si>
+  <si>
+    <t>2,3,3,4,5,5</t>
+  </si>
+  <si>
+    <t>Luck,Surveil,Surveil</t>
+  </si>
+  <si>
+    <t>3,4,4,5,5</t>
+  </si>
+  <si>
+    <t>Luck,Surveil</t>
+  </si>
+  <si>
+    <t>3,3,4</t>
+  </si>
+  <si>
+    <t>3,4,4</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>3,3,4,5</t>
+  </si>
+  <si>
+    <t>2,3,3,4</t>
+  </si>
+  <si>
+    <t>Luck,Preparation,Preparation</t>
+  </si>
+  <si>
+    <t>2,3,5,5</t>
+  </si>
+  <si>
+    <t>2,4,4</t>
+  </si>
+  <si>
+    <t>Luck,Luck</t>
+  </si>
+  <si>
+    <t>3,3,4,4</t>
+  </si>
+  <si>
+    <t>2,2</t>
+  </si>
+  <si>
+    <t>Luck,Surveil,Preparation</t>
+  </si>
+  <si>
+    <t>2,3,4,4</t>
+  </si>
+  <si>
+    <t>3,4,4,5</t>
+  </si>
+  <si>
+    <t>2,3,3,5</t>
+  </si>
+  <si>
+    <t>2,3,3,4,5</t>
+  </si>
+  <si>
+    <t>Luck,Avenger Class</t>
+  </si>
+  <si>
+    <t>2,2,2</t>
+  </si>
+  <si>
+    <t>Weak Constitution</t>
+  </si>
+  <si>
+    <t>Weak-Constitution</t>
+  </si>
+  <si>
+    <t>Astrapte Argo</t>
+  </si>
+  <si>
+    <t>Astrapte-Argo</t>
+  </si>
+  <si>
+    <t>Misfortune</t>
+  </si>
+  <si>
+    <t>Aestus Domus Aurea</t>
+  </si>
+  <si>
+    <t>Aestus Estus</t>
+  </si>
+  <si>
+    <t>Emperor's Prerogative</t>
+  </si>
+  <si>
+    <t>Clarent</t>
+  </si>
+  <si>
+    <t>Helm of Hidden Infidelity</t>
+  </si>
+  <si>
+    <t>Teardrop Photon Ray</t>
+  </si>
+  <si>
+    <t>Photon Ray</t>
+  </si>
+  <si>
+    <t>Excalibur Galatine</t>
+  </si>
+  <si>
+    <t>Numeral of the Saint</t>
+  </si>
+  <si>
+    <t>Airgetlam</t>
+  </si>
+  <si>
+    <t>Oath of Protection</t>
+  </si>
+  <si>
+    <t>Flag of Sincerity</t>
+  </si>
+  <si>
+    <t>Mumyou Sandan-Zuki</t>
+  </si>
+  <si>
+    <t>Coat of Oaths</t>
+  </si>
+  <si>
+    <t>Gram II</t>
+  </si>
+  <si>
+    <t>Bolverk Gram</t>
+  </si>
+  <si>
+    <t>Ridill &amp; Hrotti</t>
+  </si>
+  <si>
+    <t>Balmung</t>
+  </si>
+  <si>
+    <t>Armour of Fafnir</t>
+  </si>
+  <si>
+    <t>Tarnkappe</t>
+  </si>
+  <si>
+    <t>Self-Suggestion</t>
+  </si>
+  <si>
+    <t>Sword Dance</t>
+  </si>
+  <si>
+    <t>Fleur de Lys</t>
+  </si>
+  <si>
+    <t>Tsumukari Muramasa</t>
+  </si>
+  <si>
+    <t>Imperfect Edge</t>
+  </si>
+  <si>
+    <t>6 Realms, 5 Rings</t>
+  </si>
+  <si>
+    <t>Niten Ichiryu</t>
+  </si>
+  <si>
+    <t>Blackening Curse</t>
+  </si>
+  <si>
+    <t>Excalibur Morgan</t>
+  </si>
+  <si>
+    <t>Charles Patricius</t>
+  </si>
+  <si>
+    <t>Joyeuse Ordre</t>
+  </si>
+  <si>
+    <t>Pilgrim's Reward</t>
+  </si>
+  <si>
+    <t>Mother of Goats</t>
+  </si>
+  <si>
+    <t>The Goat's Invitation</t>
+  </si>
+  <si>
+    <t>Excalibur Proto</t>
+  </si>
+  <si>
+    <t>Heracles</t>
+  </si>
+  <si>
+    <t>Atalante</t>
+  </si>
+  <si>
+    <t>Medea</t>
+  </si>
+  <si>
+    <t>Black Dog Galatine</t>
+  </si>
+  <si>
+    <t>Sun Devourer</t>
+  </si>
+  <si>
+    <t>Demon Chains</t>
+  </si>
+  <si>
+    <t>Formlessness</t>
+  </si>
+  <si>
+    <t>Twin Divinity</t>
+  </si>
+  <si>
+    <t>Dioscures Tyndaridae</t>
+  </si>
+  <si>
+    <t>Gift of Mortality</t>
+  </si>
+  <si>
+    <t>Nahi Doongi</t>
+  </si>
+  <si>
+    <t>Queen of Resistance</t>
+  </si>
+  <si>
+    <t>Boundless Potential</t>
+  </si>
+  <si>
+    <t>Rengoku</t>
+  </si>
+  <si>
+    <t>Trichiliocosm</t>
+  </si>
+  <si>
+    <t>Demonic Sun-Shower</t>
+  </si>
+  <si>
+    <t>Wise Fox</t>
   </si>
 </sst>
 </file>
@@ -428,11 +887,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -767,7 +1227,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E33D7ECC-1EAA-4A40-B4DA-A93E54CBC8B5}">
-  <dimension ref="A1:K9"/>
+  <dimension ref="A1:K31"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="2" max="2" width="17.1328125" customWidth="1"/>
@@ -851,112 +1311,121 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>86</v>
+        <v>112</v>
       </c>
       <c r="B3" t="s">
-        <v>87</v>
+        <v>134</v>
       </c>
       <c r="C3" t="s">
-        <v>88</v>
+        <v>135</v>
       </c>
       <c r="D3" t="s">
-        <v>89</v>
+        <v>7</v>
       </c>
       <c r="E3" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="G3" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="I3" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="H3" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>42</v>
+      <c r="J3" s="2" t="s">
+        <v>178</v>
       </c>
       <c r="K3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
-        <v>17</v>
+        <v>113</v>
       </c>
       <c r="B4" t="s">
-        <v>18</v>
+        <v>136</v>
       </c>
       <c r="C4" t="s">
-        <v>19</v>
+        <v>155</v>
       </c>
       <c r="D4" t="s">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
-      <c r="I4" s="2" t="s">
-        <v>21</v>
+      <c r="G4" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>101</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>22</v>
+        <v>180</v>
       </c>
       <c r="K4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>97</v>
+        <v>114</v>
       </c>
       <c r="B5" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="C5" t="s">
-        <v>99</v>
+        <v>156</v>
       </c>
       <c r="D5" t="s">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="E5" t="s">
-        <v>100</v>
+        <v>8</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>176</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>102</v>
+        <v>181</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>182</v>
       </c>
       <c r="K5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>76</v>
+        <v>115</v>
       </c>
       <c r="B6" t="s">
-        <v>77</v>
+        <v>138</v>
       </c>
       <c r="C6" t="s">
-        <v>78</v>
+        <v>157</v>
       </c>
       <c r="D6" t="s">
-        <v>79</v>
+        <v>7</v>
       </c>
       <c r="E6" t="s">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>80</v>
+        <v>183</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>15</v>
+        <v>177</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>82</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>81</v>
+        <v>184</v>
       </c>
       <c r="K6" t="b">
         <v>0</v>
@@ -964,28 +1433,31 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
-        <v>23</v>
+        <v>116</v>
       </c>
       <c r="B7" t="s">
-        <v>24</v>
+        <v>139</v>
       </c>
       <c r="C7" t="s">
-        <v>25</v>
+        <v>158</v>
       </c>
       <c r="D7" t="s">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>27</v>
+        <v>185</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>28</v>
+        <v>186</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>82</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>70</v>
+        <v>187</v>
       </c>
       <c r="K7" t="b">
         <v>0</v>
@@ -993,62 +1465,736 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
-        <v>29</v>
+        <v>117</v>
       </c>
       <c r="B8" t="s">
-        <v>30</v>
+        <v>140</v>
       </c>
       <c r="C8" t="s">
-        <v>31</v>
+        <v>166</v>
       </c>
       <c r="D8" t="s">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="E8" t="s">
-        <v>33</v>
+        <v>90</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>15</v>
+        <v>177</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>34</v>
+        <v>188</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>35</v>
+        <v>189</v>
       </c>
       <c r="K8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
+        <v>118</v>
+      </c>
+      <c r="B9" t="s">
+        <v>141</v>
+      </c>
+      <c r="C9" t="s">
+        <v>159</v>
+      </c>
+      <c r="D9" t="s">
+        <v>7</v>
+      </c>
+      <c r="E9" t="s">
+        <v>90</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="K9" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A10" t="s">
+        <v>119</v>
+      </c>
+      <c r="B10" t="s">
+        <v>142</v>
+      </c>
+      <c r="C10" t="s">
+        <v>160</v>
+      </c>
+      <c r="D10" t="s">
+        <v>7</v>
+      </c>
+      <c r="E10" t="s">
+        <v>8</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="K10" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A11" t="s">
+        <v>120</v>
+      </c>
+      <c r="B11" t="s">
+        <v>143</v>
+      </c>
+      <c r="C11" t="s">
+        <v>172</v>
+      </c>
+      <c r="D11" t="s">
+        <v>7</v>
+      </c>
+      <c r="E11" t="s">
+        <v>90</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="K11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A12" t="s">
+        <v>121</v>
+      </c>
+      <c r="B12" t="s">
+        <v>144</v>
+      </c>
+      <c r="C12" t="s">
+        <v>167</v>
+      </c>
+      <c r="D12" t="s">
+        <v>79</v>
+      </c>
+      <c r="E12" t="s">
+        <v>90</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="K12" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A13" t="s">
+        <v>122</v>
+      </c>
+      <c r="B13" t="s">
+        <v>145</v>
+      </c>
+      <c r="C13" t="s">
+        <v>168</v>
+      </c>
+      <c r="D13" t="s">
+        <v>7</v>
+      </c>
+      <c r="E13" t="s">
+        <v>100</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="K13" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A14" t="s">
+        <v>123</v>
+      </c>
+      <c r="B14" t="s">
+        <v>5</v>
+      </c>
+      <c r="C14" t="s">
+        <v>173</v>
+      </c>
+      <c r="D14" t="s">
+        <v>7</v>
+      </c>
+      <c r="E14" t="s">
+        <v>8</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="K14" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A15" t="s">
+        <v>124</v>
+      </c>
+      <c r="B15" t="s">
+        <v>146</v>
+      </c>
+      <c r="C15" t="s">
+        <v>161</v>
+      </c>
+      <c r="D15" t="s">
+        <v>7</v>
+      </c>
+      <c r="E15" t="s">
+        <v>90</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="K15" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A16" t="s">
+        <v>125</v>
+      </c>
+      <c r="B16" t="s">
+        <v>147</v>
+      </c>
+      <c r="C16" t="s">
+        <v>174</v>
+      </c>
+      <c r="D16" t="s">
+        <v>7</v>
+      </c>
+      <c r="E16" t="s">
+        <v>8</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="K16" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A17" t="s">
+        <v>126</v>
+      </c>
+      <c r="B17" t="s">
+        <v>148</v>
+      </c>
+      <c r="C17" t="s">
+        <v>169</v>
+      </c>
+      <c r="D17" t="s">
+        <v>7</v>
+      </c>
+      <c r="E17" t="s">
+        <v>8</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I17" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="J17" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="K17" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A18" t="s">
+        <v>127</v>
+      </c>
+      <c r="B18" t="s">
+        <v>149</v>
+      </c>
+      <c r="C18" t="s">
+        <v>162</v>
+      </c>
+      <c r="D18" t="s">
+        <v>7</v>
+      </c>
+      <c r="E18" t="s">
+        <v>90</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="K18" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A19" t="s">
+        <v>128</v>
+      </c>
+      <c r="B19" t="s">
+        <v>150</v>
+      </c>
+      <c r="C19" t="s">
+        <v>163</v>
+      </c>
+      <c r="D19" t="s">
+        <v>7</v>
+      </c>
+      <c r="E19" t="s">
+        <v>90</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="K19" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A20" t="s">
+        <v>129</v>
+      </c>
+      <c r="B20" t="s">
+        <v>151</v>
+      </c>
+      <c r="C20" t="s">
+        <v>170</v>
+      </c>
+      <c r="D20" t="s">
+        <v>7</v>
+      </c>
+      <c r="E20" t="s">
+        <v>90</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="J20" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="K20" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A21" t="s">
+        <v>130</v>
+      </c>
+      <c r="B21" t="s">
+        <v>152</v>
+      </c>
+      <c r="C21" t="s">
+        <v>164</v>
+      </c>
+      <c r="D21" t="s">
+        <v>7</v>
+      </c>
+      <c r="E21" t="s">
+        <v>90</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="J21" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="K21" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A22" t="s">
+        <v>131</v>
+      </c>
+      <c r="B22" t="s">
+        <v>153</v>
+      </c>
+      <c r="C22" t="s">
+        <v>165</v>
+      </c>
+      <c r="D22" t="s">
+        <v>7</v>
+      </c>
+      <c r="E22" t="s">
+        <v>40</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="J22" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="K22" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A23" t="s">
+        <v>132</v>
+      </c>
+      <c r="B23" t="s">
+        <v>140</v>
+      </c>
+      <c r="C23" t="s">
+        <v>175</v>
+      </c>
+      <c r="D23" t="s">
+        <v>79</v>
+      </c>
+      <c r="E23" t="s">
+        <v>90</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="I23" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="J23" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="K23" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A24" t="s">
+        <v>133</v>
+      </c>
+      <c r="B24" t="s">
+        <v>154</v>
+      </c>
+      <c r="C24" t="s">
+        <v>171</v>
+      </c>
+      <c r="D24" t="s">
+        <v>7</v>
+      </c>
+      <c r="E24" t="s">
+        <v>90</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="I24" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="J24" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K24" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A25" t="s">
+        <v>86</v>
+      </c>
+      <c r="B25" t="s">
+        <v>87</v>
+      </c>
+      <c r="C25" t="s">
+        <v>88</v>
+      </c>
+      <c r="D25" t="s">
+        <v>89</v>
+      </c>
+      <c r="E25" t="s">
+        <v>90</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="I25" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="K25" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A26" t="s">
+        <v>17</v>
+      </c>
+      <c r="B26" t="s">
+        <v>18</v>
+      </c>
+      <c r="C26" t="s">
+        <v>19</v>
+      </c>
+      <c r="D26" t="s">
+        <v>20</v>
+      </c>
+      <c r="E26" t="s">
+        <v>8</v>
+      </c>
+      <c r="I26" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="J26" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="K26" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A27" t="s">
+        <v>97</v>
+      </c>
+      <c r="B27" t="s">
+        <v>98</v>
+      </c>
+      <c r="C27" t="s">
+        <v>99</v>
+      </c>
+      <c r="D27" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" t="s">
+        <v>100</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="I27" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="K27" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A28" t="s">
+        <v>76</v>
+      </c>
+      <c r="B28" t="s">
+        <v>77</v>
+      </c>
+      <c r="C28" t="s">
+        <v>78</v>
+      </c>
+      <c r="D28" t="s">
+        <v>79</v>
+      </c>
+      <c r="E28" t="s">
+        <v>40</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I28" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="J28" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="K28" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A29" t="s">
+        <v>23</v>
+      </c>
+      <c r="B29" t="s">
+        <v>24</v>
+      </c>
+      <c r="C29" t="s">
+        <v>25</v>
+      </c>
+      <c r="D29" t="s">
+        <v>26</v>
+      </c>
+      <c r="E29" t="s">
+        <v>8</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J29" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="K29" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A30" t="s">
+        <v>29</v>
+      </c>
+      <c r="B30" t="s">
+        <v>30</v>
+      </c>
+      <c r="C30" t="s">
+        <v>31</v>
+      </c>
+      <c r="D30" t="s">
+        <v>32</v>
+      </c>
+      <c r="E30" t="s">
+        <v>33</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="I30" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="J30" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="K30" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A31" t="s">
         <v>36</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B31" t="s">
         <v>37</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C31" t="s">
         <v>38</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D31" t="s">
         <v>39</v>
       </c>
-      <c r="E9" t="s">
+      <c r="E31" t="s">
         <v>40</v>
       </c>
-      <c r="G9" s="2" t="s">
+      <c r="G31" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="H9" s="2" t="s">
+      <c r="H31" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="J9" s="2" t="s">
+      <c r="J31" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="K9" t="b">
+      <c r="K31" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1056,14 +2202,14 @@
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="I6 H2 H8" numberStoredAsText="1"/>
+    <ignoredError sqref="H2 I28 H30 I6:I7 I10 I12 H14 I18 I22 I24" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D1BC60D8-44F3-478D-BCC0-4752624457AE}">
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="2" max="2" width="19" customWidth="1"/>
@@ -1092,122 +2238,173 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A2" t="s">
-        <v>86</v>
-      </c>
-      <c r="B2" t="s">
-        <v>87</v>
-      </c>
-      <c r="C2" t="s">
-        <v>92</v>
-      </c>
-      <c r="D2" t="s">
-        <v>93</v>
-      </c>
-      <c r="E2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A3" t="s">
-        <v>17</v>
-      </c>
-      <c r="B3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C3" t="s">
-        <v>47</v>
-      </c>
-      <c r="D3" t="s">
-        <v>72</v>
-      </c>
-      <c r="E3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A4" t="s">
-        <v>17</v>
-      </c>
-      <c r="B4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C4" t="s">
-        <v>73</v>
-      </c>
-      <c r="D4" t="s">
-        <v>74</v>
-      </c>
-      <c r="E4">
-        <v>3</v>
+    <row r="2" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A2" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="E2" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A3" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="E3" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A4" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="E4" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="B5" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="C5" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="D5" t="s">
-        <v>106</v>
+        <v>93</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>97</v>
+        <v>17</v>
       </c>
       <c r="B6" t="s">
-        <v>98</v>
+        <v>18</v>
       </c>
       <c r="C6" t="s">
-        <v>104</v>
+        <v>47</v>
       </c>
       <c r="D6" t="s">
-        <v>107</v>
+        <v>72</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
-        <v>97</v>
+        <v>17</v>
       </c>
       <c r="B7" t="s">
-        <v>98</v>
+        <v>18</v>
       </c>
       <c r="C7" t="s">
-        <v>105</v>
+        <v>73</v>
       </c>
       <c r="D7" t="s">
-        <v>108</v>
+        <v>74</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
+        <v>97</v>
+      </c>
+      <c r="B8" t="s">
+        <v>98</v>
+      </c>
+      <c r="C8" t="s">
+        <v>103</v>
+      </c>
+      <c r="D8" t="s">
+        <v>106</v>
+      </c>
+      <c r="E8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A9" t="s">
+        <v>97</v>
+      </c>
+      <c r="B9" t="s">
+        <v>98</v>
+      </c>
+      <c r="C9" t="s">
+        <v>104</v>
+      </c>
+      <c r="D9" t="s">
+        <v>107</v>
+      </c>
+      <c r="E9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A10" t="s">
+        <v>97</v>
+      </c>
+      <c r="B10" t="s">
+        <v>98</v>
+      </c>
+      <c r="C10" t="s">
+        <v>105</v>
+      </c>
+      <c r="D10" t="s">
+        <v>108</v>
+      </c>
+      <c r="E10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A11" t="s">
         <v>36</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B11" t="s">
         <v>37</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C11" t="s">
         <v>48</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D11" t="s">
         <v>48</v>
       </c>
-      <c r="E8">
+      <c r="E11">
         <v>2</v>
       </c>
     </row>
@@ -1220,13 +2417,13 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84E3BB0D-5578-4069-B1C9-C3864EB2A429}">
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:F91"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="2" max="2" width="20.59765625" customWidth="1"/>
     <col min="3" max="3" width="12.73046875" customWidth="1"/>
     <col min="4" max="4" width="17.06640625" customWidth="1"/>
-    <col min="5" max="5" width="18.1328125" customWidth="1"/>
+    <col min="5" max="5" width="21.59765625" customWidth="1"/>
     <col min="6" max="6" width="15.73046875" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1303,27 +2500,27 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>86</v>
+        <v>112</v>
       </c>
       <c r="B5" t="s">
-        <v>87</v>
+        <v>134</v>
       </c>
       <c r="C5">
         <v>1</v>
       </c>
       <c r="D5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5" t="s">
-        <v>94</v>
+        <v>213</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>86</v>
+        <v>112</v>
       </c>
       <c r="B6" t="s">
-        <v>87</v>
+        <v>134</v>
       </c>
       <c r="C6">
         <v>2</v>
@@ -1332,15 +2529,15 @@
         <v>0</v>
       </c>
       <c r="E6" t="s">
-        <v>95</v>
+        <v>214</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
-        <v>86</v>
+        <v>112</v>
       </c>
       <c r="B7" t="s">
-        <v>87</v>
+        <v>134</v>
       </c>
       <c r="C7">
         <v>3</v>
@@ -1349,15 +2546,15 @@
         <v>0</v>
       </c>
       <c r="E7" t="s">
-        <v>96</v>
+        <v>215</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
-        <v>17</v>
+        <v>113</v>
       </c>
       <c r="B8" t="s">
-        <v>18</v>
+        <v>136</v>
       </c>
       <c r="C8">
         <v>1</v>
@@ -1366,15 +2563,15 @@
         <v>1</v>
       </c>
       <c r="E8" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
-        <v>17</v>
+        <v>113</v>
       </c>
       <c r="B9" t="s">
-        <v>18</v>
+        <v>136</v>
       </c>
       <c r="C9">
         <v>2</v>
@@ -1383,15 +2580,15 @@
         <v>0</v>
       </c>
       <c r="E9" t="s">
-        <v>59</v>
+        <v>216</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
-        <v>17</v>
+        <v>113</v>
       </c>
       <c r="B10" t="s">
-        <v>18</v>
+        <v>136</v>
       </c>
       <c r="C10">
         <v>3</v>
@@ -1400,32 +2597,32 @@
         <v>0</v>
       </c>
       <c r="E10" t="s">
-        <v>60</v>
+        <v>217</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
-        <v>97</v>
+        <v>114</v>
       </c>
       <c r="B11" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="C11">
         <v>1</v>
       </c>
       <c r="D11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E11" t="s">
-        <v>109</v>
+        <v>53</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
-        <v>97</v>
+        <v>114</v>
       </c>
       <c r="B12" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="C12">
         <v>2</v>
@@ -1434,15 +2631,15 @@
         <v>0</v>
       </c>
       <c r="E12" t="s">
-        <v>110</v>
+        <v>218</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
-        <v>97</v>
+        <v>114</v>
       </c>
       <c r="B13" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="C13">
         <v>3</v>
@@ -1451,15 +2648,15 @@
         <v>0</v>
       </c>
       <c r="E13" t="s">
-        <v>111</v>
+        <v>219</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
-        <v>76</v>
+        <v>115</v>
       </c>
       <c r="B14" t="s">
-        <v>77</v>
+        <v>138</v>
       </c>
       <c r="C14">
         <v>1</v>
@@ -1468,15 +2665,15 @@
         <v>1</v>
       </c>
       <c r="E14" t="s">
-        <v>83</v>
+        <v>53</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
-        <v>76</v>
+        <v>115</v>
       </c>
       <c r="B15" t="s">
-        <v>77</v>
+        <v>138</v>
       </c>
       <c r="C15">
         <v>2</v>
@@ -1485,15 +2682,15 @@
         <v>0</v>
       </c>
       <c r="E15" t="s">
-        <v>84</v>
+        <v>220</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
-        <v>76</v>
+        <v>115</v>
       </c>
       <c r="B16" t="s">
-        <v>77</v>
+        <v>138</v>
       </c>
       <c r="C16">
         <v>3</v>
@@ -1502,32 +2699,32 @@
         <v>0</v>
       </c>
       <c r="E16" t="s">
-        <v>85</v>
+        <v>221</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
-        <v>23</v>
+        <v>116</v>
       </c>
       <c r="B17" t="s">
-        <v>24</v>
+        <v>139</v>
       </c>
       <c r="C17">
         <v>1</v>
       </c>
       <c r="D17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E17" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
-        <v>23</v>
+        <v>116</v>
       </c>
       <c r="B18" t="s">
-        <v>24</v>
+        <v>139</v>
       </c>
       <c r="C18">
         <v>2</v>
@@ -1536,15 +2733,15 @@
         <v>0</v>
       </c>
       <c r="E18" t="s">
-        <v>62</v>
+        <v>222</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
-        <v>23</v>
+        <v>116</v>
       </c>
       <c r="B19" t="s">
-        <v>24</v>
+        <v>139</v>
       </c>
       <c r="C19">
         <v>3</v>
@@ -1553,15 +2750,15 @@
         <v>0</v>
       </c>
       <c r="E19" t="s">
-        <v>63</v>
+        <v>223</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
-        <v>29</v>
+        <v>117</v>
       </c>
       <c r="B20" t="s">
-        <v>30</v>
+        <v>140</v>
       </c>
       <c r="C20">
         <v>1</v>
@@ -1570,15 +2767,15 @@
         <v>0</v>
       </c>
       <c r="E20" t="s">
-        <v>64</v>
+        <v>224</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
-        <v>29</v>
+        <v>117</v>
       </c>
       <c r="B21" t="s">
-        <v>30</v>
+        <v>140</v>
       </c>
       <c r="C21">
         <v>2</v>
@@ -1587,15 +2784,15 @@
         <v>0</v>
       </c>
       <c r="E21" t="s">
-        <v>65</v>
+        <v>225</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
-        <v>29</v>
+        <v>117</v>
       </c>
       <c r="B22" t="s">
-        <v>30</v>
+        <v>140</v>
       </c>
       <c r="C22">
         <v>3</v>
@@ -1604,15 +2801,15 @@
         <v>0</v>
       </c>
       <c r="E22" t="s">
-        <v>66</v>
+        <v>226</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
-        <v>36</v>
+        <v>118</v>
       </c>
       <c r="B23" t="s">
-        <v>37</v>
+        <v>141</v>
       </c>
       <c r="C23">
         <v>1</v>
@@ -1621,15 +2818,15 @@
         <v>0</v>
       </c>
       <c r="E23" t="s">
-        <v>67</v>
+        <v>227</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
-        <v>36</v>
+        <v>118</v>
       </c>
       <c r="B24" t="s">
-        <v>37</v>
+        <v>141</v>
       </c>
       <c r="C24">
         <v>2</v>
@@ -1638,15 +2835,15 @@
         <v>0</v>
       </c>
       <c r="E24" t="s">
-        <v>68</v>
+        <v>228</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
-        <v>36</v>
+        <v>118</v>
       </c>
       <c r="B25" t="s">
-        <v>37</v>
+        <v>141</v>
       </c>
       <c r="C25">
         <v>3</v>
@@ -1655,6 +2852,1128 @@
         <v>0</v>
       </c>
       <c r="E25" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A26" t="s">
+        <v>119</v>
+      </c>
+      <c r="B26" t="s">
+        <v>142</v>
+      </c>
+      <c r="C26">
+        <v>1</v>
+      </c>
+      <c r="D26" t="b">
+        <v>0</v>
+      </c>
+      <c r="E26" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A27" t="s">
+        <v>119</v>
+      </c>
+      <c r="B27" t="s">
+        <v>142</v>
+      </c>
+      <c r="C27">
+        <v>2</v>
+      </c>
+      <c r="D27" t="b">
+        <v>0</v>
+      </c>
+      <c r="E27" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A28" t="s">
+        <v>119</v>
+      </c>
+      <c r="B28" t="s">
+        <v>142</v>
+      </c>
+      <c r="C28">
+        <v>3</v>
+      </c>
+      <c r="D28" t="b">
+        <v>0</v>
+      </c>
+      <c r="E28" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A29" t="s">
+        <v>120</v>
+      </c>
+      <c r="B29" t="s">
+        <v>143</v>
+      </c>
+      <c r="C29">
+        <v>1</v>
+      </c>
+      <c r="D29" t="b">
+        <v>0</v>
+      </c>
+      <c r="E29" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A30" t="s">
+        <v>120</v>
+      </c>
+      <c r="B30" t="s">
+        <v>143</v>
+      </c>
+      <c r="C30">
+        <v>2</v>
+      </c>
+      <c r="D30" t="b">
+        <v>0</v>
+      </c>
+      <c r="E30" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A31" t="s">
+        <v>120</v>
+      </c>
+      <c r="B31" t="s">
+        <v>143</v>
+      </c>
+      <c r="C31">
+        <v>3</v>
+      </c>
+      <c r="D31" t="b">
+        <v>0</v>
+      </c>
+      <c r="E31" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A32" t="s">
+        <v>121</v>
+      </c>
+      <c r="B32" t="s">
+        <v>144</v>
+      </c>
+      <c r="C32">
+        <v>1</v>
+      </c>
+      <c r="D32" t="b">
+        <v>1</v>
+      </c>
+      <c r="E32" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A33" t="s">
+        <v>121</v>
+      </c>
+      <c r="B33" t="s">
+        <v>144</v>
+      </c>
+      <c r="C33">
+        <v>2</v>
+      </c>
+      <c r="D33" t="b">
+        <v>0</v>
+      </c>
+      <c r="E33" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A34" t="s">
+        <v>121</v>
+      </c>
+      <c r="B34" t="s">
+        <v>144</v>
+      </c>
+      <c r="C34">
+        <v>3</v>
+      </c>
+      <c r="D34" t="b">
+        <v>0</v>
+      </c>
+      <c r="E34" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A35" t="s">
+        <v>122</v>
+      </c>
+      <c r="B35" t="s">
+        <v>145</v>
+      </c>
+      <c r="C35">
+        <v>1</v>
+      </c>
+      <c r="D35" t="b">
+        <v>1</v>
+      </c>
+      <c r="E35" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A36" t="s">
+        <v>122</v>
+      </c>
+      <c r="B36" t="s">
+        <v>145</v>
+      </c>
+      <c r="C36">
+        <v>2</v>
+      </c>
+      <c r="D36" t="b">
+        <v>0</v>
+      </c>
+      <c r="E36" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A37" t="s">
+        <v>122</v>
+      </c>
+      <c r="B37" t="s">
+        <v>145</v>
+      </c>
+      <c r="C37">
+        <v>3</v>
+      </c>
+      <c r="D37" t="b">
+        <v>0</v>
+      </c>
+      <c r="E37" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A38" t="s">
+        <v>123</v>
+      </c>
+      <c r="B38" t="s">
+        <v>5</v>
+      </c>
+      <c r="C38">
+        <v>1</v>
+      </c>
+      <c r="D38" t="b">
+        <v>1</v>
+      </c>
+      <c r="E38" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A39" t="s">
+        <v>123</v>
+      </c>
+      <c r="B39" t="s">
+        <v>5</v>
+      </c>
+      <c r="C39">
+        <v>2</v>
+      </c>
+      <c r="D39" t="b">
+        <v>0</v>
+      </c>
+      <c r="E39" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A40" t="s">
+        <v>123</v>
+      </c>
+      <c r="B40" t="s">
+        <v>5</v>
+      </c>
+      <c r="C40">
+        <v>3</v>
+      </c>
+      <c r="D40" t="b">
+        <v>0</v>
+      </c>
+      <c r="E40" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A41" t="s">
+        <v>124</v>
+      </c>
+      <c r="B41" t="s">
+        <v>146</v>
+      </c>
+      <c r="C41">
+        <v>1</v>
+      </c>
+      <c r="D41" t="b">
+        <v>1</v>
+      </c>
+      <c r="E41" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A42" t="s">
+        <v>124</v>
+      </c>
+      <c r="B42" t="s">
+        <v>146</v>
+      </c>
+      <c r="C42">
+        <v>2</v>
+      </c>
+      <c r="D42" t="b">
+        <v>0</v>
+      </c>
+      <c r="E42" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A43" t="s">
+        <v>124</v>
+      </c>
+      <c r="B43" t="s">
+        <v>146</v>
+      </c>
+      <c r="C43">
+        <v>3</v>
+      </c>
+      <c r="D43" t="b">
+        <v>0</v>
+      </c>
+      <c r="E43" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A44" t="s">
+        <v>125</v>
+      </c>
+      <c r="B44" t="s">
+        <v>147</v>
+      </c>
+      <c r="C44">
+        <v>1</v>
+      </c>
+      <c r="D44" t="b">
+        <v>0</v>
+      </c>
+      <c r="E44" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A45" t="s">
+        <v>125</v>
+      </c>
+      <c r="B45" t="s">
+        <v>147</v>
+      </c>
+      <c r="C45">
+        <v>2</v>
+      </c>
+      <c r="D45" t="b">
+        <v>0</v>
+      </c>
+      <c r="E45" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A46" t="s">
+        <v>125</v>
+      </c>
+      <c r="B46" t="s">
+        <v>147</v>
+      </c>
+      <c r="C46">
+        <v>3</v>
+      </c>
+      <c r="D46" t="b">
+        <v>0</v>
+      </c>
+      <c r="E46" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A47" t="s">
+        <v>126</v>
+      </c>
+      <c r="B47" t="s">
+        <v>148</v>
+      </c>
+      <c r="C47">
+        <v>1</v>
+      </c>
+      <c r="D47" t="b">
+        <v>1</v>
+      </c>
+      <c r="E47" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A48" t="s">
+        <v>126</v>
+      </c>
+      <c r="B48" t="s">
+        <v>148</v>
+      </c>
+      <c r="C48">
+        <v>2</v>
+      </c>
+      <c r="D48" t="b">
+        <v>0</v>
+      </c>
+      <c r="E48" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A49" t="s">
+        <v>126</v>
+      </c>
+      <c r="B49" t="s">
+        <v>148</v>
+      </c>
+      <c r="C49">
+        <v>3</v>
+      </c>
+      <c r="D49" t="b">
+        <v>0</v>
+      </c>
+      <c r="E49" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A50" t="s">
+        <v>127</v>
+      </c>
+      <c r="B50" t="s">
+        <v>149</v>
+      </c>
+      <c r="C50">
+        <v>1</v>
+      </c>
+      <c r="D50" t="b">
+        <v>0</v>
+      </c>
+      <c r="E50" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A51" t="s">
+        <v>127</v>
+      </c>
+      <c r="B51" t="s">
+        <v>149</v>
+      </c>
+      <c r="C51">
+        <v>2</v>
+      </c>
+      <c r="D51" t="b">
+        <v>0</v>
+      </c>
+      <c r="E51" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A52" t="s">
+        <v>127</v>
+      </c>
+      <c r="B52" t="s">
+        <v>149</v>
+      </c>
+      <c r="C52">
+        <v>3</v>
+      </c>
+      <c r="D52" t="b">
+        <v>0</v>
+      </c>
+      <c r="E52" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A53" t="s">
+        <v>128</v>
+      </c>
+      <c r="B53" t="s">
+        <v>150</v>
+      </c>
+      <c r="C53">
+        <v>1</v>
+      </c>
+      <c r="D53" t="b">
+        <v>0</v>
+      </c>
+      <c r="E53" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A54" t="s">
+        <v>128</v>
+      </c>
+      <c r="B54" t="s">
+        <v>150</v>
+      </c>
+      <c r="C54">
+        <v>2</v>
+      </c>
+      <c r="D54" t="b">
+        <v>0</v>
+      </c>
+      <c r="E54" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A55" t="s">
+        <v>128</v>
+      </c>
+      <c r="B55" t="s">
+        <v>150</v>
+      </c>
+      <c r="C55">
+        <v>3</v>
+      </c>
+      <c r="D55" t="b">
+        <v>0</v>
+      </c>
+      <c r="E55" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A56" t="s">
+        <v>129</v>
+      </c>
+      <c r="B56" t="s">
+        <v>151</v>
+      </c>
+      <c r="C56">
+        <v>1</v>
+      </c>
+      <c r="D56" t="b">
+        <v>1</v>
+      </c>
+      <c r="E56" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A57" t="s">
+        <v>129</v>
+      </c>
+      <c r="B57" t="s">
+        <v>151</v>
+      </c>
+      <c r="C57">
+        <v>2</v>
+      </c>
+      <c r="D57" t="b">
+        <v>0</v>
+      </c>
+      <c r="E57" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A58" t="s">
+        <v>129</v>
+      </c>
+      <c r="B58" t="s">
+        <v>151</v>
+      </c>
+      <c r="C58">
+        <v>3</v>
+      </c>
+      <c r="D58" t="b">
+        <v>0</v>
+      </c>
+      <c r="E58" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A59" t="s">
+        <v>130</v>
+      </c>
+      <c r="B59" t="s">
+        <v>152</v>
+      </c>
+      <c r="C59">
+        <v>1</v>
+      </c>
+      <c r="D59" t="b">
+        <v>0</v>
+      </c>
+      <c r="E59" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A60" t="s">
+        <v>130</v>
+      </c>
+      <c r="B60" t="s">
+        <v>152</v>
+      </c>
+      <c r="C60">
+        <v>2</v>
+      </c>
+      <c r="D60" t="b">
+        <v>0</v>
+      </c>
+      <c r="E60" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A61" t="s">
+        <v>130</v>
+      </c>
+      <c r="B61" t="s">
+        <v>152</v>
+      </c>
+      <c r="C61">
+        <v>3</v>
+      </c>
+      <c r="D61" t="b">
+        <v>0</v>
+      </c>
+      <c r="E61" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A62" t="s">
+        <v>131</v>
+      </c>
+      <c r="B62" t="s">
+        <v>153</v>
+      </c>
+      <c r="C62">
+        <v>1</v>
+      </c>
+      <c r="D62" t="b">
+        <v>1</v>
+      </c>
+      <c r="E62" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A63" t="s">
+        <v>131</v>
+      </c>
+      <c r="B63" t="s">
+        <v>153</v>
+      </c>
+      <c r="C63">
+        <v>2</v>
+      </c>
+      <c r="D63" t="b">
+        <v>0</v>
+      </c>
+      <c r="E63" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A64" t="s">
+        <v>131</v>
+      </c>
+      <c r="B64" t="s">
+        <v>153</v>
+      </c>
+      <c r="C64">
+        <v>3</v>
+      </c>
+      <c r="D64" t="b">
+        <v>0</v>
+      </c>
+      <c r="E64" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A65" t="s">
+        <v>132</v>
+      </c>
+      <c r="B65" t="s">
+        <v>140</v>
+      </c>
+      <c r="C65">
+        <v>1</v>
+      </c>
+      <c r="D65" t="b">
+        <v>1</v>
+      </c>
+      <c r="E65" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A66" t="s">
+        <v>132</v>
+      </c>
+      <c r="B66" t="s">
+        <v>140</v>
+      </c>
+      <c r="C66">
+        <v>2</v>
+      </c>
+      <c r="D66" t="b">
+        <v>0</v>
+      </c>
+      <c r="E66" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A67" t="s">
+        <v>132</v>
+      </c>
+      <c r="B67" t="s">
+        <v>140</v>
+      </c>
+      <c r="C67">
+        <v>3</v>
+      </c>
+      <c r="D67" t="b">
+        <v>0</v>
+      </c>
+      <c r="E67" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A68" t="s">
+        <v>133</v>
+      </c>
+      <c r="B68" t="s">
+        <v>154</v>
+      </c>
+      <c r="C68">
+        <v>1</v>
+      </c>
+      <c r="D68" t="b">
+        <v>0</v>
+      </c>
+      <c r="E68" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A69" t="s">
+        <v>133</v>
+      </c>
+      <c r="B69" t="s">
+        <v>154</v>
+      </c>
+      <c r="C69">
+        <v>2</v>
+      </c>
+      <c r="D69" t="b">
+        <v>0</v>
+      </c>
+      <c r="E69" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A70" t="s">
+        <v>133</v>
+      </c>
+      <c r="B70" t="s">
+        <v>154</v>
+      </c>
+      <c r="C70">
+        <v>3</v>
+      </c>
+      <c r="D70" t="b">
+        <v>0</v>
+      </c>
+      <c r="E70" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A71" t="s">
+        <v>86</v>
+      </c>
+      <c r="B71" t="s">
+        <v>87</v>
+      </c>
+      <c r="C71">
+        <v>1</v>
+      </c>
+      <c r="D71" t="b">
+        <v>1</v>
+      </c>
+      <c r="E71" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A72" t="s">
+        <v>86</v>
+      </c>
+      <c r="B72" t="s">
+        <v>87</v>
+      </c>
+      <c r="C72">
+        <v>2</v>
+      </c>
+      <c r="D72" t="b">
+        <v>0</v>
+      </c>
+      <c r="E72" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A73" t="s">
+        <v>86</v>
+      </c>
+      <c r="B73" t="s">
+        <v>87</v>
+      </c>
+      <c r="C73">
+        <v>3</v>
+      </c>
+      <c r="D73" t="b">
+        <v>0</v>
+      </c>
+      <c r="E73" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A74" t="s">
+        <v>17</v>
+      </c>
+      <c r="B74" t="s">
+        <v>18</v>
+      </c>
+      <c r="C74">
+        <v>1</v>
+      </c>
+      <c r="D74" t="b">
+        <v>1</v>
+      </c>
+      <c r="E74" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A75" t="s">
+        <v>17</v>
+      </c>
+      <c r="B75" t="s">
+        <v>18</v>
+      </c>
+      <c r="C75">
+        <v>2</v>
+      </c>
+      <c r="D75" t="b">
+        <v>0</v>
+      </c>
+      <c r="E75" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A76" t="s">
+        <v>17</v>
+      </c>
+      <c r="B76" t="s">
+        <v>18</v>
+      </c>
+      <c r="C76">
+        <v>3</v>
+      </c>
+      <c r="D76" t="b">
+        <v>0</v>
+      </c>
+      <c r="E76" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A77" t="s">
+        <v>97</v>
+      </c>
+      <c r="B77" t="s">
+        <v>98</v>
+      </c>
+      <c r="C77">
+        <v>1</v>
+      </c>
+      <c r="D77" t="b">
+        <v>0</v>
+      </c>
+      <c r="E77" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A78" t="s">
+        <v>97</v>
+      </c>
+      <c r="B78" t="s">
+        <v>98</v>
+      </c>
+      <c r="C78">
+        <v>2</v>
+      </c>
+      <c r="D78" t="b">
+        <v>0</v>
+      </c>
+      <c r="E78" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A79" t="s">
+        <v>97</v>
+      </c>
+      <c r="B79" t="s">
+        <v>98</v>
+      </c>
+      <c r="C79">
+        <v>3</v>
+      </c>
+      <c r="D79" t="b">
+        <v>0</v>
+      </c>
+      <c r="E79" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A80" t="s">
+        <v>76</v>
+      </c>
+      <c r="B80" t="s">
+        <v>77</v>
+      </c>
+      <c r="C80">
+        <v>1</v>
+      </c>
+      <c r="D80" t="b">
+        <v>1</v>
+      </c>
+      <c r="E80" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A81" t="s">
+        <v>76</v>
+      </c>
+      <c r="B81" t="s">
+        <v>77</v>
+      </c>
+      <c r="C81">
+        <v>2</v>
+      </c>
+      <c r="D81" t="b">
+        <v>0</v>
+      </c>
+      <c r="E81" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A82" t="s">
+        <v>76</v>
+      </c>
+      <c r="B82" t="s">
+        <v>77</v>
+      </c>
+      <c r="C82">
+        <v>3</v>
+      </c>
+      <c r="D82" t="b">
+        <v>0</v>
+      </c>
+      <c r="E82" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A83" t="s">
+        <v>23</v>
+      </c>
+      <c r="B83" t="s">
+        <v>24</v>
+      </c>
+      <c r="C83">
+        <v>1</v>
+      </c>
+      <c r="D83" t="b">
+        <v>0</v>
+      </c>
+      <c r="E83" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A84" t="s">
+        <v>23</v>
+      </c>
+      <c r="B84" t="s">
+        <v>24</v>
+      </c>
+      <c r="C84">
+        <v>2</v>
+      </c>
+      <c r="D84" t="b">
+        <v>0</v>
+      </c>
+      <c r="E84" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A85" t="s">
+        <v>23</v>
+      </c>
+      <c r="B85" t="s">
+        <v>24</v>
+      </c>
+      <c r="C85">
+        <v>3</v>
+      </c>
+      <c r="D85" t="b">
+        <v>0</v>
+      </c>
+      <c r="E85" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A86" t="s">
+        <v>29</v>
+      </c>
+      <c r="B86" t="s">
+        <v>30</v>
+      </c>
+      <c r="C86">
+        <v>1</v>
+      </c>
+      <c r="D86" t="b">
+        <v>0</v>
+      </c>
+      <c r="E86" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A87" t="s">
+        <v>29</v>
+      </c>
+      <c r="B87" t="s">
+        <v>30</v>
+      </c>
+      <c r="C87">
+        <v>2</v>
+      </c>
+      <c r="D87" t="b">
+        <v>0</v>
+      </c>
+      <c r="E87" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A88" t="s">
+        <v>29</v>
+      </c>
+      <c r="B88" t="s">
+        <v>30</v>
+      </c>
+      <c r="C88">
+        <v>3</v>
+      </c>
+      <c r="D88" t="b">
+        <v>0</v>
+      </c>
+      <c r="E88" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A89" t="s">
+        <v>36</v>
+      </c>
+      <c r="B89" t="s">
+        <v>37</v>
+      </c>
+      <c r="C89">
+        <v>1</v>
+      </c>
+      <c r="D89" t="b">
+        <v>0</v>
+      </c>
+      <c r="E89" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A90" t="s">
+        <v>36</v>
+      </c>
+      <c r="B90" t="s">
+        <v>37</v>
+      </c>
+      <c r="C90">
+        <v>2</v>
+      </c>
+      <c r="D90" t="b">
+        <v>0</v>
+      </c>
+      <c r="E90" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A91" t="s">
+        <v>36</v>
+      </c>
+      <c r="B91" t="s">
+        <v>37</v>
+      </c>
+      <c r="C91">
+        <v>3</v>
+      </c>
+      <c r="D91" t="b">
+        <v>0</v>
+      </c>
+      <c r="E91" t="s">
         <v>69</v>
       </c>
     </row>

--- a/data/Fate-Spreadsheet.xlsx
+++ b/data/Fate-Spreadsheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pixel\Documents\Projects\Fate-Wiki\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33239780-26C1-4CA1-BB72-800FD4D65CD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81AC9E10-788D-4926-843F-BC146EAE4A45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{B05E798F-9EF6-4508-A0A4-311D06661AED}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="590" uniqueCount="265">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="722" uniqueCount="323">
   <si>
     <t>servant_id</t>
   </si>
@@ -838,6 +838,180 @@
   </si>
   <si>
     <t>Wise Fox</t>
+  </si>
+  <si>
+    <t>S0024</t>
+  </si>
+  <si>
+    <t>Cú Chulainn</t>
+  </si>
+  <si>
+    <t>cu-chulainn</t>
+  </si>
+  <si>
+    <t>Lancer</t>
+  </si>
+  <si>
+    <t>2,4,4,4,5</t>
+  </si>
+  <si>
+    <t>2,4,5</t>
+  </si>
+  <si>
+    <t>Surveil,Surveil</t>
+  </si>
+  <si>
+    <t>S0048</t>
+  </si>
+  <si>
+    <t>Gilgamesh</t>
+  </si>
+  <si>
+    <t>gilgamesh</t>
+  </si>
+  <si>
+    <t>Preparation,Luck,Luck</t>
+  </si>
+  <si>
+    <t>S0070</t>
+  </si>
+  <si>
+    <t>Medusa</t>
+  </si>
+  <si>
+    <t>medusa</t>
+  </si>
+  <si>
+    <t>Rider</t>
+  </si>
+  <si>
+    <t>2,3,5</t>
+  </si>
+  <si>
+    <t>3,3</t>
+  </si>
+  <si>
+    <t>S0093</t>
+  </si>
+  <si>
+    <t>medea</t>
+  </si>
+  <si>
+    <t>Surveil,Luck,Preparation</t>
+  </si>
+  <si>
+    <t>S0101</t>
+  </si>
+  <si>
+    <t>Illyasviel von Einzbern</t>
+  </si>
+  <si>
+    <t>illyasviel-von-einzbern</t>
+  </si>
+  <si>
+    <t>2,2,3,3</t>
+  </si>
+  <si>
+    <t>Saber Install</t>
+  </si>
+  <si>
+    <t>Berserker Install</t>
+  </si>
+  <si>
+    <t>Archer Install</t>
+  </si>
+  <si>
+    <t>Assassin Install</t>
+  </si>
+  <si>
+    <t>Lancer Install</t>
+  </si>
+  <si>
+    <t>Caster Install</t>
+  </si>
+  <si>
+    <t>Rider Install</t>
+  </si>
+  <si>
+    <t>Saber-Install</t>
+  </si>
+  <si>
+    <t>Berserker-Install</t>
+  </si>
+  <si>
+    <t>Archer-Install</t>
+  </si>
+  <si>
+    <t>Assassin-Install</t>
+  </si>
+  <si>
+    <t>Lancer-Install</t>
+  </si>
+  <si>
+    <t>Caster-Install</t>
+  </si>
+  <si>
+    <t>Rider-Install</t>
+  </si>
+  <si>
+    <t>Lancer Class</t>
+  </si>
+  <si>
+    <t>Gae Bolg</t>
+  </si>
+  <si>
+    <t>Enuma Elish</t>
+  </si>
+  <si>
+    <t>Gate of Babylon</t>
+  </si>
+  <si>
+    <t>Rider Class</t>
+  </si>
+  <si>
+    <t>Bellerophon</t>
+  </si>
+  <si>
+    <t>Petrification</t>
+  </si>
+  <si>
+    <t>Rain of Light</t>
+  </si>
+  <si>
+    <t>Rule Breaker</t>
+  </si>
+  <si>
+    <t>Quintett Feuer</t>
+  </si>
+  <si>
+    <t>Schneiden</t>
+  </si>
+  <si>
+    <t>Card Holster</t>
+  </si>
+  <si>
+    <t>S0121</t>
+  </si>
+  <si>
+    <t>Semiramis of Assyria</t>
+  </si>
+  <si>
+    <t>semiramis</t>
+  </si>
+  <si>
+    <t>Assassin</t>
+  </si>
+  <si>
+    <t>2,3,4,4,5</t>
+  </si>
+  <si>
+    <t>Preparation,Preparation,Luck</t>
+  </si>
+  <si>
+    <t>Assassin Class</t>
+  </si>
+  <si>
+    <t>Sikera Usum</t>
   </si>
 </sst>
 </file>
@@ -887,12 +1061,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1227,7 +1400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E33D7ECC-1EAA-4A40-B4DA-A93E54CBC8B5}">
-  <dimension ref="A1:K31"/>
+  <dimension ref="A1:K37"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="2" max="2" width="17.1328125" customWidth="1"/>
@@ -1997,80 +2170,92 @@
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
-        <v>86</v>
+        <v>265</v>
       </c>
       <c r="B25" t="s">
-        <v>87</v>
+        <v>266</v>
       </c>
       <c r="C25" t="s">
-        <v>88</v>
+        <v>267</v>
       </c>
       <c r="D25" t="s">
-        <v>89</v>
+        <v>268</v>
       </c>
       <c r="E25" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>91</v>
+        <v>269</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>42</v>
+        <v>270</v>
+      </c>
+      <c r="J25" s="2" t="s">
+        <v>271</v>
       </c>
       <c r="K25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
-        <v>17</v>
+        <v>272</v>
       </c>
       <c r="B26" t="s">
-        <v>18</v>
+        <v>273</v>
       </c>
       <c r="C26" t="s">
-        <v>19</v>
+        <v>274</v>
       </c>
       <c r="D26" t="s">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="E26" t="s">
         <v>8</v>
       </c>
+      <c r="G26" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>27</v>
+      </c>
       <c r="I26" s="2" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>22</v>
+        <v>275</v>
       </c>
       <c r="K26" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="B27" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="C27" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="D27" t="s">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="E27" t="s">
-        <v>100</v>
+        <v>90</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>15</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>102</v>
+        <v>42</v>
       </c>
       <c r="K27" t="b">
         <v>1</v>
@@ -2078,31 +2263,31 @@
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
-        <v>76</v>
+        <v>276</v>
       </c>
       <c r="B28" t="s">
-        <v>77</v>
+        <v>277</v>
       </c>
       <c r="C28" t="s">
-        <v>78</v>
+        <v>278</v>
       </c>
       <c r="D28" t="s">
-        <v>79</v>
+        <v>279</v>
       </c>
       <c r="E28" t="s">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>80</v>
+        <v>280</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>15</v>
+        <v>205</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>82</v>
+        <v>281</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>81</v>
+        <v>43</v>
       </c>
       <c r="K28" t="b">
         <v>0</v>
@@ -2110,28 +2295,28 @@
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
-        <v>23</v>
+        <v>282</v>
       </c>
       <c r="B29" t="s">
-        <v>24</v>
+        <v>250</v>
       </c>
       <c r="C29" t="s">
-        <v>25</v>
+        <v>283</v>
       </c>
       <c r="D29" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="E29" t="s">
-        <v>8</v>
-      </c>
-      <c r="G29" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H29" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="H29" s="2" t="s">
-        <v>28</v>
+      <c r="I29" s="2" t="s">
+        <v>102</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>70</v>
+        <v>284</v>
       </c>
       <c r="K29" t="b">
         <v>0</v>
@@ -2139,62 +2324,230 @@
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="B30" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="C30" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="D30" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="E30" t="s">
-        <v>33</v>
-      </c>
-      <c r="G30" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="H30" s="2" t="s">
-        <v>82</v>
+        <v>8</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="K30" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
+        <v>285</v>
+      </c>
+      <c r="B31" t="s">
+        <v>286</v>
+      </c>
+      <c r="C31" t="s">
+        <v>287</v>
+      </c>
+      <c r="D31" t="s">
+        <v>20</v>
+      </c>
+      <c r="E31" t="s">
+        <v>8</v>
+      </c>
+      <c r="I31" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="J31" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="K31" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A32" t="s">
+        <v>97</v>
+      </c>
+      <c r="B32" t="s">
+        <v>98</v>
+      </c>
+      <c r="C32" t="s">
+        <v>99</v>
+      </c>
+      <c r="D32" t="s">
+        <v>20</v>
+      </c>
+      <c r="E32" t="s">
+        <v>100</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="I32" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="K32" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A33" t="s">
+        <v>315</v>
+      </c>
+      <c r="B33" t="s">
+        <v>316</v>
+      </c>
+      <c r="C33" t="s">
+        <v>317</v>
+      </c>
+      <c r="D33" t="s">
+        <v>318</v>
+      </c>
+      <c r="E33" t="s">
+        <v>33</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I33" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="J33" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="K33" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A34" t="s">
+        <v>76</v>
+      </c>
+      <c r="B34" t="s">
+        <v>77</v>
+      </c>
+      <c r="C34" t="s">
+        <v>78</v>
+      </c>
+      <c r="D34" t="s">
+        <v>79</v>
+      </c>
+      <c r="E34" t="s">
+        <v>40</v>
+      </c>
+      <c r="G34" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I34" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="J34" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="K34" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A35" t="s">
+        <v>23</v>
+      </c>
+      <c r="B35" t="s">
+        <v>24</v>
+      </c>
+      <c r="C35" t="s">
+        <v>25</v>
+      </c>
+      <c r="D35" t="s">
+        <v>26</v>
+      </c>
+      <c r="E35" t="s">
+        <v>8</v>
+      </c>
+      <c r="G35" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="H35" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J35" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="K35" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A36" t="s">
+        <v>29</v>
+      </c>
+      <c r="B36" t="s">
+        <v>30</v>
+      </c>
+      <c r="C36" t="s">
+        <v>31</v>
+      </c>
+      <c r="D36" t="s">
+        <v>32</v>
+      </c>
+      <c r="E36" t="s">
+        <v>33</v>
+      </c>
+      <c r="G36" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H36" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="I36" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="J36" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="K36" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A37" t="s">
         <v>36</v>
       </c>
-      <c r="B31" t="s">
+      <c r="B37" t="s">
         <v>37</v>
       </c>
-      <c r="C31" t="s">
+      <c r="C37" t="s">
         <v>38</v>
       </c>
-      <c r="D31" t="s">
+      <c r="D37" t="s">
         <v>39</v>
       </c>
-      <c r="E31" t="s">
+      <c r="E37" t="s">
         <v>40</v>
       </c>
-      <c r="G31" s="2" t="s">
+      <c r="G37" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="H31" s="2" t="s">
+      <c r="H37" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="J31" s="2" t="s">
+      <c r="J37" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="K31" t="b">
+      <c r="K37" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2202,14 +2555,14 @@
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="H2 I28 H30 I6:I7 I10 I12 H14 I18 I22 I24" numberStoredAsText="1"/>
+    <ignoredError sqref="H2 I34 H36 I6:I7 I10 I12 H14 I18 I22 I24" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D1BC60D8-44F3-478D-BCC0-4752624457AE}">
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="2" max="2" width="19" customWidth="1"/>
@@ -2238,54 +2591,54 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="4" t="s">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A2" t="s">
         <v>117</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" t="s">
         <v>140</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" t="s">
         <v>208</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" t="s">
         <v>209</v>
       </c>
-      <c r="E2" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A3" s="4" t="s">
+      <c r="E2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A3" t="s">
         <v>127</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" t="s">
         <v>149</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" t="s">
         <v>210</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" t="s">
         <v>211</v>
       </c>
-      <c r="E3" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A4" s="4" t="s">
+      <c r="E3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A4" t="s">
         <v>131</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" t="s">
         <v>153</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" t="s">
         <v>212</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" t="s">
         <v>212</v>
       </c>
-      <c r="E4" s="4">
+      <c r="E4">
         <v>1</v>
       </c>
     </row>
@@ -2342,16 +2695,16 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
-        <v>97</v>
+        <v>285</v>
       </c>
       <c r="B8" t="s">
-        <v>98</v>
+        <v>286</v>
       </c>
       <c r="C8" t="s">
-        <v>103</v>
+        <v>289</v>
       </c>
       <c r="D8" t="s">
-        <v>106</v>
+        <v>296</v>
       </c>
       <c r="E8">
         <v>1</v>
@@ -2359,16 +2712,16 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
-        <v>97</v>
+        <v>285</v>
       </c>
       <c r="B9" t="s">
-        <v>98</v>
+        <v>286</v>
       </c>
       <c r="C9" t="s">
-        <v>104</v>
+        <v>290</v>
       </c>
       <c r="D9" t="s">
-        <v>107</v>
+        <v>297</v>
       </c>
       <c r="E9">
         <v>1</v>
@@ -2376,16 +2729,16 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
-        <v>97</v>
+        <v>285</v>
       </c>
       <c r="B10" t="s">
-        <v>98</v>
+        <v>286</v>
       </c>
       <c r="C10" t="s">
-        <v>105</v>
+        <v>291</v>
       </c>
       <c r="D10" t="s">
-        <v>108</v>
+        <v>298</v>
       </c>
       <c r="E10">
         <v>1</v>
@@ -2393,18 +2746,137 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
+        <v>285</v>
+      </c>
+      <c r="B11" t="s">
+        <v>286</v>
+      </c>
+      <c r="C11" t="s">
+        <v>292</v>
+      </c>
+      <c r="D11" t="s">
+        <v>299</v>
+      </c>
+      <c r="E11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A12" t="s">
+        <v>285</v>
+      </c>
+      <c r="B12" t="s">
+        <v>286</v>
+      </c>
+      <c r="C12" t="s">
+        <v>293</v>
+      </c>
+      <c r="D12" t="s">
+        <v>300</v>
+      </c>
+      <c r="E12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A13" t="s">
+        <v>285</v>
+      </c>
+      <c r="B13" t="s">
+        <v>286</v>
+      </c>
+      <c r="C13" t="s">
+        <v>294</v>
+      </c>
+      <c r="D13" t="s">
+        <v>301</v>
+      </c>
+      <c r="E13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A14" t="s">
+        <v>285</v>
+      </c>
+      <c r="B14" t="s">
+        <v>286</v>
+      </c>
+      <c r="C14" t="s">
+        <v>295</v>
+      </c>
+      <c r="D14" t="s">
+        <v>302</v>
+      </c>
+      <c r="E14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A15" t="s">
+        <v>97</v>
+      </c>
+      <c r="B15" t="s">
+        <v>98</v>
+      </c>
+      <c r="C15" t="s">
+        <v>103</v>
+      </c>
+      <c r="D15" t="s">
+        <v>106</v>
+      </c>
+      <c r="E15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A16" t="s">
+        <v>97</v>
+      </c>
+      <c r="B16" t="s">
+        <v>98</v>
+      </c>
+      <c r="C16" t="s">
+        <v>104</v>
+      </c>
+      <c r="D16" t="s">
+        <v>107</v>
+      </c>
+      <c r="E16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A17" t="s">
+        <v>97</v>
+      </c>
+      <c r="B17" t="s">
+        <v>98</v>
+      </c>
+      <c r="C17" t="s">
+        <v>105</v>
+      </c>
+      <c r="D17" t="s">
+        <v>108</v>
+      </c>
+      <c r="E17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A18" t="s">
         <v>36</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B18" t="s">
         <v>37</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C18" t="s">
         <v>48</v>
       </c>
-      <c r="D11" t="s">
+      <c r="D18" t="s">
         <v>48</v>
       </c>
-      <c r="E11">
+      <c r="E18">
         <v>2</v>
       </c>
     </row>
@@ -2417,7 +2889,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84E3BB0D-5578-4069-B1C9-C3864EB2A429}">
-  <dimension ref="A1:F91"/>
+  <dimension ref="A1:F109"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="2" max="2" width="20.59765625" customWidth="1"/>
@@ -3622,10 +4094,10 @@
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A71" t="s">
-        <v>86</v>
+        <v>265</v>
       </c>
       <c r="B71" t="s">
-        <v>87</v>
+        <v>266</v>
       </c>
       <c r="C71">
         <v>1</v>
@@ -3634,15 +4106,15 @@
         <v>1</v>
       </c>
       <c r="E71" t="s">
-        <v>94</v>
+        <v>303</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A72" t="s">
-        <v>86</v>
+        <v>265</v>
       </c>
       <c r="B72" t="s">
-        <v>87</v>
+        <v>266</v>
       </c>
       <c r="C72">
         <v>2</v>
@@ -3651,15 +4123,15 @@
         <v>0</v>
       </c>
       <c r="E72" t="s">
-        <v>95</v>
+        <v>304</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A73" t="s">
-        <v>86</v>
+        <v>265</v>
       </c>
       <c r="B73" t="s">
-        <v>87</v>
+        <v>266</v>
       </c>
       <c r="C73">
         <v>3</v>
@@ -3668,15 +4140,15 @@
         <v>0</v>
       </c>
       <c r="E73" t="s">
-        <v>96</v>
+        <v>304</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A74" t="s">
-        <v>17</v>
+        <v>272</v>
       </c>
       <c r="B74" t="s">
-        <v>18</v>
+        <v>273</v>
       </c>
       <c r="C74">
         <v>1</v>
@@ -3685,15 +4157,15 @@
         <v>1</v>
       </c>
       <c r="E74" t="s">
-        <v>58</v>
+        <v>94</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A75" t="s">
-        <v>17</v>
+        <v>272</v>
       </c>
       <c r="B75" t="s">
-        <v>18</v>
+        <v>273</v>
       </c>
       <c r="C75">
         <v>2</v>
@@ -3702,15 +4174,15 @@
         <v>0</v>
       </c>
       <c r="E75" t="s">
-        <v>59</v>
+        <v>305</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A76" t="s">
-        <v>17</v>
+        <v>272</v>
       </c>
       <c r="B76" t="s">
-        <v>18</v>
+        <v>273</v>
       </c>
       <c r="C76">
         <v>3</v>
@@ -3719,32 +4191,32 @@
         <v>0</v>
       </c>
       <c r="E76" t="s">
-        <v>60</v>
+        <v>306</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A77" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="B77" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="C77">
         <v>1</v>
       </c>
       <c r="D77" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E77" t="s">
-        <v>109</v>
+        <v>94</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A78" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="B78" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="C78">
         <v>2</v>
@@ -3753,15 +4225,15 @@
         <v>0</v>
       </c>
       <c r="E78" t="s">
-        <v>110</v>
+        <v>95</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A79" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="B79" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="C79">
         <v>3</v>
@@ -3770,15 +4242,15 @@
         <v>0</v>
       </c>
       <c r="E79" t="s">
-        <v>111</v>
+        <v>96</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A80" t="s">
-        <v>76</v>
+        <v>276</v>
       </c>
       <c r="B80" t="s">
-        <v>77</v>
+        <v>277</v>
       </c>
       <c r="C80">
         <v>1</v>
@@ -3787,15 +4259,15 @@
         <v>1</v>
       </c>
       <c r="E80" t="s">
-        <v>83</v>
+        <v>307</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A81" t="s">
-        <v>76</v>
+        <v>276</v>
       </c>
       <c r="B81" t="s">
-        <v>77</v>
+        <v>277</v>
       </c>
       <c r="C81">
         <v>2</v>
@@ -3804,15 +4276,15 @@
         <v>0</v>
       </c>
       <c r="E81" t="s">
-        <v>84</v>
+        <v>308</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A82" t="s">
-        <v>76</v>
+        <v>276</v>
       </c>
       <c r="B82" t="s">
-        <v>77</v>
+        <v>277</v>
       </c>
       <c r="C82">
         <v>3</v>
@@ -3821,32 +4293,32 @@
         <v>0</v>
       </c>
       <c r="E82" t="s">
-        <v>85</v>
+        <v>309</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A83" t="s">
-        <v>23</v>
+        <v>282</v>
       </c>
       <c r="B83" t="s">
-        <v>24</v>
+        <v>250</v>
       </c>
       <c r="C83">
         <v>1</v>
       </c>
       <c r="D83" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E83" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A84" t="s">
-        <v>23</v>
+        <v>282</v>
       </c>
       <c r="B84" t="s">
-        <v>24</v>
+        <v>250</v>
       </c>
       <c r="C84">
         <v>2</v>
@@ -3855,15 +4327,15 @@
         <v>0</v>
       </c>
       <c r="E84" t="s">
-        <v>62</v>
+        <v>310</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A85" t="s">
-        <v>23</v>
+        <v>282</v>
       </c>
       <c r="B85" t="s">
-        <v>24</v>
+        <v>250</v>
       </c>
       <c r="C85">
         <v>3</v>
@@ -3872,32 +4344,32 @@
         <v>0</v>
       </c>
       <c r="E85" t="s">
-        <v>63</v>
+        <v>311</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A86" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="B86" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="C86">
         <v>1</v>
       </c>
       <c r="D86" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E86" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A87" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="B87" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="C87">
         <v>2</v>
@@ -3906,15 +4378,15 @@
         <v>0</v>
       </c>
       <c r="E87" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A88" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="B88" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="C88">
         <v>3</v>
@@ -3923,15 +4395,15 @@
         <v>0</v>
       </c>
       <c r="E88" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A89" t="s">
-        <v>36</v>
+        <v>285</v>
       </c>
       <c r="B89" t="s">
-        <v>37</v>
+        <v>286</v>
       </c>
       <c r="C89">
         <v>1</v>
@@ -3940,15 +4412,15 @@
         <v>0</v>
       </c>
       <c r="E89" t="s">
-        <v>67</v>
+        <v>312</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A90" t="s">
-        <v>36</v>
+        <v>285</v>
       </c>
       <c r="B90" t="s">
-        <v>37</v>
+        <v>286</v>
       </c>
       <c r="C90">
         <v>2</v>
@@ -3957,15 +4429,15 @@
         <v>0</v>
       </c>
       <c r="E90" t="s">
-        <v>68</v>
+        <v>313</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A91" t="s">
-        <v>36</v>
+        <v>285</v>
       </c>
       <c r="B91" t="s">
-        <v>37</v>
+        <v>286</v>
       </c>
       <c r="C91">
         <v>3</v>
@@ -3974,6 +4446,312 @@
         <v>0</v>
       </c>
       <c r="E91" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A92" t="s">
+        <v>97</v>
+      </c>
+      <c r="B92" t="s">
+        <v>98</v>
+      </c>
+      <c r="C92">
+        <v>1</v>
+      </c>
+      <c r="D92" t="b">
+        <v>0</v>
+      </c>
+      <c r="E92" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A93" t="s">
+        <v>97</v>
+      </c>
+      <c r="B93" t="s">
+        <v>98</v>
+      </c>
+      <c r="C93">
+        <v>2</v>
+      </c>
+      <c r="D93" t="b">
+        <v>0</v>
+      </c>
+      <c r="E93" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A94" t="s">
+        <v>97</v>
+      </c>
+      <c r="B94" t="s">
+        <v>98</v>
+      </c>
+      <c r="C94">
+        <v>3</v>
+      </c>
+      <c r="D94" t="b">
+        <v>0</v>
+      </c>
+      <c r="E94" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A95" t="s">
+        <v>315</v>
+      </c>
+      <c r="B95" t="s">
+        <v>316</v>
+      </c>
+      <c r="C95">
+        <v>1</v>
+      </c>
+      <c r="D95" t="b">
+        <v>1</v>
+      </c>
+      <c r="E95" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A96" t="s">
+        <v>315</v>
+      </c>
+      <c r="B96" t="s">
+        <v>316</v>
+      </c>
+      <c r="C96">
+        <v>2</v>
+      </c>
+      <c r="D96" t="b">
+        <v>1</v>
+      </c>
+      <c r="E96" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A97" t="s">
+        <v>315</v>
+      </c>
+      <c r="B97" t="s">
+        <v>316</v>
+      </c>
+      <c r="C97">
+        <v>3</v>
+      </c>
+      <c r="D97" t="b">
+        <v>0</v>
+      </c>
+      <c r="E97" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A98" t="s">
+        <v>76</v>
+      </c>
+      <c r="B98" t="s">
+        <v>77</v>
+      </c>
+      <c r="C98">
+        <v>1</v>
+      </c>
+      <c r="D98" t="b">
+        <v>1</v>
+      </c>
+      <c r="E98" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A99" t="s">
+        <v>76</v>
+      </c>
+      <c r="B99" t="s">
+        <v>77</v>
+      </c>
+      <c r="C99">
+        <v>2</v>
+      </c>
+      <c r="D99" t="b">
+        <v>0</v>
+      </c>
+      <c r="E99" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A100" t="s">
+        <v>76</v>
+      </c>
+      <c r="B100" t="s">
+        <v>77</v>
+      </c>
+      <c r="C100">
+        <v>3</v>
+      </c>
+      <c r="D100" t="b">
+        <v>0</v>
+      </c>
+      <c r="E100" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A101" t="s">
+        <v>23</v>
+      </c>
+      <c r="B101" t="s">
+        <v>24</v>
+      </c>
+      <c r="C101">
+        <v>1</v>
+      </c>
+      <c r="D101" t="b">
+        <v>0</v>
+      </c>
+      <c r="E101" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A102" t="s">
+        <v>23</v>
+      </c>
+      <c r="B102" t="s">
+        <v>24</v>
+      </c>
+      <c r="C102">
+        <v>2</v>
+      </c>
+      <c r="D102" t="b">
+        <v>0</v>
+      </c>
+      <c r="E102" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A103" t="s">
+        <v>23</v>
+      </c>
+      <c r="B103" t="s">
+        <v>24</v>
+      </c>
+      <c r="C103">
+        <v>3</v>
+      </c>
+      <c r="D103" t="b">
+        <v>0</v>
+      </c>
+      <c r="E103" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A104" t="s">
+        <v>29</v>
+      </c>
+      <c r="B104" t="s">
+        <v>30</v>
+      </c>
+      <c r="C104">
+        <v>1</v>
+      </c>
+      <c r="D104" t="b">
+        <v>0</v>
+      </c>
+      <c r="E104" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A105" t="s">
+        <v>29</v>
+      </c>
+      <c r="B105" t="s">
+        <v>30</v>
+      </c>
+      <c r="C105">
+        <v>2</v>
+      </c>
+      <c r="D105" t="b">
+        <v>0</v>
+      </c>
+      <c r="E105" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A106" t="s">
+        <v>29</v>
+      </c>
+      <c r="B106" t="s">
+        <v>30</v>
+      </c>
+      <c r="C106">
+        <v>3</v>
+      </c>
+      <c r="D106" t="b">
+        <v>0</v>
+      </c>
+      <c r="E106" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A107" t="s">
+        <v>36</v>
+      </c>
+      <c r="B107" t="s">
+        <v>37</v>
+      </c>
+      <c r="C107">
+        <v>1</v>
+      </c>
+      <c r="D107" t="b">
+        <v>0</v>
+      </c>
+      <c r="E107" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A108" t="s">
+        <v>36</v>
+      </c>
+      <c r="B108" t="s">
+        <v>37</v>
+      </c>
+      <c r="C108">
+        <v>2</v>
+      </c>
+      <c r="D108" t="b">
+        <v>0</v>
+      </c>
+      <c r="E108" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A109" t="s">
+        <v>36</v>
+      </c>
+      <c r="B109" t="s">
+        <v>37</v>
+      </c>
+      <c r="C109">
+        <v>3</v>
+      </c>
+      <c r="D109" t="b">
+        <v>0</v>
+      </c>
+      <c r="E109" t="s">
         <v>69</v>
       </c>
     </row>

--- a/data/Fate-Spreadsheet.xlsx
+++ b/data/Fate-Spreadsheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pixel\Documents\Projects\Fate-Wiki\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81AC9E10-788D-4926-843F-BC146EAE4A45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F766361-2887-4A36-9C5B-EE2D635FDC7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{B05E798F-9EF6-4508-A0A4-311D06661AED}"/>
   </bookViews>
@@ -288,9 +288,6 @@
     <t>2,4,5,5</t>
   </si>
   <si>
-    <t>Berserker Strength 7,Berserker Strength 9,Luck,Luck,Surveil</t>
-  </si>
-  <si>
     <t>3</t>
   </si>
   <si>
@@ -1012,6 +1009,9 @@
   </si>
   <si>
     <t>Sikera Usum</t>
+  </si>
+  <si>
+    <t>Berserker_Strength_7,Berserker_Strength_9,Luck,Luck,Surveil</t>
   </si>
 </sst>
 </file>
@@ -1470,7 +1470,7 @@
         <v>14</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I2" s="2" t="s">
         <v>15</v>
@@ -1484,31 +1484,31 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B3" t="s">
+        <v>133</v>
+      </c>
+      <c r="C3" t="s">
         <v>134</v>
-      </c>
-      <c r="C3" t="s">
-        <v>135</v>
       </c>
       <c r="D3" t="s">
         <v>7</v>
       </c>
       <c r="E3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G3" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="H3" s="2" t="s">
         <v>176</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>177</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>15</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K3" t="b">
         <v>0</v>
@@ -1516,13 +1516,13 @@
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C4" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D4" t="s">
         <v>7</v>
@@ -1531,13 +1531,13 @@
         <v>8</v>
       </c>
       <c r="G4" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="J4" s="2" t="s">
         <v>179</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>180</v>
       </c>
       <c r="K4" t="b">
         <v>0</v>
@@ -1545,13 +1545,13 @@
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B5" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C5" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D5" t="s">
         <v>7</v>
@@ -1560,13 +1560,13 @@
         <v>8</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H5" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="J5" s="2" t="s">
         <v>181</v>
-      </c>
-      <c r="J5" s="2" t="s">
-        <v>182</v>
       </c>
       <c r="K5" t="b">
         <v>0</v>
@@ -1574,13 +1574,13 @@
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B6" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C6" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D6" t="s">
         <v>7</v>
@@ -1589,16 +1589,16 @@
         <v>8</v>
       </c>
       <c r="G6" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="J6" s="2" t="s">
         <v>183</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="J6" s="2" t="s">
-        <v>184</v>
       </c>
       <c r="K6" t="b">
         <v>0</v>
@@ -1606,13 +1606,13 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B7" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C7" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D7" t="s">
         <v>7</v>
@@ -1621,16 +1621,16 @@
         <v>8</v>
       </c>
       <c r="G7" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="H7" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="H7" s="2" t="s">
+      <c r="I7" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="J7" s="2" t="s">
         <v>186</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>187</v>
       </c>
       <c r="K7" t="b">
         <v>0</v>
@@ -1638,28 +1638,28 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B8" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C8" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D8" t="s">
         <v>7</v>
       </c>
       <c r="E8" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H8" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="J8" s="2" t="s">
         <v>188</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>189</v>
       </c>
       <c r="K8" t="b">
         <v>1</v>
@@ -1667,28 +1667,28 @@
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B9" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C9" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D9" t="s">
         <v>7</v>
       </c>
       <c r="E9" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="K9" t="b">
         <v>0</v>
@@ -1696,13 +1696,13 @@
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B10" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C10" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D10" t="s">
         <v>7</v>
@@ -1711,16 +1711,16 @@
         <v>8</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="H10" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="I10" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="I10" s="2" t="s">
-        <v>192</v>
-      </c>
       <c r="J10" s="2" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="K10" t="b">
         <v>0</v>
@@ -1728,31 +1728,31 @@
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B11" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C11" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D11" t="s">
         <v>7</v>
       </c>
       <c r="E11" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>27</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="K11" t="b">
         <v>0</v>
@@ -1760,31 +1760,31 @@
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B12" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C12" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D12" t="s">
         <v>79</v>
       </c>
       <c r="E12" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>80</v>
       </c>
       <c r="H12" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="J12" s="2" t="s">
         <v>194</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="J12" s="2" t="s">
-        <v>195</v>
       </c>
       <c r="K12" t="b">
         <v>0</v>
@@ -1792,28 +1792,28 @@
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B13" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C13" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D13" t="s">
         <v>7</v>
       </c>
       <c r="E13" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="K13" t="b">
         <v>0</v>
@@ -1821,13 +1821,13 @@
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B14" t="s">
         <v>5</v>
       </c>
       <c r="C14" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D14" t="s">
         <v>7</v>
@@ -1836,16 +1836,16 @@
         <v>8</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="K14" t="b">
         <v>0</v>
@@ -1853,31 +1853,31 @@
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B15" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C15" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D15" t="s">
         <v>7</v>
       </c>
       <c r="E15" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G15" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="H15" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="H15" s="2" t="s">
+      <c r="I15" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="J15" s="2" t="s">
         <v>197</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="J15" s="2" t="s">
-        <v>198</v>
       </c>
       <c r="K15" t="b">
         <v>0</v>
@@ -1885,13 +1885,13 @@
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B16" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C16" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D16" t="s">
         <v>7</v>
@@ -1900,16 +1900,16 @@
         <v>8</v>
       </c>
       <c r="G16" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="H16" s="2" t="s">
         <v>199</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>200</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>27</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="K16" t="b">
         <v>0</v>
@@ -1917,13 +1917,13 @@
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B17" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C17" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D17" t="s">
         <v>7</v>
@@ -1932,16 +1932,16 @@
         <v>8</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="H17" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="K17" t="b">
         <v>0</v>
@@ -1949,31 +1949,31 @@
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B18" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C18" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D18" t="s">
         <v>7</v>
       </c>
       <c r="E18" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>42</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="K18" t="b">
         <v>1</v>
@@ -1981,22 +1981,22 @@
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B19" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C19" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D19" t="s">
         <v>7</v>
       </c>
       <c r="E19" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>27</v>
@@ -2005,7 +2005,7 @@
         <v>15</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="K19" t="b">
         <v>0</v>
@@ -2013,28 +2013,28 @@
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B20" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C20" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D20" t="s">
         <v>7</v>
       </c>
       <c r="E20" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="K20" t="b">
         <v>0</v>
@@ -2042,31 +2042,31 @@
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B21" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C21" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D21" t="s">
         <v>7</v>
       </c>
       <c r="E21" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H21" s="2" t="s">
         <v>27</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="K21" t="b">
         <v>0</v>
@@ -2074,13 +2074,13 @@
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B22" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C22" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D22" t="s">
         <v>7</v>
@@ -2089,13 +2089,13 @@
         <v>40</v>
       </c>
       <c r="G22" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="I22" s="2" t="s">
         <v>191</v>
-      </c>
-      <c r="H22" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="I22" s="2" t="s">
-        <v>192</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>22</v>
@@ -2106,31 +2106,31 @@
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B23" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C23" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D23" t="s">
         <v>79</v>
       </c>
       <c r="E23" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="K23" t="b">
         <v>0</v>
@@ -2138,19 +2138,19 @@
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B24" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C24" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D24" t="s">
         <v>7</v>
       </c>
       <c r="E24" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>21</v>
@@ -2159,7 +2159,7 @@
         <v>41</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>43</v>
@@ -2170,31 +2170,31 @@
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
+        <v>264</v>
+      </c>
+      <c r="B25" t="s">
         <v>265</v>
       </c>
-      <c r="B25" t="s">
+      <c r="C25" t="s">
         <v>266</v>
       </c>
-      <c r="C25" t="s">
+      <c r="D25" t="s">
         <v>267</v>
       </c>
-      <c r="D25" t="s">
-        <v>268</v>
-      </c>
       <c r="E25" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H25" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="I25" s="2" t="s">
         <v>269</v>
       </c>
-      <c r="I25" s="2" t="s">
+      <c r="J25" s="2" t="s">
         <v>270</v>
-      </c>
-      <c r="J25" s="2" t="s">
-        <v>271</v>
       </c>
       <c r="K25" t="b">
         <v>0</v>
@@ -2202,16 +2202,16 @@
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
+        <v>271</v>
+      </c>
+      <c r="B26" t="s">
         <v>272</v>
       </c>
-      <c r="B26" t="s">
+      <c r="C26" t="s">
         <v>273</v>
       </c>
-      <c r="C26" t="s">
-        <v>274</v>
-      </c>
       <c r="D26" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E26" t="s">
         <v>8</v>
@@ -2226,7 +2226,7 @@
         <v>27</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="K26" t="b">
         <v>0</v>
@@ -2234,25 +2234,25 @@
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
+        <v>85</v>
+      </c>
+      <c r="B27" t="s">
         <v>86</v>
       </c>
-      <c r="B27" t="s">
+      <c r="C27" t="s">
         <v>87</v>
       </c>
-      <c r="C27" t="s">
+      <c r="D27" t="s">
         <v>88</v>
       </c>
-      <c r="D27" t="s">
+      <c r="E27" t="s">
         <v>89</v>
-      </c>
-      <c r="E27" t="s">
-        <v>90</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>42</v>
@@ -2263,28 +2263,28 @@
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
+        <v>275</v>
+      </c>
+      <c r="B28" t="s">
         <v>276</v>
       </c>
-      <c r="B28" t="s">
+      <c r="C28" t="s">
         <v>277</v>
       </c>
-      <c r="C28" t="s">
+      <c r="D28" t="s">
         <v>278</v>
-      </c>
-      <c r="D28" t="s">
-        <v>279</v>
       </c>
       <c r="E28" t="s">
         <v>8</v>
       </c>
       <c r="G28" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="I28" s="2" t="s">
         <v>280</v>
-      </c>
-      <c r="H28" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="I28" s="2" t="s">
-        <v>281</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>43</v>
@@ -2295,13 +2295,13 @@
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
+        <v>281</v>
+      </c>
+      <c r="B29" t="s">
+        <v>249</v>
+      </c>
+      <c r="C29" t="s">
         <v>282</v>
-      </c>
-      <c r="B29" t="s">
-        <v>250</v>
-      </c>
-      <c r="C29" t="s">
-        <v>283</v>
       </c>
       <c r="D29" t="s">
         <v>20</v>
@@ -2313,10 +2313,10 @@
         <v>27</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="K29" t="b">
         <v>0</v>
@@ -2350,13 +2350,13 @@
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
+        <v>284</v>
+      </c>
+      <c r="B31" t="s">
         <v>285</v>
       </c>
-      <c r="B31" t="s">
+      <c r="C31" t="s">
         <v>286</v>
-      </c>
-      <c r="C31" t="s">
-        <v>287</v>
       </c>
       <c r="D31" t="s">
         <v>20</v>
@@ -2365,10 +2365,10 @@
         <v>8</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K31" t="b">
         <v>1</v>
@@ -2376,25 +2376,25 @@
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
+        <v>96</v>
+      </c>
+      <c r="B32" t="s">
         <v>97</v>
       </c>
-      <c r="B32" t="s">
+      <c r="C32" t="s">
         <v>98</v>
-      </c>
-      <c r="C32" t="s">
-        <v>99</v>
       </c>
       <c r="D32" t="s">
         <v>20</v>
       </c>
       <c r="E32" t="s">
+        <v>99</v>
+      </c>
+      <c r="H32" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="H32" s="2" t="s">
+      <c r="I32" s="2" t="s">
         <v>101</v>
-      </c>
-      <c r="I32" s="2" t="s">
-        <v>102</v>
       </c>
       <c r="K32" t="b">
         <v>1</v>
@@ -2402,16 +2402,16 @@
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
+        <v>314</v>
+      </c>
+      <c r="B33" t="s">
         <v>315</v>
       </c>
-      <c r="B33" t="s">
+      <c r="C33" t="s">
         <v>316</v>
       </c>
-      <c r="C33" t="s">
+      <c r="D33" t="s">
         <v>317</v>
-      </c>
-      <c r="D33" t="s">
-        <v>318</v>
       </c>
       <c r="E33" t="s">
         <v>33</v>
@@ -2420,10 +2420,10 @@
         <v>21</v>
       </c>
       <c r="I33" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="J33" s="2" t="s">
         <v>319</v>
-      </c>
-      <c r="J33" s="2" t="s">
-        <v>320</v>
       </c>
       <c r="K33" t="b">
         <v>0</v>
@@ -2452,10 +2452,10 @@
         <v>15</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>81</v>
+        <v>322</v>
       </c>
       <c r="K34" t="b">
         <v>0</v>
@@ -2510,7 +2510,7 @@
         <v>15</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I36" s="2" t="s">
         <v>34</v>
@@ -2593,16 +2593,16 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C2" t="s">
+        <v>207</v>
+      </c>
+      <c r="D2" t="s">
         <v>208</v>
-      </c>
-      <c r="D2" t="s">
-        <v>209</v>
       </c>
       <c r="E2">
         <v>1</v>
@@ -2610,16 +2610,16 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C3" t="s">
+        <v>209</v>
+      </c>
+      <c r="D3" t="s">
         <v>210</v>
-      </c>
-      <c r="D3" t="s">
-        <v>211</v>
       </c>
       <c r="E3">
         <v>1</v>
@@ -2627,16 +2627,16 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B4" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C4" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D4" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E4">
         <v>1</v>
@@ -2644,16 +2644,16 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
+        <v>85</v>
+      </c>
+      <c r="B5" t="s">
         <v>86</v>
       </c>
-      <c r="B5" t="s">
-        <v>87</v>
-      </c>
       <c r="C5" t="s">
+        <v>91</v>
+      </c>
+      <c r="D5" t="s">
         <v>92</v>
-      </c>
-      <c r="D5" t="s">
-        <v>93</v>
       </c>
       <c r="E5">
         <v>2</v>
@@ -2695,16 +2695,16 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
+        <v>284</v>
+      </c>
+      <c r="B8" t="s">
         <v>285</v>
       </c>
-      <c r="B8" t="s">
-        <v>286</v>
-      </c>
       <c r="C8" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D8" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="E8">
         <v>1</v>
@@ -2712,16 +2712,16 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
+        <v>284</v>
+      </c>
+      <c r="B9" t="s">
         <v>285</v>
       </c>
-      <c r="B9" t="s">
-        <v>286</v>
-      </c>
       <c r="C9" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D9" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E9">
         <v>1</v>
@@ -2729,16 +2729,16 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
+        <v>284</v>
+      </c>
+      <c r="B10" t="s">
         <v>285</v>
       </c>
-      <c r="B10" t="s">
-        <v>286</v>
-      </c>
       <c r="C10" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="D10" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="E10">
         <v>1</v>
@@ -2746,16 +2746,16 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
+        <v>284</v>
+      </c>
+      <c r="B11" t="s">
         <v>285</v>
       </c>
-      <c r="B11" t="s">
-        <v>286</v>
-      </c>
       <c r="C11" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="D11" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="E11">
         <v>1</v>
@@ -2763,16 +2763,16 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
+        <v>284</v>
+      </c>
+      <c r="B12" t="s">
         <v>285</v>
       </c>
-      <c r="B12" t="s">
-        <v>286</v>
-      </c>
       <c r="C12" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D12" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="E12">
         <v>1</v>
@@ -2780,16 +2780,16 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
+        <v>284</v>
+      </c>
+      <c r="B13" t="s">
         <v>285</v>
       </c>
-      <c r="B13" t="s">
-        <v>286</v>
-      </c>
       <c r="C13" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="D13" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="E13">
         <v>1</v>
@@ -2797,16 +2797,16 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
+        <v>284</v>
+      </c>
+      <c r="B14" t="s">
         <v>285</v>
       </c>
-      <c r="B14" t="s">
-        <v>286</v>
-      </c>
       <c r="C14" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="D14" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="E14">
         <v>1</v>
@@ -2814,16 +2814,16 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
+        <v>96</v>
+      </c>
+      <c r="B15" t="s">
         <v>97</v>
       </c>
-      <c r="B15" t="s">
-        <v>98</v>
-      </c>
       <c r="C15" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D15" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E15">
         <v>1</v>
@@ -2831,16 +2831,16 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
+        <v>96</v>
+      </c>
+      <c r="B16" t="s">
         <v>97</v>
       </c>
-      <c r="B16" t="s">
-        <v>98</v>
-      </c>
       <c r="C16" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D16" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E16">
         <v>1</v>
@@ -2848,16 +2848,16 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
+        <v>96</v>
+      </c>
+      <c r="B17" t="s">
         <v>97</v>
       </c>
-      <c r="B17" t="s">
-        <v>98</v>
-      </c>
       <c r="C17" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D17" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E17">
         <v>1</v>
@@ -2972,10 +2972,10 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B5" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C5">
         <v>1</v>
@@ -2984,15 +2984,15 @@
         <v>0</v>
       </c>
       <c r="E5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B6" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C6">
         <v>2</v>
@@ -3001,15 +3001,15 @@
         <v>0</v>
       </c>
       <c r="E6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B7" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C7">
         <v>3</v>
@@ -3018,15 +3018,15 @@
         <v>0</v>
       </c>
       <c r="E7" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B8" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C8">
         <v>1</v>
@@ -3040,10 +3040,10 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B9" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C9">
         <v>2</v>
@@ -3052,15 +3052,15 @@
         <v>0</v>
       </c>
       <c r="E9" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C10">
         <v>3</v>
@@ -3069,15 +3069,15 @@
         <v>0</v>
       </c>
       <c r="E10" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B11" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C11">
         <v>1</v>
@@ -3091,10 +3091,10 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B12" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C12">
         <v>2</v>
@@ -3103,15 +3103,15 @@
         <v>0</v>
       </c>
       <c r="E12" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B13" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C13">
         <v>3</v>
@@ -3120,15 +3120,15 @@
         <v>0</v>
       </c>
       <c r="E13" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B14" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C14">
         <v>1</v>
@@ -3142,10 +3142,10 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B15" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C15">
         <v>2</v>
@@ -3154,15 +3154,15 @@
         <v>0</v>
       </c>
       <c r="E15" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B16" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C16">
         <v>3</v>
@@ -3171,15 +3171,15 @@
         <v>0</v>
       </c>
       <c r="E16" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B17" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C17">
         <v>1</v>
@@ -3193,10 +3193,10 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B18" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C18">
         <v>2</v>
@@ -3205,15 +3205,15 @@
         <v>0</v>
       </c>
       <c r="E18" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B19" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C19">
         <v>3</v>
@@ -3222,15 +3222,15 @@
         <v>0</v>
       </c>
       <c r="E19" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B20" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C20">
         <v>1</v>
@@ -3239,15 +3239,15 @@
         <v>0</v>
       </c>
       <c r="E20" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B21" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C21">
         <v>2</v>
@@ -3256,15 +3256,15 @@
         <v>0</v>
       </c>
       <c r="E21" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B22" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C22">
         <v>3</v>
@@ -3273,15 +3273,15 @@
         <v>0</v>
       </c>
       <c r="E22" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B23" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C23">
         <v>1</v>
@@ -3290,15 +3290,15 @@
         <v>0</v>
       </c>
       <c r="E23" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B24" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C24">
         <v>2</v>
@@ -3307,15 +3307,15 @@
         <v>0</v>
       </c>
       <c r="E24" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B25" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C25">
         <v>3</v>
@@ -3324,15 +3324,15 @@
         <v>0</v>
       </c>
       <c r="E25" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B26" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C26">
         <v>1</v>
@@ -3341,15 +3341,15 @@
         <v>0</v>
       </c>
       <c r="E26" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B27" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C27">
         <v>2</v>
@@ -3358,15 +3358,15 @@
         <v>0</v>
       </c>
       <c r="E27" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B28" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C28">
         <v>3</v>
@@ -3375,15 +3375,15 @@
         <v>0</v>
       </c>
       <c r="E28" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B29" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C29">
         <v>1</v>
@@ -3392,15 +3392,15 @@
         <v>0</v>
       </c>
       <c r="E29" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B30" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C30">
         <v>2</v>
@@ -3409,15 +3409,15 @@
         <v>0</v>
       </c>
       <c r="E30" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B31" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C31">
         <v>3</v>
@@ -3426,15 +3426,15 @@
         <v>0</v>
       </c>
       <c r="E31" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B32" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C32">
         <v>1</v>
@@ -3443,15 +3443,15 @@
         <v>1</v>
       </c>
       <c r="E32" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B33" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C33">
         <v>2</v>
@@ -3460,15 +3460,15 @@
         <v>0</v>
       </c>
       <c r="E33" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B34" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C34">
         <v>3</v>
@@ -3477,15 +3477,15 @@
         <v>0</v>
       </c>
       <c r="E34" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A35" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B35" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C35">
         <v>1</v>
@@ -3499,10 +3499,10 @@
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A36" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B36" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C36">
         <v>2</v>
@@ -3511,15 +3511,15 @@
         <v>0</v>
       </c>
       <c r="E36" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A37" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B37" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C37">
         <v>3</v>
@@ -3528,12 +3528,12 @@
         <v>0</v>
       </c>
       <c r="E37" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A38" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B38" t="s">
         <v>5</v>
@@ -3550,7 +3550,7 @@
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A39" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B39" t="s">
         <v>5</v>
@@ -3562,12 +3562,12 @@
         <v>0</v>
       </c>
       <c r="E39" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A40" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B40" t="s">
         <v>5</v>
@@ -3579,15 +3579,15 @@
         <v>0</v>
       </c>
       <c r="E40" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A41" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B41" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C41">
         <v>1</v>
@@ -3601,10 +3601,10 @@
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A42" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B42" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C42">
         <v>2</v>
@@ -3613,15 +3613,15 @@
         <v>0</v>
       </c>
       <c r="E42" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A43" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B43" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C43">
         <v>3</v>
@@ -3630,15 +3630,15 @@
         <v>0</v>
       </c>
       <c r="E43" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A44" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B44" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C44">
         <v>1</v>
@@ -3647,15 +3647,15 @@
         <v>0</v>
       </c>
       <c r="E44" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A45" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B45" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C45">
         <v>2</v>
@@ -3664,15 +3664,15 @@
         <v>0</v>
       </c>
       <c r="E45" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A46" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B46" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C46">
         <v>3</v>
@@ -3681,15 +3681,15 @@
         <v>0</v>
       </c>
       <c r="E46" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A47" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B47" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C47">
         <v>1</v>
@@ -3703,10 +3703,10 @@
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A48" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B48" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C48">
         <v>2</v>
@@ -3715,15 +3715,15 @@
         <v>0</v>
       </c>
       <c r="E48" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A49" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B49" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C49">
         <v>3</v>
@@ -3737,10 +3737,10 @@
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A50" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B50" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C50">
         <v>1</v>
@@ -3749,15 +3749,15 @@
         <v>0</v>
       </c>
       <c r="E50" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A51" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B51" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C51">
         <v>2</v>
@@ -3766,15 +3766,15 @@
         <v>0</v>
       </c>
       <c r="E51" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A52" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B52" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C52">
         <v>3</v>
@@ -3783,15 +3783,15 @@
         <v>0</v>
       </c>
       <c r="E52" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A53" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B53" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C53">
         <v>1</v>
@@ -3800,15 +3800,15 @@
         <v>0</v>
       </c>
       <c r="E53" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A54" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B54" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C54">
         <v>2</v>
@@ -3817,15 +3817,15 @@
         <v>0</v>
       </c>
       <c r="E54" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A55" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B55" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C55">
         <v>3</v>
@@ -3834,15 +3834,15 @@
         <v>0</v>
       </c>
       <c r="E55" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A56" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B56" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C56">
         <v>1</v>
@@ -3856,10 +3856,10 @@
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A57" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B57" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C57">
         <v>2</v>
@@ -3868,15 +3868,15 @@
         <v>0</v>
       </c>
       <c r="E57" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A58" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B58" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C58">
         <v>3</v>
@@ -3885,15 +3885,15 @@
         <v>0</v>
       </c>
       <c r="E58" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A59" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B59" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C59">
         <v>1</v>
@@ -3902,15 +3902,15 @@
         <v>0</v>
       </c>
       <c r="E59" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A60" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B60" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C60">
         <v>2</v>
@@ -3919,15 +3919,15 @@
         <v>0</v>
       </c>
       <c r="E60" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A61" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B61" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C61">
         <v>3</v>
@@ -3936,15 +3936,15 @@
         <v>0</v>
       </c>
       <c r="E61" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A62" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B62" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C62">
         <v>1</v>
@@ -3958,10 +3958,10 @@
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A63" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B63" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C63">
         <v>2</v>
@@ -3970,15 +3970,15 @@
         <v>0</v>
       </c>
       <c r="E63" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A64" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B64" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C64">
         <v>3</v>
@@ -3987,15 +3987,15 @@
         <v>0</v>
       </c>
       <c r="E64" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A65" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B65" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C65">
         <v>1</v>
@@ -4004,15 +4004,15 @@
         <v>1</v>
       </c>
       <c r="E65" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A66" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B66" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C66">
         <v>2</v>
@@ -4021,15 +4021,15 @@
         <v>0</v>
       </c>
       <c r="E66" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A67" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B67" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C67">
         <v>3</v>
@@ -4038,15 +4038,15 @@
         <v>0</v>
       </c>
       <c r="E67" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A68" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B68" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C68">
         <v>1</v>
@@ -4055,15 +4055,15 @@
         <v>0</v>
       </c>
       <c r="E68" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A69" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B69" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C69">
         <v>2</v>
@@ -4072,15 +4072,15 @@
         <v>0</v>
       </c>
       <c r="E69" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A70" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B70" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C70">
         <v>3</v>
@@ -4089,16 +4089,16 @@
         <v>0</v>
       </c>
       <c r="E70" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A71" t="s">
+        <v>264</v>
+      </c>
+      <c r="B71" t="s">
         <v>265</v>
       </c>
-      <c r="B71" t="s">
-        <v>266</v>
-      </c>
       <c r="C71">
         <v>1</v>
       </c>
@@ -4106,15 +4106,15 @@
         <v>1</v>
       </c>
       <c r="E71" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A72" t="s">
+        <v>264</v>
+      </c>
+      <c r="B72" t="s">
         <v>265</v>
-      </c>
-      <c r="B72" t="s">
-        <v>266</v>
       </c>
       <c r="C72">
         <v>2</v>
@@ -4123,15 +4123,15 @@
         <v>0</v>
       </c>
       <c r="E72" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A73" t="s">
+        <v>264</v>
+      </c>
+      <c r="B73" t="s">
         <v>265</v>
-      </c>
-      <c r="B73" t="s">
-        <v>266</v>
       </c>
       <c r="C73">
         <v>3</v>
@@ -4140,16 +4140,16 @@
         <v>0</v>
       </c>
       <c r="E73" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A74" t="s">
+        <v>271</v>
+      </c>
+      <c r="B74" t="s">
         <v>272</v>
       </c>
-      <c r="B74" t="s">
-        <v>273</v>
-      </c>
       <c r="C74">
         <v>1</v>
       </c>
@@ -4157,15 +4157,15 @@
         <v>1</v>
       </c>
       <c r="E74" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A75" t="s">
+        <v>271</v>
+      </c>
+      <c r="B75" t="s">
         <v>272</v>
-      </c>
-      <c r="B75" t="s">
-        <v>273</v>
       </c>
       <c r="C75">
         <v>2</v>
@@ -4174,15 +4174,15 @@
         <v>0</v>
       </c>
       <c r="E75" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A76" t="s">
+        <v>271</v>
+      </c>
+      <c r="B76" t="s">
         <v>272</v>
-      </c>
-      <c r="B76" t="s">
-        <v>273</v>
       </c>
       <c r="C76">
         <v>3</v>
@@ -4191,16 +4191,16 @@
         <v>0</v>
       </c>
       <c r="E76" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A77" t="s">
+        <v>85</v>
+      </c>
+      <c r="B77" t="s">
         <v>86</v>
       </c>
-      <c r="B77" t="s">
-        <v>87</v>
-      </c>
       <c r="C77">
         <v>1</v>
       </c>
@@ -4208,15 +4208,15 @@
         <v>1</v>
       </c>
       <c r="E77" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A78" t="s">
+        <v>85</v>
+      </c>
+      <c r="B78" t="s">
         <v>86</v>
-      </c>
-      <c r="B78" t="s">
-        <v>87</v>
       </c>
       <c r="C78">
         <v>2</v>
@@ -4225,15 +4225,15 @@
         <v>0</v>
       </c>
       <c r="E78" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A79" t="s">
+        <v>85</v>
+      </c>
+      <c r="B79" t="s">
         <v>86</v>
-      </c>
-      <c r="B79" t="s">
-        <v>87</v>
       </c>
       <c r="C79">
         <v>3</v>
@@ -4242,16 +4242,16 @@
         <v>0</v>
       </c>
       <c r="E79" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A80" t="s">
+        <v>275</v>
+      </c>
+      <c r="B80" t="s">
         <v>276</v>
       </c>
-      <c r="B80" t="s">
-        <v>277</v>
-      </c>
       <c r="C80">
         <v>1</v>
       </c>
@@ -4259,15 +4259,15 @@
         <v>1</v>
       </c>
       <c r="E80" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A81" t="s">
+        <v>275</v>
+      </c>
+      <c r="B81" t="s">
         <v>276</v>
-      </c>
-      <c r="B81" t="s">
-        <v>277</v>
       </c>
       <c r="C81">
         <v>2</v>
@@ -4276,15 +4276,15 @@
         <v>0</v>
       </c>
       <c r="E81" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A82" t="s">
+        <v>275</v>
+      </c>
+      <c r="B82" t="s">
         <v>276</v>
-      </c>
-      <c r="B82" t="s">
-        <v>277</v>
       </c>
       <c r="C82">
         <v>3</v>
@@ -4293,15 +4293,15 @@
         <v>0</v>
       </c>
       <c r="E82" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A83" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B83" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C83">
         <v>1</v>
@@ -4315,10 +4315,10 @@
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A84" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B84" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C84">
         <v>2</v>
@@ -4327,15 +4327,15 @@
         <v>0</v>
       </c>
       <c r="E84" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A85" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B85" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C85">
         <v>3</v>
@@ -4344,7 +4344,7 @@
         <v>0</v>
       </c>
       <c r="E85" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.45">
@@ -4400,11 +4400,11 @@
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A89" t="s">
+        <v>284</v>
+      </c>
+      <c r="B89" t="s">
         <v>285</v>
       </c>
-      <c r="B89" t="s">
-        <v>286</v>
-      </c>
       <c r="C89">
         <v>1</v>
       </c>
@@ -4412,15 +4412,15 @@
         <v>0</v>
       </c>
       <c r="E89" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A90" t="s">
+        <v>284</v>
+      </c>
+      <c r="B90" t="s">
         <v>285</v>
-      </c>
-      <c r="B90" t="s">
-        <v>286</v>
       </c>
       <c r="C90">
         <v>2</v>
@@ -4429,15 +4429,15 @@
         <v>0</v>
       </c>
       <c r="E90" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A91" t="s">
+        <v>284</v>
+      </c>
+      <c r="B91" t="s">
         <v>285</v>
-      </c>
-      <c r="B91" t="s">
-        <v>286</v>
       </c>
       <c r="C91">
         <v>3</v>
@@ -4446,16 +4446,16 @@
         <v>0</v>
       </c>
       <c r="E91" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A92" t="s">
+        <v>96</v>
+      </c>
+      <c r="B92" t="s">
         <v>97</v>
       </c>
-      <c r="B92" t="s">
-        <v>98</v>
-      </c>
       <c r="C92">
         <v>1</v>
       </c>
@@ -4463,15 +4463,15 @@
         <v>0</v>
       </c>
       <c r="E92" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A93" t="s">
+        <v>96</v>
+      </c>
+      <c r="B93" t="s">
         <v>97</v>
-      </c>
-      <c r="B93" t="s">
-        <v>98</v>
       </c>
       <c r="C93">
         <v>2</v>
@@ -4480,15 +4480,15 @@
         <v>0</v>
       </c>
       <c r="E93" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A94" t="s">
+        <v>96</v>
+      </c>
+      <c r="B94" t="s">
         <v>97</v>
-      </c>
-      <c r="B94" t="s">
-        <v>98</v>
       </c>
       <c r="C94">
         <v>3</v>
@@ -4497,16 +4497,16 @@
         <v>0</v>
       </c>
       <c r="E94" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A95" t="s">
+        <v>314</v>
+      </c>
+      <c r="B95" t="s">
         <v>315</v>
       </c>
-      <c r="B95" t="s">
-        <v>316</v>
-      </c>
       <c r="C95">
         <v>1</v>
       </c>
@@ -4514,15 +4514,15 @@
         <v>1</v>
       </c>
       <c r="E95" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A96" t="s">
+        <v>314</v>
+      </c>
+      <c r="B96" t="s">
         <v>315</v>
-      </c>
-      <c r="B96" t="s">
-        <v>316</v>
       </c>
       <c r="C96">
         <v>2</v>
@@ -4536,10 +4536,10 @@
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A97" t="s">
+        <v>314</v>
+      </c>
+      <c r="B97" t="s">
         <v>315</v>
-      </c>
-      <c r="B97" t="s">
-        <v>316</v>
       </c>
       <c r="C97">
         <v>3</v>
@@ -4548,7 +4548,7 @@
         <v>0</v>
       </c>
       <c r="E97" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.45">
@@ -4565,7 +4565,7 @@
         <v>1</v>
       </c>
       <c r="E98" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.45">
@@ -4582,7 +4582,7 @@
         <v>0</v>
       </c>
       <c r="E99" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.45">
@@ -4599,7 +4599,7 @@
         <v>0</v>
       </c>
       <c r="E100" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.45">

--- a/data/Fate-Spreadsheet.xlsx
+++ b/data/Fate-Spreadsheet.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pixel\Documents\Projects\Fate-Wiki\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Important\Python\Fate-Wiki\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F766361-2887-4A36-9C5B-EE2D635FDC7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{B05E798F-9EF6-4508-A0A4-311D06661AED}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{B05E798F-9EF6-4508-A0A4-311D06661AED}"/>
   </bookViews>
   <sheets>
     <sheet name="Servants" sheetId="1" r:id="rId1"/>
@@ -1401,21 +1401,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E33D7ECC-1EAA-4A40-B4DA-A93E54CBC8B5}">
   <dimension ref="A1:K37"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="17.1328125" customWidth="1"/>
-    <col min="3" max="3" width="21.9296875" customWidth="1"/>
-    <col min="4" max="4" width="12.59765625" customWidth="1"/>
-    <col min="5" max="5" width="11.265625" customWidth="1"/>
-    <col min="6" max="6" width="15.53125" customWidth="1"/>
-    <col min="7" max="7" width="13.73046875" style="2" customWidth="1"/>
-    <col min="8" max="8" width="11.73046875" style="2" customWidth="1"/>
-    <col min="9" max="9" width="11.796875" style="2" customWidth="1"/>
-    <col min="10" max="10" width="48.796875" style="2" customWidth="1"/>
-    <col min="11" max="11" width="12.59765625" customWidth="1"/>
+    <col min="2" max="2" width="17.140625" customWidth="1"/>
+    <col min="3" max="3" width="22" customWidth="1"/>
+    <col min="4" max="4" width="12.5703125" customWidth="1"/>
+    <col min="5" max="5" width="11.28515625" customWidth="1"/>
+    <col min="6" max="6" width="15.5703125" customWidth="1"/>
+    <col min="7" max="7" width="13.7109375" style="2" customWidth="1"/>
+    <col min="8" max="8" width="11.7109375" style="2" customWidth="1"/>
+    <col min="9" max="9" width="11.85546875" style="2" customWidth="1"/>
+    <col min="10" max="10" width="48.85546875" style="2" customWidth="1"/>
+    <col min="11" max="11" width="12.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1450,7 +1450,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -1482,7 +1482,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>111</v>
       </c>
@@ -1514,7 +1514,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>112</v>
       </c>
@@ -1543,7 +1543,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>113</v>
       </c>
@@ -1572,7 +1572,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>114</v>
       </c>
@@ -1604,7 +1604,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>115</v>
       </c>
@@ -1636,7 +1636,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>116</v>
       </c>
@@ -1665,7 +1665,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>117</v>
       </c>
@@ -1694,7 +1694,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>118</v>
       </c>
@@ -1726,7 +1726,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>119</v>
       </c>
@@ -1758,7 +1758,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>120</v>
       </c>
@@ -1790,7 +1790,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>121</v>
       </c>
@@ -1819,7 +1819,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>122</v>
       </c>
@@ -1851,7 +1851,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>123</v>
       </c>
@@ -1883,7 +1883,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>124</v>
       </c>
@@ -1915,7 +1915,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>125</v>
       </c>
@@ -1947,7 +1947,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>126</v>
       </c>
@@ -1979,7 +1979,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>127</v>
       </c>
@@ -2011,7 +2011,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>128</v>
       </c>
@@ -2040,7 +2040,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>129</v>
       </c>
@@ -2072,7 +2072,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>130</v>
       </c>
@@ -2104,7 +2104,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>131</v>
       </c>
@@ -2136,7 +2136,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>132</v>
       </c>
@@ -2168,7 +2168,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>264</v>
       </c>
@@ -2200,7 +2200,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>271</v>
       </c>
@@ -2232,7 +2232,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>85</v>
       </c>
@@ -2261,7 +2261,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>275</v>
       </c>
@@ -2293,7 +2293,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>281</v>
       </c>
@@ -2322,7 +2322,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>17</v>
       </c>
@@ -2348,7 +2348,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>284</v>
       </c>
@@ -2374,7 +2374,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>96</v>
       </c>
@@ -2400,7 +2400,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>314</v>
       </c>
@@ -2429,7 +2429,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>76</v>
       </c>
@@ -2461,7 +2461,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>23</v>
       </c>
@@ -2490,7 +2490,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>29</v>
       </c>
@@ -2522,7 +2522,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>36</v>
       </c>
@@ -2563,15 +2563,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D1BC60D8-44F3-478D-BCC0-4752624457AE}">
   <dimension ref="A1:F18"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="19" customWidth="1"/>
-    <col min="3" max="3" width="15.1328125" customWidth="1"/>
-    <col min="4" max="5" width="16.46484375" customWidth="1"/>
-    <col min="6" max="6" width="13.53125" customWidth="1"/>
+    <col min="3" max="3" width="15.140625" customWidth="1"/>
+    <col min="4" max="5" width="16.42578125" customWidth="1"/>
+    <col min="6" max="6" width="13.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2591,7 +2591,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>116</v>
       </c>
@@ -2608,7 +2608,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>126</v>
       </c>
@@ -2625,7 +2625,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>130</v>
       </c>
@@ -2642,7 +2642,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>85</v>
       </c>
@@ -2659,7 +2659,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>17</v>
       </c>
@@ -2676,7 +2676,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>17</v>
       </c>
@@ -2693,7 +2693,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>284</v>
       </c>
@@ -2710,7 +2710,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>284</v>
       </c>
@@ -2727,7 +2727,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>284</v>
       </c>
@@ -2744,7 +2744,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>284</v>
       </c>
@@ -2761,7 +2761,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>284</v>
       </c>
@@ -2778,7 +2778,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>284</v>
       </c>
@@ -2795,7 +2795,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>284</v>
       </c>
@@ -2812,7 +2812,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>96</v>
       </c>
@@ -2829,7 +2829,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>96</v>
       </c>
@@ -2846,7 +2846,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>96</v>
       </c>
@@ -2863,7 +2863,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>36</v>
       </c>
@@ -2890,16 +2890,16 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84E3BB0D-5578-4069-B1C9-C3864EB2A429}">
   <dimension ref="A1:F109"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="20.59765625" customWidth="1"/>
-    <col min="3" max="3" width="12.73046875" customWidth="1"/>
-    <col min="4" max="4" width="17.06640625" customWidth="1"/>
-    <col min="5" max="5" width="21.59765625" customWidth="1"/>
-    <col min="6" max="6" width="15.73046875" customWidth="1"/>
+    <col min="2" max="2" width="20.5703125" customWidth="1"/>
+    <col min="3" max="3" width="12.7109375" customWidth="1"/>
+    <col min="4" max="4" width="17" customWidth="1"/>
+    <col min="5" max="5" width="21.5703125" customWidth="1"/>
+    <col min="6" max="6" width="15.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2919,7 +2919,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -2936,7 +2936,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -2953,7 +2953,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -2970,7 +2970,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>111</v>
       </c>
@@ -2987,7 +2987,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>111</v>
       </c>
@@ -3004,7 +3004,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>111</v>
       </c>
@@ -3021,7 +3021,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>112</v>
       </c>
@@ -3038,7 +3038,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>112</v>
       </c>
@@ -3055,7 +3055,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>112</v>
       </c>
@@ -3072,7 +3072,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>113</v>
       </c>
@@ -3089,7 +3089,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>113</v>
       </c>
@@ -3106,7 +3106,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>113</v>
       </c>
@@ -3123,7 +3123,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>114</v>
       </c>
@@ -3140,7 +3140,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>114</v>
       </c>
@@ -3157,7 +3157,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>114</v>
       </c>
@@ -3174,7 +3174,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>115</v>
       </c>
@@ -3191,7 +3191,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>115</v>
       </c>
@@ -3208,7 +3208,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>115</v>
       </c>
@@ -3225,7 +3225,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>116</v>
       </c>
@@ -3242,7 +3242,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>116</v>
       </c>
@@ -3259,7 +3259,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>116</v>
       </c>
@@ -3276,7 +3276,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>117</v>
       </c>
@@ -3293,7 +3293,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>117</v>
       </c>
@@ -3310,7 +3310,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>117</v>
       </c>
@@ -3327,7 +3327,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>118</v>
       </c>
@@ -3344,7 +3344,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>118</v>
       </c>
@@ -3361,7 +3361,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>118</v>
       </c>
@@ -3378,7 +3378,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>119</v>
       </c>
@@ -3395,7 +3395,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>119</v>
       </c>
@@ -3412,7 +3412,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>119</v>
       </c>
@@ -3429,7 +3429,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>120</v>
       </c>
@@ -3446,7 +3446,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>120</v>
       </c>
@@ -3463,7 +3463,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>120</v>
       </c>
@@ -3480,7 +3480,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>121</v>
       </c>
@@ -3497,7 +3497,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>121</v>
       </c>
@@ -3514,7 +3514,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>121</v>
       </c>
@@ -3531,7 +3531,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>122</v>
       </c>
@@ -3548,7 +3548,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>122</v>
       </c>
@@ -3565,7 +3565,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>122</v>
       </c>
@@ -3582,7 +3582,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>123</v>
       </c>
@@ -3599,7 +3599,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>123</v>
       </c>
@@ -3616,7 +3616,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>123</v>
       </c>
@@ -3633,7 +3633,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>124</v>
       </c>
@@ -3650,7 +3650,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>124</v>
       </c>
@@ -3667,7 +3667,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>124</v>
       </c>
@@ -3684,7 +3684,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>125</v>
       </c>
@@ -3701,7 +3701,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>125</v>
       </c>
@@ -3718,7 +3718,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>125</v>
       </c>
@@ -3735,7 +3735,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>126</v>
       </c>
@@ -3752,7 +3752,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>126</v>
       </c>
@@ -3769,7 +3769,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>126</v>
       </c>
@@ -3786,7 +3786,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>127</v>
       </c>
@@ -3803,7 +3803,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>127</v>
       </c>
@@ -3820,7 +3820,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>127</v>
       </c>
@@ -3837,7 +3837,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>128</v>
       </c>
@@ -3854,7 +3854,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>128</v>
       </c>
@@ -3871,7 +3871,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>128</v>
       </c>
@@ -3888,7 +3888,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>129</v>
       </c>
@@ -3905,7 +3905,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>129</v>
       </c>
@@ -3922,7 +3922,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>129</v>
       </c>
@@ -3939,7 +3939,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>130</v>
       </c>
@@ -3956,7 +3956,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>130</v>
       </c>
@@ -3973,7 +3973,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>130</v>
       </c>
@@ -3990,7 +3990,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>131</v>
       </c>
@@ -4007,7 +4007,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>131</v>
       </c>
@@ -4024,7 +4024,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>131</v>
       </c>
@@ -4041,7 +4041,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>132</v>
       </c>
@@ -4058,7 +4058,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>132</v>
       </c>
@@ -4075,7 +4075,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>132</v>
       </c>
@@ -4092,7 +4092,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>264</v>
       </c>
@@ -4109,7 +4109,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>264</v>
       </c>
@@ -4126,7 +4126,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>264</v>
       </c>
@@ -4143,7 +4143,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>271</v>
       </c>
@@ -4160,7 +4160,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>271</v>
       </c>
@@ -4177,7 +4177,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>271</v>
       </c>
@@ -4194,7 +4194,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>85</v>
       </c>
@@ -4211,7 +4211,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>85</v>
       </c>
@@ -4228,7 +4228,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>85</v>
       </c>
@@ -4245,7 +4245,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>275</v>
       </c>
@@ -4262,7 +4262,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>275</v>
       </c>
@@ -4279,7 +4279,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>275</v>
       </c>
@@ -4296,7 +4296,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>281</v>
       </c>
@@ -4313,7 +4313,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>281</v>
       </c>
@@ -4330,7 +4330,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>281</v>
       </c>
@@ -4347,7 +4347,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>17</v>
       </c>
@@ -4364,7 +4364,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>17</v>
       </c>
@@ -4381,7 +4381,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>17</v>
       </c>
@@ -4398,7 +4398,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>284</v>
       </c>
@@ -4415,7 +4415,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>284</v>
       </c>
@@ -4432,7 +4432,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>284</v>
       </c>
@@ -4449,7 +4449,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>96</v>
       </c>
@@ -4466,7 +4466,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>96</v>
       </c>
@@ -4483,7 +4483,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>96</v>
       </c>
@@ -4500,7 +4500,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>314</v>
       </c>
@@ -4517,7 +4517,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>314</v>
       </c>
@@ -4534,7 +4534,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>314</v>
       </c>
@@ -4551,7 +4551,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>76</v>
       </c>
@@ -4568,7 +4568,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>76</v>
       </c>
@@ -4585,7 +4585,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>76</v>
       </c>
@@ -4602,7 +4602,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>23</v>
       </c>
@@ -4619,7 +4619,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>23</v>
       </c>
@@ -4636,7 +4636,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>23</v>
       </c>
@@ -4653,7 +4653,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>29</v>
       </c>
@@ -4670,7 +4670,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>29</v>
       </c>
@@ -4687,7 +4687,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>29</v>
       </c>
@@ -4704,7 +4704,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>36</v>
       </c>
@@ -4721,7 +4721,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>36</v>
       </c>
@@ -4738,7 +4738,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>36</v>
       </c>
@@ -4764,7 +4764,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32F3CD10-C054-4484-ABE2-D426F834FC22}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4773,7 +4773,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{931309AC-3B5D-4169-8BD3-83BC320E154C}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/Fate-Spreadsheet.xlsx
+++ b/data/Fate-Spreadsheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Important\Python\Fate-Wiki\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F766361-2887-4A36-9C5B-EE2D635FDC7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74FB2C1B-B3D2-4F80-982D-47219B1EFE02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{B05E798F-9EF6-4508-A0A4-311D06661AED}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="722" uniqueCount="323">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1141" uniqueCount="476">
   <si>
     <t>servant_id</t>
   </si>
@@ -1012,6 +1012,465 @@
   </si>
   <si>
     <t>Berserker_Strength_7,Berserker_Strength_9,Luck,Luck,Surveil</t>
+  </si>
+  <si>
+    <t>S0025</t>
+  </si>
+  <si>
+    <t>Diarmuid Ua Duibhne</t>
+  </si>
+  <si>
+    <t>diarmuid-ua-duibhne</t>
+  </si>
+  <si>
+    <t>3,4,5</t>
+  </si>
+  <si>
+    <t>2,3,3,4,4,4,5,5</t>
+  </si>
+  <si>
+    <t>Surveil</t>
+  </si>
+  <si>
+    <t>S0026</t>
+  </si>
+  <si>
+    <t>S0027</t>
+  </si>
+  <si>
+    <t>S0028</t>
+  </si>
+  <si>
+    <t>S0029</t>
+  </si>
+  <si>
+    <t>S0030</t>
+  </si>
+  <si>
+    <t>S0031</t>
+  </si>
+  <si>
+    <t>S0032</t>
+  </si>
+  <si>
+    <t>S0033</t>
+  </si>
+  <si>
+    <t>S0034</t>
+  </si>
+  <si>
+    <t>S0035</t>
+  </si>
+  <si>
+    <t>S0036</t>
+  </si>
+  <si>
+    <t>S0037</t>
+  </si>
+  <si>
+    <t>S0038</t>
+  </si>
+  <si>
+    <t>S0039</t>
+  </si>
+  <si>
+    <t>S0040</t>
+  </si>
+  <si>
+    <t>S0041</t>
+  </si>
+  <si>
+    <t>S0042</t>
+  </si>
+  <si>
+    <t>S0043</t>
+  </si>
+  <si>
+    <t>S0044</t>
+  </si>
+  <si>
+    <t>S0045</t>
+  </si>
+  <si>
+    <t>S0046</t>
+  </si>
+  <si>
+    <t>Gae Buidhe</t>
+  </si>
+  <si>
+    <t>Gae Dearg</t>
+  </si>
+  <si>
+    <t>Vasavi Shakti</t>
+  </si>
+  <si>
+    <t>Brahmastra Kundala</t>
+  </si>
+  <si>
+    <t>Kavacha &amp; Kundala</t>
+  </si>
+  <si>
+    <t>Karna</t>
+  </si>
+  <si>
+    <t>Vlad Tepes</t>
+  </si>
+  <si>
+    <t>Elizabeth Bathory</t>
+  </si>
+  <si>
+    <t>scathach</t>
+  </si>
+  <si>
+    <t>elizabeth-bathory</t>
+  </si>
+  <si>
+    <t>vlad-tepes</t>
+  </si>
+  <si>
+    <t>karna</t>
+  </si>
+  <si>
+    <t>Valkyrie</t>
+  </si>
+  <si>
+    <t>valkyrie</t>
+  </si>
+  <si>
+    <t>Ereshkigal</t>
+  </si>
+  <si>
+    <t>ereshkigal</t>
+  </si>
+  <si>
+    <t>Enkidu</t>
+  </si>
+  <si>
+    <t>enkidu</t>
+  </si>
+  <si>
+    <t>Meltryllis</t>
+  </si>
+  <si>
+    <t>meltryllis</t>
+  </si>
+  <si>
+    <t>Brynhildr</t>
+  </si>
+  <si>
+    <t>Caenis</t>
+  </si>
+  <si>
+    <t>Leonidas I</t>
+  </si>
+  <si>
+    <t>leonidas-i</t>
+  </si>
+  <si>
+    <t>caenis</t>
+  </si>
+  <si>
+    <t>brynhildr</t>
+  </si>
+  <si>
+    <t>Romulus</t>
+  </si>
+  <si>
+    <t>Jaguar Man</t>
+  </si>
+  <si>
+    <t>Musashibou Benkei</t>
+  </si>
+  <si>
+    <t>Don Quixote</t>
+  </si>
+  <si>
+    <t>The Lion King</t>
+  </si>
+  <si>
+    <t>Bradamante</t>
+  </si>
+  <si>
+    <t>Gareth</t>
+  </si>
+  <si>
+    <t>Nagao Kagetora</t>
+  </si>
+  <si>
+    <t>Parvati</t>
+  </si>
+  <si>
+    <t>romulus</t>
+  </si>
+  <si>
+    <t>bradamante</t>
+  </si>
+  <si>
+    <t>gareth</t>
+  </si>
+  <si>
+    <t>melusine</t>
+  </si>
+  <si>
+    <t>parvati</t>
+  </si>
+  <si>
+    <t>jaguar-man</t>
+  </si>
+  <si>
+    <t>musashibou-benkei</t>
+  </si>
+  <si>
+    <t>don-quixote</t>
+  </si>
+  <si>
+    <t>nagao-kagetora</t>
+  </si>
+  <si>
+    <t>the-lion-king</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>Luck,Surveil,Preparation,Preparation</t>
+  </si>
+  <si>
+    <t>2,2,4</t>
+  </si>
+  <si>
+    <t>Commander Ortlinde</t>
+  </si>
+  <si>
+    <t>Commander Hildr</t>
+  </si>
+  <si>
+    <t>Commander Thrud</t>
+  </si>
+  <si>
+    <t>Commander-Ortlinde</t>
+  </si>
+  <si>
+    <t>Commander-Hildr</t>
+  </si>
+  <si>
+    <t>Commander-Thrud</t>
+  </si>
+  <si>
+    <t>Kazikli Bey</t>
+  </si>
+  <si>
+    <t>Protector of the Nation</t>
+  </si>
+  <si>
+    <t>Prison Castle Csejte</t>
+  </si>
+  <si>
+    <t>Kilenc Sárkány</t>
+  </si>
+  <si>
+    <t>Torture Techniques</t>
+  </si>
+  <si>
+    <t>Scáthach</t>
+  </si>
+  <si>
+    <t>Gate of Skye</t>
+  </si>
+  <si>
+    <t>Gáe Bolg Alternative</t>
+  </si>
+  <si>
+    <t>Wisdom of Dun Scaith</t>
+  </si>
+  <si>
+    <t>Gungnir</t>
+  </si>
+  <si>
+    <t>Ragnarök</t>
+  </si>
+  <si>
+    <t>Svanhvit</t>
+  </si>
+  <si>
+    <t>2,4</t>
+  </si>
+  <si>
+    <t>Kur Kigal Irkalla</t>
+  </si>
+  <si>
+    <t>Blessing of Kur</t>
+  </si>
+  <si>
+    <t>Enuma Elish (Enkidu)</t>
+  </si>
+  <si>
+    <t>Transfiguration</t>
+  </si>
+  <si>
+    <t>Saraswati Meltout</t>
+  </si>
+  <si>
+    <t>Melt Virus</t>
+  </si>
+  <si>
+    <t>Brynhildr Romantia</t>
+  </si>
+  <si>
+    <t>Hero's Bridesmaid</t>
+  </si>
+  <si>
+    <t>Great Golden Wings</t>
+  </si>
+  <si>
+    <t>Poseidon's Favor</t>
+  </si>
+  <si>
+    <t>Poseidon's Maelstrom</t>
+  </si>
+  <si>
+    <t>Thermopylae Enomotia</t>
+  </si>
+  <si>
+    <t>Spartan War Cry</t>
+  </si>
+  <si>
+    <t>Rear Guard's Pride</t>
+  </si>
+  <si>
+    <t>2,2,3,5</t>
+  </si>
+  <si>
+    <t>Luck,Preparation,Preparation,Preparation</t>
+  </si>
+  <si>
+    <t>Magna Voluisse Magnum</t>
+  </si>
+  <si>
+    <t>Moles Necessrie</t>
+  </si>
+  <si>
+    <t>2,2,4,5</t>
+  </si>
+  <si>
+    <t>Luck,Luck,Preparation</t>
+  </si>
+  <si>
+    <t>Great Death Claw</t>
+  </si>
+  <si>
+    <t>Law of the Jungle</t>
+  </si>
+  <si>
+    <t>2,2,4,4,5</t>
+  </si>
+  <si>
+    <t>Bulwark Stance</t>
+  </si>
+  <si>
+    <t>Evenly Matched</t>
+  </si>
+  <si>
+    <t>3,4,5,5,5</t>
+  </si>
+  <si>
+    <t>3,3,3</t>
+  </si>
+  <si>
+    <t>Valiente Asalto</t>
+  </si>
+  <si>
+    <t>Knight's Fantasy</t>
+  </si>
+  <si>
+    <t>2,2,3,4,4</t>
+  </si>
+  <si>
+    <t>Rhongomyniad</t>
+  </si>
+  <si>
+    <t>Divine Command</t>
+  </si>
+  <si>
+    <t>Dun Stallion</t>
+  </si>
+  <si>
+    <t>2,2,3,4,5,5</t>
+  </si>
+  <si>
+    <t>3,4</t>
+  </si>
+  <si>
+    <t>Bouclier d'Atlante</t>
+  </si>
+  <si>
+    <t>Angelica Cathay</t>
+  </si>
+  <si>
+    <t>2,4,4,5</t>
+  </si>
+  <si>
+    <t>Ira Lupus</t>
+  </si>
+  <si>
+    <t>Gun Lance</t>
+  </si>
+  <si>
+    <t>Ring of Transformation</t>
+  </si>
+  <si>
+    <t>8 Phase Wheel Charge</t>
+  </si>
+  <si>
+    <t>God of War</t>
+  </si>
+  <si>
+    <t>2,2,2,3,3</t>
+  </si>
+  <si>
+    <t>4,4,5,5</t>
+  </si>
+  <si>
+    <t>Mélusine</t>
+  </si>
+  <si>
+    <t>Innocence Arondight</t>
+  </si>
+  <si>
+    <t>Ray Horizon</t>
+  </si>
+  <si>
+    <t>Perl Dancer</t>
+  </si>
+  <si>
+    <t>S0047</t>
+  </si>
+  <si>
+    <t>Emiya</t>
+  </si>
+  <si>
+    <t>emiya</t>
+  </si>
+  <si>
+    <t>Trishula Shakti</t>
+  </si>
+  <si>
+    <t>Imaginary Around</t>
+  </si>
+  <si>
+    <t>Ashes of Kama</t>
+  </si>
+  <si>
+    <t>Caladbolg II</t>
+  </si>
+  <si>
+    <t>Unlimited Blade Works</t>
+  </si>
+  <si>
+    <t>Rho Aias</t>
+  </si>
+  <si>
+    <t>4,4,4</t>
   </si>
 </sst>
 </file>
@@ -1400,16 +1859,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E33D7ECC-1EAA-4A40-B4DA-A93E54CBC8B5}">
-  <dimension ref="A1:K37"/>
+  <dimension ref="A1:K60"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="17.140625" customWidth="1"/>
-    <col min="3" max="3" width="22" customWidth="1"/>
+    <col min="2" max="3" width="22" customWidth="1"/>
     <col min="4" max="4" width="12.5703125" customWidth="1"/>
     <col min="5" max="5" width="11.28515625" customWidth="1"/>
     <col min="6" max="6" width="15.5703125" customWidth="1"/>
     <col min="7" max="7" width="13.7109375" style="2" customWidth="1"/>
-    <col min="8" max="8" width="11.7109375" style="2" customWidth="1"/>
+    <col min="8" max="8" width="16.5703125" style="2" customWidth="1"/>
     <col min="9" max="9" width="11.85546875" style="2" customWidth="1"/>
     <col min="10" max="10" width="48.85546875" style="2" customWidth="1"/>
     <col min="11" max="11" width="12.5703125" customWidth="1"/>
@@ -2202,31 +2660,28 @@
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>271</v>
+        <v>323</v>
       </c>
       <c r="B26" t="s">
-        <v>272</v>
+        <v>324</v>
       </c>
       <c r="C26" t="s">
-        <v>273</v>
+        <v>325</v>
       </c>
       <c r="D26" t="s">
-        <v>88</v>
+        <v>267</v>
       </c>
       <c r="E26" t="s">
-        <v>8</v>
+        <v>99</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>27</v>
+        <v>326</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="I26" s="2" t="s">
-        <v>27</v>
+        <v>327</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>274</v>
+        <v>328</v>
       </c>
       <c r="K26" t="b">
         <v>0</v>
@@ -2234,60 +2689,60 @@
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>85</v>
+        <v>329</v>
       </c>
       <c r="B27" t="s">
-        <v>86</v>
+        <v>355</v>
       </c>
       <c r="C27" t="s">
-        <v>87</v>
+        <v>361</v>
       </c>
       <c r="D27" t="s">
-        <v>88</v>
+        <v>267</v>
       </c>
       <c r="E27" t="s">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>15</v>
+        <v>269</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>90</v>
+        <v>204</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>42</v>
+        <v>395</v>
+      </c>
+      <c r="J27" s="2" t="s">
+        <v>200</v>
       </c>
       <c r="K27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>275</v>
+        <v>330</v>
       </c>
       <c r="B28" t="s">
-        <v>276</v>
+        <v>356</v>
       </c>
       <c r="C28" t="s">
-        <v>277</v>
+        <v>360</v>
       </c>
       <c r="D28" t="s">
-        <v>278</v>
+        <v>267</v>
       </c>
       <c r="E28" t="s">
-        <v>8</v>
+        <v>89</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>279</v>
+        <v>100</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="I28" s="2" t="s">
-        <v>280</v>
+        <v>182</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>43</v>
+        <v>396</v>
       </c>
       <c r="K28" t="b">
         <v>0</v>
@@ -2295,28 +2750,31 @@
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>281</v>
+        <v>331</v>
       </c>
       <c r="B29" t="s">
-        <v>249</v>
+        <v>357</v>
       </c>
       <c r="C29" t="s">
-        <v>282</v>
+        <v>359</v>
       </c>
       <c r="D29" t="s">
-        <v>20</v>
+        <v>267</v>
       </c>
       <c r="E29" t="s">
-        <v>33</v>
+        <v>8</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>201</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>27</v>
+        <v>193</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>101</v>
+        <v>15</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>283</v>
+        <v>197</v>
       </c>
       <c r="K29" t="b">
         <v>0</v>
@@ -2324,51 +2782,60 @@
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>17</v>
+        <v>332</v>
       </c>
       <c r="B30" t="s">
-        <v>18</v>
+        <v>409</v>
       </c>
       <c r="C30" t="s">
-        <v>19</v>
+        <v>358</v>
       </c>
       <c r="D30" t="s">
-        <v>20</v>
+        <v>267</v>
       </c>
       <c r="E30" t="s">
-        <v>8</v>
+        <v>99</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>175</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>21</v>
+        <v>176</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>22</v>
+        <v>200</v>
       </c>
       <c r="K30" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>284</v>
+        <v>333</v>
       </c>
       <c r="B31" t="s">
-        <v>285</v>
+        <v>362</v>
       </c>
       <c r="C31" t="s">
-        <v>286</v>
+        <v>363</v>
       </c>
       <c r="D31" t="s">
-        <v>20</v>
+        <v>267</v>
       </c>
       <c r="E31" t="s">
-        <v>8</v>
+        <v>89</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>397</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>287</v>
+        <v>15</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>177</v>
+        <v>197</v>
       </c>
       <c r="K31" t="b">
         <v>1</v>
@@ -2376,54 +2843,63 @@
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>96</v>
+        <v>334</v>
       </c>
       <c r="B32" t="s">
-        <v>97</v>
+        <v>364</v>
       </c>
       <c r="C32" t="s">
-        <v>98</v>
+        <v>365</v>
       </c>
       <c r="D32" t="s">
-        <v>20</v>
+        <v>267</v>
       </c>
       <c r="E32" t="s">
-        <v>99</v>
+        <v>8</v>
+      </c>
+      <c r="G32" s="2" t="s">
+        <v>416</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>100</v>
+        <v>193</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>101</v>
+        <v>269</v>
+      </c>
+      <c r="J32" s="2" t="s">
+        <v>194</v>
       </c>
       <c r="K32" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>314</v>
+        <v>335</v>
       </c>
       <c r="B33" t="s">
-        <v>315</v>
+        <v>366</v>
       </c>
       <c r="C33" t="s">
-        <v>316</v>
+        <v>367</v>
       </c>
       <c r="D33" t="s">
-        <v>317</v>
+        <v>267</v>
       </c>
       <c r="E33" t="s">
-        <v>33</v>
+        <v>89</v>
+      </c>
+      <c r="G33" s="2" t="s">
+        <v>27</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>21</v>
+        <v>190</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>318</v>
+        <v>27</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>319</v>
+        <v>200</v>
       </c>
       <c r="K33" t="b">
         <v>0</v>
@@ -2431,13 +2907,13 @@
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>76</v>
+        <v>336</v>
       </c>
       <c r="B34" t="s">
-        <v>77</v>
+        <v>368</v>
       </c>
       <c r="C34" t="s">
-        <v>78</v>
+        <v>369</v>
       </c>
       <c r="D34" t="s">
         <v>79</v>
@@ -2446,16 +2922,16 @@
         <v>40</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>80</v>
+        <v>191</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>15</v>
+        <v>204</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>81</v>
+        <v>27</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>322</v>
+        <v>186</v>
       </c>
       <c r="K34" t="b">
         <v>0</v>
@@ -2463,28 +2939,31 @@
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>23</v>
+        <v>337</v>
       </c>
       <c r="B35" t="s">
-        <v>24</v>
+        <v>370</v>
       </c>
       <c r="C35" t="s">
-        <v>25</v>
+        <v>375</v>
       </c>
       <c r="D35" t="s">
-        <v>26</v>
+        <v>267</v>
       </c>
       <c r="E35" t="s">
         <v>8</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>27</v>
+        <v>100</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>28</v>
+        <v>176</v>
+      </c>
+      <c r="I35" s="2" t="s">
+        <v>326</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>70</v>
+        <v>188</v>
       </c>
       <c r="K35" t="b">
         <v>0</v>
@@ -2492,31 +2971,28 @@
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>29</v>
+        <v>338</v>
       </c>
       <c r="B36" t="s">
-        <v>30</v>
+        <v>371</v>
       </c>
       <c r="C36" t="s">
-        <v>31</v>
+        <v>374</v>
       </c>
       <c r="D36" t="s">
-        <v>32</v>
+        <v>267</v>
       </c>
       <c r="E36" t="s">
-        <v>33</v>
+        <v>89</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>15</v>
+        <v>175</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="I36" s="2" t="s">
-        <v>34</v>
+        <v>193</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>35</v>
+        <v>179</v>
       </c>
       <c r="K36" t="b">
         <v>0</v>
@@ -2524,30 +3000,727 @@
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>36</v>
+        <v>339</v>
       </c>
       <c r="B37" t="s">
-        <v>37</v>
+        <v>372</v>
       </c>
       <c r="C37" t="s">
-        <v>38</v>
+        <v>373</v>
       </c>
       <c r="D37" t="s">
-        <v>39</v>
+        <v>267</v>
       </c>
       <c r="E37" t="s">
         <v>40</v>
       </c>
       <c r="G37" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="H37" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="J37" s="2" t="s">
+        <v>432</v>
+      </c>
+      <c r="K37" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>340</v>
+      </c>
+      <c r="B38" t="s">
+        <v>376</v>
+      </c>
+      <c r="C38" t="s">
+        <v>385</v>
+      </c>
+      <c r="D38" t="s">
+        <v>267</v>
+      </c>
+      <c r="E38" t="s">
+        <v>99</v>
+      </c>
+      <c r="G38" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>435</v>
+      </c>
+      <c r="I38" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J38" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="K38" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>341</v>
+      </c>
+      <c r="B39" t="s">
+        <v>377</v>
+      </c>
+      <c r="C39" t="s">
+        <v>390</v>
+      </c>
+      <c r="D39" t="s">
+        <v>267</v>
+      </c>
+      <c r="E39" t="s">
+        <v>89</v>
+      </c>
+      <c r="G39" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="H39" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="J39" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="K39" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>342</v>
+      </c>
+      <c r="B40" t="s">
+        <v>378</v>
+      </c>
+      <c r="C40" t="s">
+        <v>391</v>
+      </c>
+      <c r="D40" t="s">
+        <v>267</v>
+      </c>
+      <c r="E40" t="s">
+        <v>89</v>
+      </c>
+      <c r="G40" s="2" t="s">
+        <v>442</v>
+      </c>
+      <c r="H40" s="2" t="s">
+        <v>443</v>
+      </c>
+      <c r="I40" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="J40" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="K40" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>343</v>
+      </c>
+      <c r="B41" t="s">
+        <v>379</v>
+      </c>
+      <c r="C41" t="s">
+        <v>392</v>
+      </c>
+      <c r="D41" t="s">
+        <v>267</v>
+      </c>
+      <c r="E41" t="s">
+        <v>89</v>
+      </c>
+      <c r="G41" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="H41" s="2" t="s">
+        <v>446</v>
+      </c>
+      <c r="J41" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="K41" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>344</v>
+      </c>
+      <c r="B42" t="s">
+        <v>380</v>
+      </c>
+      <c r="C42" t="s">
+        <v>394</v>
+      </c>
+      <c r="D42" t="s">
+        <v>267</v>
+      </c>
+      <c r="E42" t="s">
+        <v>99</v>
+      </c>
+      <c r="G42" s="2" t="s">
+        <v>450</v>
+      </c>
+      <c r="H42" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="I42" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="J42" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="K42" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>345</v>
+      </c>
+      <c r="B43" t="s">
+        <v>381</v>
+      </c>
+      <c r="C43" t="s">
+        <v>386</v>
+      </c>
+      <c r="D43" t="s">
+        <v>267</v>
+      </c>
+      <c r="E43" t="s">
+        <v>40</v>
+      </c>
+      <c r="G43" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="H43" s="2" t="s">
+        <v>454</v>
+      </c>
+      <c r="I43" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="J43" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="K43" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>346</v>
+      </c>
+      <c r="B44" t="s">
+        <v>382</v>
+      </c>
+      <c r="C44" t="s">
+        <v>387</v>
+      </c>
+      <c r="D44" t="s">
+        <v>267</v>
+      </c>
+      <c r="E44" t="s">
+        <v>40</v>
+      </c>
+      <c r="G44" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="H44" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="I44" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="J44" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="K44" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>347</v>
+      </c>
+      <c r="B45" t="s">
+        <v>383</v>
+      </c>
+      <c r="C45" t="s">
+        <v>393</v>
+      </c>
+      <c r="D45" t="s">
+        <v>267</v>
+      </c>
+      <c r="E45" t="s">
+        <v>89</v>
+      </c>
+      <c r="G45" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="H45" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="I45" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="J45" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="K45" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>348</v>
+      </c>
+      <c r="B46" t="s">
+        <v>462</v>
+      </c>
+      <c r="C46" t="s">
+        <v>388</v>
+      </c>
+      <c r="D46" t="s">
+        <v>267</v>
+      </c>
+      <c r="E46" t="s">
+        <v>89</v>
+      </c>
+      <c r="G46" s="2" t="s">
+        <v>443</v>
+      </c>
+      <c r="H46" s="2" t="s">
+        <v>461</v>
+      </c>
+      <c r="I46" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J46" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="K46" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>349</v>
+      </c>
+      <c r="B47" t="s">
+        <v>384</v>
+      </c>
+      <c r="C47" t="s">
+        <v>389</v>
+      </c>
+      <c r="D47" t="s">
+        <v>267</v>
+      </c>
+      <c r="E47" t="s">
+        <v>89</v>
+      </c>
+      <c r="G47" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="H47" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="I47" s="2" t="s">
+        <v>475</v>
+      </c>
+      <c r="J47" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="K47" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>466</v>
+      </c>
+      <c r="B48" t="s">
+        <v>467</v>
+      </c>
+      <c r="C48" t="s">
+        <v>468</v>
+      </c>
+      <c r="D48" t="s">
+        <v>88</v>
+      </c>
+      <c r="E48" t="s">
+        <v>99</v>
+      </c>
+      <c r="G48" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H48" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I48" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="J48" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="K48" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>271</v>
+      </c>
+      <c r="B49" t="s">
+        <v>272</v>
+      </c>
+      <c r="C49" t="s">
+        <v>273</v>
+      </c>
+      <c r="D49" t="s">
+        <v>88</v>
+      </c>
+      <c r="E49" t="s">
+        <v>8</v>
+      </c>
+      <c r="G49" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="H49" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="I49" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="J49" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="K49" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>85</v>
+      </c>
+      <c r="B50" t="s">
+        <v>86</v>
+      </c>
+      <c r="C50" t="s">
+        <v>87</v>
+      </c>
+      <c r="D50" t="s">
+        <v>88</v>
+      </c>
+      <c r="E50" t="s">
+        <v>89</v>
+      </c>
+      <c r="G50" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H50" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="I50" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="K50" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>275</v>
+      </c>
+      <c r="B51" t="s">
+        <v>276</v>
+      </c>
+      <c r="C51" t="s">
+        <v>277</v>
+      </c>
+      <c r="D51" t="s">
+        <v>278</v>
+      </c>
+      <c r="E51" t="s">
+        <v>8</v>
+      </c>
+      <c r="G51" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="H51" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="I51" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="J51" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K51" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>281</v>
+      </c>
+      <c r="B52" t="s">
+        <v>249</v>
+      </c>
+      <c r="C52" t="s">
+        <v>282</v>
+      </c>
+      <c r="D52" t="s">
+        <v>20</v>
+      </c>
+      <c r="E52" t="s">
+        <v>33</v>
+      </c>
+      <c r="H52" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="I52" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="J52" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="K52" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>17</v>
+      </c>
+      <c r="B53" t="s">
+        <v>18</v>
+      </c>
+      <c r="C53" t="s">
+        <v>19</v>
+      </c>
+      <c r="D53" t="s">
+        <v>20</v>
+      </c>
+      <c r="E53" t="s">
+        <v>8</v>
+      </c>
+      <c r="I53" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="J53" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="K53" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>284</v>
+      </c>
+      <c r="B54" t="s">
+        <v>285</v>
+      </c>
+      <c r="C54" t="s">
+        <v>286</v>
+      </c>
+      <c r="D54" t="s">
+        <v>20</v>
+      </c>
+      <c r="E54" t="s">
+        <v>8</v>
+      </c>
+      <c r="I54" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="J54" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="K54" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>96</v>
+      </c>
+      <c r="B55" t="s">
+        <v>97</v>
+      </c>
+      <c r="C55" t="s">
+        <v>98</v>
+      </c>
+      <c r="D55" t="s">
+        <v>20</v>
+      </c>
+      <c r="E55" t="s">
+        <v>99</v>
+      </c>
+      <c r="H55" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="I55" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="K55" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>314</v>
+      </c>
+      <c r="B56" t="s">
+        <v>315</v>
+      </c>
+      <c r="C56" t="s">
+        <v>316</v>
+      </c>
+      <c r="D56" t="s">
+        <v>317</v>
+      </c>
+      <c r="E56" t="s">
+        <v>33</v>
+      </c>
+      <c r="H56" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I56" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="J56" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="K56" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>76</v>
+      </c>
+      <c r="B57" t="s">
+        <v>77</v>
+      </c>
+      <c r="C57" t="s">
+        <v>78</v>
+      </c>
+      <c r="D57" t="s">
+        <v>79</v>
+      </c>
+      <c r="E57" t="s">
+        <v>40</v>
+      </c>
+      <c r="G57" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="H57" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I57" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="J57" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="K57" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>23</v>
+      </c>
+      <c r="B58" t="s">
+        <v>24</v>
+      </c>
+      <c r="C58" t="s">
+        <v>25</v>
+      </c>
+      <c r="D58" t="s">
+        <v>26</v>
+      </c>
+      <c r="E58" t="s">
+        <v>8</v>
+      </c>
+      <c r="G58" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="H58" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J58" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="K58" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>29</v>
+      </c>
+      <c r="B59" t="s">
+        <v>30</v>
+      </c>
+      <c r="C59" t="s">
+        <v>31</v>
+      </c>
+      <c r="D59" t="s">
+        <v>32</v>
+      </c>
+      <c r="E59" t="s">
+        <v>33</v>
+      </c>
+      <c r="G59" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H59" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="I59" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="J59" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="K59" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>36</v>
+      </c>
+      <c r="B60" t="s">
+        <v>37</v>
+      </c>
+      <c r="C60" t="s">
+        <v>38</v>
+      </c>
+      <c r="D60" t="s">
+        <v>39</v>
+      </c>
+      <c r="E60" t="s">
+        <v>40</v>
+      </c>
+      <c r="G60" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="H37" s="2" t="s">
+      <c r="H60" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="J37" s="2" t="s">
+      <c r="J60" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="K37" t="b">
+      <c r="K60" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2555,19 +3728,20 @@
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="H2 I34 H36 I6:I7 I10 I12 H14 I18 I22 I24" numberStoredAsText="1"/>
+    <ignoredError sqref="H2 I6:I7 I10 I12 H14 I18 I22 I24 I27 G34 I40 I42 I45" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D1BC60D8-44F3-478D-BCC0-4752624457AE}">
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="19" customWidth="1"/>
-    <col min="3" max="3" width="15.140625" customWidth="1"/>
-    <col min="4" max="5" width="16.42578125" customWidth="1"/>
+    <col min="3" max="3" width="25.5703125" customWidth="1"/>
+    <col min="4" max="4" width="23.42578125" customWidth="1"/>
+    <col min="5" max="5" width="16.42578125" customWidth="1"/>
     <col min="6" max="6" width="13.5703125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2644,104 +3818,104 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>85</v>
+        <v>333</v>
       </c>
       <c r="B5" t="s">
-        <v>86</v>
+        <v>362</v>
       </c>
       <c r="C5" t="s">
-        <v>91</v>
+        <v>398</v>
       </c>
       <c r="D5" t="s">
-        <v>92</v>
+        <v>401</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>17</v>
+        <v>333</v>
       </c>
       <c r="B6" t="s">
-        <v>18</v>
+        <v>362</v>
       </c>
       <c r="C6" t="s">
-        <v>47</v>
+        <v>399</v>
       </c>
       <c r="D6" t="s">
-        <v>72</v>
+        <v>402</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>17</v>
+        <v>333</v>
       </c>
       <c r="B7" t="s">
-        <v>18</v>
+        <v>362</v>
       </c>
       <c r="C7" t="s">
-        <v>73</v>
+        <v>400</v>
       </c>
       <c r="D7" t="s">
-        <v>74</v>
+        <v>403</v>
       </c>
       <c r="E7">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>284</v>
+        <v>85</v>
       </c>
       <c r="B8" t="s">
-        <v>285</v>
+        <v>86</v>
       </c>
       <c r="C8" t="s">
-        <v>288</v>
+        <v>91</v>
       </c>
       <c r="D8" t="s">
-        <v>295</v>
+        <v>92</v>
       </c>
       <c r="E8">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>284</v>
+        <v>17</v>
       </c>
       <c r="B9" t="s">
-        <v>285</v>
+        <v>18</v>
       </c>
       <c r="C9" t="s">
-        <v>289</v>
+        <v>47</v>
       </c>
       <c r="D9" t="s">
-        <v>296</v>
+        <v>72</v>
       </c>
       <c r="E9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>284</v>
+        <v>17</v>
       </c>
       <c r="B10" t="s">
-        <v>285</v>
+        <v>18</v>
       </c>
       <c r="C10" t="s">
-        <v>290</v>
+        <v>73</v>
       </c>
       <c r="D10" t="s">
-        <v>297</v>
+        <v>74</v>
       </c>
       <c r="E10">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -2752,10 +3926,10 @@
         <v>285</v>
       </c>
       <c r="C11" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="D11" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="E11">
         <v>1</v>
@@ -2769,10 +3943,10 @@
         <v>285</v>
       </c>
       <c r="C12" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="D12" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="E12">
         <v>1</v>
@@ -2786,10 +3960,10 @@
         <v>285</v>
       </c>
       <c r="C13" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="D13" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="E13">
         <v>1</v>
@@ -2803,10 +3977,10 @@
         <v>285</v>
       </c>
       <c r="C14" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="D14" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="E14">
         <v>1</v>
@@ -2814,16 +3988,16 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>96</v>
+        <v>284</v>
       </c>
       <c r="B15" t="s">
-        <v>97</v>
+        <v>285</v>
       </c>
       <c r="C15" t="s">
-        <v>102</v>
+        <v>292</v>
       </c>
       <c r="D15" t="s">
-        <v>105</v>
+        <v>299</v>
       </c>
       <c r="E15">
         <v>1</v>
@@ -2831,16 +4005,16 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>96</v>
+        <v>284</v>
       </c>
       <c r="B16" t="s">
-        <v>97</v>
+        <v>285</v>
       </c>
       <c r="C16" t="s">
-        <v>103</v>
+        <v>293</v>
       </c>
       <c r="D16" t="s">
-        <v>106</v>
+        <v>300</v>
       </c>
       <c r="E16">
         <v>1</v>
@@ -2848,16 +4022,16 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>96</v>
+        <v>284</v>
       </c>
       <c r="B17" t="s">
-        <v>97</v>
+        <v>285</v>
       </c>
       <c r="C17" t="s">
-        <v>104</v>
+        <v>294</v>
       </c>
       <c r="D17" t="s">
-        <v>107</v>
+        <v>301</v>
       </c>
       <c r="E17">
         <v>1</v>
@@ -2865,18 +4039,69 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
+        <v>96</v>
+      </c>
+      <c r="B18" t="s">
+        <v>97</v>
+      </c>
+      <c r="C18" t="s">
+        <v>102</v>
+      </c>
+      <c r="D18" t="s">
+        <v>105</v>
+      </c>
+      <c r="E18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>96</v>
+      </c>
+      <c r="B19" t="s">
+        <v>97</v>
+      </c>
+      <c r="C19" t="s">
+        <v>103</v>
+      </c>
+      <c r="D19" t="s">
+        <v>106</v>
+      </c>
+      <c r="E19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>96</v>
+      </c>
+      <c r="B20" t="s">
+        <v>97</v>
+      </c>
+      <c r="C20" t="s">
+        <v>104</v>
+      </c>
+      <c r="D20" t="s">
+        <v>107</v>
+      </c>
+      <c r="E20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
         <v>36</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B21" t="s">
         <v>37</v>
       </c>
-      <c r="C18" t="s">
+      <c r="C21" t="s">
         <v>48</v>
       </c>
-      <c r="D18" t="s">
+      <c r="D21" t="s">
         <v>48</v>
       </c>
-      <c r="E18">
+      <c r="E21">
         <v>2</v>
       </c>
     </row>
@@ -2889,13 +4114,13 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84E3BB0D-5578-4069-B1C9-C3864EB2A429}">
-  <dimension ref="A1:F109"/>
+  <dimension ref="A1:F178"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="20.5703125" customWidth="1"/>
     <col min="3" max="3" width="12.7109375" customWidth="1"/>
     <col min="4" max="4" width="17" customWidth="1"/>
-    <col min="5" max="5" width="21.5703125" customWidth="1"/>
+    <col min="5" max="5" width="23.5703125" customWidth="1"/>
     <col min="6" max="6" width="15.7109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4145,10 +5370,10 @@
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>271</v>
+        <v>323</v>
       </c>
       <c r="B74" t="s">
-        <v>272</v>
+        <v>324</v>
       </c>
       <c r="C74">
         <v>1</v>
@@ -4157,15 +5382,15 @@
         <v>1</v>
       </c>
       <c r="E74" t="s">
-        <v>93</v>
+        <v>302</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>271</v>
+        <v>323</v>
       </c>
       <c r="B75" t="s">
-        <v>272</v>
+        <v>324</v>
       </c>
       <c r="C75">
         <v>2</v>
@@ -4174,15 +5399,15 @@
         <v>0</v>
       </c>
       <c r="E75" t="s">
-        <v>304</v>
+        <v>350</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>271</v>
+        <v>323</v>
       </c>
       <c r="B76" t="s">
-        <v>272</v>
+        <v>324</v>
       </c>
       <c r="C76">
         <v>3</v>
@@ -4191,32 +5416,32 @@
         <v>0</v>
       </c>
       <c r="E76" t="s">
-        <v>305</v>
+        <v>351</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>85</v>
+        <v>329</v>
       </c>
       <c r="B77" t="s">
-        <v>86</v>
+        <v>355</v>
       </c>
       <c r="C77">
         <v>1</v>
       </c>
       <c r="D77" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E77" t="s">
-        <v>93</v>
+        <v>352</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>85</v>
+        <v>329</v>
       </c>
       <c r="B78" t="s">
-        <v>86</v>
+        <v>355</v>
       </c>
       <c r="C78">
         <v>2</v>
@@ -4225,15 +5450,15 @@
         <v>0</v>
       </c>
       <c r="E78" t="s">
-        <v>94</v>
+        <v>353</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>85</v>
+        <v>329</v>
       </c>
       <c r="B79" t="s">
-        <v>86</v>
+        <v>355</v>
       </c>
       <c r="C79">
         <v>3</v>
@@ -4242,15 +5467,15 @@
         <v>0</v>
       </c>
       <c r="E79" t="s">
-        <v>95</v>
+        <v>354</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>275</v>
+        <v>330</v>
       </c>
       <c r="B80" t="s">
-        <v>276</v>
+        <v>356</v>
       </c>
       <c r="C80">
         <v>1</v>
@@ -4259,15 +5484,15 @@
         <v>1</v>
       </c>
       <c r="E80" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>275</v>
+        <v>330</v>
       </c>
       <c r="B81" t="s">
-        <v>276</v>
+        <v>356</v>
       </c>
       <c r="C81">
         <v>2</v>
@@ -4276,15 +5501,15 @@
         <v>0</v>
       </c>
       <c r="E81" t="s">
-        <v>307</v>
+        <v>404</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>275</v>
+        <v>330</v>
       </c>
       <c r="B82" t="s">
-        <v>276</v>
+        <v>356</v>
       </c>
       <c r="C82">
         <v>3</v>
@@ -4293,32 +5518,32 @@
         <v>0</v>
       </c>
       <c r="E82" t="s">
-        <v>308</v>
+        <v>405</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>281</v>
+        <v>331</v>
       </c>
       <c r="B83" t="s">
-        <v>249</v>
+        <v>357</v>
       </c>
       <c r="C83">
         <v>1</v>
       </c>
       <c r="D83" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E83" t="s">
-        <v>58</v>
+        <v>406</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>281</v>
+        <v>331</v>
       </c>
       <c r="B84" t="s">
-        <v>249</v>
+        <v>357</v>
       </c>
       <c r="C84">
         <v>2</v>
@@ -4327,15 +5552,15 @@
         <v>0</v>
       </c>
       <c r="E84" t="s">
-        <v>309</v>
+        <v>407</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>281</v>
+        <v>331</v>
       </c>
       <c r="B85" t="s">
-        <v>249</v>
+        <v>357</v>
       </c>
       <c r="C85">
         <v>3</v>
@@ -4344,32 +5569,32 @@
         <v>0</v>
       </c>
       <c r="E85" t="s">
-        <v>310</v>
+        <v>408</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>17</v>
+        <v>332</v>
       </c>
       <c r="B86" t="s">
-        <v>18</v>
+        <v>409</v>
       </c>
       <c r="C86">
         <v>1</v>
       </c>
       <c r="D86" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E86" t="s">
-        <v>58</v>
+        <v>410</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>17</v>
+        <v>332</v>
       </c>
       <c r="B87" t="s">
-        <v>18</v>
+        <v>409</v>
       </c>
       <c r="C87">
         <v>2</v>
@@ -4378,15 +5603,15 @@
         <v>0</v>
       </c>
       <c r="E87" t="s">
-        <v>59</v>
+        <v>411</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>17</v>
+        <v>332</v>
       </c>
       <c r="B88" t="s">
-        <v>18</v>
+        <v>409</v>
       </c>
       <c r="C88">
         <v>3</v>
@@ -4395,15 +5620,15 @@
         <v>0</v>
       </c>
       <c r="E88" t="s">
-        <v>60</v>
+        <v>412</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>284</v>
+        <v>333</v>
       </c>
       <c r="B89" t="s">
-        <v>285</v>
+        <v>362</v>
       </c>
       <c r="C89">
         <v>1</v>
@@ -4412,15 +5637,15 @@
         <v>0</v>
       </c>
       <c r="E89" t="s">
-        <v>311</v>
+        <v>413</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>284</v>
+        <v>333</v>
       </c>
       <c r="B90" t="s">
-        <v>285</v>
+        <v>362</v>
       </c>
       <c r="C90">
         <v>2</v>
@@ -4429,15 +5654,15 @@
         <v>0</v>
       </c>
       <c r="E90" t="s">
-        <v>312</v>
+        <v>414</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>284</v>
+        <v>333</v>
       </c>
       <c r="B91" t="s">
-        <v>285</v>
+        <v>362</v>
       </c>
       <c r="C91">
         <v>3</v>
@@ -4446,32 +5671,32 @@
         <v>0</v>
       </c>
       <c r="E91" t="s">
-        <v>313</v>
+        <v>415</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>96</v>
+        <v>334</v>
       </c>
       <c r="B92" t="s">
-        <v>97</v>
+        <v>364</v>
       </c>
       <c r="C92">
         <v>1</v>
       </c>
       <c r="D92" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E92" t="s">
-        <v>108</v>
+        <v>302</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>96</v>
+        <v>334</v>
       </c>
       <c r="B93" t="s">
-        <v>97</v>
+        <v>364</v>
       </c>
       <c r="C93">
         <v>2</v>
@@ -4480,15 +5705,15 @@
         <v>0</v>
       </c>
       <c r="E93" t="s">
-        <v>109</v>
+        <v>417</v>
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>96</v>
+        <v>334</v>
       </c>
       <c r="B94" t="s">
-        <v>97</v>
+        <v>364</v>
       </c>
       <c r="C94">
         <v>3</v>
@@ -4497,15 +5722,15 @@
         <v>0</v>
       </c>
       <c r="E94" t="s">
-        <v>110</v>
+        <v>418</v>
       </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>314</v>
+        <v>335</v>
       </c>
       <c r="B95" t="s">
-        <v>315</v>
+        <v>366</v>
       </c>
       <c r="C95">
         <v>1</v>
@@ -4514,32 +5739,32 @@
         <v>1</v>
       </c>
       <c r="E95" t="s">
-        <v>320</v>
+        <v>302</v>
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>314</v>
+        <v>335</v>
       </c>
       <c r="B96" t="s">
-        <v>315</v>
+        <v>366</v>
       </c>
       <c r="C96">
         <v>2</v>
       </c>
       <c r="D96" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E96" t="s">
-        <v>58</v>
+        <v>419</v>
       </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>314</v>
+        <v>335</v>
       </c>
       <c r="B97" t="s">
-        <v>315</v>
+        <v>366</v>
       </c>
       <c r="C97">
         <v>3</v>
@@ -4548,15 +5773,15 @@
         <v>0</v>
       </c>
       <c r="E97" t="s">
-        <v>321</v>
+        <v>420</v>
       </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>76</v>
+        <v>336</v>
       </c>
       <c r="B98" t="s">
-        <v>77</v>
+        <v>368</v>
       </c>
       <c r="C98">
         <v>1</v>
@@ -4570,10 +5795,10 @@
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>76</v>
+        <v>336</v>
       </c>
       <c r="B99" t="s">
-        <v>77</v>
+        <v>368</v>
       </c>
       <c r="C99">
         <v>2</v>
@@ -4582,15 +5807,15 @@
         <v>0</v>
       </c>
       <c r="E99" t="s">
-        <v>83</v>
+        <v>421</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>76</v>
+        <v>336</v>
       </c>
       <c r="B100" t="s">
-        <v>77</v>
+        <v>368</v>
       </c>
       <c r="C100">
         <v>3</v>
@@ -4599,32 +5824,32 @@
         <v>0</v>
       </c>
       <c r="E100" t="s">
-        <v>84</v>
+        <v>422</v>
       </c>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>23</v>
+        <v>337</v>
       </c>
       <c r="B101" t="s">
-        <v>24</v>
+        <v>370</v>
       </c>
       <c r="C101">
         <v>1</v>
       </c>
       <c r="D101" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E101" t="s">
-        <v>61</v>
+        <v>302</v>
       </c>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>23</v>
+        <v>337</v>
       </c>
       <c r="B102" t="s">
-        <v>24</v>
+        <v>370</v>
       </c>
       <c r="C102">
         <v>2</v>
@@ -4633,15 +5858,15 @@
         <v>0</v>
       </c>
       <c r="E102" t="s">
-        <v>62</v>
+        <v>423</v>
       </c>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>23</v>
+        <v>337</v>
       </c>
       <c r="B103" t="s">
-        <v>24</v>
+        <v>370</v>
       </c>
       <c r="C103">
         <v>3</v>
@@ -4650,15 +5875,15 @@
         <v>0</v>
       </c>
       <c r="E103" t="s">
-        <v>63</v>
+        <v>424</v>
       </c>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>29</v>
+        <v>338</v>
       </c>
       <c r="B104" t="s">
-        <v>30</v>
+        <v>371</v>
       </c>
       <c r="C104">
         <v>1</v>
@@ -4667,15 +5892,15 @@
         <v>0</v>
       </c>
       <c r="E104" t="s">
-        <v>64</v>
+        <v>425</v>
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>29</v>
+        <v>338</v>
       </c>
       <c r="B105" t="s">
-        <v>30</v>
+        <v>371</v>
       </c>
       <c r="C105">
         <v>2</v>
@@ -4684,15 +5909,15 @@
         <v>0</v>
       </c>
       <c r="E105" t="s">
-        <v>65</v>
+        <v>426</v>
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>29</v>
+        <v>338</v>
       </c>
       <c r="B106" t="s">
-        <v>30</v>
+        <v>371</v>
       </c>
       <c r="C106">
         <v>3</v>
@@ -4701,15 +5926,15 @@
         <v>0</v>
       </c>
       <c r="E106" t="s">
-        <v>66</v>
+        <v>427</v>
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>36</v>
+        <v>339</v>
       </c>
       <c r="B107" t="s">
-        <v>37</v>
+        <v>372</v>
       </c>
       <c r="C107">
         <v>1</v>
@@ -4718,15 +5943,15 @@
         <v>0</v>
       </c>
       <c r="E107" t="s">
-        <v>67</v>
+        <v>428</v>
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>36</v>
+        <v>339</v>
       </c>
       <c r="B108" t="s">
-        <v>37</v>
+        <v>372</v>
       </c>
       <c r="C108">
         <v>2</v>
@@ -4735,15 +5960,15 @@
         <v>0</v>
       </c>
       <c r="E108" t="s">
-        <v>68</v>
+        <v>429</v>
       </c>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>36</v>
+        <v>339</v>
       </c>
       <c r="B109" t="s">
-        <v>37</v>
+        <v>372</v>
       </c>
       <c r="C109">
         <v>3</v>
@@ -4752,6 +5977,1179 @@
         <v>0</v>
       </c>
       <c r="E109" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>340</v>
+      </c>
+      <c r="B110" t="s">
+        <v>376</v>
+      </c>
+      <c r="C110">
+        <v>1</v>
+      </c>
+      <c r="D110" t="b">
+        <v>1</v>
+      </c>
+      <c r="E110" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>340</v>
+      </c>
+      <c r="B111" t="s">
+        <v>376</v>
+      </c>
+      <c r="C111">
+        <v>2</v>
+      </c>
+      <c r="D111" t="b">
+        <v>0</v>
+      </c>
+      <c r="E111" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>340</v>
+      </c>
+      <c r="B112" t="s">
+        <v>376</v>
+      </c>
+      <c r="C112">
+        <v>3</v>
+      </c>
+      <c r="D112" t="b">
+        <v>0</v>
+      </c>
+      <c r="E112" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>341</v>
+      </c>
+      <c r="B113" t="s">
+        <v>377</v>
+      </c>
+      <c r="C113">
+        <v>1</v>
+      </c>
+      <c r="D113" t="b">
+        <v>1</v>
+      </c>
+      <c r="E113" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>341</v>
+      </c>
+      <c r="B114" t="s">
+        <v>377</v>
+      </c>
+      <c r="C114">
+        <v>2</v>
+      </c>
+      <c r="D114" t="b">
+        <v>0</v>
+      </c>
+      <c r="E114" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>341</v>
+      </c>
+      <c r="B115" t="s">
+        <v>377</v>
+      </c>
+      <c r="C115">
+        <v>3</v>
+      </c>
+      <c r="D115" t="b">
+        <v>0</v>
+      </c>
+      <c r="E115" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>342</v>
+      </c>
+      <c r="B116" t="s">
+        <v>378</v>
+      </c>
+      <c r="C116">
+        <v>1</v>
+      </c>
+      <c r="D116" t="b">
+        <v>1</v>
+      </c>
+      <c r="E116" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>342</v>
+      </c>
+      <c r="B117" t="s">
+        <v>378</v>
+      </c>
+      <c r="C117">
+        <v>2</v>
+      </c>
+      <c r="D117" t="b">
+        <v>0</v>
+      </c>
+      <c r="E117" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>342</v>
+      </c>
+      <c r="B118" t="s">
+        <v>378</v>
+      </c>
+      <c r="C118">
+        <v>3</v>
+      </c>
+      <c r="D118" t="b">
+        <v>0</v>
+      </c>
+      <c r="E118" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>343</v>
+      </c>
+      <c r="B119" t="s">
+        <v>379</v>
+      </c>
+      <c r="C119">
+        <v>1</v>
+      </c>
+      <c r="D119" t="b">
+        <v>1</v>
+      </c>
+      <c r="E119" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>343</v>
+      </c>
+      <c r="B120" t="s">
+        <v>379</v>
+      </c>
+      <c r="C120">
+        <v>2</v>
+      </c>
+      <c r="D120" t="b">
+        <v>0</v>
+      </c>
+      <c r="E120" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>343</v>
+      </c>
+      <c r="B121" t="s">
+        <v>379</v>
+      </c>
+      <c r="C121">
+        <v>3</v>
+      </c>
+      <c r="D121" t="b">
+        <v>0</v>
+      </c>
+      <c r="E121" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>344</v>
+      </c>
+      <c r="B122" t="s">
+        <v>380</v>
+      </c>
+      <c r="C122">
+        <v>1</v>
+      </c>
+      <c r="D122" t="b">
+        <v>0</v>
+      </c>
+      <c r="E122" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>344</v>
+      </c>
+      <c r="B123" t="s">
+        <v>380</v>
+      </c>
+      <c r="C123">
+        <v>2</v>
+      </c>
+      <c r="D123" t="b">
+        <v>0</v>
+      </c>
+      <c r="E123" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>344</v>
+      </c>
+      <c r="B124" t="s">
+        <v>380</v>
+      </c>
+      <c r="C124">
+        <v>3</v>
+      </c>
+      <c r="D124" t="b">
+        <v>0</v>
+      </c>
+      <c r="E124" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>345</v>
+      </c>
+      <c r="B125" t="s">
+        <v>381</v>
+      </c>
+      <c r="C125">
+        <v>1</v>
+      </c>
+      <c r="D125" t="b">
+        <v>1</v>
+      </c>
+      <c r="E125" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>345</v>
+      </c>
+      <c r="B126" t="s">
+        <v>381</v>
+      </c>
+      <c r="C126">
+        <v>2</v>
+      </c>
+      <c r="D126" t="b">
+        <v>0</v>
+      </c>
+      <c r="E126" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>345</v>
+      </c>
+      <c r="B127" t="s">
+        <v>381</v>
+      </c>
+      <c r="C127">
+        <v>3</v>
+      </c>
+      <c r="D127" t="b">
+        <v>0</v>
+      </c>
+      <c r="E127" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="128" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>346</v>
+      </c>
+      <c r="B128" t="s">
+        <v>382</v>
+      </c>
+      <c r="C128">
+        <v>1</v>
+      </c>
+      <c r="D128" t="b">
+        <v>0</v>
+      </c>
+      <c r="E128" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="129" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>346</v>
+      </c>
+      <c r="B129" t="s">
+        <v>382</v>
+      </c>
+      <c r="C129">
+        <v>2</v>
+      </c>
+      <c r="D129" t="b">
+        <v>0</v>
+      </c>
+      <c r="E129" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="130" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>346</v>
+      </c>
+      <c r="B130" t="s">
+        <v>382</v>
+      </c>
+      <c r="C130">
+        <v>3</v>
+      </c>
+      <c r="D130" t="b">
+        <v>0</v>
+      </c>
+      <c r="E130" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="131" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
+        <v>347</v>
+      </c>
+      <c r="B131" t="s">
+        <v>383</v>
+      </c>
+      <c r="C131">
+        <v>1</v>
+      </c>
+      <c r="D131" t="b">
+        <v>1</v>
+      </c>
+      <c r="E131" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="132" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>347</v>
+      </c>
+      <c r="B132" t="s">
+        <v>383</v>
+      </c>
+      <c r="C132">
+        <v>2</v>
+      </c>
+      <c r="D132" t="b">
+        <v>0</v>
+      </c>
+      <c r="E132" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="133" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
+        <v>347</v>
+      </c>
+      <c r="B133" t="s">
+        <v>383</v>
+      </c>
+      <c r="C133">
+        <v>3</v>
+      </c>
+      <c r="D133" t="b">
+        <v>0</v>
+      </c>
+      <c r="E133" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="134" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
+        <v>348</v>
+      </c>
+      <c r="B134" t="s">
+        <v>462</v>
+      </c>
+      <c r="C134">
+        <v>1</v>
+      </c>
+      <c r="D134" t="b">
+        <v>0</v>
+      </c>
+      <c r="E134" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="135" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
+        <v>348</v>
+      </c>
+      <c r="B135" t="s">
+        <v>462</v>
+      </c>
+      <c r="C135">
+        <v>2</v>
+      </c>
+      <c r="D135" t="b">
+        <v>0</v>
+      </c>
+      <c r="E135" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="136" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
+        <v>348</v>
+      </c>
+      <c r="B136" t="s">
+        <v>462</v>
+      </c>
+      <c r="C136">
+        <v>3</v>
+      </c>
+      <c r="D136" t="b">
+        <v>0</v>
+      </c>
+      <c r="E136" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="137" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
+        <v>349</v>
+      </c>
+      <c r="B137" t="s">
+        <v>384</v>
+      </c>
+      <c r="C137">
+        <v>1</v>
+      </c>
+      <c r="D137" t="b">
+        <v>0</v>
+      </c>
+      <c r="E137" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="138" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
+        <v>349</v>
+      </c>
+      <c r="B138" t="s">
+        <v>384</v>
+      </c>
+      <c r="C138">
+        <v>2</v>
+      </c>
+      <c r="D138" t="b">
+        <v>0</v>
+      </c>
+      <c r="E138" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="139" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A139" t="s">
+        <v>349</v>
+      </c>
+      <c r="B139" t="s">
+        <v>384</v>
+      </c>
+      <c r="C139">
+        <v>3</v>
+      </c>
+      <c r="D139" t="b">
+        <v>0</v>
+      </c>
+      <c r="E139" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="140" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A140" t="s">
+        <v>466</v>
+      </c>
+      <c r="B140" t="s">
+        <v>467</v>
+      </c>
+      <c r="C140">
+        <v>1</v>
+      </c>
+      <c r="D140" t="b">
+        <v>0</v>
+      </c>
+      <c r="E140" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="141" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A141" t="s">
+        <v>466</v>
+      </c>
+      <c r="B141" t="s">
+        <v>467</v>
+      </c>
+      <c r="C141">
+        <v>2</v>
+      </c>
+      <c r="D141" t="b">
+        <v>0</v>
+      </c>
+      <c r="E141" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="142" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A142" t="s">
+        <v>466</v>
+      </c>
+      <c r="B142" t="s">
+        <v>467</v>
+      </c>
+      <c r="C142">
+        <v>3</v>
+      </c>
+      <c r="D142" t="b">
+        <v>0</v>
+      </c>
+      <c r="E142" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="143" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A143" t="s">
+        <v>271</v>
+      </c>
+      <c r="B143" t="s">
+        <v>272</v>
+      </c>
+      <c r="C143">
+        <v>1</v>
+      </c>
+      <c r="D143" t="b">
+        <v>1</v>
+      </c>
+      <c r="E143" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="144" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A144" t="s">
+        <v>271</v>
+      </c>
+      <c r="B144" t="s">
+        <v>272</v>
+      </c>
+      <c r="C144">
+        <v>2</v>
+      </c>
+      <c r="D144" t="b">
+        <v>0</v>
+      </c>
+      <c r="E144" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="145" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A145" t="s">
+        <v>271</v>
+      </c>
+      <c r="B145" t="s">
+        <v>272</v>
+      </c>
+      <c r="C145">
+        <v>3</v>
+      </c>
+      <c r="D145" t="b">
+        <v>0</v>
+      </c>
+      <c r="E145" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="146" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A146" t="s">
+        <v>85</v>
+      </c>
+      <c r="B146" t="s">
+        <v>86</v>
+      </c>
+      <c r="C146">
+        <v>1</v>
+      </c>
+      <c r="D146" t="b">
+        <v>1</v>
+      </c>
+      <c r="E146" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="147" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A147" t="s">
+        <v>85</v>
+      </c>
+      <c r="B147" t="s">
+        <v>86</v>
+      </c>
+      <c r="C147">
+        <v>2</v>
+      </c>
+      <c r="D147" t="b">
+        <v>0</v>
+      </c>
+      <c r="E147" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="148" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A148" t="s">
+        <v>85</v>
+      </c>
+      <c r="B148" t="s">
+        <v>86</v>
+      </c>
+      <c r="C148">
+        <v>3</v>
+      </c>
+      <c r="D148" t="b">
+        <v>0</v>
+      </c>
+      <c r="E148" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="149" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A149" t="s">
+        <v>275</v>
+      </c>
+      <c r="B149" t="s">
+        <v>276</v>
+      </c>
+      <c r="C149">
+        <v>1</v>
+      </c>
+      <c r="D149" t="b">
+        <v>1</v>
+      </c>
+      <c r="E149" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="150" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A150" t="s">
+        <v>275</v>
+      </c>
+      <c r="B150" t="s">
+        <v>276</v>
+      </c>
+      <c r="C150">
+        <v>2</v>
+      </c>
+      <c r="D150" t="b">
+        <v>0</v>
+      </c>
+      <c r="E150" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="151" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A151" t="s">
+        <v>275</v>
+      </c>
+      <c r="B151" t="s">
+        <v>276</v>
+      </c>
+      <c r="C151">
+        <v>3</v>
+      </c>
+      <c r="D151" t="b">
+        <v>0</v>
+      </c>
+      <c r="E151" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="152" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A152" t="s">
+        <v>281</v>
+      </c>
+      <c r="B152" t="s">
+        <v>249</v>
+      </c>
+      <c r="C152">
+        <v>1</v>
+      </c>
+      <c r="D152" t="b">
+        <v>1</v>
+      </c>
+      <c r="E152" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="153" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A153" t="s">
+        <v>281</v>
+      </c>
+      <c r="B153" t="s">
+        <v>249</v>
+      </c>
+      <c r="C153">
+        <v>2</v>
+      </c>
+      <c r="D153" t="b">
+        <v>0</v>
+      </c>
+      <c r="E153" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="154" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A154" t="s">
+        <v>281</v>
+      </c>
+      <c r="B154" t="s">
+        <v>249</v>
+      </c>
+      <c r="C154">
+        <v>3</v>
+      </c>
+      <c r="D154" t="b">
+        <v>0</v>
+      </c>
+      <c r="E154" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="155" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A155" t="s">
+        <v>17</v>
+      </c>
+      <c r="B155" t="s">
+        <v>18</v>
+      </c>
+      <c r="C155">
+        <v>1</v>
+      </c>
+      <c r="D155" t="b">
+        <v>1</v>
+      </c>
+      <c r="E155" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="156" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A156" t="s">
+        <v>17</v>
+      </c>
+      <c r="B156" t="s">
+        <v>18</v>
+      </c>
+      <c r="C156">
+        <v>2</v>
+      </c>
+      <c r="D156" t="b">
+        <v>0</v>
+      </c>
+      <c r="E156" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="157" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A157" t="s">
+        <v>17</v>
+      </c>
+      <c r="B157" t="s">
+        <v>18</v>
+      </c>
+      <c r="C157">
+        <v>3</v>
+      </c>
+      <c r="D157" t="b">
+        <v>0</v>
+      </c>
+      <c r="E157" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="158" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A158" t="s">
+        <v>284</v>
+      </c>
+      <c r="B158" t="s">
+        <v>285</v>
+      </c>
+      <c r="C158">
+        <v>1</v>
+      </c>
+      <c r="D158" t="b">
+        <v>0</v>
+      </c>
+      <c r="E158" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="159" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A159" t="s">
+        <v>284</v>
+      </c>
+      <c r="B159" t="s">
+        <v>285</v>
+      </c>
+      <c r="C159">
+        <v>2</v>
+      </c>
+      <c r="D159" t="b">
+        <v>0</v>
+      </c>
+      <c r="E159" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="160" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A160" t="s">
+        <v>284</v>
+      </c>
+      <c r="B160" t="s">
+        <v>285</v>
+      </c>
+      <c r="C160">
+        <v>3</v>
+      </c>
+      <c r="D160" t="b">
+        <v>0</v>
+      </c>
+      <c r="E160" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="161" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A161" t="s">
+        <v>96</v>
+      </c>
+      <c r="B161" t="s">
+        <v>97</v>
+      </c>
+      <c r="C161">
+        <v>1</v>
+      </c>
+      <c r="D161" t="b">
+        <v>0</v>
+      </c>
+      <c r="E161" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="162" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A162" t="s">
+        <v>96</v>
+      </c>
+      <c r="B162" t="s">
+        <v>97</v>
+      </c>
+      <c r="C162">
+        <v>2</v>
+      </c>
+      <c r="D162" t="b">
+        <v>0</v>
+      </c>
+      <c r="E162" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="163" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A163" t="s">
+        <v>96</v>
+      </c>
+      <c r="B163" t="s">
+        <v>97</v>
+      </c>
+      <c r="C163">
+        <v>3</v>
+      </c>
+      <c r="D163" t="b">
+        <v>0</v>
+      </c>
+      <c r="E163" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="164" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A164" t="s">
+        <v>314</v>
+      </c>
+      <c r="B164" t="s">
+        <v>315</v>
+      </c>
+      <c r="C164">
+        <v>1</v>
+      </c>
+      <c r="D164" t="b">
+        <v>1</v>
+      </c>
+      <c r="E164" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="165" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A165" t="s">
+        <v>314</v>
+      </c>
+      <c r="B165" t="s">
+        <v>315</v>
+      </c>
+      <c r="C165">
+        <v>2</v>
+      </c>
+      <c r="D165" t="b">
+        <v>1</v>
+      </c>
+      <c r="E165" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="166" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A166" t="s">
+        <v>314</v>
+      </c>
+      <c r="B166" t="s">
+        <v>315</v>
+      </c>
+      <c r="C166">
+        <v>3</v>
+      </c>
+      <c r="D166" t="b">
+        <v>0</v>
+      </c>
+      <c r="E166" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="167" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A167" t="s">
+        <v>76</v>
+      </c>
+      <c r="B167" t="s">
+        <v>77</v>
+      </c>
+      <c r="C167">
+        <v>1</v>
+      </c>
+      <c r="D167" t="b">
+        <v>1</v>
+      </c>
+      <c r="E167" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="168" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A168" t="s">
+        <v>76</v>
+      </c>
+      <c r="B168" t="s">
+        <v>77</v>
+      </c>
+      <c r="C168">
+        <v>2</v>
+      </c>
+      <c r="D168" t="b">
+        <v>0</v>
+      </c>
+      <c r="E168" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="169" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A169" t="s">
+        <v>76</v>
+      </c>
+      <c r="B169" t="s">
+        <v>77</v>
+      </c>
+      <c r="C169">
+        <v>3</v>
+      </c>
+      <c r="D169" t="b">
+        <v>0</v>
+      </c>
+      <c r="E169" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="170" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A170" t="s">
+        <v>23</v>
+      </c>
+      <c r="B170" t="s">
+        <v>24</v>
+      </c>
+      <c r="C170">
+        <v>1</v>
+      </c>
+      <c r="D170" t="b">
+        <v>0</v>
+      </c>
+      <c r="E170" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="171" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A171" t="s">
+        <v>23</v>
+      </c>
+      <c r="B171" t="s">
+        <v>24</v>
+      </c>
+      <c r="C171">
+        <v>2</v>
+      </c>
+      <c r="D171" t="b">
+        <v>0</v>
+      </c>
+      <c r="E171" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="172" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A172" t="s">
+        <v>23</v>
+      </c>
+      <c r="B172" t="s">
+        <v>24</v>
+      </c>
+      <c r="C172">
+        <v>3</v>
+      </c>
+      <c r="D172" t="b">
+        <v>0</v>
+      </c>
+      <c r="E172" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="173" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A173" t="s">
+        <v>29</v>
+      </c>
+      <c r="B173" t="s">
+        <v>30</v>
+      </c>
+      <c r="C173">
+        <v>1</v>
+      </c>
+      <c r="D173" t="b">
+        <v>0</v>
+      </c>
+      <c r="E173" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="174" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A174" t="s">
+        <v>29</v>
+      </c>
+      <c r="B174" t="s">
+        <v>30</v>
+      </c>
+      <c r="C174">
+        <v>2</v>
+      </c>
+      <c r="D174" t="b">
+        <v>0</v>
+      </c>
+      <c r="E174" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="175" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A175" t="s">
+        <v>29</v>
+      </c>
+      <c r="B175" t="s">
+        <v>30</v>
+      </c>
+      <c r="C175">
+        <v>3</v>
+      </c>
+      <c r="D175" t="b">
+        <v>0</v>
+      </c>
+      <c r="E175" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="176" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A176" t="s">
+        <v>36</v>
+      </c>
+      <c r="B176" t="s">
+        <v>37</v>
+      </c>
+      <c r="C176">
+        <v>1</v>
+      </c>
+      <c r="D176" t="b">
+        <v>0</v>
+      </c>
+      <c r="E176" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="177" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A177" t="s">
+        <v>36</v>
+      </c>
+      <c r="B177" t="s">
+        <v>37</v>
+      </c>
+      <c r="C177">
+        <v>2</v>
+      </c>
+      <c r="D177" t="b">
+        <v>0</v>
+      </c>
+      <c r="E177" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="178" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A178" t="s">
+        <v>36</v>
+      </c>
+      <c r="B178" t="s">
+        <v>37</v>
+      </c>
+      <c r="C178">
+        <v>3</v>
+      </c>
+      <c r="D178" t="b">
+        <v>0</v>
+      </c>
+      <c r="E178" t="s">
         <v>69</v>
       </c>
     </row>

--- a/data/Fate-Spreadsheet.xlsx
+++ b/data/Fate-Spreadsheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Important\Python\Fate-Wiki\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74FB2C1B-B3D2-4F80-982D-47219B1EFE02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAE09173-3834-4445-B317-789F4733B023}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{B05E798F-9EF6-4508-A0A4-311D06661AED}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1141" uniqueCount="476">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1515" uniqueCount="622">
   <si>
     <t>servant_id</t>
   </si>
@@ -1471,6 +1471,444 @@
   </si>
   <si>
     <t>4,4,4</t>
+  </si>
+  <si>
+    <t>S0049</t>
+  </si>
+  <si>
+    <t>S0050</t>
+  </si>
+  <si>
+    <t>S0051</t>
+  </si>
+  <si>
+    <t>S0052</t>
+  </si>
+  <si>
+    <t>S0053</t>
+  </si>
+  <si>
+    <t>S0054</t>
+  </si>
+  <si>
+    <t>S0055</t>
+  </si>
+  <si>
+    <t>S0056</t>
+  </si>
+  <si>
+    <t>S0057</t>
+  </si>
+  <si>
+    <t>S0058</t>
+  </si>
+  <si>
+    <t>S0059</t>
+  </si>
+  <si>
+    <t>S0060</t>
+  </si>
+  <si>
+    <t>S0061</t>
+  </si>
+  <si>
+    <t>S0062</t>
+  </si>
+  <si>
+    <t>S0063</t>
+  </si>
+  <si>
+    <t>S0064</t>
+  </si>
+  <si>
+    <t>S0065</t>
+  </si>
+  <si>
+    <t>S0066</t>
+  </si>
+  <si>
+    <t>S0067</t>
+  </si>
+  <si>
+    <t>S0068</t>
+  </si>
+  <si>
+    <t>Oda Nobunaga</t>
+  </si>
+  <si>
+    <t>oda-nobunaga</t>
+  </si>
+  <si>
+    <t>Atalanta</t>
+  </si>
+  <si>
+    <t>Chiron</t>
+  </si>
+  <si>
+    <t>Robin Hood</t>
+  </si>
+  <si>
+    <t>Arjuna</t>
+  </si>
+  <si>
+    <t>Ishtar</t>
+  </si>
+  <si>
+    <t>Mecha Eli-chan</t>
+  </si>
+  <si>
+    <t>Arash</t>
+  </si>
+  <si>
+    <t>Nikola Tesla</t>
+  </si>
+  <si>
+    <t>Billy the Kid</t>
+  </si>
+  <si>
+    <t>Napoleon Bonaparte</t>
+  </si>
+  <si>
+    <t>Chloe von Einzbern</t>
+  </si>
+  <si>
+    <t>Tristan</t>
+  </si>
+  <si>
+    <t>Emiya Shirou</t>
+  </si>
+  <si>
+    <t>emiya-shirou-alter</t>
+  </si>
+  <si>
+    <t>Baobhan Sith</t>
+  </si>
+  <si>
+    <t>Tomoe Gozen</t>
+  </si>
+  <si>
+    <t>Orion</t>
+  </si>
+  <si>
+    <t>James Moriarty</t>
+  </si>
+  <si>
+    <t>Sei Shounagon</t>
+  </si>
+  <si>
+    <t>atalanta</t>
+  </si>
+  <si>
+    <t>chiron</t>
+  </si>
+  <si>
+    <t>arjuna</t>
+  </si>
+  <si>
+    <t>ishtar</t>
+  </si>
+  <si>
+    <t>arash</t>
+  </si>
+  <si>
+    <t>tristan</t>
+  </si>
+  <si>
+    <t>asvatthama</t>
+  </si>
+  <si>
+    <t>orion</t>
+  </si>
+  <si>
+    <t>robin-hood</t>
+  </si>
+  <si>
+    <t>nikola-tesla</t>
+  </si>
+  <si>
+    <t>napoleon-bonaparte</t>
+  </si>
+  <si>
+    <t>baobhan-sith</t>
+  </si>
+  <si>
+    <t>tomoe-gozen</t>
+  </si>
+  <si>
+    <t>james-moriarty</t>
+  </si>
+  <si>
+    <t>sei-shounagon</t>
+  </si>
+  <si>
+    <t>mecha-eli-chan</t>
+  </si>
+  <si>
+    <t>billy-the-kid</t>
+  </si>
+  <si>
+    <t>chloe-von-einzbern</t>
+  </si>
+  <si>
+    <t>S0071</t>
+  </si>
+  <si>
+    <t>S0072</t>
+  </si>
+  <si>
+    <t>S0073</t>
+  </si>
+  <si>
+    <t>S0074</t>
+  </si>
+  <si>
+    <t>S0075</t>
+  </si>
+  <si>
+    <t>S0076</t>
+  </si>
+  <si>
+    <t>S0077</t>
+  </si>
+  <si>
+    <t>S0078</t>
+  </si>
+  <si>
+    <t>S0079</t>
+  </si>
+  <si>
+    <t>S0080</t>
+  </si>
+  <si>
+    <t>S0081</t>
+  </si>
+  <si>
+    <t>S0082</t>
+  </si>
+  <si>
+    <t>S0083</t>
+  </si>
+  <si>
+    <t>S0084</t>
+  </si>
+  <si>
+    <t>S0085</t>
+  </si>
+  <si>
+    <t>S0086</t>
+  </si>
+  <si>
+    <t>S0087</t>
+  </si>
+  <si>
+    <t>S0088</t>
+  </si>
+  <si>
+    <t>S0089</t>
+  </si>
+  <si>
+    <t>S0090</t>
+  </si>
+  <si>
+    <t>S0091</t>
+  </si>
+  <si>
+    <t>S0092</t>
+  </si>
+  <si>
+    <t>2,3,4,4,4</t>
+  </si>
+  <si>
+    <t>Preparation,Preparation,Preparation</t>
+  </si>
+  <si>
+    <t>2,2,3,4,4,4</t>
+  </si>
+  <si>
+    <t>Preparation,Preparation,Surveil</t>
+  </si>
+  <si>
+    <t>2,2,5,5</t>
+  </si>
+  <si>
+    <t>2,2,3,5,5</t>
+  </si>
+  <si>
+    <t>2,2,3,3,3,4</t>
+  </si>
+  <si>
+    <t>Surveil,Surveil,Preparation</t>
+  </si>
+  <si>
+    <t>5,5,5,5</t>
+  </si>
+  <si>
+    <t>2,5,5</t>
+  </si>
+  <si>
+    <t>3,4,5,5</t>
+  </si>
+  <si>
+    <t>2,2,3,3,4</t>
+  </si>
+  <si>
+    <t>5,5,5</t>
+  </si>
+  <si>
+    <t>Luck,Luck,Surveil,Surveil,Preparation</t>
+  </si>
+  <si>
+    <t>Three Line Formation</t>
+  </si>
+  <si>
+    <t>Papiyas</t>
+  </si>
+  <si>
+    <t>Fool of Owari</t>
+  </si>
+  <si>
+    <t>Phoebus Catastrophe</t>
+  </si>
+  <si>
+    <t>Agrius Metamorphosis</t>
+  </si>
+  <si>
+    <t>Antares Snipe</t>
+  </si>
+  <si>
+    <t>Divine Wisdom</t>
+  </si>
+  <si>
+    <t>Yew Bow</t>
+  </si>
+  <si>
+    <t>No Face May King</t>
+  </si>
+  <si>
+    <t>Pashupata</t>
+  </si>
+  <si>
+    <t>Agni Gandiva</t>
+  </si>
+  <si>
+    <t>The Endowed Hero</t>
+  </si>
+  <si>
+    <t>An Gal Ta Kigal She</t>
+  </si>
+  <si>
+    <t>Divine Authority</t>
+  </si>
+  <si>
+    <t>Breast Zero</t>
+  </si>
+  <si>
+    <t>Rocket Fists</t>
+  </si>
+  <si>
+    <t>Stella</t>
+  </si>
+  <si>
+    <t>Solemn Prayer</t>
+  </si>
+  <si>
+    <t>Clairvoyance</t>
+  </si>
+  <si>
+    <t>System Keraunos</t>
+  </si>
+  <si>
+    <t>System Keraunos (Overload)</t>
+  </si>
+  <si>
+    <t>Transhumanism</t>
+  </si>
+  <si>
+    <t>Thunderer (Attack)</t>
+  </si>
+  <si>
+    <t>Thunderer (Passive)</t>
+  </si>
+  <si>
+    <t>Quick Draw</t>
+  </si>
+  <si>
+    <t>Arc de Triomphe</t>
+  </si>
+  <si>
+    <t>Hidden Trump Card</t>
+  </si>
+  <si>
+    <t>Kanshou &amp; Bakuya (Chloe)</t>
+  </si>
+  <si>
+    <t>Projection Magic</t>
+  </si>
+  <si>
+    <t>Unlimited Blade Works (Chloe)</t>
+  </si>
+  <si>
+    <t>Failnaught</t>
+  </si>
+  <si>
+    <t>Soothing Serenade</t>
+  </si>
+  <si>
+    <t>Aśvatthāma</t>
+  </si>
+  <si>
+    <t>Sudarshan Chakra</t>
+  </si>
+  <si>
+    <t>Mahakala Shakti</t>
+  </si>
+  <si>
+    <t>Avatar of Rage</t>
+  </si>
+  <si>
+    <t>Kanshou &amp; Bakuya (Alter)</t>
+  </si>
+  <si>
+    <t>Unlimited Lost Works</t>
+  </si>
+  <si>
+    <t>Fetch Failnaught</t>
+  </si>
+  <si>
+    <t>Part Collector</t>
+  </si>
+  <si>
+    <t>On Arorikya Sowaka</t>
+  </si>
+  <si>
+    <t>Oni Raiders</t>
+  </si>
+  <si>
+    <t>Aegis Eclipse</t>
+  </si>
+  <si>
+    <t>Divine Embrace</t>
+  </si>
+  <si>
+    <t>Moontouched Hunter</t>
+  </si>
+  <si>
+    <t>Dynamics of an Asteroid</t>
+  </si>
+  <si>
+    <t>Wicked Charisma</t>
+  </si>
+  <si>
+    <t>In the Spider's Web</t>
+  </si>
+  <si>
+    <t>Emotional Engine</t>
+  </si>
+  <si>
+    <t>Vivid Sensation</t>
+  </si>
+  <si>
+    <t>Nostalgia Drive</t>
   </si>
 </sst>
 </file>
@@ -1859,7 +2297,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E33D7ECC-1EAA-4A40-B4DA-A93E54CBC8B5}">
-  <dimension ref="A1:K60"/>
+  <dimension ref="A1:K102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="3" width="22" customWidth="1"/>
@@ -3407,60 +3845,57 @@
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>85</v>
+        <v>476</v>
       </c>
       <c r="B50" t="s">
-        <v>86</v>
+        <v>496</v>
       </c>
       <c r="C50" t="s">
-        <v>87</v>
+        <v>497</v>
       </c>
       <c r="D50" t="s">
         <v>88</v>
       </c>
       <c r="E50" t="s">
-        <v>89</v>
+        <v>8</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>15</v>
+        <v>431</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="I50" s="2" t="s">
-        <v>42</v>
+        <v>557</v>
+      </c>
+      <c r="J50" s="2" t="s">
+        <v>558</v>
       </c>
       <c r="K50" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>275</v>
+        <v>477</v>
       </c>
       <c r="B51" t="s">
-        <v>276</v>
+        <v>498</v>
       </c>
       <c r="C51" t="s">
-        <v>277</v>
+        <v>517</v>
       </c>
       <c r="D51" t="s">
-        <v>278</v>
+        <v>88</v>
       </c>
       <c r="E51" t="s">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>279</v>
+        <v>100</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="I51" s="2" t="s">
-        <v>280</v>
+        <v>559</v>
       </c>
       <c r="J51" s="2" t="s">
-        <v>43</v>
+        <v>560</v>
       </c>
       <c r="K51" t="b">
         <v>0</v>
@@ -3468,28 +3903,31 @@
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>281</v>
+        <v>478</v>
       </c>
       <c r="B52" t="s">
-        <v>249</v>
+        <v>499</v>
       </c>
       <c r="C52" t="s">
-        <v>282</v>
+        <v>518</v>
       </c>
       <c r="D52" t="s">
-        <v>20</v>
+        <v>88</v>
       </c>
       <c r="E52" t="s">
         <v>33</v>
       </c>
+      <c r="G52" s="2" t="s">
+        <v>561</v>
+      </c>
       <c r="H52" s="2" t="s">
-        <v>27</v>
+        <v>562</v>
       </c>
       <c r="I52" s="2" t="s">
-        <v>101</v>
+        <v>191</v>
       </c>
       <c r="J52" s="2" t="s">
-        <v>283</v>
+        <v>188</v>
       </c>
       <c r="K52" t="b">
         <v>0</v>
@@ -3497,106 +3935,124 @@
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>17</v>
+        <v>479</v>
       </c>
       <c r="B53" t="s">
-        <v>18</v>
+        <v>500</v>
       </c>
       <c r="C53" t="s">
-        <v>19</v>
+        <v>525</v>
       </c>
       <c r="D53" t="s">
-        <v>20</v>
+        <v>88</v>
       </c>
       <c r="E53" t="s">
-        <v>8</v>
+        <v>33</v>
+      </c>
+      <c r="H53" s="2" t="s">
+        <v>563</v>
       </c>
       <c r="I53" s="2" t="s">
-        <v>21</v>
+        <v>100</v>
       </c>
       <c r="J53" s="2" t="s">
         <v>22</v>
       </c>
       <c r="K53" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>284</v>
+        <v>480</v>
       </c>
       <c r="B54" t="s">
-        <v>285</v>
+        <v>501</v>
       </c>
       <c r="C54" t="s">
-        <v>286</v>
+        <v>519</v>
       </c>
       <c r="D54" t="s">
-        <v>20</v>
+        <v>88</v>
       </c>
       <c r="E54" t="s">
-        <v>8</v>
+        <v>89</v>
+      </c>
+      <c r="G54" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="H54" s="2" t="s">
+        <v>176</v>
       </c>
       <c r="I54" s="2" t="s">
-        <v>287</v>
+        <v>15</v>
       </c>
       <c r="J54" s="2" t="s">
-        <v>177</v>
+        <v>200</v>
       </c>
       <c r="K54" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>96</v>
+        <v>481</v>
       </c>
       <c r="B55" t="s">
-        <v>97</v>
+        <v>502</v>
       </c>
       <c r="C55" t="s">
-        <v>98</v>
+        <v>520</v>
       </c>
       <c r="D55" t="s">
-        <v>20</v>
+        <v>88</v>
       </c>
       <c r="E55" t="s">
-        <v>99</v>
+        <v>33</v>
+      </c>
+      <c r="G55" s="2" t="s">
+        <v>15</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>100</v>
+        <v>27</v>
       </c>
       <c r="I55" s="2" t="s">
-        <v>101</v>
+        <v>454</v>
+      </c>
+      <c r="J55" s="2" t="s">
+        <v>564</v>
       </c>
       <c r="K55" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>314</v>
+        <v>482</v>
       </c>
       <c r="B56" t="s">
-        <v>315</v>
+        <v>503</v>
       </c>
       <c r="C56" t="s">
-        <v>316</v>
+        <v>532</v>
       </c>
       <c r="D56" t="s">
-        <v>317</v>
+        <v>79</v>
       </c>
       <c r="E56" t="s">
-        <v>33</v>
+        <v>8</v>
+      </c>
+      <c r="G56" s="2" t="s">
+        <v>279</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>21</v>
+        <v>397</v>
       </c>
       <c r="I56" s="2" t="s">
-        <v>318</v>
+        <v>27</v>
       </c>
       <c r="J56" s="2" t="s">
-        <v>319</v>
+        <v>186</v>
       </c>
       <c r="K56" t="b">
         <v>0</v>
@@ -3604,31 +4060,28 @@
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>76</v>
+        <v>483</v>
       </c>
       <c r="B57" t="s">
-        <v>77</v>
+        <v>504</v>
       </c>
       <c r="C57" t="s">
-        <v>78</v>
+        <v>521</v>
       </c>
       <c r="D57" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="E57" t="s">
-        <v>40</v>
+        <v>99</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>80</v>
+        <v>176</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I57" s="2" t="s">
-        <v>81</v>
+        <v>204</v>
       </c>
       <c r="J57" s="2" t="s">
-        <v>322</v>
+        <v>186</v>
       </c>
       <c r="K57" t="b">
         <v>0</v>
@@ -3636,28 +4089,31 @@
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>23</v>
+        <v>484</v>
       </c>
       <c r="B58" t="s">
-        <v>24</v>
+        <v>505</v>
       </c>
       <c r="C58" t="s">
-        <v>25</v>
+        <v>526</v>
       </c>
       <c r="D58" t="s">
-        <v>26</v>
+        <v>88</v>
       </c>
       <c r="E58" t="s">
         <v>8</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>27</v>
+        <v>199</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>28</v>
+        <v>287</v>
+      </c>
+      <c r="I58" s="2" t="s">
+        <v>565</v>
       </c>
       <c r="J58" s="2" t="s">
-        <v>70</v>
+        <v>183</v>
       </c>
       <c r="K58" t="b">
         <v>0</v>
@@ -3665,31 +4121,28 @@
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>29</v>
+        <v>485</v>
       </c>
       <c r="B59" t="s">
-        <v>30</v>
+        <v>506</v>
       </c>
       <c r="C59" t="s">
-        <v>31</v>
+        <v>533</v>
       </c>
       <c r="D59" t="s">
-        <v>32</v>
+        <v>88</v>
       </c>
       <c r="E59" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>15</v>
+        <v>100</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="I59" s="2" t="s">
-        <v>34</v>
+        <v>101</v>
       </c>
       <c r="J59" s="2" t="s">
-        <v>35</v>
+        <v>200</v>
       </c>
       <c r="K59" t="b">
         <v>0</v>
@@ -3697,30 +4150,741 @@
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
+        <v>486</v>
+      </c>
+      <c r="B60" t="s">
+        <v>507</v>
+      </c>
+      <c r="C60" t="s">
+        <v>527</v>
+      </c>
+      <c r="D60" t="s">
+        <v>88</v>
+      </c>
+      <c r="E60" t="s">
+        <v>33</v>
+      </c>
+      <c r="G60" s="2" t="s">
+        <v>450</v>
+      </c>
+      <c r="H60" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="J60" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="K60" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>487</v>
+      </c>
+      <c r="B61" t="s">
+        <v>508</v>
+      </c>
+      <c r="C61" t="s">
+        <v>534</v>
+      </c>
+      <c r="D61" t="s">
+        <v>88</v>
+      </c>
+      <c r="E61" t="s">
+        <v>89</v>
+      </c>
+      <c r="G61" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="H61" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="I61" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="J61" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="K61" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>488</v>
+      </c>
+      <c r="B62" t="s">
+        <v>509</v>
+      </c>
+      <c r="C62" t="s">
+        <v>522</v>
+      </c>
+      <c r="D62" t="s">
+        <v>88</v>
+      </c>
+      <c r="E62" t="s">
+        <v>8</v>
+      </c>
+      <c r="G62" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="H62" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="I62" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="J62" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K62" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>489</v>
+      </c>
+      <c r="B63" t="s">
+        <v>603</v>
+      </c>
+      <c r="C63" t="s">
+        <v>523</v>
+      </c>
+      <c r="D63" t="s">
+        <v>88</v>
+      </c>
+      <c r="E63" t="s">
+        <v>8</v>
+      </c>
+      <c r="G63" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="H63" s="2" t="s">
+        <v>435</v>
+      </c>
+      <c r="I63" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="J63" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="K63" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>490</v>
+      </c>
+      <c r="B64" t="s">
+        <v>510</v>
+      </c>
+      <c r="C64" t="s">
+        <v>511</v>
+      </c>
+      <c r="D64" t="s">
+        <v>88</v>
+      </c>
+      <c r="E64" t="s">
+        <v>89</v>
+      </c>
+      <c r="G64" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H64" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="I64" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="J64" s="2" t="s">
+        <v>564</v>
+      </c>
+      <c r="K64" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>491</v>
+      </c>
+      <c r="B65" t="s">
+        <v>512</v>
+      </c>
+      <c r="C65" t="s">
+        <v>528</v>
+      </c>
+      <c r="D65" t="s">
+        <v>88</v>
+      </c>
+      <c r="E65" t="s">
+        <v>8</v>
+      </c>
+      <c r="G65" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="H65" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="I65" s="2" t="s">
+        <v>566</v>
+      </c>
+      <c r="J65" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="K65" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>492</v>
+      </c>
+      <c r="B66" t="s">
+        <v>513</v>
+      </c>
+      <c r="C66" t="s">
+        <v>529</v>
+      </c>
+      <c r="D66" t="s">
+        <v>88</v>
+      </c>
+      <c r="E66" t="s">
+        <v>89</v>
+      </c>
+      <c r="G66" s="2" t="s">
+        <v>567</v>
+      </c>
+      <c r="H66" s="2" t="s">
+        <v>568</v>
+      </c>
+      <c r="J66" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="K66" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>493</v>
+      </c>
+      <c r="B67" t="s">
+        <v>514</v>
+      </c>
+      <c r="C67" t="s">
+        <v>524</v>
+      </c>
+      <c r="D67" t="s">
+        <v>88</v>
+      </c>
+      <c r="E67" t="s">
+        <v>89</v>
+      </c>
+      <c r="G67" s="2" t="s">
+        <v>569</v>
+      </c>
+      <c r="H67" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="J67" s="2" t="s">
+        <v>570</v>
+      </c>
+      <c r="K67" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>494</v>
+      </c>
+      <c r="B68" t="s">
+        <v>515</v>
+      </c>
+      <c r="C68" t="s">
+        <v>530</v>
+      </c>
+      <c r="D68" t="s">
+        <v>88</v>
+      </c>
+      <c r="E68" t="s">
+        <v>8</v>
+      </c>
+      <c r="G68" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H68" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="I68" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="J68" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="K68" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>495</v>
+      </c>
+      <c r="B69" t="s">
+        <v>516</v>
+      </c>
+      <c r="C69" t="s">
+        <v>531</v>
+      </c>
+      <c r="D69" t="s">
+        <v>88</v>
+      </c>
+      <c r="E69" t="s">
+        <v>89</v>
+      </c>
+      <c r="G69" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="H69" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="I69" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="J69" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="K69" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>85</v>
+      </c>
+      <c r="B70" t="s">
+        <v>86</v>
+      </c>
+      <c r="C70" t="s">
+        <v>87</v>
+      </c>
+      <c r="D70" t="s">
+        <v>88</v>
+      </c>
+      <c r="E70" t="s">
+        <v>89</v>
+      </c>
+      <c r="G70" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H70" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="I70" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="K70" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>275</v>
+      </c>
+      <c r="B71" t="s">
+        <v>276</v>
+      </c>
+      <c r="C71" t="s">
+        <v>277</v>
+      </c>
+      <c r="D71" t="s">
+        <v>278</v>
+      </c>
+      <c r="E71" t="s">
+        <v>8</v>
+      </c>
+      <c r="G71" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="H71" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="I71" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="J71" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K71" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="73" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="74" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="75" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="76" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="77" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="78" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="79" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="80" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="81" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="82" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="83" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="84" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="85" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="86" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="87" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="88" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="89" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="90" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="91" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="92" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="93" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="94" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>281</v>
+      </c>
+      <c r="B94" t="s">
+        <v>249</v>
+      </c>
+      <c r="C94" t="s">
+        <v>282</v>
+      </c>
+      <c r="D94" t="s">
+        <v>20</v>
+      </c>
+      <c r="E94" t="s">
+        <v>33</v>
+      </c>
+      <c r="H94" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="I94" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="J94" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="K94" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>17</v>
+      </c>
+      <c r="B95" t="s">
+        <v>18</v>
+      </c>
+      <c r="C95" t="s">
+        <v>19</v>
+      </c>
+      <c r="D95" t="s">
+        <v>20</v>
+      </c>
+      <c r="E95" t="s">
+        <v>8</v>
+      </c>
+      <c r="I95" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="J95" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="K95" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="96" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>284</v>
+      </c>
+      <c r="B96" t="s">
+        <v>285</v>
+      </c>
+      <c r="C96" t="s">
+        <v>286</v>
+      </c>
+      <c r="D96" t="s">
+        <v>20</v>
+      </c>
+      <c r="E96" t="s">
+        <v>8</v>
+      </c>
+      <c r="I96" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="J96" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="K96" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>96</v>
+      </c>
+      <c r="B97" t="s">
+        <v>97</v>
+      </c>
+      <c r="C97" t="s">
+        <v>98</v>
+      </c>
+      <c r="D97" t="s">
+        <v>20</v>
+      </c>
+      <c r="E97" t="s">
+        <v>99</v>
+      </c>
+      <c r="H97" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="I97" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="K97" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="98" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>314</v>
+      </c>
+      <c r="B98" t="s">
+        <v>315</v>
+      </c>
+      <c r="C98" t="s">
+        <v>316</v>
+      </c>
+      <c r="D98" t="s">
+        <v>317</v>
+      </c>
+      <c r="E98" t="s">
+        <v>33</v>
+      </c>
+      <c r="H98" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I98" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="J98" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="K98" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>76</v>
+      </c>
+      <c r="B99" t="s">
+        <v>77</v>
+      </c>
+      <c r="C99" t="s">
+        <v>78</v>
+      </c>
+      <c r="D99" t="s">
+        <v>79</v>
+      </c>
+      <c r="E99" t="s">
+        <v>40</v>
+      </c>
+      <c r="G99" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="H99" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I99" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="J99" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="K99" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>23</v>
+      </c>
+      <c r="B100" t="s">
+        <v>24</v>
+      </c>
+      <c r="C100" t="s">
+        <v>25</v>
+      </c>
+      <c r="D100" t="s">
+        <v>26</v>
+      </c>
+      <c r="E100" t="s">
+        <v>8</v>
+      </c>
+      <c r="G100" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="H100" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J100" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="K100" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>29</v>
+      </c>
+      <c r="B101" t="s">
+        <v>30</v>
+      </c>
+      <c r="C101" t="s">
+        <v>31</v>
+      </c>
+      <c r="D101" t="s">
+        <v>32</v>
+      </c>
+      <c r="E101" t="s">
+        <v>33</v>
+      </c>
+      <c r="G101" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H101" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="I101" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="J101" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="K101" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
         <v>36</v>
       </c>
-      <c r="B60" t="s">
+      <c r="B102" t="s">
         <v>37</v>
       </c>
-      <c r="C60" t="s">
+      <c r="C102" t="s">
         <v>38</v>
       </c>
-      <c r="D60" t="s">
+      <c r="D102" t="s">
         <v>39</v>
       </c>
-      <c r="E60" t="s">
+      <c r="E102" t="s">
         <v>40</v>
       </c>
-      <c r="G60" s="2" t="s">
+      <c r="G102" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="H60" s="2" t="s">
+      <c r="H102" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="J60" s="2" t="s">
+      <c r="J102" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="K60" t="b">
+      <c r="K102" t="b">
         <v>1</v>
       </c>
     </row>
@@ -3728,7 +4892,7 @@
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="H2 I6:I7 I10 I12 H14 I18 I22 I24 I27 G34 I40 I42 I45" numberStoredAsText="1"/>
+    <ignoredError sqref="H2 I6:I7 I10 I12 H14 I18 I22 I24 I27 G34 I40 I42 I45 I52 I62" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -4114,13 +5278,13 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84E3BB0D-5578-4069-B1C9-C3864EB2A429}">
-  <dimension ref="A1:F178"/>
+  <dimension ref="A1:F238"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="20.5703125" customWidth="1"/>
     <col min="3" max="3" width="12.7109375" customWidth="1"/>
     <col min="4" max="4" width="17" customWidth="1"/>
-    <col min="5" max="5" width="23.5703125" customWidth="1"/>
+    <col min="5" max="5" width="29.5703125" customWidth="1"/>
     <col min="6" max="6" width="15.7109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -6594,27 +7758,27 @@
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>85</v>
+        <v>476</v>
       </c>
       <c r="B146" t="s">
-        <v>86</v>
+        <v>496</v>
       </c>
       <c r="C146">
         <v>1</v>
       </c>
       <c r="D146" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E146" t="s">
-        <v>93</v>
+        <v>571</v>
       </c>
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>85</v>
+        <v>476</v>
       </c>
       <c r="B147" t="s">
-        <v>86</v>
+        <v>496</v>
       </c>
       <c r="C147">
         <v>2</v>
@@ -6623,15 +7787,15 @@
         <v>0</v>
       </c>
       <c r="E147" t="s">
-        <v>94</v>
+        <v>572</v>
       </c>
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>85</v>
+        <v>476</v>
       </c>
       <c r="B148" t="s">
-        <v>86</v>
+        <v>496</v>
       </c>
       <c r="C148">
         <v>3</v>
@@ -6640,15 +7804,15 @@
         <v>0</v>
       </c>
       <c r="E148" t="s">
-        <v>95</v>
+        <v>573</v>
       </c>
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>275</v>
+        <v>477</v>
       </c>
       <c r="B149" t="s">
-        <v>276</v>
+        <v>498</v>
       </c>
       <c r="C149">
         <v>1</v>
@@ -6657,15 +7821,15 @@
         <v>1</v>
       </c>
       <c r="E149" t="s">
-        <v>306</v>
+        <v>93</v>
       </c>
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>275</v>
+        <v>477</v>
       </c>
       <c r="B150" t="s">
-        <v>276</v>
+        <v>498</v>
       </c>
       <c r="C150">
         <v>2</v>
@@ -6674,15 +7838,15 @@
         <v>0</v>
       </c>
       <c r="E150" t="s">
-        <v>307</v>
+        <v>574</v>
       </c>
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>275</v>
+        <v>477</v>
       </c>
       <c r="B151" t="s">
-        <v>276</v>
+        <v>498</v>
       </c>
       <c r="C151">
         <v>3</v>
@@ -6691,15 +7855,15 @@
         <v>0</v>
       </c>
       <c r="E151" t="s">
-        <v>308</v>
+        <v>575</v>
       </c>
     </row>
     <row r="152" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>281</v>
+        <v>478</v>
       </c>
       <c r="B152" t="s">
-        <v>249</v>
+        <v>499</v>
       </c>
       <c r="C152">
         <v>1</v>
@@ -6708,15 +7872,15 @@
         <v>1</v>
       </c>
       <c r="E152" t="s">
-        <v>58</v>
+        <v>93</v>
       </c>
     </row>
     <row r="153" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>281</v>
+        <v>478</v>
       </c>
       <c r="B153" t="s">
-        <v>249</v>
+        <v>499</v>
       </c>
       <c r="C153">
         <v>2</v>
@@ -6725,15 +7889,15 @@
         <v>0</v>
       </c>
       <c r="E153" t="s">
-        <v>309</v>
+        <v>576</v>
       </c>
     </row>
     <row r="154" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>281</v>
+        <v>478</v>
       </c>
       <c r="B154" t="s">
-        <v>249</v>
+        <v>499</v>
       </c>
       <c r="C154">
         <v>3</v>
@@ -6742,15 +7906,15 @@
         <v>0</v>
       </c>
       <c r="E154" t="s">
-        <v>310</v>
+        <v>577</v>
       </c>
     </row>
     <row r="155" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>17</v>
+        <v>479</v>
       </c>
       <c r="B155" t="s">
-        <v>18</v>
+        <v>500</v>
       </c>
       <c r="C155">
         <v>1</v>
@@ -6759,15 +7923,15 @@
         <v>1</v>
       </c>
       <c r="E155" t="s">
-        <v>58</v>
+        <v>93</v>
       </c>
     </row>
     <row r="156" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>17</v>
+        <v>479</v>
       </c>
       <c r="B156" t="s">
-        <v>18</v>
+        <v>500</v>
       </c>
       <c r="C156">
         <v>2</v>
@@ -6776,15 +7940,15 @@
         <v>0</v>
       </c>
       <c r="E156" t="s">
-        <v>59</v>
+        <v>578</v>
       </c>
     </row>
     <row r="157" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>17</v>
+        <v>479</v>
       </c>
       <c r="B157" t="s">
-        <v>18</v>
+        <v>500</v>
       </c>
       <c r="C157">
         <v>3</v>
@@ -6793,15 +7957,15 @@
         <v>0</v>
       </c>
       <c r="E157" t="s">
-        <v>60</v>
+        <v>579</v>
       </c>
     </row>
     <row r="158" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>284</v>
+        <v>480</v>
       </c>
       <c r="B158" t="s">
-        <v>285</v>
+        <v>501</v>
       </c>
       <c r="C158">
         <v>1</v>
@@ -6810,15 +7974,15 @@
         <v>0</v>
       </c>
       <c r="E158" t="s">
-        <v>311</v>
+        <v>580</v>
       </c>
     </row>
     <row r="159" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>284</v>
+        <v>480</v>
       </c>
       <c r="B159" t="s">
-        <v>285</v>
+        <v>501</v>
       </c>
       <c r="C159">
         <v>2</v>
@@ -6827,15 +7991,15 @@
         <v>0</v>
       </c>
       <c r="E159" t="s">
-        <v>312</v>
+        <v>581</v>
       </c>
     </row>
     <row r="160" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>284</v>
+        <v>480</v>
       </c>
       <c r="B160" t="s">
-        <v>285</v>
+        <v>501</v>
       </c>
       <c r="C160">
         <v>3</v>
@@ -6844,32 +8008,32 @@
         <v>0</v>
       </c>
       <c r="E160" t="s">
-        <v>313</v>
+        <v>582</v>
       </c>
     </row>
     <row r="161" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>96</v>
+        <v>481</v>
       </c>
       <c r="B161" t="s">
-        <v>97</v>
+        <v>502</v>
       </c>
       <c r="C161">
         <v>1</v>
       </c>
       <c r="D161" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E161" t="s">
-        <v>108</v>
+        <v>93</v>
       </c>
     </row>
     <row r="162" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>96</v>
+        <v>481</v>
       </c>
       <c r="B162" t="s">
-        <v>97</v>
+        <v>502</v>
       </c>
       <c r="C162">
         <v>2</v>
@@ -6878,15 +8042,15 @@
         <v>0</v>
       </c>
       <c r="E162" t="s">
-        <v>109</v>
+        <v>583</v>
       </c>
     </row>
     <row r="163" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>96</v>
+        <v>481</v>
       </c>
       <c r="B163" t="s">
-        <v>97</v>
+        <v>502</v>
       </c>
       <c r="C163">
         <v>3</v>
@@ -6895,15 +8059,15 @@
         <v>0</v>
       </c>
       <c r="E163" t="s">
-        <v>110</v>
+        <v>584</v>
       </c>
     </row>
     <row r="164" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>314</v>
+        <v>482</v>
       </c>
       <c r="B164" t="s">
-        <v>315</v>
+        <v>503</v>
       </c>
       <c r="C164">
         <v>1</v>
@@ -6912,32 +8076,32 @@
         <v>1</v>
       </c>
       <c r="E164" t="s">
-        <v>320</v>
+        <v>82</v>
       </c>
     </row>
     <row r="165" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>314</v>
+        <v>482</v>
       </c>
       <c r="B165" t="s">
-        <v>315</v>
+        <v>503</v>
       </c>
       <c r="C165">
         <v>2</v>
       </c>
       <c r="D165" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E165" t="s">
-        <v>58</v>
+        <v>585</v>
       </c>
     </row>
     <row r="166" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>314</v>
+        <v>482</v>
       </c>
       <c r="B166" t="s">
-        <v>315</v>
+        <v>503</v>
       </c>
       <c r="C166">
         <v>3</v>
@@ -6946,32 +8110,32 @@
         <v>0</v>
       </c>
       <c r="E166" t="s">
-        <v>321</v>
+        <v>586</v>
       </c>
     </row>
     <row r="167" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>76</v>
+        <v>483</v>
       </c>
       <c r="B167" t="s">
-        <v>77</v>
+        <v>504</v>
       </c>
       <c r="C167">
         <v>1</v>
       </c>
       <c r="D167" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E167" t="s">
-        <v>82</v>
+        <v>587</v>
       </c>
     </row>
     <row r="168" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>76</v>
+        <v>483</v>
       </c>
       <c r="B168" t="s">
-        <v>77</v>
+        <v>504</v>
       </c>
       <c r="C168">
         <v>2</v>
@@ -6980,15 +8144,15 @@
         <v>0</v>
       </c>
       <c r="E168" t="s">
-        <v>83</v>
+        <v>588</v>
       </c>
     </row>
     <row r="169" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>76</v>
+        <v>483</v>
       </c>
       <c r="B169" t="s">
-        <v>77</v>
+        <v>504</v>
       </c>
       <c r="C169">
         <v>3</v>
@@ -6997,15 +8161,15 @@
         <v>0</v>
       </c>
       <c r="E169" t="s">
-        <v>84</v>
+        <v>589</v>
       </c>
     </row>
     <row r="170" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>23</v>
+        <v>484</v>
       </c>
       <c r="B170" t="s">
-        <v>24</v>
+        <v>505</v>
       </c>
       <c r="C170">
         <v>1</v>
@@ -7014,15 +8178,15 @@
         <v>0</v>
       </c>
       <c r="E170" t="s">
-        <v>61</v>
+        <v>590</v>
       </c>
     </row>
     <row r="171" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>23</v>
+        <v>484</v>
       </c>
       <c r="B171" t="s">
-        <v>24</v>
+        <v>505</v>
       </c>
       <c r="C171">
         <v>2</v>
@@ -7031,15 +8195,15 @@
         <v>0</v>
       </c>
       <c r="E171" t="s">
-        <v>62</v>
+        <v>591</v>
       </c>
     </row>
     <row r="172" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>23</v>
+        <v>484</v>
       </c>
       <c r="B172" t="s">
-        <v>24</v>
+        <v>505</v>
       </c>
       <c r="C172">
         <v>3</v>
@@ -7048,15 +8212,15 @@
         <v>0</v>
       </c>
       <c r="E172" t="s">
-        <v>63</v>
+        <v>592</v>
       </c>
     </row>
     <row r="173" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>29</v>
+        <v>485</v>
       </c>
       <c r="B173" t="s">
-        <v>30</v>
+        <v>506</v>
       </c>
       <c r="C173">
         <v>1</v>
@@ -7065,15 +8229,15 @@
         <v>0</v>
       </c>
       <c r="E173" t="s">
-        <v>64</v>
+        <v>593</v>
       </c>
     </row>
     <row r="174" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>29</v>
+        <v>485</v>
       </c>
       <c r="B174" t="s">
-        <v>30</v>
+        <v>506</v>
       </c>
       <c r="C174">
         <v>2</v>
@@ -7082,15 +8246,15 @@
         <v>0</v>
       </c>
       <c r="E174" t="s">
-        <v>65</v>
+        <v>594</v>
       </c>
     </row>
     <row r="175" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>29</v>
+        <v>485</v>
       </c>
       <c r="B175" t="s">
-        <v>30</v>
+        <v>506</v>
       </c>
       <c r="C175">
         <v>3</v>
@@ -7099,32 +8263,32 @@
         <v>0</v>
       </c>
       <c r="E175" t="s">
-        <v>66</v>
+        <v>595</v>
       </c>
     </row>
     <row r="176" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>36</v>
+        <v>486</v>
       </c>
       <c r="B176" t="s">
-        <v>37</v>
+        <v>507</v>
       </c>
       <c r="C176">
         <v>1</v>
       </c>
       <c r="D176" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E176" t="s">
-        <v>67</v>
+        <v>93</v>
       </c>
     </row>
     <row r="177" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>36</v>
+        <v>486</v>
       </c>
       <c r="B177" t="s">
-        <v>37</v>
+        <v>507</v>
       </c>
       <c r="C177">
         <v>2</v>
@@ -7133,15 +8297,15 @@
         <v>0</v>
       </c>
       <c r="E177" t="s">
-        <v>68</v>
+        <v>596</v>
       </c>
     </row>
     <row r="178" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>36</v>
+        <v>486</v>
       </c>
       <c r="B178" t="s">
-        <v>37</v>
+        <v>507</v>
       </c>
       <c r="C178">
         <v>3</v>
@@ -7150,6 +8314,1026 @@
         <v>0</v>
       </c>
       <c r="E178" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="179" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A179" t="s">
+        <v>487</v>
+      </c>
+      <c r="B179" t="s">
+        <v>508</v>
+      </c>
+      <c r="C179">
+        <v>1</v>
+      </c>
+      <c r="D179" t="b">
+        <v>0</v>
+      </c>
+      <c r="E179" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="180" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A180" t="s">
+        <v>487</v>
+      </c>
+      <c r="B180" t="s">
+        <v>508</v>
+      </c>
+      <c r="C180">
+        <v>2</v>
+      </c>
+      <c r="D180" t="b">
+        <v>0</v>
+      </c>
+      <c r="E180" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="181" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A181" t="s">
+        <v>487</v>
+      </c>
+      <c r="B181" t="s">
+        <v>508</v>
+      </c>
+      <c r="C181">
+        <v>3</v>
+      </c>
+      <c r="D181" t="b">
+        <v>0</v>
+      </c>
+      <c r="E181" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="182" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A182" t="s">
+        <v>488</v>
+      </c>
+      <c r="B182" t="s">
+        <v>509</v>
+      </c>
+      <c r="C182">
+        <v>1</v>
+      </c>
+      <c r="D182" t="b">
+        <v>1</v>
+      </c>
+      <c r="E182" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="183" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A183" t="s">
+        <v>488</v>
+      </c>
+      <c r="B183" t="s">
+        <v>509</v>
+      </c>
+      <c r="C183">
+        <v>2</v>
+      </c>
+      <c r="D183" t="b">
+        <v>0</v>
+      </c>
+      <c r="E183" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="184" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A184" t="s">
+        <v>488</v>
+      </c>
+      <c r="B184" t="s">
+        <v>509</v>
+      </c>
+      <c r="C184">
+        <v>3</v>
+      </c>
+      <c r="D184" t="b">
+        <v>0</v>
+      </c>
+      <c r="E184" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="185" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A185" t="s">
+        <v>489</v>
+      </c>
+      <c r="B185" t="s">
+        <v>603</v>
+      </c>
+      <c r="C185">
+        <v>1</v>
+      </c>
+      <c r="D185" t="b">
+        <v>0</v>
+      </c>
+      <c r="E185" t="s">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="186" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A186" t="s">
+        <v>489</v>
+      </c>
+      <c r="B186" t="s">
+        <v>603</v>
+      </c>
+      <c r="C186">
+        <v>2</v>
+      </c>
+      <c r="D186" t="b">
+        <v>0</v>
+      </c>
+      <c r="E186" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="187" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A187" t="s">
+        <v>489</v>
+      </c>
+      <c r="B187" t="s">
+        <v>603</v>
+      </c>
+      <c r="C187">
+        <v>3</v>
+      </c>
+      <c r="D187" t="b">
+        <v>0</v>
+      </c>
+      <c r="E187" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="188" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A188" t="s">
+        <v>490</v>
+      </c>
+      <c r="B188" t="s">
+        <v>510</v>
+      </c>
+      <c r="C188">
+        <v>1</v>
+      </c>
+      <c r="D188" t="b">
+        <v>1</v>
+      </c>
+      <c r="E188" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="189" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A189" t="s">
+        <v>490</v>
+      </c>
+      <c r="B189" t="s">
+        <v>510</v>
+      </c>
+      <c r="C189">
+        <v>2</v>
+      </c>
+      <c r="D189" t="b">
+        <v>0</v>
+      </c>
+      <c r="E189" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="190" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A190" t="s">
+        <v>490</v>
+      </c>
+      <c r="B190" t="s">
+        <v>510</v>
+      </c>
+      <c r="C190">
+        <v>3</v>
+      </c>
+      <c r="D190" t="b">
+        <v>0</v>
+      </c>
+      <c r="E190" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="191" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A191" t="s">
+        <v>491</v>
+      </c>
+      <c r="B191" t="s">
+        <v>512</v>
+      </c>
+      <c r="C191">
+        <v>1</v>
+      </c>
+      <c r="D191" t="b">
+        <v>1</v>
+      </c>
+      <c r="E191" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="192" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A192" t="s">
+        <v>491</v>
+      </c>
+      <c r="B192" t="s">
+        <v>512</v>
+      </c>
+      <c r="C192">
+        <v>2</v>
+      </c>
+      <c r="D192" t="b">
+        <v>0</v>
+      </c>
+      <c r="E192" t="s">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="193" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A193" t="s">
+        <v>491</v>
+      </c>
+      <c r="B193" t="s">
+        <v>512</v>
+      </c>
+      <c r="C193">
+        <v>3</v>
+      </c>
+      <c r="D193" t="b">
+        <v>0</v>
+      </c>
+      <c r="E193" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="194" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A194" t="s">
+        <v>492</v>
+      </c>
+      <c r="B194" t="s">
+        <v>513</v>
+      </c>
+      <c r="C194">
+        <v>1</v>
+      </c>
+      <c r="D194" t="b">
+        <v>1</v>
+      </c>
+      <c r="E194" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="195" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A195" t="s">
+        <v>492</v>
+      </c>
+      <c r="B195" t="s">
+        <v>513</v>
+      </c>
+      <c r="C195">
+        <v>2</v>
+      </c>
+      <c r="D195" t="b">
+        <v>0</v>
+      </c>
+      <c r="E195" t="s">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="196" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A196" t="s">
+        <v>492</v>
+      </c>
+      <c r="B196" t="s">
+        <v>513</v>
+      </c>
+      <c r="C196">
+        <v>3</v>
+      </c>
+      <c r="D196" t="b">
+        <v>0</v>
+      </c>
+      <c r="E196" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="197" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A197" t="s">
+        <v>493</v>
+      </c>
+      <c r="B197" t="s">
+        <v>514</v>
+      </c>
+      <c r="C197">
+        <v>1</v>
+      </c>
+      <c r="D197" t="b">
+        <v>0</v>
+      </c>
+      <c r="E197" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="198" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A198" t="s">
+        <v>493</v>
+      </c>
+      <c r="B198" t="s">
+        <v>514</v>
+      </c>
+      <c r="C198">
+        <v>2</v>
+      </c>
+      <c r="D198" t="b">
+        <v>0</v>
+      </c>
+      <c r="E198" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="199" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A199" t="s">
+        <v>493</v>
+      </c>
+      <c r="B199" t="s">
+        <v>514</v>
+      </c>
+      <c r="C199">
+        <v>3</v>
+      </c>
+      <c r="D199" t="b">
+        <v>0</v>
+      </c>
+      <c r="E199" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="200" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A200" t="s">
+        <v>494</v>
+      </c>
+      <c r="B200" t="s">
+        <v>515</v>
+      </c>
+      <c r="C200">
+        <v>1</v>
+      </c>
+      <c r="D200" t="b">
+        <v>0</v>
+      </c>
+      <c r="E200" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="201" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A201" t="s">
+        <v>494</v>
+      </c>
+      <c r="B201" t="s">
+        <v>515</v>
+      </c>
+      <c r="C201">
+        <v>2</v>
+      </c>
+      <c r="D201" t="b">
+        <v>0</v>
+      </c>
+      <c r="E201" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="202" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A202" t="s">
+        <v>494</v>
+      </c>
+      <c r="B202" t="s">
+        <v>515</v>
+      </c>
+      <c r="C202">
+        <v>3</v>
+      </c>
+      <c r="D202" t="b">
+        <v>0</v>
+      </c>
+      <c r="E202" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="203" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A203" t="s">
+        <v>495</v>
+      </c>
+      <c r="B203" t="s">
+        <v>516</v>
+      </c>
+      <c r="C203">
+        <v>1</v>
+      </c>
+      <c r="D203" t="b">
+        <v>0</v>
+      </c>
+      <c r="E203" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="204" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A204" t="s">
+        <v>495</v>
+      </c>
+      <c r="B204" t="s">
+        <v>516</v>
+      </c>
+      <c r="C204">
+        <v>2</v>
+      </c>
+      <c r="D204" t="b">
+        <v>0</v>
+      </c>
+      <c r="E204" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="205" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A205" t="s">
+        <v>495</v>
+      </c>
+      <c r="B205" t="s">
+        <v>516</v>
+      </c>
+      <c r="C205">
+        <v>3</v>
+      </c>
+      <c r="D205" t="b">
+        <v>0</v>
+      </c>
+      <c r="E205" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="206" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A206" t="s">
+        <v>85</v>
+      </c>
+      <c r="B206" t="s">
+        <v>86</v>
+      </c>
+      <c r="C206">
+        <v>1</v>
+      </c>
+      <c r="D206" t="b">
+        <v>1</v>
+      </c>
+      <c r="E206" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="207" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A207" t="s">
+        <v>85</v>
+      </c>
+      <c r="B207" t="s">
+        <v>86</v>
+      </c>
+      <c r="C207">
+        <v>2</v>
+      </c>
+      <c r="D207" t="b">
+        <v>0</v>
+      </c>
+      <c r="E207" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="208" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A208" t="s">
+        <v>85</v>
+      </c>
+      <c r="B208" t="s">
+        <v>86</v>
+      </c>
+      <c r="C208">
+        <v>3</v>
+      </c>
+      <c r="D208" t="b">
+        <v>0</v>
+      </c>
+      <c r="E208" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="209" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A209" t="s">
+        <v>275</v>
+      </c>
+      <c r="B209" t="s">
+        <v>276</v>
+      </c>
+      <c r="C209">
+        <v>1</v>
+      </c>
+      <c r="D209" t="b">
+        <v>1</v>
+      </c>
+      <c r="E209" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="210" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A210" t="s">
+        <v>275</v>
+      </c>
+      <c r="B210" t="s">
+        <v>276</v>
+      </c>
+      <c r="C210">
+        <v>2</v>
+      </c>
+      <c r="D210" t="b">
+        <v>0</v>
+      </c>
+      <c r="E210" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="211" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A211" t="s">
+        <v>275</v>
+      </c>
+      <c r="B211" t="s">
+        <v>276</v>
+      </c>
+      <c r="C211">
+        <v>3</v>
+      </c>
+      <c r="D211" t="b">
+        <v>0</v>
+      </c>
+      <c r="E211" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="212" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A212" t="s">
+        <v>281</v>
+      </c>
+      <c r="B212" t="s">
+        <v>249</v>
+      </c>
+      <c r="C212">
+        <v>1</v>
+      </c>
+      <c r="D212" t="b">
+        <v>1</v>
+      </c>
+      <c r="E212" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="213" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A213" t="s">
+        <v>281</v>
+      </c>
+      <c r="B213" t="s">
+        <v>249</v>
+      </c>
+      <c r="C213">
+        <v>2</v>
+      </c>
+      <c r="D213" t="b">
+        <v>0</v>
+      </c>
+      <c r="E213" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="214" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A214" t="s">
+        <v>281</v>
+      </c>
+      <c r="B214" t="s">
+        <v>249</v>
+      </c>
+      <c r="C214">
+        <v>3</v>
+      </c>
+      <c r="D214" t="b">
+        <v>0</v>
+      </c>
+      <c r="E214" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="215" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A215" t="s">
+        <v>17</v>
+      </c>
+      <c r="B215" t="s">
+        <v>18</v>
+      </c>
+      <c r="C215">
+        <v>1</v>
+      </c>
+      <c r="D215" t="b">
+        <v>1</v>
+      </c>
+      <c r="E215" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="216" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A216" t="s">
+        <v>17</v>
+      </c>
+      <c r="B216" t="s">
+        <v>18</v>
+      </c>
+      <c r="C216">
+        <v>2</v>
+      </c>
+      <c r="D216" t="b">
+        <v>0</v>
+      </c>
+      <c r="E216" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="217" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A217" t="s">
+        <v>17</v>
+      </c>
+      <c r="B217" t="s">
+        <v>18</v>
+      </c>
+      <c r="C217">
+        <v>3</v>
+      </c>
+      <c r="D217" t="b">
+        <v>0</v>
+      </c>
+      <c r="E217" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="218" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A218" t="s">
+        <v>284</v>
+      </c>
+      <c r="B218" t="s">
+        <v>285</v>
+      </c>
+      <c r="C218">
+        <v>1</v>
+      </c>
+      <c r="D218" t="b">
+        <v>0</v>
+      </c>
+      <c r="E218" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="219" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A219" t="s">
+        <v>284</v>
+      </c>
+      <c r="B219" t="s">
+        <v>285</v>
+      </c>
+      <c r="C219">
+        <v>2</v>
+      </c>
+      <c r="D219" t="b">
+        <v>0</v>
+      </c>
+      <c r="E219" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="220" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A220" t="s">
+        <v>284</v>
+      </c>
+      <c r="B220" t="s">
+        <v>285</v>
+      </c>
+      <c r="C220">
+        <v>3</v>
+      </c>
+      <c r="D220" t="b">
+        <v>0</v>
+      </c>
+      <c r="E220" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="221" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A221" t="s">
+        <v>96</v>
+      </c>
+      <c r="B221" t="s">
+        <v>97</v>
+      </c>
+      <c r="C221">
+        <v>1</v>
+      </c>
+      <c r="D221" t="b">
+        <v>0</v>
+      </c>
+      <c r="E221" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="222" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A222" t="s">
+        <v>96</v>
+      </c>
+      <c r="B222" t="s">
+        <v>97</v>
+      </c>
+      <c r="C222">
+        <v>2</v>
+      </c>
+      <c r="D222" t="b">
+        <v>0</v>
+      </c>
+      <c r="E222" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="223" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A223" t="s">
+        <v>96</v>
+      </c>
+      <c r="B223" t="s">
+        <v>97</v>
+      </c>
+      <c r="C223">
+        <v>3</v>
+      </c>
+      <c r="D223" t="b">
+        <v>0</v>
+      </c>
+      <c r="E223" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="224" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A224" t="s">
+        <v>314</v>
+      </c>
+      <c r="B224" t="s">
+        <v>315</v>
+      </c>
+      <c r="C224">
+        <v>1</v>
+      </c>
+      <c r="D224" t="b">
+        <v>1</v>
+      </c>
+      <c r="E224" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="225" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A225" t="s">
+        <v>314</v>
+      </c>
+      <c r="B225" t="s">
+        <v>315</v>
+      </c>
+      <c r="C225">
+        <v>2</v>
+      </c>
+      <c r="D225" t="b">
+        <v>1</v>
+      </c>
+      <c r="E225" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="226" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A226" t="s">
+        <v>314</v>
+      </c>
+      <c r="B226" t="s">
+        <v>315</v>
+      </c>
+      <c r="C226">
+        <v>3</v>
+      </c>
+      <c r="D226" t="b">
+        <v>0</v>
+      </c>
+      <c r="E226" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="227" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A227" t="s">
+        <v>76</v>
+      </c>
+      <c r="B227" t="s">
+        <v>77</v>
+      </c>
+      <c r="C227">
+        <v>1</v>
+      </c>
+      <c r="D227" t="b">
+        <v>1</v>
+      </c>
+      <c r="E227" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="228" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A228" t="s">
+        <v>76</v>
+      </c>
+      <c r="B228" t="s">
+        <v>77</v>
+      </c>
+      <c r="C228">
+        <v>2</v>
+      </c>
+      <c r="D228" t="b">
+        <v>0</v>
+      </c>
+      <c r="E228" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="229" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A229" t="s">
+        <v>76</v>
+      </c>
+      <c r="B229" t="s">
+        <v>77</v>
+      </c>
+      <c r="C229">
+        <v>3</v>
+      </c>
+      <c r="D229" t="b">
+        <v>0</v>
+      </c>
+      <c r="E229" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="230" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A230" t="s">
+        <v>23</v>
+      </c>
+      <c r="B230" t="s">
+        <v>24</v>
+      </c>
+      <c r="C230">
+        <v>1</v>
+      </c>
+      <c r="D230" t="b">
+        <v>0</v>
+      </c>
+      <c r="E230" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="231" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A231" t="s">
+        <v>23</v>
+      </c>
+      <c r="B231" t="s">
+        <v>24</v>
+      </c>
+      <c r="C231">
+        <v>2</v>
+      </c>
+      <c r="D231" t="b">
+        <v>0</v>
+      </c>
+      <c r="E231" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="232" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A232" t="s">
+        <v>23</v>
+      </c>
+      <c r="B232" t="s">
+        <v>24</v>
+      </c>
+      <c r="C232">
+        <v>3</v>
+      </c>
+      <c r="D232" t="b">
+        <v>0</v>
+      </c>
+      <c r="E232" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="233" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A233" t="s">
+        <v>29</v>
+      </c>
+      <c r="B233" t="s">
+        <v>30</v>
+      </c>
+      <c r="C233">
+        <v>1</v>
+      </c>
+      <c r="D233" t="b">
+        <v>0</v>
+      </c>
+      <c r="E233" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="234" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A234" t="s">
+        <v>29</v>
+      </c>
+      <c r="B234" t="s">
+        <v>30</v>
+      </c>
+      <c r="C234">
+        <v>2</v>
+      </c>
+      <c r="D234" t="b">
+        <v>0</v>
+      </c>
+      <c r="E234" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="235" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A235" t="s">
+        <v>29</v>
+      </c>
+      <c r="B235" t="s">
+        <v>30</v>
+      </c>
+      <c r="C235">
+        <v>3</v>
+      </c>
+      <c r="D235" t="b">
+        <v>0</v>
+      </c>
+      <c r="E235" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="236" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A236" t="s">
+        <v>36</v>
+      </c>
+      <c r="B236" t="s">
+        <v>37</v>
+      </c>
+      <c r="C236">
+        <v>1</v>
+      </c>
+      <c r="D236" t="b">
+        <v>0</v>
+      </c>
+      <c r="E236" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="237" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A237" t="s">
+        <v>36</v>
+      </c>
+      <c r="B237" t="s">
+        <v>37</v>
+      </c>
+      <c r="C237">
+        <v>2</v>
+      </c>
+      <c r="D237" t="b">
+        <v>0</v>
+      </c>
+      <c r="E237" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="238" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A238" t="s">
+        <v>36</v>
+      </c>
+      <c r="B238" t="s">
+        <v>37</v>
+      </c>
+      <c r="C238">
+        <v>3</v>
+      </c>
+      <c r="D238" t="b">
+        <v>0</v>
+      </c>
+      <c r="E238" t="s">
         <v>69</v>
       </c>
     </row>

--- a/data/Fate-Spreadsheet.xlsx
+++ b/data/Fate-Spreadsheet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Important\Python\Fate-Wiki\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAE09173-3834-4445-B317-789F4733B023}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74414681-1B7E-4E20-8CB8-128DF038A562}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{B05E798F-9EF6-4508-A0A4-311D06661AED}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{B05E798F-9EF6-4508-A0A4-311D06661AED}"/>
   </bookViews>
   <sheets>
     <sheet name="Servants" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1515" uniqueCount="622">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1860" uniqueCount="717">
   <si>
     <t>servant_id</t>
   </si>
@@ -1909,6 +1909,291 @@
   </si>
   <si>
     <t>Nostalgia Drive</t>
+  </si>
+  <si>
+    <t>Iskander of Macedonia</t>
+  </si>
+  <si>
+    <t>iskander-of-macedonia</t>
+  </si>
+  <si>
+    <t>2,2,3,3,4,5</t>
+  </si>
+  <si>
+    <t>Astolfo</t>
+  </si>
+  <si>
+    <t>Achilles</t>
+  </si>
+  <si>
+    <t>Ivan the Terrible</t>
+  </si>
+  <si>
+    <t>Francis Drake</t>
+  </si>
+  <si>
+    <t>Ushiwakamaru</t>
+  </si>
+  <si>
+    <t>Ozymandias</t>
+  </si>
+  <si>
+    <t>Sitonai</t>
+  </si>
+  <si>
+    <t>Odysseus</t>
+  </si>
+  <si>
+    <t>Queen Medb</t>
+  </si>
+  <si>
+    <t>Bartholomew Roberts</t>
+  </si>
+  <si>
+    <t>Boudica</t>
+  </si>
+  <si>
+    <t>Quetzalcoatl</t>
+  </si>
+  <si>
+    <t>Hephaistion</t>
+  </si>
+  <si>
+    <t>Sakamoto Ryouma</t>
+  </si>
+  <si>
+    <t>Edward Teach</t>
+  </si>
+  <si>
+    <t>Mandricardo</t>
+  </si>
+  <si>
+    <t>Saint Martha</t>
+  </si>
+  <si>
+    <t>Saint Georgios</t>
+  </si>
+  <si>
+    <t>Captain Nemo</t>
+  </si>
+  <si>
+    <t>Taisui Xingjun</t>
+  </si>
+  <si>
+    <t>Constantine XI</t>
+  </si>
+  <si>
+    <t>Pretender</t>
+  </si>
+  <si>
+    <t>3,3,3,4,5,5</t>
+  </si>
+  <si>
+    <t>3,3,3,5</t>
+  </si>
+  <si>
+    <t>Luck,Surveil,Surveil,Surveil</t>
+  </si>
+  <si>
+    <t>Surveil,Surveil,Preparation,Preparation</t>
+  </si>
+  <si>
+    <t>Luck,Surveil,Preparation,Berserker_Strength_9</t>
+  </si>
+  <si>
+    <t>3,3,3,4</t>
+  </si>
+  <si>
+    <t>Surveil,Surveil,Surveil,Luck,Luck</t>
+  </si>
+  <si>
+    <t>2,3,3,3</t>
+  </si>
+  <si>
+    <t>2,3,3,3,4</t>
+  </si>
+  <si>
+    <t>2,5,5,5</t>
+  </si>
+  <si>
+    <t>3,3,5</t>
+  </si>
+  <si>
+    <t>2,2,2,3,3,4</t>
+  </si>
+  <si>
+    <t>2,2,3,3,5,5</t>
+  </si>
+  <si>
+    <t>2,3,3,3,5</t>
+  </si>
+  <si>
+    <t>2,2,3,4,4,5</t>
+  </si>
+  <si>
+    <t>3,5</t>
+  </si>
+  <si>
+    <t>Luck,Luck,Surveil,Surveil,Preparation,Preparation</t>
+  </si>
+  <si>
+    <t>3,3,5,5</t>
+  </si>
+  <si>
+    <t>Luck,Luck,Surveil,Preparation</t>
+  </si>
+  <si>
+    <t>Ionian Hetairoi</t>
+  </si>
+  <si>
+    <t>Gordius Wheel</t>
+  </si>
+  <si>
+    <t>Casseur de Logistille</t>
+  </si>
+  <si>
+    <t>La Lune Noire</t>
+  </si>
+  <si>
+    <t>Trap of Argalia</t>
+  </si>
+  <si>
+    <t>Diatrekhon Aster Lonkhe</t>
+  </si>
+  <si>
+    <t>Akhilleus Kosmos</t>
+  </si>
+  <si>
+    <t>Andreias Amarantos</t>
+  </si>
+  <si>
+    <t>Oprichniki</t>
+  </si>
+  <si>
+    <t>Monstrous Form</t>
+  </si>
+  <si>
+    <t>The Golden Hind</t>
+  </si>
+  <si>
+    <t>Privateer's Glory</t>
+  </si>
+  <si>
+    <t>Eight Boat Leap</t>
+  </si>
+  <si>
+    <t>Icicle Cutter</t>
+  </si>
+  <si>
+    <t>Abu el-Hol Sphinx</t>
+  </si>
+  <si>
+    <t>Dendera Electric Bulb</t>
+  </si>
+  <si>
+    <t>Ramesseum Tentyris</t>
+  </si>
+  <si>
+    <t>Pohjola Fimbul</t>
+  </si>
+  <si>
+    <t>Combination Attack</t>
+  </si>
+  <si>
+    <t>Aigis</t>
+  </si>
+  <si>
+    <t>Troia Hippos</t>
+  </si>
+  <si>
+    <t>Chariot My Love</t>
+  </si>
+  <si>
+    <t>My Red Mead</t>
+  </si>
+  <si>
+    <t>The Royal Rover</t>
+  </si>
+  <si>
+    <t>Pirate's Code</t>
+  </si>
+  <si>
+    <t>Sword of Boudica</t>
+  </si>
+  <si>
+    <t>Chariot of Boudica</t>
+  </si>
+  <si>
+    <t>Piedra del Sol</t>
+  </si>
+  <si>
+    <t>Quetzalcoatlus</t>
+  </si>
+  <si>
+    <t>Blood Frenzy</t>
+  </si>
+  <si>
+    <t>Pretender Class</t>
+  </si>
+  <si>
+    <t>Hecatic Wheel</t>
+  </si>
+  <si>
+    <t>Like a Soaring Dragon</t>
+  </si>
+  <si>
+    <t>Dragon of Restoration</t>
+  </si>
+  <si>
+    <t>Blade of Restoration</t>
+  </si>
+  <si>
+    <t>Queen Anne's Revenge</t>
+  </si>
+  <si>
+    <t>Deviant Tastes</t>
+  </si>
+  <si>
+    <t>Serment de Durandal</t>
+  </si>
+  <si>
+    <t>Wooden Sword</t>
+  </si>
+  <si>
+    <t>Tarasque</t>
+  </si>
+  <si>
+    <t>Divine Obedience</t>
+  </si>
+  <si>
+    <t>Ascalon</t>
+  </si>
+  <si>
+    <t>Bayard</t>
+  </si>
+  <si>
+    <t>Martyr's Soul</t>
+  </si>
+  <si>
+    <t>The Nautilus</t>
+  </si>
+  <si>
+    <t>Memory Partition</t>
+  </si>
+  <si>
+    <t>Triton's Favour</t>
+  </si>
+  <si>
+    <t>Taisu Awaken</t>
+  </si>
+  <si>
+    <t>God of Calamity</t>
+  </si>
+  <si>
+    <t>Theodosios Constantinos</t>
+  </si>
+  <si>
+    <t>Twilit Empire</t>
   </si>
 </sst>
 </file>
@@ -4524,110 +4809,617 @@
       <c r="A72" t="s">
         <v>535</v>
       </c>
+      <c r="B72" t="s">
+        <v>622</v>
+      </c>
+      <c r="C72" t="s">
+        <v>623</v>
+      </c>
+      <c r="D72" t="s">
+        <v>278</v>
+      </c>
+      <c r="E72" t="s">
+        <v>8</v>
+      </c>
+      <c r="G72" s="2" t="s">
+        <v>624</v>
+      </c>
+      <c r="H72" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="I72" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="J72" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="K72" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="73" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>536</v>
       </c>
+      <c r="B73" t="s">
+        <v>625</v>
+      </c>
+      <c r="D73" t="s">
+        <v>278</v>
+      </c>
+      <c r="E73" t="s">
+        <v>89</v>
+      </c>
+      <c r="G73" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H73" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="I73" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="J73" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="K73" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="74" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>537</v>
       </c>
+      <c r="B74" t="s">
+        <v>626</v>
+      </c>
+      <c r="D74" t="s">
+        <v>278</v>
+      </c>
+      <c r="E74" t="s">
+        <v>40</v>
+      </c>
+      <c r="G74" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="H74" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="J74" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="K74" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="75" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>538</v>
       </c>
+      <c r="B75" t="s">
+        <v>627</v>
+      </c>
+      <c r="D75" t="s">
+        <v>278</v>
+      </c>
+      <c r="E75" t="s">
+        <v>40</v>
+      </c>
+      <c r="G75" s="2" t="s">
+        <v>647</v>
+      </c>
+      <c r="I75" s="2" t="s">
+        <v>648</v>
+      </c>
+      <c r="J75" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="K75" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="76" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>539</v>
       </c>
+      <c r="B76" t="s">
+        <v>628</v>
+      </c>
+      <c r="D76" t="s">
+        <v>278</v>
+      </c>
+      <c r="E76" t="s">
+        <v>8</v>
+      </c>
+      <c r="G76" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="H76" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="J76" s="2" t="s">
+        <v>649</v>
+      </c>
+      <c r="K76" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="77" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>540</v>
       </c>
+      <c r="B77" t="s">
+        <v>629</v>
+      </c>
+      <c r="D77" t="s">
+        <v>278</v>
+      </c>
+      <c r="E77" t="s">
+        <v>89</v>
+      </c>
+      <c r="G77" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H77" s="2" t="s">
+        <v>624</v>
+      </c>
+      <c r="J77" s="2" t="s">
+        <v>650</v>
+      </c>
+      <c r="K77" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="78" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>541</v>
       </c>
+      <c r="B78" t="s">
+        <v>630</v>
+      </c>
+      <c r="D78" t="s">
+        <v>278</v>
+      </c>
+      <c r="E78" t="s">
+        <v>40</v>
+      </c>
+      <c r="G78" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="H78" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I78" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="J78" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="K78" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="79" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>542</v>
       </c>
+      <c r="B79" t="s">
+        <v>631</v>
+      </c>
+      <c r="D79" t="s">
+        <v>79</v>
+      </c>
+      <c r="E79" t="s">
+        <v>99</v>
+      </c>
+      <c r="G79" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="H79" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="I79" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="J79" s="2" t="s">
+        <v>651</v>
+      </c>
+      <c r="K79" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="80" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>543</v>
       </c>
+      <c r="B80" t="s">
+        <v>632</v>
+      </c>
+      <c r="D80" t="s">
+        <v>278</v>
+      </c>
+      <c r="E80" t="s">
+        <v>8</v>
+      </c>
+      <c r="G80" s="2" t="s">
+        <v>652</v>
+      </c>
+      <c r="H80" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I80" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="J80" s="2" t="s">
+        <v>653</v>
+      </c>
+      <c r="K80" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="81" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>544</v>
       </c>
+      <c r="B81" t="s">
+        <v>633</v>
+      </c>
+      <c r="D81" t="s">
+        <v>278</v>
+      </c>
+      <c r="E81" t="s">
+        <v>33</v>
+      </c>
+      <c r="G81" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="H81" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="I81" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="J81" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="K81" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="82" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>545</v>
       </c>
+      <c r="B82" t="s">
+        <v>634</v>
+      </c>
+      <c r="D82" t="s">
+        <v>278</v>
+      </c>
+      <c r="E82" t="s">
+        <v>33</v>
+      </c>
+      <c r="G82" s="2" t="s">
+        <v>654</v>
+      </c>
+      <c r="H82" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="J82" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="K82" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="83" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>546</v>
       </c>
+      <c r="B83" t="s">
+        <v>635</v>
+      </c>
+      <c r="D83" t="s">
+        <v>278</v>
+      </c>
+      <c r="E83" t="s">
+        <v>89</v>
+      </c>
+      <c r="G83" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="H83" s="2" t="s">
+        <v>655</v>
+      </c>
+      <c r="J83" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="K83" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="84" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>547</v>
       </c>
+      <c r="B84" t="s">
+        <v>636</v>
+      </c>
+      <c r="D84" t="s">
+        <v>278</v>
+      </c>
+      <c r="E84" t="s">
+        <v>89</v>
+      </c>
+      <c r="G84" s="2" t="s">
+        <v>656</v>
+      </c>
+      <c r="H84" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="I84" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="J84" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="K84" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="85" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>548</v>
       </c>
+      <c r="B85" t="s">
+        <v>637</v>
+      </c>
+      <c r="D85" t="s">
+        <v>646</v>
+      </c>
+      <c r="E85" t="s">
+        <v>8</v>
+      </c>
+      <c r="G85" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="H85" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I85" s="2" t="s">
+        <v>657</v>
+      </c>
+      <c r="J85" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="K85" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="86" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>549</v>
       </c>
+      <c r="B86" t="s">
+        <v>638</v>
+      </c>
+      <c r="D86" t="s">
+        <v>278</v>
+      </c>
+      <c r="E86" t="s">
+        <v>89</v>
+      </c>
+      <c r="G86" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="H86" s="2" t="s">
+        <v>658</v>
+      </c>
+      <c r="J86" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="K86" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="87" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>550</v>
       </c>
+      <c r="B87" t="s">
+        <v>639</v>
+      </c>
+      <c r="D87" t="s">
+        <v>278</v>
+      </c>
+      <c r="E87" t="s">
+        <v>99</v>
+      </c>
+      <c r="G87" s="2" t="s">
+        <v>659</v>
+      </c>
+      <c r="H87" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="J87" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="K87" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="88" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>551</v>
       </c>
+      <c r="B88" t="s">
+        <v>640</v>
+      </c>
+      <c r="D88" t="s">
+        <v>278</v>
+      </c>
+      <c r="E88" t="s">
+        <v>99</v>
+      </c>
+      <c r="G88" s="2" t="s">
+        <v>660</v>
+      </c>
+      <c r="H88" s="2" t="s">
+        <v>652</v>
+      </c>
+      <c r="I88" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="J88" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="K88" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="89" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>552</v>
       </c>
+      <c r="B89" t="s">
+        <v>641</v>
+      </c>
+      <c r="D89" t="s">
+        <v>278</v>
+      </c>
+      <c r="E89" t="s">
+        <v>8</v>
+      </c>
+      <c r="G89" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="H89" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="I89" s="2" t="s">
+        <v>657</v>
+      </c>
+      <c r="J89" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="K89" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="90" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>553</v>
       </c>
+      <c r="B90" t="s">
+        <v>642</v>
+      </c>
+      <c r="D90" t="s">
+        <v>278</v>
+      </c>
+      <c r="E90" t="s">
+        <v>8</v>
+      </c>
+      <c r="G90" s="2" t="s">
+        <v>661</v>
+      </c>
+      <c r="H90" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="I90" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="J90" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="K90" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="91" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>554</v>
       </c>
+      <c r="B91" t="s">
+        <v>643</v>
+      </c>
+      <c r="D91" t="s">
+        <v>278</v>
+      </c>
+      <c r="E91" t="s">
+        <v>8</v>
+      </c>
+      <c r="G91" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="H91" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="I91" s="2" t="s">
+        <v>662</v>
+      </c>
+      <c r="J91" s="2" t="s">
+        <v>663</v>
+      </c>
+      <c r="K91" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="92" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>555</v>
       </c>
+      <c r="B92" t="s">
+        <v>644</v>
+      </c>
+      <c r="D92" t="s">
+        <v>79</v>
+      </c>
+      <c r="E92" t="s">
+        <v>89</v>
+      </c>
+      <c r="G92" s="2" t="s">
+        <v>664</v>
+      </c>
+      <c r="H92" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="I92" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="J92" s="2" t="s">
+        <v>665</v>
+      </c>
+      <c r="K92" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="93" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>556</v>
+      </c>
+      <c r="B93" t="s">
+        <v>645</v>
+      </c>
+      <c r="D93" t="s">
+        <v>278</v>
+      </c>
+      <c r="E93" t="s">
+        <v>40</v>
+      </c>
+      <c r="G93" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="H93" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="I93" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J93" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="K93" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="94" spans="1:11" x14ac:dyDescent="0.25">
@@ -4892,7 +5684,7 @@
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="H2 I6:I7 I10 I12 H14 I18 I22 I24 I27 G34 I40 I42 I45 I52 I62" numberStoredAsText="1"/>
+    <ignoredError sqref="H2 I6:I7 I10 I12 H14 I18 I22 I24 I27 G34 I40 I42 I45 I52 I62 I72 H79 I80 I84 I88 I90 G91" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -5278,7 +6070,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84E3BB0D-5578-4069-B1C9-C3864EB2A429}">
-  <dimension ref="A1:F238"/>
+  <dimension ref="A1:F304"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="20.5703125" customWidth="1"/>
@@ -8880,10 +9672,10 @@
     </row>
     <row r="212" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
-        <v>281</v>
+        <v>535</v>
       </c>
       <c r="B212" t="s">
-        <v>249</v>
+        <v>622</v>
       </c>
       <c r="C212">
         <v>1</v>
@@ -8892,15 +9684,15 @@
         <v>1</v>
       </c>
       <c r="E212" t="s">
-        <v>58</v>
+        <v>306</v>
       </c>
     </row>
     <row r="213" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
-        <v>281</v>
+        <v>535</v>
       </c>
       <c r="B213" t="s">
-        <v>249</v>
+        <v>622</v>
       </c>
       <c r="C213">
         <v>2</v>
@@ -8909,15 +9701,15 @@
         <v>0</v>
       </c>
       <c r="E213" t="s">
-        <v>309</v>
+        <v>666</v>
       </c>
     </row>
     <row r="214" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
-        <v>281</v>
+        <v>535</v>
       </c>
       <c r="B214" t="s">
-        <v>249</v>
+        <v>622</v>
       </c>
       <c r="C214">
         <v>3</v>
@@ -8926,32 +9718,32 @@
         <v>0</v>
       </c>
       <c r="E214" t="s">
-        <v>310</v>
+        <v>667</v>
       </c>
     </row>
     <row r="215" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
-        <v>17</v>
+        <v>536</v>
       </c>
       <c r="B215" t="s">
-        <v>18</v>
+        <v>625</v>
       </c>
       <c r="C215">
         <v>1</v>
       </c>
       <c r="D215" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E215" t="s">
-        <v>58</v>
+        <v>668</v>
       </c>
     </row>
     <row r="216" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
-        <v>17</v>
+        <v>536</v>
       </c>
       <c r="B216" t="s">
-        <v>18</v>
+        <v>625</v>
       </c>
       <c r="C216">
         <v>2</v>
@@ -8960,15 +9752,15 @@
         <v>0</v>
       </c>
       <c r="E216" t="s">
-        <v>59</v>
+        <v>669</v>
       </c>
     </row>
     <row r="217" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
-        <v>17</v>
+        <v>536</v>
       </c>
       <c r="B217" t="s">
-        <v>18</v>
+        <v>625</v>
       </c>
       <c r="C217">
         <v>3</v>
@@ -8977,15 +9769,15 @@
         <v>0</v>
       </c>
       <c r="E217" t="s">
-        <v>60</v>
+        <v>670</v>
       </c>
     </row>
     <row r="218" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
-        <v>284</v>
+        <v>537</v>
       </c>
       <c r="B218" t="s">
-        <v>285</v>
+        <v>626</v>
       </c>
       <c r="C218">
         <v>1</v>
@@ -8994,15 +9786,15 @@
         <v>0</v>
       </c>
       <c r="E218" t="s">
-        <v>311</v>
+        <v>671</v>
       </c>
     </row>
     <row r="219" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
-        <v>284</v>
+        <v>537</v>
       </c>
       <c r="B219" t="s">
-        <v>285</v>
+        <v>626</v>
       </c>
       <c r="C219">
         <v>2</v>
@@ -9011,15 +9803,15 @@
         <v>0</v>
       </c>
       <c r="E219" t="s">
-        <v>312</v>
+        <v>672</v>
       </c>
     </row>
     <row r="220" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
-        <v>284</v>
+        <v>537</v>
       </c>
       <c r="B220" t="s">
-        <v>285</v>
+        <v>626</v>
       </c>
       <c r="C220">
         <v>3</v>
@@ -9028,32 +9820,32 @@
         <v>0</v>
       </c>
       <c r="E220" t="s">
-        <v>313</v>
+        <v>673</v>
       </c>
     </row>
     <row r="221" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
-        <v>96</v>
+        <v>538</v>
       </c>
       <c r="B221" t="s">
-        <v>97</v>
+        <v>627</v>
       </c>
       <c r="C221">
         <v>1</v>
       </c>
       <c r="D221" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E221" t="s">
-        <v>108</v>
+        <v>306</v>
       </c>
     </row>
     <row r="222" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
-        <v>96</v>
+        <v>538</v>
       </c>
       <c r="B222" t="s">
-        <v>97</v>
+        <v>627</v>
       </c>
       <c r="C222">
         <v>2</v>
@@ -9062,15 +9854,15 @@
         <v>0</v>
       </c>
       <c r="E222" t="s">
-        <v>109</v>
+        <v>674</v>
       </c>
     </row>
     <row r="223" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
-        <v>96</v>
+        <v>538</v>
       </c>
       <c r="B223" t="s">
-        <v>97</v>
+        <v>627</v>
       </c>
       <c r="C223">
         <v>3</v>
@@ -9079,15 +9871,15 @@
         <v>0</v>
       </c>
       <c r="E223" t="s">
-        <v>110</v>
+        <v>675</v>
       </c>
     </row>
     <row r="224" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
-        <v>314</v>
+        <v>539</v>
       </c>
       <c r="B224" t="s">
-        <v>315</v>
+        <v>628</v>
       </c>
       <c r="C224">
         <v>1</v>
@@ -9096,32 +9888,32 @@
         <v>1</v>
       </c>
       <c r="E224" t="s">
-        <v>320</v>
+        <v>306</v>
       </c>
     </row>
     <row r="225" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
-        <v>314</v>
+        <v>539</v>
       </c>
       <c r="B225" t="s">
-        <v>315</v>
+        <v>628</v>
       </c>
       <c r="C225">
         <v>2</v>
       </c>
       <c r="D225" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E225" t="s">
-        <v>58</v>
+        <v>676</v>
       </c>
     </row>
     <row r="226" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
-        <v>314</v>
+        <v>539</v>
       </c>
       <c r="B226" t="s">
-        <v>315</v>
+        <v>628</v>
       </c>
       <c r="C226">
         <v>3</v>
@@ -9130,15 +9922,15 @@
         <v>0</v>
       </c>
       <c r="E226" t="s">
-        <v>321</v>
+        <v>677</v>
       </c>
     </row>
     <row r="227" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
-        <v>76</v>
+        <v>540</v>
       </c>
       <c r="B227" t="s">
-        <v>77</v>
+        <v>629</v>
       </c>
       <c r="C227">
         <v>1</v>
@@ -9147,15 +9939,15 @@
         <v>1</v>
       </c>
       <c r="E227" t="s">
-        <v>82</v>
+        <v>306</v>
       </c>
     </row>
     <row r="228" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
-        <v>76</v>
+        <v>540</v>
       </c>
       <c r="B228" t="s">
-        <v>77</v>
+        <v>629</v>
       </c>
       <c r="C228">
         <v>2</v>
@@ -9164,15 +9956,15 @@
         <v>0</v>
       </c>
       <c r="E228" t="s">
-        <v>83</v>
+        <v>678</v>
       </c>
     </row>
     <row r="229" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
-        <v>76</v>
+        <v>540</v>
       </c>
       <c r="B229" t="s">
-        <v>77</v>
+        <v>629</v>
       </c>
       <c r="C229">
         <v>3</v>
@@ -9181,15 +9973,15 @@
         <v>0</v>
       </c>
       <c r="E229" t="s">
-        <v>84</v>
+        <v>679</v>
       </c>
     </row>
     <row r="230" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
-        <v>23</v>
+        <v>541</v>
       </c>
       <c r="B230" t="s">
-        <v>24</v>
+        <v>630</v>
       </c>
       <c r="C230">
         <v>1</v>
@@ -9198,15 +9990,15 @@
         <v>0</v>
       </c>
       <c r="E230" t="s">
-        <v>61</v>
+        <v>680</v>
       </c>
     </row>
     <row r="231" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
-        <v>23</v>
+        <v>541</v>
       </c>
       <c r="B231" t="s">
-        <v>24</v>
+        <v>630</v>
       </c>
       <c r="C231">
         <v>2</v>
@@ -9215,15 +10007,15 @@
         <v>0</v>
       </c>
       <c r="E231" t="s">
-        <v>62</v>
+        <v>681</v>
       </c>
     </row>
     <row r="232" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
-        <v>23</v>
+        <v>541</v>
       </c>
       <c r="B232" t="s">
-        <v>24</v>
+        <v>630</v>
       </c>
       <c r="C232">
         <v>3</v>
@@ -9232,32 +10024,32 @@
         <v>0</v>
       </c>
       <c r="E232" t="s">
-        <v>63</v>
+        <v>682</v>
       </c>
     </row>
     <row r="233" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
-        <v>29</v>
+        <v>542</v>
       </c>
       <c r="B233" t="s">
-        <v>30</v>
+        <v>631</v>
       </c>
       <c r="C233">
         <v>1</v>
       </c>
       <c r="D233" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E233" t="s">
-        <v>64</v>
+        <v>82</v>
       </c>
     </row>
     <row r="234" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
-        <v>29</v>
+        <v>542</v>
       </c>
       <c r="B234" t="s">
-        <v>30</v>
+        <v>631</v>
       </c>
       <c r="C234">
         <v>2</v>
@@ -9266,15 +10058,15 @@
         <v>0</v>
       </c>
       <c r="E234" t="s">
-        <v>65</v>
+        <v>683</v>
       </c>
     </row>
     <row r="235" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
-        <v>29</v>
+        <v>542</v>
       </c>
       <c r="B235" t="s">
-        <v>30</v>
+        <v>631</v>
       </c>
       <c r="C235">
         <v>3</v>
@@ -9283,32 +10075,32 @@
         <v>0</v>
       </c>
       <c r="E235" t="s">
-        <v>66</v>
+        <v>684</v>
       </c>
     </row>
     <row r="236" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
-        <v>36</v>
+        <v>543</v>
       </c>
       <c r="B236" t="s">
-        <v>37</v>
+        <v>632</v>
       </c>
       <c r="C236">
         <v>1</v>
       </c>
       <c r="D236" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E236" t="s">
-        <v>67</v>
+        <v>306</v>
       </c>
     </row>
     <row r="237" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
-        <v>36</v>
+        <v>543</v>
       </c>
       <c r="B237" t="s">
-        <v>37</v>
+        <v>632</v>
       </c>
       <c r="C237">
         <v>2</v>
@@ -9317,15 +10109,15 @@
         <v>0</v>
       </c>
       <c r="E237" t="s">
-        <v>68</v>
+        <v>685</v>
       </c>
     </row>
     <row r="238" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
-        <v>36</v>
+        <v>543</v>
       </c>
       <c r="B238" t="s">
-        <v>37</v>
+        <v>632</v>
       </c>
       <c r="C238">
         <v>3</v>
@@ -9334,6 +10126,1128 @@
         <v>0</v>
       </c>
       <c r="E238" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="239" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A239" t="s">
+        <v>544</v>
+      </c>
+      <c r="B239" t="s">
+        <v>633</v>
+      </c>
+      <c r="C239">
+        <v>1</v>
+      </c>
+      <c r="D239" t="b">
+        <v>1</v>
+      </c>
+      <c r="E239" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="240" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A240" t="s">
+        <v>544</v>
+      </c>
+      <c r="B240" t="s">
+        <v>633</v>
+      </c>
+      <c r="C240">
+        <v>2</v>
+      </c>
+      <c r="D240" t="b">
+        <v>0</v>
+      </c>
+      <c r="E240" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="241" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A241" t="s">
+        <v>544</v>
+      </c>
+      <c r="B241" t="s">
+        <v>633</v>
+      </c>
+      <c r="C241">
+        <v>3</v>
+      </c>
+      <c r="D241" t="b">
+        <v>0</v>
+      </c>
+      <c r="E241" t="s">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="242" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A242" t="s">
+        <v>545</v>
+      </c>
+      <c r="B242" t="s">
+        <v>634</v>
+      </c>
+      <c r="C242">
+        <v>1</v>
+      </c>
+      <c r="D242" t="b">
+        <v>1</v>
+      </c>
+      <c r="E242" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="243" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A243" t="s">
+        <v>545</v>
+      </c>
+      <c r="B243" t="s">
+        <v>634</v>
+      </c>
+      <c r="C243">
+        <v>2</v>
+      </c>
+      <c r="D243" t="b">
+        <v>0</v>
+      </c>
+      <c r="E243" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="244" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A244" t="s">
+        <v>545</v>
+      </c>
+      <c r="B244" t="s">
+        <v>634</v>
+      </c>
+      <c r="C244">
+        <v>3</v>
+      </c>
+      <c r="D244" t="b">
+        <v>0</v>
+      </c>
+      <c r="E244" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="245" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A245" t="s">
+        <v>546</v>
+      </c>
+      <c r="B245" t="s">
+        <v>635</v>
+      </c>
+      <c r="C245">
+        <v>1</v>
+      </c>
+      <c r="D245" t="b">
+        <v>1</v>
+      </c>
+      <c r="E245" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="246" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A246" t="s">
+        <v>546</v>
+      </c>
+      <c r="B246" t="s">
+        <v>635</v>
+      </c>
+      <c r="C246">
+        <v>2</v>
+      </c>
+      <c r="D246" t="b">
+        <v>0</v>
+      </c>
+      <c r="E246" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="247" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A247" t="s">
+        <v>546</v>
+      </c>
+      <c r="B247" t="s">
+        <v>635</v>
+      </c>
+      <c r="C247">
+        <v>3</v>
+      </c>
+      <c r="D247" t="b">
+        <v>0</v>
+      </c>
+      <c r="E247" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="248" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A248" t="s">
+        <v>547</v>
+      </c>
+      <c r="B248" t="s">
+        <v>636</v>
+      </c>
+      <c r="C248">
+        <v>1</v>
+      </c>
+      <c r="D248" t="b">
+        <v>0</v>
+      </c>
+      <c r="E248" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="249" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A249" t="s">
+        <v>547</v>
+      </c>
+      <c r="B249" t="s">
+        <v>636</v>
+      </c>
+      <c r="C249">
+        <v>2</v>
+      </c>
+      <c r="D249" t="b">
+        <v>0</v>
+      </c>
+      <c r="E249" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="250" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A250" t="s">
+        <v>547</v>
+      </c>
+      <c r="B250" t="s">
+        <v>636</v>
+      </c>
+      <c r="C250">
+        <v>3</v>
+      </c>
+      <c r="D250" t="b">
+        <v>0</v>
+      </c>
+      <c r="E250" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="251" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A251" t="s">
+        <v>548</v>
+      </c>
+      <c r="B251" t="s">
+        <v>637</v>
+      </c>
+      <c r="C251">
+        <v>1</v>
+      </c>
+      <c r="D251" t="b">
+        <v>1</v>
+      </c>
+      <c r="E251" t="s">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="252" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A252" t="s">
+        <v>548</v>
+      </c>
+      <c r="B252" t="s">
+        <v>637</v>
+      </c>
+      <c r="C252">
+        <v>2</v>
+      </c>
+      <c r="D252" t="b">
+        <v>1</v>
+      </c>
+      <c r="E252" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="253" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A253" t="s">
+        <v>548</v>
+      </c>
+      <c r="B253" t="s">
+        <v>637</v>
+      </c>
+      <c r="C253">
+        <v>3</v>
+      </c>
+      <c r="D253" t="b">
+        <v>0</v>
+      </c>
+      <c r="E253" t="s">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="254" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A254" t="s">
+        <v>549</v>
+      </c>
+      <c r="B254" t="s">
+        <v>638</v>
+      </c>
+      <c r="C254">
+        <v>1</v>
+      </c>
+      <c r="D254" t="b">
+        <v>0</v>
+      </c>
+      <c r="E254" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="255" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A255" t="s">
+        <v>549</v>
+      </c>
+      <c r="B255" t="s">
+        <v>638</v>
+      </c>
+      <c r="C255">
+        <v>2</v>
+      </c>
+      <c r="D255" t="b">
+        <v>0</v>
+      </c>
+      <c r="E255" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="256" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A256" t="s">
+        <v>549</v>
+      </c>
+      <c r="B256" t="s">
+        <v>638</v>
+      </c>
+      <c r="C256">
+        <v>3</v>
+      </c>
+      <c r="D256" t="b">
+        <v>0</v>
+      </c>
+      <c r="E256" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="257" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A257" t="s">
+        <v>550</v>
+      </c>
+      <c r="B257" t="s">
+        <v>639</v>
+      </c>
+      <c r="C257">
+        <v>1</v>
+      </c>
+      <c r="D257" t="b">
+        <v>1</v>
+      </c>
+      <c r="E257" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="258" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A258" t="s">
+        <v>550</v>
+      </c>
+      <c r="B258" t="s">
+        <v>639</v>
+      </c>
+      <c r="C258">
+        <v>2</v>
+      </c>
+      <c r="D258" t="b">
+        <v>0</v>
+      </c>
+      <c r="E258" t="s">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="259" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A259" t="s">
+        <v>550</v>
+      </c>
+      <c r="B259" t="s">
+        <v>639</v>
+      </c>
+      <c r="C259">
+        <v>3</v>
+      </c>
+      <c r="D259" t="b">
+        <v>0</v>
+      </c>
+      <c r="E259" t="s">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="260" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A260" t="s">
+        <v>551</v>
+      </c>
+      <c r="B260" t="s">
+        <v>640</v>
+      </c>
+      <c r="C260">
+        <v>1</v>
+      </c>
+      <c r="D260" t="b">
+        <v>1</v>
+      </c>
+      <c r="E260" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="261" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A261" t="s">
+        <v>551</v>
+      </c>
+      <c r="B261" t="s">
+        <v>640</v>
+      </c>
+      <c r="C261">
+        <v>2</v>
+      </c>
+      <c r="D261" t="b">
+        <v>0</v>
+      </c>
+      <c r="E261" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="262" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A262" t="s">
+        <v>551</v>
+      </c>
+      <c r="B262" t="s">
+        <v>640</v>
+      </c>
+      <c r="C262">
+        <v>3</v>
+      </c>
+      <c r="D262" t="b">
+        <v>0</v>
+      </c>
+      <c r="E262" t="s">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="263" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A263" t="s">
+        <v>552</v>
+      </c>
+      <c r="B263" t="s">
+        <v>641</v>
+      </c>
+      <c r="C263">
+        <v>1</v>
+      </c>
+      <c r="D263" t="b">
+        <v>1</v>
+      </c>
+      <c r="E263" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="264" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A264" t="s">
+        <v>552</v>
+      </c>
+      <c r="B264" t="s">
+        <v>641</v>
+      </c>
+      <c r="C264">
+        <v>2</v>
+      </c>
+      <c r="D264" t="b">
+        <v>0</v>
+      </c>
+      <c r="E264" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="265" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A265" t="s">
+        <v>552</v>
+      </c>
+      <c r="B265" t="s">
+        <v>641</v>
+      </c>
+      <c r="C265">
+        <v>3</v>
+      </c>
+      <c r="D265" t="b">
+        <v>0</v>
+      </c>
+      <c r="E265" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="266" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A266" t="s">
+        <v>553</v>
+      </c>
+      <c r="B266" t="s">
+        <v>642</v>
+      </c>
+      <c r="C266">
+        <v>1</v>
+      </c>
+      <c r="D266" t="b">
+        <v>0</v>
+      </c>
+      <c r="E266" t="s">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="267" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A267" t="s">
+        <v>553</v>
+      </c>
+      <c r="B267" t="s">
+        <v>642</v>
+      </c>
+      <c r="C267">
+        <v>2</v>
+      </c>
+      <c r="D267" t="b">
+        <v>0</v>
+      </c>
+      <c r="E267" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="268" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A268" t="s">
+        <v>553</v>
+      </c>
+      <c r="B268" t="s">
+        <v>642</v>
+      </c>
+      <c r="C268">
+        <v>3</v>
+      </c>
+      <c r="D268" t="b">
+        <v>0</v>
+      </c>
+      <c r="E268" t="s">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="269" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A269" t="s">
+        <v>554</v>
+      </c>
+      <c r="B269" t="s">
+        <v>643</v>
+      </c>
+      <c r="C269">
+        <v>1</v>
+      </c>
+      <c r="D269" t="b">
+        <v>0</v>
+      </c>
+      <c r="E269" t="s">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="270" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A270" t="s">
+        <v>554</v>
+      </c>
+      <c r="B270" t="s">
+        <v>643</v>
+      </c>
+      <c r="C270">
+        <v>2</v>
+      </c>
+      <c r="D270" t="b">
+        <v>0</v>
+      </c>
+      <c r="E270" t="s">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="271" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A271" t="s">
+        <v>554</v>
+      </c>
+      <c r="B271" t="s">
+        <v>643</v>
+      </c>
+      <c r="C271">
+        <v>3</v>
+      </c>
+      <c r="D271" t="b">
+        <v>0</v>
+      </c>
+      <c r="E271" t="s">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="272" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A272" t="s">
+        <v>555</v>
+      </c>
+      <c r="B272" t="s">
+        <v>644</v>
+      </c>
+      <c r="C272">
+        <v>1</v>
+      </c>
+      <c r="D272" t="b">
+        <v>1</v>
+      </c>
+      <c r="E272" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="273" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A273" t="s">
+        <v>555</v>
+      </c>
+      <c r="B273" t="s">
+        <v>644</v>
+      </c>
+      <c r="C273">
+        <v>2</v>
+      </c>
+      <c r="D273" t="b">
+        <v>0</v>
+      </c>
+      <c r="E273" t="s">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="274" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A274" t="s">
+        <v>555</v>
+      </c>
+      <c r="B274" t="s">
+        <v>644</v>
+      </c>
+      <c r="C274">
+        <v>3</v>
+      </c>
+      <c r="D274" t="b">
+        <v>0</v>
+      </c>
+      <c r="E274" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="275" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A275" t="s">
+        <v>556</v>
+      </c>
+      <c r="B275" t="s">
+        <v>645</v>
+      </c>
+      <c r="C275">
+        <v>1</v>
+      </c>
+      <c r="D275" t="b">
+        <v>1</v>
+      </c>
+      <c r="E275" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="276" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A276" t="s">
+        <v>556</v>
+      </c>
+      <c r="B276" t="s">
+        <v>645</v>
+      </c>
+      <c r="C276">
+        <v>2</v>
+      </c>
+      <c r="D276" t="b">
+        <v>0</v>
+      </c>
+      <c r="E276" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="277" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A277" t="s">
+        <v>556</v>
+      </c>
+      <c r="B277" t="s">
+        <v>645</v>
+      </c>
+      <c r="C277">
+        <v>3</v>
+      </c>
+      <c r="D277" t="b">
+        <v>0</v>
+      </c>
+      <c r="E277" t="s">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="278" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A278" t="s">
+        <v>281</v>
+      </c>
+      <c r="B278" t="s">
+        <v>249</v>
+      </c>
+      <c r="C278">
+        <v>1</v>
+      </c>
+      <c r="D278" t="b">
+        <v>1</v>
+      </c>
+      <c r="E278" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="279" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A279" t="s">
+        <v>281</v>
+      </c>
+      <c r="B279" t="s">
+        <v>249</v>
+      </c>
+      <c r="C279">
+        <v>2</v>
+      </c>
+      <c r="D279" t="b">
+        <v>0</v>
+      </c>
+      <c r="E279" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="280" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A280" t="s">
+        <v>281</v>
+      </c>
+      <c r="B280" t="s">
+        <v>249</v>
+      </c>
+      <c r="C280">
+        <v>3</v>
+      </c>
+      <c r="D280" t="b">
+        <v>0</v>
+      </c>
+      <c r="E280" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="281" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A281" t="s">
+        <v>17</v>
+      </c>
+      <c r="B281" t="s">
+        <v>18</v>
+      </c>
+      <c r="C281">
+        <v>1</v>
+      </c>
+      <c r="D281" t="b">
+        <v>1</v>
+      </c>
+      <c r="E281" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="282" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A282" t="s">
+        <v>17</v>
+      </c>
+      <c r="B282" t="s">
+        <v>18</v>
+      </c>
+      <c r="C282">
+        <v>2</v>
+      </c>
+      <c r="D282" t="b">
+        <v>0</v>
+      </c>
+      <c r="E282" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="283" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A283" t="s">
+        <v>17</v>
+      </c>
+      <c r="B283" t="s">
+        <v>18</v>
+      </c>
+      <c r="C283">
+        <v>3</v>
+      </c>
+      <c r="D283" t="b">
+        <v>0</v>
+      </c>
+      <c r="E283" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="284" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A284" t="s">
+        <v>284</v>
+      </c>
+      <c r="B284" t="s">
+        <v>285</v>
+      </c>
+      <c r="C284">
+        <v>1</v>
+      </c>
+      <c r="D284" t="b">
+        <v>0</v>
+      </c>
+      <c r="E284" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="285" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A285" t="s">
+        <v>284</v>
+      </c>
+      <c r="B285" t="s">
+        <v>285</v>
+      </c>
+      <c r="C285">
+        <v>2</v>
+      </c>
+      <c r="D285" t="b">
+        <v>0</v>
+      </c>
+      <c r="E285" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="286" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A286" t="s">
+        <v>284</v>
+      </c>
+      <c r="B286" t="s">
+        <v>285</v>
+      </c>
+      <c r="C286">
+        <v>3</v>
+      </c>
+      <c r="D286" t="b">
+        <v>0</v>
+      </c>
+      <c r="E286" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="287" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A287" t="s">
+        <v>96</v>
+      </c>
+      <c r="B287" t="s">
+        <v>97</v>
+      </c>
+      <c r="C287">
+        <v>1</v>
+      </c>
+      <c r="D287" t="b">
+        <v>0</v>
+      </c>
+      <c r="E287" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="288" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A288" t="s">
+        <v>96</v>
+      </c>
+      <c r="B288" t="s">
+        <v>97</v>
+      </c>
+      <c r="C288">
+        <v>2</v>
+      </c>
+      <c r="D288" t="b">
+        <v>0</v>
+      </c>
+      <c r="E288" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="289" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A289" t="s">
+        <v>96</v>
+      </c>
+      <c r="B289" t="s">
+        <v>97</v>
+      </c>
+      <c r="C289">
+        <v>3</v>
+      </c>
+      <c r="D289" t="b">
+        <v>0</v>
+      </c>
+      <c r="E289" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="290" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A290" t="s">
+        <v>314</v>
+      </c>
+      <c r="B290" t="s">
+        <v>315</v>
+      </c>
+      <c r="C290">
+        <v>1</v>
+      </c>
+      <c r="D290" t="b">
+        <v>1</v>
+      </c>
+      <c r="E290" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="291" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A291" t="s">
+        <v>314</v>
+      </c>
+      <c r="B291" t="s">
+        <v>315</v>
+      </c>
+      <c r="C291">
+        <v>2</v>
+      </c>
+      <c r="D291" t="b">
+        <v>1</v>
+      </c>
+      <c r="E291" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="292" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A292" t="s">
+        <v>314</v>
+      </c>
+      <c r="B292" t="s">
+        <v>315</v>
+      </c>
+      <c r="C292">
+        <v>3</v>
+      </c>
+      <c r="D292" t="b">
+        <v>0</v>
+      </c>
+      <c r="E292" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="293" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A293" t="s">
+        <v>76</v>
+      </c>
+      <c r="B293" t="s">
+        <v>77</v>
+      </c>
+      <c r="C293">
+        <v>1</v>
+      </c>
+      <c r="D293" t="b">
+        <v>1</v>
+      </c>
+      <c r="E293" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="294" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A294" t="s">
+        <v>76</v>
+      </c>
+      <c r="B294" t="s">
+        <v>77</v>
+      </c>
+      <c r="C294">
+        <v>2</v>
+      </c>
+      <c r="D294" t="b">
+        <v>0</v>
+      </c>
+      <c r="E294" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="295" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A295" t="s">
+        <v>76</v>
+      </c>
+      <c r="B295" t="s">
+        <v>77</v>
+      </c>
+      <c r="C295">
+        <v>3</v>
+      </c>
+      <c r="D295" t="b">
+        <v>0</v>
+      </c>
+      <c r="E295" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="296" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A296" t="s">
+        <v>23</v>
+      </c>
+      <c r="B296" t="s">
+        <v>24</v>
+      </c>
+      <c r="C296">
+        <v>1</v>
+      </c>
+      <c r="D296" t="b">
+        <v>0</v>
+      </c>
+      <c r="E296" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="297" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A297" t="s">
+        <v>23</v>
+      </c>
+      <c r="B297" t="s">
+        <v>24</v>
+      </c>
+      <c r="C297">
+        <v>2</v>
+      </c>
+      <c r="D297" t="b">
+        <v>0</v>
+      </c>
+      <c r="E297" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="298" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A298" t="s">
+        <v>23</v>
+      </c>
+      <c r="B298" t="s">
+        <v>24</v>
+      </c>
+      <c r="C298">
+        <v>3</v>
+      </c>
+      <c r="D298" t="b">
+        <v>0</v>
+      </c>
+      <c r="E298" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="299" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A299" t="s">
+        <v>29</v>
+      </c>
+      <c r="B299" t="s">
+        <v>30</v>
+      </c>
+      <c r="C299">
+        <v>1</v>
+      </c>
+      <c r="D299" t="b">
+        <v>0</v>
+      </c>
+      <c r="E299" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="300" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A300" t="s">
+        <v>29</v>
+      </c>
+      <c r="B300" t="s">
+        <v>30</v>
+      </c>
+      <c r="C300">
+        <v>2</v>
+      </c>
+      <c r="D300" t="b">
+        <v>0</v>
+      </c>
+      <c r="E300" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="301" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A301" t="s">
+        <v>29</v>
+      </c>
+      <c r="B301" t="s">
+        <v>30</v>
+      </c>
+      <c r="C301">
+        <v>3</v>
+      </c>
+      <c r="D301" t="b">
+        <v>0</v>
+      </c>
+      <c r="E301" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="302" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A302" t="s">
+        <v>36</v>
+      </c>
+      <c r="B302" t="s">
+        <v>37</v>
+      </c>
+      <c r="C302">
+        <v>1</v>
+      </c>
+      <c r="D302" t="b">
+        <v>0</v>
+      </c>
+      <c r="E302" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="303" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A303" t="s">
+        <v>36</v>
+      </c>
+      <c r="B303" t="s">
+        <v>37</v>
+      </c>
+      <c r="C303">
+        <v>2</v>
+      </c>
+      <c r="D303" t="b">
+        <v>0</v>
+      </c>
+      <c r="E303" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="304" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A304" t="s">
+        <v>36</v>
+      </c>
+      <c r="B304" t="s">
+        <v>37</v>
+      </c>
+      <c r="C304">
+        <v>3</v>
+      </c>
+      <c r="D304" t="b">
+        <v>0</v>
+      </c>
+      <c r="E304" t="s">
         <v>69</v>
       </c>
     </row>

--- a/data/Fate-Spreadsheet.xlsx
+++ b/data/Fate-Spreadsheet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Important\Python\Fate-Wiki\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74414681-1B7E-4E20-8CB8-128DF038A562}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF92ED3E-3185-4BAF-9CCD-CBCFD6240792}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{B05E798F-9EF6-4508-A0A4-311D06661AED}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{B05E798F-9EF6-4508-A0A4-311D06661AED}"/>
   </bookViews>
   <sheets>
     <sheet name="Servants" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1860" uniqueCount="717">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1881" uniqueCount="738">
   <si>
     <t>servant_id</t>
   </si>
@@ -2194,6 +2194,69 @@
   </si>
   <si>
     <t>Twilit Empire</t>
+  </si>
+  <si>
+    <t>astolfo</t>
+  </si>
+  <si>
+    <t>achilles</t>
+  </si>
+  <si>
+    <t>ushiwakamaru</t>
+  </si>
+  <si>
+    <t>ozymandias</t>
+  </si>
+  <si>
+    <t>sitonai</t>
+  </si>
+  <si>
+    <t>odysseus</t>
+  </si>
+  <si>
+    <t>boudica</t>
+  </si>
+  <si>
+    <t>quetzalcoatl</t>
+  </si>
+  <si>
+    <t>hephaistion</t>
+  </si>
+  <si>
+    <t>mandricardo</t>
+  </si>
+  <si>
+    <t>ivan-the-terrible</t>
+  </si>
+  <si>
+    <t>edward-teach</t>
+  </si>
+  <si>
+    <t>saint-georgios</t>
+  </si>
+  <si>
+    <t>francis-drake</t>
+  </si>
+  <si>
+    <t>queen-medb</t>
+  </si>
+  <si>
+    <t>bartholomew-roberts</t>
+  </si>
+  <si>
+    <t>sakamoto-ryouma</t>
+  </si>
+  <si>
+    <t>saint-martha</t>
+  </si>
+  <si>
+    <t>captain-nemo</t>
+  </si>
+  <si>
+    <t>taisui-xingjun</t>
+  </si>
+  <si>
+    <t>constantine-xi</t>
   </si>
 </sst>
 </file>
@@ -4844,6 +4907,9 @@
       <c r="B73" t="s">
         <v>625</v>
       </c>
+      <c r="C73" t="s">
+        <v>717</v>
+      </c>
       <c r="D73" t="s">
         <v>278</v>
       </c>
@@ -4873,6 +4939,9 @@
       <c r="B74" t="s">
         <v>626</v>
       </c>
+      <c r="C74" t="s">
+        <v>718</v>
+      </c>
       <c r="D74" t="s">
         <v>278</v>
       </c>
@@ -4899,6 +4968,9 @@
       <c r="B75" t="s">
         <v>627</v>
       </c>
+      <c r="C75" t="s">
+        <v>727</v>
+      </c>
       <c r="D75" t="s">
         <v>278</v>
       </c>
@@ -4925,6 +4997,9 @@
       <c r="B76" t="s">
         <v>628</v>
       </c>
+      <c r="C76" t="s">
+        <v>730</v>
+      </c>
       <c r="D76" t="s">
         <v>278</v>
       </c>
@@ -4951,6 +5026,9 @@
       <c r="B77" t="s">
         <v>629</v>
       </c>
+      <c r="C77" t="s">
+        <v>719</v>
+      </c>
       <c r="D77" t="s">
         <v>278</v>
       </c>
@@ -4977,6 +5055,9 @@
       <c r="B78" t="s">
         <v>630</v>
       </c>
+      <c r="C78" t="s">
+        <v>720</v>
+      </c>
       <c r="D78" t="s">
         <v>278</v>
       </c>
@@ -5006,6 +5087,9 @@
       <c r="B79" t="s">
         <v>631</v>
       </c>
+      <c r="C79" t="s">
+        <v>721</v>
+      </c>
       <c r="D79" t="s">
         <v>79</v>
       </c>
@@ -5035,6 +5119,9 @@
       <c r="B80" t="s">
         <v>632</v>
       </c>
+      <c r="C80" t="s">
+        <v>722</v>
+      </c>
       <c r="D80" t="s">
         <v>278</v>
       </c>
@@ -5064,6 +5151,9 @@
       <c r="B81" t="s">
         <v>633</v>
       </c>
+      <c r="C81" t="s">
+        <v>731</v>
+      </c>
       <c r="D81" t="s">
         <v>278</v>
       </c>
@@ -5093,6 +5183,9 @@
       <c r="B82" t="s">
         <v>634</v>
       </c>
+      <c r="C82" t="s">
+        <v>732</v>
+      </c>
       <c r="D82" t="s">
         <v>278</v>
       </c>
@@ -5119,6 +5212,9 @@
       <c r="B83" t="s">
         <v>635</v>
       </c>
+      <c r="C83" t="s">
+        <v>723</v>
+      </c>
       <c r="D83" t="s">
         <v>278</v>
       </c>
@@ -5145,6 +5241,9 @@
       <c r="B84" t="s">
         <v>636</v>
       </c>
+      <c r="C84" t="s">
+        <v>724</v>
+      </c>
       <c r="D84" t="s">
         <v>278</v>
       </c>
@@ -5174,6 +5273,9 @@
       <c r="B85" t="s">
         <v>637</v>
       </c>
+      <c r="C85" t="s">
+        <v>725</v>
+      </c>
       <c r="D85" t="s">
         <v>646</v>
       </c>
@@ -5203,6 +5305,9 @@
       <c r="B86" t="s">
         <v>638</v>
       </c>
+      <c r="C86" t="s">
+        <v>733</v>
+      </c>
       <c r="D86" t="s">
         <v>278</v>
       </c>
@@ -5229,6 +5334,9 @@
       <c r="B87" t="s">
         <v>639</v>
       </c>
+      <c r="C87" t="s">
+        <v>728</v>
+      </c>
       <c r="D87" t="s">
         <v>278</v>
       </c>
@@ -5255,6 +5363,9 @@
       <c r="B88" t="s">
         <v>640</v>
       </c>
+      <c r="C88" t="s">
+        <v>726</v>
+      </c>
       <c r="D88" t="s">
         <v>278</v>
       </c>
@@ -5284,6 +5395,9 @@
       <c r="B89" t="s">
         <v>641</v>
       </c>
+      <c r="C89" t="s">
+        <v>734</v>
+      </c>
       <c r="D89" t="s">
         <v>278</v>
       </c>
@@ -5313,6 +5427,9 @@
       <c r="B90" t="s">
         <v>642</v>
       </c>
+      <c r="C90" t="s">
+        <v>729</v>
+      </c>
       <c r="D90" t="s">
         <v>278</v>
       </c>
@@ -5342,6 +5459,9 @@
       <c r="B91" t="s">
         <v>643</v>
       </c>
+      <c r="C91" t="s">
+        <v>735</v>
+      </c>
       <c r="D91" t="s">
         <v>278</v>
       </c>
@@ -5371,6 +5491,9 @@
       <c r="B92" t="s">
         <v>644</v>
       </c>
+      <c r="C92" t="s">
+        <v>736</v>
+      </c>
       <c r="D92" t="s">
         <v>79</v>
       </c>
@@ -5399,6 +5522,9 @@
       </c>
       <c r="B93" t="s">
         <v>645</v>
+      </c>
+      <c r="C93" t="s">
+        <v>737</v>
       </c>
       <c r="D93" t="s">
         <v>278</v>

--- a/data/Fate-Spreadsheet.xlsx
+++ b/data/Fate-Spreadsheet.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Important\Python\Fate-Wiki\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pixel\Documents\Projects\Fate-Wiki\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF92ED3E-3185-4BAF-9CCD-CBCFD6240792}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4E4DA1A-8EF8-4ECB-96CB-33B68CAC1907}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{B05E798F-9EF6-4508-A0A4-311D06661AED}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{B05E798F-9EF6-4508-A0A4-311D06661AED}"/>
   </bookViews>
   <sheets>
     <sheet name="Servants" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1881" uniqueCount="738">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2478" uniqueCount="950">
   <si>
     <t>servant_id</t>
   </si>
@@ -2257,6 +2257,642 @@
   </si>
   <si>
     <t>constantine-xi</t>
+  </si>
+  <si>
+    <t>S0094</t>
+  </si>
+  <si>
+    <t>S0095</t>
+  </si>
+  <si>
+    <t>S0096</t>
+  </si>
+  <si>
+    <t>Gilles de Rais</t>
+  </si>
+  <si>
+    <t>gilles-de-rais</t>
+  </si>
+  <si>
+    <t>2,2,2,3,3,3,4,4,5,5</t>
+  </si>
+  <si>
+    <t>Preparation,Preparation</t>
+  </si>
+  <si>
+    <t>Tamamo no Mae</t>
+  </si>
+  <si>
+    <t>tamamo-no-mae</t>
+  </si>
+  <si>
+    <t>Hans Christian Andersen</t>
+  </si>
+  <si>
+    <t>hans-christian-andersen</t>
+  </si>
+  <si>
+    <t>2,2,2,2,3,3,</t>
+  </si>
+  <si>
+    <t>Prelati's Spellbook (Call the Ancients)</t>
+  </si>
+  <si>
+    <t>Prelati's Spellbook (Mass Summoning)</t>
+  </si>
+  <si>
+    <t>Amaterasu's Blessing (Transcendence)</t>
+  </si>
+  <si>
+    <t>Amaterasu's Blessing (Cascade)</t>
+  </si>
+  <si>
+    <t>Witchcraft</t>
+  </si>
+  <si>
+    <t>Märchen Meines Lebens</t>
+  </si>
+  <si>
+    <t>Curses of the Readers</t>
+  </si>
+  <si>
+    <t>S0098</t>
+  </si>
+  <si>
+    <t>S0099</t>
+  </si>
+  <si>
+    <t>S0100</t>
+  </si>
+  <si>
+    <t>William Shakespeare</t>
+  </si>
+  <si>
+    <t>william-shakespeare</t>
+  </si>
+  <si>
+    <t>Wildcard</t>
+  </si>
+  <si>
+    <t>Preparation,Surveil</t>
+  </si>
+  <si>
+    <t>First Folio</t>
+  </si>
+  <si>
+    <t>Inspire Heroism</t>
+  </si>
+  <si>
+    <t>Leonardo Da Vinci</t>
+  </si>
+  <si>
+    <t>leonardo-da-vinci</t>
+  </si>
+  <si>
+    <t>Uomo Universale</t>
+  </si>
+  <si>
+    <t>Da Vinci's Workshop</t>
+  </si>
+  <si>
+    <t>Natural Born Genius</t>
+  </si>
+  <si>
+    <t>Wolfgang Amadeus Mozart</t>
+  </si>
+  <si>
+    <t>wolfgang-amadeus-mozart</t>
+  </si>
+  <si>
+    <t>Requiem</t>
+  </si>
+  <si>
+    <t>Eine Kleine Nachtmusik</t>
+  </si>
+  <si>
+    <t>S0102</t>
+  </si>
+  <si>
+    <t>S0103</t>
+  </si>
+  <si>
+    <t>S0104</t>
+  </si>
+  <si>
+    <t>S0105</t>
+  </si>
+  <si>
+    <t>S0106</t>
+  </si>
+  <si>
+    <t>S0107</t>
+  </si>
+  <si>
+    <t>Ashiya Douman</t>
+  </si>
+  <si>
+    <t>ashiya-douman</t>
+  </si>
+  <si>
+    <t>Curse of Annihilation</t>
+  </si>
+  <si>
+    <t>Ridicule Cat</t>
+  </si>
+  <si>
+    <t>Merlin</t>
+  </si>
+  <si>
+    <t>Garden of Avalon</t>
+  </si>
+  <si>
+    <t>Sea of Flowers</t>
+  </si>
+  <si>
+    <t>Dreamlike Charisma</t>
+  </si>
+  <si>
+    <t>merlin</t>
+  </si>
+  <si>
+    <t>Thomas Edison</t>
+  </si>
+  <si>
+    <t>thomas-edison</t>
+  </si>
+  <si>
+    <t>World Faith Domination</t>
+  </si>
+  <si>
+    <t>Galvanic Cell</t>
+  </si>
+  <si>
+    <t>Fordism</t>
+  </si>
+  <si>
+    <t>Anastasia Romanova</t>
+  </si>
+  <si>
+    <t>anastasia-romanova</t>
+  </si>
+  <si>
+    <t>3,3,4,4,4,5</t>
+  </si>
+  <si>
+    <t>Viy, Viy, Viy</t>
+  </si>
+  <si>
+    <t>Sumerki Kremlin</t>
+  </si>
+  <si>
+    <t>Maxwell's Demon</t>
+  </si>
+  <si>
+    <t>maxwells-demon</t>
+  </si>
+  <si>
+    <t>Maxwell's Demon (Noble Phantasm)</t>
+  </si>
+  <si>
+    <t>The Devil's Proof</t>
+  </si>
+  <si>
+    <t>King Gilgamesh</t>
+  </si>
+  <si>
+    <t>king-gilgamesh</t>
+  </si>
+  <si>
+    <t>Melammu Dingir</t>
+  </si>
+  <si>
+    <t>Gate of Babylon (King Gilgamesh)</t>
+  </si>
+  <si>
+    <t>S0109</t>
+  </si>
+  <si>
+    <t>S0110</t>
+  </si>
+  <si>
+    <t>S0111</t>
+  </si>
+  <si>
+    <t>S0112</t>
+  </si>
+  <si>
+    <t>S0113</t>
+  </si>
+  <si>
+    <t>S0114</t>
+  </si>
+  <si>
+    <t>S0115</t>
+  </si>
+  <si>
+    <t>S0116</t>
+  </si>
+  <si>
+    <t>S0117</t>
+  </si>
+  <si>
+    <t>S0118</t>
+  </si>
+  <si>
+    <t>S0119</t>
+  </si>
+  <si>
+    <t>S0120</t>
+  </si>
+  <si>
+    <t>Mephistopheles</t>
+  </si>
+  <si>
+    <t>mephistopheles</t>
+  </si>
+  <si>
+    <t>Scathach Skadi</t>
+  </si>
+  <si>
+    <t>scathach-skadi</t>
+  </si>
+  <si>
+    <t>Xuangzang Sanzang</t>
+  </si>
+  <si>
+    <t>xuangzang-sanzang</t>
+  </si>
+  <si>
+    <t>Nitocris</t>
+  </si>
+  <si>
+    <t>nitocris</t>
+  </si>
+  <si>
+    <t>Helena Blavatsky</t>
+  </si>
+  <si>
+    <t>Lady Avalon</t>
+  </si>
+  <si>
+    <t>Nursery Rhyme</t>
+  </si>
+  <si>
+    <t>lady-avalon</t>
+  </si>
+  <si>
+    <t>nursery-rhyme</t>
+  </si>
+  <si>
+    <t>helena-blavatsky</t>
+  </si>
+  <si>
+    <t>Ticktock Bomb</t>
+  </si>
+  <si>
+    <t>Combustive Centipede</t>
+  </si>
+  <si>
+    <t>2,5</t>
+  </si>
+  <si>
+    <t>3,3,4,5,5</t>
+  </si>
+  <si>
+    <t>Luck,Luck,Luck</t>
+  </si>
+  <si>
+    <t>3,4,4,4,5,5</t>
+  </si>
+  <si>
+    <t>2,3,4,4,5,5</t>
+  </si>
+  <si>
+    <t>Castle of Skye</t>
+  </si>
+  <si>
+    <t>Allfather's Wisdom</t>
+  </si>
+  <si>
+    <t>Primordial Runes</t>
+  </si>
+  <si>
+    <t>Buddha Palm</t>
+  </si>
+  <si>
+    <t>Teachings of Tripitaka</t>
+  </si>
+  <si>
+    <t>Divine Inspiration</t>
+  </si>
+  <si>
+    <t>Nether Mirror</t>
+  </si>
+  <si>
+    <t>Child of Horus</t>
+  </si>
+  <si>
+    <t>Sacred Offering</t>
+  </si>
+  <si>
+    <t>Hope of Avalon</t>
+  </si>
+  <si>
+    <t>Queen's Glass Game</t>
+  </si>
+  <si>
+    <t>Nameless Forest</t>
+  </si>
+  <si>
+    <t>Jabberwock</t>
+  </si>
+  <si>
+    <t>Sanat Kumara</t>
+  </si>
+  <si>
+    <t>Colonel Olcott</t>
+  </si>
+  <si>
+    <t>Search for the Unknown</t>
+  </si>
+  <si>
+    <t>Sasaki Kojirou</t>
+  </si>
+  <si>
+    <t>sasaki-kojirou</t>
+  </si>
+  <si>
+    <t>Hassan of the Cursed Arm</t>
+  </si>
+  <si>
+    <t>hassan-of-the-cursed-arm</t>
+  </si>
+  <si>
+    <t>Hassan of the Hundred Faces</t>
+  </si>
+  <si>
+    <t>hassan-of-the-hundred-faces</t>
+  </si>
+  <si>
+    <t>Hassan of Serenity</t>
+  </si>
+  <si>
+    <t>hassan-of-serenity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">King Hassan </t>
+  </si>
+  <si>
+    <t>king-hassan</t>
+  </si>
+  <si>
+    <t>Surveil,Surveil,Surveil</t>
+  </si>
+  <si>
+    <t>First Strike</t>
+  </si>
+  <si>
+    <t>Second Strike</t>
+  </si>
+  <si>
+    <t>Third Strike</t>
+  </si>
+  <si>
+    <t>Cursed Arm</t>
+  </si>
+  <si>
+    <t>Metamorphosis</t>
+  </si>
+  <si>
+    <t>Hundred Faces</t>
+  </si>
+  <si>
+    <t>Hundred Faces (Noble Phantasm)</t>
+  </si>
+  <si>
+    <t>Poison Body</t>
+  </si>
+  <si>
+    <t>Silent Dance</t>
+  </si>
+  <si>
+    <t>Azrael (Cut From Fate)</t>
+  </si>
+  <si>
+    <t>Final Bell Toll - Heavy</t>
+  </si>
+  <si>
+    <t>Final Bell Toll - Light</t>
+  </si>
+  <si>
+    <t>S0122</t>
+  </si>
+  <si>
+    <t>S0123</t>
+  </si>
+  <si>
+    <t>S0124</t>
+  </si>
+  <si>
+    <t>S0125</t>
+  </si>
+  <si>
+    <t>S0126</t>
+  </si>
+  <si>
+    <t>S0127</t>
+  </si>
+  <si>
+    <t>S0128</t>
+  </si>
+  <si>
+    <t>S0129</t>
+  </si>
+  <si>
+    <t>S0130</t>
+  </si>
+  <si>
+    <t>S0131</t>
+  </si>
+  <si>
+    <t>S0132</t>
+  </si>
+  <si>
+    <t>S0133</t>
+  </si>
+  <si>
+    <t>S0134</t>
+  </si>
+  <si>
+    <t>S0135</t>
+  </si>
+  <si>
+    <t>S0136</t>
+  </si>
+  <si>
+    <t>S0137</t>
+  </si>
+  <si>
+    <t>S0138</t>
+  </si>
+  <si>
+    <t>S0139</t>
+  </si>
+  <si>
+    <t>S0140</t>
+  </si>
+  <si>
+    <t>S0141</t>
+  </si>
+  <si>
+    <t>S0142</t>
+  </si>
+  <si>
+    <t>S0143</t>
+  </si>
+  <si>
+    <t>S0144</t>
+  </si>
+  <si>
+    <t>S0145</t>
+  </si>
+  <si>
+    <t>S0146</t>
+  </si>
+  <si>
+    <t>Jack the Ripper</t>
+  </si>
+  <si>
+    <t>Li Shuwen</t>
+  </si>
+  <si>
+    <t>Shuten Douji</t>
+  </si>
+  <si>
+    <t>Dr. Henry Jekyll</t>
+  </si>
+  <si>
+    <t>dr-henry-jekyll</t>
+  </si>
+  <si>
+    <t>Charlotte Corday</t>
+  </si>
+  <si>
+    <t>Charles-Henri Sanson</t>
+  </si>
+  <si>
+    <t>Koyanskaya</t>
+  </si>
+  <si>
+    <t>Kama</t>
+  </si>
+  <si>
+    <t>Stheno</t>
+  </si>
+  <si>
+    <t>Fuuma Kotarou</t>
+  </si>
+  <si>
+    <t>Katou Danzou</t>
+  </si>
+  <si>
+    <t>Okada Izou</t>
+  </si>
+  <si>
+    <t>Mysterious Heroine X</t>
+  </si>
+  <si>
+    <t>Osakabehime</t>
+  </si>
+  <si>
+    <t>Carmilla</t>
+  </si>
+  <si>
+    <t>Tezcatlipoca</t>
+  </si>
+  <si>
+    <t>jack-the-ripper</t>
+  </si>
+  <si>
+    <t>li-shuwen</t>
+  </si>
+  <si>
+    <t>shuten-douji</t>
+  </si>
+  <si>
+    <t>charlotte-corday</t>
+  </si>
+  <si>
+    <t>charles-henri-sanson</t>
+  </si>
+  <si>
+    <t>koyanskaya</t>
+  </si>
+  <si>
+    <t>kama</t>
+  </si>
+  <si>
+    <t>stheno</t>
+  </si>
+  <si>
+    <t>fuuma-kotarou</t>
+  </si>
+  <si>
+    <t>katou-danzou</t>
+  </si>
+  <si>
+    <t>okada-izou</t>
+  </si>
+  <si>
+    <t>mysterious-heroine-x</t>
+  </si>
+  <si>
+    <t>osakabehime</t>
+  </si>
+  <si>
+    <t>carmilla</t>
+  </si>
+  <si>
+    <t>tezcatlipoca</t>
+  </si>
+  <si>
+    <t>Preparation,Surveil,Surveil</t>
+  </si>
+  <si>
+    <t>2,4,4,5,5</t>
+  </si>
+  <si>
+    <t>Berserker_Strength_7,Berserker_Agility_7,Berserker_Agility_9,Surveil,Preparation</t>
+  </si>
+  <si>
+    <t>2,2,3,3,5</t>
+  </si>
+  <si>
+    <t>Luck,Luck,Surveil,Surveil</t>
+  </si>
+  <si>
+    <t>Luck,Luck,Surveil,Preparation,Preparation</t>
+  </si>
+  <si>
+    <t>2,2,2,5</t>
+  </si>
+  <si>
+    <t>3,4,4,4</t>
+  </si>
+  <si>
+    <t>Surveil,Surveil,Surveil,Preparation,Preparation,Preparation</t>
+  </si>
+  <si>
+    <t>3,3,4,4,4</t>
+  </si>
+  <si>
+    <t>2,2,4,4</t>
+  </si>
+  <si>
+    <t>5,5</t>
+  </si>
+  <si>
+    <t>Berserker_Strength_7,Luck,Luck,Surveil</t>
   </si>
 </sst>
 </file>
@@ -2645,21 +3281,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E33D7ECC-1EAA-4A40-B4DA-A93E54CBC8B5}">
-  <dimension ref="A1:K102"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:K151"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="2" max="3" width="22" customWidth="1"/>
-    <col min="4" max="4" width="12.5703125" customWidth="1"/>
-    <col min="5" max="5" width="11.28515625" customWidth="1"/>
-    <col min="6" max="6" width="15.5703125" customWidth="1"/>
-    <col min="7" max="7" width="13.7109375" style="2" customWidth="1"/>
-    <col min="8" max="8" width="16.5703125" style="2" customWidth="1"/>
-    <col min="9" max="9" width="11.85546875" style="2" customWidth="1"/>
-    <col min="10" max="10" width="48.85546875" style="2" customWidth="1"/>
-    <col min="11" max="11" width="12.5703125" customWidth="1"/>
+    <col min="4" max="4" width="12.59765625" customWidth="1"/>
+    <col min="5" max="5" width="11.265625" customWidth="1"/>
+    <col min="6" max="6" width="15.59765625" customWidth="1"/>
+    <col min="7" max="7" width="13.73046875" style="2" customWidth="1"/>
+    <col min="8" max="8" width="16.59765625" style="2" customWidth="1"/>
+    <col min="9" max="9" width="17.59765625" style="2" customWidth="1"/>
+    <col min="10" max="10" width="63.53125" style="2" customWidth="1"/>
+    <col min="11" max="11" width="12.59765625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2694,7 +3330,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -2726,7 +3362,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>111</v>
       </c>
@@ -2758,7 +3394,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>112</v>
       </c>
@@ -2787,7 +3423,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>113</v>
       </c>
@@ -2816,7 +3452,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>114</v>
       </c>
@@ -2848,7 +3484,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>115</v>
       </c>
@@ -2880,7 +3516,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>116</v>
       </c>
@@ -2909,7 +3545,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>117</v>
       </c>
@@ -2938,7 +3574,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>118</v>
       </c>
@@ -2970,7 +3606,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>119</v>
       </c>
@@ -3002,7 +3638,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>120</v>
       </c>
@@ -3034,7 +3670,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>121</v>
       </c>
@@ -3063,7 +3699,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>122</v>
       </c>
@@ -3095,7 +3731,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>123</v>
       </c>
@@ -3127,7 +3763,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>124</v>
       </c>
@@ -3159,7 +3795,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>125</v>
       </c>
@@ -3191,7 +3827,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>126</v>
       </c>
@@ -3223,7 +3859,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
         <v>127</v>
       </c>
@@ -3255,7 +3891,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>128</v>
       </c>
@@ -3284,7 +3920,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
         <v>129</v>
       </c>
@@ -3316,7 +3952,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
         <v>130</v>
       </c>
@@ -3348,7 +3984,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
         <v>131</v>
       </c>
@@ -3380,7 +4016,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
         <v>132</v>
       </c>
@@ -3412,7 +4048,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
         <v>264</v>
       </c>
@@ -3444,7 +4080,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
         <v>323</v>
       </c>
@@ -3473,7 +4109,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
         <v>329</v>
       </c>
@@ -3505,7 +4141,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
         <v>330</v>
       </c>
@@ -3534,7 +4170,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
         <v>331</v>
       </c>
@@ -3566,7 +4202,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
         <v>332</v>
       </c>
@@ -3595,7 +4231,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
         <v>333</v>
       </c>
@@ -3627,7 +4263,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
         <v>334</v>
       </c>
@@ -3659,7 +4295,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
         <v>335</v>
       </c>
@@ -3691,7 +4327,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
         <v>336</v>
       </c>
@@ -3723,7 +4359,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A35" t="s">
         <v>337</v>
       </c>
@@ -3755,7 +4391,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A36" t="s">
         <v>338</v>
       </c>
@@ -3784,7 +4420,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A37" t="s">
         <v>339</v>
       </c>
@@ -3813,7 +4449,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A38" t="s">
         <v>340</v>
       </c>
@@ -3845,7 +4481,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A39" t="s">
         <v>341</v>
       </c>
@@ -3874,7 +4510,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A40" t="s">
         <v>342</v>
       </c>
@@ -3906,7 +4542,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A41" t="s">
         <v>343</v>
       </c>
@@ -3935,7 +4571,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A42" t="s">
         <v>344</v>
       </c>
@@ -3967,7 +4603,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A43" t="s">
         <v>345</v>
       </c>
@@ -3999,7 +4635,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A44" t="s">
         <v>346</v>
       </c>
@@ -4031,7 +4667,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A45" t="s">
         <v>347</v>
       </c>
@@ -4063,7 +4699,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A46" t="s">
         <v>348</v>
       </c>
@@ -4095,7 +4731,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A47" t="s">
         <v>349</v>
       </c>
@@ -4127,7 +4763,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A48" t="s">
         <v>466</v>
       </c>
@@ -4159,7 +4795,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A49" t="s">
         <v>271</v>
       </c>
@@ -4191,7 +4827,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A50" t="s">
         <v>476</v>
       </c>
@@ -4220,7 +4856,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A51" t="s">
         <v>477</v>
       </c>
@@ -4249,7 +4885,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A52" t="s">
         <v>478</v>
       </c>
@@ -4281,7 +4917,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A53" t="s">
         <v>479</v>
       </c>
@@ -4310,7 +4946,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A54" t="s">
         <v>480</v>
       </c>
@@ -4342,7 +4978,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A55" t="s">
         <v>481</v>
       </c>
@@ -4374,7 +5010,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A56" t="s">
         <v>482</v>
       </c>
@@ -4406,7 +5042,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A57" t="s">
         <v>483</v>
       </c>
@@ -4435,7 +5071,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A58" t="s">
         <v>484</v>
       </c>
@@ -4467,7 +5103,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A59" t="s">
         <v>485</v>
       </c>
@@ -4496,7 +5132,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A60" t="s">
         <v>486</v>
       </c>
@@ -4525,7 +5161,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A61" t="s">
         <v>487</v>
       </c>
@@ -4557,7 +5193,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A62" t="s">
         <v>488</v>
       </c>
@@ -4589,7 +5225,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A63" t="s">
         <v>489</v>
       </c>
@@ -4621,7 +5257,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A64" t="s">
         <v>490</v>
       </c>
@@ -4653,7 +5289,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A65" t="s">
         <v>491</v>
       </c>
@@ -4685,7 +5321,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A66" t="s">
         <v>492</v>
       </c>
@@ -4714,7 +5350,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A67" t="s">
         <v>493</v>
       </c>
@@ -4743,7 +5379,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A68" t="s">
         <v>494</v>
       </c>
@@ -4775,7 +5411,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A69" t="s">
         <v>495</v>
       </c>
@@ -4807,7 +5443,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A70" t="s">
         <v>85</v>
       </c>
@@ -4836,7 +5472,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A71" t="s">
         <v>275</v>
       </c>
@@ -4868,7 +5504,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A72" t="s">
         <v>535</v>
       </c>
@@ -4900,7 +5536,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A73" t="s">
         <v>536</v>
       </c>
@@ -4932,7 +5568,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A74" t="s">
         <v>537</v>
       </c>
@@ -4961,7 +5597,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A75" t="s">
         <v>538</v>
       </c>
@@ -4990,7 +5626,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A76" t="s">
         <v>539</v>
       </c>
@@ -5019,7 +5655,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A77" t="s">
         <v>540</v>
       </c>
@@ -5048,7 +5684,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A78" t="s">
         <v>541</v>
       </c>
@@ -5080,7 +5716,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A79" t="s">
         <v>542</v>
       </c>
@@ -5112,7 +5748,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A80" t="s">
         <v>543</v>
       </c>
@@ -5144,7 +5780,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A81" t="s">
         <v>544</v>
       </c>
@@ -5176,7 +5812,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A82" t="s">
         <v>545</v>
       </c>
@@ -5205,7 +5841,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A83" t="s">
         <v>546</v>
       </c>
@@ -5234,7 +5870,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A84" t="s">
         <v>547</v>
       </c>
@@ -5266,7 +5902,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A85" t="s">
         <v>548</v>
       </c>
@@ -5298,7 +5934,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A86" t="s">
         <v>549</v>
       </c>
@@ -5327,7 +5963,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A87" t="s">
         <v>550</v>
       </c>
@@ -5356,7 +5992,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A88" t="s">
         <v>551</v>
       </c>
@@ -5388,7 +6024,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A89" t="s">
         <v>552</v>
       </c>
@@ -5420,7 +6056,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A90" t="s">
         <v>553</v>
       </c>
@@ -5452,7 +6088,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A91" t="s">
         <v>554</v>
       </c>
@@ -5484,7 +6120,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A92" t="s">
         <v>555</v>
       </c>
@@ -5516,7 +6152,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A93" t="s">
         <v>556</v>
       </c>
@@ -5548,7 +6184,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A94" t="s">
         <v>281</v>
       </c>
@@ -5577,15 +6213,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A95" t="s">
-        <v>17</v>
+        <v>738</v>
       </c>
       <c r="B95" t="s">
-        <v>18</v>
+        <v>741</v>
       </c>
       <c r="C95" t="s">
-        <v>19</v>
+        <v>742</v>
       </c>
       <c r="D95" t="s">
         <v>20</v>
@@ -5594,24 +6230,24 @@
         <v>8</v>
       </c>
       <c r="I95" s="2" t="s">
-        <v>21</v>
+        <v>743</v>
       </c>
       <c r="J95" s="2" t="s">
-        <v>22</v>
+        <v>744</v>
       </c>
       <c r="K95" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="96" spans="1:11" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A96" t="s">
-        <v>284</v>
+        <v>739</v>
       </c>
       <c r="B96" t="s">
-        <v>285</v>
+        <v>745</v>
       </c>
       <c r="C96" t="s">
-        <v>286</v>
+        <v>746</v>
       </c>
       <c r="D96" t="s">
         <v>20</v>
@@ -5619,190 +6255,1488 @@
       <c r="E96" t="s">
         <v>8</v>
       </c>
+      <c r="G96" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H96" s="2" t="s">
+        <v>27</v>
+      </c>
       <c r="I96" s="2" t="s">
-        <v>287</v>
+        <v>318</v>
       </c>
       <c r="J96" s="2" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="K96" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="97" spans="1:11" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A97" t="s">
-        <v>96</v>
+        <v>740</v>
       </c>
       <c r="B97" t="s">
-        <v>97</v>
+        <v>747</v>
       </c>
       <c r="C97" t="s">
-        <v>98</v>
+        <v>748</v>
       </c>
       <c r="D97" t="s">
         <v>20</v>
       </c>
       <c r="E97" t="s">
-        <v>99</v>
+        <v>33</v>
       </c>
       <c r="H97" s="2" t="s">
         <v>100</v>
       </c>
       <c r="I97" s="2" t="s">
-        <v>101</v>
+        <v>749</v>
+      </c>
+      <c r="J97" s="2" t="s">
+        <v>558</v>
       </c>
       <c r="K97" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="98" spans="1:11" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A98" t="s">
-        <v>314</v>
+        <v>17</v>
       </c>
       <c r="B98" t="s">
-        <v>315</v>
+        <v>18</v>
       </c>
       <c r="C98" t="s">
-        <v>316</v>
+        <v>19</v>
       </c>
       <c r="D98" t="s">
-        <v>317</v>
+        <v>20</v>
       </c>
       <c r="E98" t="s">
-        <v>33</v>
-      </c>
-      <c r="H98" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I98" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="I98" s="2" t="s">
-        <v>318</v>
-      </c>
       <c r="J98" s="2" t="s">
-        <v>319</v>
+        <v>22</v>
       </c>
       <c r="K98" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="99" spans="1:11" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="99" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A99" t="s">
-        <v>76</v>
+        <v>757</v>
       </c>
       <c r="B99" t="s">
-        <v>77</v>
+        <v>760</v>
       </c>
       <c r="C99" t="s">
-        <v>78</v>
+        <v>761</v>
       </c>
       <c r="D99" t="s">
-        <v>79</v>
+        <v>20</v>
       </c>
       <c r="E99" t="s">
-        <v>40</v>
+        <v>762</v>
       </c>
       <c r="G99" s="2" t="s">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="H99" s="2" t="s">
-        <v>15</v>
+        <v>100</v>
       </c>
       <c r="I99" s="2" t="s">
-        <v>81</v>
+        <v>193</v>
       </c>
       <c r="J99" s="2" t="s">
-        <v>322</v>
+        <v>763</v>
       </c>
       <c r="K99" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A100" t="s">
-        <v>23</v>
+        <v>758</v>
       </c>
       <c r="B100" t="s">
-        <v>24</v>
+        <v>766</v>
       </c>
       <c r="C100" t="s">
-        <v>25</v>
+        <v>767</v>
       </c>
       <c r="D100" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="E100" t="s">
         <v>8</v>
       </c>
       <c r="G100" s="2" t="s">
-        <v>27</v>
+        <v>100</v>
       </c>
       <c r="H100" s="2" t="s">
-        <v>28</v>
+        <v>191</v>
+      </c>
+      <c r="I100" s="2" t="s">
+        <v>624</v>
       </c>
       <c r="J100" s="2" t="s">
-        <v>70</v>
+        <v>183</v>
       </c>
       <c r="K100" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A101" t="s">
-        <v>29</v>
+        <v>759</v>
       </c>
       <c r="B101" t="s">
-        <v>30</v>
+        <v>771</v>
       </c>
       <c r="C101" t="s">
-        <v>31</v>
+        <v>772</v>
       </c>
       <c r="D101" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="E101" t="s">
         <v>33</v>
       </c>
-      <c r="G101" s="2" t="s">
+      <c r="H101" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="I101" s="2" t="s">
+        <v>661</v>
+      </c>
+      <c r="J101" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="K101" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A102" t="s">
+        <v>284</v>
+      </c>
+      <c r="B102" t="s">
+        <v>285</v>
+      </c>
+      <c r="C102" t="s">
+        <v>286</v>
+      </c>
+      <c r="D102" t="s">
+        <v>20</v>
+      </c>
+      <c r="E102" t="s">
+        <v>8</v>
+      </c>
+      <c r="I102" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="J102" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="K102" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="103" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A103" t="s">
+        <v>775</v>
+      </c>
+      <c r="B103" t="s">
+        <v>781</v>
+      </c>
+      <c r="C103" t="s">
+        <v>782</v>
+      </c>
+      <c r="D103" t="s">
+        <v>79</v>
+      </c>
+      <c r="E103" t="s">
+        <v>33</v>
+      </c>
+      <c r="G103" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="I103" s="2" t="s">
+        <v>450</v>
+      </c>
+      <c r="J103" s="2" t="s">
+        <v>564</v>
+      </c>
+      <c r="K103" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A104" t="s">
+        <v>776</v>
+      </c>
+      <c r="B104" t="s">
+        <v>785</v>
+      </c>
+      <c r="C104" t="s">
+        <v>789</v>
+      </c>
+      <c r="D104" t="s">
+        <v>20</v>
+      </c>
+      <c r="E104" t="s">
+        <v>33</v>
+      </c>
+      <c r="G104" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="I104" s="2" t="s">
+        <v>567</v>
+      </c>
+      <c r="J104" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="K104" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A105" t="s">
+        <v>777</v>
+      </c>
+      <c r="B105" t="s">
+        <v>790</v>
+      </c>
+      <c r="C105" t="s">
+        <v>791</v>
+      </c>
+      <c r="D105" t="s">
+        <v>20</v>
+      </c>
+      <c r="E105" t="s">
+        <v>33</v>
+      </c>
+      <c r="G105" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="I105" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="J105" s="2" t="s">
+        <v>558</v>
+      </c>
+      <c r="K105" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A106" t="s">
+        <v>778</v>
+      </c>
+      <c r="B106" t="s">
+        <v>795</v>
+      </c>
+      <c r="C106" t="s">
+        <v>796</v>
+      </c>
+      <c r="D106" t="s">
+        <v>20</v>
+      </c>
+      <c r="E106" t="s">
+        <v>89</v>
+      </c>
+      <c r="H106" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="I106" s="2" t="s">
+        <v>797</v>
+      </c>
+      <c r="J106" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="K106" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A107" t="s">
+        <v>779</v>
+      </c>
+      <c r="B107" t="s">
+        <v>800</v>
+      </c>
+      <c r="C107" t="s">
+        <v>801</v>
+      </c>
+      <c r="D107" t="s">
+        <v>20</v>
+      </c>
+      <c r="E107" t="s">
+        <v>8</v>
+      </c>
+      <c r="G107" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="H101" s="2" t="s">
+      <c r="H107" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="I107" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="J107" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="K107" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A108" t="s">
+        <v>780</v>
+      </c>
+      <c r="B108" t="s">
+        <v>804</v>
+      </c>
+      <c r="C108" t="s">
+        <v>805</v>
+      </c>
+      <c r="D108" t="s">
+        <v>20</v>
+      </c>
+      <c r="E108" t="s">
+        <v>8</v>
+      </c>
+      <c r="G108" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="H108" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="I108" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="J108" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="K108" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A109" t="s">
+        <v>96</v>
+      </c>
+      <c r="B109" t="s">
+        <v>97</v>
+      </c>
+      <c r="C109" t="s">
+        <v>98</v>
+      </c>
+      <c r="D109" t="s">
+        <v>20</v>
+      </c>
+      <c r="E109" t="s">
+        <v>99</v>
+      </c>
+      <c r="H109" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="I109" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="K109" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="110" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A110" t="s">
+        <v>808</v>
+      </c>
+      <c r="B110" t="s">
+        <v>820</v>
+      </c>
+      <c r="C110" t="s">
+        <v>821</v>
+      </c>
+      <c r="D110" t="s">
+        <v>20</v>
+      </c>
+      <c r="E110" t="s">
+        <v>33</v>
+      </c>
+      <c r="G110" s="2" t="s">
+        <v>836</v>
+      </c>
+      <c r="H110" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="I110" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="J110" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="K110" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A111" t="s">
+        <v>809</v>
+      </c>
+      <c r="B111" t="s">
+        <v>822</v>
+      </c>
+      <c r="C111" t="s">
+        <v>823</v>
+      </c>
+      <c r="D111" t="s">
+        <v>20</v>
+      </c>
+      <c r="E111" t="s">
+        <v>89</v>
+      </c>
+      <c r="H111" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="I111" s="2" t="s">
+        <v>837</v>
+      </c>
+      <c r="J111" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="K111" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A112" t="s">
+        <v>810</v>
+      </c>
+      <c r="B112" t="s">
+        <v>824</v>
+      </c>
+      <c r="C112" t="s">
+        <v>825</v>
+      </c>
+      <c r="D112" t="s">
+        <v>20</v>
+      </c>
+      <c r="E112" t="s">
+        <v>89</v>
+      </c>
+      <c r="G112" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="H112" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="I112" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="J112" s="2" t="s">
+        <v>838</v>
+      </c>
+      <c r="K112" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A113" t="s">
+        <v>811</v>
+      </c>
+      <c r="B113" t="s">
+        <v>826</v>
+      </c>
+      <c r="C113" t="s">
+        <v>827</v>
+      </c>
+      <c r="D113" t="s">
+        <v>20</v>
+      </c>
+      <c r="E113" t="s">
+        <v>99</v>
+      </c>
+      <c r="H113" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="I113" s="2" t="s">
+        <v>839</v>
+      </c>
+      <c r="J113" s="2" t="s">
+        <v>744</v>
+      </c>
+      <c r="K113" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A114" t="s">
+        <v>812</v>
+      </c>
+      <c r="B114" t="s">
+        <v>829</v>
+      </c>
+      <c r="C114" t="s">
+        <v>831</v>
+      </c>
+      <c r="D114" t="s">
+        <v>646</v>
+      </c>
+      <c r="E114" t="s">
+        <v>33</v>
+      </c>
+      <c r="H114" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="I114" s="2" t="s">
+        <v>840</v>
+      </c>
+      <c r="J114" s="2" t="s">
+        <v>564</v>
+      </c>
+      <c r="K114" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A115" t="s">
+        <v>813</v>
+      </c>
+      <c r="B115" t="s">
+        <v>830</v>
+      </c>
+      <c r="C115" t="s">
+        <v>832</v>
+      </c>
+      <c r="D115" t="s">
+        <v>20</v>
+      </c>
+      <c r="E115" t="s">
+        <v>89</v>
+      </c>
+      <c r="G115" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="H115" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I115" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="J115" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="K115" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A116" t="s">
+        <v>814</v>
+      </c>
+      <c r="B116" t="s">
+        <v>828</v>
+      </c>
+      <c r="C116" t="s">
+        <v>833</v>
+      </c>
+      <c r="D116" t="s">
+        <v>20</v>
+      </c>
+      <c r="E116" t="s">
+        <v>33</v>
+      </c>
+      <c r="G116" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="H116" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I116" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="J116" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="K116" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A117" t="s">
+        <v>815</v>
+      </c>
+      <c r="B117" t="s">
+        <v>857</v>
+      </c>
+      <c r="C117" t="s">
+        <v>858</v>
+      </c>
+      <c r="D117" t="s">
+        <v>317</v>
+      </c>
+      <c r="E117" t="s">
+        <v>89</v>
+      </c>
+      <c r="G117" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="H117" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="J117" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="K117" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A118" t="s">
+        <v>816</v>
+      </c>
+      <c r="B118" t="s">
+        <v>859</v>
+      </c>
+      <c r="C118" t="s">
+        <v>860</v>
+      </c>
+      <c r="D118" t="s">
+        <v>317</v>
+      </c>
+      <c r="E118" t="s">
+        <v>99</v>
+      </c>
+      <c r="G118" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="H118" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="I118" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="J118" s="2" t="s">
+        <v>564</v>
+      </c>
+      <c r="K118" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A119" t="s">
+        <v>817</v>
+      </c>
+      <c r="B119" t="s">
+        <v>861</v>
+      </c>
+      <c r="C119" t="s">
+        <v>862</v>
+      </c>
+      <c r="D119" t="s">
+        <v>317</v>
+      </c>
+      <c r="E119" t="s">
+        <v>33</v>
+      </c>
+      <c r="G119" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="H119" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="I119" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="J119" s="2" t="s">
+        <v>867</v>
+      </c>
+      <c r="K119" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A120" t="s">
+        <v>818</v>
+      </c>
+      <c r="B120" t="s">
+        <v>863</v>
+      </c>
+      <c r="C120" t="s">
+        <v>864</v>
+      </c>
+      <c r="D120" t="s">
+        <v>317</v>
+      </c>
+      <c r="E120" t="s">
+        <v>8</v>
+      </c>
+      <c r="G120" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H120" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="I120" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="J120" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="K120" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A121" t="s">
+        <v>819</v>
+      </c>
+      <c r="B121" t="s">
+        <v>865</v>
+      </c>
+      <c r="C121" t="s">
+        <v>866</v>
+      </c>
+      <c r="D121" t="s">
+        <v>317</v>
+      </c>
+      <c r="E121" t="s">
+        <v>40</v>
+      </c>
+      <c r="G121" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="H121" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="I121" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="I101" s="2" t="s">
+      <c r="J121" s="2" t="s">
+        <v>838</v>
+      </c>
+      <c r="K121" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A122" t="s">
+        <v>314</v>
+      </c>
+      <c r="B122" t="s">
+        <v>315</v>
+      </c>
+      <c r="C122" t="s">
+        <v>316</v>
+      </c>
+      <c r="D122" t="s">
+        <v>317</v>
+      </c>
+      <c r="E122" t="s">
+        <v>33</v>
+      </c>
+      <c r="H122" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I122" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="J122" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="K122" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A123" t="s">
+        <v>880</v>
+      </c>
+      <c r="B123" t="s">
+        <v>467</v>
+      </c>
+      <c r="C123" t="s">
+        <v>468</v>
+      </c>
+      <c r="D123" t="s">
+        <v>317</v>
+      </c>
+      <c r="E123" t="s">
+        <v>33</v>
+      </c>
+      <c r="G123" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H123" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="I123" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="J123" s="2" t="s">
+        <v>564</v>
+      </c>
+      <c r="K123" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A124" t="s">
+        <v>881</v>
+      </c>
+      <c r="B124" t="s">
+        <v>905</v>
+      </c>
+      <c r="C124" t="s">
+        <v>922</v>
+      </c>
+      <c r="D124" t="s">
+        <v>317</v>
+      </c>
+      <c r="E124" t="s">
+        <v>89</v>
+      </c>
+      <c r="G124" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H124" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="I124" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="J124" s="2" t="s">
+        <v>937</v>
+      </c>
+      <c r="K124" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A125" t="s">
+        <v>882</v>
+      </c>
+      <c r="B125" t="s">
+        <v>906</v>
+      </c>
+      <c r="C125" t="s">
+        <v>923</v>
+      </c>
+      <c r="D125" t="s">
+        <v>317</v>
+      </c>
+      <c r="E125" t="s">
+        <v>89</v>
+      </c>
+      <c r="G125" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="H125" s="2" t="s">
+        <v>938</v>
+      </c>
+      <c r="J125" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="K125" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A126" t="s">
+        <v>883</v>
+      </c>
+      <c r="B126" t="s">
+        <v>907</v>
+      </c>
+      <c r="C126" t="s">
+        <v>924</v>
+      </c>
+      <c r="D126" t="s">
+        <v>317</v>
+      </c>
+      <c r="E126" t="s">
+        <v>40</v>
+      </c>
+      <c r="G126" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="H126" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I126" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="J126" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="K126" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A127" t="s">
+        <v>884</v>
+      </c>
+      <c r="B127" t="s">
+        <v>908</v>
+      </c>
+      <c r="C127" t="s">
+        <v>909</v>
+      </c>
+      <c r="D127" t="s">
+        <v>317</v>
+      </c>
+      <c r="E127" t="s">
+        <v>89</v>
+      </c>
+      <c r="G127" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="H127" s="2" t="s">
+        <v>454</v>
+      </c>
+      <c r="J127" s="2" t="s">
+        <v>939</v>
+      </c>
+      <c r="K127" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A128" t="s">
+        <v>885</v>
+      </c>
+      <c r="B128" t="s">
+        <v>910</v>
+      </c>
+      <c r="C128" t="s">
+        <v>925</v>
+      </c>
+      <c r="D128" t="s">
+        <v>317</v>
+      </c>
+      <c r="E128" t="s">
+        <v>8</v>
+      </c>
+      <c r="G128" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="H128" s="2" t="s">
+        <v>940</v>
+      </c>
+      <c r="J128" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="K128" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A129" t="s">
+        <v>886</v>
+      </c>
+      <c r="B129" t="s">
+        <v>911</v>
+      </c>
+      <c r="C129" t="s">
+        <v>926</v>
+      </c>
+      <c r="D129" t="s">
+        <v>317</v>
+      </c>
+      <c r="E129" t="s">
+        <v>89</v>
+      </c>
+      <c r="G129" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="H129" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="J129" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="K129" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A130" t="s">
+        <v>887</v>
+      </c>
+      <c r="B130" t="s">
+        <v>912</v>
+      </c>
+      <c r="C130" t="s">
+        <v>927</v>
+      </c>
+      <c r="D130" t="s">
+        <v>79</v>
+      </c>
+      <c r="E130" t="s">
+        <v>89</v>
+      </c>
+      <c r="G130" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="H130" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="I130" s="2" t="s">
+        <v>836</v>
+      </c>
+      <c r="J130" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="K130" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="131" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A131" t="s">
+        <v>888</v>
+      </c>
+      <c r="B131" t="s">
+        <v>913</v>
+      </c>
+      <c r="C131" t="s">
+        <v>928</v>
+      </c>
+      <c r="D131" t="s">
+        <v>317</v>
+      </c>
+      <c r="E131" t="s">
+        <v>89</v>
+      </c>
+      <c r="G131" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H131" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="I131" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="J131" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="K131" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A132" t="s">
+        <v>889</v>
+      </c>
+      <c r="B132" t="s">
+        <v>914</v>
+      </c>
+      <c r="C132" t="s">
+        <v>929</v>
+      </c>
+      <c r="D132" t="s">
+        <v>317</v>
+      </c>
+      <c r="E132" t="s">
+        <v>99</v>
+      </c>
+      <c r="G132" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="H132" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I132" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="J132" s="2" t="s">
+        <v>942</v>
+      </c>
+      <c r="K132" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A133" t="s">
+        <v>890</v>
+      </c>
+      <c r="B133" t="s">
+        <v>915</v>
+      </c>
+      <c r="C133" t="s">
+        <v>930</v>
+      </c>
+      <c r="D133" t="s">
+        <v>317</v>
+      </c>
+      <c r="E133" t="s">
+        <v>33</v>
+      </c>
+      <c r="G133" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="H133" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="I133" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="J133" s="2" t="s">
+        <v>564</v>
+      </c>
+      <c r="K133" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A134" t="s">
+        <v>891</v>
+      </c>
+      <c r="B134" t="s">
+        <v>916</v>
+      </c>
+      <c r="C134" t="s">
+        <v>931</v>
+      </c>
+      <c r="D134" t="s">
+        <v>317</v>
+      </c>
+      <c r="E134" t="s">
+        <v>8</v>
+      </c>
+      <c r="G134" s="2" t="s">
+        <v>943</v>
+      </c>
+      <c r="H134" s="2" t="s">
+        <v>568</v>
+      </c>
+      <c r="I134" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="J134" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="K134" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A135" t="s">
+        <v>892</v>
+      </c>
+      <c r="B135" t="s">
+        <v>917</v>
+      </c>
+      <c r="C135" t="s">
+        <v>932</v>
+      </c>
+      <c r="D135" t="s">
+        <v>317</v>
+      </c>
+      <c r="E135" t="s">
+        <v>99</v>
+      </c>
+      <c r="G135" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="H135" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="J135" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="K135" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A136" t="s">
+        <v>893</v>
+      </c>
+      <c r="B136" t="s">
+        <v>918</v>
+      </c>
+      <c r="C136" t="s">
+        <v>933</v>
+      </c>
+      <c r="D136" t="s">
+        <v>317</v>
+      </c>
+      <c r="E136" t="s">
+        <v>8</v>
+      </c>
+      <c r="G136" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="H136" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="I136" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="J136" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="K136" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A137" t="s">
+        <v>894</v>
+      </c>
+      <c r="B137" t="s">
+        <v>919</v>
+      </c>
+      <c r="C137" t="s">
+        <v>934</v>
+      </c>
+      <c r="D137" t="s">
+        <v>317</v>
+      </c>
+      <c r="E137" t="s">
+        <v>33</v>
+      </c>
+      <c r="H137" s="2" t="s">
+        <v>944</v>
+      </c>
+      <c r="I137" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J137" s="2" t="s">
+        <v>945</v>
+      </c>
+      <c r="K137" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A138" t="s">
+        <v>895</v>
+      </c>
+      <c r="B138" t="s">
+        <v>920</v>
+      </c>
+      <c r="C138" t="s">
+        <v>935</v>
+      </c>
+      <c r="D138" t="s">
+        <v>317</v>
+      </c>
+      <c r="E138" t="s">
+        <v>99</v>
+      </c>
+      <c r="G138" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H138" s="2" t="s">
+        <v>946</v>
+      </c>
+      <c r="I138" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="J138" s="2" t="s">
+        <v>744</v>
+      </c>
+      <c r="K138" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A139" t="s">
+        <v>896</v>
+      </c>
+      <c r="B139" t="s">
+        <v>921</v>
+      </c>
+      <c r="C139" t="s">
+        <v>936</v>
+      </c>
+      <c r="D139" t="s">
+        <v>317</v>
+      </c>
+      <c r="E139" t="s">
+        <v>89</v>
+      </c>
+      <c r="G139" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="H139" s="2" t="s">
+        <v>947</v>
+      </c>
+      <c r="I139" s="2" t="s">
+        <v>948</v>
+      </c>
+      <c r="J139" s="2" t="s">
+        <v>949</v>
+      </c>
+      <c r="K139" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A140" t="s">
+        <v>897</v>
+      </c>
+    </row>
+    <row r="141" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A141" t="s">
+        <v>898</v>
+      </c>
+    </row>
+    <row r="142" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A142" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="143" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A143" t="s">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="144" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A144" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="145" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A145" t="s">
+        <v>902</v>
+      </c>
+    </row>
+    <row r="146" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A146" t="s">
+        <v>903</v>
+      </c>
+    </row>
+    <row r="147" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A147" t="s">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="148" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A148" t="s">
+        <v>76</v>
+      </c>
+      <c r="B148" t="s">
+        <v>77</v>
+      </c>
+      <c r="C148" t="s">
+        <v>78</v>
+      </c>
+      <c r="D148" t="s">
+        <v>79</v>
+      </c>
+      <c r="E148" t="s">
+        <v>40</v>
+      </c>
+      <c r="G148" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="H148" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I148" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="J148" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="K148" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A149" t="s">
+        <v>23</v>
+      </c>
+      <c r="B149" t="s">
+        <v>24</v>
+      </c>
+      <c r="C149" t="s">
+        <v>25</v>
+      </c>
+      <c r="D149" t="s">
+        <v>26</v>
+      </c>
+      <c r="E149" t="s">
+        <v>8</v>
+      </c>
+      <c r="G149" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="H149" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J149" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="K149" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="150" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A150" t="s">
+        <v>29</v>
+      </c>
+      <c r="B150" t="s">
+        <v>30</v>
+      </c>
+      <c r="C150" t="s">
+        <v>31</v>
+      </c>
+      <c r="D150" t="s">
+        <v>32</v>
+      </c>
+      <c r="E150" t="s">
+        <v>33</v>
+      </c>
+      <c r="G150" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H150" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="I150" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="J101" s="2" t="s">
+      <c r="J150" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="K101" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A102" t="s">
+      <c r="K150" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="151" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A151" t="s">
         <v>36</v>
       </c>
-      <c r="B102" t="s">
+      <c r="B151" t="s">
         <v>37</v>
       </c>
-      <c r="C102" t="s">
+      <c r="C151" t="s">
         <v>38</v>
       </c>
-      <c r="D102" t="s">
+      <c r="D151" t="s">
         <v>39</v>
       </c>
-      <c r="E102" t="s">
+      <c r="E151" t="s">
         <v>40</v>
       </c>
-      <c r="G102" s="2" t="s">
+      <c r="G151" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="H102" s="2" t="s">
+      <c r="H151" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="J102" s="2" t="s">
+      <c r="J151" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="K102" t="b">
+      <c r="K151" t="b">
         <v>1</v>
       </c>
     </row>
@@ -5810,24 +7744,24 @@
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="H2 I6:I7 I10 I12 H14 I18 I22 I24 I27 G34 I40 I42 I45 I52 I62 I72 H79 I80 I84 I88 I90 G91" numberStoredAsText="1"/>
+    <ignoredError sqref="H2 I6:I7 I10 I12 H14 I18 I22 I24 I27 G34 I40 I42 I45 I52 I62 I72 H79 I80 I84 I88 I90 G91 H100 I119 I124 I121:I123 G130:I139" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D1BC60D8-44F3-478D-BCC0-4752624457AE}">
-  <dimension ref="A1:F21"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:F24"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="2" max="2" width="19" customWidth="1"/>
-    <col min="3" max="3" width="25.5703125" customWidth="1"/>
-    <col min="4" max="4" width="23.42578125" customWidth="1"/>
-    <col min="5" max="5" width="16.42578125" customWidth="1"/>
-    <col min="6" max="6" width="13.5703125" customWidth="1"/>
+    <col min="3" max="3" width="25.59765625" customWidth="1"/>
+    <col min="4" max="4" width="23.3984375" customWidth="1"/>
+    <col min="5" max="5" width="16.3984375" customWidth="1"/>
+    <col min="6" max="6" width="13.59765625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5847,7 +7781,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>116</v>
       </c>
@@ -5864,7 +7798,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>126</v>
       </c>
@@ -5881,7 +7815,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>130</v>
       </c>
@@ -5898,7 +7832,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>333</v>
       </c>
@@ -5915,7 +7849,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>333</v>
       </c>
@@ -5932,7 +7866,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>333</v>
       </c>
@@ -5949,7 +7883,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>85</v>
       </c>
@@ -5966,7 +7900,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>17</v>
       </c>
@@ -5983,7 +7917,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>17</v>
       </c>
@@ -6000,7 +7934,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>284</v>
       </c>
@@ -6017,7 +7951,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>284</v>
       </c>
@@ -6034,7 +7968,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>284</v>
       </c>
@@ -6051,7 +7985,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>284</v>
       </c>
@@ -6068,7 +8002,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>284</v>
       </c>
@@ -6085,7 +8019,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>284</v>
       </c>
@@ -6102,7 +8036,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>284</v>
       </c>
@@ -6119,7 +8053,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>96</v>
       </c>
@@ -6136,7 +8070,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
         <v>96</v>
       </c>
@@ -6153,7 +8087,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>96</v>
       </c>
@@ -6170,20 +8104,44 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
+        <v>887</v>
+      </c>
+      <c r="B21" t="s">
+        <v>912</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A22" t="s">
+        <v>887</v>
+      </c>
+      <c r="B22" t="s">
+        <v>912</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A23" t="s">
+        <v>887</v>
+      </c>
+      <c r="B23" t="s">
+        <v>912</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A24" t="s">
         <v>36</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B24" t="s">
         <v>37</v>
       </c>
-      <c r="C21" t="s">
+      <c r="C24" t="s">
         <v>48</v>
       </c>
-      <c r="D21" t="s">
+      <c r="D24" t="s">
         <v>48</v>
       </c>
-      <c r="E21">
+      <c r="E24">
         <v>2</v>
       </c>
     </row>
@@ -6196,17 +8154,17 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84E3BB0D-5578-4069-B1C9-C3864EB2A429}">
-  <dimension ref="A1:F304"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:F376"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="2" max="2" width="20.5703125" customWidth="1"/>
-    <col min="3" max="3" width="12.7109375" customWidth="1"/>
+    <col min="2" max="2" width="26.33203125" customWidth="1"/>
+    <col min="3" max="3" width="12.73046875" customWidth="1"/>
     <col min="4" max="4" width="17" customWidth="1"/>
-    <col min="5" max="5" width="29.5703125" customWidth="1"/>
-    <col min="6" max="6" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="29.59765625" customWidth="1"/>
+    <col min="6" max="6" width="15.73046875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -6226,7 +8184,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -6243,7 +8201,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -6260,7 +8218,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -6277,7 +8235,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>111</v>
       </c>
@@ -6294,7 +8252,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>111</v>
       </c>
@@ -6311,7 +8269,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>111</v>
       </c>
@@ -6328,7 +8286,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>112</v>
       </c>
@@ -6345,7 +8303,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>112</v>
       </c>
@@ -6362,7 +8320,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>112</v>
       </c>
@@ -6379,7 +8337,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>113</v>
       </c>
@@ -6396,7 +8354,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>113</v>
       </c>
@@ -6413,7 +8371,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>113</v>
       </c>
@@ -6430,7 +8388,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>114</v>
       </c>
@@ -6447,7 +8405,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>114</v>
       </c>
@@ -6464,7 +8422,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>114</v>
       </c>
@@ -6481,7 +8439,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>115</v>
       </c>
@@ -6498,7 +8456,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>115</v>
       </c>
@@ -6515,7 +8473,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
         <v>115</v>
       </c>
@@ -6532,7 +8490,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>116</v>
       </c>
@@ -6549,7 +8507,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
         <v>116</v>
       </c>
@@ -6566,7 +8524,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
         <v>116</v>
       </c>
@@ -6583,7 +8541,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
         <v>117</v>
       </c>
@@ -6600,7 +8558,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
         <v>117</v>
       </c>
@@ -6617,7 +8575,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
         <v>117</v>
       </c>
@@ -6634,7 +8592,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
         <v>118</v>
       </c>
@@ -6651,7 +8609,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
         <v>118</v>
       </c>
@@ -6668,7 +8626,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
         <v>118</v>
       </c>
@@ -6685,7 +8643,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
         <v>119</v>
       </c>
@@ -6702,7 +8660,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
         <v>119</v>
       </c>
@@ -6719,7 +8677,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
         <v>119</v>
       </c>
@@ -6736,7 +8694,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
         <v>120</v>
       </c>
@@ -6753,7 +8711,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
         <v>120</v>
       </c>
@@ -6770,7 +8728,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
         <v>120</v>
       </c>
@@ -6787,7 +8745,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A35" t="s">
         <v>121</v>
       </c>
@@ -6804,7 +8762,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A36" t="s">
         <v>121</v>
       </c>
@@ -6821,7 +8779,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A37" t="s">
         <v>121</v>
       </c>
@@ -6838,7 +8796,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A38" t="s">
         <v>122</v>
       </c>
@@ -6855,7 +8813,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A39" t="s">
         <v>122</v>
       </c>
@@ -6872,7 +8830,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A40" t="s">
         <v>122</v>
       </c>
@@ -6889,7 +8847,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A41" t="s">
         <v>123</v>
       </c>
@@ -6906,7 +8864,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A42" t="s">
         <v>123</v>
       </c>
@@ -6923,7 +8881,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A43" t="s">
         <v>123</v>
       </c>
@@ -6940,7 +8898,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A44" t="s">
         <v>124</v>
       </c>
@@ -6957,7 +8915,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A45" t="s">
         <v>124</v>
       </c>
@@ -6974,7 +8932,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A46" t="s">
         <v>124</v>
       </c>
@@ -6991,7 +8949,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A47" t="s">
         <v>125</v>
       </c>
@@ -7008,7 +8966,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A48" t="s">
         <v>125</v>
       </c>
@@ -7025,7 +8983,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A49" t="s">
         <v>125</v>
       </c>
@@ -7042,7 +9000,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A50" t="s">
         <v>126</v>
       </c>
@@ -7059,7 +9017,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A51" t="s">
         <v>126</v>
       </c>
@@ -7076,7 +9034,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A52" t="s">
         <v>126</v>
       </c>
@@ -7093,7 +9051,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A53" t="s">
         <v>127</v>
       </c>
@@ -7110,7 +9068,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A54" t="s">
         <v>127</v>
       </c>
@@ -7127,7 +9085,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A55" t="s">
         <v>127</v>
       </c>
@@ -7144,7 +9102,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A56" t="s">
         <v>128</v>
       </c>
@@ -7161,7 +9119,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A57" t="s">
         <v>128</v>
       </c>
@@ -7178,7 +9136,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A58" t="s">
         <v>128</v>
       </c>
@@ -7195,7 +9153,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A59" t="s">
         <v>129</v>
       </c>
@@ -7212,7 +9170,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A60" t="s">
         <v>129</v>
       </c>
@@ -7229,7 +9187,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A61" t="s">
         <v>129</v>
       </c>
@@ -7246,7 +9204,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A62" t="s">
         <v>130</v>
       </c>
@@ -7263,7 +9221,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A63" t="s">
         <v>130</v>
       </c>
@@ -7280,7 +9238,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A64" t="s">
         <v>130</v>
       </c>
@@ -7297,7 +9255,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A65" t="s">
         <v>131</v>
       </c>
@@ -7314,7 +9272,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A66" t="s">
         <v>131</v>
       </c>
@@ -7331,7 +9289,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A67" t="s">
         <v>131</v>
       </c>
@@ -7348,7 +9306,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A68" t="s">
         <v>132</v>
       </c>
@@ -7365,7 +9323,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A69" t="s">
         <v>132</v>
       </c>
@@ -7382,7 +9340,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A70" t="s">
         <v>132</v>
       </c>
@@ -7399,7 +9357,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A71" t="s">
         <v>264</v>
       </c>
@@ -7416,7 +9374,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A72" t="s">
         <v>264</v>
       </c>
@@ -7433,7 +9391,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A73" t="s">
         <v>264</v>
       </c>
@@ -7450,7 +9408,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A74" t="s">
         <v>323</v>
       </c>
@@ -7467,7 +9425,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A75" t="s">
         <v>323</v>
       </c>
@@ -7484,7 +9442,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A76" t="s">
         <v>323</v>
       </c>
@@ -7501,7 +9459,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A77" t="s">
         <v>329</v>
       </c>
@@ -7518,7 +9476,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A78" t="s">
         <v>329</v>
       </c>
@@ -7535,7 +9493,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A79" t="s">
         <v>329</v>
       </c>
@@ -7552,7 +9510,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A80" t="s">
         <v>330</v>
       </c>
@@ -7569,7 +9527,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A81" t="s">
         <v>330</v>
       </c>
@@ -7586,7 +9544,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A82" t="s">
         <v>330</v>
       </c>
@@ -7603,7 +9561,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A83" t="s">
         <v>331</v>
       </c>
@@ -7620,7 +9578,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A84" t="s">
         <v>331</v>
       </c>
@@ -7637,7 +9595,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A85" t="s">
         <v>331</v>
       </c>
@@ -7654,7 +9612,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A86" t="s">
         <v>332</v>
       </c>
@@ -7671,7 +9629,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A87" t="s">
         <v>332</v>
       </c>
@@ -7688,7 +9646,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A88" t="s">
         <v>332</v>
       </c>
@@ -7705,7 +9663,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A89" t="s">
         <v>333</v>
       </c>
@@ -7722,7 +9680,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A90" t="s">
         <v>333</v>
       </c>
@@ -7739,7 +9697,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A91" t="s">
         <v>333</v>
       </c>
@@ -7756,7 +9714,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A92" t="s">
         <v>334</v>
       </c>
@@ -7773,7 +9731,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A93" t="s">
         <v>334</v>
       </c>
@@ -7790,7 +9748,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A94" t="s">
         <v>334</v>
       </c>
@@ -7807,7 +9765,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A95" t="s">
         <v>335</v>
       </c>
@@ -7824,7 +9782,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A96" t="s">
         <v>335</v>
       </c>
@@ -7841,7 +9799,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A97" t="s">
         <v>335</v>
       </c>
@@ -7858,7 +9816,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A98" t="s">
         <v>336</v>
       </c>
@@ -7875,7 +9833,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A99" t="s">
         <v>336</v>
       </c>
@@ -7892,7 +9850,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A100" t="s">
         <v>336</v>
       </c>
@@ -7909,7 +9867,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A101" t="s">
         <v>337</v>
       </c>
@@ -7926,7 +9884,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A102" t="s">
         <v>337</v>
       </c>
@@ -7943,7 +9901,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A103" t="s">
         <v>337</v>
       </c>
@@ -7960,7 +9918,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A104" t="s">
         <v>338</v>
       </c>
@@ -7977,7 +9935,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A105" t="s">
         <v>338</v>
       </c>
@@ -7994,7 +9952,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A106" t="s">
         <v>338</v>
       </c>
@@ -8011,7 +9969,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A107" t="s">
         <v>339</v>
       </c>
@@ -8028,7 +9986,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A108" t="s">
         <v>339</v>
       </c>
@@ -8045,7 +10003,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A109" t="s">
         <v>339</v>
       </c>
@@ -8062,7 +10020,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A110" t="s">
         <v>340</v>
       </c>
@@ -8079,7 +10037,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A111" t="s">
         <v>340</v>
       </c>
@@ -8096,7 +10054,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A112" t="s">
         <v>340</v>
       </c>
@@ -8113,7 +10071,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A113" t="s">
         <v>341</v>
       </c>
@@ -8130,7 +10088,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A114" t="s">
         <v>341</v>
       </c>
@@ -8147,7 +10105,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A115" t="s">
         <v>341</v>
       </c>
@@ -8164,7 +10122,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A116" t="s">
         <v>342</v>
       </c>
@@ -8181,7 +10139,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A117" t="s">
         <v>342</v>
       </c>
@@ -8198,7 +10156,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A118" t="s">
         <v>342</v>
       </c>
@@ -8215,7 +10173,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A119" t="s">
         <v>343</v>
       </c>
@@ -8232,7 +10190,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A120" t="s">
         <v>343</v>
       </c>
@@ -8249,7 +10207,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A121" t="s">
         <v>343</v>
       </c>
@@ -8266,7 +10224,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A122" t="s">
         <v>344</v>
       </c>
@@ -8283,7 +10241,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="123" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A123" t="s">
         <v>344</v>
       </c>
@@ -8300,7 +10258,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A124" t="s">
         <v>344</v>
       </c>
@@ -8317,7 +10275,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="125" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A125" t="s">
         <v>345</v>
       </c>
@@ -8334,7 +10292,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="126" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A126" t="s">
         <v>345</v>
       </c>
@@ -8351,7 +10309,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A127" t="s">
         <v>345</v>
       </c>
@@ -8368,7 +10326,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="128" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A128" t="s">
         <v>346</v>
       </c>
@@ -8385,7 +10343,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="129" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A129" t="s">
         <v>346</v>
       </c>
@@ -8402,7 +10360,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="130" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A130" t="s">
         <v>346</v>
       </c>
@@ -8419,7 +10377,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="131" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A131" t="s">
         <v>347</v>
       </c>
@@ -8436,7 +10394,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="132" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A132" t="s">
         <v>347</v>
       </c>
@@ -8453,7 +10411,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="133" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A133" t="s">
         <v>347</v>
       </c>
@@ -8470,7 +10428,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="134" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A134" t="s">
         <v>348</v>
       </c>
@@ -8487,7 +10445,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="135" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A135" t="s">
         <v>348</v>
       </c>
@@ -8504,7 +10462,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="136" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A136" t="s">
         <v>348</v>
       </c>
@@ -8521,7 +10479,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="137" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A137" t="s">
         <v>349</v>
       </c>
@@ -8538,7 +10496,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="138" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A138" t="s">
         <v>349</v>
       </c>
@@ -8555,7 +10513,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="139" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A139" t="s">
         <v>349</v>
       </c>
@@ -8572,7 +10530,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="140" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A140" t="s">
         <v>466</v>
       </c>
@@ -8589,7 +10547,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="141" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A141" t="s">
         <v>466</v>
       </c>
@@ -8606,7 +10564,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="142" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A142" t="s">
         <v>466</v>
       </c>
@@ -8623,7 +10581,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="143" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A143" t="s">
         <v>271</v>
       </c>
@@ -8640,7 +10598,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="144" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A144" t="s">
         <v>271</v>
       </c>
@@ -8657,7 +10615,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="145" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A145" t="s">
         <v>271</v>
       </c>
@@ -8674,7 +10632,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="146" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A146" t="s">
         <v>476</v>
       </c>
@@ -8691,7 +10649,7 @@
         <v>571</v>
       </c>
     </row>
-    <row r="147" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A147" t="s">
         <v>476</v>
       </c>
@@ -8708,7 +10666,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="148" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A148" t="s">
         <v>476</v>
       </c>
@@ -8725,7 +10683,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="149" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A149" t="s">
         <v>477</v>
       </c>
@@ -8742,7 +10700,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="150" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A150" t="s">
         <v>477</v>
       </c>
@@ -8759,7 +10717,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="151" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A151" t="s">
         <v>477</v>
       </c>
@@ -8776,7 +10734,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="152" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A152" t="s">
         <v>478</v>
       </c>
@@ -8793,7 +10751,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="153" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A153" t="s">
         <v>478</v>
       </c>
@@ -8810,7 +10768,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="154" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A154" t="s">
         <v>478</v>
       </c>
@@ -8827,7 +10785,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="155" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A155" t="s">
         <v>479</v>
       </c>
@@ -8844,7 +10802,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="156" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A156" t="s">
         <v>479</v>
       </c>
@@ -8861,7 +10819,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="157" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A157" t="s">
         <v>479</v>
       </c>
@@ -8878,7 +10836,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="158" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A158" t="s">
         <v>480</v>
       </c>
@@ -8895,7 +10853,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="159" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A159" t="s">
         <v>480</v>
       </c>
@@ -8912,7 +10870,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="160" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A160" t="s">
         <v>480</v>
       </c>
@@ -8929,7 +10887,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="161" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A161" t="s">
         <v>481</v>
       </c>
@@ -8946,7 +10904,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="162" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A162" t="s">
         <v>481</v>
       </c>
@@ -8963,7 +10921,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="163" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A163" t="s">
         <v>481</v>
       </c>
@@ -8980,7 +10938,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="164" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A164" t="s">
         <v>482</v>
       </c>
@@ -8997,7 +10955,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="165" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A165" t="s">
         <v>482</v>
       </c>
@@ -9014,7 +10972,7 @@
         <v>585</v>
       </c>
     </row>
-    <row r="166" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A166" t="s">
         <v>482</v>
       </c>
@@ -9031,7 +10989,7 @@
         <v>586</v>
       </c>
     </row>
-    <row r="167" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A167" t="s">
         <v>483</v>
       </c>
@@ -9048,7 +11006,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="168" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A168" t="s">
         <v>483</v>
       </c>
@@ -9065,7 +11023,7 @@
         <v>588</v>
       </c>
     </row>
-    <row r="169" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A169" t="s">
         <v>483</v>
       </c>
@@ -9082,7 +11040,7 @@
         <v>589</v>
       </c>
     </row>
-    <row r="170" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A170" t="s">
         <v>484</v>
       </c>
@@ -9099,7 +11057,7 @@
         <v>590</v>
       </c>
     </row>
-    <row r="171" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A171" t="s">
         <v>484</v>
       </c>
@@ -9116,7 +11074,7 @@
         <v>591</v>
       </c>
     </row>
-    <row r="172" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A172" t="s">
         <v>484</v>
       </c>
@@ -9133,7 +11091,7 @@
         <v>592</v>
       </c>
     </row>
-    <row r="173" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A173" t="s">
         <v>485</v>
       </c>
@@ -9150,7 +11108,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="174" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A174" t="s">
         <v>485</v>
       </c>
@@ -9167,7 +11125,7 @@
         <v>594</v>
       </c>
     </row>
-    <row r="175" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A175" t="s">
         <v>485</v>
       </c>
@@ -9184,7 +11142,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="176" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A176" t="s">
         <v>486</v>
       </c>
@@ -9201,7 +11159,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="177" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A177" t="s">
         <v>486</v>
       </c>
@@ -9218,7 +11176,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="178" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A178" t="s">
         <v>486</v>
       </c>
@@ -9235,7 +11193,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="179" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A179" t="s">
         <v>487</v>
       </c>
@@ -9252,7 +11210,7 @@
         <v>598</v>
       </c>
     </row>
-    <row r="180" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A180" t="s">
         <v>487</v>
       </c>
@@ -9269,7 +11227,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="181" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A181" t="s">
         <v>487</v>
       </c>
@@ -9286,7 +11244,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="182" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A182" t="s">
         <v>488</v>
       </c>
@@ -9303,7 +11261,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="183" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A183" t="s">
         <v>488</v>
       </c>
@@ -9320,7 +11278,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="184" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A184" t="s">
         <v>488</v>
       </c>
@@ -9337,7 +11295,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="185" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A185" t="s">
         <v>489</v>
       </c>
@@ -9354,7 +11312,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="186" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A186" t="s">
         <v>489</v>
       </c>
@@ -9371,7 +11329,7 @@
         <v>605</v>
       </c>
     </row>
-    <row r="187" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A187" t="s">
         <v>489</v>
       </c>
@@ -9388,7 +11346,7 @@
         <v>606</v>
       </c>
     </row>
-    <row r="188" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A188" t="s">
         <v>490</v>
       </c>
@@ -9405,7 +11363,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="189" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A189" t="s">
         <v>490</v>
       </c>
@@ -9422,7 +11380,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="190" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A190" t="s">
         <v>490</v>
       </c>
@@ -9439,7 +11397,7 @@
         <v>608</v>
       </c>
     </row>
-    <row r="191" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A191" t="s">
         <v>491</v>
       </c>
@@ -9456,7 +11414,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="192" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A192" t="s">
         <v>491</v>
       </c>
@@ -9473,7 +11431,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="193" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A193" t="s">
         <v>491</v>
       </c>
@@ -9490,7 +11448,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="194" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A194" t="s">
         <v>492</v>
       </c>
@@ -9507,7 +11465,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="195" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A195" t="s">
         <v>492</v>
       </c>
@@ -9524,7 +11482,7 @@
         <v>611</v>
       </c>
     </row>
-    <row r="196" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A196" t="s">
         <v>492</v>
       </c>
@@ -9541,7 +11499,7 @@
         <v>612</v>
       </c>
     </row>
-    <row r="197" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A197" t="s">
         <v>493</v>
       </c>
@@ -9558,7 +11516,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="198" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A198" t="s">
         <v>493</v>
       </c>
@@ -9575,7 +11533,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="199" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A199" t="s">
         <v>493</v>
       </c>
@@ -9592,7 +11550,7 @@
         <v>615</v>
       </c>
     </row>
-    <row r="200" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A200" t="s">
         <v>494</v>
       </c>
@@ -9609,7 +11567,7 @@
         <v>616</v>
       </c>
     </row>
-    <row r="201" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A201" t="s">
         <v>494</v>
       </c>
@@ -9626,7 +11584,7 @@
         <v>617</v>
       </c>
     </row>
-    <row r="202" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A202" t="s">
         <v>494</v>
       </c>
@@ -9643,7 +11601,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="203" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A203" t="s">
         <v>495</v>
       </c>
@@ -9660,7 +11618,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="204" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A204" t="s">
         <v>495</v>
       </c>
@@ -9677,7 +11635,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="205" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A205" t="s">
         <v>495</v>
       </c>
@@ -9694,7 +11652,7 @@
         <v>621</v>
       </c>
     </row>
-    <row r="206" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A206" t="s">
         <v>85</v>
       </c>
@@ -9711,7 +11669,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="207" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A207" t="s">
         <v>85</v>
       </c>
@@ -9728,7 +11686,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="208" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A208" t="s">
         <v>85</v>
       </c>
@@ -9745,7 +11703,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="209" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A209" t="s">
         <v>275</v>
       </c>
@@ -9762,7 +11720,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="210" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A210" t="s">
         <v>275</v>
       </c>
@@ -9779,7 +11737,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="211" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A211" t="s">
         <v>275</v>
       </c>
@@ -9796,7 +11754,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="212" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A212" t="s">
         <v>535</v>
       </c>
@@ -9813,7 +11771,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="213" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A213" t="s">
         <v>535</v>
       </c>
@@ -9830,7 +11788,7 @@
         <v>666</v>
       </c>
     </row>
-    <row r="214" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A214" t="s">
         <v>535</v>
       </c>
@@ -9847,7 +11805,7 @@
         <v>667</v>
       </c>
     </row>
-    <row r="215" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A215" t="s">
         <v>536</v>
       </c>
@@ -9864,7 +11822,7 @@
         <v>668</v>
       </c>
     </row>
-    <row r="216" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A216" t="s">
         <v>536</v>
       </c>
@@ -9881,7 +11839,7 @@
         <v>669</v>
       </c>
     </row>
-    <row r="217" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A217" t="s">
         <v>536</v>
       </c>
@@ -9898,7 +11856,7 @@
         <v>670</v>
       </c>
     </row>
-    <row r="218" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A218" t="s">
         <v>537</v>
       </c>
@@ -9915,7 +11873,7 @@
         <v>671</v>
       </c>
     </row>
-    <row r="219" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A219" t="s">
         <v>537</v>
       </c>
@@ -9932,7 +11890,7 @@
         <v>672</v>
       </c>
     </row>
-    <row r="220" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A220" t="s">
         <v>537</v>
       </c>
@@ -9949,7 +11907,7 @@
         <v>673</v>
       </c>
     </row>
-    <row r="221" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A221" t="s">
         <v>538</v>
       </c>
@@ -9966,7 +11924,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="222" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A222" t="s">
         <v>538</v>
       </c>
@@ -9983,7 +11941,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="223" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A223" t="s">
         <v>538</v>
       </c>
@@ -10000,7 +11958,7 @@
         <v>675</v>
       </c>
     </row>
-    <row r="224" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A224" t="s">
         <v>539</v>
       </c>
@@ -10017,7 +11975,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="225" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A225" t="s">
         <v>539</v>
       </c>
@@ -10034,7 +11992,7 @@
         <v>676</v>
       </c>
     </row>
-    <row r="226" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A226" t="s">
         <v>539</v>
       </c>
@@ -10051,7 +12009,7 @@
         <v>677</v>
       </c>
     </row>
-    <row r="227" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A227" t="s">
         <v>540</v>
       </c>
@@ -10068,7 +12026,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="228" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A228" t="s">
         <v>540</v>
       </c>
@@ -10085,7 +12043,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="229" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A229" t="s">
         <v>540</v>
       </c>
@@ -10102,7 +12060,7 @@
         <v>679</v>
       </c>
     </row>
-    <row r="230" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A230" t="s">
         <v>541</v>
       </c>
@@ -10119,7 +12077,7 @@
         <v>680</v>
       </c>
     </row>
-    <row r="231" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A231" t="s">
         <v>541</v>
       </c>
@@ -10136,7 +12094,7 @@
         <v>681</v>
       </c>
     </row>
-    <row r="232" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A232" t="s">
         <v>541</v>
       </c>
@@ -10153,7 +12111,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="233" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A233" t="s">
         <v>542</v>
       </c>
@@ -10170,7 +12128,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="234" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A234" t="s">
         <v>542</v>
       </c>
@@ -10187,7 +12145,7 @@
         <v>683</v>
       </c>
     </row>
-    <row r="235" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A235" t="s">
         <v>542</v>
       </c>
@@ -10204,7 +12162,7 @@
         <v>684</v>
       </c>
     </row>
-    <row r="236" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A236" t="s">
         <v>543</v>
       </c>
@@ -10221,7 +12179,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="237" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A237" t="s">
         <v>543</v>
       </c>
@@ -10238,7 +12196,7 @@
         <v>685</v>
       </c>
     </row>
-    <row r="238" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A238" t="s">
         <v>543</v>
       </c>
@@ -10255,7 +12213,7 @@
         <v>686</v>
       </c>
     </row>
-    <row r="239" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A239" t="s">
         <v>544</v>
       </c>
@@ -10272,7 +12230,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="240" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A240" t="s">
         <v>544</v>
       </c>
@@ -10289,7 +12247,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="241" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A241" t="s">
         <v>544</v>
       </c>
@@ -10306,7 +12264,7 @@
         <v>688</v>
       </c>
     </row>
-    <row r="242" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A242" t="s">
         <v>545</v>
       </c>
@@ -10323,7 +12281,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="243" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A243" t="s">
         <v>545</v>
       </c>
@@ -10340,7 +12298,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="244" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A244" t="s">
         <v>545</v>
       </c>
@@ -10357,7 +12315,7 @@
         <v>690</v>
       </c>
     </row>
-    <row r="245" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A245" t="s">
         <v>546</v>
       </c>
@@ -10374,7 +12332,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="246" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A246" t="s">
         <v>546</v>
       </c>
@@ -10391,7 +12349,7 @@
         <v>691</v>
       </c>
     </row>
-    <row r="247" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A247" t="s">
         <v>546</v>
       </c>
@@ -10408,7 +12366,7 @@
         <v>692</v>
       </c>
     </row>
-    <row r="248" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A248" t="s">
         <v>547</v>
       </c>
@@ -10425,7 +12383,7 @@
         <v>693</v>
       </c>
     </row>
-    <row r="249" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A249" t="s">
         <v>547</v>
       </c>
@@ -10442,7 +12400,7 @@
         <v>694</v>
       </c>
     </row>
-    <row r="250" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A250" t="s">
         <v>547</v>
       </c>
@@ -10459,7 +12417,7 @@
         <v>695</v>
       </c>
     </row>
-    <row r="251" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A251" t="s">
         <v>548</v>
       </c>
@@ -10476,7 +12434,7 @@
         <v>696</v>
       </c>
     </row>
-    <row r="252" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A252" t="s">
         <v>548</v>
       </c>
@@ -10493,7 +12451,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="253" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A253" t="s">
         <v>548</v>
       </c>
@@ -10510,7 +12468,7 @@
         <v>697</v>
       </c>
     </row>
-    <row r="254" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A254" t="s">
         <v>549</v>
       </c>
@@ -10527,7 +12485,7 @@
         <v>698</v>
       </c>
     </row>
-    <row r="255" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A255" t="s">
         <v>549</v>
       </c>
@@ -10544,7 +12502,7 @@
         <v>699</v>
       </c>
     </row>
-    <row r="256" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A256" t="s">
         <v>549</v>
       </c>
@@ -10561,7 +12519,7 @@
         <v>700</v>
       </c>
     </row>
-    <row r="257" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A257" t="s">
         <v>550</v>
       </c>
@@ -10578,7 +12536,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="258" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A258" t="s">
         <v>550</v>
       </c>
@@ -10595,7 +12553,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="259" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A259" t="s">
         <v>550</v>
       </c>
@@ -10612,7 +12570,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="260" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A260" t="s">
         <v>551</v>
       </c>
@@ -10629,7 +12587,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="261" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A261" t="s">
         <v>551</v>
       </c>
@@ -10646,7 +12604,7 @@
         <v>703</v>
       </c>
     </row>
-    <row r="262" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A262" t="s">
         <v>551</v>
       </c>
@@ -10663,7 +12621,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="263" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A263" t="s">
         <v>552</v>
       </c>
@@ -10680,7 +12638,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="264" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A264" t="s">
         <v>552</v>
       </c>
@@ -10697,7 +12655,7 @@
         <v>705</v>
       </c>
     </row>
-    <row r="265" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A265" t="s">
         <v>552</v>
       </c>
@@ -10714,7 +12672,7 @@
         <v>706</v>
       </c>
     </row>
-    <row r="266" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A266" t="s">
         <v>553</v>
       </c>
@@ -10731,7 +12689,7 @@
         <v>707</v>
       </c>
     </row>
-    <row r="267" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A267" t="s">
         <v>553</v>
       </c>
@@ -10748,7 +12706,7 @@
         <v>708</v>
       </c>
     </row>
-    <row r="268" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A268" t="s">
         <v>553</v>
       </c>
@@ -10765,7 +12723,7 @@
         <v>709</v>
       </c>
     </row>
-    <row r="269" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A269" t="s">
         <v>554</v>
       </c>
@@ -10782,7 +12740,7 @@
         <v>710</v>
       </c>
     </row>
-    <row r="270" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A270" t="s">
         <v>554</v>
       </c>
@@ -10799,7 +12757,7 @@
         <v>711</v>
       </c>
     </row>
-    <row r="271" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A271" t="s">
         <v>554</v>
       </c>
@@ -10816,7 +12774,7 @@
         <v>712</v>
       </c>
     </row>
-    <row r="272" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A272" t="s">
         <v>555</v>
       </c>
@@ -10833,7 +12791,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="273" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A273" t="s">
         <v>555</v>
       </c>
@@ -10850,7 +12808,7 @@
         <v>713</v>
       </c>
     </row>
-    <row r="274" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A274" t="s">
         <v>555</v>
       </c>
@@ -10867,7 +12825,7 @@
         <v>714</v>
       </c>
     </row>
-    <row r="275" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A275" t="s">
         <v>556</v>
       </c>
@@ -10884,7 +12842,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="276" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A276" t="s">
         <v>556</v>
       </c>
@@ -10901,7 +12859,7 @@
         <v>715</v>
       </c>
     </row>
-    <row r="277" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A277" t="s">
         <v>556</v>
       </c>
@@ -10918,7 +12876,7 @@
         <v>716</v>
       </c>
     </row>
-    <row r="278" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A278" t="s">
         <v>281</v>
       </c>
@@ -10935,7 +12893,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="279" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A279" t="s">
         <v>281</v>
       </c>
@@ -10952,7 +12910,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="280" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A280" t="s">
         <v>281</v>
       </c>
@@ -10969,12 +12927,12 @@
         <v>310</v>
       </c>
     </row>
-    <row r="281" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A281" t="s">
-        <v>17</v>
+        <v>738</v>
       </c>
       <c r="B281" t="s">
-        <v>18</v>
+        <v>741</v>
       </c>
       <c r="C281">
         <v>1</v>
@@ -10986,12 +12944,12 @@
         <v>58</v>
       </c>
     </row>
-    <row r="282" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A282" t="s">
-        <v>17</v>
+        <v>738</v>
       </c>
       <c r="B282" t="s">
-        <v>18</v>
+        <v>741</v>
       </c>
       <c r="C282">
         <v>2</v>
@@ -11000,15 +12958,15 @@
         <v>0</v>
       </c>
       <c r="E282" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="283" spans="1:5" x14ac:dyDescent="0.25">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="283" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A283" t="s">
-        <v>17</v>
+        <v>738</v>
       </c>
       <c r="B283" t="s">
-        <v>18</v>
+        <v>741</v>
       </c>
       <c r="C283">
         <v>3</v>
@@ -11017,15 +12975,15 @@
         <v>0</v>
       </c>
       <c r="E283" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="284" spans="1:5" x14ac:dyDescent="0.25">
+        <v>751</v>
+      </c>
+    </row>
+    <row r="284" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A284" t="s">
-        <v>284</v>
+        <v>739</v>
       </c>
       <c r="B284" t="s">
-        <v>285</v>
+        <v>745</v>
       </c>
       <c r="C284">
         <v>1</v>
@@ -11034,15 +12992,15 @@
         <v>0</v>
       </c>
       <c r="E284" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="285" spans="1:5" x14ac:dyDescent="0.25">
+        <v>752</v>
+      </c>
+    </row>
+    <row r="285" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A285" t="s">
-        <v>284</v>
+        <v>739</v>
       </c>
       <c r="B285" t="s">
-        <v>285</v>
+        <v>745</v>
       </c>
       <c r="C285">
         <v>2</v>
@@ -11051,15 +13009,15 @@
         <v>0</v>
       </c>
       <c r="E285" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="286" spans="1:5" x14ac:dyDescent="0.25">
+        <v>753</v>
+      </c>
+    </row>
+    <row r="286" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A286" t="s">
-        <v>284</v>
+        <v>739</v>
       </c>
       <c r="B286" t="s">
-        <v>285</v>
+        <v>745</v>
       </c>
       <c r="C286">
         <v>3</v>
@@ -11068,32 +13026,32 @@
         <v>0</v>
       </c>
       <c r="E286" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="287" spans="1:5" x14ac:dyDescent="0.25">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="287" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A287" t="s">
-        <v>96</v>
+        <v>740</v>
       </c>
       <c r="B287" t="s">
-        <v>97</v>
+        <v>747</v>
       </c>
       <c r="C287">
         <v>1</v>
       </c>
       <c r="D287" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E287" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="288" spans="1:5" x14ac:dyDescent="0.25">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="288" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A288" t="s">
-        <v>96</v>
+        <v>740</v>
       </c>
       <c r="B288" t="s">
-        <v>97</v>
+        <v>747</v>
       </c>
       <c r="C288">
         <v>2</v>
@@ -11102,15 +13060,15 @@
         <v>0</v>
       </c>
       <c r="E288" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="289" spans="1:5" x14ac:dyDescent="0.25">
+        <v>755</v>
+      </c>
+    </row>
+    <row r="289" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A289" t="s">
-        <v>96</v>
+        <v>740</v>
       </c>
       <c r="B289" t="s">
-        <v>97</v>
+        <v>747</v>
       </c>
       <c r="C289">
         <v>3</v>
@@ -11119,15 +13077,15 @@
         <v>0</v>
       </c>
       <c r="E289" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="290" spans="1:5" x14ac:dyDescent="0.25">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="290" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A290" t="s">
-        <v>314</v>
+        <v>17</v>
       </c>
       <c r="B290" t="s">
-        <v>315</v>
+        <v>18</v>
       </c>
       <c r="C290">
         <v>1</v>
@@ -11136,32 +13094,32 @@
         <v>1</v>
       </c>
       <c r="E290" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="291" spans="1:5" x14ac:dyDescent="0.25">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="291" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A291" t="s">
-        <v>314</v>
+        <v>17</v>
       </c>
       <c r="B291" t="s">
-        <v>315</v>
+        <v>18</v>
       </c>
       <c r="C291">
         <v>2</v>
       </c>
       <c r="D291" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E291" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="292" spans="1:5" x14ac:dyDescent="0.25">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="292" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A292" t="s">
-        <v>314</v>
+        <v>17</v>
       </c>
       <c r="B292" t="s">
-        <v>315</v>
+        <v>18</v>
       </c>
       <c r="C292">
         <v>3</v>
@@ -11170,15 +13128,15 @@
         <v>0</v>
       </c>
       <c r="E292" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="293" spans="1:5" x14ac:dyDescent="0.25">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="293" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A293" t="s">
-        <v>76</v>
+        <v>757</v>
       </c>
       <c r="B293" t="s">
-        <v>77</v>
+        <v>760</v>
       </c>
       <c r="C293">
         <v>1</v>
@@ -11187,15 +13145,15 @@
         <v>1</v>
       </c>
       <c r="E293" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="294" spans="1:5" x14ac:dyDescent="0.25">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="294" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A294" t="s">
-        <v>76</v>
+        <v>757</v>
       </c>
       <c r="B294" t="s">
-        <v>77</v>
+        <v>760</v>
       </c>
       <c r="C294">
         <v>2</v>
@@ -11204,15 +13162,15 @@
         <v>0</v>
       </c>
       <c r="E294" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="295" spans="1:5" x14ac:dyDescent="0.25">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="295" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A295" t="s">
-        <v>76</v>
+        <v>757</v>
       </c>
       <c r="B295" t="s">
-        <v>77</v>
+        <v>760</v>
       </c>
       <c r="C295">
         <v>3</v>
@@ -11221,15 +13179,15 @@
         <v>0</v>
       </c>
       <c r="E295" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="296" spans="1:5" x14ac:dyDescent="0.25">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="296" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A296" t="s">
-        <v>23</v>
+        <v>758</v>
       </c>
       <c r="B296" t="s">
-        <v>24</v>
+        <v>766</v>
       </c>
       <c r="C296">
         <v>1</v>
@@ -11238,15 +13196,15 @@
         <v>0</v>
       </c>
       <c r="E296" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="297" spans="1:5" x14ac:dyDescent="0.25">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="297" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A297" t="s">
-        <v>23</v>
+        <v>758</v>
       </c>
       <c r="B297" t="s">
-        <v>24</v>
+        <v>766</v>
       </c>
       <c r="C297">
         <v>2</v>
@@ -11255,15 +13213,15 @@
         <v>0</v>
       </c>
       <c r="E297" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="298" spans="1:5" x14ac:dyDescent="0.25">
+        <v>769</v>
+      </c>
+    </row>
+    <row r="298" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A298" t="s">
-        <v>23</v>
+        <v>758</v>
       </c>
       <c r="B298" t="s">
-        <v>24</v>
+        <v>766</v>
       </c>
       <c r="C298">
         <v>3</v>
@@ -11272,32 +13230,32 @@
         <v>0</v>
       </c>
       <c r="E298" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="299" spans="1:5" x14ac:dyDescent="0.25">
+        <v>770</v>
+      </c>
+    </row>
+    <row r="299" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A299" t="s">
-        <v>29</v>
+        <v>759</v>
       </c>
       <c r="B299" t="s">
-        <v>30</v>
+        <v>771</v>
       </c>
       <c r="C299">
         <v>1</v>
       </c>
       <c r="D299" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E299" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="300" spans="1:5" x14ac:dyDescent="0.25">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="300" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A300" t="s">
-        <v>29</v>
+        <v>759</v>
       </c>
       <c r="B300" t="s">
-        <v>30</v>
+        <v>771</v>
       </c>
       <c r="C300">
         <v>2</v>
@@ -11306,15 +13264,15 @@
         <v>0</v>
       </c>
       <c r="E300" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="301" spans="1:5" x14ac:dyDescent="0.25">
+        <v>773</v>
+      </c>
+    </row>
+    <row r="301" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A301" t="s">
-        <v>29</v>
+        <v>759</v>
       </c>
       <c r="B301" t="s">
-        <v>30</v>
+        <v>771</v>
       </c>
       <c r="C301">
         <v>3</v>
@@ -11323,15 +13281,15 @@
         <v>0</v>
       </c>
       <c r="E301" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="302" spans="1:5" x14ac:dyDescent="0.25">
+        <v>774</v>
+      </c>
+    </row>
+    <row r="302" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A302" t="s">
-        <v>36</v>
+        <v>284</v>
       </c>
       <c r="B302" t="s">
-        <v>37</v>
+        <v>285</v>
       </c>
       <c r="C302">
         <v>1</v>
@@ -11340,15 +13298,15 @@
         <v>0</v>
       </c>
       <c r="E302" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="303" spans="1:5" x14ac:dyDescent="0.25">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="303" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A303" t="s">
-        <v>36</v>
+        <v>284</v>
       </c>
       <c r="B303" t="s">
-        <v>37</v>
+        <v>285</v>
       </c>
       <c r="C303">
         <v>2</v>
@@ -11357,15 +13315,15 @@
         <v>0</v>
       </c>
       <c r="E303" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="304" spans="1:5" x14ac:dyDescent="0.25">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="304" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A304" t="s">
-        <v>36</v>
+        <v>284</v>
       </c>
       <c r="B304" t="s">
-        <v>37</v>
+        <v>285</v>
       </c>
       <c r="C304">
         <v>3</v>
@@ -11374,6 +13332,1230 @@
         <v>0</v>
       </c>
       <c r="E304" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="305" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A305" t="s">
+        <v>775</v>
+      </c>
+      <c r="B305" t="s">
+        <v>781</v>
+      </c>
+      <c r="C305">
+        <v>1</v>
+      </c>
+      <c r="D305" t="b">
+        <v>1</v>
+      </c>
+      <c r="E305" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="306" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A306" t="s">
+        <v>775</v>
+      </c>
+      <c r="B306" t="s">
+        <v>781</v>
+      </c>
+      <c r="C306">
+        <v>2</v>
+      </c>
+      <c r="D306" t="b">
+        <v>0</v>
+      </c>
+      <c r="E306" t="s">
+        <v>783</v>
+      </c>
+    </row>
+    <row r="307" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A307" t="s">
+        <v>775</v>
+      </c>
+      <c r="B307" t="s">
+        <v>781</v>
+      </c>
+      <c r="C307">
+        <v>3</v>
+      </c>
+      <c r="D307" t="b">
+        <v>0</v>
+      </c>
+      <c r="E307" t="s">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="308" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A308" t="s">
+        <v>776</v>
+      </c>
+      <c r="B308" t="s">
+        <v>785</v>
+      </c>
+      <c r="C308">
+        <v>1</v>
+      </c>
+      <c r="D308" t="b">
+        <v>0</v>
+      </c>
+      <c r="E308" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="309" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A309" t="s">
+        <v>776</v>
+      </c>
+      <c r="B309" t="s">
+        <v>785</v>
+      </c>
+      <c r="C309">
+        <v>2</v>
+      </c>
+      <c r="D309" t="b">
+        <v>0</v>
+      </c>
+      <c r="E309" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="310" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A310" t="s">
+        <v>776</v>
+      </c>
+      <c r="B310" t="s">
+        <v>785</v>
+      </c>
+      <c r="C310">
+        <v>3</v>
+      </c>
+      <c r="D310" t="b">
+        <v>0</v>
+      </c>
+      <c r="E310" t="s">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="311" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A311" t="s">
+        <v>777</v>
+      </c>
+      <c r="B311" t="s">
+        <v>790</v>
+      </c>
+      <c r="C311">
+        <v>1</v>
+      </c>
+      <c r="D311" t="b">
+        <v>0</v>
+      </c>
+      <c r="E311" t="s">
+        <v>792</v>
+      </c>
+    </row>
+    <row r="312" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A312" t="s">
+        <v>777</v>
+      </c>
+      <c r="B312" t="s">
+        <v>790</v>
+      </c>
+      <c r="C312">
+        <v>2</v>
+      </c>
+      <c r="D312" t="b">
+        <v>0</v>
+      </c>
+      <c r="E312" t="s">
+        <v>793</v>
+      </c>
+    </row>
+    <row r="313" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A313" t="s">
+        <v>777</v>
+      </c>
+      <c r="B313" t="s">
+        <v>790</v>
+      </c>
+      <c r="C313">
+        <v>3</v>
+      </c>
+      <c r="D313" t="b">
+        <v>0</v>
+      </c>
+      <c r="E313" t="s">
+        <v>794</v>
+      </c>
+    </row>
+    <row r="314" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A314" t="s">
+        <v>778</v>
+      </c>
+      <c r="B314" t="s">
+        <v>795</v>
+      </c>
+      <c r="C314">
+        <v>1</v>
+      </c>
+      <c r="D314" t="b">
+        <v>1</v>
+      </c>
+      <c r="E314" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="315" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A315" t="s">
+        <v>778</v>
+      </c>
+      <c r="B315" t="s">
+        <v>795</v>
+      </c>
+      <c r="C315">
+        <v>2</v>
+      </c>
+      <c r="D315" t="b">
+        <v>0</v>
+      </c>
+      <c r="E315" t="s">
+        <v>798</v>
+      </c>
+    </row>
+    <row r="316" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A316" t="s">
+        <v>778</v>
+      </c>
+      <c r="B316" t="s">
+        <v>795</v>
+      </c>
+      <c r="C316">
+        <v>3</v>
+      </c>
+      <c r="D316" t="b">
+        <v>0</v>
+      </c>
+      <c r="E316" t="s">
+        <v>799</v>
+      </c>
+    </row>
+    <row r="317" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A317" t="s">
+        <v>779</v>
+      </c>
+      <c r="B317" t="s">
+        <v>800</v>
+      </c>
+      <c r="C317">
+        <v>1</v>
+      </c>
+      <c r="D317" t="b">
+        <v>1</v>
+      </c>
+      <c r="E317" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="318" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A318" t="s">
+        <v>779</v>
+      </c>
+      <c r="B318" t="s">
+        <v>800</v>
+      </c>
+      <c r="C318">
+        <v>2</v>
+      </c>
+      <c r="D318" t="b">
+        <v>0</v>
+      </c>
+      <c r="E318" t="s">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="319" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A319" t="s">
+        <v>779</v>
+      </c>
+      <c r="B319" t="s">
+        <v>800</v>
+      </c>
+      <c r="C319">
+        <v>3</v>
+      </c>
+      <c r="D319" t="b">
+        <v>0</v>
+      </c>
+      <c r="E319" t="s">
+        <v>803</v>
+      </c>
+    </row>
+    <row r="320" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A320" t="s">
+        <v>780</v>
+      </c>
+      <c r="B320" t="s">
+        <v>804</v>
+      </c>
+      <c r="C320">
+        <v>1</v>
+      </c>
+      <c r="D320" t="b">
+        <v>1</v>
+      </c>
+      <c r="E320" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="321" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A321" t="s">
+        <v>780</v>
+      </c>
+      <c r="B321" t="s">
+        <v>804</v>
+      </c>
+      <c r="C321">
+        <v>2</v>
+      </c>
+      <c r="D321" t="b">
+        <v>0</v>
+      </c>
+      <c r="E321" t="s">
+        <v>806</v>
+      </c>
+    </row>
+    <row r="322" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A322" t="s">
+        <v>780</v>
+      </c>
+      <c r="B322" t="s">
+        <v>804</v>
+      </c>
+      <c r="C322">
+        <v>3</v>
+      </c>
+      <c r="D322" t="b">
+        <v>0</v>
+      </c>
+      <c r="E322" t="s">
+        <v>807</v>
+      </c>
+    </row>
+    <row r="323" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A323" t="s">
+        <v>96</v>
+      </c>
+      <c r="B323" t="s">
+        <v>97</v>
+      </c>
+      <c r="C323">
+        <v>1</v>
+      </c>
+      <c r="D323" t="b">
+        <v>0</v>
+      </c>
+      <c r="E323" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="324" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A324" t="s">
+        <v>96</v>
+      </c>
+      <c r="B324" t="s">
+        <v>97</v>
+      </c>
+      <c r="C324">
+        <v>2</v>
+      </c>
+      <c r="D324" t="b">
+        <v>0</v>
+      </c>
+      <c r="E324" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="325" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A325" t="s">
+        <v>96</v>
+      </c>
+      <c r="B325" t="s">
+        <v>97</v>
+      </c>
+      <c r="C325">
+        <v>3</v>
+      </c>
+      <c r="D325" t="b">
+        <v>0</v>
+      </c>
+      <c r="E325" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="326" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A326" t="s">
+        <v>808</v>
+      </c>
+      <c r="B326" t="s">
+        <v>820</v>
+      </c>
+      <c r="C326">
+        <v>1</v>
+      </c>
+      <c r="D326" t="b">
+        <v>1</v>
+      </c>
+      <c r="E326" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="327" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A327" t="s">
+        <v>808</v>
+      </c>
+      <c r="B327" t="s">
+        <v>820</v>
+      </c>
+      <c r="C327">
+        <v>2</v>
+      </c>
+      <c r="D327" t="b">
+        <v>0</v>
+      </c>
+      <c r="E327" t="s">
+        <v>834</v>
+      </c>
+    </row>
+    <row r="328" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A328" t="s">
+        <v>808</v>
+      </c>
+      <c r="B328" t="s">
+        <v>820</v>
+      </c>
+      <c r="C328">
+        <v>3</v>
+      </c>
+      <c r="D328" t="b">
+        <v>0</v>
+      </c>
+      <c r="E328" t="s">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="329" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A329" t="s">
+        <v>809</v>
+      </c>
+      <c r="B329" t="s">
+        <v>822</v>
+      </c>
+      <c r="C329">
+        <v>1</v>
+      </c>
+      <c r="D329" t="b">
+        <v>0</v>
+      </c>
+      <c r="E329" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="330" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A330" t="s">
+        <v>809</v>
+      </c>
+      <c r="B330" t="s">
+        <v>822</v>
+      </c>
+      <c r="C330">
+        <v>2</v>
+      </c>
+      <c r="D330" t="b">
+        <v>0</v>
+      </c>
+      <c r="E330" t="s">
+        <v>842</v>
+      </c>
+    </row>
+    <row r="331" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A331" t="s">
+        <v>809</v>
+      </c>
+      <c r="B331" t="s">
+        <v>822</v>
+      </c>
+      <c r="C331">
+        <v>3</v>
+      </c>
+      <c r="D331" t="b">
+        <v>0</v>
+      </c>
+      <c r="E331" t="s">
+        <v>843</v>
+      </c>
+    </row>
+    <row r="332" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A332" t="s">
+        <v>810</v>
+      </c>
+      <c r="B332" t="s">
+        <v>824</v>
+      </c>
+      <c r="C332">
+        <v>1</v>
+      </c>
+      <c r="D332" t="b">
+        <v>0</v>
+      </c>
+      <c r="E332" t="s">
+        <v>844</v>
+      </c>
+    </row>
+    <row r="333" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A333" t="s">
+        <v>810</v>
+      </c>
+      <c r="B333" t="s">
+        <v>824</v>
+      </c>
+      <c r="C333">
+        <v>2</v>
+      </c>
+      <c r="D333" t="b">
+        <v>0</v>
+      </c>
+      <c r="E333" t="s">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="334" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A334" t="s">
+        <v>810</v>
+      </c>
+      <c r="B334" t="s">
+        <v>824</v>
+      </c>
+      <c r="C334">
+        <v>3</v>
+      </c>
+      <c r="D334" t="b">
+        <v>0</v>
+      </c>
+      <c r="E334" t="s">
+        <v>846</v>
+      </c>
+    </row>
+    <row r="335" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A335" t="s">
+        <v>811</v>
+      </c>
+      <c r="B335" t="s">
+        <v>826</v>
+      </c>
+      <c r="C335">
+        <v>1</v>
+      </c>
+      <c r="D335" t="b">
+        <v>0</v>
+      </c>
+      <c r="E335" t="s">
+        <v>847</v>
+      </c>
+    </row>
+    <row r="336" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A336" t="s">
+        <v>811</v>
+      </c>
+      <c r="B336" t="s">
+        <v>826</v>
+      </c>
+      <c r="C336">
+        <v>2</v>
+      </c>
+      <c r="D336" t="b">
+        <v>0</v>
+      </c>
+      <c r="E336" t="s">
+        <v>848</v>
+      </c>
+    </row>
+    <row r="337" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A337" t="s">
+        <v>811</v>
+      </c>
+      <c r="B337" t="s">
+        <v>826</v>
+      </c>
+      <c r="C337">
+        <v>3</v>
+      </c>
+      <c r="D337" t="b">
+        <v>0</v>
+      </c>
+      <c r="E337" t="s">
+        <v>849</v>
+      </c>
+    </row>
+    <row r="338" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A338" t="s">
+        <v>812</v>
+      </c>
+      <c r="B338" t="s">
+        <v>829</v>
+      </c>
+      <c r="C338">
+        <v>1</v>
+      </c>
+      <c r="D338" t="b">
+        <v>1</v>
+      </c>
+      <c r="E338" t="s">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="339" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A339" t="s">
+        <v>812</v>
+      </c>
+      <c r="B339" t="s">
+        <v>829</v>
+      </c>
+      <c r="C339">
+        <v>2</v>
+      </c>
+      <c r="D339" t="b">
+        <v>1</v>
+      </c>
+      <c r="E339" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="340" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A340" t="s">
+        <v>812</v>
+      </c>
+      <c r="B340" t="s">
+        <v>829</v>
+      </c>
+      <c r="C340">
+        <v>3</v>
+      </c>
+      <c r="D340" t="b">
+        <v>0</v>
+      </c>
+      <c r="E340" t="s">
+        <v>850</v>
+      </c>
+    </row>
+    <row r="341" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A341" t="s">
+        <v>813</v>
+      </c>
+      <c r="B341" t="s">
+        <v>830</v>
+      </c>
+      <c r="C341">
+        <v>1</v>
+      </c>
+      <c r="D341" t="b">
+        <v>0</v>
+      </c>
+      <c r="E341" t="s">
+        <v>851</v>
+      </c>
+    </row>
+    <row r="342" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A342" t="s">
+        <v>813</v>
+      </c>
+      <c r="B342" t="s">
+        <v>830</v>
+      </c>
+      <c r="C342">
+        <v>2</v>
+      </c>
+      <c r="D342" t="b">
+        <v>0</v>
+      </c>
+      <c r="E342" t="s">
+        <v>852</v>
+      </c>
+    </row>
+    <row r="343" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A343" t="s">
+        <v>813</v>
+      </c>
+      <c r="B343" t="s">
+        <v>830</v>
+      </c>
+      <c r="C343">
+        <v>3</v>
+      </c>
+      <c r="D343" t="b">
+        <v>0</v>
+      </c>
+      <c r="E343" t="s">
+        <v>853</v>
+      </c>
+    </row>
+    <row r="344" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A344" t="s">
+        <v>814</v>
+      </c>
+      <c r="B344" t="s">
+        <v>828</v>
+      </c>
+      <c r="C344">
+        <v>1</v>
+      </c>
+      <c r="D344" t="b">
+        <v>0</v>
+      </c>
+      <c r="E344" t="s">
+        <v>854</v>
+      </c>
+    </row>
+    <row r="345" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A345" t="s">
+        <v>814</v>
+      </c>
+      <c r="B345" t="s">
+        <v>828</v>
+      </c>
+      <c r="C345">
+        <v>2</v>
+      </c>
+      <c r="D345" t="b">
+        <v>0</v>
+      </c>
+      <c r="E345" t="s">
+        <v>855</v>
+      </c>
+    </row>
+    <row r="346" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A346" t="s">
+        <v>814</v>
+      </c>
+      <c r="B346" t="s">
+        <v>828</v>
+      </c>
+      <c r="C346">
+        <v>3</v>
+      </c>
+      <c r="D346" t="b">
+        <v>0</v>
+      </c>
+      <c r="E346" t="s">
+        <v>856</v>
+      </c>
+    </row>
+    <row r="347" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A347" t="s">
+        <v>815</v>
+      </c>
+      <c r="B347" t="s">
+        <v>857</v>
+      </c>
+      <c r="C347">
+        <v>1</v>
+      </c>
+      <c r="D347" t="b">
+        <v>0</v>
+      </c>
+      <c r="E347" t="s">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="348" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A348" t="s">
+        <v>815</v>
+      </c>
+      <c r="B348" t="s">
+        <v>857</v>
+      </c>
+      <c r="C348">
+        <v>2</v>
+      </c>
+      <c r="D348" t="b">
+        <v>0</v>
+      </c>
+      <c r="E348" t="s">
+        <v>869</v>
+      </c>
+    </row>
+    <row r="349" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A349" t="s">
+        <v>815</v>
+      </c>
+      <c r="B349" t="s">
+        <v>857</v>
+      </c>
+      <c r="C349">
+        <v>3</v>
+      </c>
+      <c r="D349" t="b">
+        <v>0</v>
+      </c>
+      <c r="E349" t="s">
+        <v>870</v>
+      </c>
+    </row>
+    <row r="350" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A350" t="s">
+        <v>816</v>
+      </c>
+      <c r="B350" t="s">
+        <v>859</v>
+      </c>
+      <c r="C350">
+        <v>1</v>
+      </c>
+      <c r="D350" t="b">
+        <v>1</v>
+      </c>
+      <c r="E350" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="351" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A351" t="s">
+        <v>816</v>
+      </c>
+      <c r="B351" t="s">
+        <v>859</v>
+      </c>
+      <c r="C351">
+        <v>2</v>
+      </c>
+      <c r="D351" t="b">
+        <v>0</v>
+      </c>
+      <c r="E351" t="s">
+        <v>871</v>
+      </c>
+    </row>
+    <row r="352" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A352" t="s">
+        <v>816</v>
+      </c>
+      <c r="B352" t="s">
+        <v>859</v>
+      </c>
+      <c r="C352">
+        <v>3</v>
+      </c>
+      <c r="D352" t="b">
+        <v>0</v>
+      </c>
+      <c r="E352" t="s">
+        <v>872</v>
+      </c>
+    </row>
+    <row r="353" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A353" t="s">
+        <v>817</v>
+      </c>
+      <c r="B353" t="s">
+        <v>861</v>
+      </c>
+      <c r="C353">
+        <v>1</v>
+      </c>
+      <c r="D353" t="b">
+        <v>1</v>
+      </c>
+      <c r="E353" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="354" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A354" t="s">
+        <v>817</v>
+      </c>
+      <c r="B354" t="s">
+        <v>861</v>
+      </c>
+      <c r="C354">
+        <v>2</v>
+      </c>
+      <c r="D354" t="b">
+        <v>0</v>
+      </c>
+      <c r="E354" t="s">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="355" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A355" t="s">
+        <v>817</v>
+      </c>
+      <c r="B355" t="s">
+        <v>861</v>
+      </c>
+      <c r="C355">
+        <v>3</v>
+      </c>
+      <c r="D355" t="b">
+        <v>0</v>
+      </c>
+      <c r="E355" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="356" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A356" t="s">
+        <v>818</v>
+      </c>
+      <c r="B356" t="s">
+        <v>863</v>
+      </c>
+      <c r="C356">
+        <v>1</v>
+      </c>
+      <c r="D356" t="b">
+        <v>1</v>
+      </c>
+      <c r="E356" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="357" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A357" t="s">
+        <v>818</v>
+      </c>
+      <c r="B357" t="s">
+        <v>863</v>
+      </c>
+      <c r="C357">
+        <v>2</v>
+      </c>
+      <c r="D357" t="b">
+        <v>0</v>
+      </c>
+      <c r="E357" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="358" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A358" t="s">
+        <v>818</v>
+      </c>
+      <c r="B358" t="s">
+        <v>863</v>
+      </c>
+      <c r="C358">
+        <v>3</v>
+      </c>
+      <c r="D358" t="b">
+        <v>0</v>
+      </c>
+      <c r="E358" t="s">
+        <v>876</v>
+      </c>
+    </row>
+    <row r="359" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A359" t="s">
+        <v>819</v>
+      </c>
+      <c r="B359" t="s">
+        <v>865</v>
+      </c>
+      <c r="C359">
+        <v>1</v>
+      </c>
+      <c r="D359" t="b">
+        <v>0</v>
+      </c>
+      <c r="E359" t="s">
+        <v>877</v>
+      </c>
+    </row>
+    <row r="360" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A360" t="s">
+        <v>819</v>
+      </c>
+      <c r="B360" t="s">
+        <v>865</v>
+      </c>
+      <c r="C360">
+        <v>2</v>
+      </c>
+      <c r="D360" t="b">
+        <v>0</v>
+      </c>
+      <c r="E360" t="s">
+        <v>878</v>
+      </c>
+    </row>
+    <row r="361" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A361" t="s">
+        <v>819</v>
+      </c>
+      <c r="B361" t="s">
+        <v>865</v>
+      </c>
+      <c r="C361">
+        <v>3</v>
+      </c>
+      <c r="D361" t="b">
+        <v>0</v>
+      </c>
+      <c r="E361" t="s">
+        <v>879</v>
+      </c>
+    </row>
+    <row r="362" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A362" t="s">
+        <v>314</v>
+      </c>
+      <c r="B362" t="s">
+        <v>315</v>
+      </c>
+      <c r="C362">
+        <v>1</v>
+      </c>
+      <c r="D362" t="b">
+        <v>1</v>
+      </c>
+      <c r="E362" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="363" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A363" t="s">
+        <v>314</v>
+      </c>
+      <c r="B363" t="s">
+        <v>315</v>
+      </c>
+      <c r="C363">
+        <v>2</v>
+      </c>
+      <c r="D363" t="b">
+        <v>1</v>
+      </c>
+      <c r="E363" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="364" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A364" t="s">
+        <v>314</v>
+      </c>
+      <c r="B364" t="s">
+        <v>315</v>
+      </c>
+      <c r="C364">
+        <v>3</v>
+      </c>
+      <c r="D364" t="b">
+        <v>0</v>
+      </c>
+      <c r="E364" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="365" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A365" t="s">
+        <v>76</v>
+      </c>
+      <c r="B365" t="s">
+        <v>77</v>
+      </c>
+      <c r="C365">
+        <v>1</v>
+      </c>
+      <c r="D365" t="b">
+        <v>1</v>
+      </c>
+      <c r="E365" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="366" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A366" t="s">
+        <v>76</v>
+      </c>
+      <c r="B366" t="s">
+        <v>77</v>
+      </c>
+      <c r="C366">
+        <v>2</v>
+      </c>
+      <c r="D366" t="b">
+        <v>0</v>
+      </c>
+      <c r="E366" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="367" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A367" t="s">
+        <v>76</v>
+      </c>
+      <c r="B367" t="s">
+        <v>77</v>
+      </c>
+      <c r="C367">
+        <v>3</v>
+      </c>
+      <c r="D367" t="b">
+        <v>0</v>
+      </c>
+      <c r="E367" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="368" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A368" t="s">
+        <v>23</v>
+      </c>
+      <c r="B368" t="s">
+        <v>24</v>
+      </c>
+      <c r="C368">
+        <v>1</v>
+      </c>
+      <c r="D368" t="b">
+        <v>0</v>
+      </c>
+      <c r="E368" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="369" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A369" t="s">
+        <v>23</v>
+      </c>
+      <c r="B369" t="s">
+        <v>24</v>
+      </c>
+      <c r="C369">
+        <v>2</v>
+      </c>
+      <c r="D369" t="b">
+        <v>0</v>
+      </c>
+      <c r="E369" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="370" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A370" t="s">
+        <v>23</v>
+      </c>
+      <c r="B370" t="s">
+        <v>24</v>
+      </c>
+      <c r="C370">
+        <v>3</v>
+      </c>
+      <c r="D370" t="b">
+        <v>0</v>
+      </c>
+      <c r="E370" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="371" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A371" t="s">
+        <v>29</v>
+      </c>
+      <c r="B371" t="s">
+        <v>30</v>
+      </c>
+      <c r="C371">
+        <v>1</v>
+      </c>
+      <c r="D371" t="b">
+        <v>0</v>
+      </c>
+      <c r="E371" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="372" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A372" t="s">
+        <v>29</v>
+      </c>
+      <c r="B372" t="s">
+        <v>30</v>
+      </c>
+      <c r="C372">
+        <v>2</v>
+      </c>
+      <c r="D372" t="b">
+        <v>0</v>
+      </c>
+      <c r="E372" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="373" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A373" t="s">
+        <v>29</v>
+      </c>
+      <c r="B373" t="s">
+        <v>30</v>
+      </c>
+      <c r="C373">
+        <v>3</v>
+      </c>
+      <c r="D373" t="b">
+        <v>0</v>
+      </c>
+      <c r="E373" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="374" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A374" t="s">
+        <v>36</v>
+      </c>
+      <c r="B374" t="s">
+        <v>37</v>
+      </c>
+      <c r="C374">
+        <v>1</v>
+      </c>
+      <c r="D374" t="b">
+        <v>0</v>
+      </c>
+      <c r="E374" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="375" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A375" t="s">
+        <v>36</v>
+      </c>
+      <c r="B375" t="s">
+        <v>37</v>
+      </c>
+      <c r="C375">
+        <v>2</v>
+      </c>
+      <c r="D375" t="b">
+        <v>0</v>
+      </c>
+      <c r="E375" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="376" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A376" t="s">
+        <v>36</v>
+      </c>
+      <c r="B376" t="s">
+        <v>37</v>
+      </c>
+      <c r="C376">
+        <v>3</v>
+      </c>
+      <c r="D376" t="b">
+        <v>0</v>
+      </c>
+      <c r="E376" t="s">
         <v>69</v>
       </c>
     </row>
@@ -11386,7 +14568,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32F3CD10-C054-4484-ABE2-D426F834FC22}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -11395,7 +14577,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{931309AC-3B5D-4169-8BD3-83BC320E154C}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/Fate-Spreadsheet.xlsx
+++ b/data/Fate-Spreadsheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pixel\Documents\Projects\Fate-Wiki\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4E4DA1A-8EF8-4ECB-96CB-33B68CAC1907}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC4AA550-D884-4558-B74C-930BA076FA13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{B05E798F-9EF6-4508-A0A4-311D06661AED}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2478" uniqueCount="950">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2812" uniqueCount="1060">
   <si>
     <t>servant_id</t>
   </si>
@@ -2893,6 +2893,336 @@
   </si>
   <si>
     <t>Berserker_Strength_7,Luck,Luck,Surveil</t>
+  </si>
+  <si>
+    <t>Chronos Rose</t>
+  </si>
+  <si>
+    <t>Phantasm Punishment</t>
+  </si>
+  <si>
+    <t>Maria the Ripper</t>
+  </si>
+  <si>
+    <t>The Mist</t>
+  </si>
+  <si>
+    <t>Dissociation</t>
+  </si>
+  <si>
+    <t>No Second Strike</t>
+  </si>
+  <si>
+    <t>Sphere Boundary</t>
+  </si>
+  <si>
+    <t>Bone Collector</t>
+  </si>
+  <si>
+    <t>Noxious Sake</t>
+  </si>
+  <si>
+    <t>Debaucherous Banquet</t>
+  </si>
+  <si>
+    <t>Dangerous Game (Noble Phantasm)</t>
+  </si>
+  <si>
+    <t>Dangerous Game (Passive)</t>
+  </si>
+  <si>
+    <t>Le Rêve Ensoleillé</t>
+  </si>
+  <si>
+    <t>Haphazard Planning</t>
+  </si>
+  <si>
+    <t>La Mort d'Espoir (Noble Phantasm)</t>
+  </si>
+  <si>
+    <t>La Mort d'Espoir (Passive)</t>
+  </si>
+  <si>
+    <t>Kingslayer</t>
+  </si>
+  <si>
+    <t>Gospel of Slaughter</t>
+  </si>
+  <si>
+    <t>NFF Special Delivery</t>
+  </si>
+  <si>
+    <t>NF00</t>
+  </si>
+  <si>
+    <t>NF14</t>
+  </si>
+  <si>
+    <t>NF56</t>
+  </si>
+  <si>
+    <t>NF-00 Cyanide Cake</t>
+  </si>
+  <si>
+    <t>NF-56 Mini Miko</t>
+  </si>
+  <si>
+    <t>NF-14 Mobile Turret</t>
+  </si>
+  <si>
+    <t>Ananga</t>
+  </si>
+  <si>
+    <t>Samsara Kama</t>
+  </si>
+  <si>
+    <t>Smile of the Stheno</t>
+  </si>
+  <si>
+    <t>Divine Excellence</t>
+  </si>
+  <si>
+    <t>Chaos Brigade</t>
+  </si>
+  <si>
+    <t>Shinobi Sabotage</t>
+  </si>
+  <si>
+    <t>Mechanical Illusion</t>
+  </si>
+  <si>
+    <t>Synthetic Limbs</t>
+  </si>
+  <si>
+    <t>Shimatsuken</t>
+  </si>
+  <si>
+    <t>Man Slayer</t>
+  </si>
+  <si>
+    <t>Secret - Calibur</t>
+  </si>
+  <si>
+    <t>Assassin In Denial</t>
+  </si>
+  <si>
+    <t>Hakuro Castle</t>
+  </si>
+  <si>
+    <t>Chiyogami Bats</t>
+  </si>
+  <si>
+    <t>Castle Apparition</t>
+  </si>
+  <si>
+    <t>Phantom Maiden</t>
+  </si>
+  <si>
+    <t>Immoral Suggestion</t>
+  </si>
+  <si>
+    <t>Fresh Blood</t>
+  </si>
+  <si>
+    <t>Tepeyollotl</t>
+  </si>
+  <si>
+    <t>Guise of the Warrior</t>
+  </si>
+  <si>
+    <t>First Sun Xibalba</t>
+  </si>
+  <si>
+    <t>S0148</t>
+  </si>
+  <si>
+    <t>S0149</t>
+  </si>
+  <si>
+    <t>S0150</t>
+  </si>
+  <si>
+    <t>S0151</t>
+  </si>
+  <si>
+    <t>S0152</t>
+  </si>
+  <si>
+    <t>S0153</t>
+  </si>
+  <si>
+    <t>S0154</t>
+  </si>
+  <si>
+    <t>S0155</t>
+  </si>
+  <si>
+    <t>S0156</t>
+  </si>
+  <si>
+    <t>S0157</t>
+  </si>
+  <si>
+    <t>S0158</t>
+  </si>
+  <si>
+    <t>S0159</t>
+  </si>
+  <si>
+    <t>S0160</t>
+  </si>
+  <si>
+    <t>S0161</t>
+  </si>
+  <si>
+    <t>S0162</t>
+  </si>
+  <si>
+    <t>S0163</t>
+  </si>
+  <si>
+    <t>S0164</t>
+  </si>
+  <si>
+    <t>S0165</t>
+  </si>
+  <si>
+    <t>S0166</t>
+  </si>
+  <si>
+    <t>heracles</t>
+  </si>
+  <si>
+    <t>Berserker</t>
+  </si>
+  <si>
+    <t>Asterios</t>
+  </si>
+  <si>
+    <t>asterios</t>
+  </si>
+  <si>
+    <t>Lancelot of the Lake</t>
+  </si>
+  <si>
+    <t>lancelot-of-the-lake</t>
+  </si>
+  <si>
+    <t>Arcueid Brunestud</t>
+  </si>
+  <si>
+    <t>arcueid-brunestud</t>
+  </si>
+  <si>
+    <t>Frakenstein's Monster</t>
+  </si>
+  <si>
+    <t>frankensteins-monster</t>
+  </si>
+  <si>
+    <t>Spartacus</t>
+  </si>
+  <si>
+    <t>spartacus</t>
+  </si>
+  <si>
+    <t>Kiyohime</t>
+  </si>
+  <si>
+    <t>kiyohime</t>
+  </si>
+  <si>
+    <t>Penthesilea</t>
+  </si>
+  <si>
+    <t>penthesilea</t>
+  </si>
+  <si>
+    <t>Sakata Kintoki</t>
+  </si>
+  <si>
+    <t>sakata-kintoki</t>
+  </si>
+  <si>
+    <t>Minamoto no Raikou</t>
+  </si>
+  <si>
+    <t>minamoto-no-raikou</t>
+  </si>
+  <si>
+    <t>Darius III</t>
+  </si>
+  <si>
+    <t>darius-iii</t>
+  </si>
+  <si>
+    <t>Lu Bu Fengxian</t>
+  </si>
+  <si>
+    <t>lu-bu-fengxian</t>
+  </si>
+  <si>
+    <t>Xiang Yu</t>
+  </si>
+  <si>
+    <t>xiang-yu</t>
+  </si>
+  <si>
+    <t>God Arjuna</t>
+  </si>
+  <si>
+    <t>god-arjuna</t>
+  </si>
+  <si>
+    <t>Florence Nightingale</t>
+  </si>
+  <si>
+    <t>cu-chulainn-alter</t>
+  </si>
+  <si>
+    <t>florence-nightingale</t>
+  </si>
+  <si>
+    <t>Cu Chulainn</t>
+  </si>
+  <si>
+    <t>Kingprotea</t>
+  </si>
+  <si>
+    <t>kingprotea</t>
+  </si>
+  <si>
+    <t>Kijyo Koyo</t>
+  </si>
+  <si>
+    <t>kijyo-koyo</t>
+  </si>
+  <si>
+    <t>Kriemhild</t>
+  </si>
+  <si>
+    <t>kriemhild</t>
+  </si>
+  <si>
+    <t>Hijikata Toshizou</t>
+  </si>
+  <si>
+    <t>hijikata-toshizou</t>
+  </si>
+  <si>
+    <t>Ibaraki Douji</t>
+  </si>
+  <si>
+    <t>ibaraki-douji</t>
+  </si>
+  <si>
+    <t>Caligula</t>
+  </si>
+  <si>
+    <t>caligula</t>
+  </si>
+  <si>
+    <t>Berserker_Strength_7,Berserker_Strength_9,Berserker_Agility_7,Luck,Luck</t>
   </si>
 </sst>
 </file>
@@ -3281,7 +3611,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E33D7ECC-1EAA-4A40-B4DA-A93E54CBC8B5}">
-  <dimension ref="A1:K151"/>
+  <dimension ref="A1:K170"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="2" max="3" width="22" customWidth="1"/>
@@ -7582,41 +7912,149 @@
       <c r="A140" t="s">
         <v>897</v>
       </c>
+      <c r="B140" t="s">
+        <v>247</v>
+      </c>
+      <c r="C140" t="s">
+        <v>1015</v>
+      </c>
+      <c r="D140" t="s">
+        <v>1016</v>
+      </c>
+      <c r="E140" t="s">
+        <v>40</v>
+      </c>
+      <c r="G140" s="2" t="s">
+        <v>562</v>
+      </c>
+      <c r="H140" s="2" t="s">
+        <v>416</v>
+      </c>
+      <c r="J140" s="2" t="s">
+        <v>1059</v>
+      </c>
+      <c r="K140" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="141" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A141" t="s">
         <v>898</v>
       </c>
+      <c r="B141" t="s">
+        <v>1019</v>
+      </c>
+      <c r="C141" t="s">
+        <v>1020</v>
+      </c>
+      <c r="D141" t="s">
+        <v>1016</v>
+      </c>
+      <c r="E141" t="s">
+        <v>89</v>
+      </c>
     </row>
     <row r="142" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A142" t="s">
         <v>899</v>
       </c>
+      <c r="B142" t="s">
+        <v>1021</v>
+      </c>
+      <c r="C142" t="s">
+        <v>1022</v>
+      </c>
+      <c r="D142" t="s">
+        <v>1016</v>
+      </c>
+      <c r="E142" t="s">
+        <v>40</v>
+      </c>
     </row>
     <row r="143" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A143" t="s">
         <v>900</v>
       </c>
+      <c r="B143" t="s">
+        <v>1023</v>
+      </c>
+      <c r="C143" t="s">
+        <v>1024</v>
+      </c>
+      <c r="D143" t="s">
+        <v>1016</v>
+      </c>
+      <c r="E143" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="144" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A144" t="s">
         <v>901</v>
       </c>
+      <c r="B144" t="s">
+        <v>1025</v>
+      </c>
+      <c r="C144" t="s">
+        <v>1026</v>
+      </c>
+      <c r="D144" t="s">
+        <v>1016</v>
+      </c>
+      <c r="E144" t="s">
+        <v>40</v>
+      </c>
     </row>
     <row r="145" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A145" t="s">
         <v>902</v>
       </c>
+      <c r="B145" t="s">
+        <v>1027</v>
+      </c>
+      <c r="C145" t="s">
+        <v>1028</v>
+      </c>
+      <c r="D145" t="s">
+        <v>1016</v>
+      </c>
+      <c r="E145" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="146" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A146" t="s">
         <v>903</v>
       </c>
+      <c r="B146" t="s">
+        <v>1029</v>
+      </c>
+      <c r="C146" t="s">
+        <v>1030</v>
+      </c>
+      <c r="D146" t="s">
+        <v>1016</v>
+      </c>
+      <c r="E146" t="s">
+        <v>99</v>
+      </c>
     </row>
     <row r="147" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A147" t="s">
         <v>904</v>
       </c>
+      <c r="B147" t="s">
+        <v>1031</v>
+      </c>
+      <c r="C147" t="s">
+        <v>1032</v>
+      </c>
+      <c r="D147" t="s">
+        <v>1016</v>
+      </c>
+      <c r="E147" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="148" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A148" t="s">
@@ -7652,91 +8090,354 @@
     </row>
     <row r="149" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A149" t="s">
-        <v>23</v>
+        <v>996</v>
       </c>
       <c r="B149" t="s">
-        <v>24</v>
+        <v>1033</v>
       </c>
       <c r="C149" t="s">
-        <v>25</v>
+        <v>1034</v>
       </c>
       <c r="D149" t="s">
-        <v>26</v>
+        <v>1016</v>
       </c>
       <c r="E149" t="s">
         <v>8</v>
       </c>
-      <c r="G149" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="H149" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="J149" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="K149" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="150" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A150" t="s">
-        <v>29</v>
+        <v>997</v>
       </c>
       <c r="B150" t="s">
-        <v>30</v>
+        <v>1035</v>
       </c>
       <c r="C150" t="s">
-        <v>31</v>
+        <v>1036</v>
       </c>
       <c r="D150" t="s">
-        <v>32</v>
+        <v>1016</v>
       </c>
       <c r="E150" t="s">
-        <v>33</v>
-      </c>
-      <c r="G150" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="H150" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="I150" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="J150" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="K150" t="b">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="151" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A151" t="s">
+        <v>998</v>
+      </c>
+      <c r="B151" t="s">
+        <v>1037</v>
+      </c>
+      <c r="C151" t="s">
+        <v>1038</v>
+      </c>
+      <c r="D151" t="s">
+        <v>1016</v>
+      </c>
+      <c r="E151" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="152" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A152" t="s">
+        <v>999</v>
+      </c>
+      <c r="B152" t="s">
+        <v>1039</v>
+      </c>
+      <c r="C152" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D152" t="s">
+        <v>1016</v>
+      </c>
+      <c r="E152" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="153" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A153" t="s">
+        <v>1000</v>
+      </c>
+      <c r="B153" t="s">
+        <v>1041</v>
+      </c>
+      <c r="C153" t="s">
+        <v>1042</v>
+      </c>
+      <c r="D153" t="s">
+        <v>1016</v>
+      </c>
+      <c r="E153" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="154" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A154" t="s">
+        <v>1001</v>
+      </c>
+      <c r="B154" t="s">
+        <v>1043</v>
+      </c>
+      <c r="C154" t="s">
+        <v>1045</v>
+      </c>
+      <c r="D154" t="s">
+        <v>1016</v>
+      </c>
+      <c r="E154" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="155" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A155" t="s">
+        <v>1002</v>
+      </c>
+      <c r="B155" t="s">
+        <v>1046</v>
+      </c>
+      <c r="C155" t="s">
+        <v>1044</v>
+      </c>
+      <c r="D155" t="s">
+        <v>1016</v>
+      </c>
+      <c r="E155" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="156" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A156" t="s">
+        <v>1003</v>
+      </c>
+      <c r="B156" t="s">
+        <v>1047</v>
+      </c>
+      <c r="C156" t="s">
+        <v>1048</v>
+      </c>
+      <c r="D156" t="s">
+        <v>79</v>
+      </c>
+      <c r="E156" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="157" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A157" t="s">
+        <v>1004</v>
+      </c>
+      <c r="B157" t="s">
+        <v>1049</v>
+      </c>
+      <c r="C157" t="s">
+        <v>1050</v>
+      </c>
+      <c r="D157" t="s">
+        <v>1016</v>
+      </c>
+      <c r="E157" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="158" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A158" t="s">
+        <v>1005</v>
+      </c>
+      <c r="B158" t="s">
+        <v>1051</v>
+      </c>
+      <c r="C158" t="s">
+        <v>1052</v>
+      </c>
+      <c r="D158" t="s">
+        <v>1016</v>
+      </c>
+      <c r="E158" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="159" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A159" t="s">
+        <v>1006</v>
+      </c>
+      <c r="B159" t="s">
+        <v>1053</v>
+      </c>
+      <c r="C159" t="s">
+        <v>1054</v>
+      </c>
+      <c r="D159" t="s">
+        <v>1016</v>
+      </c>
+      <c r="E159" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="160" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A160" t="s">
+        <v>1007</v>
+      </c>
+      <c r="B160" t="s">
+        <v>1055</v>
+      </c>
+      <c r="C160" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D160" t="s">
+        <v>1016</v>
+      </c>
+      <c r="E160" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="161" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A161" t="s">
+        <v>1008</v>
+      </c>
+      <c r="B161" t="s">
+        <v>1057</v>
+      </c>
+      <c r="C161" t="s">
+        <v>1058</v>
+      </c>
+      <c r="D161" t="s">
+        <v>1016</v>
+      </c>
+      <c r="E161" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="162" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A162" t="s">
+        <v>1009</v>
+      </c>
+      <c r="B162" t="s">
+        <v>1017</v>
+      </c>
+      <c r="C162" t="s">
+        <v>1018</v>
+      </c>
+      <c r="D162" t="s">
+        <v>1016</v>
+      </c>
+      <c r="E162" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="163" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A163" t="s">
+        <v>1010</v>
+      </c>
+    </row>
+    <row r="164" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A164" t="s">
+        <v>1011</v>
+      </c>
+    </row>
+    <row r="165" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A165" t="s">
+        <v>1012</v>
+      </c>
+    </row>
+    <row r="166" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A166" t="s">
+        <v>1013</v>
+      </c>
+    </row>
+    <row r="167" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A167" t="s">
+        <v>1014</v>
+      </c>
+    </row>
+    <row r="168" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A168" t="s">
+        <v>23</v>
+      </c>
+      <c r="B168" t="s">
+        <v>24</v>
+      </c>
+      <c r="C168" t="s">
+        <v>25</v>
+      </c>
+      <c r="D168" t="s">
+        <v>26</v>
+      </c>
+      <c r="E168" t="s">
+        <v>8</v>
+      </c>
+      <c r="G168" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="H168" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J168" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="K168" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="169" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A169" t="s">
+        <v>29</v>
+      </c>
+      <c r="B169" t="s">
+        <v>30</v>
+      </c>
+      <c r="C169" t="s">
+        <v>31</v>
+      </c>
+      <c r="D169" t="s">
+        <v>32</v>
+      </c>
+      <c r="E169" t="s">
+        <v>33</v>
+      </c>
+      <c r="G169" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H169" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="I169" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="J169" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="K169" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="170" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A170" t="s">
         <v>36</v>
       </c>
-      <c r="B151" t="s">
+      <c r="B170" t="s">
         <v>37</v>
       </c>
-      <c r="C151" t="s">
+      <c r="C170" t="s">
         <v>38</v>
       </c>
-      <c r="D151" t="s">
+      <c r="D170" t="s">
         <v>39</v>
       </c>
-      <c r="E151" t="s">
+      <c r="E170" t="s">
         <v>40</v>
       </c>
-      <c r="G151" s="2" t="s">
+      <c r="G170" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="H151" s="2" t="s">
+      <c r="H170" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="J151" s="2" t="s">
+      <c r="J170" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="K151" t="b">
+      <c r="K170" t="b">
         <v>1</v>
       </c>
     </row>
@@ -8111,6 +8812,15 @@
       <c r="B21" t="s">
         <v>912</v>
       </c>
+      <c r="C21" t="s">
+        <v>972</v>
+      </c>
+      <c r="D21" t="s">
+        <v>969</v>
+      </c>
+      <c r="E21">
+        <v>1</v>
+      </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
@@ -8119,6 +8829,15 @@
       <c r="B22" t="s">
         <v>912</v>
       </c>
+      <c r="C22" t="s">
+        <v>974</v>
+      </c>
+      <c r="D22" t="s">
+        <v>970</v>
+      </c>
+      <c r="E22">
+        <v>1</v>
+      </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
@@ -8126,6 +8845,15 @@
       </c>
       <c r="B23" t="s">
         <v>912</v>
+      </c>
+      <c r="C23" t="s">
+        <v>973</v>
+      </c>
+      <c r="D23" t="s">
+        <v>971</v>
+      </c>
+      <c r="E23">
+        <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.45">
@@ -8154,7 +8882,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84E3BB0D-5578-4069-B1C9-C3864EB2A429}">
-  <dimension ref="A1:F376"/>
+  <dimension ref="A1:F508"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="2" max="2" width="26.33203125" customWidth="1"/>
@@ -14357,10 +15085,10 @@
     </row>
     <row r="365" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A365" t="s">
-        <v>76</v>
+        <v>880</v>
       </c>
       <c r="B365" t="s">
-        <v>77</v>
+        <v>467</v>
       </c>
       <c r="C365">
         <v>1</v>
@@ -14369,15 +15097,15 @@
         <v>1</v>
       </c>
       <c r="E365" t="s">
-        <v>82</v>
+        <v>320</v>
       </c>
     </row>
     <row r="366" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A366" t="s">
-        <v>76</v>
+        <v>880</v>
       </c>
       <c r="B366" t="s">
-        <v>77</v>
+        <v>467</v>
       </c>
       <c r="C366">
         <v>2</v>
@@ -14386,15 +15114,15 @@
         <v>0</v>
       </c>
       <c r="E366" t="s">
-        <v>83</v>
+        <v>950</v>
       </c>
     </row>
     <row r="367" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A367" t="s">
-        <v>76</v>
+        <v>880</v>
       </c>
       <c r="B367" t="s">
-        <v>77</v>
+        <v>467</v>
       </c>
       <c r="C367">
         <v>3</v>
@@ -14403,15 +15131,15 @@
         <v>0</v>
       </c>
       <c r="E367" t="s">
-        <v>84</v>
+        <v>951</v>
       </c>
     </row>
     <row r="368" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A368" t="s">
-        <v>23</v>
+        <v>881</v>
       </c>
       <c r="B368" t="s">
-        <v>24</v>
+        <v>905</v>
       </c>
       <c r="C368">
         <v>1</v>
@@ -14420,15 +15148,15 @@
         <v>0</v>
       </c>
       <c r="E368" t="s">
-        <v>61</v>
+        <v>952</v>
       </c>
     </row>
     <row r="369" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A369" t="s">
-        <v>23</v>
+        <v>881</v>
       </c>
       <c r="B369" t="s">
-        <v>24</v>
+        <v>905</v>
       </c>
       <c r="C369">
         <v>2</v>
@@ -14437,15 +15165,15 @@
         <v>0</v>
       </c>
       <c r="E369" t="s">
-        <v>62</v>
+        <v>953</v>
       </c>
     </row>
     <row r="370" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A370" t="s">
-        <v>23</v>
+        <v>881</v>
       </c>
       <c r="B370" t="s">
-        <v>24</v>
+        <v>905</v>
       </c>
       <c r="C370">
         <v>3</v>
@@ -14454,32 +15182,32 @@
         <v>0</v>
       </c>
       <c r="E370" t="s">
-        <v>63</v>
+        <v>954</v>
       </c>
     </row>
     <row r="371" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A371" t="s">
-        <v>29</v>
+        <v>882</v>
       </c>
       <c r="B371" t="s">
-        <v>30</v>
+        <v>906</v>
       </c>
       <c r="C371">
         <v>1</v>
       </c>
       <c r="D371" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E371" t="s">
-        <v>64</v>
+        <v>302</v>
       </c>
     </row>
     <row r="372" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A372" t="s">
-        <v>29</v>
+        <v>882</v>
       </c>
       <c r="B372" t="s">
-        <v>30</v>
+        <v>906</v>
       </c>
       <c r="C372">
         <v>2</v>
@@ -14488,15 +15216,15 @@
         <v>0</v>
       </c>
       <c r="E372" t="s">
-        <v>65</v>
+        <v>955</v>
       </c>
     </row>
     <row r="373" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A373" t="s">
-        <v>29</v>
+        <v>882</v>
       </c>
       <c r="B373" t="s">
-        <v>30</v>
+        <v>906</v>
       </c>
       <c r="C373">
         <v>3</v>
@@ -14505,15 +15233,15 @@
         <v>0</v>
       </c>
       <c r="E373" t="s">
-        <v>66</v>
+        <v>956</v>
       </c>
     </row>
     <row r="374" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A374" t="s">
-        <v>36</v>
+        <v>883</v>
       </c>
       <c r="B374" t="s">
-        <v>37</v>
+        <v>907</v>
       </c>
       <c r="C374">
         <v>1</v>
@@ -14522,15 +15250,15 @@
         <v>0</v>
       </c>
       <c r="E374" t="s">
-        <v>67</v>
+        <v>957</v>
       </c>
     </row>
     <row r="375" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A375" t="s">
-        <v>36</v>
+        <v>883</v>
       </c>
       <c r="B375" t="s">
-        <v>37</v>
+        <v>907</v>
       </c>
       <c r="C375">
         <v>2</v>
@@ -14539,15 +15267,15 @@
         <v>0</v>
       </c>
       <c r="E375" t="s">
-        <v>68</v>
+        <v>958</v>
       </c>
     </row>
     <row r="376" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A376" t="s">
-        <v>36</v>
+        <v>883</v>
       </c>
       <c r="B376" t="s">
-        <v>37</v>
+        <v>907</v>
       </c>
       <c r="C376">
         <v>3</v>
@@ -14556,6 +15284,1278 @@
         <v>0</v>
       </c>
       <c r="E376" t="s">
+        <v>959</v>
+      </c>
+    </row>
+    <row r="377" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A377" t="s">
+        <v>884</v>
+      </c>
+      <c r="B377" t="s">
+        <v>908</v>
+      </c>
+      <c r="C377">
+        <v>1</v>
+      </c>
+      <c r="D377" t="b">
+        <v>1</v>
+      </c>
+      <c r="E377" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="378" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A378" t="s">
+        <v>884</v>
+      </c>
+      <c r="B378" t="s">
+        <v>908</v>
+      </c>
+      <c r="C378">
+        <v>2</v>
+      </c>
+      <c r="D378" t="b">
+        <v>0</v>
+      </c>
+      <c r="E378" t="s">
+        <v>960</v>
+      </c>
+    </row>
+    <row r="379" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A379" t="s">
+        <v>884</v>
+      </c>
+      <c r="B379" t="s">
+        <v>908</v>
+      </c>
+      <c r="C379">
+        <v>3</v>
+      </c>
+      <c r="D379" t="b">
+        <v>0</v>
+      </c>
+      <c r="E379" t="s">
+        <v>961</v>
+      </c>
+    </row>
+    <row r="380" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A380" t="s">
+        <v>885</v>
+      </c>
+      <c r="B380" t="s">
+        <v>910</v>
+      </c>
+      <c r="C380">
+        <v>1</v>
+      </c>
+      <c r="D380" t="b">
+        <v>1</v>
+      </c>
+      <c r="E380" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="381" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A381" t="s">
+        <v>885</v>
+      </c>
+      <c r="B381" t="s">
+        <v>910</v>
+      </c>
+      <c r="C381">
+        <v>2</v>
+      </c>
+      <c r="D381" t="b">
+        <v>0</v>
+      </c>
+      <c r="E381" t="s">
+        <v>962</v>
+      </c>
+    </row>
+    <row r="382" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A382" t="s">
+        <v>885</v>
+      </c>
+      <c r="B382" t="s">
+        <v>910</v>
+      </c>
+      <c r="C382">
+        <v>3</v>
+      </c>
+      <c r="D382" t="b">
+        <v>0</v>
+      </c>
+      <c r="E382" t="s">
+        <v>963</v>
+      </c>
+    </row>
+    <row r="383" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A383" t="s">
+        <v>886</v>
+      </c>
+      <c r="B383" t="s">
+        <v>911</v>
+      </c>
+      <c r="C383">
+        <v>1</v>
+      </c>
+      <c r="D383" t="b">
+        <v>0</v>
+      </c>
+      <c r="E383" t="s">
+        <v>964</v>
+      </c>
+    </row>
+    <row r="384" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A384" t="s">
+        <v>886</v>
+      </c>
+      <c r="B384" t="s">
+        <v>911</v>
+      </c>
+      <c r="C384">
+        <v>2</v>
+      </c>
+      <c r="D384" t="b">
+        <v>0</v>
+      </c>
+      <c r="E384" t="s">
+        <v>966</v>
+      </c>
+    </row>
+    <row r="385" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A385" t="s">
+        <v>886</v>
+      </c>
+      <c r="B385" t="s">
+        <v>911</v>
+      </c>
+      <c r="C385">
+        <v>3</v>
+      </c>
+      <c r="D385" t="b">
+        <v>0</v>
+      </c>
+      <c r="E385" t="s">
+        <v>965</v>
+      </c>
+    </row>
+    <row r="386" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A386" t="s">
+        <v>887</v>
+      </c>
+      <c r="B386" t="s">
+        <v>912</v>
+      </c>
+      <c r="C386">
+        <v>1</v>
+      </c>
+      <c r="D386" t="b">
+        <v>1</v>
+      </c>
+      <c r="E386" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="387" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A387" t="s">
+        <v>887</v>
+      </c>
+      <c r="B387" t="s">
+        <v>912</v>
+      </c>
+      <c r="C387">
+        <v>2</v>
+      </c>
+      <c r="D387" t="b">
+        <v>0</v>
+      </c>
+      <c r="E387" t="s">
+        <v>967</v>
+      </c>
+    </row>
+    <row r="388" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A388" t="s">
+        <v>887</v>
+      </c>
+      <c r="B388" t="s">
+        <v>912</v>
+      </c>
+      <c r="C388">
+        <v>3</v>
+      </c>
+      <c r="D388" t="b">
+        <v>0</v>
+      </c>
+      <c r="E388" t="s">
+        <v>968</v>
+      </c>
+    </row>
+    <row r="389" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A389" t="s">
+        <v>888</v>
+      </c>
+      <c r="B389" t="s">
+        <v>913</v>
+      </c>
+      <c r="C389">
+        <v>1</v>
+      </c>
+      <c r="D389" t="b">
+        <v>1</v>
+      </c>
+      <c r="E389" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="390" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A390" t="s">
+        <v>888</v>
+      </c>
+      <c r="B390" t="s">
+        <v>913</v>
+      </c>
+      <c r="C390">
+        <v>2</v>
+      </c>
+      <c r="D390" t="b">
+        <v>0</v>
+      </c>
+      <c r="E390" t="s">
+        <v>975</v>
+      </c>
+    </row>
+    <row r="391" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A391" t="s">
+        <v>888</v>
+      </c>
+      <c r="B391" t="s">
+        <v>913</v>
+      </c>
+      <c r="C391">
+        <v>3</v>
+      </c>
+      <c r="D391" t="b">
+        <v>0</v>
+      </c>
+      <c r="E391" t="s">
+        <v>976</v>
+      </c>
+    </row>
+    <row r="392" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A392" t="s">
+        <v>889</v>
+      </c>
+      <c r="B392" t="s">
+        <v>914</v>
+      </c>
+      <c r="C392">
+        <v>1</v>
+      </c>
+      <c r="D392" t="b">
+        <v>1</v>
+      </c>
+      <c r="E392" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="393" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A393" t="s">
+        <v>889</v>
+      </c>
+      <c r="B393" t="s">
+        <v>914</v>
+      </c>
+      <c r="C393">
+        <v>2</v>
+      </c>
+      <c r="D393" t="b">
+        <v>0</v>
+      </c>
+      <c r="E393" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="394" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A394" t="s">
+        <v>889</v>
+      </c>
+      <c r="B394" t="s">
+        <v>914</v>
+      </c>
+      <c r="C394">
+        <v>3</v>
+      </c>
+      <c r="D394" t="b">
+        <v>0</v>
+      </c>
+      <c r="E394" t="s">
+        <v>978</v>
+      </c>
+    </row>
+    <row r="395" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A395" t="s">
+        <v>890</v>
+      </c>
+      <c r="B395" t="s">
+        <v>915</v>
+      </c>
+      <c r="C395">
+        <v>1</v>
+      </c>
+      <c r="D395" t="b">
+        <v>1</v>
+      </c>
+      <c r="E395" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="396" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A396" t="s">
+        <v>890</v>
+      </c>
+      <c r="B396" t="s">
+        <v>915</v>
+      </c>
+      <c r="C396">
+        <v>2</v>
+      </c>
+      <c r="D396" t="b">
+        <v>0</v>
+      </c>
+      <c r="E396" t="s">
+        <v>979</v>
+      </c>
+    </row>
+    <row r="397" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A397" t="s">
+        <v>890</v>
+      </c>
+      <c r="B397" t="s">
+        <v>915</v>
+      </c>
+      <c r="C397">
+        <v>3</v>
+      </c>
+      <c r="D397" t="b">
+        <v>0</v>
+      </c>
+      <c r="E397" t="s">
+        <v>980</v>
+      </c>
+    </row>
+    <row r="398" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A398" t="s">
+        <v>891</v>
+      </c>
+      <c r="B398" t="s">
+        <v>916</v>
+      </c>
+      <c r="C398">
+        <v>1</v>
+      </c>
+      <c r="D398" t="b">
+        <v>1</v>
+      </c>
+      <c r="E398" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="399" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A399" t="s">
+        <v>891</v>
+      </c>
+      <c r="B399" t="s">
+        <v>916</v>
+      </c>
+      <c r="C399">
+        <v>2</v>
+      </c>
+      <c r="D399" t="b">
+        <v>0</v>
+      </c>
+      <c r="E399" t="s">
+        <v>981</v>
+      </c>
+    </row>
+    <row r="400" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A400" t="s">
+        <v>891</v>
+      </c>
+      <c r="B400" t="s">
+        <v>916</v>
+      </c>
+      <c r="C400">
+        <v>3</v>
+      </c>
+      <c r="D400" t="b">
+        <v>0</v>
+      </c>
+      <c r="E400" t="s">
+        <v>982</v>
+      </c>
+    </row>
+    <row r="401" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A401" t="s">
+        <v>892</v>
+      </c>
+      <c r="B401" t="s">
+        <v>917</v>
+      </c>
+      <c r="C401">
+        <v>1</v>
+      </c>
+      <c r="D401" t="b">
+        <v>1</v>
+      </c>
+      <c r="E401" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="402" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A402" t="s">
+        <v>892</v>
+      </c>
+      <c r="B402" t="s">
+        <v>917</v>
+      </c>
+      <c r="C402">
+        <v>2</v>
+      </c>
+      <c r="D402" t="b">
+        <v>0</v>
+      </c>
+      <c r="E402" t="s">
+        <v>983</v>
+      </c>
+    </row>
+    <row r="403" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A403" t="s">
+        <v>892</v>
+      </c>
+      <c r="B403" t="s">
+        <v>917</v>
+      </c>
+      <c r="C403">
+        <v>3</v>
+      </c>
+      <c r="D403" t="b">
+        <v>0</v>
+      </c>
+      <c r="E403" t="s">
+        <v>984</v>
+      </c>
+    </row>
+    <row r="404" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A404" t="s">
+        <v>893</v>
+      </c>
+      <c r="B404" t="s">
+        <v>918</v>
+      </c>
+      <c r="C404">
+        <v>1</v>
+      </c>
+      <c r="D404" t="b">
+        <v>1</v>
+      </c>
+      <c r="E404" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="405" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A405" t="s">
+        <v>893</v>
+      </c>
+      <c r="B405" t="s">
+        <v>918</v>
+      </c>
+      <c r="C405">
+        <v>2</v>
+      </c>
+      <c r="D405" t="b">
+        <v>0</v>
+      </c>
+      <c r="E405" t="s">
+        <v>985</v>
+      </c>
+    </row>
+    <row r="406" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A406" t="s">
+        <v>893</v>
+      </c>
+      <c r="B406" t="s">
+        <v>918</v>
+      </c>
+      <c r="C406">
+        <v>3</v>
+      </c>
+      <c r="D406" t="b">
+        <v>0</v>
+      </c>
+      <c r="E406" t="s">
+        <v>986</v>
+      </c>
+    </row>
+    <row r="407" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A407" t="s">
+        <v>894</v>
+      </c>
+      <c r="B407" t="s">
+        <v>919</v>
+      </c>
+      <c r="C407">
+        <v>1</v>
+      </c>
+      <c r="D407" t="b">
+        <v>0</v>
+      </c>
+      <c r="E407" t="s">
+        <v>987</v>
+      </c>
+    </row>
+    <row r="408" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A408" t="s">
+        <v>894</v>
+      </c>
+      <c r="B408" t="s">
+        <v>919</v>
+      </c>
+      <c r="C408">
+        <v>2</v>
+      </c>
+      <c r="D408" t="b">
+        <v>0</v>
+      </c>
+      <c r="E408" t="s">
+        <v>988</v>
+      </c>
+    </row>
+    <row r="409" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A409" t="s">
+        <v>894</v>
+      </c>
+      <c r="B409" t="s">
+        <v>919</v>
+      </c>
+      <c r="C409">
+        <v>3</v>
+      </c>
+      <c r="D409" t="b">
+        <v>0</v>
+      </c>
+      <c r="E409" t="s">
+        <v>989</v>
+      </c>
+    </row>
+    <row r="410" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A410" t="s">
+        <v>895</v>
+      </c>
+      <c r="B410" t="s">
+        <v>920</v>
+      </c>
+      <c r="C410">
+        <v>1</v>
+      </c>
+      <c r="D410" t="b">
+        <v>0</v>
+      </c>
+      <c r="E410" t="s">
+        <v>990</v>
+      </c>
+    </row>
+    <row r="411" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A411" t="s">
+        <v>895</v>
+      </c>
+      <c r="B411" t="s">
+        <v>920</v>
+      </c>
+      <c r="C411">
+        <v>2</v>
+      </c>
+      <c r="D411" t="b">
+        <v>0</v>
+      </c>
+      <c r="E411" t="s">
+        <v>991</v>
+      </c>
+    </row>
+    <row r="412" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A412" t="s">
+        <v>895</v>
+      </c>
+      <c r="B412" t="s">
+        <v>920</v>
+      </c>
+      <c r="C412">
+        <v>3</v>
+      </c>
+      <c r="D412" t="b">
+        <v>0</v>
+      </c>
+      <c r="E412" t="s">
+        <v>992</v>
+      </c>
+    </row>
+    <row r="413" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A413" t="s">
+        <v>896</v>
+      </c>
+      <c r="B413" t="s">
+        <v>921</v>
+      </c>
+      <c r="C413">
+        <v>1</v>
+      </c>
+      <c r="D413" t="b">
+        <v>0</v>
+      </c>
+      <c r="E413" t="s">
+        <v>993</v>
+      </c>
+    </row>
+    <row r="414" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A414" t="s">
+        <v>896</v>
+      </c>
+      <c r="B414" t="s">
+        <v>921</v>
+      </c>
+      <c r="C414">
+        <v>2</v>
+      </c>
+      <c r="D414" t="b">
+        <v>0</v>
+      </c>
+      <c r="E414" t="s">
+        <v>994</v>
+      </c>
+    </row>
+    <row r="415" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A415" t="s">
+        <v>896</v>
+      </c>
+      <c r="B415" t="s">
+        <v>921</v>
+      </c>
+      <c r="C415">
+        <v>3</v>
+      </c>
+      <c r="D415" t="b">
+        <v>0</v>
+      </c>
+      <c r="E415" t="s">
+        <v>995</v>
+      </c>
+    </row>
+    <row r="416" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A416" t="s">
+        <v>897</v>
+      </c>
+    </row>
+    <row r="417" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A417" t="s">
+        <v>897</v>
+      </c>
+    </row>
+    <row r="418" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A418" t="s">
+        <v>897</v>
+      </c>
+    </row>
+    <row r="419" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A419" t="s">
+        <v>898</v>
+      </c>
+    </row>
+    <row r="420" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A420" t="s">
+        <v>898</v>
+      </c>
+    </row>
+    <row r="421" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A421" t="s">
+        <v>898</v>
+      </c>
+    </row>
+    <row r="422" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A422" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="423" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A423" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="424" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A424" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="425" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A425" t="s">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="426" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A426" t="s">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="427" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A427" t="s">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="428" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A428" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="429" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A429" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="430" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A430" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="431" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A431" t="s">
+        <v>902</v>
+      </c>
+    </row>
+    <row r="432" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A432" t="s">
+        <v>902</v>
+      </c>
+    </row>
+    <row r="433" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A433" t="s">
+        <v>902</v>
+      </c>
+    </row>
+    <row r="434" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A434" t="s">
+        <v>903</v>
+      </c>
+    </row>
+    <row r="435" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A435" t="s">
+        <v>903</v>
+      </c>
+    </row>
+    <row r="436" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A436" t="s">
+        <v>903</v>
+      </c>
+    </row>
+    <row r="437" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A437" t="s">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="438" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A438" t="s">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="439" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A439" t="s">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="440" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A440" t="s">
+        <v>76</v>
+      </c>
+      <c r="B440" t="s">
+        <v>77</v>
+      </c>
+      <c r="C440">
+        <v>1</v>
+      </c>
+      <c r="D440" t="b">
+        <v>1</v>
+      </c>
+      <c r="E440" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="441" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A441" t="s">
+        <v>76</v>
+      </c>
+      <c r="B441" t="s">
+        <v>77</v>
+      </c>
+      <c r="C441">
+        <v>2</v>
+      </c>
+      <c r="D441" t="b">
+        <v>0</v>
+      </c>
+      <c r="E441" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="442" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A442" t="s">
+        <v>76</v>
+      </c>
+      <c r="B442" t="s">
+        <v>77</v>
+      </c>
+      <c r="C442">
+        <v>3</v>
+      </c>
+      <c r="D442" t="b">
+        <v>0</v>
+      </c>
+      <c r="E442" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="443" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A443" t="s">
+        <v>996</v>
+      </c>
+    </row>
+    <row r="444" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A444" t="s">
+        <v>996</v>
+      </c>
+    </row>
+    <row r="445" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A445" t="s">
+        <v>996</v>
+      </c>
+    </row>
+    <row r="446" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A446" t="s">
+        <v>997</v>
+      </c>
+    </row>
+    <row r="447" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A447" t="s">
+        <v>997</v>
+      </c>
+    </row>
+    <row r="448" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A448" t="s">
+        <v>997</v>
+      </c>
+    </row>
+    <row r="449" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A449" t="s">
+        <v>998</v>
+      </c>
+    </row>
+    <row r="450" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A450" t="s">
+        <v>998</v>
+      </c>
+    </row>
+    <row r="451" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A451" t="s">
+        <v>998</v>
+      </c>
+    </row>
+    <row r="452" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A452" t="s">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="453" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A453" t="s">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="454" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A454" t="s">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="455" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A455" t="s">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="456" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A456" t="s">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="457" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A457" t="s">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="458" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A458" t="s">
+        <v>1001</v>
+      </c>
+    </row>
+    <row r="459" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A459" t="s">
+        <v>1001</v>
+      </c>
+    </row>
+    <row r="460" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A460" t="s">
+        <v>1001</v>
+      </c>
+    </row>
+    <row r="461" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A461" t="s">
+        <v>1002</v>
+      </c>
+    </row>
+    <row r="462" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A462" t="s">
+        <v>1002</v>
+      </c>
+    </row>
+    <row r="463" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A463" t="s">
+        <v>1002</v>
+      </c>
+    </row>
+    <row r="464" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A464" t="s">
+        <v>1003</v>
+      </c>
+    </row>
+    <row r="465" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A465" t="s">
+        <v>1003</v>
+      </c>
+    </row>
+    <row r="466" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A466" t="s">
+        <v>1003</v>
+      </c>
+    </row>
+    <row r="467" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A467" t="s">
+        <v>1004</v>
+      </c>
+    </row>
+    <row r="468" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A468" t="s">
+        <v>1004</v>
+      </c>
+    </row>
+    <row r="469" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A469" t="s">
+        <v>1004</v>
+      </c>
+    </row>
+    <row r="470" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A470" t="s">
+        <v>1005</v>
+      </c>
+    </row>
+    <row r="471" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A471" t="s">
+        <v>1005</v>
+      </c>
+    </row>
+    <row r="472" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A472" t="s">
+        <v>1005</v>
+      </c>
+    </row>
+    <row r="473" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A473" t="s">
+        <v>1006</v>
+      </c>
+    </row>
+    <row r="474" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A474" t="s">
+        <v>1006</v>
+      </c>
+    </row>
+    <row r="475" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A475" t="s">
+        <v>1006</v>
+      </c>
+    </row>
+    <row r="476" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A476" t="s">
+        <v>1007</v>
+      </c>
+    </row>
+    <row r="477" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A477" t="s">
+        <v>1007</v>
+      </c>
+    </row>
+    <row r="478" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A478" t="s">
+        <v>1007</v>
+      </c>
+    </row>
+    <row r="479" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A479" t="s">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="480" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A480" t="s">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="481" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A481" t="s">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="482" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A482" t="s">
+        <v>1009</v>
+      </c>
+    </row>
+    <row r="483" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A483" t="s">
+        <v>1009</v>
+      </c>
+    </row>
+    <row r="484" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A484" t="s">
+        <v>1009</v>
+      </c>
+    </row>
+    <row r="485" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A485" t="s">
+        <v>1010</v>
+      </c>
+    </row>
+    <row r="486" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A486" t="s">
+        <v>1010</v>
+      </c>
+    </row>
+    <row r="487" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A487" t="s">
+        <v>1010</v>
+      </c>
+    </row>
+    <row r="488" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A488" t="s">
+        <v>1011</v>
+      </c>
+    </row>
+    <row r="489" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A489" t="s">
+        <v>1011</v>
+      </c>
+    </row>
+    <row r="490" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A490" t="s">
+        <v>1011</v>
+      </c>
+    </row>
+    <row r="491" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A491" t="s">
+        <v>1012</v>
+      </c>
+    </row>
+    <row r="492" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A492" t="s">
+        <v>1012</v>
+      </c>
+    </row>
+    <row r="493" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A493" t="s">
+        <v>1012</v>
+      </c>
+    </row>
+    <row r="494" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A494" t="s">
+        <v>1013</v>
+      </c>
+    </row>
+    <row r="495" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A495" t="s">
+        <v>1013</v>
+      </c>
+    </row>
+    <row r="496" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A496" t="s">
+        <v>1013</v>
+      </c>
+    </row>
+    <row r="497" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A497" t="s">
+        <v>1014</v>
+      </c>
+    </row>
+    <row r="498" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A498" t="s">
+        <v>1014</v>
+      </c>
+    </row>
+    <row r="499" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A499" t="s">
+        <v>1014</v>
+      </c>
+    </row>
+    <row r="500" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A500" t="s">
+        <v>23</v>
+      </c>
+      <c r="B500" t="s">
+        <v>24</v>
+      </c>
+      <c r="C500">
+        <v>1</v>
+      </c>
+      <c r="D500" t="b">
+        <v>0</v>
+      </c>
+      <c r="E500" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="501" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A501" t="s">
+        <v>23</v>
+      </c>
+      <c r="B501" t="s">
+        <v>24</v>
+      </c>
+      <c r="C501">
+        <v>2</v>
+      </c>
+      <c r="D501" t="b">
+        <v>0</v>
+      </c>
+      <c r="E501" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="502" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A502" t="s">
+        <v>23</v>
+      </c>
+      <c r="B502" t="s">
+        <v>24</v>
+      </c>
+      <c r="C502">
+        <v>3</v>
+      </c>
+      <c r="D502" t="b">
+        <v>0</v>
+      </c>
+      <c r="E502" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="503" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A503" t="s">
+        <v>29</v>
+      </c>
+      <c r="B503" t="s">
+        <v>30</v>
+      </c>
+      <c r="C503">
+        <v>1</v>
+      </c>
+      <c r="D503" t="b">
+        <v>0</v>
+      </c>
+      <c r="E503" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="504" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A504" t="s">
+        <v>29</v>
+      </c>
+      <c r="B504" t="s">
+        <v>30</v>
+      </c>
+      <c r="C504">
+        <v>2</v>
+      </c>
+      <c r="D504" t="b">
+        <v>0</v>
+      </c>
+      <c r="E504" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="505" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A505" t="s">
+        <v>29</v>
+      </c>
+      <c r="B505" t="s">
+        <v>30</v>
+      </c>
+      <c r="C505">
+        <v>3</v>
+      </c>
+      <c r="D505" t="b">
+        <v>0</v>
+      </c>
+      <c r="E505" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="506" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A506" t="s">
+        <v>36</v>
+      </c>
+      <c r="B506" t="s">
+        <v>37</v>
+      </c>
+      <c r="C506">
+        <v>1</v>
+      </c>
+      <c r="D506" t="b">
+        <v>0</v>
+      </c>
+      <c r="E506" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="507" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A507" t="s">
+        <v>36</v>
+      </c>
+      <c r="B507" t="s">
+        <v>37</v>
+      </c>
+      <c r="C507">
+        <v>2</v>
+      </c>
+      <c r="D507" t="b">
+        <v>0</v>
+      </c>
+      <c r="E507" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="508" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A508" t="s">
+        <v>36</v>
+      </c>
+      <c r="B508" t="s">
+        <v>37</v>
+      </c>
+      <c r="C508">
+        <v>3</v>
+      </c>
+      <c r="D508" t="b">
+        <v>0</v>
+      </c>
+      <c r="E508" t="s">
         <v>69</v>
       </c>
     </row>

--- a/data/Fate-Spreadsheet.xlsx
+++ b/data/Fate-Spreadsheet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pixel\Documents\Projects\Fate-Wiki\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC4AA550-D884-4558-B74C-930BA076FA13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAA49089-B904-4768-8ED1-7E8B35224ADA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{B05E798F-9EF6-4508-A0A4-311D06661AED}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="2" xr2:uid="{B05E798F-9EF6-4508-A0A4-311D06661AED}"/>
   </bookViews>
   <sheets>
     <sheet name="Servants" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2812" uniqueCount="1060">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3015" uniqueCount="1141">
   <si>
     <t>servant_id</t>
   </si>
@@ -3156,9 +3156,6 @@
     <t>darius-iii</t>
   </si>
   <si>
-    <t>Lu Bu Fengxian</t>
-  </si>
-  <si>
     <t>lu-bu-fengxian</t>
   </si>
   <si>
@@ -3183,9 +3180,6 @@
     <t>florence-nightingale</t>
   </si>
   <si>
-    <t>Cu Chulainn</t>
-  </si>
-  <si>
     <t>Kingprotea</t>
   </si>
   <si>
@@ -3223,6 +3217,255 @@
   </si>
   <si>
     <t>Berserker_Strength_7,Berserker_Strength_9,Berserker_Agility_7,Luck,Luck</t>
+  </si>
+  <si>
+    <t>Berserker_Strength_7,Berserker_Agility_7,Berserker_Agility_9,Luck,Luck,Luck</t>
+  </si>
+  <si>
+    <t>Berserker_Strength_7,Berserker_Agility_7,Berserker_Magic_9,Luck,Luck,Luck</t>
+  </si>
+  <si>
+    <t>4,4,5,5,5</t>
+  </si>
+  <si>
+    <t>2,3,5,5,5</t>
+  </si>
+  <si>
+    <t>Berserker_Strength_7,Berserker_Strength_7,Berserker_Strength_9,Luck</t>
+  </si>
+  <si>
+    <t>Berserker_Magic_7,Berserker_Magic_7,Berserker_Magic_9,Luck,Surveil,Surveil</t>
+  </si>
+  <si>
+    <t>2,2,2,3</t>
+  </si>
+  <si>
+    <t>Berserker_Strength_7,Berserker_Strength_7,Berserker_Strength_9,Berserker_Agility_7,Berserker_Agility_9,Luck,Surveil</t>
+  </si>
+  <si>
+    <t>2,3,5,5,5,5</t>
+  </si>
+  <si>
+    <t>Berserker_Strength_7,Berserker_Strength_9,Berserker_Agility_7,Luck,Surveil</t>
+  </si>
+  <si>
+    <t>Berserker_Strength_7,Berserker_Strength_7,Berserker_Agility_7,Luck,Luck</t>
+  </si>
+  <si>
+    <t>Berserker_Strength_7,Berserker_Strength_7,Berserker_Strength_9,Berserker_Agility_7,Luck</t>
+  </si>
+  <si>
+    <t>Berserker_Strength_7,Berserker_Strength_7,Berserker_Agility_7,Berserker_Agility_7,Luck,Surveil</t>
+  </si>
+  <si>
+    <t>4,5,5</t>
+  </si>
+  <si>
+    <t>Berserker_Strength_7,Berserker_Agility_7,Berserker_Agility_9</t>
+  </si>
+  <si>
+    <t>Berserker_Strength_9,Luck,Preparation</t>
+  </si>
+  <si>
+    <t>Berserker_Strength_7,Berserker_Strength_9,Berserker_Magic_7</t>
+  </si>
+  <si>
+    <t>Berserker_Strength_9,Berserker_Agility_7,Luck,Preparation,Preparation</t>
+  </si>
+  <si>
+    <t>Berserker_Strength_7,Berserker_Strength_9,Berserker_Strength_9,Berserker_Agility_7,Luck,Preparation</t>
+  </si>
+  <si>
+    <t>God Hand</t>
+  </si>
+  <si>
+    <t>For Someone's Glory (Noble Phantasm)</t>
+  </si>
+  <si>
+    <t>For Someone's Glory (Passive)</t>
+  </si>
+  <si>
+    <t>Eternal Arms Mastery</t>
+  </si>
+  <si>
+    <t>Crimson Moon</t>
+  </si>
+  <si>
+    <t>Millenium Castle</t>
+  </si>
+  <si>
+    <t>Marble Phantasm</t>
+  </si>
+  <si>
+    <t>Bridal Chest (Galvanism)</t>
+  </si>
+  <si>
+    <t>Bridal Chest (Power Conversion)</t>
+  </si>
+  <si>
+    <t>Blasted Tree</t>
+  </si>
+  <si>
+    <t>Revolt</t>
+  </si>
+  <si>
+    <t>Crying Warmonger</t>
+  </si>
+  <si>
+    <t>Free Spirit</t>
+  </si>
+  <si>
+    <t>No More Lies</t>
+  </si>
+  <si>
+    <t>Flame Colored Kiss</t>
+  </si>
+  <si>
+    <t>Samadhi</t>
+  </si>
+  <si>
+    <t>Roar of the War God</t>
+  </si>
+  <si>
+    <t>Divine Beauty</t>
+  </si>
+  <si>
+    <t>Eviscerate</t>
+  </si>
+  <si>
+    <t>Golden Spark</t>
+  </si>
+  <si>
+    <t>Golden Eater</t>
+  </si>
+  <si>
+    <t>Ox-King Storm Call</t>
+  </si>
+  <si>
+    <t>Cleansing Wave</t>
+  </si>
+  <si>
+    <t>Oni Slayer</t>
+  </si>
+  <si>
+    <t>Athanaton 10.000</t>
+  </si>
+  <si>
+    <t>Battle Continuation</t>
+  </si>
+  <si>
+    <t>Gate of Babylon (Darius)</t>
+  </si>
+  <si>
+    <t>Lü Bu Fengxian</t>
+  </si>
+  <si>
+    <t>Restless Soul</t>
+  </si>
+  <si>
+    <t>Defiance</t>
+  </si>
+  <si>
+    <t>God Force</t>
+  </si>
+  <si>
+    <t>Conquering Might</t>
+  </si>
+  <si>
+    <t>Ultimate Defense Matrix</t>
+  </si>
+  <si>
+    <t>Martial Force</t>
+  </si>
+  <si>
+    <t>Mahapralaya (Imperfection is Sin)</t>
+  </si>
+  <si>
+    <t>Mahapralaya (World Reset)</t>
+  </si>
+  <si>
+    <t>Divine Supremacy</t>
+  </si>
+  <si>
+    <t>Nightingale Pledge</t>
+  </si>
+  <si>
+    <t>Iron Nurse</t>
+  </si>
+  <si>
+    <t>Angel of Crimea</t>
+  </si>
+  <si>
+    <t>Cú Chulainn (Alter)</t>
+  </si>
+  <si>
+    <t>Gae Bolg (Alter)</t>
+  </si>
+  <si>
+    <t>Curruid Coinchenn (Permanent)</t>
+  </si>
+  <si>
+    <t>Curruid Coinchenn (Passive)</t>
+  </si>
+  <si>
+    <t>Das Rhiengold</t>
+  </si>
+  <si>
+    <t>Black Wedding</t>
+  </si>
+  <si>
+    <t>Corrupted Balmung</t>
+  </si>
+  <si>
+    <t>Limit Break</t>
+  </si>
+  <si>
+    <t>Hibernation</t>
+  </si>
+  <si>
+    <t>Infinite Growth</t>
+  </si>
+  <si>
+    <t>Momijigari</t>
+  </si>
+  <si>
+    <t>Demon Form</t>
+  </si>
+  <si>
+    <t>Fire Breathing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coat of Oaths </t>
+  </si>
+  <si>
+    <t>Shinsengumi Law</t>
+  </si>
+  <si>
+    <t>Grudge of Rashoumon</t>
+  </si>
+  <si>
+    <t>Boiling Blood</t>
+  </si>
+  <si>
+    <t>Flame of Mount Ooe</t>
+  </si>
+  <si>
+    <t>Flucticulus Diana</t>
+  </si>
+  <si>
+    <t>Mad Tyrant</t>
+  </si>
+  <si>
+    <t>Gentle Moonlight</t>
+  </si>
+  <si>
+    <t>Chaos Labyrinthos</t>
+  </si>
+  <si>
+    <t>Natural Demon</t>
+  </si>
+  <si>
+    <t>Innocent Monster</t>
   </si>
 </sst>
 </file>
@@ -7931,7 +8174,7 @@
         <v>416</v>
       </c>
       <c r="J140" s="2" t="s">
-        <v>1059</v>
+        <v>1057</v>
       </c>
       <c r="K140" t="b">
         <v>0</v>
@@ -7953,6 +8196,18 @@
       <c r="E141" t="s">
         <v>89</v>
       </c>
+      <c r="G141" s="2" t="s">
+        <v>397</v>
+      </c>
+      <c r="H141" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="J141" s="2" t="s">
+        <v>1058</v>
+      </c>
+      <c r="K141" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="142" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A142" t="s">
@@ -7970,6 +8225,21 @@
       <c r="E142" t="s">
         <v>40</v>
       </c>
+      <c r="G142" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="H142" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="I142" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J142" s="2" t="s">
+        <v>1059</v>
+      </c>
+      <c r="K142" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="143" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A143" t="s">
@@ -7987,6 +8257,18 @@
       <c r="E143" t="s">
         <v>8</v>
       </c>
+      <c r="G143" s="2" t="s">
+        <v>1060</v>
+      </c>
+      <c r="I143" s="2" t="s">
+        <v>1060</v>
+      </c>
+      <c r="J143" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="K143" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="144" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A144" t="s">
@@ -8004,6 +8286,18 @@
       <c r="E144" t="s">
         <v>40</v>
       </c>
+      <c r="G144" s="2" t="s">
+        <v>1061</v>
+      </c>
+      <c r="H144" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="J144" s="2" t="s">
+        <v>1062</v>
+      </c>
+      <c r="K144" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="145" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A145" t="s">
@@ -8021,6 +8315,18 @@
       <c r="E145" t="s">
         <v>8</v>
       </c>
+      <c r="G145" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="I145" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="J145" s="2" t="s">
+        <v>1063</v>
+      </c>
+      <c r="K145" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="146" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A146" t="s">
@@ -8038,6 +8344,18 @@
       <c r="E146" t="s">
         <v>99</v>
       </c>
+      <c r="G146" s="2" t="s">
+        <v>1064</v>
+      </c>
+      <c r="H146" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="J146" s="2" t="s">
+        <v>1065</v>
+      </c>
+      <c r="K146" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="147" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A147" t="s">
@@ -8055,6 +8373,18 @@
       <c r="E147" t="s">
         <v>8</v>
       </c>
+      <c r="G147" s="2" t="s">
+        <v>1066</v>
+      </c>
+      <c r="H147" s="2" t="s">
+        <v>435</v>
+      </c>
+      <c r="J147" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="K147" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="148" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A148" t="s">
@@ -8104,6 +8434,21 @@
       <c r="E149" t="s">
         <v>8</v>
       </c>
+      <c r="G149" s="2" t="s">
+        <v>836</v>
+      </c>
+      <c r="H149" s="2" t="s">
+        <v>416</v>
+      </c>
+      <c r="I149" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="J149" s="2" t="s">
+        <v>1067</v>
+      </c>
+      <c r="K149" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="150" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A150" t="s">
@@ -8121,22 +8466,49 @@
       <c r="E150" t="s">
         <v>8</v>
       </c>
+      <c r="G150" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="H150" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="I150" s="2" t="s">
+        <v>416</v>
+      </c>
+      <c r="J150" s="2" t="s">
+        <v>1068</v>
+      </c>
+      <c r="K150" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="151" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A151" t="s">
         <v>998</v>
       </c>
       <c r="B151" t="s">
+        <v>1104</v>
+      </c>
+      <c r="C151" t="s">
         <v>1037</v>
-      </c>
-      <c r="C151" t="s">
-        <v>1038</v>
       </c>
       <c r="D151" t="s">
         <v>1016</v>
       </c>
       <c r="E151" t="s">
         <v>89</v>
+      </c>
+      <c r="G151" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="H151" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="J151" s="2" t="s">
+        <v>1069</v>
+      </c>
+      <c r="K151" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="152" spans="1:11" x14ac:dyDescent="0.45">
@@ -8144,16 +8516,28 @@
         <v>999</v>
       </c>
       <c r="B152" t="s">
+        <v>1038</v>
+      </c>
+      <c r="C152" t="s">
         <v>1039</v>
-      </c>
-      <c r="C152" t="s">
-        <v>1040</v>
       </c>
       <c r="D152" t="s">
         <v>1016</v>
       </c>
       <c r="E152" t="s">
         <v>89</v>
+      </c>
+      <c r="G152" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="H152" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J152" s="2" t="s">
+        <v>1070</v>
+      </c>
+      <c r="K152" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="153" spans="1:11" x14ac:dyDescent="0.45">
@@ -8161,16 +8545,31 @@
         <v>1000</v>
       </c>
       <c r="B153" t="s">
+        <v>1040</v>
+      </c>
+      <c r="C153" t="s">
         <v>1041</v>
-      </c>
-      <c r="C153" t="s">
-        <v>1042</v>
       </c>
       <c r="D153" t="s">
         <v>1016</v>
       </c>
       <c r="E153" t="s">
         <v>8</v>
+      </c>
+      <c r="G153" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="H153" s="2" t="s">
+        <v>836</v>
+      </c>
+      <c r="I153" s="2" t="s">
+        <v>1071</v>
+      </c>
+      <c r="J153" s="2" t="s">
+        <v>838</v>
+      </c>
+      <c r="K153" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="154" spans="1:11" x14ac:dyDescent="0.45">
@@ -8178,16 +8577,28 @@
         <v>1001</v>
       </c>
       <c r="B154" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="C154" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="D154" t="s">
         <v>1016</v>
       </c>
       <c r="E154" t="s">
         <v>40</v>
+      </c>
+      <c r="G154" s="2" t="s">
+        <v>940</v>
+      </c>
+      <c r="H154" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J154" s="2" t="s">
+        <v>1067</v>
+      </c>
+      <c r="K154" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="155" spans="1:11" x14ac:dyDescent="0.45">
@@ -8195,16 +8606,31 @@
         <v>1002</v>
       </c>
       <c r="B155" t="s">
-        <v>1046</v>
+        <v>1117</v>
       </c>
       <c r="C155" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="D155" t="s">
         <v>1016</v>
       </c>
       <c r="E155" t="s">
         <v>40</v>
+      </c>
+      <c r="G155" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="H155" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="I155" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="J155" s="2" t="s">
+        <v>1072</v>
+      </c>
+      <c r="K155" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="156" spans="1:11" x14ac:dyDescent="0.45">
@@ -8212,16 +8638,28 @@
         <v>1003</v>
       </c>
       <c r="B156" t="s">
-        <v>1047</v>
+        <v>1045</v>
       </c>
       <c r="C156" t="s">
-        <v>1048</v>
+        <v>1046</v>
       </c>
       <c r="D156" t="s">
         <v>79</v>
       </c>
       <c r="E156" t="s">
         <v>89</v>
+      </c>
+      <c r="G156" s="2" t="s">
+        <v>660</v>
+      </c>
+      <c r="H156" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="J156" s="2" t="s">
+        <v>1073</v>
+      </c>
+      <c r="K156" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="157" spans="1:11" x14ac:dyDescent="0.45">
@@ -8229,16 +8667,31 @@
         <v>1004</v>
       </c>
       <c r="B157" t="s">
-        <v>1049</v>
+        <v>1047</v>
       </c>
       <c r="C157" t="s">
-        <v>1050</v>
+        <v>1048</v>
       </c>
       <c r="D157" t="s">
         <v>1016</v>
       </c>
       <c r="E157" t="s">
         <v>8</v>
+      </c>
+      <c r="G157" s="2" t="s">
+        <v>568</v>
+      </c>
+      <c r="H157" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="I157" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="J157" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="K157" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="158" spans="1:11" x14ac:dyDescent="0.45">
@@ -8246,16 +8699,31 @@
         <v>1005</v>
       </c>
       <c r="B158" t="s">
-        <v>1051</v>
+        <v>1049</v>
       </c>
       <c r="C158" t="s">
-        <v>1052</v>
+        <v>1050</v>
       </c>
       <c r="D158" t="s">
         <v>1016</v>
       </c>
       <c r="E158" t="s">
         <v>40</v>
+      </c>
+      <c r="G158" s="2" t="s">
+        <v>946</v>
+      </c>
+      <c r="H158" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I158" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="J158" s="2" t="s">
+        <v>744</v>
+      </c>
+      <c r="K158" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="159" spans="1:11" x14ac:dyDescent="0.45">
@@ -8263,16 +8731,28 @@
         <v>1006</v>
       </c>
       <c r="B159" t="s">
-        <v>1053</v>
+        <v>1051</v>
       </c>
       <c r="C159" t="s">
-        <v>1054</v>
+        <v>1052</v>
       </c>
       <c r="D159" t="s">
         <v>1016</v>
       </c>
       <c r="E159" t="s">
         <v>89</v>
+      </c>
+      <c r="G159" s="2" t="s">
+        <v>1061</v>
+      </c>
+      <c r="H159" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="J159" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="K159" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="160" spans="1:11" x14ac:dyDescent="0.45">
@@ -8280,16 +8760,31 @@
         <v>1007</v>
       </c>
       <c r="B160" t="s">
-        <v>1055</v>
+        <v>1053</v>
       </c>
       <c r="C160" t="s">
-        <v>1056</v>
+        <v>1054</v>
       </c>
       <c r="D160" t="s">
         <v>1016</v>
       </c>
       <c r="E160" t="s">
         <v>40</v>
+      </c>
+      <c r="G160" s="2" t="s">
+        <v>569</v>
+      </c>
+      <c r="H160" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="I160" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J160" s="2" t="s">
+        <v>1074</v>
+      </c>
+      <c r="K160" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="161" spans="1:11" x14ac:dyDescent="0.45">
@@ -8297,16 +8792,28 @@
         <v>1008</v>
       </c>
       <c r="B161" t="s">
-        <v>1057</v>
+        <v>1055</v>
       </c>
       <c r="C161" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
       <c r="D161" t="s">
         <v>1016</v>
       </c>
       <c r="E161" t="s">
         <v>89</v>
+      </c>
+      <c r="G161" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="H161" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="J161" s="2" t="s">
+        <v>1075</v>
+      </c>
+      <c r="K161" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="162" spans="1:11" x14ac:dyDescent="0.45">
@@ -8324,6 +8831,18 @@
       </c>
       <c r="E162" t="s">
         <v>33</v>
+      </c>
+      <c r="G162" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="H162" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="J162" s="2" t="s">
+        <v>1076</v>
+      </c>
+      <c r="K162" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="163" spans="1:11" x14ac:dyDescent="0.45">
@@ -8445,7 +8964,7 @@
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="H2 I6:I7 I10 I12 H14 I18 I22 I24 I27 G34 I40 I42 I45 I52 I62 I72 H79 I80 I84 I88 I90 G91 H100 I119 I124 I121:I123 G130:I139" numberStoredAsText="1"/>
+    <ignoredError sqref="H2 I6:I7 I10 I12 H14 I18 I22 I24 I27 G34 I40 I42 I45 I52 I62 I72 H79 I80 I84 I88 I90 G91 H100 I119 I124 I121:I123 G130:I139 G142:I148" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -15954,121 +16473,409 @@
       <c r="A416" t="s">
         <v>897</v>
       </c>
-    </row>
-    <row r="417" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="B416" t="s">
+        <v>247</v>
+      </c>
+      <c r="C416">
+        <v>1</v>
+      </c>
+      <c r="D416" t="b">
+        <v>0</v>
+      </c>
+      <c r="E416" t="s">
+        <v>1077</v>
+      </c>
+    </row>
+    <row r="417" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A417" t="s">
         <v>897</v>
       </c>
-    </row>
-    <row r="418" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="B417" t="s">
+        <v>247</v>
+      </c>
+      <c r="C417">
+        <v>2</v>
+      </c>
+      <c r="D417" t="b">
+        <v>0</v>
+      </c>
+      <c r="E417" t="s">
+        <v>1077</v>
+      </c>
+    </row>
+    <row r="418" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A418" t="s">
         <v>897</v>
       </c>
-    </row>
-    <row r="419" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="B418" t="s">
+        <v>247</v>
+      </c>
+      <c r="C418">
+        <v>3</v>
+      </c>
+      <c r="D418" t="b">
+        <v>0</v>
+      </c>
+      <c r="E418" t="s">
+        <v>1077</v>
+      </c>
+    </row>
+    <row r="419" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A419" t="s">
         <v>898</v>
       </c>
-    </row>
-    <row r="420" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="B419" t="s">
+        <v>1019</v>
+      </c>
+      <c r="C419">
+        <v>1</v>
+      </c>
+      <c r="D419" t="b">
+        <v>0</v>
+      </c>
+      <c r="E419" t="s">
+        <v>1078</v>
+      </c>
+    </row>
+    <row r="420" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A420" t="s">
         <v>898</v>
       </c>
-    </row>
-    <row r="421" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="B420" t="s">
+        <v>1019</v>
+      </c>
+      <c r="C420">
+        <v>2</v>
+      </c>
+      <c r="D420" t="b">
+        <v>0</v>
+      </c>
+      <c r="E420" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="421" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A421" t="s">
         <v>898</v>
       </c>
-    </row>
-    <row r="422" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="B421" t="s">
+        <v>1019</v>
+      </c>
+      <c r="C421">
+        <v>3</v>
+      </c>
+      <c r="D421" t="b">
+        <v>0</v>
+      </c>
+      <c r="E421" t="s">
+        <v>1080</v>
+      </c>
+    </row>
+    <row r="422" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A422" t="s">
         <v>899</v>
       </c>
-    </row>
-    <row r="423" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="B422" t="s">
+        <v>1021</v>
+      </c>
+      <c r="C422">
+        <v>1</v>
+      </c>
+      <c r="D422" t="b">
+        <v>0</v>
+      </c>
+      <c r="E422" t="s">
+        <v>1081</v>
+      </c>
+    </row>
+    <row r="423" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A423" t="s">
         <v>899</v>
       </c>
-    </row>
-    <row r="424" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="B423" t="s">
+        <v>1021</v>
+      </c>
+      <c r="C423">
+        <v>2</v>
+      </c>
+      <c r="D423" t="b">
+        <v>0</v>
+      </c>
+      <c r="E423" t="s">
+        <v>1082</v>
+      </c>
+    </row>
+    <row r="424" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A424" t="s">
         <v>899</v>
       </c>
-    </row>
-    <row r="425" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="B424" t="s">
+        <v>1021</v>
+      </c>
+      <c r="C424">
+        <v>3</v>
+      </c>
+      <c r="D424" t="b">
+        <v>0</v>
+      </c>
+      <c r="E424" t="s">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="425" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A425" t="s">
         <v>900</v>
       </c>
-    </row>
-    <row r="426" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="B425" t="s">
+        <v>1023</v>
+      </c>
+      <c r="C425">
+        <v>1</v>
+      </c>
+      <c r="D425" t="b">
+        <v>0</v>
+      </c>
+      <c r="E425" t="s">
+        <v>1084</v>
+      </c>
+    </row>
+    <row r="426" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A426" t="s">
         <v>900</v>
       </c>
-    </row>
-    <row r="427" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="B426" t="s">
+        <v>1023</v>
+      </c>
+      <c r="C426">
+        <v>2</v>
+      </c>
+      <c r="D426" t="b">
+        <v>0</v>
+      </c>
+      <c r="E426" t="s">
+        <v>1085</v>
+      </c>
+    </row>
+    <row r="427" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A427" t="s">
         <v>900</v>
       </c>
-    </row>
-    <row r="428" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="B427" t="s">
+        <v>1023</v>
+      </c>
+      <c r="C427">
+        <v>3</v>
+      </c>
+      <c r="D427" t="b">
+        <v>0</v>
+      </c>
+      <c r="E427" t="s">
+        <v>1086</v>
+      </c>
+    </row>
+    <row r="428" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A428" t="s">
         <v>901</v>
       </c>
-    </row>
-    <row r="429" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="B428" t="s">
+        <v>1025</v>
+      </c>
+      <c r="C428">
+        <v>1</v>
+      </c>
+      <c r="D428" t="b">
+        <v>0</v>
+      </c>
+      <c r="E428" t="s">
+        <v>1087</v>
+      </c>
+    </row>
+    <row r="429" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A429" t="s">
         <v>901</v>
       </c>
-    </row>
-    <row r="430" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="B429" t="s">
+        <v>1025</v>
+      </c>
+      <c r="C429">
+        <v>2</v>
+      </c>
+      <c r="D429" t="b">
+        <v>0</v>
+      </c>
+      <c r="E429" t="s">
+        <v>1088</v>
+      </c>
+    </row>
+    <row r="430" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A430" t="s">
         <v>901</v>
       </c>
-    </row>
-    <row r="431" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="B430" t="s">
+        <v>1025</v>
+      </c>
+      <c r="C430">
+        <v>3</v>
+      </c>
+      <c r="D430" t="b">
+        <v>0</v>
+      </c>
+      <c r="E430" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="431" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A431" t="s">
         <v>902</v>
       </c>
-    </row>
-    <row r="432" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="B431" t="s">
+        <v>1027</v>
+      </c>
+      <c r="C431">
+        <v>1</v>
+      </c>
+      <c r="D431" t="b">
+        <v>0</v>
+      </c>
+      <c r="E431" t="s">
+        <v>1090</v>
+      </c>
+    </row>
+    <row r="432" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A432" t="s">
         <v>902</v>
+      </c>
+      <c r="B432" t="s">
+        <v>1027</v>
+      </c>
+      <c r="C432">
+        <v>2</v>
+      </c>
+      <c r="D432" t="b">
+        <v>0</v>
+      </c>
+      <c r="E432" t="s">
+        <v>1091</v>
       </c>
     </row>
     <row r="433" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A433" t="s">
         <v>902</v>
       </c>
+      <c r="B433" t="s">
+        <v>1027</v>
+      </c>
+      <c r="C433">
+        <v>3</v>
+      </c>
+      <c r="D433" t="b">
+        <v>0</v>
+      </c>
+      <c r="E433" t="s">
+        <v>1092</v>
+      </c>
     </row>
     <row r="434" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A434" t="s">
         <v>903</v>
       </c>
+      <c r="B434" t="s">
+        <v>1029</v>
+      </c>
+      <c r="C434">
+        <v>1</v>
+      </c>
+      <c r="D434" t="b">
+        <v>0</v>
+      </c>
+      <c r="E434" t="s">
+        <v>1093</v>
+      </c>
     </row>
     <row r="435" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A435" t="s">
         <v>903</v>
       </c>
+      <c r="B435" t="s">
+        <v>1029</v>
+      </c>
+      <c r="C435">
+        <v>2</v>
+      </c>
+      <c r="D435" t="b">
+        <v>0</v>
+      </c>
+      <c r="E435" t="s">
+        <v>1094</v>
+      </c>
     </row>
     <row r="436" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A436" t="s">
         <v>903</v>
       </c>
+      <c r="B436" t="s">
+        <v>1029</v>
+      </c>
+      <c r="C436">
+        <v>3</v>
+      </c>
+      <c r="D436" t="b">
+        <v>0</v>
+      </c>
+      <c r="E436" t="s">
+        <v>1095</v>
+      </c>
     </row>
     <row r="437" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A437" t="s">
         <v>904</v>
       </c>
+      <c r="B437" t="s">
+        <v>1031</v>
+      </c>
+      <c r="C437">
+        <v>1</v>
+      </c>
+      <c r="D437" t="b">
+        <v>0</v>
+      </c>
+      <c r="E437" t="s">
+        <v>1096</v>
+      </c>
     </row>
     <row r="438" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A438" t="s">
         <v>904</v>
       </c>
+      <c r="B438" t="s">
+        <v>1031</v>
+      </c>
+      <c r="C438">
+        <v>2</v>
+      </c>
+      <c r="D438" t="b">
+        <v>0</v>
+      </c>
+      <c r="E438" t="s">
+        <v>1096</v>
+      </c>
     </row>
     <row r="439" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A439" t="s">
         <v>904</v>
       </c>
+      <c r="B439" t="s">
+        <v>1031</v>
+      </c>
+      <c r="C439">
+        <v>3</v>
+      </c>
+      <c r="D439" t="b">
+        <v>0</v>
+      </c>
+      <c r="E439" t="s">
+        <v>1097</v>
+      </c>
     </row>
     <row r="440" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A440" t="s">
@@ -16125,268 +16932,772 @@
       <c r="A443" t="s">
         <v>996</v>
       </c>
+      <c r="B443" t="s">
+        <v>1033</v>
+      </c>
+      <c r="C443">
+        <v>1</v>
+      </c>
+      <c r="D443" t="b">
+        <v>0</v>
+      </c>
+      <c r="E443" t="s">
+        <v>1098</v>
+      </c>
     </row>
     <row r="444" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A444" t="s">
         <v>996</v>
       </c>
+      <c r="B444" t="s">
+        <v>1033</v>
+      </c>
+      <c r="C444">
+        <v>2</v>
+      </c>
+      <c r="D444" t="b">
+        <v>0</v>
+      </c>
+      <c r="E444" t="s">
+        <v>1099</v>
+      </c>
     </row>
     <row r="445" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A445" t="s">
         <v>996</v>
       </c>
+      <c r="B445" t="s">
+        <v>1033</v>
+      </c>
+      <c r="C445">
+        <v>3</v>
+      </c>
+      <c r="D445" t="b">
+        <v>0</v>
+      </c>
+      <c r="E445" t="s">
+        <v>1100</v>
+      </c>
     </row>
     <row r="446" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A446" t="s">
         <v>997</v>
       </c>
+      <c r="B446" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C446">
+        <v>1</v>
+      </c>
+      <c r="D446" t="b">
+        <v>0</v>
+      </c>
+      <c r="E446" t="s">
+        <v>1101</v>
+      </c>
     </row>
     <row r="447" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A447" t="s">
         <v>997</v>
       </c>
+      <c r="B447" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C447">
+        <v>2</v>
+      </c>
+      <c r="D447" t="b">
+        <v>0</v>
+      </c>
+      <c r="E447" t="s">
+        <v>1103</v>
+      </c>
     </row>
     <row r="448" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A448" t="s">
         <v>997</v>
       </c>
-    </row>
-    <row r="449" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="B448" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C448">
+        <v>3</v>
+      </c>
+      <c r="D448" t="b">
+        <v>0</v>
+      </c>
+      <c r="E448" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="449" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A449" t="s">
         <v>998</v>
       </c>
-    </row>
-    <row r="450" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="B449" t="s">
+        <v>1104</v>
+      </c>
+      <c r="C449">
+        <v>1</v>
+      </c>
+      <c r="D449" t="b">
+        <v>0</v>
+      </c>
+      <c r="E449" t="s">
+        <v>1105</v>
+      </c>
+    </row>
+    <row r="450" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A450" t="s">
         <v>998</v>
       </c>
-    </row>
-    <row r="451" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="B450" t="s">
+        <v>1104</v>
+      </c>
+      <c r="C450">
+        <v>2</v>
+      </c>
+      <c r="D450" t="b">
+        <v>0</v>
+      </c>
+      <c r="E450" t="s">
+        <v>1106</v>
+      </c>
+    </row>
+    <row r="451" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A451" t="s">
         <v>998</v>
       </c>
-    </row>
-    <row r="452" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="B451" t="s">
+        <v>1104</v>
+      </c>
+      <c r="C451">
+        <v>3</v>
+      </c>
+      <c r="D451" t="b">
+        <v>0</v>
+      </c>
+      <c r="E451" t="s">
+        <v>1107</v>
+      </c>
+    </row>
+    <row r="452" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A452" t="s">
         <v>999</v>
       </c>
-    </row>
-    <row r="453" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="B452" t="s">
+        <v>1038</v>
+      </c>
+      <c r="C452">
+        <v>1</v>
+      </c>
+      <c r="D452" t="b">
+        <v>0</v>
+      </c>
+      <c r="E452" t="s">
+        <v>1108</v>
+      </c>
+    </row>
+    <row r="453" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A453" t="s">
         <v>999</v>
       </c>
-    </row>
-    <row r="454" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="B453" t="s">
+        <v>1038</v>
+      </c>
+      <c r="C453">
+        <v>2</v>
+      </c>
+      <c r="D453" t="b">
+        <v>0</v>
+      </c>
+      <c r="E453" t="s">
+        <v>1109</v>
+      </c>
+    </row>
+    <row r="454" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A454" t="s">
         <v>999</v>
       </c>
-    </row>
-    <row r="455" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="B454" t="s">
+        <v>1038</v>
+      </c>
+      <c r="C454">
+        <v>3</v>
+      </c>
+      <c r="D454" t="b">
+        <v>0</v>
+      </c>
+      <c r="E454" t="s">
+        <v>1110</v>
+      </c>
+    </row>
+    <row r="455" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A455" t="s">
         <v>1000</v>
       </c>
-    </row>
-    <row r="456" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="B455" t="s">
+        <v>1040</v>
+      </c>
+      <c r="C455">
+        <v>1</v>
+      </c>
+      <c r="D455" t="b">
+        <v>0</v>
+      </c>
+      <c r="E455" t="s">
+        <v>1111</v>
+      </c>
+    </row>
+    <row r="456" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A456" t="s">
         <v>1000</v>
       </c>
-    </row>
-    <row r="457" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="B456" t="s">
+        <v>1040</v>
+      </c>
+      <c r="C456">
+        <v>2</v>
+      </c>
+      <c r="D456" t="b">
+        <v>0</v>
+      </c>
+      <c r="E456" t="s">
+        <v>1112</v>
+      </c>
+    </row>
+    <row r="457" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A457" t="s">
         <v>1000</v>
       </c>
-    </row>
-    <row r="458" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="B457" t="s">
+        <v>1040</v>
+      </c>
+      <c r="C457">
+        <v>3</v>
+      </c>
+      <c r="D457" t="b">
+        <v>0</v>
+      </c>
+      <c r="E457" t="s">
+        <v>1113</v>
+      </c>
+    </row>
+    <row r="458" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A458" t="s">
         <v>1001</v>
       </c>
-    </row>
-    <row r="459" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="B458" t="s">
+        <v>1042</v>
+      </c>
+      <c r="C458">
+        <v>1</v>
+      </c>
+      <c r="D458" t="b">
+        <v>0</v>
+      </c>
+      <c r="E458" t="s">
+        <v>1114</v>
+      </c>
+    </row>
+    <row r="459" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A459" t="s">
         <v>1001</v>
       </c>
-    </row>
-    <row r="460" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="B459" t="s">
+        <v>1042</v>
+      </c>
+      <c r="C459">
+        <v>2</v>
+      </c>
+      <c r="D459" t="b">
+        <v>0</v>
+      </c>
+      <c r="E459" t="s">
+        <v>1115</v>
+      </c>
+    </row>
+    <row r="460" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A460" t="s">
         <v>1001</v>
       </c>
-    </row>
-    <row r="461" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="B460" t="s">
+        <v>1042</v>
+      </c>
+      <c r="C460">
+        <v>3</v>
+      </c>
+      <c r="D460" t="b">
+        <v>0</v>
+      </c>
+      <c r="E460" t="s">
+        <v>1116</v>
+      </c>
+    </row>
+    <row r="461" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A461" t="s">
         <v>1002</v>
       </c>
-    </row>
-    <row r="462" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="B461" t="s">
+        <v>1117</v>
+      </c>
+      <c r="C461">
+        <v>1</v>
+      </c>
+      <c r="D461" t="b">
+        <v>0</v>
+      </c>
+      <c r="E461" t="s">
+        <v>1118</v>
+      </c>
+    </row>
+    <row r="462" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A462" t="s">
         <v>1002</v>
       </c>
-    </row>
-    <row r="463" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="B462" t="s">
+        <v>1117</v>
+      </c>
+      <c r="C462">
+        <v>2</v>
+      </c>
+      <c r="D462" t="b">
+        <v>0</v>
+      </c>
+      <c r="E462" t="s">
+        <v>1119</v>
+      </c>
+    </row>
+    <row r="463" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A463" t="s">
         <v>1002</v>
       </c>
-    </row>
-    <row r="464" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="B463" t="s">
+        <v>1117</v>
+      </c>
+      <c r="C463">
+        <v>3</v>
+      </c>
+      <c r="D463" t="b">
+        <v>0</v>
+      </c>
+      <c r="E463" t="s">
+        <v>1120</v>
+      </c>
+    </row>
+    <row r="464" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A464" t="s">
         <v>1003</v>
       </c>
-    </row>
-    <row r="465" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="B464" t="s">
+        <v>1045</v>
+      </c>
+      <c r="C464">
+        <v>1</v>
+      </c>
+      <c r="D464" t="b">
+        <v>0</v>
+      </c>
+      <c r="E464" t="s">
+        <v>1124</v>
+      </c>
+    </row>
+    <row r="465" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A465" t="s">
         <v>1003</v>
       </c>
-    </row>
-    <row r="466" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="B465" t="s">
+        <v>1045</v>
+      </c>
+      <c r="C465">
+        <v>2</v>
+      </c>
+      <c r="D465" t="b">
+        <v>0</v>
+      </c>
+      <c r="E465" t="s">
+        <v>1125</v>
+      </c>
+    </row>
+    <row r="466" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A466" t="s">
         <v>1003</v>
       </c>
-    </row>
-    <row r="467" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="B466" t="s">
+        <v>1045</v>
+      </c>
+      <c r="C466">
+        <v>3</v>
+      </c>
+      <c r="D466" t="b">
+        <v>0</v>
+      </c>
+      <c r="E466" t="s">
+        <v>1126</v>
+      </c>
+    </row>
+    <row r="467" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A467" t="s">
         <v>1004</v>
       </c>
-    </row>
-    <row r="468" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="B467" t="s">
+        <v>1047</v>
+      </c>
+      <c r="C467">
+        <v>1</v>
+      </c>
+      <c r="D467" t="b">
+        <v>0</v>
+      </c>
+      <c r="E467" t="s">
+        <v>1127</v>
+      </c>
+    </row>
+    <row r="468" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A468" t="s">
         <v>1004</v>
       </c>
-    </row>
-    <row r="469" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="B468" t="s">
+        <v>1047</v>
+      </c>
+      <c r="C468">
+        <v>2</v>
+      </c>
+      <c r="D468" t="b">
+        <v>0</v>
+      </c>
+      <c r="E468" t="s">
+        <v>1128</v>
+      </c>
+    </row>
+    <row r="469" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A469" t="s">
         <v>1004</v>
       </c>
-    </row>
-    <row r="470" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="B469" t="s">
+        <v>1047</v>
+      </c>
+      <c r="C469">
+        <v>3</v>
+      </c>
+      <c r="D469" t="b">
+        <v>0</v>
+      </c>
+      <c r="E469" t="s">
+        <v>1129</v>
+      </c>
+    </row>
+    <row r="470" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A470" t="s">
         <v>1005</v>
       </c>
-    </row>
-    <row r="471" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="B470" t="s">
+        <v>1049</v>
+      </c>
+      <c r="C470">
+        <v>1</v>
+      </c>
+      <c r="D470" t="b">
+        <v>0</v>
+      </c>
+      <c r="E470" t="s">
+        <v>1121</v>
+      </c>
+    </row>
+    <row r="471" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A471" t="s">
         <v>1005</v>
       </c>
-    </row>
-    <row r="472" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="B471" t="s">
+        <v>1049</v>
+      </c>
+      <c r="C471">
+        <v>2</v>
+      </c>
+      <c r="D471" t="b">
+        <v>0</v>
+      </c>
+      <c r="E471" t="s">
+        <v>1122</v>
+      </c>
+    </row>
+    <row r="472" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A472" t="s">
         <v>1005</v>
       </c>
-    </row>
-    <row r="473" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="B472" t="s">
+        <v>1049</v>
+      </c>
+      <c r="C472">
+        <v>3</v>
+      </c>
+      <c r="D472" t="b">
+        <v>0</v>
+      </c>
+      <c r="E472" t="s">
+        <v>1123</v>
+      </c>
+    </row>
+    <row r="473" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A473" t="s">
         <v>1006</v>
       </c>
-    </row>
-    <row r="474" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="B473" t="s">
+        <v>1051</v>
+      </c>
+      <c r="C473">
+        <v>1</v>
+      </c>
+      <c r="D473" t="b">
+        <v>0</v>
+      </c>
+      <c r="E473" t="s">
+        <v>1130</v>
+      </c>
+    </row>
+    <row r="474" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A474" t="s">
         <v>1006</v>
       </c>
-    </row>
-    <row r="475" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="B474" t="s">
+        <v>1051</v>
+      </c>
+      <c r="C474">
+        <v>2</v>
+      </c>
+      <c r="D474" t="b">
+        <v>0</v>
+      </c>
+      <c r="E474" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="475" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A475" t="s">
         <v>1006</v>
       </c>
-    </row>
-    <row r="476" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="B475" t="s">
+        <v>1051</v>
+      </c>
+      <c r="C475">
+        <v>3</v>
+      </c>
+      <c r="D475" t="b">
+        <v>0</v>
+      </c>
+      <c r="E475" t="s">
+        <v>1131</v>
+      </c>
+    </row>
+    <row r="476" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A476" t="s">
         <v>1007</v>
       </c>
-    </row>
-    <row r="477" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="B476" t="s">
+        <v>1053</v>
+      </c>
+      <c r="C476">
+        <v>1</v>
+      </c>
+      <c r="D476" t="b">
+        <v>0</v>
+      </c>
+      <c r="E476" t="s">
+        <v>1132</v>
+      </c>
+    </row>
+    <row r="477" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A477" t="s">
         <v>1007</v>
       </c>
-    </row>
-    <row r="478" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="B477" t="s">
+        <v>1053</v>
+      </c>
+      <c r="C477">
+        <v>2</v>
+      </c>
+      <c r="D477" t="b">
+        <v>0</v>
+      </c>
+      <c r="E477" t="s">
+        <v>1133</v>
+      </c>
+    </row>
+    <row r="478" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A478" t="s">
         <v>1007</v>
       </c>
-    </row>
-    <row r="479" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="B478" t="s">
+        <v>1053</v>
+      </c>
+      <c r="C478">
+        <v>3</v>
+      </c>
+      <c r="D478" t="b">
+        <v>0</v>
+      </c>
+      <c r="E478" t="s">
+        <v>1134</v>
+      </c>
+    </row>
+    <row r="479" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A479" t="s">
         <v>1008</v>
       </c>
-    </row>
-    <row r="480" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="B479" t="s">
+        <v>1055</v>
+      </c>
+      <c r="C479">
+        <v>1</v>
+      </c>
+      <c r="D479" t="b">
+        <v>0</v>
+      </c>
+      <c r="E479" t="s">
+        <v>1135</v>
+      </c>
+    </row>
+    <row r="480" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A480" t="s">
         <v>1008</v>
       </c>
-    </row>
-    <row r="481" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="B480" t="s">
+        <v>1055</v>
+      </c>
+      <c r="C480">
+        <v>2</v>
+      </c>
+      <c r="D480" t="b">
+        <v>0</v>
+      </c>
+      <c r="E480" t="s">
+        <v>1136</v>
+      </c>
+    </row>
+    <row r="481" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A481" t="s">
         <v>1008</v>
       </c>
-    </row>
-    <row r="482" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="B481" t="s">
+        <v>1055</v>
+      </c>
+      <c r="C481">
+        <v>3</v>
+      </c>
+      <c r="D481" t="b">
+        <v>0</v>
+      </c>
+      <c r="E481" t="s">
+        <v>1137</v>
+      </c>
+    </row>
+    <row r="482" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A482" t="s">
         <v>1009</v>
       </c>
-    </row>
-    <row r="483" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="B482" t="s">
+        <v>1017</v>
+      </c>
+      <c r="C482">
+        <v>1</v>
+      </c>
+      <c r="D482" t="b">
+        <v>0</v>
+      </c>
+      <c r="E482" t="s">
+        <v>1138</v>
+      </c>
+    </row>
+    <row r="483" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A483" t="s">
         <v>1009</v>
       </c>
-    </row>
-    <row r="484" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="B483" t="s">
+        <v>1017</v>
+      </c>
+      <c r="C483">
+        <v>2</v>
+      </c>
+      <c r="D483" t="b">
+        <v>0</v>
+      </c>
+      <c r="E483" t="s">
+        <v>1139</v>
+      </c>
+    </row>
+    <row r="484" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A484" t="s">
         <v>1009</v>
       </c>
-    </row>
-    <row r="485" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="B484" t="s">
+        <v>1017</v>
+      </c>
+      <c r="C484">
+        <v>3</v>
+      </c>
+      <c r="D484" t="b">
+        <v>0</v>
+      </c>
+      <c r="E484" t="s">
+        <v>1140</v>
+      </c>
+    </row>
+    <row r="485" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A485" t="s">
         <v>1010</v>
       </c>
     </row>
-    <row r="486" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="486" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A486" t="s">
         <v>1010</v>
       </c>
     </row>
-    <row r="487" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="487" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A487" t="s">
         <v>1010</v>
       </c>
     </row>
-    <row r="488" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="488" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A488" t="s">
         <v>1011</v>
       </c>
     </row>
-    <row r="489" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="489" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A489" t="s">
         <v>1011</v>
       </c>
     </row>
-    <row r="490" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="490" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A490" t="s">
         <v>1011</v>
       </c>
     </row>
-    <row r="491" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="491" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A491" t="s">
         <v>1012</v>
       </c>
     </row>
-    <row r="492" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="492" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A492" t="s">
         <v>1012</v>
       </c>
     </row>
-    <row r="493" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="493" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A493" t="s">
         <v>1012</v>
       </c>
     </row>
-    <row r="494" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="494" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A494" t="s">
         <v>1013</v>
       </c>
     </row>
-    <row r="495" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="495" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A495" t="s">
         <v>1013</v>
       </c>
     </row>
-    <row r="496" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="496" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A496" t="s">
         <v>1013</v>
       </c>

--- a/data/Fate-Spreadsheet.xlsx
+++ b/data/Fate-Spreadsheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pixel\Documents\Projects\Fate-Wiki\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAA49089-B904-4768-8ED1-7E8B35224ADA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6178DA6D-4EFC-4131-AAE1-759A02D550AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="2" xr2:uid="{B05E798F-9EF6-4508-A0A4-311D06661AED}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3015" uniqueCount="1141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3351" uniqueCount="1261">
   <si>
     <t>servant_id</t>
   </si>
@@ -3466,6 +3466,366 @@
   </si>
   <si>
     <t>Innocent Monster</t>
+  </si>
+  <si>
+    <t>S0168</t>
+  </si>
+  <si>
+    <t>S0169</t>
+  </si>
+  <si>
+    <t>S0170</t>
+  </si>
+  <si>
+    <t>S0171</t>
+  </si>
+  <si>
+    <t>S0172</t>
+  </si>
+  <si>
+    <t>S0173</t>
+  </si>
+  <si>
+    <t>S0174</t>
+  </si>
+  <si>
+    <t>S0175</t>
+  </si>
+  <si>
+    <t>S0176</t>
+  </si>
+  <si>
+    <t>S0177</t>
+  </si>
+  <si>
+    <t>S0179</t>
+  </si>
+  <si>
+    <t>S0180</t>
+  </si>
+  <si>
+    <t>S0181</t>
+  </si>
+  <si>
+    <t>S0182</t>
+  </si>
+  <si>
+    <t>S0183</t>
+  </si>
+  <si>
+    <t>Angra Mainyu</t>
+  </si>
+  <si>
+    <t>angra-mainyu</t>
+  </si>
+  <si>
+    <t>Mysterious Heroine XX</t>
+  </si>
+  <si>
+    <t>Edmond Dantès</t>
+  </si>
+  <si>
+    <t>edmond-dantes</t>
+  </si>
+  <si>
+    <t>Antonio Salieri</t>
+  </si>
+  <si>
+    <t>antonio-salieri</t>
+  </si>
+  <si>
+    <t>Jeanne d'Arc (Alter)</t>
+  </si>
+  <si>
+    <t>jeanne-darc-alter</t>
+  </si>
+  <si>
+    <t>Hessian Lobo</t>
+  </si>
+  <si>
+    <t>hessian-lobo</t>
+  </si>
+  <si>
+    <t>Gorgon</t>
+  </si>
+  <si>
+    <t>gorgon</t>
+  </si>
+  <si>
+    <t>Jeanne d'Arc</t>
+  </si>
+  <si>
+    <t>jeanne-darc</t>
+  </si>
+  <si>
+    <t>Ruler</t>
+  </si>
+  <si>
+    <t>Amakusa Shirou Tokisada</t>
+  </si>
+  <si>
+    <t>amakusa-shirou-tokisada</t>
+  </si>
+  <si>
+    <t>Sherlock Holmes</t>
+  </si>
+  <si>
+    <t>sherlock-holmes</t>
+  </si>
+  <si>
+    <t>Astraea</t>
+  </si>
+  <si>
+    <t>astraea</t>
+  </si>
+  <si>
+    <t>Oberon Vortigern</t>
+  </si>
+  <si>
+    <t>oberon-vortigern</t>
+  </si>
+  <si>
+    <t>Morgan le Fay</t>
+  </si>
+  <si>
+    <t>morgan-le-fay</t>
+  </si>
+  <si>
+    <t>Amor</t>
+  </si>
+  <si>
+    <t>amor</t>
+  </si>
+  <si>
+    <t>Himiko</t>
+  </si>
+  <si>
+    <t>himiko</t>
+  </si>
+  <si>
+    <t>B.B.</t>
+  </si>
+  <si>
+    <t>bb</t>
+  </si>
+  <si>
+    <t>Abigail Williams</t>
+  </si>
+  <si>
+    <t>abigail-williams</t>
+  </si>
+  <si>
+    <t>Foreigner</t>
+  </si>
+  <si>
+    <t>Katsushika Hokusai &amp; Oui</t>
+  </si>
+  <si>
+    <t>hokusai</t>
+  </si>
+  <si>
+    <t>Voyager</t>
+  </si>
+  <si>
+    <t>Clytie van Gogh</t>
+  </si>
+  <si>
+    <t>clytie-van-gogh</t>
+  </si>
+  <si>
+    <t>voyager</t>
+  </si>
+  <si>
+    <t>mysterious-heroine-xx</t>
+  </si>
+  <si>
+    <t>Avenger Class,Avenger Class,Avenger Class</t>
+  </si>
+  <si>
+    <t>Avenger Class,Avenger Class,Avenger Class,Luck,Luck,Luck</t>
+  </si>
+  <si>
+    <t>Avenger Class,Avenger Class,Avenger Class,Avenger Class,Preparation,Preparation</t>
+  </si>
+  <si>
+    <t>2,3,3,4,4,4</t>
+  </si>
+  <si>
+    <t>Surveil,Avenger Class,Avenger Class</t>
+  </si>
+  <si>
+    <t>Luck,Luck,Luck,Luck,Surveil,Surveil</t>
+  </si>
+  <si>
+    <t>Surveil,Preparation,Luck,Luck,Luck</t>
+  </si>
+  <si>
+    <t>Luck,Luck,Luck,Surveil,Preparation</t>
+  </si>
+  <si>
+    <t>Luck,Luck,Preparation,Preparation</t>
+  </si>
+  <si>
+    <t>2,2,5</t>
+  </si>
+  <si>
+    <t>Luck,Preparation,Moon Cancer,Moon Cancer</t>
+  </si>
+  <si>
+    <t>Foreigner Class,Foreigner Class,Surveil,Surveil</t>
+  </si>
+  <si>
+    <t>Preparation,Foreigner Class,Foreigner Class</t>
+  </si>
+  <si>
+    <t>Infinite Remains</t>
+  </si>
+  <si>
+    <t>Tawrich &amp; Zarich</t>
+  </si>
+  <si>
+    <t>Empathy</t>
+  </si>
+  <si>
+    <t>Enfer Château d'If</t>
+  </si>
+  <si>
+    <t>Attendre, Espérer</t>
+  </si>
+  <si>
+    <t>King of the Cavern</t>
+  </si>
+  <si>
+    <t>Misericordia</t>
+  </si>
+  <si>
+    <t>Wildfire</t>
+  </si>
+  <si>
+    <t>Grondement de Haine</t>
+  </si>
+  <si>
+    <t>Dragon Witch</t>
+  </si>
+  <si>
+    <t>Frostes Henker</t>
+  </si>
+  <si>
+    <t>Ghastly Howl</t>
+  </si>
+  <si>
+    <t>Pandemonium Cetus</t>
+  </si>
+  <si>
+    <t>Demonic Mutation</t>
+  </si>
+  <si>
+    <t>La Pucelle</t>
+  </si>
+  <si>
+    <t>Luminosité Eternelle</t>
+  </si>
+  <si>
+    <t>Ruler Class</t>
+  </si>
+  <si>
+    <t>Big Crunch</t>
+  </si>
+  <si>
+    <t>Thaumaturgy</t>
+  </si>
+  <si>
+    <t>Elementary, My Dear</t>
+  </si>
+  <si>
+    <t>The Empty House</t>
+  </si>
+  <si>
+    <t>Retroduction</t>
+  </si>
+  <si>
+    <t>Custos Morum</t>
+  </si>
+  <si>
+    <t>Et Iam Virgo Redit</t>
+  </si>
+  <si>
+    <t>Edictum Astrorum</t>
+  </si>
+  <si>
+    <t>Lie Like Vortigern</t>
+  </si>
+  <si>
+    <t>Infinity Mirror</t>
+  </si>
+  <si>
+    <t>Golden Arrow</t>
+  </si>
+  <si>
+    <t>Calling Agape</t>
+  </si>
+  <si>
+    <t>Oracle of Light</t>
+  </si>
+  <si>
+    <t>Kidou Arts</t>
+  </si>
+  <si>
+    <t>Eternal Mirror</t>
+  </si>
+  <si>
+    <t>Cursed Cutting Crater</t>
+  </si>
+  <si>
+    <t>B.B. Slots</t>
+  </si>
+  <si>
+    <t>Root Access</t>
+  </si>
+  <si>
+    <t>Witching Hour</t>
+  </si>
+  <si>
+    <t>Witch Trial</t>
+  </si>
+  <si>
+    <t>Gate to Nowhere</t>
+  </si>
+  <si>
+    <t>The Great Wave</t>
+  </si>
+  <si>
+    <t>Colors of the World</t>
+  </si>
+  <si>
+    <t>Colors of Beyond</t>
+  </si>
+  <si>
+    <t>Pale Blue Dot</t>
+  </si>
+  <si>
+    <t>Message of Peace</t>
+  </si>
+  <si>
+    <t>Message of Hope</t>
+  </si>
+  <si>
+    <t>De Sterrennacht</t>
+  </si>
+  <si>
+    <t>Sea of Monsters</t>
+  </si>
+  <si>
+    <t>Composite Soul</t>
+  </si>
+  <si>
+    <t>Cosmo Reactor</t>
+  </si>
+  <si>
+    <t>Holy Armor Avalon</t>
+  </si>
+  <si>
+    <t>Rhongomyniad LR</t>
   </si>
 </sst>
 </file>
@@ -3854,7 +4214,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E33D7ECC-1EAA-4A40-B4DA-A93E54CBC8B5}">
-  <dimension ref="A1:K170"/>
+  <dimension ref="A1:K185"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="2" max="3" width="22" customWidth="1"/>
@@ -8849,26 +9209,158 @@
       <c r="A163" t="s">
         <v>1010</v>
       </c>
+      <c r="B163" t="s">
+        <v>1156</v>
+      </c>
+      <c r="C163" t="s">
+        <v>1157</v>
+      </c>
+      <c r="D163" t="s">
+        <v>26</v>
+      </c>
+      <c r="E163" t="s">
+        <v>33</v>
+      </c>
+      <c r="G163" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="H163" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I163" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J163" s="2" t="s">
+        <v>1198</v>
+      </c>
+      <c r="K163" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="164" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A164" t="s">
         <v>1011</v>
       </c>
+      <c r="B164" t="s">
+        <v>1159</v>
+      </c>
+      <c r="C164" t="s">
+        <v>1160</v>
+      </c>
+      <c r="D164" t="s">
+        <v>26</v>
+      </c>
+      <c r="E164" t="s">
+        <v>40</v>
+      </c>
+      <c r="G164" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="H164" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="I164" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="J164" s="2" t="s">
+        <v>1199</v>
+      </c>
+      <c r="K164" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="165" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A165" t="s">
         <v>1012</v>
       </c>
+      <c r="B165" t="s">
+        <v>1161</v>
+      </c>
+      <c r="C165" t="s">
+        <v>1162</v>
+      </c>
+      <c r="D165" t="s">
+        <v>26</v>
+      </c>
+      <c r="E165" t="s">
+        <v>8</v>
+      </c>
+      <c r="G165" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="H165" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="J165" s="2" t="s">
+        <v>1200</v>
+      </c>
+      <c r="K165" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="166" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A166" t="s">
         <v>1013</v>
       </c>
+      <c r="B166" t="s">
+        <v>1163</v>
+      </c>
+      <c r="C166" t="s">
+        <v>1164</v>
+      </c>
+      <c r="D166" t="s">
+        <v>26</v>
+      </c>
+      <c r="E166" t="s">
+        <v>8</v>
+      </c>
+      <c r="G166" s="2" t="s">
+        <v>567</v>
+      </c>
+      <c r="H166" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I166" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="J166" s="2" t="s">
+        <v>1198</v>
+      </c>
+      <c r="K166" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="167" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A167" t="s">
         <v>1014</v>
       </c>
+      <c r="B167" t="s">
+        <v>1165</v>
+      </c>
+      <c r="C167" t="s">
+        <v>1166</v>
+      </c>
+      <c r="D167" t="s">
+        <v>26</v>
+      </c>
+      <c r="E167" t="s">
+        <v>89</v>
+      </c>
+      <c r="G167" s="2" t="s">
+        <v>948</v>
+      </c>
+      <c r="H167" s="2" t="s">
+        <v>1201</v>
+      </c>
+      <c r="I167" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="J167" s="2" t="s">
+        <v>1202</v>
+      </c>
+      <c r="K167" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="168" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A168" t="s">
@@ -8901,31 +9393,31 @@
     </row>
     <row r="169" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A169" t="s">
-        <v>29</v>
+        <v>1141</v>
       </c>
       <c r="B169" t="s">
-        <v>30</v>
+        <v>1167</v>
       </c>
       <c r="C169" t="s">
-        <v>31</v>
+        <v>1168</v>
       </c>
       <c r="D169" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="E169" t="s">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="G169" s="2" t="s">
+        <v>567</v>
+      </c>
+      <c r="H169" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="H169" s="2" t="s">
-        <v>81</v>
-      </c>
       <c r="I169" s="2" t="s">
-        <v>34</v>
+        <v>196</v>
       </c>
       <c r="J169" s="2" t="s">
-        <v>35</v>
+        <v>1198</v>
       </c>
       <c r="K169" t="b">
         <v>0</v>
@@ -8933,30 +9425,501 @@
     </row>
     <row r="170" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A170" t="s">
-        <v>36</v>
+        <v>1142</v>
       </c>
       <c r="B170" t="s">
-        <v>37</v>
+        <v>1169</v>
       </c>
       <c r="C170" t="s">
-        <v>38</v>
+        <v>1170</v>
       </c>
       <c r="D170" t="s">
-        <v>39</v>
+        <v>1171</v>
       </c>
       <c r="E170" t="s">
         <v>40</v>
       </c>
       <c r="G170" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="H170" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I170" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="J170" s="2" t="s">
+        <v>1203</v>
+      </c>
+      <c r="K170" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="171" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A171" t="s">
+        <v>1143</v>
+      </c>
+      <c r="B171" t="s">
+        <v>1172</v>
+      </c>
+      <c r="C171" t="s">
+        <v>1173</v>
+      </c>
+      <c r="D171" t="s">
+        <v>1171</v>
+      </c>
+      <c r="E171" t="s">
+        <v>40</v>
+      </c>
+      <c r="G171" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H171" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="I171" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="J171" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="K171" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="172" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A172" t="s">
+        <v>1144</v>
+      </c>
+      <c r="B172" t="s">
+        <v>1174</v>
+      </c>
+      <c r="C172" t="s">
+        <v>1175</v>
+      </c>
+      <c r="D172" t="s">
+        <v>1171</v>
+      </c>
+      <c r="E172" t="s">
+        <v>89</v>
+      </c>
+      <c r="H172" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="I172" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="J172" s="2" t="s">
+        <v>1204</v>
+      </c>
+      <c r="K172" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="173" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A173" t="s">
+        <v>1145</v>
+      </c>
+      <c r="B173" t="s">
+        <v>1176</v>
+      </c>
+      <c r="C173" t="s">
+        <v>1177</v>
+      </c>
+      <c r="D173" t="s">
+        <v>1171</v>
+      </c>
+      <c r="E173" t="s">
+        <v>40</v>
+      </c>
+      <c r="G173" s="2" t="s">
+        <v>567</v>
+      </c>
+      <c r="H173" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I173" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="J173" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="K173" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="174" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A174" t="s">
+        <v>1146</v>
+      </c>
+      <c r="B174" t="s">
+        <v>1178</v>
+      </c>
+      <c r="C174" t="s">
+        <v>1179</v>
+      </c>
+      <c r="D174" t="s">
+        <v>646</v>
+      </c>
+      <c r="E174" t="s">
+        <v>8</v>
+      </c>
+      <c r="G174" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H174" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="I174" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="J174" s="2" t="s">
+        <v>1205</v>
+      </c>
+      <c r="K174" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="175" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A175" t="s">
+        <v>1147</v>
+      </c>
+      <c r="B175" t="s">
+        <v>1180</v>
+      </c>
+      <c r="C175" t="s">
+        <v>1181</v>
+      </c>
+      <c r="D175" t="s">
+        <v>1171</v>
+      </c>
+      <c r="E175" t="s">
+        <v>99</v>
+      </c>
+      <c r="G175" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H175" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="I175" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="J175" s="2" t="s">
+        <v>1206</v>
+      </c>
+      <c r="K175" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="176" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A176" t="s">
+        <v>1148</v>
+      </c>
+      <c r="B176" t="s">
+        <v>1182</v>
+      </c>
+      <c r="C176" t="s">
+        <v>1183</v>
+      </c>
+      <c r="D176" t="s">
+        <v>1171</v>
+      </c>
+      <c r="E176" t="s">
+        <v>99</v>
+      </c>
+      <c r="G176" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H176" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="I176" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="J176" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="K176" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="177" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A177" t="s">
+        <v>1149</v>
+      </c>
+      <c r="B177" t="s">
+        <v>1184</v>
+      </c>
+      <c r="C177" t="s">
+        <v>1185</v>
+      </c>
+      <c r="D177" t="s">
+        <v>1171</v>
+      </c>
+      <c r="E177" t="s">
+        <v>40</v>
+      </c>
+      <c r="G177" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="H177" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I177" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="J177" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="K177" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="178" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A178" t="s">
+        <v>1150</v>
+      </c>
+      <c r="B178" t="s">
+        <v>1186</v>
+      </c>
+      <c r="C178" t="s">
+        <v>1187</v>
+      </c>
+      <c r="D178" t="s">
+        <v>32</v>
+      </c>
+      <c r="E178" t="s">
+        <v>99</v>
+      </c>
+      <c r="G178" s="2" t="s">
+        <v>1207</v>
+      </c>
+      <c r="H178" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I178" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="J178" s="2" t="s">
+        <v>1208</v>
+      </c>
+      <c r="K178" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="179" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A179" t="s">
+        <v>29</v>
+      </c>
+      <c r="B179" t="s">
+        <v>30</v>
+      </c>
+      <c r="C179" t="s">
+        <v>31</v>
+      </c>
+      <c r="D179" t="s">
+        <v>32</v>
+      </c>
+      <c r="E179" t="s">
+        <v>33</v>
+      </c>
+      <c r="G179" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H179" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="I179" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="J179" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="K179" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="180" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A180" t="s">
+        <v>1151</v>
+      </c>
+      <c r="B180" t="s">
+        <v>1188</v>
+      </c>
+      <c r="C180" t="s">
+        <v>1189</v>
+      </c>
+      <c r="D180" t="s">
+        <v>1190</v>
+      </c>
+      <c r="E180" t="s">
+        <v>8</v>
+      </c>
+      <c r="H180" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="I180" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="J180" s="2" t="s">
+        <v>1209</v>
+      </c>
+      <c r="K180" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="181" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A181" t="s">
+        <v>1152</v>
+      </c>
+      <c r="B181" t="s">
+        <v>1191</v>
+      </c>
+      <c r="C181" t="s">
+        <v>1192</v>
+      </c>
+      <c r="D181" t="s">
+        <v>1190</v>
+      </c>
+      <c r="E181" t="s">
+        <v>89</v>
+      </c>
+      <c r="G181" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="H181" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="I181" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="J181" s="2" t="s">
+        <v>1210</v>
+      </c>
+      <c r="K181" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="182" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A182" t="s">
+        <v>1153</v>
+      </c>
+      <c r="B182" t="s">
+        <v>1193</v>
+      </c>
+      <c r="C182" t="s">
+        <v>1196</v>
+      </c>
+      <c r="D182" t="s">
+        <v>1190</v>
+      </c>
+      <c r="E182" t="s">
+        <v>33</v>
+      </c>
+      <c r="H182" s="2" t="s">
+        <v>1201</v>
+      </c>
+      <c r="I182" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="J182" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="K182" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="183" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A183" t="s">
+        <v>1154</v>
+      </c>
+      <c r="B183" t="s">
+        <v>1194</v>
+      </c>
+      <c r="C183" t="s">
+        <v>1195</v>
+      </c>
+      <c r="D183" t="s">
+        <v>1190</v>
+      </c>
+      <c r="E183" t="s">
+        <v>89</v>
+      </c>
+      <c r="G183" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="H183" s="2" t="s">
+        <v>443</v>
+      </c>
+      <c r="I183" s="2" t="s">
+        <v>475</v>
+      </c>
+      <c r="J183" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="K183" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="184" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A184" t="s">
+        <v>1155</v>
+      </c>
+      <c r="B184" t="s">
+        <v>1158</v>
+      </c>
+      <c r="C184" t="s">
+        <v>1197</v>
+      </c>
+      <c r="D184" t="s">
+        <v>1190</v>
+      </c>
+      <c r="E184" t="s">
+        <v>8</v>
+      </c>
+      <c r="G184" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="H184" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="I184" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J184" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="K184" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="185" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A185" t="s">
+        <v>36</v>
+      </c>
+      <c r="B185" t="s">
+        <v>37</v>
+      </c>
+      <c r="C185" t="s">
+        <v>38</v>
+      </c>
+      <c r="D185" t="s">
+        <v>39</v>
+      </c>
+      <c r="E185" t="s">
+        <v>40</v>
+      </c>
+      <c r="G185" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="H170" s="2" t="s">
+      <c r="H185" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="J170" s="2" t="s">
+      <c r="J185" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="K170" t="b">
+      <c r="K185" t="b">
         <v>1</v>
       </c>
     </row>
@@ -8964,7 +9927,7 @@
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="H2 I6:I7 I10 I12 H14 I18 I22 I24 I27 G34 I40 I42 I45 I52 I62 I72 H79 I80 I84 I88 I90 G91 H100 I119 I124 I121:I123 G130:I139 G142:I148" numberStoredAsText="1"/>
+    <ignoredError sqref="H2 I6:I7 I10 I12 H14 I18 I22 I24 I27 G34 I40 I42 I45 I52 I62 I72 H79 I80 I84 I88 I90 G91 H100 I119 I124 I121:I123 G130:I139 G142:I148 G164:I186" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -9401,7 +10364,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84E3BB0D-5578-4069-B1C9-C3864EB2A429}">
-  <dimension ref="A1:F508"/>
+  <dimension ref="A1:F553"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="2" max="2" width="26.33203125" customWidth="1"/>
@@ -17646,76 +18609,256 @@
       <c r="A485" t="s">
         <v>1010</v>
       </c>
+      <c r="B485" t="s">
+        <v>1156</v>
+      </c>
+      <c r="C485">
+        <v>1</v>
+      </c>
+      <c r="D485" t="b">
+        <v>0</v>
+      </c>
+      <c r="E485" t="s">
+        <v>1211</v>
+      </c>
     </row>
     <row r="486" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A486" t="s">
         <v>1010</v>
       </c>
+      <c r="B486" t="s">
+        <v>1156</v>
+      </c>
+      <c r="C486">
+        <v>2</v>
+      </c>
+      <c r="D486" t="b">
+        <v>0</v>
+      </c>
+      <c r="E486" t="s">
+        <v>1212</v>
+      </c>
     </row>
     <row r="487" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A487" t="s">
         <v>1010</v>
       </c>
+      <c r="B487" t="s">
+        <v>1156</v>
+      </c>
+      <c r="C487">
+        <v>3</v>
+      </c>
+      <c r="D487" t="b">
+        <v>0</v>
+      </c>
+      <c r="E487" t="s">
+        <v>1213</v>
+      </c>
     </row>
     <row r="488" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A488" t="s">
         <v>1011</v>
       </c>
+      <c r="B488" t="s">
+        <v>1159</v>
+      </c>
+      <c r="C488">
+        <v>1</v>
+      </c>
+      <c r="D488" t="b">
+        <v>0</v>
+      </c>
+      <c r="E488" t="s">
+        <v>1214</v>
+      </c>
     </row>
     <row r="489" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A489" t="s">
         <v>1011</v>
       </c>
+      <c r="B489" t="s">
+        <v>1159</v>
+      </c>
+      <c r="C489">
+        <v>2</v>
+      </c>
+      <c r="D489" t="b">
+        <v>0</v>
+      </c>
+      <c r="E489" t="s">
+        <v>1215</v>
+      </c>
     </row>
     <row r="490" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A490" t="s">
         <v>1011</v>
       </c>
+      <c r="B490" t="s">
+        <v>1159</v>
+      </c>
+      <c r="C490">
+        <v>3</v>
+      </c>
+      <c r="D490" t="b">
+        <v>0</v>
+      </c>
+      <c r="E490" t="s">
+        <v>1216</v>
+      </c>
     </row>
     <row r="491" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A491" t="s">
         <v>1012</v>
       </c>
+      <c r="B491" t="s">
+        <v>1161</v>
+      </c>
+      <c r="C491">
+        <v>1</v>
+      </c>
+      <c r="D491" t="b">
+        <v>0</v>
+      </c>
+      <c r="E491" t="s">
+        <v>1217</v>
+      </c>
     </row>
     <row r="492" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A492" t="s">
         <v>1012</v>
       </c>
+      <c r="B492" t="s">
+        <v>1161</v>
+      </c>
+      <c r="C492">
+        <v>2</v>
+      </c>
+      <c r="D492" t="b">
+        <v>0</v>
+      </c>
+      <c r="E492" t="s">
+        <v>1218</v>
+      </c>
     </row>
     <row r="493" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A493" t="s">
         <v>1012</v>
       </c>
+      <c r="B493" t="s">
+        <v>1161</v>
+      </c>
+      <c r="C493">
+        <v>3</v>
+      </c>
+      <c r="D493" t="b">
+        <v>0</v>
+      </c>
+      <c r="E493" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="494" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A494" t="s">
         <v>1013</v>
       </c>
+      <c r="B494" t="s">
+        <v>1163</v>
+      </c>
+      <c r="C494">
+        <v>1</v>
+      </c>
+      <c r="D494" t="b">
+        <v>0</v>
+      </c>
+      <c r="E494" t="s">
+        <v>1219</v>
+      </c>
     </row>
     <row r="495" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A495" t="s">
         <v>1013</v>
       </c>
+      <c r="B495" t="s">
+        <v>1163</v>
+      </c>
+      <c r="C495">
+        <v>2</v>
+      </c>
+      <c r="D495" t="b">
+        <v>0</v>
+      </c>
+      <c r="E495" t="s">
+        <v>1220</v>
+      </c>
     </row>
     <row r="496" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A496" t="s">
         <v>1013</v>
       </c>
+      <c r="B496" t="s">
+        <v>1163</v>
+      </c>
+      <c r="C496">
+        <v>3</v>
+      </c>
+      <c r="D496" t="b">
+        <v>0</v>
+      </c>
+      <c r="E496" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="497" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A497" t="s">
         <v>1014</v>
       </c>
+      <c r="B497" t="s">
+        <v>1165</v>
+      </c>
+      <c r="C497">
+        <v>1</v>
+      </c>
+      <c r="D497" t="b">
+        <v>0</v>
+      </c>
+      <c r="E497" t="s">
+        <v>1221</v>
+      </c>
     </row>
     <row r="498" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A498" t="s">
         <v>1014</v>
       </c>
+      <c r="B498" t="s">
+        <v>1165</v>
+      </c>
+      <c r="C498">
+        <v>2</v>
+      </c>
+      <c r="D498" t="b">
+        <v>0</v>
+      </c>
+      <c r="E498" t="s">
+        <v>1222</v>
+      </c>
     </row>
     <row r="499" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A499" t="s">
         <v>1014</v>
       </c>
+      <c r="B499" t="s">
+        <v>1165</v>
+      </c>
+      <c r="C499">
+        <v>3</v>
+      </c>
+      <c r="D499" t="b">
+        <v>0</v>
+      </c>
+      <c r="E499" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="500" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A500" t="s">
@@ -17770,10 +18913,10 @@
     </row>
     <row r="503" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A503" t="s">
-        <v>29</v>
+        <v>1141</v>
       </c>
       <c r="B503" t="s">
-        <v>30</v>
+        <v>1167</v>
       </c>
       <c r="C503">
         <v>1</v>
@@ -17782,15 +18925,15 @@
         <v>0</v>
       </c>
       <c r="E503" t="s">
-        <v>64</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="504" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A504" t="s">
-        <v>29</v>
+        <v>1141</v>
       </c>
       <c r="B504" t="s">
-        <v>30</v>
+        <v>1167</v>
       </c>
       <c r="C504">
         <v>2</v>
@@ -17799,15 +18942,15 @@
         <v>0</v>
       </c>
       <c r="E504" t="s">
-        <v>65</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="505" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A505" t="s">
-        <v>29</v>
+        <v>1141</v>
       </c>
       <c r="B505" t="s">
-        <v>30</v>
+        <v>1167</v>
       </c>
       <c r="C505">
         <v>3</v>
@@ -17816,32 +18959,32 @@
         <v>0</v>
       </c>
       <c r="E505" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
     </row>
     <row r="506" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A506" t="s">
-        <v>36</v>
+        <v>1142</v>
       </c>
       <c r="B506" t="s">
-        <v>37</v>
+        <v>1169</v>
       </c>
       <c r="C506">
         <v>1</v>
       </c>
       <c r="D506" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E506" t="s">
-        <v>67</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="507" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A507" t="s">
-        <v>36</v>
+        <v>1142</v>
       </c>
       <c r="B507" t="s">
-        <v>37</v>
+        <v>1169</v>
       </c>
       <c r="C507">
         <v>2</v>
@@ -17850,15 +18993,15 @@
         <v>0</v>
       </c>
       <c r="E507" t="s">
-        <v>68</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="508" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A508" t="s">
-        <v>36</v>
+        <v>1142</v>
       </c>
       <c r="B508" t="s">
-        <v>37</v>
+        <v>1169</v>
       </c>
       <c r="C508">
         <v>3</v>
@@ -17867,6 +19010,771 @@
         <v>0</v>
       </c>
       <c r="E508" t="s">
+        <v>1226</v>
+      </c>
+    </row>
+    <row r="509" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A509" t="s">
+        <v>1143</v>
+      </c>
+      <c r="B509" t="s">
+        <v>1172</v>
+      </c>
+      <c r="C509">
+        <v>1</v>
+      </c>
+      <c r="D509" t="b">
+        <v>1</v>
+      </c>
+      <c r="E509" t="s">
+        <v>1227</v>
+      </c>
+    </row>
+    <row r="510" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A510" t="s">
+        <v>1143</v>
+      </c>
+      <c r="B510" t="s">
+        <v>1172</v>
+      </c>
+      <c r="C510">
+        <v>2</v>
+      </c>
+      <c r="D510" t="b">
+        <v>0</v>
+      </c>
+      <c r="E510" t="s">
+        <v>1228</v>
+      </c>
+    </row>
+    <row r="511" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A511" t="s">
+        <v>1143</v>
+      </c>
+      <c r="B511" t="s">
+        <v>1172</v>
+      </c>
+      <c r="C511">
+        <v>3</v>
+      </c>
+      <c r="D511" t="b">
+        <v>0</v>
+      </c>
+      <c r="E511" t="s">
+        <v>1229</v>
+      </c>
+    </row>
+    <row r="512" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A512" t="s">
+        <v>1144</v>
+      </c>
+      <c r="B512" t="s">
+        <v>1174</v>
+      </c>
+      <c r="C512">
+        <v>1</v>
+      </c>
+      <c r="D512" t="b">
+        <v>0</v>
+      </c>
+      <c r="E512" t="s">
+        <v>1230</v>
+      </c>
+    </row>
+    <row r="513" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A513" t="s">
+        <v>1144</v>
+      </c>
+      <c r="B513" t="s">
+        <v>1174</v>
+      </c>
+      <c r="C513">
+        <v>2</v>
+      </c>
+      <c r="D513" t="b">
+        <v>0</v>
+      </c>
+      <c r="E513" t="s">
+        <v>1231</v>
+      </c>
+    </row>
+    <row r="514" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A514" t="s">
+        <v>1144</v>
+      </c>
+      <c r="B514" t="s">
+        <v>1174</v>
+      </c>
+      <c r="C514">
+        <v>3</v>
+      </c>
+      <c r="D514" t="b">
+        <v>0</v>
+      </c>
+      <c r="E514" t="s">
+        <v>1232</v>
+      </c>
+    </row>
+    <row r="515" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A515" t="s">
+        <v>1145</v>
+      </c>
+      <c r="B515" t="s">
+        <v>1176</v>
+      </c>
+      <c r="C515">
+        <v>1</v>
+      </c>
+      <c r="D515" t="b">
+        <v>0</v>
+      </c>
+      <c r="E515" t="s">
+        <v>1233</v>
+      </c>
+    </row>
+    <row r="516" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A516" t="s">
+        <v>1145</v>
+      </c>
+      <c r="B516" t="s">
+        <v>1176</v>
+      </c>
+      <c r="C516">
+        <v>2</v>
+      </c>
+      <c r="D516" t="b">
+        <v>0</v>
+      </c>
+      <c r="E516" t="s">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="517" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A517" t="s">
+        <v>1145</v>
+      </c>
+      <c r="B517" t="s">
+        <v>1176</v>
+      </c>
+      <c r="C517">
+        <v>3</v>
+      </c>
+      <c r="D517" t="b">
+        <v>0</v>
+      </c>
+      <c r="E517" t="s">
+        <v>1235</v>
+      </c>
+    </row>
+    <row r="518" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A518" t="s">
+        <v>1146</v>
+      </c>
+      <c r="B518" t="s">
+        <v>1178</v>
+      </c>
+      <c r="C518">
+        <v>1</v>
+      </c>
+      <c r="D518" t="b">
+        <v>1</v>
+      </c>
+      <c r="E518" t="s">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="519" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A519" t="s">
+        <v>1146</v>
+      </c>
+      <c r="B519" t="s">
+        <v>1178</v>
+      </c>
+      <c r="C519">
+        <v>2</v>
+      </c>
+      <c r="D519" t="b">
+        <v>1</v>
+      </c>
+      <c r="E519" t="s">
+        <v>1227</v>
+      </c>
+    </row>
+    <row r="520" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A520" t="s">
+        <v>1146</v>
+      </c>
+      <c r="B520" t="s">
+        <v>1178</v>
+      </c>
+      <c r="C520">
+        <v>3</v>
+      </c>
+      <c r="D520" t="b">
+        <v>0</v>
+      </c>
+      <c r="E520" t="s">
+        <v>1236</v>
+      </c>
+    </row>
+    <row r="521" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A521" t="s">
+        <v>1147</v>
+      </c>
+      <c r="B521" t="s">
+        <v>1180</v>
+      </c>
+      <c r="C521">
+        <v>1</v>
+      </c>
+      <c r="D521" t="b">
+        <v>1</v>
+      </c>
+      <c r="E521" t="s">
+        <v>1227</v>
+      </c>
+    </row>
+    <row r="522" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A522" t="s">
+        <v>1147</v>
+      </c>
+      <c r="B522" t="s">
+        <v>1180</v>
+      </c>
+      <c r="C522">
+        <v>2</v>
+      </c>
+      <c r="D522" t="b">
+        <v>0</v>
+      </c>
+      <c r="E522" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="523" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A523" t="s">
+        <v>1147</v>
+      </c>
+      <c r="B523" t="s">
+        <v>1180</v>
+      </c>
+      <c r="C523">
+        <v>3</v>
+      </c>
+      <c r="D523" t="b">
+        <v>0</v>
+      </c>
+      <c r="E523" t="s">
+        <v>1237</v>
+      </c>
+    </row>
+    <row r="524" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A524" t="s">
+        <v>1148</v>
+      </c>
+      <c r="B524" t="s">
+        <v>1182</v>
+      </c>
+      <c r="C524">
+        <v>1</v>
+      </c>
+      <c r="D524" t="b">
+        <v>1</v>
+      </c>
+      <c r="E524" t="s">
+        <v>1227</v>
+      </c>
+    </row>
+    <row r="525" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A525" t="s">
+        <v>1148</v>
+      </c>
+      <c r="B525" t="s">
+        <v>1182</v>
+      </c>
+      <c r="C525">
+        <v>2</v>
+      </c>
+      <c r="D525" t="b">
+        <v>0</v>
+      </c>
+      <c r="E525" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="526" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A526" t="s">
+        <v>1148</v>
+      </c>
+      <c r="B526" t="s">
+        <v>1182</v>
+      </c>
+      <c r="C526">
+        <v>3</v>
+      </c>
+      <c r="D526" t="b">
+        <v>0</v>
+      </c>
+      <c r="E526" t="s">
+        <v>1239</v>
+      </c>
+    </row>
+    <row r="527" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A527" t="s">
+        <v>1149</v>
+      </c>
+      <c r="B527" t="s">
+        <v>1184</v>
+      </c>
+      <c r="C527">
+        <v>1</v>
+      </c>
+      <c r="D527" t="b">
+        <v>0</v>
+      </c>
+      <c r="E527" t="s">
+        <v>1240</v>
+      </c>
+    </row>
+    <row r="528" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A528" t="s">
+        <v>1149</v>
+      </c>
+      <c r="B528" t="s">
+        <v>1184</v>
+      </c>
+      <c r="C528">
+        <v>2</v>
+      </c>
+      <c r="D528" t="b">
+        <v>0</v>
+      </c>
+      <c r="E528" t="s">
+        <v>1241</v>
+      </c>
+    </row>
+    <row r="529" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A529" t="s">
+        <v>1149</v>
+      </c>
+      <c r="B529" t="s">
+        <v>1184</v>
+      </c>
+      <c r="C529">
+        <v>3</v>
+      </c>
+      <c r="D529" t="b">
+        <v>0</v>
+      </c>
+      <c r="E529" t="s">
+        <v>1242</v>
+      </c>
+    </row>
+    <row r="530" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A530" t="s">
+        <v>1150</v>
+      </c>
+      <c r="B530" t="s">
+        <v>1186</v>
+      </c>
+      <c r="C530">
+        <v>1</v>
+      </c>
+      <c r="D530" t="b">
+        <v>0</v>
+      </c>
+      <c r="E530" t="s">
+        <v>1243</v>
+      </c>
+    </row>
+    <row r="531" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A531" t="s">
+        <v>1150</v>
+      </c>
+      <c r="B531" t="s">
+        <v>1186</v>
+      </c>
+      <c r="C531">
+        <v>2</v>
+      </c>
+      <c r="D531" t="b">
+        <v>0</v>
+      </c>
+      <c r="E531" t="s">
+        <v>1244</v>
+      </c>
+    </row>
+    <row r="532" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A532" t="s">
+        <v>1150</v>
+      </c>
+      <c r="B532" t="s">
+        <v>1186</v>
+      </c>
+      <c r="C532">
+        <v>3</v>
+      </c>
+      <c r="D532" t="b">
+        <v>0</v>
+      </c>
+      <c r="E532" t="s">
+        <v>1245</v>
+      </c>
+    </row>
+    <row r="533" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A533" t="s">
+        <v>29</v>
+      </c>
+      <c r="B533" t="s">
+        <v>30</v>
+      </c>
+      <c r="C533">
+        <v>1</v>
+      </c>
+      <c r="D533" t="b">
+        <v>0</v>
+      </c>
+      <c r="E533" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="534" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A534" t="s">
+        <v>29</v>
+      </c>
+      <c r="B534" t="s">
+        <v>30</v>
+      </c>
+      <c r="C534">
+        <v>2</v>
+      </c>
+      <c r="D534" t="b">
+        <v>0</v>
+      </c>
+      <c r="E534" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="535" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A535" t="s">
+        <v>29</v>
+      </c>
+      <c r="B535" t="s">
+        <v>30</v>
+      </c>
+      <c r="C535">
+        <v>3</v>
+      </c>
+      <c r="D535" t="b">
+        <v>0</v>
+      </c>
+      <c r="E535" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="536" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A536" t="s">
+        <v>1151</v>
+      </c>
+      <c r="B536" t="s">
+        <v>1188</v>
+      </c>
+      <c r="C536">
+        <v>1</v>
+      </c>
+      <c r="D536" t="b">
+        <v>0</v>
+      </c>
+      <c r="E536" t="s">
+        <v>1246</v>
+      </c>
+    </row>
+    <row r="537" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A537" t="s">
+        <v>1151</v>
+      </c>
+      <c r="B537" t="s">
+        <v>1188</v>
+      </c>
+      <c r="C537">
+        <v>2</v>
+      </c>
+      <c r="D537" t="b">
+        <v>0</v>
+      </c>
+      <c r="E537" t="s">
+        <v>1247</v>
+      </c>
+    </row>
+    <row r="538" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A538" t="s">
+        <v>1151</v>
+      </c>
+      <c r="B538" t="s">
+        <v>1188</v>
+      </c>
+      <c r="C538">
+        <v>3</v>
+      </c>
+      <c r="D538" t="b">
+        <v>0</v>
+      </c>
+      <c r="E538" t="s">
+        <v>1248</v>
+      </c>
+    </row>
+    <row r="539" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A539" t="s">
+        <v>1152</v>
+      </c>
+      <c r="B539" t="s">
+        <v>1191</v>
+      </c>
+      <c r="C539">
+        <v>1</v>
+      </c>
+      <c r="D539" t="b">
+        <v>0</v>
+      </c>
+      <c r="E539" t="s">
+        <v>1249</v>
+      </c>
+    </row>
+    <row r="540" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A540" t="s">
+        <v>1152</v>
+      </c>
+      <c r="B540" t="s">
+        <v>1191</v>
+      </c>
+      <c r="C540">
+        <v>2</v>
+      </c>
+      <c r="D540" t="b">
+        <v>0</v>
+      </c>
+      <c r="E540" t="s">
+        <v>1250</v>
+      </c>
+    </row>
+    <row r="541" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A541" t="s">
+        <v>1152</v>
+      </c>
+      <c r="B541" t="s">
+        <v>1191</v>
+      </c>
+      <c r="C541">
+        <v>3</v>
+      </c>
+      <c r="D541" t="b">
+        <v>0</v>
+      </c>
+      <c r="E541" t="s">
+        <v>1251</v>
+      </c>
+    </row>
+    <row r="542" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A542" t="s">
+        <v>1153</v>
+      </c>
+      <c r="B542" t="s">
+        <v>1193</v>
+      </c>
+      <c r="C542">
+        <v>1</v>
+      </c>
+      <c r="D542" t="b">
+        <v>0</v>
+      </c>
+      <c r="E542" t="s">
+        <v>1252</v>
+      </c>
+    </row>
+    <row r="543" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A543" t="s">
+        <v>1153</v>
+      </c>
+      <c r="B543" t="s">
+        <v>1193</v>
+      </c>
+      <c r="C543">
+        <v>2</v>
+      </c>
+      <c r="D543" t="b">
+        <v>0</v>
+      </c>
+      <c r="E543" t="s">
+        <v>1253</v>
+      </c>
+    </row>
+    <row r="544" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A544" t="s">
+        <v>1153</v>
+      </c>
+      <c r="B544" t="s">
+        <v>1193</v>
+      </c>
+      <c r="C544">
+        <v>3</v>
+      </c>
+      <c r="D544" t="b">
+        <v>0</v>
+      </c>
+      <c r="E544" t="s">
+        <v>1254</v>
+      </c>
+    </row>
+    <row r="545" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A545" t="s">
+        <v>1154</v>
+      </c>
+      <c r="B545" t="s">
+        <v>1194</v>
+      </c>
+      <c r="C545">
+        <v>1</v>
+      </c>
+      <c r="D545" t="b">
+        <v>0</v>
+      </c>
+      <c r="E545" t="s">
+        <v>1255</v>
+      </c>
+    </row>
+    <row r="546" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A546" t="s">
+        <v>1154</v>
+      </c>
+      <c r="B546" t="s">
+        <v>1194</v>
+      </c>
+      <c r="C546">
+        <v>2</v>
+      </c>
+      <c r="D546" t="b">
+        <v>0</v>
+      </c>
+      <c r="E546" t="s">
+        <v>1256</v>
+      </c>
+    </row>
+    <row r="547" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A547" t="s">
+        <v>1154</v>
+      </c>
+      <c r="B547" t="s">
+        <v>1194</v>
+      </c>
+      <c r="C547">
+        <v>3</v>
+      </c>
+      <c r="D547" t="b">
+        <v>0</v>
+      </c>
+      <c r="E547" t="s">
+        <v>1257</v>
+      </c>
+    </row>
+    <row r="548" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A548" t="s">
+        <v>1155</v>
+      </c>
+      <c r="B548" t="s">
+        <v>1158</v>
+      </c>
+      <c r="C548">
+        <v>1</v>
+      </c>
+      <c r="D548" t="b">
+        <v>0</v>
+      </c>
+      <c r="E548" t="s">
+        <v>1258</v>
+      </c>
+    </row>
+    <row r="549" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A549" t="s">
+        <v>1155</v>
+      </c>
+      <c r="B549" t="s">
+        <v>1158</v>
+      </c>
+      <c r="C549">
+        <v>2</v>
+      </c>
+      <c r="D549" t="b">
+        <v>0</v>
+      </c>
+      <c r="E549" t="s">
+        <v>1259</v>
+      </c>
+    </row>
+    <row r="550" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A550" t="s">
+        <v>1155</v>
+      </c>
+      <c r="B550" t="s">
+        <v>1158</v>
+      </c>
+      <c r="C550">
+        <v>3</v>
+      </c>
+      <c r="D550" t="b">
+        <v>0</v>
+      </c>
+      <c r="E550" t="s">
+        <v>1260</v>
+      </c>
+    </row>
+    <row r="551" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A551" t="s">
+        <v>36</v>
+      </c>
+      <c r="B551" t="s">
+        <v>37</v>
+      </c>
+      <c r="C551">
+        <v>1</v>
+      </c>
+      <c r="D551" t="b">
+        <v>0</v>
+      </c>
+      <c r="E551" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="552" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A552" t="s">
+        <v>36</v>
+      </c>
+      <c r="B552" t="s">
+        <v>37</v>
+      </c>
+      <c r="C552">
+        <v>2</v>
+      </c>
+      <c r="D552" t="b">
+        <v>0</v>
+      </c>
+      <c r="E552" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="553" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A553" t="s">
+        <v>36</v>
+      </c>
+      <c r="B553" t="s">
+        <v>37</v>
+      </c>
+      <c r="C553">
+        <v>3</v>
+      </c>
+      <c r="D553" t="b">
+        <v>0</v>
+      </c>
+      <c r="E553" t="s">
         <v>69</v>
       </c>
     </row>

--- a/data/Fate-Spreadsheet.xlsx
+++ b/data/Fate-Spreadsheet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pixel\Documents\Projects\Fate-Wiki\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6178DA6D-4EFC-4131-AAE1-759A02D550AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFFB8807-7EA1-489A-B2D9-DACB6B2DF62F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="2" xr2:uid="{B05E798F-9EF6-4508-A0A4-311D06661AED}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{B05E798F-9EF6-4508-A0A4-311D06661AED}"/>
   </bookViews>
   <sheets>
     <sheet name="Servants" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3351" uniqueCount="1261">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3373" uniqueCount="1271">
   <si>
     <t>servant_id</t>
   </si>
@@ -3826,6 +3826,36 @@
   </si>
   <si>
     <t>Rhongomyniad LR</t>
+  </si>
+  <si>
+    <t>form</t>
+  </si>
+  <si>
+    <t>Albion's Remnant</t>
+  </si>
+  <si>
+    <t>Red Calamity</t>
+  </si>
+  <si>
+    <t>alt</t>
+  </si>
+  <si>
+    <t>Hollow Heart</t>
+  </si>
+  <si>
+    <t>has_form</t>
+  </si>
+  <si>
+    <t>form_special</t>
+  </si>
+  <si>
+    <t>form_strength</t>
+  </si>
+  <si>
+    <t>form_agility</t>
+  </si>
+  <si>
+    <t>form_magic</t>
   </si>
 </sst>
 </file>
@@ -4214,7 +4244,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E33D7ECC-1EAA-4A40-B4DA-A93E54CBC8B5}">
-  <dimension ref="A1:K185"/>
+  <dimension ref="A1:P185"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="2" max="3" width="22" customWidth="1"/>
@@ -4226,9 +4256,13 @@
     <col min="9" max="9" width="17.59765625" style="2" customWidth="1"/>
     <col min="10" max="10" width="63.53125" style="2" customWidth="1"/>
     <col min="11" max="11" width="12.59765625" customWidth="1"/>
+    <col min="13" max="13" width="12" customWidth="1"/>
+    <col min="14" max="14" width="11.53125" customWidth="1"/>
+    <col min="15" max="15" width="11.796875" customWidth="1"/>
+    <col min="16" max="16" width="18.19921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4262,8 +4296,23 @@
       <c r="K1" s="1" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L1" s="3" t="s">
+        <v>1266</v>
+      </c>
+      <c r="M1" s="3" t="s">
+        <v>1268</v>
+      </c>
+      <c r="N1" s="3" t="s">
+        <v>1269</v>
+      </c>
+      <c r="O1" s="3" t="s">
+        <v>1270</v>
+      </c>
+      <c r="P1" s="3" t="s">
+        <v>1267</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -4295,7 +4344,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>111</v>
       </c>
@@ -4327,7 +4376,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>112</v>
       </c>
@@ -4356,7 +4405,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>113</v>
       </c>
@@ -4385,7 +4434,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>114</v>
       </c>
@@ -4417,7 +4466,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>115</v>
       </c>
@@ -4449,7 +4498,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>116</v>
       </c>
@@ -4478,7 +4527,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>117</v>
       </c>
@@ -4507,7 +4556,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>118</v>
       </c>
@@ -4539,7 +4588,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>119</v>
       </c>
@@ -4571,7 +4620,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>120</v>
       </c>
@@ -4603,7 +4652,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>121</v>
       </c>
@@ -4632,7 +4681,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>122</v>
       </c>
@@ -4664,7 +4713,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>123</v>
       </c>
@@ -4696,7 +4745,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>124</v>
       </c>
@@ -5228,7 +5277,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
         <v>335</v>
       </c>
@@ -5260,7 +5309,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
         <v>336</v>
       </c>
@@ -5292,7 +5341,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A35" t="s">
         <v>337</v>
       </c>
@@ -5324,7 +5373,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A36" t="s">
         <v>338</v>
       </c>
@@ -5353,7 +5402,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A37" t="s">
         <v>339</v>
       </c>
@@ -5382,7 +5431,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A38" t="s">
         <v>340</v>
       </c>
@@ -5414,7 +5463,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A39" t="s">
         <v>341</v>
       </c>
@@ -5443,7 +5492,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A40" t="s">
         <v>342</v>
       </c>
@@ -5475,7 +5524,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A41" t="s">
         <v>343</v>
       </c>
@@ -5504,7 +5553,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A42" t="s">
         <v>344</v>
       </c>
@@ -5536,7 +5585,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A43" t="s">
         <v>345</v>
       </c>
@@ -5568,7 +5617,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A44" t="s">
         <v>346</v>
       </c>
@@ -5600,7 +5649,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A45" t="s">
         <v>347</v>
       </c>
@@ -5632,7 +5681,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A46" t="s">
         <v>348</v>
       </c>
@@ -5663,8 +5712,23 @@
       <c r="K46" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L46" t="b">
+        <v>1</v>
+      </c>
+      <c r="M46" s="2" t="s">
+        <v>569</v>
+      </c>
+      <c r="N46" s="2" t="s">
+        <v>565</v>
+      </c>
+      <c r="O46" s="2" t="s">
+        <v>948</v>
+      </c>
+      <c r="P46" s="2" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="47" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A47" t="s">
         <v>349</v>
       </c>
@@ -5696,7 +5760,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A48" t="s">
         <v>466</v>
       </c>
@@ -10364,7 +10428,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84E3BB0D-5578-4069-B1C9-C3864EB2A429}">
-  <dimension ref="A1:F553"/>
+  <dimension ref="A1:G556"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="2" max="2" width="26.33203125" customWidth="1"/>
@@ -10374,7 +10438,7 @@
     <col min="6" max="6" width="15.73046875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -10393,8 +10457,11 @@
       <c r="F1" s="1" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G1" s="1" t="s">
+        <v>1261</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -10411,7 +10478,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -10428,7 +10495,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -10445,7 +10512,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>111</v>
       </c>
@@ -10462,7 +10529,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>111</v>
       </c>
@@ -10479,7 +10546,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>111</v>
       </c>
@@ -10496,7 +10563,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>112</v>
       </c>
@@ -10513,7 +10580,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>112</v>
       </c>
@@ -10530,7 +10597,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>112</v>
       </c>
@@ -10547,7 +10614,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>113</v>
       </c>
@@ -10564,7 +10631,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>113</v>
       </c>
@@ -10581,7 +10648,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>113</v>
       </c>
@@ -10598,7 +10665,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>114</v>
       </c>
@@ -10615,7 +10682,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>114</v>
       </c>
@@ -10632,7 +10699,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>114</v>
       </c>
@@ -12553,7 +12620,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="129" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="129" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A129" t="s">
         <v>346</v>
       </c>
@@ -12570,7 +12637,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="130" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="130" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A130" t="s">
         <v>346</v>
       </c>
@@ -12587,7 +12654,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="131" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="131" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A131" t="s">
         <v>347</v>
       </c>
@@ -12604,7 +12671,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="132" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="132" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A132" t="s">
         <v>347</v>
       </c>
@@ -12621,7 +12688,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="133" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="133" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A133" t="s">
         <v>347</v>
       </c>
@@ -12638,7 +12705,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="134" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="134" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A134" t="s">
         <v>348</v>
       </c>
@@ -12655,7 +12722,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="135" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="135" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A135" t="s">
         <v>348</v>
       </c>
@@ -12672,7 +12739,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="136" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="136" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A136" t="s">
         <v>348</v>
       </c>
@@ -12689,12 +12756,12 @@
         <v>465</v>
       </c>
     </row>
-    <row r="137" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="137" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A137" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B137" t="s">
-        <v>384</v>
+        <v>1262</v>
       </c>
       <c r="C137">
         <v>1</v>
@@ -12703,15 +12770,18 @@
         <v>0</v>
       </c>
       <c r="E137" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="138" spans="1:5" x14ac:dyDescent="0.45">
+        <v>1263</v>
+      </c>
+      <c r="G137" t="s">
+        <v>1264</v>
+      </c>
+    </row>
+    <row r="138" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A138" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B138" t="s">
-        <v>384</v>
+        <v>1262</v>
       </c>
       <c r="C138">
         <v>2</v>
@@ -12720,15 +12790,18 @@
         <v>0</v>
       </c>
       <c r="E138" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="139" spans="1:5" x14ac:dyDescent="0.45">
+        <v>463</v>
+      </c>
+      <c r="G138" t="s">
+        <v>1264</v>
+      </c>
+    </row>
+    <row r="139" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A139" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B139" t="s">
-        <v>384</v>
+        <v>1262</v>
       </c>
       <c r="C139">
         <v>3</v>
@@ -12737,15 +12810,18 @@
         <v>0</v>
       </c>
       <c r="E139" t="s">
-        <v>471</v>
-      </c>
-    </row>
-    <row r="140" spans="1:5" x14ac:dyDescent="0.45">
+        <v>1265</v>
+      </c>
+      <c r="G139" t="s">
+        <v>1264</v>
+      </c>
+    </row>
+    <row r="140" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A140" t="s">
-        <v>466</v>
+        <v>349</v>
       </c>
       <c r="B140" t="s">
-        <v>467</v>
+        <v>384</v>
       </c>
       <c r="C140">
         <v>1</v>
@@ -12754,15 +12830,15 @@
         <v>0</v>
       </c>
       <c r="E140" t="s">
-        <v>472</v>
-      </c>
-    </row>
-    <row r="141" spans="1:5" x14ac:dyDescent="0.45">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="141" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A141" t="s">
-        <v>466</v>
+        <v>349</v>
       </c>
       <c r="B141" t="s">
-        <v>467</v>
+        <v>384</v>
       </c>
       <c r="C141">
         <v>2</v>
@@ -12771,15 +12847,15 @@
         <v>0</v>
       </c>
       <c r="E141" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="142" spans="1:5" x14ac:dyDescent="0.45">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="142" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A142" t="s">
-        <v>466</v>
+        <v>349</v>
       </c>
       <c r="B142" t="s">
-        <v>467</v>
+        <v>384</v>
       </c>
       <c r="C142">
         <v>3</v>
@@ -12788,32 +12864,32 @@
         <v>0</v>
       </c>
       <c r="E142" t="s">
-        <v>474</v>
-      </c>
-    </row>
-    <row r="143" spans="1:5" x14ac:dyDescent="0.45">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="143" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A143" t="s">
-        <v>271</v>
+        <v>466</v>
       </c>
       <c r="B143" t="s">
-        <v>272</v>
+        <v>467</v>
       </c>
       <c r="C143">
         <v>1</v>
       </c>
       <c r="D143" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E143" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="144" spans="1:5" x14ac:dyDescent="0.45">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="144" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A144" t="s">
-        <v>271</v>
+        <v>466</v>
       </c>
       <c r="B144" t="s">
-        <v>272</v>
+        <v>467</v>
       </c>
       <c r="C144">
         <v>2</v>
@@ -12822,15 +12898,15 @@
         <v>0</v>
       </c>
       <c r="E144" t="s">
-        <v>304</v>
+        <v>473</v>
       </c>
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A145" t="s">
-        <v>271</v>
+        <v>466</v>
       </c>
       <c r="B145" t="s">
-        <v>272</v>
+        <v>467</v>
       </c>
       <c r="C145">
         <v>3</v>
@@ -12839,32 +12915,32 @@
         <v>0</v>
       </c>
       <c r="E145" t="s">
-        <v>305</v>
+        <v>474</v>
       </c>
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A146" t="s">
-        <v>476</v>
+        <v>271</v>
       </c>
       <c r="B146" t="s">
-        <v>496</v>
+        <v>272</v>
       </c>
       <c r="C146">
         <v>1</v>
       </c>
       <c r="D146" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E146" t="s">
-        <v>571</v>
+        <v>93</v>
       </c>
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A147" t="s">
-        <v>476</v>
+        <v>271</v>
       </c>
       <c r="B147" t="s">
-        <v>496</v>
+        <v>272</v>
       </c>
       <c r="C147">
         <v>2</v>
@@ -12873,15 +12949,15 @@
         <v>0</v>
       </c>
       <c r="E147" t="s">
-        <v>572</v>
+        <v>304</v>
       </c>
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A148" t="s">
-        <v>476</v>
+        <v>271</v>
       </c>
       <c r="B148" t="s">
-        <v>496</v>
+        <v>272</v>
       </c>
       <c r="C148">
         <v>3</v>
@@ -12890,32 +12966,32 @@
         <v>0</v>
       </c>
       <c r="E148" t="s">
-        <v>573</v>
+        <v>305</v>
       </c>
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A149" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="B149" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="C149">
         <v>1</v>
       </c>
       <c r="D149" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E149" t="s">
-        <v>93</v>
+        <v>571</v>
       </c>
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A150" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="B150" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="C150">
         <v>2</v>
@@ -12924,15 +13000,15 @@
         <v>0</v>
       </c>
       <c r="E150" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A151" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="B151" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="C151">
         <v>3</v>
@@ -12941,15 +13017,15 @@
         <v>0</v>
       </c>
       <c r="E151" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
     </row>
     <row r="152" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A152" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="B152" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="C152">
         <v>1</v>
@@ -12963,10 +13039,10 @@
     </row>
     <row r="153" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A153" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="B153" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="C153">
         <v>2</v>
@@ -12975,15 +13051,15 @@
         <v>0</v>
       </c>
       <c r="E153" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
     </row>
     <row r="154" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A154" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="B154" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="C154">
         <v>3</v>
@@ -12992,15 +13068,15 @@
         <v>0</v>
       </c>
       <c r="E154" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
     </row>
     <row r="155" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A155" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="B155" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="C155">
         <v>1</v>
@@ -13014,10 +13090,10 @@
     </row>
     <row r="156" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A156" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="B156" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="C156">
         <v>2</v>
@@ -13026,15 +13102,15 @@
         <v>0</v>
       </c>
       <c r="E156" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
     </row>
     <row r="157" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A157" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="B157" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="C157">
         <v>3</v>
@@ -13043,32 +13119,32 @@
         <v>0</v>
       </c>
       <c r="E157" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
     </row>
     <row r="158" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A158" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="B158" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="C158">
         <v>1</v>
       </c>
       <c r="D158" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E158" t="s">
-        <v>580</v>
+        <v>93</v>
       </c>
     </row>
     <row r="159" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A159" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="B159" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="C159">
         <v>2</v>
@@ -13077,15 +13153,15 @@
         <v>0</v>
       </c>
       <c r="E159" t="s">
-        <v>581</v>
+        <v>578</v>
       </c>
     </row>
     <row r="160" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A160" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="B160" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="C160">
         <v>3</v>
@@ -13094,32 +13170,32 @@
         <v>0</v>
       </c>
       <c r="E160" t="s">
-        <v>582</v>
+        <v>579</v>
       </c>
     </row>
     <row r="161" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A161" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="B161" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="C161">
         <v>1</v>
       </c>
       <c r="D161" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E161" t="s">
-        <v>93</v>
+        <v>580</v>
       </c>
     </row>
     <row r="162" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A162" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="B162" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="C162">
         <v>2</v>
@@ -13128,15 +13204,15 @@
         <v>0</v>
       </c>
       <c r="E162" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
     </row>
     <row r="163" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A163" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="B163" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="C163">
         <v>3</v>
@@ -13145,15 +13221,15 @@
         <v>0</v>
       </c>
       <c r="E163" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
     <row r="164" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A164" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="B164" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="C164">
         <v>1</v>
@@ -13162,15 +13238,15 @@
         <v>1</v>
       </c>
       <c r="E164" t="s">
-        <v>82</v>
+        <v>93</v>
       </c>
     </row>
     <row r="165" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A165" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="B165" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="C165">
         <v>2</v>
@@ -13179,15 +13255,15 @@
         <v>0</v>
       </c>
       <c r="E165" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
     </row>
     <row r="166" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A166" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="B166" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="C166">
         <v>3</v>
@@ -13196,32 +13272,32 @@
         <v>0</v>
       </c>
       <c r="E166" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="167" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A167" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B167" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="C167">
         <v>1</v>
       </c>
       <c r="D167" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E167" t="s">
-        <v>587</v>
+        <v>82</v>
       </c>
     </row>
     <row r="168" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A168" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B168" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="C168">
         <v>2</v>
@@ -13230,15 +13306,15 @@
         <v>0</v>
       </c>
       <c r="E168" t="s">
-        <v>588</v>
+        <v>585</v>
       </c>
     </row>
     <row r="169" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A169" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B169" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="C169">
         <v>3</v>
@@ -13247,15 +13323,15 @@
         <v>0</v>
       </c>
       <c r="E169" t="s">
-        <v>589</v>
+        <v>586</v>
       </c>
     </row>
     <row r="170" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A170" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="B170" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="C170">
         <v>1</v>
@@ -13264,15 +13340,15 @@
         <v>0</v>
       </c>
       <c r="E170" t="s">
-        <v>590</v>
+        <v>587</v>
       </c>
     </row>
     <row r="171" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A171" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="B171" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="C171">
         <v>2</v>
@@ -13281,15 +13357,15 @@
         <v>0</v>
       </c>
       <c r="E171" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
     </row>
     <row r="172" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A172" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="B172" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="C172">
         <v>3</v>
@@ -13298,15 +13374,15 @@
         <v>0</v>
       </c>
       <c r="E172" t="s">
-        <v>592</v>
+        <v>589</v>
       </c>
     </row>
     <row r="173" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A173" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="B173" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C173">
         <v>1</v>
@@ -13315,15 +13391,15 @@
         <v>0</v>
       </c>
       <c r="E173" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
     </row>
     <row r="174" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A174" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="B174" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C174">
         <v>2</v>
@@ -13332,15 +13408,15 @@
         <v>0</v>
       </c>
       <c r="E174" t="s">
-        <v>594</v>
+        <v>591</v>
       </c>
     </row>
     <row r="175" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A175" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="B175" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C175">
         <v>3</v>
@@ -13349,32 +13425,32 @@
         <v>0</v>
       </c>
       <c r="E175" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
     </row>
     <row r="176" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A176" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="B176" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="C176">
         <v>1</v>
       </c>
       <c r="D176" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E176" t="s">
-        <v>93</v>
+        <v>593</v>
       </c>
     </row>
     <row r="177" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A177" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="B177" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="C177">
         <v>2</v>
@@ -13383,15 +13459,15 @@
         <v>0</v>
       </c>
       <c r="E177" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
     </row>
     <row r="178" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A178" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="B178" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="C178">
         <v>3</v>
@@ -13400,32 +13476,32 @@
         <v>0</v>
       </c>
       <c r="E178" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
     </row>
     <row r="179" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A179" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B179" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C179">
         <v>1</v>
       </c>
       <c r="D179" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E179" t="s">
-        <v>598</v>
+        <v>93</v>
       </c>
     </row>
     <row r="180" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A180" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B180" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C180">
         <v>2</v>
@@ -13434,15 +13510,15 @@
         <v>0</v>
       </c>
       <c r="E180" t="s">
-        <v>599</v>
+        <v>596</v>
       </c>
     </row>
     <row r="181" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A181" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B181" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C181">
         <v>3</v>
@@ -13451,32 +13527,32 @@
         <v>0</v>
       </c>
       <c r="E181" t="s">
-        <v>600</v>
+        <v>597</v>
       </c>
     </row>
     <row r="182" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A182" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="B182" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C182">
         <v>1</v>
       </c>
       <c r="D182" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E182" t="s">
-        <v>93</v>
+        <v>598</v>
       </c>
     </row>
     <row r="183" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A183" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="B183" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C183">
         <v>2</v>
@@ -13485,15 +13561,15 @@
         <v>0</v>
       </c>
       <c r="E183" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
     </row>
     <row r="184" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A184" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="B184" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C184">
         <v>3</v>
@@ -13502,32 +13578,32 @@
         <v>0</v>
       </c>
       <c r="E184" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="185" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A185" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="B185" t="s">
-        <v>603</v>
+        <v>509</v>
       </c>
       <c r="C185">
         <v>1</v>
       </c>
       <c r="D185" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E185" t="s">
-        <v>604</v>
+        <v>93</v>
       </c>
     </row>
     <row r="186" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A186" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="B186" t="s">
-        <v>603</v>
+        <v>509</v>
       </c>
       <c r="C186">
         <v>2</v>
@@ -13536,15 +13612,15 @@
         <v>0</v>
       </c>
       <c r="E186" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
     </row>
     <row r="187" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A187" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="B187" t="s">
-        <v>603</v>
+        <v>509</v>
       </c>
       <c r="C187">
         <v>3</v>
@@ -13553,32 +13629,32 @@
         <v>0</v>
       </c>
       <c r="E187" t="s">
-        <v>606</v>
+        <v>602</v>
       </c>
     </row>
     <row r="188" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A188" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="B188" t="s">
-        <v>510</v>
+        <v>603</v>
       </c>
       <c r="C188">
         <v>1</v>
       </c>
       <c r="D188" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E188" t="s">
-        <v>93</v>
+        <v>604</v>
       </c>
     </row>
     <row r="189" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A189" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="B189" t="s">
-        <v>510</v>
+        <v>603</v>
       </c>
       <c r="C189">
         <v>2</v>
@@ -13587,15 +13663,15 @@
         <v>0</v>
       </c>
       <c r="E189" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
     </row>
     <row r="190" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A190" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="B190" t="s">
-        <v>510</v>
+        <v>603</v>
       </c>
       <c r="C190">
         <v>3</v>
@@ -13604,15 +13680,15 @@
         <v>0</v>
       </c>
       <c r="E190" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
     </row>
     <row r="191" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A191" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="B191" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="C191">
         <v>1</v>
@@ -13626,10 +13702,10 @@
     </row>
     <row r="192" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A192" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="B192" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="C192">
         <v>2</v>
@@ -13638,15 +13714,15 @@
         <v>0</v>
       </c>
       <c r="E192" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
     </row>
     <row r="193" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A193" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="B193" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="C193">
         <v>3</v>
@@ -13655,15 +13731,15 @@
         <v>0</v>
       </c>
       <c r="E193" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
     </row>
     <row r="194" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A194" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="B194" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="C194">
         <v>1</v>
@@ -13677,10 +13753,10 @@
     </row>
     <row r="195" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A195" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="B195" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="C195">
         <v>2</v>
@@ -13689,15 +13765,15 @@
         <v>0</v>
       </c>
       <c r="E195" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
     </row>
     <row r="196" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A196" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="B196" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="C196">
         <v>3</v>
@@ -13706,32 +13782,32 @@
         <v>0</v>
       </c>
       <c r="E196" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
     </row>
     <row r="197" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A197" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="B197" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C197">
         <v>1</v>
       </c>
       <c r="D197" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E197" t="s">
-        <v>613</v>
+        <v>93</v>
       </c>
     </row>
     <row r="198" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A198" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="B198" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C198">
         <v>2</v>
@@ -13740,15 +13816,15 @@
         <v>0</v>
       </c>
       <c r="E198" t="s">
-        <v>614</v>
+        <v>611</v>
       </c>
     </row>
     <row r="199" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A199" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="B199" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C199">
         <v>3</v>
@@ -13757,15 +13833,15 @@
         <v>0</v>
       </c>
       <c r="E199" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
     </row>
     <row r="200" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A200" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="B200" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="C200">
         <v>1</v>
@@ -13774,15 +13850,15 @@
         <v>0</v>
       </c>
       <c r="E200" t="s">
-        <v>616</v>
+        <v>613</v>
       </c>
     </row>
     <row r="201" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A201" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="B201" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="C201">
         <v>2</v>
@@ -13791,15 +13867,15 @@
         <v>0</v>
       </c>
       <c r="E201" t="s">
-        <v>617</v>
+        <v>614</v>
       </c>
     </row>
     <row r="202" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A202" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="B202" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="C202">
         <v>3</v>
@@ -13808,15 +13884,15 @@
         <v>0</v>
       </c>
       <c r="E202" t="s">
-        <v>618</v>
+        <v>615</v>
       </c>
     </row>
     <row r="203" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A203" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="B203" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="C203">
         <v>1</v>
@@ -13825,15 +13901,15 @@
         <v>0</v>
       </c>
       <c r="E203" t="s">
-        <v>619</v>
+        <v>616</v>
       </c>
     </row>
     <row r="204" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A204" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="B204" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="C204">
         <v>2</v>
@@ -13842,15 +13918,15 @@
         <v>0</v>
       </c>
       <c r="E204" t="s">
-        <v>620</v>
+        <v>617</v>
       </c>
     </row>
     <row r="205" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A205" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="B205" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="C205">
         <v>3</v>
@@ -13859,32 +13935,32 @@
         <v>0</v>
       </c>
       <c r="E205" t="s">
-        <v>621</v>
+        <v>618</v>
       </c>
     </row>
     <row r="206" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A206" t="s">
-        <v>85</v>
+        <v>495</v>
       </c>
       <c r="B206" t="s">
-        <v>86</v>
+        <v>516</v>
       </c>
       <c r="C206">
         <v>1</v>
       </c>
       <c r="D206" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E206" t="s">
-        <v>93</v>
+        <v>619</v>
       </c>
     </row>
     <row r="207" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A207" t="s">
-        <v>85</v>
+        <v>495</v>
       </c>
       <c r="B207" t="s">
-        <v>86</v>
+        <v>516</v>
       </c>
       <c r="C207">
         <v>2</v>
@@ -13893,15 +13969,15 @@
         <v>0</v>
       </c>
       <c r="E207" t="s">
-        <v>94</v>
+        <v>620</v>
       </c>
     </row>
     <row r="208" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A208" t="s">
-        <v>85</v>
+        <v>495</v>
       </c>
       <c r="B208" t="s">
-        <v>86</v>
+        <v>516</v>
       </c>
       <c r="C208">
         <v>3</v>
@@ -13910,15 +13986,15 @@
         <v>0</v>
       </c>
       <c r="E208" t="s">
-        <v>95</v>
+        <v>621</v>
       </c>
     </row>
     <row r="209" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A209" t="s">
-        <v>275</v>
+        <v>85</v>
       </c>
       <c r="B209" t="s">
-        <v>276</v>
+        <v>86</v>
       </c>
       <c r="C209">
         <v>1</v>
@@ -13927,15 +14003,15 @@
         <v>1</v>
       </c>
       <c r="E209" t="s">
-        <v>306</v>
+        <v>93</v>
       </c>
     </row>
     <row r="210" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A210" t="s">
-        <v>275</v>
+        <v>85</v>
       </c>
       <c r="B210" t="s">
-        <v>276</v>
+        <v>86</v>
       </c>
       <c r="C210">
         <v>2</v>
@@ -13944,15 +14020,15 @@
         <v>0</v>
       </c>
       <c r="E210" t="s">
-        <v>307</v>
+        <v>94</v>
       </c>
     </row>
     <row r="211" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A211" t="s">
-        <v>275</v>
+        <v>85</v>
       </c>
       <c r="B211" t="s">
-        <v>276</v>
+        <v>86</v>
       </c>
       <c r="C211">
         <v>3</v>
@@ -13961,15 +14037,15 @@
         <v>0</v>
       </c>
       <c r="E211" t="s">
-        <v>308</v>
+        <v>95</v>
       </c>
     </row>
     <row r="212" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A212" t="s">
-        <v>535</v>
+        <v>275</v>
       </c>
       <c r="B212" t="s">
-        <v>622</v>
+        <v>276</v>
       </c>
       <c r="C212">
         <v>1</v>
@@ -13983,10 +14059,10 @@
     </row>
     <row r="213" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A213" t="s">
-        <v>535</v>
+        <v>275</v>
       </c>
       <c r="B213" t="s">
-        <v>622</v>
+        <v>276</v>
       </c>
       <c r="C213">
         <v>2</v>
@@ -13995,15 +14071,15 @@
         <v>0</v>
       </c>
       <c r="E213" t="s">
-        <v>666</v>
+        <v>307</v>
       </c>
     </row>
     <row r="214" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A214" t="s">
-        <v>535</v>
+        <v>275</v>
       </c>
       <c r="B214" t="s">
-        <v>622</v>
+        <v>276</v>
       </c>
       <c r="C214">
         <v>3</v>
@@ -14012,32 +14088,32 @@
         <v>0</v>
       </c>
       <c r="E214" t="s">
-        <v>667</v>
+        <v>308</v>
       </c>
     </row>
     <row r="215" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A215" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="B215" t="s">
-        <v>625</v>
+        <v>622</v>
       </c>
       <c r="C215">
         <v>1</v>
       </c>
       <c r="D215" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E215" t="s">
-        <v>668</v>
+        <v>306</v>
       </c>
     </row>
     <row r="216" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A216" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="B216" t="s">
-        <v>625</v>
+        <v>622</v>
       </c>
       <c r="C216">
         <v>2</v>
@@ -14046,15 +14122,15 @@
         <v>0</v>
       </c>
       <c r="E216" t="s">
-        <v>669</v>
+        <v>666</v>
       </c>
     </row>
     <row r="217" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A217" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="B217" t="s">
-        <v>625</v>
+        <v>622</v>
       </c>
       <c r="C217">
         <v>3</v>
@@ -14063,15 +14139,15 @@
         <v>0</v>
       </c>
       <c r="E217" t="s">
-        <v>670</v>
+        <v>667</v>
       </c>
     </row>
     <row r="218" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A218" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="B218" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="C218">
         <v>1</v>
@@ -14080,15 +14156,15 @@
         <v>0</v>
       </c>
       <c r="E218" t="s">
-        <v>671</v>
+        <v>668</v>
       </c>
     </row>
     <row r="219" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A219" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="B219" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="C219">
         <v>2</v>
@@ -14097,15 +14173,15 @@
         <v>0</v>
       </c>
       <c r="E219" t="s">
-        <v>672</v>
+        <v>669</v>
       </c>
     </row>
     <row r="220" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A220" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="B220" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="C220">
         <v>3</v>
@@ -14114,32 +14190,32 @@
         <v>0</v>
       </c>
       <c r="E220" t="s">
-        <v>673</v>
+        <v>670</v>
       </c>
     </row>
     <row r="221" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A221" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="B221" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="C221">
         <v>1</v>
       </c>
       <c r="D221" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E221" t="s">
-        <v>306</v>
+        <v>671</v>
       </c>
     </row>
     <row r="222" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A222" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="B222" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="C222">
         <v>2</v>
@@ -14148,15 +14224,15 @@
         <v>0</v>
       </c>
       <c r="E222" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
     </row>
     <row r="223" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A223" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="B223" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="C223">
         <v>3</v>
@@ -14165,15 +14241,15 @@
         <v>0</v>
       </c>
       <c r="E223" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
     </row>
     <row r="224" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A224" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="B224" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="C224">
         <v>1</v>
@@ -14187,10 +14263,10 @@
     </row>
     <row r="225" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A225" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="B225" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="C225">
         <v>2</v>
@@ -14199,15 +14275,15 @@
         <v>0</v>
       </c>
       <c r="E225" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
     </row>
     <row r="226" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A226" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="B226" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="C226">
         <v>3</v>
@@ -14216,15 +14292,15 @@
         <v>0</v>
       </c>
       <c r="E226" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
     </row>
     <row r="227" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A227" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="B227" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="C227">
         <v>1</v>
@@ -14238,10 +14314,10 @@
     </row>
     <row r="228" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A228" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="B228" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="C228">
         <v>2</v>
@@ -14250,15 +14326,15 @@
         <v>0</v>
       </c>
       <c r="E228" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
     </row>
     <row r="229" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A229" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="B229" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="C229">
         <v>3</v>
@@ -14267,32 +14343,32 @@
         <v>0</v>
       </c>
       <c r="E229" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
     </row>
     <row r="230" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A230" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="B230" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="C230">
         <v>1</v>
       </c>
       <c r="D230" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E230" t="s">
-        <v>680</v>
+        <v>306</v>
       </c>
     </row>
     <row r="231" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A231" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="B231" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="C231">
         <v>2</v>
@@ -14301,15 +14377,15 @@
         <v>0</v>
       </c>
       <c r="E231" t="s">
-        <v>681</v>
+        <v>678</v>
       </c>
     </row>
     <row r="232" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A232" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="B232" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="C232">
         <v>3</v>
@@ -14318,32 +14394,32 @@
         <v>0</v>
       </c>
       <c r="E232" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
     </row>
     <row r="233" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A233" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="B233" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="C233">
         <v>1</v>
       </c>
       <c r="D233" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E233" t="s">
-        <v>82</v>
+        <v>680</v>
       </c>
     </row>
     <row r="234" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A234" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="B234" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="C234">
         <v>2</v>
@@ -14352,15 +14428,15 @@
         <v>0</v>
       </c>
       <c r="E234" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
     </row>
     <row r="235" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A235" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="B235" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="C235">
         <v>3</v>
@@ -14369,15 +14445,15 @@
         <v>0</v>
       </c>
       <c r="E235" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
     </row>
     <row r="236" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A236" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="B236" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="C236">
         <v>1</v>
@@ -14386,15 +14462,15 @@
         <v>1</v>
       </c>
       <c r="E236" t="s">
-        <v>306</v>
+        <v>82</v>
       </c>
     </row>
     <row r="237" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A237" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="B237" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="C237">
         <v>2</v>
@@ -14403,15 +14479,15 @@
         <v>0</v>
       </c>
       <c r="E237" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
     </row>
     <row r="238" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A238" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="B238" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="C238">
         <v>3</v>
@@ -14420,15 +14496,15 @@
         <v>0</v>
       </c>
       <c r="E238" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
     </row>
     <row r="239" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A239" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="B239" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="C239">
         <v>1</v>
@@ -14442,10 +14518,10 @@
     </row>
     <row r="240" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A240" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="B240" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="C240">
         <v>2</v>
@@ -14454,15 +14530,15 @@
         <v>0</v>
       </c>
       <c r="E240" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
     </row>
     <row r="241" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A241" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="B241" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="C241">
         <v>3</v>
@@ -14471,15 +14547,15 @@
         <v>0</v>
       </c>
       <c r="E241" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
     </row>
     <row r="242" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A242" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="B242" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="C242">
         <v>1</v>
@@ -14493,10 +14569,10 @@
     </row>
     <row r="243" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A243" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="B243" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="C243">
         <v>2</v>
@@ -14505,15 +14581,15 @@
         <v>0</v>
       </c>
       <c r="E243" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
     </row>
     <row r="244" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A244" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="B244" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="C244">
         <v>3</v>
@@ -14522,15 +14598,15 @@
         <v>0</v>
       </c>
       <c r="E244" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
     </row>
     <row r="245" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A245" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="B245" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="C245">
         <v>1</v>
@@ -14544,10 +14620,10 @@
     </row>
     <row r="246" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A246" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="B246" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="C246">
         <v>2</v>
@@ -14556,15 +14632,15 @@
         <v>0</v>
       </c>
       <c r="E246" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
     </row>
     <row r="247" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A247" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="B247" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="C247">
         <v>3</v>
@@ -14573,32 +14649,32 @@
         <v>0</v>
       </c>
       <c r="E247" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
     </row>
     <row r="248" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A248" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="B248" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="C248">
         <v>1</v>
       </c>
       <c r="D248" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E248" t="s">
-        <v>693</v>
+        <v>306</v>
       </c>
     </row>
     <row r="249" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A249" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="B249" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="C249">
         <v>2</v>
@@ -14607,15 +14683,15 @@
         <v>0</v>
       </c>
       <c r="E249" t="s">
-        <v>694</v>
+        <v>691</v>
       </c>
     </row>
     <row r="250" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A250" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="B250" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="C250">
         <v>3</v>
@@ -14624,49 +14700,49 @@
         <v>0</v>
       </c>
       <c r="E250" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
     </row>
     <row r="251" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A251" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="B251" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="C251">
         <v>1</v>
       </c>
       <c r="D251" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E251" t="s">
-        <v>696</v>
+        <v>693</v>
       </c>
     </row>
     <row r="252" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A252" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="B252" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="C252">
         <v>2</v>
       </c>
       <c r="D252" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E252" t="s">
-        <v>306</v>
+        <v>694</v>
       </c>
     </row>
     <row r="253" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A253" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="B253" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="C253">
         <v>3</v>
@@ -14675,49 +14751,49 @@
         <v>0</v>
       </c>
       <c r="E253" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
     </row>
     <row r="254" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A254" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B254" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="C254">
         <v>1</v>
       </c>
       <c r="D254" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E254" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
     </row>
     <row r="255" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A255" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B255" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="C255">
         <v>2</v>
       </c>
       <c r="D255" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E255" t="s">
-        <v>699</v>
+        <v>306</v>
       </c>
     </row>
     <row r="256" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A256" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B256" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="C256">
         <v>3</v>
@@ -14726,32 +14802,32 @@
         <v>0</v>
       </c>
       <c r="E256" t="s">
-        <v>700</v>
+        <v>697</v>
       </c>
     </row>
     <row r="257" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A257" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="B257" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="C257">
         <v>1</v>
       </c>
       <c r="D257" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E257" t="s">
-        <v>306</v>
+        <v>698</v>
       </c>
     </row>
     <row r="258" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A258" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="B258" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="C258">
         <v>2</v>
@@ -14760,15 +14836,15 @@
         <v>0</v>
       </c>
       <c r="E258" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
     </row>
     <row r="259" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A259" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="B259" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="C259">
         <v>3</v>
@@ -14777,15 +14853,15 @@
         <v>0</v>
       </c>
       <c r="E259" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
     </row>
     <row r="260" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A260" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B260" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="C260">
         <v>1</v>
@@ -14799,10 +14875,10 @@
     </row>
     <row r="261" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A261" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B261" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="C261">
         <v>2</v>
@@ -14811,15 +14887,15 @@
         <v>0</v>
       </c>
       <c r="E261" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
     </row>
     <row r="262" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A262" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B262" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="C262">
         <v>3</v>
@@ -14828,15 +14904,15 @@
         <v>0</v>
       </c>
       <c r="E262" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
     </row>
     <row r="263" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A263" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="B263" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="C263">
         <v>1</v>
@@ -14850,10 +14926,10 @@
     </row>
     <row r="264" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A264" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="B264" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="C264">
         <v>2</v>
@@ -14862,15 +14938,15 @@
         <v>0</v>
       </c>
       <c r="E264" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
     </row>
     <row r="265" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A265" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="B265" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="C265">
         <v>3</v>
@@ -14879,32 +14955,32 @@
         <v>0</v>
       </c>
       <c r="E265" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
     </row>
     <row r="266" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A266" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="B266" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C266">
         <v>1</v>
       </c>
       <c r="D266" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E266" t="s">
-        <v>707</v>
+        <v>306</v>
       </c>
     </row>
     <row r="267" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A267" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="B267" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C267">
         <v>2</v>
@@ -14913,15 +14989,15 @@
         <v>0</v>
       </c>
       <c r="E267" t="s">
-        <v>708</v>
+        <v>705</v>
       </c>
     </row>
     <row r="268" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A268" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="B268" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C268">
         <v>3</v>
@@ -14930,15 +15006,15 @@
         <v>0</v>
       </c>
       <c r="E268" t="s">
-        <v>709</v>
+        <v>706</v>
       </c>
     </row>
     <row r="269" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A269" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="B269" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="C269">
         <v>1</v>
@@ -14947,15 +15023,15 @@
         <v>0</v>
       </c>
       <c r="E269" t="s">
-        <v>710</v>
+        <v>707</v>
       </c>
     </row>
     <row r="270" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A270" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="B270" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="C270">
         <v>2</v>
@@ -14964,15 +15040,15 @@
         <v>0</v>
       </c>
       <c r="E270" t="s">
-        <v>711</v>
+        <v>708</v>
       </c>
     </row>
     <row r="271" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A271" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="B271" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="C271">
         <v>3</v>
@@ -14981,32 +15057,32 @@
         <v>0</v>
       </c>
       <c r="E271" t="s">
-        <v>712</v>
+        <v>709</v>
       </c>
     </row>
     <row r="272" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A272" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="B272" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="C272">
         <v>1</v>
       </c>
       <c r="D272" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E272" t="s">
-        <v>82</v>
+        <v>710</v>
       </c>
     </row>
     <row r="273" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A273" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="B273" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="C273">
         <v>2</v>
@@ -15015,15 +15091,15 @@
         <v>0</v>
       </c>
       <c r="E273" t="s">
-        <v>713</v>
+        <v>711</v>
       </c>
     </row>
     <row r="274" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A274" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="B274" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="C274">
         <v>3</v>
@@ -15032,15 +15108,15 @@
         <v>0</v>
       </c>
       <c r="E274" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
     </row>
     <row r="275" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A275" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="B275" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="C275">
         <v>1</v>
@@ -15049,15 +15125,15 @@
         <v>1</v>
       </c>
       <c r="E275" t="s">
-        <v>306</v>
+        <v>82</v>
       </c>
     </row>
     <row r="276" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A276" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="B276" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="C276">
         <v>2</v>
@@ -15066,15 +15142,15 @@
         <v>0</v>
       </c>
       <c r="E276" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
     </row>
     <row r="277" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A277" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="B277" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="C277">
         <v>3</v>
@@ -15083,15 +15159,15 @@
         <v>0</v>
       </c>
       <c r="E277" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
     </row>
     <row r="278" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A278" t="s">
-        <v>281</v>
+        <v>556</v>
       </c>
       <c r="B278" t="s">
-        <v>249</v>
+        <v>645</v>
       </c>
       <c r="C278">
         <v>1</v>
@@ -15100,15 +15176,15 @@
         <v>1</v>
       </c>
       <c r="E278" t="s">
-        <v>58</v>
+        <v>306</v>
       </c>
     </row>
     <row r="279" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A279" t="s">
-        <v>281</v>
+        <v>556</v>
       </c>
       <c r="B279" t="s">
-        <v>249</v>
+        <v>645</v>
       </c>
       <c r="C279">
         <v>2</v>
@@ -15117,15 +15193,15 @@
         <v>0</v>
       </c>
       <c r="E279" t="s">
-        <v>309</v>
+        <v>715</v>
       </c>
     </row>
     <row r="280" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A280" t="s">
-        <v>281</v>
+        <v>556</v>
       </c>
       <c r="B280" t="s">
-        <v>249</v>
+        <v>645</v>
       </c>
       <c r="C280">
         <v>3</v>
@@ -15134,15 +15210,15 @@
         <v>0</v>
       </c>
       <c r="E280" t="s">
-        <v>310</v>
+        <v>716</v>
       </c>
     </row>
     <row r="281" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A281" t="s">
-        <v>738</v>
+        <v>281</v>
       </c>
       <c r="B281" t="s">
-        <v>741</v>
+        <v>249</v>
       </c>
       <c r="C281">
         <v>1</v>
@@ -15156,10 +15232,10 @@
     </row>
     <row r="282" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A282" t="s">
-        <v>738</v>
+        <v>281</v>
       </c>
       <c r="B282" t="s">
-        <v>741</v>
+        <v>249</v>
       </c>
       <c r="C282">
         <v>2</v>
@@ -15168,15 +15244,15 @@
         <v>0</v>
       </c>
       <c r="E282" t="s">
-        <v>750</v>
+        <v>309</v>
       </c>
     </row>
     <row r="283" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A283" t="s">
-        <v>738</v>
+        <v>281</v>
       </c>
       <c r="B283" t="s">
-        <v>741</v>
+        <v>249</v>
       </c>
       <c r="C283">
         <v>3</v>
@@ -15185,32 +15261,32 @@
         <v>0</v>
       </c>
       <c r="E283" t="s">
-        <v>751</v>
+        <v>310</v>
       </c>
     </row>
     <row r="284" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A284" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="B284" t="s">
-        <v>745</v>
+        <v>741</v>
       </c>
       <c r="C284">
         <v>1</v>
       </c>
       <c r="D284" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E284" t="s">
-        <v>752</v>
+        <v>58</v>
       </c>
     </row>
     <row r="285" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A285" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="B285" t="s">
-        <v>745</v>
+        <v>741</v>
       </c>
       <c r="C285">
         <v>2</v>
@@ -15219,15 +15295,15 @@
         <v>0</v>
       </c>
       <c r="E285" t="s">
-        <v>753</v>
+        <v>750</v>
       </c>
     </row>
     <row r="286" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A286" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="B286" t="s">
-        <v>745</v>
+        <v>741</v>
       </c>
       <c r="C286">
         <v>3</v>
@@ -15236,32 +15312,32 @@
         <v>0</v>
       </c>
       <c r="E286" t="s">
-        <v>754</v>
+        <v>751</v>
       </c>
     </row>
     <row r="287" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A287" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="B287" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="C287">
         <v>1</v>
       </c>
       <c r="D287" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E287" t="s">
-        <v>58</v>
+        <v>752</v>
       </c>
     </row>
     <row r="288" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A288" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="B288" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="C288">
         <v>2</v>
@@ -15270,15 +15346,15 @@
         <v>0</v>
       </c>
       <c r="E288" t="s">
-        <v>755</v>
+        <v>753</v>
       </c>
     </row>
     <row r="289" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A289" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="B289" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="C289">
         <v>3</v>
@@ -15287,15 +15363,15 @@
         <v>0</v>
       </c>
       <c r="E289" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
     </row>
     <row r="290" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A290" t="s">
-        <v>17</v>
+        <v>740</v>
       </c>
       <c r="B290" t="s">
-        <v>18</v>
+        <v>747</v>
       </c>
       <c r="C290">
         <v>1</v>
@@ -15309,10 +15385,10 @@
     </row>
     <row r="291" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A291" t="s">
-        <v>17</v>
+        <v>740</v>
       </c>
       <c r="B291" t="s">
-        <v>18</v>
+        <v>747</v>
       </c>
       <c r="C291">
         <v>2</v>
@@ -15321,15 +15397,15 @@
         <v>0</v>
       </c>
       <c r="E291" t="s">
-        <v>59</v>
+        <v>755</v>
       </c>
     </row>
     <row r="292" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A292" t="s">
-        <v>17</v>
+        <v>740</v>
       </c>
       <c r="B292" t="s">
-        <v>18</v>
+        <v>747</v>
       </c>
       <c r="C292">
         <v>3</v>
@@ -15338,15 +15414,15 @@
         <v>0</v>
       </c>
       <c r="E292" t="s">
-        <v>60</v>
+        <v>756</v>
       </c>
     </row>
     <row r="293" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A293" t="s">
-        <v>757</v>
+        <v>17</v>
       </c>
       <c r="B293" t="s">
-        <v>760</v>
+        <v>18</v>
       </c>
       <c r="C293">
         <v>1</v>
@@ -15360,10 +15436,10 @@
     </row>
     <row r="294" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A294" t="s">
-        <v>757</v>
+        <v>17</v>
       </c>
       <c r="B294" t="s">
-        <v>760</v>
+        <v>18</v>
       </c>
       <c r="C294">
         <v>2</v>
@@ -15372,15 +15448,15 @@
         <v>0</v>
       </c>
       <c r="E294" t="s">
-        <v>764</v>
+        <v>59</v>
       </c>
     </row>
     <row r="295" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A295" t="s">
-        <v>757</v>
+        <v>17</v>
       </c>
       <c r="B295" t="s">
-        <v>760</v>
+        <v>18</v>
       </c>
       <c r="C295">
         <v>3</v>
@@ -15389,32 +15465,32 @@
         <v>0</v>
       </c>
       <c r="E295" t="s">
-        <v>765</v>
+        <v>60</v>
       </c>
     </row>
     <row r="296" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A296" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="B296" t="s">
-        <v>766</v>
+        <v>760</v>
       </c>
       <c r="C296">
         <v>1</v>
       </c>
       <c r="D296" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E296" t="s">
-        <v>768</v>
+        <v>58</v>
       </c>
     </row>
     <row r="297" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A297" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="B297" t="s">
-        <v>766</v>
+        <v>760</v>
       </c>
       <c r="C297">
         <v>2</v>
@@ -15423,15 +15499,15 @@
         <v>0</v>
       </c>
       <c r="E297" t="s">
-        <v>769</v>
+        <v>764</v>
       </c>
     </row>
     <row r="298" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A298" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="B298" t="s">
-        <v>766</v>
+        <v>760</v>
       </c>
       <c r="C298">
         <v>3</v>
@@ -15440,32 +15516,32 @@
         <v>0</v>
       </c>
       <c r="E298" t="s">
-        <v>770</v>
+        <v>765</v>
       </c>
     </row>
     <row r="299" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A299" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="B299" t="s">
-        <v>771</v>
+        <v>766</v>
       </c>
       <c r="C299">
         <v>1</v>
       </c>
       <c r="D299" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E299" t="s">
-        <v>58</v>
+        <v>768</v>
       </c>
     </row>
     <row r="300" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A300" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="B300" t="s">
-        <v>771</v>
+        <v>766</v>
       </c>
       <c r="C300">
         <v>2</v>
@@ -15474,15 +15550,15 @@
         <v>0</v>
       </c>
       <c r="E300" t="s">
-        <v>773</v>
+        <v>769</v>
       </c>
     </row>
     <row r="301" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A301" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="B301" t="s">
-        <v>771</v>
+        <v>766</v>
       </c>
       <c r="C301">
         <v>3</v>
@@ -15491,32 +15567,32 @@
         <v>0</v>
       </c>
       <c r="E301" t="s">
-        <v>774</v>
+        <v>770</v>
       </c>
     </row>
     <row r="302" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A302" t="s">
-        <v>284</v>
+        <v>759</v>
       </c>
       <c r="B302" t="s">
-        <v>285</v>
+        <v>771</v>
       </c>
       <c r="C302">
         <v>1</v>
       </c>
       <c r="D302" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E302" t="s">
-        <v>311</v>
+        <v>58</v>
       </c>
     </row>
     <row r="303" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A303" t="s">
-        <v>284</v>
+        <v>759</v>
       </c>
       <c r="B303" t="s">
-        <v>285</v>
+        <v>771</v>
       </c>
       <c r="C303">
         <v>2</v>
@@ -15525,15 +15601,15 @@
         <v>0</v>
       </c>
       <c r="E303" t="s">
-        <v>312</v>
+        <v>773</v>
       </c>
     </row>
     <row r="304" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A304" t="s">
-        <v>284</v>
+        <v>759</v>
       </c>
       <c r="B304" t="s">
-        <v>285</v>
+        <v>771</v>
       </c>
       <c r="C304">
         <v>3</v>
@@ -15542,32 +15618,32 @@
         <v>0</v>
       </c>
       <c r="E304" t="s">
-        <v>313</v>
+        <v>774</v>
       </c>
     </row>
     <row r="305" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A305" t="s">
-        <v>775</v>
+        <v>284</v>
       </c>
       <c r="B305" t="s">
-        <v>781</v>
+        <v>285</v>
       </c>
       <c r="C305">
         <v>1</v>
       </c>
       <c r="D305" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E305" t="s">
-        <v>82</v>
+        <v>311</v>
       </c>
     </row>
     <row r="306" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A306" t="s">
-        <v>775</v>
+        <v>284</v>
       </c>
       <c r="B306" t="s">
-        <v>781</v>
+        <v>285</v>
       </c>
       <c r="C306">
         <v>2</v>
@@ -15576,15 +15652,15 @@
         <v>0</v>
       </c>
       <c r="E306" t="s">
-        <v>783</v>
+        <v>312</v>
       </c>
     </row>
     <row r="307" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A307" t="s">
-        <v>775</v>
+        <v>284</v>
       </c>
       <c r="B307" t="s">
-        <v>781</v>
+        <v>285</v>
       </c>
       <c r="C307">
         <v>3</v>
@@ -15593,32 +15669,32 @@
         <v>0</v>
       </c>
       <c r="E307" t="s">
-        <v>784</v>
+        <v>313</v>
       </c>
     </row>
     <row r="308" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A308" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="B308" t="s">
-        <v>785</v>
+        <v>781</v>
       </c>
       <c r="C308">
         <v>1</v>
       </c>
       <c r="D308" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E308" t="s">
-        <v>786</v>
+        <v>82</v>
       </c>
     </row>
     <row r="309" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A309" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="B309" t="s">
-        <v>785</v>
+        <v>781</v>
       </c>
       <c r="C309">
         <v>2</v>
@@ -15627,15 +15703,15 @@
         <v>0</v>
       </c>
       <c r="E309" t="s">
-        <v>787</v>
+        <v>783</v>
       </c>
     </row>
     <row r="310" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A310" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="B310" t="s">
-        <v>785</v>
+        <v>781</v>
       </c>
       <c r="C310">
         <v>3</v>
@@ -15644,15 +15720,15 @@
         <v>0</v>
       </c>
       <c r="E310" t="s">
-        <v>788</v>
+        <v>784</v>
       </c>
     </row>
     <row r="311" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A311" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="B311" t="s">
-        <v>790</v>
+        <v>785</v>
       </c>
       <c r="C311">
         <v>1</v>
@@ -15661,15 +15737,15 @@
         <v>0</v>
       </c>
       <c r="E311" t="s">
-        <v>792</v>
+        <v>786</v>
       </c>
     </row>
     <row r="312" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A312" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="B312" t="s">
-        <v>790</v>
+        <v>785</v>
       </c>
       <c r="C312">
         <v>2</v>
@@ -15678,15 +15754,15 @@
         <v>0</v>
       </c>
       <c r="E312" t="s">
-        <v>793</v>
+        <v>787</v>
       </c>
     </row>
     <row r="313" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A313" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="B313" t="s">
-        <v>790</v>
+        <v>785</v>
       </c>
       <c r="C313">
         <v>3</v>
@@ -15695,32 +15771,32 @@
         <v>0</v>
       </c>
       <c r="E313" t="s">
-        <v>794</v>
+        <v>788</v>
       </c>
     </row>
     <row r="314" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A314" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="B314" t="s">
-        <v>795</v>
+        <v>790</v>
       </c>
       <c r="C314">
         <v>1</v>
       </c>
       <c r="D314" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E314" t="s">
-        <v>58</v>
+        <v>792</v>
       </c>
     </row>
     <row r="315" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A315" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="B315" t="s">
-        <v>795</v>
+        <v>790</v>
       </c>
       <c r="C315">
         <v>2</v>
@@ -15729,15 +15805,15 @@
         <v>0</v>
       </c>
       <c r="E315" t="s">
-        <v>798</v>
+        <v>793</v>
       </c>
     </row>
     <row r="316" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A316" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="B316" t="s">
-        <v>795</v>
+        <v>790</v>
       </c>
       <c r="C316">
         <v>3</v>
@@ -15746,15 +15822,15 @@
         <v>0</v>
       </c>
       <c r="E316" t="s">
-        <v>799</v>
+        <v>794</v>
       </c>
     </row>
     <row r="317" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A317" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="B317" t="s">
-        <v>800</v>
+        <v>795</v>
       </c>
       <c r="C317">
         <v>1</v>
@@ -15768,10 +15844,10 @@
     </row>
     <row r="318" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A318" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="B318" t="s">
-        <v>800</v>
+        <v>795</v>
       </c>
       <c r="C318">
         <v>2</v>
@@ -15780,15 +15856,15 @@
         <v>0</v>
       </c>
       <c r="E318" t="s">
-        <v>802</v>
+        <v>798</v>
       </c>
     </row>
     <row r="319" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A319" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="B319" t="s">
-        <v>800</v>
+        <v>795</v>
       </c>
       <c r="C319">
         <v>3</v>
@@ -15797,15 +15873,15 @@
         <v>0</v>
       </c>
       <c r="E319" t="s">
-        <v>803</v>
+        <v>799</v>
       </c>
     </row>
     <row r="320" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A320" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="B320" t="s">
-        <v>804</v>
+        <v>800</v>
       </c>
       <c r="C320">
         <v>1</v>
@@ -15819,10 +15895,10 @@
     </row>
     <row r="321" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A321" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="B321" t="s">
-        <v>804</v>
+        <v>800</v>
       </c>
       <c r="C321">
         <v>2</v>
@@ -15831,15 +15907,15 @@
         <v>0</v>
       </c>
       <c r="E321" t="s">
-        <v>806</v>
+        <v>802</v>
       </c>
     </row>
     <row r="322" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A322" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="B322" t="s">
-        <v>804</v>
+        <v>800</v>
       </c>
       <c r="C322">
         <v>3</v>
@@ -15848,32 +15924,32 @@
         <v>0</v>
       </c>
       <c r="E322" t="s">
-        <v>807</v>
+        <v>803</v>
       </c>
     </row>
     <row r="323" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A323" t="s">
-        <v>96</v>
+        <v>780</v>
       </c>
       <c r="B323" t="s">
-        <v>97</v>
+        <v>804</v>
       </c>
       <c r="C323">
         <v>1</v>
       </c>
       <c r="D323" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E323" t="s">
-        <v>108</v>
+        <v>58</v>
       </c>
     </row>
     <row r="324" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A324" t="s">
-        <v>96</v>
+        <v>780</v>
       </c>
       <c r="B324" t="s">
-        <v>97</v>
+        <v>804</v>
       </c>
       <c r="C324">
         <v>2</v>
@@ -15882,15 +15958,15 @@
         <v>0</v>
       </c>
       <c r="E324" t="s">
-        <v>109</v>
+        <v>806</v>
       </c>
     </row>
     <row r="325" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A325" t="s">
-        <v>96</v>
+        <v>780</v>
       </c>
       <c r="B325" t="s">
-        <v>97</v>
+        <v>804</v>
       </c>
       <c r="C325">
         <v>3</v>
@@ -15899,32 +15975,32 @@
         <v>0</v>
       </c>
       <c r="E325" t="s">
-        <v>110</v>
+        <v>807</v>
       </c>
     </row>
     <row r="326" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A326" t="s">
-        <v>808</v>
+        <v>96</v>
       </c>
       <c r="B326" t="s">
-        <v>820</v>
+        <v>97</v>
       </c>
       <c r="C326">
         <v>1</v>
       </c>
       <c r="D326" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E326" t="s">
-        <v>58</v>
+        <v>108</v>
       </c>
     </row>
     <row r="327" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A327" t="s">
-        <v>808</v>
+        <v>96</v>
       </c>
       <c r="B327" t="s">
-        <v>820</v>
+        <v>97</v>
       </c>
       <c r="C327">
         <v>2</v>
@@ -15933,15 +16009,15 @@
         <v>0</v>
       </c>
       <c r="E327" t="s">
-        <v>834</v>
+        <v>109</v>
       </c>
     </row>
     <row r="328" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A328" t="s">
-        <v>808</v>
+        <v>96</v>
       </c>
       <c r="B328" t="s">
-        <v>820</v>
+        <v>97</v>
       </c>
       <c r="C328">
         <v>3</v>
@@ -15950,32 +16026,32 @@
         <v>0</v>
       </c>
       <c r="E328" t="s">
-        <v>835</v>
+        <v>110</v>
       </c>
     </row>
     <row r="329" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A329" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="B329" t="s">
-        <v>822</v>
+        <v>820</v>
       </c>
       <c r="C329">
         <v>1</v>
       </c>
       <c r="D329" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E329" t="s">
-        <v>841</v>
+        <v>58</v>
       </c>
     </row>
     <row r="330" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A330" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="B330" t="s">
-        <v>822</v>
+        <v>820</v>
       </c>
       <c r="C330">
         <v>2</v>
@@ -15984,15 +16060,15 @@
         <v>0</v>
       </c>
       <c r="E330" t="s">
-        <v>842</v>
+        <v>834</v>
       </c>
     </row>
     <row r="331" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A331" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="B331" t="s">
-        <v>822</v>
+        <v>820</v>
       </c>
       <c r="C331">
         <v>3</v>
@@ -16001,15 +16077,15 @@
         <v>0</v>
       </c>
       <c r="E331" t="s">
-        <v>843</v>
+        <v>835</v>
       </c>
     </row>
     <row r="332" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A332" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="B332" t="s">
-        <v>824</v>
+        <v>822</v>
       </c>
       <c r="C332">
         <v>1</v>
@@ -16018,15 +16094,15 @@
         <v>0</v>
       </c>
       <c r="E332" t="s">
-        <v>844</v>
+        <v>841</v>
       </c>
     </row>
     <row r="333" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A333" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="B333" t="s">
-        <v>824</v>
+        <v>822</v>
       </c>
       <c r="C333">
         <v>2</v>
@@ -16035,15 +16111,15 @@
         <v>0</v>
       </c>
       <c r="E333" t="s">
-        <v>845</v>
+        <v>842</v>
       </c>
     </row>
     <row r="334" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A334" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="B334" t="s">
-        <v>824</v>
+        <v>822</v>
       </c>
       <c r="C334">
         <v>3</v>
@@ -16052,15 +16128,15 @@
         <v>0</v>
       </c>
       <c r="E334" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="335" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A335" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="B335" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="C335">
         <v>1</v>
@@ -16069,15 +16145,15 @@
         <v>0</v>
       </c>
       <c r="E335" t="s">
-        <v>847</v>
+        <v>844</v>
       </c>
     </row>
     <row r="336" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A336" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="B336" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="C336">
         <v>2</v>
@@ -16086,15 +16162,15 @@
         <v>0</v>
       </c>
       <c r="E336" t="s">
-        <v>848</v>
+        <v>845</v>
       </c>
     </row>
     <row r="337" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A337" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="B337" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="C337">
         <v>3</v>
@@ -16103,49 +16179,49 @@
         <v>0</v>
       </c>
       <c r="E337" t="s">
-        <v>849</v>
+        <v>846</v>
       </c>
     </row>
     <row r="338" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A338" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="B338" t="s">
-        <v>829</v>
+        <v>826</v>
       </c>
       <c r="C338">
         <v>1</v>
       </c>
       <c r="D338" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E338" t="s">
-        <v>696</v>
+        <v>847</v>
       </c>
     </row>
     <row r="339" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A339" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="B339" t="s">
-        <v>829</v>
+        <v>826</v>
       </c>
       <c r="C339">
         <v>2</v>
       </c>
       <c r="D339" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E339" t="s">
-        <v>58</v>
+        <v>848</v>
       </c>
     </row>
     <row r="340" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A340" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="B340" t="s">
-        <v>829</v>
+        <v>826</v>
       </c>
       <c r="C340">
         <v>3</v>
@@ -16154,49 +16230,49 @@
         <v>0</v>
       </c>
       <c r="E340" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
     </row>
     <row r="341" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A341" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="B341" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="C341">
         <v>1</v>
       </c>
       <c r="D341" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E341" t="s">
-        <v>851</v>
+        <v>696</v>
       </c>
     </row>
     <row r="342" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A342" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="B342" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="C342">
         <v>2</v>
       </c>
       <c r="D342" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E342" t="s">
-        <v>852</v>
+        <v>58</v>
       </c>
     </row>
     <row r="343" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A343" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="B343" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="C343">
         <v>3</v>
@@ -16205,15 +16281,15 @@
         <v>0</v>
       </c>
       <c r="E343" t="s">
-        <v>853</v>
+        <v>850</v>
       </c>
     </row>
     <row r="344" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A344" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="B344" t="s">
-        <v>828</v>
+        <v>830</v>
       </c>
       <c r="C344">
         <v>1</v>
@@ -16222,15 +16298,15 @@
         <v>0</v>
       </c>
       <c r="E344" t="s">
-        <v>854</v>
+        <v>851</v>
       </c>
     </row>
     <row r="345" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A345" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="B345" t="s">
-        <v>828</v>
+        <v>830</v>
       </c>
       <c r="C345">
         <v>2</v>
@@ -16239,15 +16315,15 @@
         <v>0</v>
       </c>
       <c r="E345" t="s">
-        <v>855</v>
+        <v>852</v>
       </c>
     </row>
     <row r="346" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A346" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="B346" t="s">
-        <v>828</v>
+        <v>830</v>
       </c>
       <c r="C346">
         <v>3</v>
@@ -16256,15 +16332,15 @@
         <v>0</v>
       </c>
       <c r="E346" t="s">
-        <v>856</v>
+        <v>853</v>
       </c>
     </row>
     <row r="347" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A347" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="B347" t="s">
-        <v>857</v>
+        <v>828</v>
       </c>
       <c r="C347">
         <v>1</v>
@@ -16273,15 +16349,15 @@
         <v>0</v>
       </c>
       <c r="E347" t="s">
-        <v>868</v>
+        <v>854</v>
       </c>
     </row>
     <row r="348" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A348" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="B348" t="s">
-        <v>857</v>
+        <v>828</v>
       </c>
       <c r="C348">
         <v>2</v>
@@ -16290,15 +16366,15 @@
         <v>0</v>
       </c>
       <c r="E348" t="s">
-        <v>869</v>
+        <v>855</v>
       </c>
     </row>
     <row r="349" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A349" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="B349" t="s">
-        <v>857</v>
+        <v>828</v>
       </c>
       <c r="C349">
         <v>3</v>
@@ -16307,32 +16383,32 @@
         <v>0</v>
       </c>
       <c r="E349" t="s">
-        <v>870</v>
+        <v>856</v>
       </c>
     </row>
     <row r="350" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A350" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="B350" t="s">
-        <v>859</v>
+        <v>857</v>
       </c>
       <c r="C350">
         <v>1</v>
       </c>
       <c r="D350" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E350" t="s">
-        <v>320</v>
+        <v>868</v>
       </c>
     </row>
     <row r="351" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A351" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="B351" t="s">
-        <v>859</v>
+        <v>857</v>
       </c>
       <c r="C351">
         <v>2</v>
@@ -16341,15 +16417,15 @@
         <v>0</v>
       </c>
       <c r="E351" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
     </row>
     <row r="352" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A352" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="B352" t="s">
-        <v>859</v>
+        <v>857</v>
       </c>
       <c r="C352">
         <v>3</v>
@@ -16358,15 +16434,15 @@
         <v>0</v>
       </c>
       <c r="E352" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
     </row>
     <row r="353" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A353" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="B353" t="s">
-        <v>861</v>
+        <v>859</v>
       </c>
       <c r="C353">
         <v>1</v>
@@ -16380,10 +16456,10 @@
     </row>
     <row r="354" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A354" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="B354" t="s">
-        <v>861</v>
+        <v>859</v>
       </c>
       <c r="C354">
         <v>2</v>
@@ -16392,15 +16468,15 @@
         <v>0</v>
       </c>
       <c r="E354" t="s">
-        <v>873</v>
+        <v>871</v>
       </c>
     </row>
     <row r="355" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A355" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="B355" t="s">
-        <v>861</v>
+        <v>859</v>
       </c>
       <c r="C355">
         <v>3</v>
@@ -16409,15 +16485,15 @@
         <v>0</v>
       </c>
       <c r="E355" t="s">
-        <v>874</v>
+        <v>872</v>
       </c>
     </row>
     <row r="356" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A356" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="B356" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
       <c r="C356">
         <v>1</v>
@@ -16431,10 +16507,10 @@
     </row>
     <row r="357" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A357" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="B357" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
       <c r="C357">
         <v>2</v>
@@ -16443,15 +16519,15 @@
         <v>0</v>
       </c>
       <c r="E357" t="s">
-        <v>875</v>
+        <v>873</v>
       </c>
     </row>
     <row r="358" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A358" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="B358" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
       <c r="C358">
         <v>3</v>
@@ -16460,32 +16536,32 @@
         <v>0</v>
       </c>
       <c r="E358" t="s">
-        <v>876</v>
+        <v>874</v>
       </c>
     </row>
     <row r="359" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A359" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="B359" t="s">
-        <v>865</v>
+        <v>863</v>
       </c>
       <c r="C359">
         <v>1</v>
       </c>
       <c r="D359" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E359" t="s">
-        <v>877</v>
+        <v>320</v>
       </c>
     </row>
     <row r="360" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A360" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="B360" t="s">
-        <v>865</v>
+        <v>863</v>
       </c>
       <c r="C360">
         <v>2</v>
@@ -16494,15 +16570,15 @@
         <v>0</v>
       </c>
       <c r="E360" t="s">
-        <v>878</v>
+        <v>875</v>
       </c>
     </row>
     <row r="361" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A361" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="B361" t="s">
-        <v>865</v>
+        <v>863</v>
       </c>
       <c r="C361">
         <v>3</v>
@@ -16511,49 +16587,49 @@
         <v>0</v>
       </c>
       <c r="E361" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
     </row>
     <row r="362" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A362" t="s">
-        <v>314</v>
+        <v>819</v>
       </c>
       <c r="B362" t="s">
-        <v>315</v>
+        <v>865</v>
       </c>
       <c r="C362">
         <v>1</v>
       </c>
       <c r="D362" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E362" t="s">
-        <v>320</v>
+        <v>877</v>
       </c>
     </row>
     <row r="363" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A363" t="s">
-        <v>314</v>
+        <v>819</v>
       </c>
       <c r="B363" t="s">
-        <v>315</v>
+        <v>865</v>
       </c>
       <c r="C363">
         <v>2</v>
       </c>
       <c r="D363" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E363" t="s">
-        <v>58</v>
+        <v>878</v>
       </c>
     </row>
     <row r="364" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A364" t="s">
-        <v>314</v>
+        <v>819</v>
       </c>
       <c r="B364" t="s">
-        <v>315</v>
+        <v>865</v>
       </c>
       <c r="C364">
         <v>3</v>
@@ -16562,15 +16638,15 @@
         <v>0</v>
       </c>
       <c r="E364" t="s">
-        <v>321</v>
+        <v>879</v>
       </c>
     </row>
     <row r="365" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A365" t="s">
-        <v>880</v>
+        <v>314</v>
       </c>
       <c r="B365" t="s">
-        <v>467</v>
+        <v>315</v>
       </c>
       <c r="C365">
         <v>1</v>
@@ -16584,27 +16660,27 @@
     </row>
     <row r="366" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A366" t="s">
-        <v>880</v>
+        <v>314</v>
       </c>
       <c r="B366" t="s">
-        <v>467</v>
+        <v>315</v>
       </c>
       <c r="C366">
         <v>2</v>
       </c>
       <c r="D366" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E366" t="s">
-        <v>950</v>
+        <v>58</v>
       </c>
     </row>
     <row r="367" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A367" t="s">
-        <v>880</v>
+        <v>314</v>
       </c>
       <c r="B367" t="s">
-        <v>467</v>
+        <v>315</v>
       </c>
       <c r="C367">
         <v>3</v>
@@ -16613,32 +16689,32 @@
         <v>0</v>
       </c>
       <c r="E367" t="s">
-        <v>951</v>
+        <v>321</v>
       </c>
     </row>
     <row r="368" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A368" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="B368" t="s">
-        <v>905</v>
+        <v>467</v>
       </c>
       <c r="C368">
         <v>1</v>
       </c>
       <c r="D368" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E368" t="s">
-        <v>952</v>
+        <v>320</v>
       </c>
     </row>
     <row r="369" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A369" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="B369" t="s">
-        <v>905</v>
+        <v>467</v>
       </c>
       <c r="C369">
         <v>2</v>
@@ -16647,15 +16723,15 @@
         <v>0</v>
       </c>
       <c r="E369" t="s">
-        <v>953</v>
+        <v>950</v>
       </c>
     </row>
     <row r="370" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A370" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="B370" t="s">
-        <v>905</v>
+        <v>467</v>
       </c>
       <c r="C370">
         <v>3</v>
@@ -16664,32 +16740,32 @@
         <v>0</v>
       </c>
       <c r="E370" t="s">
-        <v>954</v>
+        <v>951</v>
       </c>
     </row>
     <row r="371" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A371" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="B371" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="C371">
         <v>1</v>
       </c>
       <c r="D371" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E371" t="s">
-        <v>302</v>
+        <v>952</v>
       </c>
     </row>
     <row r="372" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A372" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="B372" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="C372">
         <v>2</v>
@@ -16698,15 +16774,15 @@
         <v>0</v>
       </c>
       <c r="E372" t="s">
-        <v>955</v>
+        <v>953</v>
       </c>
     </row>
     <row r="373" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A373" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="B373" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="C373">
         <v>3</v>
@@ -16715,32 +16791,32 @@
         <v>0</v>
       </c>
       <c r="E373" t="s">
-        <v>956</v>
+        <v>954</v>
       </c>
     </row>
     <row r="374" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A374" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="B374" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="C374">
         <v>1</v>
       </c>
       <c r="D374" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E374" t="s">
-        <v>957</v>
+        <v>302</v>
       </c>
     </row>
     <row r="375" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A375" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="B375" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="C375">
         <v>2</v>
@@ -16749,15 +16825,15 @@
         <v>0</v>
       </c>
       <c r="E375" t="s">
-        <v>958</v>
+        <v>955</v>
       </c>
     </row>
     <row r="376" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A376" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="B376" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="C376">
         <v>3</v>
@@ -16766,32 +16842,32 @@
         <v>0</v>
       </c>
       <c r="E376" t="s">
-        <v>959</v>
+        <v>956</v>
       </c>
     </row>
     <row r="377" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A377" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="B377" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="C377">
         <v>1</v>
       </c>
       <c r="D377" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E377" t="s">
-        <v>320</v>
+        <v>957</v>
       </c>
     </row>
     <row r="378" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A378" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="B378" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="C378">
         <v>2</v>
@@ -16800,15 +16876,15 @@
         <v>0</v>
       </c>
       <c r="E378" t="s">
-        <v>960</v>
+        <v>958</v>
       </c>
     </row>
     <row r="379" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A379" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="B379" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="C379">
         <v>3</v>
@@ -16817,15 +16893,15 @@
         <v>0</v>
       </c>
       <c r="E379" t="s">
-        <v>961</v>
+        <v>959</v>
       </c>
     </row>
     <row r="380" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A380" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="B380" t="s">
-        <v>910</v>
+        <v>908</v>
       </c>
       <c r="C380">
         <v>1</v>
@@ -16839,10 +16915,10 @@
     </row>
     <row r="381" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A381" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="B381" t="s">
-        <v>910</v>
+        <v>908</v>
       </c>
       <c r="C381">
         <v>2</v>
@@ -16851,15 +16927,15 @@
         <v>0</v>
       </c>
       <c r="E381" t="s">
-        <v>962</v>
+        <v>960</v>
       </c>
     </row>
     <row r="382" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A382" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="B382" t="s">
-        <v>910</v>
+        <v>908</v>
       </c>
       <c r="C382">
         <v>3</v>
@@ -16868,32 +16944,32 @@
         <v>0</v>
       </c>
       <c r="E382" t="s">
-        <v>963</v>
+        <v>961</v>
       </c>
     </row>
     <row r="383" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A383" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="B383" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="C383">
         <v>1</v>
       </c>
       <c r="D383" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E383" t="s">
-        <v>964</v>
+        <v>320</v>
       </c>
     </row>
     <row r="384" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A384" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="B384" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="C384">
         <v>2</v>
@@ -16902,15 +16978,15 @@
         <v>0</v>
       </c>
       <c r="E384" t="s">
-        <v>966</v>
+        <v>962</v>
       </c>
     </row>
     <row r="385" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A385" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="B385" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="C385">
         <v>3</v>
@@ -16919,32 +16995,32 @@
         <v>0</v>
       </c>
       <c r="E385" t="s">
-        <v>965</v>
+        <v>963</v>
       </c>
     </row>
     <row r="386" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A386" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="B386" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="C386">
         <v>1</v>
       </c>
       <c r="D386" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E386" t="s">
-        <v>82</v>
+        <v>964</v>
       </c>
     </row>
     <row r="387" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A387" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="B387" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="C387">
         <v>2</v>
@@ -16953,15 +17029,15 @@
         <v>0</v>
       </c>
       <c r="E387" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
     </row>
     <row r="388" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A388" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="B388" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="C388">
         <v>3</v>
@@ -16970,15 +17046,15 @@
         <v>0</v>
       </c>
       <c r="E388" t="s">
-        <v>968</v>
+        <v>965</v>
       </c>
     </row>
     <row r="389" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A389" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="B389" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="C389">
         <v>1</v>
@@ -16987,15 +17063,15 @@
         <v>1</v>
       </c>
       <c r="E389" t="s">
-        <v>320</v>
+        <v>82</v>
       </c>
     </row>
     <row r="390" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A390" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="B390" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="C390">
         <v>2</v>
@@ -17004,15 +17080,15 @@
         <v>0</v>
       </c>
       <c r="E390" t="s">
-        <v>975</v>
+        <v>967</v>
       </c>
     </row>
     <row r="391" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A391" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="B391" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="C391">
         <v>3</v>
@@ -17021,15 +17097,15 @@
         <v>0</v>
       </c>
       <c r="E391" t="s">
-        <v>976</v>
+        <v>968</v>
       </c>
     </row>
     <row r="392" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A392" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="B392" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="C392">
         <v>1</v>
@@ -17043,10 +17119,10 @@
     </row>
     <row r="393" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A393" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="B393" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="C393">
         <v>2</v>
@@ -17055,15 +17131,15 @@
         <v>0</v>
       </c>
       <c r="E393" t="s">
-        <v>977</v>
+        <v>975</v>
       </c>
     </row>
     <row r="394" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A394" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="B394" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="C394">
         <v>3</v>
@@ -17072,15 +17148,15 @@
         <v>0</v>
       </c>
       <c r="E394" t="s">
-        <v>978</v>
+        <v>976</v>
       </c>
     </row>
     <row r="395" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A395" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="B395" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="C395">
         <v>1</v>
@@ -17094,10 +17170,10 @@
     </row>
     <row r="396" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A396" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="B396" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="C396">
         <v>2</v>
@@ -17106,15 +17182,15 @@
         <v>0</v>
       </c>
       <c r="E396" t="s">
-        <v>979</v>
+        <v>977</v>
       </c>
     </row>
     <row r="397" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A397" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="B397" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="C397">
         <v>3</v>
@@ -17123,15 +17199,15 @@
         <v>0</v>
       </c>
       <c r="E397" t="s">
-        <v>980</v>
+        <v>978</v>
       </c>
     </row>
     <row r="398" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A398" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="B398" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="C398">
         <v>1</v>
@@ -17145,10 +17221,10 @@
     </row>
     <row r="399" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A399" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="B399" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="C399">
         <v>2</v>
@@ -17157,15 +17233,15 @@
         <v>0</v>
       </c>
       <c r="E399" t="s">
-        <v>981</v>
+        <v>979</v>
       </c>
     </row>
     <row r="400" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A400" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="B400" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="C400">
         <v>3</v>
@@ -17174,15 +17250,15 @@
         <v>0</v>
       </c>
       <c r="E400" t="s">
-        <v>982</v>
+        <v>980</v>
       </c>
     </row>
     <row r="401" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A401" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="B401" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="C401">
         <v>1</v>
@@ -17196,10 +17272,10 @@
     </row>
     <row r="402" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A402" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="B402" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="C402">
         <v>2</v>
@@ -17208,15 +17284,15 @@
         <v>0</v>
       </c>
       <c r="E402" t="s">
-        <v>983</v>
+        <v>981</v>
       </c>
     </row>
     <row r="403" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A403" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="B403" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="C403">
         <v>3</v>
@@ -17225,15 +17301,15 @@
         <v>0</v>
       </c>
       <c r="E403" t="s">
-        <v>984</v>
+        <v>982</v>
       </c>
     </row>
     <row r="404" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A404" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="B404" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="C404">
         <v>1</v>
@@ -17242,15 +17318,15 @@
         <v>1</v>
       </c>
       <c r="E404" t="s">
-        <v>53</v>
+        <v>320</v>
       </c>
     </row>
     <row r="405" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A405" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="B405" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="C405">
         <v>2</v>
@@ -17259,15 +17335,15 @@
         <v>0</v>
       </c>
       <c r="E405" t="s">
-        <v>985</v>
+        <v>983</v>
       </c>
     </row>
     <row r="406" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A406" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="B406" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="C406">
         <v>3</v>
@@ -17276,32 +17352,32 @@
         <v>0</v>
       </c>
       <c r="E406" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
     </row>
     <row r="407" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A407" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="B407" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="C407">
         <v>1</v>
       </c>
       <c r="D407" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E407" t="s">
-        <v>987</v>
+        <v>53</v>
       </c>
     </row>
     <row r="408" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A408" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="B408" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="C408">
         <v>2</v>
@@ -17310,15 +17386,15 @@
         <v>0</v>
       </c>
       <c r="E408" t="s">
-        <v>988</v>
+        <v>985</v>
       </c>
     </row>
     <row r="409" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A409" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="B409" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="C409">
         <v>3</v>
@@ -17327,15 +17403,15 @@
         <v>0</v>
       </c>
       <c r="E409" t="s">
-        <v>989</v>
+        <v>986</v>
       </c>
     </row>
     <row r="410" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A410" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="B410" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="C410">
         <v>1</v>
@@ -17344,15 +17420,15 @@
         <v>0</v>
       </c>
       <c r="E410" t="s">
-        <v>990</v>
+        <v>987</v>
       </c>
     </row>
     <row r="411" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A411" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="B411" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="C411">
         <v>2</v>
@@ -17361,15 +17437,15 @@
         <v>0</v>
       </c>
       <c r="E411" t="s">
-        <v>991</v>
+        <v>988</v>
       </c>
     </row>
     <row r="412" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A412" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="B412" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="C412">
         <v>3</v>
@@ -17378,15 +17454,15 @@
         <v>0</v>
       </c>
       <c r="E412" t="s">
-        <v>992</v>
+        <v>989</v>
       </c>
     </row>
     <row r="413" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A413" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="B413" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="C413">
         <v>1</v>
@@ -17395,15 +17471,15 @@
         <v>0</v>
       </c>
       <c r="E413" t="s">
-        <v>993</v>
+        <v>990</v>
       </c>
     </row>
     <row r="414" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A414" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="B414" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="C414">
         <v>2</v>
@@ -17412,15 +17488,15 @@
         <v>0</v>
       </c>
       <c r="E414" t="s">
-        <v>994</v>
+        <v>991</v>
       </c>
     </row>
     <row r="415" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A415" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="B415" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="C415">
         <v>3</v>
@@ -17429,15 +17505,15 @@
         <v>0</v>
       </c>
       <c r="E415" t="s">
-        <v>995</v>
+        <v>992</v>
       </c>
     </row>
     <row r="416" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A416" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="B416" t="s">
-        <v>247</v>
+        <v>921</v>
       </c>
       <c r="C416">
         <v>1</v>
@@ -17446,15 +17522,15 @@
         <v>0</v>
       </c>
       <c r="E416" t="s">
-        <v>1077</v>
+        <v>993</v>
       </c>
     </row>
     <row r="417" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A417" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="B417" t="s">
-        <v>247</v>
+        <v>921</v>
       </c>
       <c r="C417">
         <v>2</v>
@@ -17463,15 +17539,15 @@
         <v>0</v>
       </c>
       <c r="E417" t="s">
-        <v>1077</v>
+        <v>994</v>
       </c>
     </row>
     <row r="418" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A418" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="B418" t="s">
-        <v>247</v>
+        <v>921</v>
       </c>
       <c r="C418">
         <v>3</v>
@@ -17480,15 +17556,15 @@
         <v>0</v>
       </c>
       <c r="E418" t="s">
-        <v>1077</v>
+        <v>995</v>
       </c>
     </row>
     <row r="419" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A419" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="B419" t="s">
-        <v>1019</v>
+        <v>247</v>
       </c>
       <c r="C419">
         <v>1</v>
@@ -17497,15 +17573,15 @@
         <v>0</v>
       </c>
       <c r="E419" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="420" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A420" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="B420" t="s">
-        <v>1019</v>
+        <v>247</v>
       </c>
       <c r="C420">
         <v>2</v>
@@ -17514,15 +17590,15 @@
         <v>0</v>
       </c>
       <c r="E420" t="s">
-        <v>1079</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="421" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A421" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="B421" t="s">
-        <v>1019</v>
+        <v>247</v>
       </c>
       <c r="C421">
         <v>3</v>
@@ -17531,15 +17607,15 @@
         <v>0</v>
       </c>
       <c r="E421" t="s">
-        <v>1080</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="422" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A422" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="B422" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="C422">
         <v>1</v>
@@ -17548,15 +17624,15 @@
         <v>0</v>
       </c>
       <c r="E422" t="s">
-        <v>1081</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="423" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A423" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="B423" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="C423">
         <v>2</v>
@@ -17565,15 +17641,15 @@
         <v>0</v>
       </c>
       <c r="E423" t="s">
-        <v>1082</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="424" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A424" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="B424" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="C424">
         <v>3</v>
@@ -17582,15 +17658,15 @@
         <v>0</v>
       </c>
       <c r="E424" t="s">
-        <v>1083</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="425" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A425" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="B425" t="s">
-        <v>1023</v>
+        <v>1021</v>
       </c>
       <c r="C425">
         <v>1</v>
@@ -17599,15 +17675,15 @@
         <v>0</v>
       </c>
       <c r="E425" t="s">
-        <v>1084</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="426" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A426" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="B426" t="s">
-        <v>1023</v>
+        <v>1021</v>
       </c>
       <c r="C426">
         <v>2</v>
@@ -17616,15 +17692,15 @@
         <v>0</v>
       </c>
       <c r="E426" t="s">
-        <v>1085</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="427" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A427" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="B427" t="s">
-        <v>1023</v>
+        <v>1021</v>
       </c>
       <c r="C427">
         <v>3</v>
@@ -17633,15 +17709,15 @@
         <v>0</v>
       </c>
       <c r="E427" t="s">
-        <v>1086</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="428" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A428" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="B428" t="s">
-        <v>1025</v>
+        <v>1023</v>
       </c>
       <c r="C428">
         <v>1</v>
@@ -17650,15 +17726,15 @@
         <v>0</v>
       </c>
       <c r="E428" t="s">
-        <v>1087</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="429" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A429" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="B429" t="s">
-        <v>1025</v>
+        <v>1023</v>
       </c>
       <c r="C429">
         <v>2</v>
@@ -17667,15 +17743,15 @@
         <v>0</v>
       </c>
       <c r="E429" t="s">
-        <v>1088</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="430" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A430" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="B430" t="s">
-        <v>1025</v>
+        <v>1023</v>
       </c>
       <c r="C430">
         <v>3</v>
@@ -17684,15 +17760,15 @@
         <v>0</v>
       </c>
       <c r="E430" t="s">
-        <v>1089</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="431" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A431" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="B431" t="s">
-        <v>1027</v>
+        <v>1025</v>
       </c>
       <c r="C431">
         <v>1</v>
@@ -17701,15 +17777,15 @@
         <v>0</v>
       </c>
       <c r="E431" t="s">
-        <v>1090</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="432" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A432" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="B432" t="s">
-        <v>1027</v>
+        <v>1025</v>
       </c>
       <c r="C432">
         <v>2</v>
@@ -17718,15 +17794,15 @@
         <v>0</v>
       </c>
       <c r="E432" t="s">
-        <v>1091</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="433" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A433" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="B433" t="s">
-        <v>1027</v>
+        <v>1025</v>
       </c>
       <c r="C433">
         <v>3</v>
@@ -17735,15 +17811,15 @@
         <v>0</v>
       </c>
       <c r="E433" t="s">
-        <v>1092</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="434" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A434" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="B434" t="s">
-        <v>1029</v>
+        <v>1027</v>
       </c>
       <c r="C434">
         <v>1</v>
@@ -17752,15 +17828,15 @@
         <v>0</v>
       </c>
       <c r="E434" t="s">
-        <v>1093</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="435" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A435" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="B435" t="s">
-        <v>1029</v>
+        <v>1027</v>
       </c>
       <c r="C435">
         <v>2</v>
@@ -17769,15 +17845,15 @@
         <v>0</v>
       </c>
       <c r="E435" t="s">
-        <v>1094</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="436" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A436" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="B436" t="s">
-        <v>1029</v>
+        <v>1027</v>
       </c>
       <c r="C436">
         <v>3</v>
@@ -17786,15 +17862,15 @@
         <v>0</v>
       </c>
       <c r="E436" t="s">
-        <v>1095</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="437" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A437" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="B437" t="s">
-        <v>1031</v>
+        <v>1029</v>
       </c>
       <c r="C437">
         <v>1</v>
@@ -17803,15 +17879,15 @@
         <v>0</v>
       </c>
       <c r="E437" t="s">
-        <v>1096</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="438" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A438" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="B438" t="s">
-        <v>1031</v>
+        <v>1029</v>
       </c>
       <c r="C438">
         <v>2</v>
@@ -17820,15 +17896,15 @@
         <v>0</v>
       </c>
       <c r="E438" t="s">
-        <v>1096</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="439" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A439" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="B439" t="s">
-        <v>1031</v>
+        <v>1029</v>
       </c>
       <c r="C439">
         <v>3</v>
@@ -17837,32 +17913,32 @@
         <v>0</v>
       </c>
       <c r="E439" t="s">
-        <v>1097</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="440" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A440" t="s">
-        <v>76</v>
+        <v>904</v>
       </c>
       <c r="B440" t="s">
-        <v>77</v>
+        <v>1031</v>
       </c>
       <c r="C440">
         <v>1</v>
       </c>
       <c r="D440" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E440" t="s">
-        <v>82</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="441" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A441" t="s">
-        <v>76</v>
+        <v>904</v>
       </c>
       <c r="B441" t="s">
-        <v>77</v>
+        <v>1031</v>
       </c>
       <c r="C441">
         <v>2</v>
@@ -17871,15 +17947,15 @@
         <v>0</v>
       </c>
       <c r="E441" t="s">
-        <v>83</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="442" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A442" t="s">
-        <v>76</v>
+        <v>904</v>
       </c>
       <c r="B442" t="s">
-        <v>77</v>
+        <v>1031</v>
       </c>
       <c r="C442">
         <v>3</v>
@@ -17888,32 +17964,32 @@
         <v>0</v>
       </c>
       <c r="E442" t="s">
-        <v>84</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="443" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A443" t="s">
-        <v>996</v>
+        <v>76</v>
       </c>
       <c r="B443" t="s">
-        <v>1033</v>
+        <v>77</v>
       </c>
       <c r="C443">
         <v>1</v>
       </c>
       <c r="D443" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E443" t="s">
-        <v>1098</v>
+        <v>82</v>
       </c>
     </row>
     <row r="444" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A444" t="s">
-        <v>996</v>
+        <v>76</v>
       </c>
       <c r="B444" t="s">
-        <v>1033</v>
+        <v>77</v>
       </c>
       <c r="C444">
         <v>2</v>
@@ -17922,15 +17998,15 @@
         <v>0</v>
       </c>
       <c r="E444" t="s">
-        <v>1099</v>
+        <v>83</v>
       </c>
     </row>
     <row r="445" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A445" t="s">
-        <v>996</v>
+        <v>76</v>
       </c>
       <c r="B445" t="s">
-        <v>1033</v>
+        <v>77</v>
       </c>
       <c r="C445">
         <v>3</v>
@@ -17939,15 +18015,15 @@
         <v>0</v>
       </c>
       <c r="E445" t="s">
-        <v>1100</v>
+        <v>84</v>
       </c>
     </row>
     <row r="446" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A446" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="B446" t="s">
-        <v>1035</v>
+        <v>1033</v>
       </c>
       <c r="C446">
         <v>1</v>
@@ -17956,15 +18032,15 @@
         <v>0</v>
       </c>
       <c r="E446" t="s">
-        <v>1101</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="447" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A447" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="B447" t="s">
-        <v>1035</v>
+        <v>1033</v>
       </c>
       <c r="C447">
         <v>2</v>
@@ -17973,15 +18049,15 @@
         <v>0</v>
       </c>
       <c r="E447" t="s">
-        <v>1103</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="448" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A448" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="B448" t="s">
-        <v>1035</v>
+        <v>1033</v>
       </c>
       <c r="C448">
         <v>3</v>
@@ -17990,15 +18066,15 @@
         <v>0</v>
       </c>
       <c r="E448" t="s">
-        <v>1102</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="449" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A449" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="B449" t="s">
-        <v>1104</v>
+        <v>1035</v>
       </c>
       <c r="C449">
         <v>1</v>
@@ -18007,15 +18083,15 @@
         <v>0</v>
       </c>
       <c r="E449" t="s">
-        <v>1105</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="450" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A450" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="B450" t="s">
-        <v>1104</v>
+        <v>1035</v>
       </c>
       <c r="C450">
         <v>2</v>
@@ -18024,15 +18100,15 @@
         <v>0</v>
       </c>
       <c r="E450" t="s">
-        <v>1106</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="451" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A451" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="B451" t="s">
-        <v>1104</v>
+        <v>1035</v>
       </c>
       <c r="C451">
         <v>3</v>
@@ -18041,15 +18117,15 @@
         <v>0</v>
       </c>
       <c r="E451" t="s">
-        <v>1107</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="452" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A452" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="B452" t="s">
-        <v>1038</v>
+        <v>1104</v>
       </c>
       <c r="C452">
         <v>1</v>
@@ -18058,15 +18134,15 @@
         <v>0</v>
       </c>
       <c r="E452" t="s">
-        <v>1108</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="453" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A453" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="B453" t="s">
-        <v>1038</v>
+        <v>1104</v>
       </c>
       <c r="C453">
         <v>2</v>
@@ -18075,15 +18151,15 @@
         <v>0</v>
       </c>
       <c r="E453" t="s">
-        <v>1109</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="454" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A454" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="B454" t="s">
-        <v>1038</v>
+        <v>1104</v>
       </c>
       <c r="C454">
         <v>3</v>
@@ -18092,15 +18168,15 @@
         <v>0</v>
       </c>
       <c r="E454" t="s">
-        <v>1110</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="455" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A455" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="B455" t="s">
-        <v>1040</v>
+        <v>1038</v>
       </c>
       <c r="C455">
         <v>1</v>
@@ -18109,15 +18185,15 @@
         <v>0</v>
       </c>
       <c r="E455" t="s">
-        <v>1111</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="456" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A456" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="B456" t="s">
-        <v>1040</v>
+        <v>1038</v>
       </c>
       <c r="C456">
         <v>2</v>
@@ -18126,15 +18202,15 @@
         <v>0</v>
       </c>
       <c r="E456" t="s">
-        <v>1112</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="457" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A457" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="B457" t="s">
-        <v>1040</v>
+        <v>1038</v>
       </c>
       <c r="C457">
         <v>3</v>
@@ -18143,15 +18219,15 @@
         <v>0</v>
       </c>
       <c r="E457" t="s">
-        <v>1113</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="458" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A458" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="B458" t="s">
-        <v>1042</v>
+        <v>1040</v>
       </c>
       <c r="C458">
         <v>1</v>
@@ -18160,15 +18236,15 @@
         <v>0</v>
       </c>
       <c r="E458" t="s">
-        <v>1114</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="459" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A459" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="B459" t="s">
-        <v>1042</v>
+        <v>1040</v>
       </c>
       <c r="C459">
         <v>2</v>
@@ -18177,15 +18253,15 @@
         <v>0</v>
       </c>
       <c r="E459" t="s">
-        <v>1115</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="460" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A460" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="B460" t="s">
-        <v>1042</v>
+        <v>1040</v>
       </c>
       <c r="C460">
         <v>3</v>
@@ -18194,15 +18270,15 @@
         <v>0</v>
       </c>
       <c r="E460" t="s">
-        <v>1116</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="461" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A461" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="B461" t="s">
-        <v>1117</v>
+        <v>1042</v>
       </c>
       <c r="C461">
         <v>1</v>
@@ -18211,15 +18287,15 @@
         <v>0</v>
       </c>
       <c r="E461" t="s">
-        <v>1118</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="462" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A462" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="B462" t="s">
-        <v>1117</v>
+        <v>1042</v>
       </c>
       <c r="C462">
         <v>2</v>
@@ -18228,15 +18304,15 @@
         <v>0</v>
       </c>
       <c r="E462" t="s">
-        <v>1119</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="463" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A463" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="B463" t="s">
-        <v>1117</v>
+        <v>1042</v>
       </c>
       <c r="C463">
         <v>3</v>
@@ -18245,15 +18321,15 @@
         <v>0</v>
       </c>
       <c r="E463" t="s">
-        <v>1120</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="464" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A464" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="B464" t="s">
-        <v>1045</v>
+        <v>1117</v>
       </c>
       <c r="C464">
         <v>1</v>
@@ -18262,15 +18338,15 @@
         <v>0</v>
       </c>
       <c r="E464" t="s">
-        <v>1124</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="465" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A465" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="B465" t="s">
-        <v>1045</v>
+        <v>1117</v>
       </c>
       <c r="C465">
         <v>2</v>
@@ -18279,15 +18355,15 @@
         <v>0</v>
       </c>
       <c r="E465" t="s">
-        <v>1125</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="466" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A466" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="B466" t="s">
-        <v>1045</v>
+        <v>1117</v>
       </c>
       <c r="C466">
         <v>3</v>
@@ -18296,15 +18372,15 @@
         <v>0</v>
       </c>
       <c r="E466" t="s">
-        <v>1126</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="467" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A467" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="B467" t="s">
-        <v>1047</v>
+        <v>1045</v>
       </c>
       <c r="C467">
         <v>1</v>
@@ -18313,15 +18389,15 @@
         <v>0</v>
       </c>
       <c r="E467" t="s">
-        <v>1127</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="468" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A468" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="B468" t="s">
-        <v>1047</v>
+        <v>1045</v>
       </c>
       <c r="C468">
         <v>2</v>
@@ -18330,15 +18406,15 @@
         <v>0</v>
       </c>
       <c r="E468" t="s">
-        <v>1128</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="469" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A469" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="B469" t="s">
-        <v>1047</v>
+        <v>1045</v>
       </c>
       <c r="C469">
         <v>3</v>
@@ -18347,15 +18423,15 @@
         <v>0</v>
       </c>
       <c r="E469" t="s">
-        <v>1129</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="470" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A470" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="B470" t="s">
-        <v>1049</v>
+        <v>1047</v>
       </c>
       <c r="C470">
         <v>1</v>
@@ -18364,15 +18440,15 @@
         <v>0</v>
       </c>
       <c r="E470" t="s">
-        <v>1121</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="471" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A471" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="B471" t="s">
-        <v>1049</v>
+        <v>1047</v>
       </c>
       <c r="C471">
         <v>2</v>
@@ -18381,15 +18457,15 @@
         <v>0</v>
       </c>
       <c r="E471" t="s">
-        <v>1122</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="472" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A472" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="B472" t="s">
-        <v>1049</v>
+        <v>1047</v>
       </c>
       <c r="C472">
         <v>3</v>
@@ -18398,15 +18474,15 @@
         <v>0</v>
       </c>
       <c r="E472" t="s">
-        <v>1123</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="473" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A473" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="B473" t="s">
-        <v>1051</v>
+        <v>1049</v>
       </c>
       <c r="C473">
         <v>1</v>
@@ -18415,15 +18491,15 @@
         <v>0</v>
       </c>
       <c r="E473" t="s">
-        <v>1130</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="474" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A474" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="B474" t="s">
-        <v>1051</v>
+        <v>1049</v>
       </c>
       <c r="C474">
         <v>2</v>
@@ -18432,15 +18508,15 @@
         <v>0</v>
       </c>
       <c r="E474" t="s">
-        <v>223</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="475" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A475" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="B475" t="s">
-        <v>1051</v>
+        <v>1049</v>
       </c>
       <c r="C475">
         <v>3</v>
@@ -18449,15 +18525,15 @@
         <v>0</v>
       </c>
       <c r="E475" t="s">
-        <v>1131</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="476" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A476" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="B476" t="s">
-        <v>1053</v>
+        <v>1051</v>
       </c>
       <c r="C476">
         <v>1</v>
@@ -18466,15 +18542,15 @@
         <v>0</v>
       </c>
       <c r="E476" t="s">
-        <v>1132</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="477" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A477" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="B477" t="s">
-        <v>1053</v>
+        <v>1051</v>
       </c>
       <c r="C477">
         <v>2</v>
@@ -18483,15 +18559,15 @@
         <v>0</v>
       </c>
       <c r="E477" t="s">
-        <v>1133</v>
+        <v>223</v>
       </c>
     </row>
     <row r="478" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A478" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="B478" t="s">
-        <v>1053</v>
+        <v>1051</v>
       </c>
       <c r="C478">
         <v>3</v>
@@ -18500,15 +18576,15 @@
         <v>0</v>
       </c>
       <c r="E478" t="s">
-        <v>1134</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="479" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A479" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="B479" t="s">
-        <v>1055</v>
+        <v>1053</v>
       </c>
       <c r="C479">
         <v>1</v>
@@ -18517,15 +18593,15 @@
         <v>0</v>
       </c>
       <c r="E479" t="s">
-        <v>1135</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="480" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A480" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="B480" t="s">
-        <v>1055</v>
+        <v>1053</v>
       </c>
       <c r="C480">
         <v>2</v>
@@ -18534,15 +18610,15 @@
         <v>0</v>
       </c>
       <c r="E480" t="s">
-        <v>1136</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="481" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A481" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="B481" t="s">
-        <v>1055</v>
+        <v>1053</v>
       </c>
       <c r="C481">
         <v>3</v>
@@ -18551,15 +18627,15 @@
         <v>0</v>
       </c>
       <c r="E481" t="s">
-        <v>1137</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="482" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A482" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="B482" t="s">
-        <v>1017</v>
+        <v>1055</v>
       </c>
       <c r="C482">
         <v>1</v>
@@ -18568,15 +18644,15 @@
         <v>0</v>
       </c>
       <c r="E482" t="s">
-        <v>1138</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="483" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A483" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="B483" t="s">
-        <v>1017</v>
+        <v>1055</v>
       </c>
       <c r="C483">
         <v>2</v>
@@ -18585,15 +18661,15 @@
         <v>0</v>
       </c>
       <c r="E483" t="s">
-        <v>1139</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="484" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A484" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="B484" t="s">
-        <v>1017</v>
+        <v>1055</v>
       </c>
       <c r="C484">
         <v>3</v>
@@ -18602,15 +18678,15 @@
         <v>0</v>
       </c>
       <c r="E484" t="s">
-        <v>1140</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="485" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A485" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="B485" t="s">
-        <v>1156</v>
+        <v>1017</v>
       </c>
       <c r="C485">
         <v>1</v>
@@ -18619,15 +18695,15 @@
         <v>0</v>
       </c>
       <c r="E485" t="s">
-        <v>1211</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="486" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A486" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="B486" t="s">
-        <v>1156</v>
+        <v>1017</v>
       </c>
       <c r="C486">
         <v>2</v>
@@ -18636,15 +18712,15 @@
         <v>0</v>
       </c>
       <c r="E486" t="s">
-        <v>1212</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="487" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A487" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="B487" t="s">
-        <v>1156</v>
+        <v>1017</v>
       </c>
       <c r="C487">
         <v>3</v>
@@ -18653,15 +18729,15 @@
         <v>0</v>
       </c>
       <c r="E487" t="s">
-        <v>1213</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="488" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A488" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="B488" t="s">
-        <v>1159</v>
+        <v>1156</v>
       </c>
       <c r="C488">
         <v>1</v>
@@ -18670,15 +18746,15 @@
         <v>0</v>
       </c>
       <c r="E488" t="s">
-        <v>1214</v>
+        <v>1211</v>
       </c>
     </row>
     <row r="489" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A489" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="B489" t="s">
-        <v>1159</v>
+        <v>1156</v>
       </c>
       <c r="C489">
         <v>2</v>
@@ -18687,15 +18763,15 @@
         <v>0</v>
       </c>
       <c r="E489" t="s">
-        <v>1215</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="490" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A490" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="B490" t="s">
-        <v>1159</v>
+        <v>1156</v>
       </c>
       <c r="C490">
         <v>3</v>
@@ -18704,15 +18780,15 @@
         <v>0</v>
       </c>
       <c r="E490" t="s">
-        <v>1216</v>
+        <v>1213</v>
       </c>
     </row>
     <row r="491" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A491" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="B491" t="s">
-        <v>1161</v>
+        <v>1159</v>
       </c>
       <c r="C491">
         <v>1</v>
@@ -18721,15 +18797,15 @@
         <v>0</v>
       </c>
       <c r="E491" t="s">
-        <v>1217</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="492" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A492" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="B492" t="s">
-        <v>1161</v>
+        <v>1159</v>
       </c>
       <c r="C492">
         <v>2</v>
@@ -18738,15 +18814,15 @@
         <v>0</v>
       </c>
       <c r="E492" t="s">
-        <v>1218</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="493" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A493" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="B493" t="s">
-        <v>1161</v>
+        <v>1159</v>
       </c>
       <c r="C493">
         <v>3</v>
@@ -18755,15 +18831,15 @@
         <v>0</v>
       </c>
       <c r="E493" t="s">
-        <v>63</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="494" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A494" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="B494" t="s">
-        <v>1163</v>
+        <v>1161</v>
       </c>
       <c r="C494">
         <v>1</v>
@@ -18772,15 +18848,15 @@
         <v>0</v>
       </c>
       <c r="E494" t="s">
-        <v>1219</v>
+        <v>1217</v>
       </c>
     </row>
     <row r="495" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A495" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="B495" t="s">
-        <v>1163</v>
+        <v>1161</v>
       </c>
       <c r="C495">
         <v>2</v>
@@ -18789,15 +18865,15 @@
         <v>0</v>
       </c>
       <c r="E495" t="s">
-        <v>1220</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="496" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A496" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="B496" t="s">
-        <v>1163</v>
+        <v>1161</v>
       </c>
       <c r="C496">
         <v>3</v>
@@ -18811,10 +18887,10 @@
     </row>
     <row r="497" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A497" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="B497" t="s">
-        <v>1165</v>
+        <v>1163</v>
       </c>
       <c r="C497">
         <v>1</v>
@@ -18823,15 +18899,15 @@
         <v>0</v>
       </c>
       <c r="E497" t="s">
-        <v>1221</v>
+        <v>1219</v>
       </c>
     </row>
     <row r="498" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A498" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="B498" t="s">
-        <v>1165</v>
+        <v>1163</v>
       </c>
       <c r="C498">
         <v>2</v>
@@ -18840,15 +18916,15 @@
         <v>0</v>
       </c>
       <c r="E498" t="s">
-        <v>1222</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="499" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A499" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="B499" t="s">
-        <v>1165</v>
+        <v>1163</v>
       </c>
       <c r="C499">
         <v>3</v>
@@ -18862,10 +18938,10 @@
     </row>
     <row r="500" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A500" t="s">
-        <v>23</v>
+        <v>1014</v>
       </c>
       <c r="B500" t="s">
-        <v>24</v>
+        <v>1165</v>
       </c>
       <c r="C500">
         <v>1</v>
@@ -18874,15 +18950,15 @@
         <v>0</v>
       </c>
       <c r="E500" t="s">
-        <v>61</v>
+        <v>1221</v>
       </c>
     </row>
     <row r="501" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A501" t="s">
-        <v>23</v>
+        <v>1014</v>
       </c>
       <c r="B501" t="s">
-        <v>24</v>
+        <v>1165</v>
       </c>
       <c r="C501">
         <v>2</v>
@@ -18891,15 +18967,15 @@
         <v>0</v>
       </c>
       <c r="E501" t="s">
-        <v>62</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="502" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A502" t="s">
-        <v>23</v>
+        <v>1014</v>
       </c>
       <c r="B502" t="s">
-        <v>24</v>
+        <v>1165</v>
       </c>
       <c r="C502">
         <v>3</v>
@@ -18913,10 +18989,10 @@
     </row>
     <row r="503" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A503" t="s">
-        <v>1141</v>
+        <v>23</v>
       </c>
       <c r="B503" t="s">
-        <v>1167</v>
+        <v>24</v>
       </c>
       <c r="C503">
         <v>1</v>
@@ -18925,15 +19001,15 @@
         <v>0</v>
       </c>
       <c r="E503" t="s">
-        <v>1223</v>
+        <v>61</v>
       </c>
     </row>
     <row r="504" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A504" t="s">
-        <v>1141</v>
+        <v>23</v>
       </c>
       <c r="B504" t="s">
-        <v>1167</v>
+        <v>24</v>
       </c>
       <c r="C504">
         <v>2</v>
@@ -18942,15 +19018,15 @@
         <v>0</v>
       </c>
       <c r="E504" t="s">
-        <v>1224</v>
+        <v>62</v>
       </c>
     </row>
     <row r="505" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A505" t="s">
-        <v>1141</v>
+        <v>23</v>
       </c>
       <c r="B505" t="s">
-        <v>1167</v>
+        <v>24</v>
       </c>
       <c r="C505">
         <v>3</v>
@@ -18964,27 +19040,27 @@
     </row>
     <row r="506" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A506" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
       <c r="B506" t="s">
-        <v>1169</v>
+        <v>1167</v>
       </c>
       <c r="C506">
         <v>1</v>
       </c>
       <c r="D506" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E506" t="s">
-        <v>1227</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="507" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A507" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
       <c r="B507" t="s">
-        <v>1169</v>
+        <v>1167</v>
       </c>
       <c r="C507">
         <v>2</v>
@@ -18993,15 +19069,15 @@
         <v>0</v>
       </c>
       <c r="E507" t="s">
-        <v>1225</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="508" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A508" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
       <c r="B508" t="s">
-        <v>1169</v>
+        <v>1167</v>
       </c>
       <c r="C508">
         <v>3</v>
@@ -19010,15 +19086,15 @@
         <v>0</v>
       </c>
       <c r="E508" t="s">
-        <v>1226</v>
+        <v>63</v>
       </c>
     </row>
     <row r="509" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A509" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="B509" t="s">
-        <v>1172</v>
+        <v>1169</v>
       </c>
       <c r="C509">
         <v>1</v>
@@ -19032,10 +19108,10 @@
     </row>
     <row r="510" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A510" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="B510" t="s">
-        <v>1172</v>
+        <v>1169</v>
       </c>
       <c r="C510">
         <v>2</v>
@@ -19044,15 +19120,15 @@
         <v>0</v>
       </c>
       <c r="E510" t="s">
-        <v>1228</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="511" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A511" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="B511" t="s">
-        <v>1172</v>
+        <v>1169</v>
       </c>
       <c r="C511">
         <v>3</v>
@@ -19061,32 +19137,32 @@
         <v>0</v>
       </c>
       <c r="E511" t="s">
-        <v>1229</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="512" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A512" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="B512" t="s">
-        <v>1174</v>
+        <v>1172</v>
       </c>
       <c r="C512">
         <v>1</v>
       </c>
       <c r="D512" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E512" t="s">
-        <v>1230</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="513" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A513" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="B513" t="s">
-        <v>1174</v>
+        <v>1172</v>
       </c>
       <c r="C513">
         <v>2</v>
@@ -19095,15 +19171,15 @@
         <v>0</v>
       </c>
       <c r="E513" t="s">
-        <v>1231</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="514" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A514" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="B514" t="s">
-        <v>1174</v>
+        <v>1172</v>
       </c>
       <c r="C514">
         <v>3</v>
@@ -19112,15 +19188,15 @@
         <v>0</v>
       </c>
       <c r="E514" t="s">
-        <v>1232</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="515" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A515" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
       <c r="B515" t="s">
-        <v>1176</v>
+        <v>1174</v>
       </c>
       <c r="C515">
         <v>1</v>
@@ -19129,15 +19205,15 @@
         <v>0</v>
       </c>
       <c r="E515" t="s">
-        <v>1233</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="516" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A516" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
       <c r="B516" t="s">
-        <v>1176</v>
+        <v>1174</v>
       </c>
       <c r="C516">
         <v>2</v>
@@ -19146,15 +19222,15 @@
         <v>0</v>
       </c>
       <c r="E516" t="s">
-        <v>1234</v>
+        <v>1231</v>
       </c>
     </row>
     <row r="517" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A517" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
       <c r="B517" t="s">
-        <v>1176</v>
+        <v>1174</v>
       </c>
       <c r="C517">
         <v>3</v>
@@ -19163,49 +19239,49 @@
         <v>0</v>
       </c>
       <c r="E517" t="s">
-        <v>1235</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="518" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A518" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
       <c r="B518" t="s">
-        <v>1178</v>
+        <v>1176</v>
       </c>
       <c r="C518">
         <v>1</v>
       </c>
       <c r="D518" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E518" t="s">
-        <v>696</v>
+        <v>1233</v>
       </c>
     </row>
     <row r="519" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A519" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
       <c r="B519" t="s">
-        <v>1178</v>
+        <v>1176</v>
       </c>
       <c r="C519">
         <v>2</v>
       </c>
       <c r="D519" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E519" t="s">
-        <v>1227</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="520" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A520" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
       <c r="B520" t="s">
-        <v>1178</v>
+        <v>1176</v>
       </c>
       <c r="C520">
         <v>3</v>
@@ -19214,15 +19290,15 @@
         <v>0</v>
       </c>
       <c r="E520" t="s">
-        <v>1236</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="521" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A521" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
       <c r="B521" t="s">
-        <v>1180</v>
+        <v>1178</v>
       </c>
       <c r="C521">
         <v>1</v>
@@ -19231,32 +19307,32 @@
         <v>1</v>
       </c>
       <c r="E521" t="s">
-        <v>1227</v>
+        <v>696</v>
       </c>
     </row>
     <row r="522" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A522" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
       <c r="B522" t="s">
-        <v>1180</v>
+        <v>1178</v>
       </c>
       <c r="C522">
         <v>2</v>
       </c>
       <c r="D522" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E522" t="s">
-        <v>447</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="523" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A523" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
       <c r="B523" t="s">
-        <v>1180</v>
+        <v>1178</v>
       </c>
       <c r="C523">
         <v>3</v>
@@ -19265,15 +19341,15 @@
         <v>0</v>
       </c>
       <c r="E523" t="s">
-        <v>1237</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="524" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A524" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="B524" t="s">
-        <v>1182</v>
+        <v>1180</v>
       </c>
       <c r="C524">
         <v>1</v>
@@ -19287,10 +19363,10 @@
     </row>
     <row r="525" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A525" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="B525" t="s">
-        <v>1182</v>
+        <v>1180</v>
       </c>
       <c r="C525">
         <v>2</v>
@@ -19299,15 +19375,15 @@
         <v>0</v>
       </c>
       <c r="E525" t="s">
-        <v>1238</v>
+        <v>447</v>
       </c>
     </row>
     <row r="526" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A526" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="B526" t="s">
-        <v>1182</v>
+        <v>1180</v>
       </c>
       <c r="C526">
         <v>3</v>
@@ -19316,32 +19392,32 @@
         <v>0</v>
       </c>
       <c r="E526" t="s">
-        <v>1239</v>
+        <v>1237</v>
       </c>
     </row>
     <row r="527" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A527" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
       <c r="B527" t="s">
-        <v>1184</v>
+        <v>1182</v>
       </c>
       <c r="C527">
         <v>1</v>
       </c>
       <c r="D527" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E527" t="s">
-        <v>1240</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="528" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A528" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
       <c r="B528" t="s">
-        <v>1184</v>
+        <v>1182</v>
       </c>
       <c r="C528">
         <v>2</v>
@@ -19350,15 +19426,15 @@
         <v>0</v>
       </c>
       <c r="E528" t="s">
-        <v>1241</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="529" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A529" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
       <c r="B529" t="s">
-        <v>1184</v>
+        <v>1182</v>
       </c>
       <c r="C529">
         <v>3</v>
@@ -19367,15 +19443,15 @@
         <v>0</v>
       </c>
       <c r="E529" t="s">
-        <v>1242</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="530" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A530" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
       <c r="B530" t="s">
-        <v>1186</v>
+        <v>1184</v>
       </c>
       <c r="C530">
         <v>1</v>
@@ -19384,15 +19460,15 @@
         <v>0</v>
       </c>
       <c r="E530" t="s">
-        <v>1243</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="531" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A531" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
       <c r="B531" t="s">
-        <v>1186</v>
+        <v>1184</v>
       </c>
       <c r="C531">
         <v>2</v>
@@ -19401,15 +19477,15 @@
         <v>0</v>
       </c>
       <c r="E531" t="s">
-        <v>1244</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="532" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A532" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
       <c r="B532" t="s">
-        <v>1186</v>
+        <v>1184</v>
       </c>
       <c r="C532">
         <v>3</v>
@@ -19418,15 +19494,15 @@
         <v>0</v>
       </c>
       <c r="E532" t="s">
-        <v>1245</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="533" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A533" t="s">
-        <v>29</v>
+        <v>1150</v>
       </c>
       <c r="B533" t="s">
-        <v>30</v>
+        <v>1186</v>
       </c>
       <c r="C533">
         <v>1</v>
@@ -19435,15 +19511,15 @@
         <v>0</v>
       </c>
       <c r="E533" t="s">
-        <v>64</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="534" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A534" t="s">
-        <v>29</v>
+        <v>1150</v>
       </c>
       <c r="B534" t="s">
-        <v>30</v>
+        <v>1186</v>
       </c>
       <c r="C534">
         <v>2</v>
@@ -19452,15 +19528,15 @@
         <v>0</v>
       </c>
       <c r="E534" t="s">
-        <v>65</v>
+        <v>1244</v>
       </c>
     </row>
     <row r="535" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A535" t="s">
-        <v>29</v>
+        <v>1150</v>
       </c>
       <c r="B535" t="s">
-        <v>30</v>
+        <v>1186</v>
       </c>
       <c r="C535">
         <v>3</v>
@@ -19469,15 +19545,15 @@
         <v>0</v>
       </c>
       <c r="E535" t="s">
-        <v>66</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="536" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A536" t="s">
-        <v>1151</v>
+        <v>29</v>
       </c>
       <c r="B536" t="s">
-        <v>1188</v>
+        <v>30</v>
       </c>
       <c r="C536">
         <v>1</v>
@@ -19486,15 +19562,15 @@
         <v>0</v>
       </c>
       <c r="E536" t="s">
-        <v>1246</v>
+        <v>64</v>
       </c>
     </row>
     <row r="537" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A537" t="s">
-        <v>1151</v>
+        <v>29</v>
       </c>
       <c r="B537" t="s">
-        <v>1188</v>
+        <v>30</v>
       </c>
       <c r="C537">
         <v>2</v>
@@ -19503,15 +19579,15 @@
         <v>0</v>
       </c>
       <c r="E537" t="s">
-        <v>1247</v>
+        <v>65</v>
       </c>
     </row>
     <row r="538" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A538" t="s">
-        <v>1151</v>
+        <v>29</v>
       </c>
       <c r="B538" t="s">
-        <v>1188</v>
+        <v>30</v>
       </c>
       <c r="C538">
         <v>3</v>
@@ -19520,15 +19596,15 @@
         <v>0</v>
       </c>
       <c r="E538" t="s">
-        <v>1248</v>
+        <v>66</v>
       </c>
     </row>
     <row r="539" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A539" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
       <c r="B539" t="s">
-        <v>1191</v>
+        <v>1188</v>
       </c>
       <c r="C539">
         <v>1</v>
@@ -19537,15 +19613,15 @@
         <v>0</v>
       </c>
       <c r="E539" t="s">
-        <v>1249</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="540" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A540" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
       <c r="B540" t="s">
-        <v>1191</v>
+        <v>1188</v>
       </c>
       <c r="C540">
         <v>2</v>
@@ -19554,15 +19630,15 @@
         <v>0</v>
       </c>
       <c r="E540" t="s">
-        <v>1250</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="541" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A541" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
       <c r="B541" t="s">
-        <v>1191</v>
+        <v>1188</v>
       </c>
       <c r="C541">
         <v>3</v>
@@ -19571,15 +19647,15 @@
         <v>0</v>
       </c>
       <c r="E541" t="s">
-        <v>1251</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="542" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A542" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
       <c r="B542" t="s">
-        <v>1193</v>
+        <v>1191</v>
       </c>
       <c r="C542">
         <v>1</v>
@@ -19588,15 +19664,15 @@
         <v>0</v>
       </c>
       <c r="E542" t="s">
-        <v>1252</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="543" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A543" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
       <c r="B543" t="s">
-        <v>1193</v>
+        <v>1191</v>
       </c>
       <c r="C543">
         <v>2</v>
@@ -19605,15 +19681,15 @@
         <v>0</v>
       </c>
       <c r="E543" t="s">
-        <v>1253</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="544" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A544" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
       <c r="B544" t="s">
-        <v>1193</v>
+        <v>1191</v>
       </c>
       <c r="C544">
         <v>3</v>
@@ -19622,15 +19698,15 @@
         <v>0</v>
       </c>
       <c r="E544" t="s">
-        <v>1254</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="545" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A545" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="B545" t="s">
-        <v>1194</v>
+        <v>1193</v>
       </c>
       <c r="C545">
         <v>1</v>
@@ -19639,15 +19715,15 @@
         <v>0</v>
       </c>
       <c r="E545" t="s">
-        <v>1255</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="546" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A546" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="B546" t="s">
-        <v>1194</v>
+        <v>1193</v>
       </c>
       <c r="C546">
         <v>2</v>
@@ -19656,15 +19732,15 @@
         <v>0</v>
       </c>
       <c r="E546" t="s">
-        <v>1256</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="547" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A547" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="B547" t="s">
-        <v>1194</v>
+        <v>1193</v>
       </c>
       <c r="C547">
         <v>3</v>
@@ -19673,15 +19749,15 @@
         <v>0</v>
       </c>
       <c r="E547" t="s">
-        <v>1257</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="548" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A548" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
       <c r="B548" t="s">
-        <v>1158</v>
+        <v>1194</v>
       </c>
       <c r="C548">
         <v>1</v>
@@ -19690,15 +19766,15 @@
         <v>0</v>
       </c>
       <c r="E548" t="s">
-        <v>1258</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="549" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A549" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
       <c r="B549" t="s">
-        <v>1158</v>
+        <v>1194</v>
       </c>
       <c r="C549">
         <v>2</v>
@@ -19707,15 +19783,15 @@
         <v>0</v>
       </c>
       <c r="E549" t="s">
-        <v>1259</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="550" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A550" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
       <c r="B550" t="s">
-        <v>1158</v>
+        <v>1194</v>
       </c>
       <c r="C550">
         <v>3</v>
@@ -19724,15 +19800,15 @@
         <v>0</v>
       </c>
       <c r="E550" t="s">
-        <v>1260</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="551" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A551" t="s">
-        <v>36</v>
+        <v>1155</v>
       </c>
       <c r="B551" t="s">
-        <v>37</v>
+        <v>1158</v>
       </c>
       <c r="C551">
         <v>1</v>
@@ -19741,15 +19817,15 @@
         <v>0</v>
       </c>
       <c r="E551" t="s">
-        <v>67</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="552" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A552" t="s">
-        <v>36</v>
+        <v>1155</v>
       </c>
       <c r="B552" t="s">
-        <v>37</v>
+        <v>1158</v>
       </c>
       <c r="C552">
         <v>2</v>
@@ -19758,15 +19834,15 @@
         <v>0</v>
       </c>
       <c r="E552" t="s">
-        <v>68</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="553" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A553" t="s">
-        <v>36</v>
+        <v>1155</v>
       </c>
       <c r="B553" t="s">
-        <v>37</v>
+        <v>1158</v>
       </c>
       <c r="C553">
         <v>3</v>
@@ -19775,6 +19851,57 @@
         <v>0</v>
       </c>
       <c r="E553" t="s">
+        <v>1260</v>
+      </c>
+    </row>
+    <row r="554" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A554" t="s">
+        <v>36</v>
+      </c>
+      <c r="B554" t="s">
+        <v>37</v>
+      </c>
+      <c r="C554">
+        <v>1</v>
+      </c>
+      <c r="D554" t="b">
+        <v>0</v>
+      </c>
+      <c r="E554" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="555" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A555" t="s">
+        <v>36</v>
+      </c>
+      <c r="B555" t="s">
+        <v>37</v>
+      </c>
+      <c r="C555">
+        <v>2</v>
+      </c>
+      <c r="D555" t="b">
+        <v>0</v>
+      </c>
+      <c r="E555" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="556" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A556" t="s">
+        <v>36</v>
+      </c>
+      <c r="B556" t="s">
+        <v>37</v>
+      </c>
+      <c r="C556">
+        <v>3</v>
+      </c>
+      <c r="D556" t="b">
+        <v>0</v>
+      </c>
+      <c r="E556" t="s">
         <v>69</v>
       </c>
     </row>

--- a/data/Fate-Spreadsheet.xlsx
+++ b/data/Fate-Spreadsheet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pixel\Documents\Projects\Fate-Wiki\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFFB8807-7EA1-489A-B2D9-DACB6B2DF62F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1173C242-17D1-4877-8E86-FD83C74B9C4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{B05E798F-9EF6-4508-A0A4-311D06661AED}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="2" xr2:uid="{B05E798F-9EF6-4508-A0A4-311D06661AED}"/>
   </bookViews>
   <sheets>
     <sheet name="Servants" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3373" uniqueCount="1271">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3641" uniqueCount="1472">
   <si>
     <t>servant_id</t>
   </si>
@@ -3856,6 +3856,609 @@
   </si>
   <si>
     <t>form_magic</t>
+  </si>
+  <si>
+    <t>master_id</t>
+  </si>
+  <si>
+    <t>M001</t>
+  </si>
+  <si>
+    <t>M002</t>
+  </si>
+  <si>
+    <t>M003</t>
+  </si>
+  <si>
+    <t>M004</t>
+  </si>
+  <si>
+    <t>M005</t>
+  </si>
+  <si>
+    <t>M006</t>
+  </si>
+  <si>
+    <t>M007</t>
+  </si>
+  <si>
+    <t>M008</t>
+  </si>
+  <si>
+    <t>M009</t>
+  </si>
+  <si>
+    <t>M010</t>
+  </si>
+  <si>
+    <t>M011</t>
+  </si>
+  <si>
+    <t>M012</t>
+  </si>
+  <si>
+    <t>M013</t>
+  </si>
+  <si>
+    <t>M014</t>
+  </si>
+  <si>
+    <t>M015</t>
+  </si>
+  <si>
+    <t>M016</t>
+  </si>
+  <si>
+    <t>M017</t>
+  </si>
+  <si>
+    <t>M018</t>
+  </si>
+  <si>
+    <t>M019</t>
+  </si>
+  <si>
+    <t>M020</t>
+  </si>
+  <si>
+    <t>M021</t>
+  </si>
+  <si>
+    <t>M022</t>
+  </si>
+  <si>
+    <t>M023</t>
+  </si>
+  <si>
+    <t>M024</t>
+  </si>
+  <si>
+    <t>M025</t>
+  </si>
+  <si>
+    <t>M026</t>
+  </si>
+  <si>
+    <t>M027</t>
+  </si>
+  <si>
+    <t>M028</t>
+  </si>
+  <si>
+    <t>M029</t>
+  </si>
+  <si>
+    <t>M030</t>
+  </si>
+  <si>
+    <t>M031</t>
+  </si>
+  <si>
+    <t>M032</t>
+  </si>
+  <si>
+    <t>M033</t>
+  </si>
+  <si>
+    <t>M034</t>
+  </si>
+  <si>
+    <t>M035</t>
+  </si>
+  <si>
+    <t>M036</t>
+  </si>
+  <si>
+    <t>M037</t>
+  </si>
+  <si>
+    <t>M038</t>
+  </si>
+  <si>
+    <t>M039</t>
+  </si>
+  <si>
+    <t>M040</t>
+  </si>
+  <si>
+    <t>M041</t>
+  </si>
+  <si>
+    <t>M042</t>
+  </si>
+  <si>
+    <t>M043</t>
+  </si>
+  <si>
+    <t>M044</t>
+  </si>
+  <si>
+    <t>M045</t>
+  </si>
+  <si>
+    <t>M046</t>
+  </si>
+  <si>
+    <t>M047</t>
+  </si>
+  <si>
+    <t>M048</t>
+  </si>
+  <si>
+    <t>M049</t>
+  </si>
+  <si>
+    <t>M050</t>
+  </si>
+  <si>
+    <t>M051</t>
+  </si>
+  <si>
+    <t>M052</t>
+  </si>
+  <si>
+    <t>M053</t>
+  </si>
+  <si>
+    <t>M054</t>
+  </si>
+  <si>
+    <t>M055</t>
+  </si>
+  <si>
+    <t>M056</t>
+  </si>
+  <si>
+    <t>M057</t>
+  </si>
+  <si>
+    <t>M058</t>
+  </si>
+  <si>
+    <t>M059</t>
+  </si>
+  <si>
+    <t>M060</t>
+  </si>
+  <si>
+    <t>M061</t>
+  </si>
+  <si>
+    <t>M062</t>
+  </si>
+  <si>
+    <t>M063</t>
+  </si>
+  <si>
+    <t>M064</t>
+  </si>
+  <si>
+    <t>M065</t>
+  </si>
+  <si>
+    <t>M066</t>
+  </si>
+  <si>
+    <t>master_name</t>
+  </si>
+  <si>
+    <t>mechanic</t>
+  </si>
+  <si>
+    <t>Tohsaka Rin</t>
+  </si>
+  <si>
+    <t>Combat</t>
+  </si>
+  <si>
+    <t>Utility</t>
+  </si>
+  <si>
+    <t>Mana Gain</t>
+  </si>
+  <si>
+    <t>End Game</t>
+  </si>
+  <si>
+    <t>VP Gain</t>
+  </si>
+  <si>
+    <t>Matou Shinji</t>
+  </si>
+  <si>
+    <t>Matou Sakura</t>
+  </si>
+  <si>
+    <t>Illyasviel Von Einzbern</t>
+  </si>
+  <si>
+    <t>Kuzuki Soichirou</t>
+  </si>
+  <si>
+    <t>Kotomine Kirei</t>
+  </si>
+  <si>
+    <t>Matou Zouken</t>
+  </si>
+  <si>
+    <t>Fujimura Taiga</t>
+  </si>
+  <si>
+    <t>Bazett Fraga McRemitz</t>
+  </si>
+  <si>
+    <t>Caren Hortensia</t>
+  </si>
+  <si>
+    <t>Emiya Kiritsugu</t>
+  </si>
+  <si>
+    <t>Irisviel von Einzbern</t>
+  </si>
+  <si>
+    <t>Tohsaka Tokiomi</t>
+  </si>
+  <si>
+    <t>Matou Kariya</t>
+  </si>
+  <si>
+    <t>Waver Velvet</t>
+  </si>
+  <si>
+    <t>Kayneth Archibald</t>
+  </si>
+  <si>
+    <t>Uryuu Ryuunosuke</t>
+  </si>
+  <si>
+    <t>Kishinami Hakuno (Male)</t>
+  </si>
+  <si>
+    <t>Kishinami Hakuno (Female)</t>
+  </si>
+  <si>
+    <t>Rani VIII</t>
+  </si>
+  <si>
+    <t>Jinako Carigiri</t>
+  </si>
+  <si>
+    <t>Dan Blackmore</t>
+  </si>
+  <si>
+    <t>Alice</t>
+  </si>
+  <si>
+    <t>Julius Belisk Harwey</t>
+  </si>
+  <si>
+    <t>Leonardo Bistario Harwey</t>
+  </si>
+  <si>
+    <t>Sesshouin Kiara</t>
+  </si>
+  <si>
+    <t>Twice H. Pieceman</t>
+  </si>
+  <si>
+    <t>Darnic Prestone</t>
+  </si>
+  <si>
+    <t>Fiore Forvedge</t>
+  </si>
+  <si>
+    <t>Caules Forvedge</t>
+  </si>
+  <si>
+    <t>Roche Frain</t>
+  </si>
+  <si>
+    <t>Celenike Icecolle</t>
+  </si>
+  <si>
+    <t>Sieg</t>
+  </si>
+  <si>
+    <t>Kotomine Shirou</t>
+  </si>
+  <si>
+    <t>Shishigou Kairi</t>
+  </si>
+  <si>
+    <t>Fujimaru Ritsuka (Female)</t>
+  </si>
+  <si>
+    <t>Servant Enhancement</t>
+  </si>
+  <si>
+    <t>Fujimaru Ritsuka (Male)</t>
+  </si>
+  <si>
+    <t>Goredolf Musik</t>
+  </si>
+  <si>
+    <t>Sion Sokaris</t>
+  </si>
+  <si>
+    <t>Fou</t>
+  </si>
+  <si>
+    <t>Kadoc Zemplupus</t>
+  </si>
+  <si>
+    <t>Ophelia Phamrsolone</t>
+  </si>
+  <si>
+    <t>Akuta Hinako</t>
+  </si>
+  <si>
+    <t>Scandinavia Peperoncino</t>
+  </si>
+  <si>
+    <t>Kirschtaria Wodime</t>
+  </si>
+  <si>
+    <t>Demon God Goetia</t>
+  </si>
+  <si>
+    <t>Tiamat</t>
+  </si>
+  <si>
+    <t>Reines Archisorte</t>
+  </si>
+  <si>
+    <t>Magical Ruby</t>
+  </si>
+  <si>
+    <t>Magical Sapphire</t>
+  </si>
+  <si>
+    <t>Nanaya Shiki</t>
+  </si>
+  <si>
+    <t>Tohno Akiha</t>
+  </si>
+  <si>
+    <t>Ciel</t>
+  </si>
+  <si>
+    <t>Magical Amber</t>
+  </si>
+  <si>
+    <t>Brainwash Detective Hisui</t>
+  </si>
+  <si>
+    <t>Nrvnqsr Chaos</t>
+  </si>
+  <si>
+    <t>The Serpent of Akasha</t>
+  </si>
+  <si>
+    <t>Tohno SHIKI</t>
+  </si>
+  <si>
+    <t>The Night of Wallachia</t>
+  </si>
+  <si>
+    <t>Ryougi Shiki</t>
+  </si>
+  <si>
+    <t>Asagami Fujino</t>
+  </si>
+  <si>
+    <t>Araya Souren</t>
+  </si>
+  <si>
+    <t>master_slug</t>
+  </si>
+  <si>
+    <t>emiya-shirou</t>
+  </si>
+  <si>
+    <t>tohsaka-rin</t>
+  </si>
+  <si>
+    <t>matou-shinji</t>
+  </si>
+  <si>
+    <t>matou-sakura</t>
+  </si>
+  <si>
+    <t>kuzuki-soichirou</t>
+  </si>
+  <si>
+    <t>kotomine-kirei</t>
+  </si>
+  <si>
+    <t>matou-zouken</t>
+  </si>
+  <si>
+    <t>fujimura-taiga</t>
+  </si>
+  <si>
+    <t>caren-hortensia</t>
+  </si>
+  <si>
+    <t>emiya-kiritsugu</t>
+  </si>
+  <si>
+    <t>tohsaka-tokiomi</t>
+  </si>
+  <si>
+    <t>matou-kariya</t>
+  </si>
+  <si>
+    <t>waver-velvet</t>
+  </si>
+  <si>
+    <t>kayneth-archibald</t>
+  </si>
+  <si>
+    <t>uryuu-ryuunosuke</t>
+  </si>
+  <si>
+    <t>rani-viii</t>
+  </si>
+  <si>
+    <t>jinako-carigiri</t>
+  </si>
+  <si>
+    <t>dan-blackmore</t>
+  </si>
+  <si>
+    <t>sesshouin-kiara</t>
+  </si>
+  <si>
+    <t>darnic-prestone</t>
+  </si>
+  <si>
+    <t>fiore-forvedge</t>
+  </si>
+  <si>
+    <t>caules-forvedge</t>
+  </si>
+  <si>
+    <t>roche-frain</t>
+  </si>
+  <si>
+    <t>celenike-icecolle</t>
+  </si>
+  <si>
+    <t>kotomine-shirou</t>
+  </si>
+  <si>
+    <t>shishigou-kairi</t>
+  </si>
+  <si>
+    <t>goredolf-musik</t>
+  </si>
+  <si>
+    <t>sion-sokaris</t>
+  </si>
+  <si>
+    <t>kadoc-zemplupus</t>
+  </si>
+  <si>
+    <t>ophelia-phamrsolone</t>
+  </si>
+  <si>
+    <t>akuta-hinako</t>
+  </si>
+  <si>
+    <t>scandinavia-peperoncino</t>
+  </si>
+  <si>
+    <t>kirschtaria-wodime</t>
+  </si>
+  <si>
+    <t>reines-archisorte</t>
+  </si>
+  <si>
+    <t>magical-ruby</t>
+  </si>
+  <si>
+    <t>magical-sapphire</t>
+  </si>
+  <si>
+    <t>nanaya-shiki</t>
+  </si>
+  <si>
+    <t>tohno-akiha</t>
+  </si>
+  <si>
+    <t>magical-amber</t>
+  </si>
+  <si>
+    <t>nrvnqsr-chaos</t>
+  </si>
+  <si>
+    <t>tohno-shiki</t>
+  </si>
+  <si>
+    <t>ryougi-shiki</t>
+  </si>
+  <si>
+    <t>asagami-fujino</t>
+  </si>
+  <si>
+    <t>araya-souren</t>
+  </si>
+  <si>
+    <t>bazett-fraga-mcremitz</t>
+  </si>
+  <si>
+    <t>irisviel-von-einzbern</t>
+  </si>
+  <si>
+    <t>julius-belisk-harwey</t>
+  </si>
+  <si>
+    <t>leonardo-bistario-harwey</t>
+  </si>
+  <si>
+    <t>twice-h-pieceman</t>
+  </si>
+  <si>
+    <t>demon-god-goetia</t>
+  </si>
+  <si>
+    <t>brainwash-detective-hisui</t>
+  </si>
+  <si>
+    <t>kishinami-hakuno-male</t>
+  </si>
+  <si>
+    <t>kishinami-hakuno-female</t>
+  </si>
+  <si>
+    <t>fujimaru-ritsuka-female</t>
+  </si>
+  <si>
+    <t>fujimaru-ritsuka-male</t>
+  </si>
+  <si>
+    <t>the-serpent-of-akasha</t>
+  </si>
+  <si>
+    <t>the-night-of-wallachia</t>
+  </si>
+  <si>
+    <t>sieg</t>
+  </si>
+  <si>
+    <t>alice</t>
+  </si>
+  <si>
+    <t>fou</t>
+  </si>
+  <si>
+    <t>tiamat</t>
+  </si>
+  <si>
+    <t>ciel</t>
+  </si>
+  <si>
+    <t>emiya-shirou-cook</t>
   </si>
 </sst>
 </file>
@@ -19913,9 +20516,956 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32F3CD10-C054-4484-ABE2-D426F834FC22}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:E67"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="13.3984375" customWidth="1"/>
+    <col min="2" max="3" width="26" customWidth="1"/>
+    <col min="4" max="4" width="20.46484375" customWidth="1"/>
+    <col min="5" max="5" width="14.6640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A1" s="1" t="s">
+        <v>1271</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1338</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1408</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>1339</v>
+      </c>
+      <c r="E1" s="1"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A2" t="s">
+        <v>1272</v>
+      </c>
+      <c r="B2" t="s">
+        <v>510</v>
+      </c>
+      <c r="C2" t="s">
+        <v>1409</v>
+      </c>
+      <c r="D2" t="s">
+        <v>1341</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A3" t="s">
+        <v>1273</v>
+      </c>
+      <c r="B3" t="s">
+        <v>1340</v>
+      </c>
+      <c r="C3" t="s">
+        <v>1410</v>
+      </c>
+      <c r="D3" t="s">
+        <v>1342</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A4" t="s">
+        <v>1274</v>
+      </c>
+      <c r="B4" t="s">
+        <v>1346</v>
+      </c>
+      <c r="C4" t="s">
+        <v>1411</v>
+      </c>
+      <c r="D4" t="s">
+        <v>1343</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A5" t="s">
+        <v>1275</v>
+      </c>
+      <c r="B5" t="s">
+        <v>1347</v>
+      </c>
+      <c r="C5" t="s">
+        <v>1412</v>
+      </c>
+      <c r="D5" t="s">
+        <v>1344</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A6" t="s">
+        <v>1276</v>
+      </c>
+      <c r="B6" t="s">
+        <v>1348</v>
+      </c>
+      <c r="C6" t="s">
+        <v>286</v>
+      </c>
+      <c r="D6" t="s">
+        <v>1343</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A7" t="s">
+        <v>1277</v>
+      </c>
+      <c r="B7" t="s">
+        <v>1349</v>
+      </c>
+      <c r="C7" t="s">
+        <v>1413</v>
+      </c>
+      <c r="D7" t="s">
+        <v>1345</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A8" t="s">
+        <v>1278</v>
+      </c>
+      <c r="B8" t="s">
+        <v>1350</v>
+      </c>
+      <c r="C8" t="s">
+        <v>1414</v>
+      </c>
+      <c r="D8" t="s">
+        <v>1345</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A9" t="s">
+        <v>1279</v>
+      </c>
+      <c r="B9" t="s">
+        <v>1351</v>
+      </c>
+      <c r="C9" t="s">
+        <v>1415</v>
+      </c>
+      <c r="D9" t="s">
+        <v>1343</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A10" t="s">
+        <v>1280</v>
+      </c>
+      <c r="B10" t="s">
+        <v>1352</v>
+      </c>
+      <c r="C10" t="s">
+        <v>1416</v>
+      </c>
+      <c r="D10" t="s">
+        <v>1345</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A11" t="s">
+        <v>1281</v>
+      </c>
+      <c r="B11" t="s">
+        <v>1353</v>
+      </c>
+      <c r="C11" t="s">
+        <v>1453</v>
+      </c>
+      <c r="D11" t="s">
+        <v>1345</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A12" t="s">
+        <v>1282</v>
+      </c>
+      <c r="B12" t="s">
+        <v>1354</v>
+      </c>
+      <c r="C12" t="s">
+        <v>1417</v>
+      </c>
+      <c r="D12" t="s">
+        <v>1345</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A13" t="s">
+        <v>1283</v>
+      </c>
+      <c r="B13" t="s">
+        <v>5</v>
+      </c>
+      <c r="C13" t="s">
+        <v>6</v>
+      </c>
+      <c r="D13" t="s">
+        <v>1341</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A14" t="s">
+        <v>1284</v>
+      </c>
+      <c r="B14" t="s">
+        <v>1355</v>
+      </c>
+      <c r="C14" t="s">
+        <v>1418</v>
+      </c>
+      <c r="D14" t="s">
+        <v>1341</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A15" t="s">
+        <v>1285</v>
+      </c>
+      <c r="B15" t="s">
+        <v>1356</v>
+      </c>
+      <c r="C15" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D15" t="s">
+        <v>1343</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A16" t="s">
+        <v>1286</v>
+      </c>
+      <c r="B16" t="s">
+        <v>1357</v>
+      </c>
+      <c r="C16" t="s">
+        <v>1419</v>
+      </c>
+      <c r="D16" t="s">
+        <v>1345</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A17" t="s">
+        <v>1287</v>
+      </c>
+      <c r="B17" t="s">
+        <v>1358</v>
+      </c>
+      <c r="C17" t="s">
+        <v>1420</v>
+      </c>
+      <c r="D17" t="s">
+        <v>1343</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A18" t="s">
+        <v>1288</v>
+      </c>
+      <c r="B18" t="s">
+        <v>1359</v>
+      </c>
+      <c r="C18" t="s">
+        <v>1421</v>
+      </c>
+      <c r="D18" t="s">
+        <v>1342</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A19" t="s">
+        <v>1289</v>
+      </c>
+      <c r="B19" t="s">
+        <v>1360</v>
+      </c>
+      <c r="C19" t="s">
+        <v>1422</v>
+      </c>
+      <c r="D19" t="s">
+        <v>1341</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A20" t="s">
+        <v>1290</v>
+      </c>
+      <c r="B20" t="s">
+        <v>1361</v>
+      </c>
+      <c r="C20" t="s">
+        <v>1423</v>
+      </c>
+      <c r="D20" t="s">
+        <v>1343</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A21" t="s">
+        <v>1291</v>
+      </c>
+      <c r="B21" t="s">
+        <v>1362</v>
+      </c>
+      <c r="C21" t="s">
+        <v>1460</v>
+      </c>
+      <c r="D21" t="s">
+        <v>1341</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A22" t="s">
+        <v>1292</v>
+      </c>
+      <c r="B22" t="s">
+        <v>1363</v>
+      </c>
+      <c r="C22" t="s">
+        <v>1461</v>
+      </c>
+      <c r="D22" t="s">
+        <v>1342</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A23" t="s">
+        <v>1293</v>
+      </c>
+      <c r="B23" t="s">
+        <v>1364</v>
+      </c>
+      <c r="C23" t="s">
+        <v>1424</v>
+      </c>
+      <c r="D23" t="s">
+        <v>1345</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A24" t="s">
+        <v>1294</v>
+      </c>
+      <c r="B24" t="s">
+        <v>1365</v>
+      </c>
+      <c r="C24" t="s">
+        <v>1425</v>
+      </c>
+      <c r="D24" t="s">
+        <v>1341</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A25" t="s">
+        <v>1295</v>
+      </c>
+      <c r="B25" t="s">
+        <v>1366</v>
+      </c>
+      <c r="C25" t="s">
+        <v>1426</v>
+      </c>
+      <c r="D25" t="s">
+        <v>1341</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A26" t="s">
+        <v>1296</v>
+      </c>
+      <c r="B26" t="s">
+        <v>1367</v>
+      </c>
+      <c r="C26" t="s">
+        <v>1467</v>
+      </c>
+      <c r="D26" t="s">
+        <v>1345</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A27" t="s">
+        <v>1297</v>
+      </c>
+      <c r="B27" t="s">
+        <v>1368</v>
+      </c>
+      <c r="C27" t="s">
+        <v>1455</v>
+      </c>
+      <c r="D27" t="s">
+        <v>1342</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A28" t="s">
+        <v>1298</v>
+      </c>
+      <c r="B28" t="s">
+        <v>1369</v>
+      </c>
+      <c r="C28" t="s">
+        <v>1456</v>
+      </c>
+      <c r="D28" t="s">
+        <v>1341</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A29" t="s">
+        <v>1299</v>
+      </c>
+      <c r="B29" t="s">
+        <v>1370</v>
+      </c>
+      <c r="C29" t="s">
+        <v>1427</v>
+      </c>
+      <c r="D29" t="s">
+        <v>1344</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A30" t="s">
+        <v>1300</v>
+      </c>
+      <c r="B30" t="s">
+        <v>1371</v>
+      </c>
+      <c r="C30" t="s">
+        <v>1457</v>
+      </c>
+      <c r="D30" t="s">
+        <v>1342</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A31" t="s">
+        <v>1301</v>
+      </c>
+      <c r="B31" t="s">
+        <v>1372</v>
+      </c>
+      <c r="C31" t="s">
+        <v>1428</v>
+      </c>
+      <c r="D31" t="s">
+        <v>1343</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A32" t="s">
+        <v>1302</v>
+      </c>
+      <c r="B32" t="s">
+        <v>1373</v>
+      </c>
+      <c r="C32" t="s">
+        <v>1429</v>
+      </c>
+      <c r="D32" t="s">
+        <v>1341</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A33" t="s">
+        <v>1303</v>
+      </c>
+      <c r="B33" t="s">
+        <v>1374</v>
+      </c>
+      <c r="C33" t="s">
+        <v>1430</v>
+      </c>
+      <c r="D33" t="s">
+        <v>1341</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A34" t="s">
+        <v>1304</v>
+      </c>
+      <c r="B34" t="s">
+        <v>1375</v>
+      </c>
+      <c r="C34" t="s">
+        <v>1431</v>
+      </c>
+      <c r="D34" t="s">
+        <v>1345</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A35" t="s">
+        <v>1305</v>
+      </c>
+      <c r="B35" t="s">
+        <v>1376</v>
+      </c>
+      <c r="C35" t="s">
+        <v>1432</v>
+      </c>
+      <c r="D35" t="s">
+        <v>1343</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A36" t="s">
+        <v>1306</v>
+      </c>
+      <c r="B36" t="s">
+        <v>1377</v>
+      </c>
+      <c r="C36" t="s">
+        <v>1466</v>
+      </c>
+      <c r="D36" t="s">
+        <v>1341</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A37" t="s">
+        <v>1307</v>
+      </c>
+      <c r="B37" t="s">
+        <v>1378</v>
+      </c>
+      <c r="C37" t="s">
+        <v>1433</v>
+      </c>
+      <c r="D37" t="s">
+        <v>1342</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A38" t="s">
+        <v>1308</v>
+      </c>
+      <c r="B38" t="s">
+        <v>1379</v>
+      </c>
+      <c r="C38" t="s">
+        <v>1434</v>
+      </c>
+      <c r="D38" t="s">
+        <v>1341</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A39" t="s">
+        <v>1309</v>
+      </c>
+      <c r="B39" t="s">
+        <v>1380</v>
+      </c>
+      <c r="C39" t="s">
+        <v>1462</v>
+      </c>
+      <c r="D39" t="s">
+        <v>1381</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A40" t="s">
+        <v>1310</v>
+      </c>
+      <c r="B40" t="s">
+        <v>1382</v>
+      </c>
+      <c r="C40" t="s">
+        <v>1463</v>
+      </c>
+      <c r="D40" t="s">
+        <v>1342</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A41" t="s">
+        <v>1311</v>
+      </c>
+      <c r="B41" t="s">
+        <v>1383</v>
+      </c>
+      <c r="C41" t="s">
+        <v>1435</v>
+      </c>
+      <c r="D41" t="s">
+        <v>1345</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A42" t="s">
+        <v>1312</v>
+      </c>
+      <c r="B42" t="s">
+        <v>1384</v>
+      </c>
+      <c r="C42" t="s">
+        <v>1436</v>
+      </c>
+      <c r="D42" t="s">
+        <v>1381</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A43" t="s">
+        <v>1313</v>
+      </c>
+      <c r="B43" t="s">
+        <v>1385</v>
+      </c>
+      <c r="C43" t="s">
+        <v>1468</v>
+      </c>
+      <c r="D43" t="s">
+        <v>1343</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A44" t="s">
+        <v>1314</v>
+      </c>
+      <c r="B44" t="s">
+        <v>1386</v>
+      </c>
+      <c r="C44" t="s">
+        <v>1437</v>
+      </c>
+      <c r="D44" t="s">
+        <v>1342</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A45" t="s">
+        <v>1315</v>
+      </c>
+      <c r="B45" t="s">
+        <v>1387</v>
+      </c>
+      <c r="C45" t="s">
+        <v>1438</v>
+      </c>
+      <c r="D45" t="s">
+        <v>1341</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A46" t="s">
+        <v>1316</v>
+      </c>
+      <c r="B46" t="s">
+        <v>1388</v>
+      </c>
+      <c r="C46" t="s">
+        <v>1439</v>
+      </c>
+      <c r="D46" t="s">
+        <v>1341</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A47" t="s">
+        <v>1317</v>
+      </c>
+      <c r="B47" t="s">
+        <v>1389</v>
+      </c>
+      <c r="C47" t="s">
+        <v>1440</v>
+      </c>
+      <c r="D47" t="s">
+        <v>1341</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A48" t="s">
+        <v>1318</v>
+      </c>
+      <c r="B48" t="s">
+        <v>1390</v>
+      </c>
+      <c r="C48" t="s">
+        <v>1441</v>
+      </c>
+      <c r="D48" t="s">
+        <v>1341</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A49" t="s">
+        <v>1319</v>
+      </c>
+      <c r="B49" t="s">
+        <v>1391</v>
+      </c>
+      <c r="C49" t="s">
+        <v>1458</v>
+      </c>
+      <c r="D49" t="s">
+        <v>1341</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A50" t="s">
+        <v>1320</v>
+      </c>
+      <c r="B50" t="s">
+        <v>1392</v>
+      </c>
+      <c r="C50" t="s">
+        <v>1469</v>
+      </c>
+      <c r="D50" t="s">
+        <v>1344</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A51" t="s">
+        <v>1321</v>
+      </c>
+      <c r="B51" t="s">
+        <v>510</v>
+      </c>
+      <c r="C51" t="s">
+        <v>1471</v>
+      </c>
+      <c r="D51" t="s">
+        <v>1343</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A52" t="s">
+        <v>1322</v>
+      </c>
+      <c r="B52" t="s">
+        <v>1393</v>
+      </c>
+      <c r="C52" t="s">
+        <v>1442</v>
+      </c>
+      <c r="D52" t="s">
+        <v>1342</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A53" t="s">
+        <v>1323</v>
+      </c>
+      <c r="B53" t="s">
+        <v>1394</v>
+      </c>
+      <c r="C53" t="s">
+        <v>1443</v>
+      </c>
+      <c r="D53" t="s">
+        <v>1342</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A54" t="s">
+        <v>1324</v>
+      </c>
+      <c r="B54" t="s">
+        <v>1395</v>
+      </c>
+      <c r="C54" t="s">
+        <v>1444</v>
+      </c>
+      <c r="D54" t="s">
+        <v>1381</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A55" t="s">
+        <v>1325</v>
+      </c>
+      <c r="B55" t="s">
+        <v>1396</v>
+      </c>
+      <c r="C55" t="s">
+        <v>1445</v>
+      </c>
+      <c r="D55" t="s">
+        <v>1341</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A56" t="s">
+        <v>1326</v>
+      </c>
+      <c r="B56" t="s">
+        <v>1397</v>
+      </c>
+      <c r="C56" t="s">
+        <v>1446</v>
+      </c>
+      <c r="D56" t="s">
+        <v>1341</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A57" t="s">
+        <v>1327</v>
+      </c>
+      <c r="B57" t="s">
+        <v>1021</v>
+      </c>
+      <c r="C57" t="s">
+        <v>1022</v>
+      </c>
+      <c r="D57" t="s">
+        <v>1341</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A58" t="s">
+        <v>1328</v>
+      </c>
+      <c r="B58" t="s">
+        <v>1398</v>
+      </c>
+      <c r="C58" t="s">
+        <v>1470</v>
+      </c>
+      <c r="D58" t="s">
+        <v>1342</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A59" t="s">
+        <v>1329</v>
+      </c>
+      <c r="B59" t="s">
+        <v>1399</v>
+      </c>
+      <c r="C59" t="s">
+        <v>1447</v>
+      </c>
+      <c r="D59" t="s">
+        <v>1342</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A60" t="s">
+        <v>1330</v>
+      </c>
+      <c r="B60" t="s">
+        <v>1400</v>
+      </c>
+      <c r="C60" t="s">
+        <v>1459</v>
+      </c>
+      <c r="D60" t="s">
+        <v>1342</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A61" t="s">
+        <v>1331</v>
+      </c>
+      <c r="B61" t="s">
+        <v>1401</v>
+      </c>
+      <c r="C61" t="s">
+        <v>1448</v>
+      </c>
+      <c r="D61" t="s">
+        <v>1342</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A62" t="s">
+        <v>1332</v>
+      </c>
+      <c r="B62" t="s">
+        <v>1402</v>
+      </c>
+      <c r="C62" t="s">
+        <v>1464</v>
+      </c>
+      <c r="D62" t="s">
+        <v>1341</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A63" t="s">
+        <v>1333</v>
+      </c>
+      <c r="B63" t="s">
+        <v>1403</v>
+      </c>
+      <c r="C63" t="s">
+        <v>1449</v>
+      </c>
+      <c r="D63" t="s">
+        <v>1341</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A64" t="s">
+        <v>1334</v>
+      </c>
+      <c r="B64" t="s">
+        <v>1404</v>
+      </c>
+      <c r="C64" t="s">
+        <v>1465</v>
+      </c>
+      <c r="D64" t="s">
+        <v>1341</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A65" t="s">
+        <v>1335</v>
+      </c>
+      <c r="B65" t="s">
+        <v>1405</v>
+      </c>
+      <c r="C65" t="s">
+        <v>1450</v>
+      </c>
+      <c r="D65" t="s">
+        <v>1341</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A66" t="s">
+        <v>1336</v>
+      </c>
+      <c r="B66" t="s">
+        <v>1406</v>
+      </c>
+      <c r="C66" t="s">
+        <v>1451</v>
+      </c>
+      <c r="D66" t="s">
+        <v>1343</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A67" t="s">
+        <v>1337</v>
+      </c>
+      <c r="B67" t="s">
+        <v>1407</v>
+      </c>
+      <c r="C67" t="s">
+        <v>1452</v>
+      </c>
+      <c r="D67" t="s">
+        <v>1343</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/data/Fate-Spreadsheet.xlsx
+++ b/data/Fate-Spreadsheet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pixel\Documents\Projects\Fate-Wiki\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF22F243-7CE9-4C5E-8F8B-BD38A949953E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A8AEC5F-F014-4DE0-B160-E5C74668FC87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{B05E798F-9EF6-4508-A0A4-311D06661AED}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="3" xr2:uid="{B05E798F-9EF6-4508-A0A4-311D06661AED}"/>
   </bookViews>
   <sheets>
     <sheet name="Servants" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3712" uniqueCount="1499">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3752" uniqueCount="1509">
   <si>
     <t>servant_id</t>
   </si>
@@ -3265,9 +3265,6 @@
     <t>Berserker_Strength_9,Luck,Preparation</t>
   </si>
   <si>
-    <t>Berserker_Strength_7,Berserker_Strength_9,Berserker_Magic_7</t>
-  </si>
-  <si>
     <t>Berserker_Strength_9,Berserker_Agility_7,Luck,Preparation,Preparation</t>
   </si>
   <si>
@@ -4462,9 +4459,6 @@
     <t>Level-Up</t>
   </si>
   <si>
-    <t>Albion's-Remnant</t>
-  </si>
-  <si>
     <t>Red-Calamity</t>
   </si>
   <si>
@@ -4541,6 +4535,42 @@
   </si>
   <si>
     <t>Pocket-Da-Vinci</t>
+  </si>
+  <si>
+    <t>Destroyed Dockside</t>
+  </si>
+  <si>
+    <t>Destroyed City Center</t>
+  </si>
+  <si>
+    <t>Destroyed Temple</t>
+  </si>
+  <si>
+    <t>Destroyed-Dockside</t>
+  </si>
+  <si>
+    <t>Destroyed-Temple</t>
+  </si>
+  <si>
+    <t>Destroyed-City-Center</t>
+  </si>
+  <si>
+    <t>objective</t>
+  </si>
+  <si>
+    <t>Ruler Seal</t>
+  </si>
+  <si>
+    <t>Ruler-Seal</t>
+  </si>
+  <si>
+    <t>resource</t>
+  </si>
+  <si>
+    <t>Berserker_Strength_7,Berserker_Strength_9,Berserker_Magic_7,Luck,Surveil</t>
+  </si>
+  <si>
+    <t>Albions-Remnant</t>
   </si>
 </sst>
 </file>
@@ -4939,7 +4969,7 @@
     <col min="7" max="7" width="13.73046875" style="2" customWidth="1"/>
     <col min="8" max="8" width="16.59765625" style="2" customWidth="1"/>
     <col min="9" max="9" width="17.59765625" style="2" customWidth="1"/>
-    <col min="10" max="10" width="63.53125" style="2" customWidth="1"/>
+    <col min="10" max="10" width="97" style="2" customWidth="1"/>
     <col min="11" max="11" width="12.59765625" customWidth="1"/>
     <col min="12" max="12" width="10.9296875" customWidth="1"/>
     <col min="13" max="13" width="12" customWidth="1"/>
@@ -4983,7 +5013,7 @@
         <v>12</v>
       </c>
       <c r="L1" s="3" t="s">
-        <v>1467</v>
+        <v>1466</v>
       </c>
       <c r="M1" s="3"/>
       <c r="N1" s="3"/>
@@ -5018,9 +5048,6 @@
       <c r="J2" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="K2" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
@@ -5050,9 +5077,6 @@
       <c r="J3" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="K3" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
@@ -5079,9 +5103,6 @@
       <c r="J4" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="K4" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
@@ -5108,8 +5129,8 @@
       <c r="J5" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="K5" t="b">
-        <v>0</v>
+      <c r="L5" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.45">
@@ -5140,9 +5161,6 @@
       <c r="J6" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="K6" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
@@ -5172,9 +5190,6 @@
       <c r="J7" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="K7" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
@@ -5230,9 +5245,6 @@
       <c r="J9" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="K9" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
@@ -5262,9 +5274,6 @@
       <c r="J10" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="K10" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
@@ -5294,9 +5303,6 @@
       <c r="J11" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="K11" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
@@ -5326,9 +5332,6 @@
       <c r="J12" s="2" t="s">
         <v>194</v>
       </c>
-      <c r="K12" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
@@ -5355,9 +5358,6 @@
       <c r="J13" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="K13" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
@@ -5387,9 +5387,6 @@
       <c r="J14" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="K14" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
@@ -5419,9 +5416,6 @@
       <c r="J15" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="K15" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
@@ -5451,9 +5445,6 @@
       <c r="J16" s="2" t="s">
         <v>200</v>
       </c>
-      <c r="K16" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
@@ -5483,9 +5474,6 @@
       <c r="J17" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="K17" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
@@ -5547,9 +5535,6 @@
       <c r="J19" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="K19" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
@@ -5576,9 +5561,6 @@
       <c r="J20" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="K20" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
@@ -5608,9 +5590,6 @@
       <c r="J21" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="K21" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
@@ -5672,9 +5651,6 @@
       <c r="J23" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="K23" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
@@ -5704,9 +5680,6 @@
       <c r="J24" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="K24" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
@@ -5736,9 +5709,6 @@
       <c r="J25" s="2" t="s">
         <v>270</v>
       </c>
-      <c r="K25" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
@@ -5765,9 +5735,6 @@
       <c r="J26" s="2" t="s">
         <v>328</v>
       </c>
-      <c r="K26" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
@@ -5797,9 +5764,6 @@
       <c r="J27" s="2" t="s">
         <v>200</v>
       </c>
-      <c r="K27" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
@@ -5826,9 +5790,6 @@
       <c r="J28" s="2" t="s">
         <v>396</v>
       </c>
-      <c r="K28" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
@@ -5858,9 +5819,6 @@
       <c r="J29" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="K29" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
@@ -5887,9 +5845,6 @@
       <c r="J30" s="2" t="s">
         <v>200</v>
       </c>
-      <c r="K30" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
@@ -5951,9 +5906,6 @@
       <c r="J32" s="2" t="s">
         <v>194</v>
       </c>
-      <c r="K32" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="33" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
@@ -5983,9 +5935,6 @@
       <c r="J33" s="2" t="s">
         <v>200</v>
       </c>
-      <c r="K33" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="34" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
@@ -6015,9 +5964,6 @@
       <c r="J34" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="K34" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="35" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A35" t="s">
@@ -6047,9 +5993,6 @@
       <c r="J35" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="K35" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="36" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A36" t="s">
@@ -6076,9 +6019,6 @@
       <c r="J36" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="K36" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="37" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A37" t="s">
@@ -6105,9 +6045,6 @@
       <c r="J37" s="2" t="s">
         <v>432</v>
       </c>
-      <c r="K37" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="38" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A38" t="s">
@@ -6137,9 +6074,6 @@
       <c r="J38" s="2" t="s">
         <v>436</v>
       </c>
-      <c r="K38" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="39" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A39" t="s">
@@ -6166,9 +6100,6 @@
       <c r="J39" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="K39" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="40" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A40" t="s">
@@ -6198,9 +6129,6 @@
       <c r="J40" s="2" t="s">
         <v>194</v>
       </c>
-      <c r="K40" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="41" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A41" t="s">
@@ -6227,9 +6155,6 @@
       <c r="J41" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="K41" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="42" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A42" t="s">
@@ -6259,9 +6184,6 @@
       <c r="J42" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="K42" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="43" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A43" t="s">
@@ -6291,9 +6213,6 @@
       <c r="J43" s="2" t="s">
         <v>200</v>
       </c>
-      <c r="K43" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="44" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A44" t="s">
@@ -6323,9 +6242,6 @@
       <c r="J44" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="K44" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="45" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A45" t="s">
@@ -6355,9 +6271,6 @@
       <c r="J45" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="K45" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="46" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A46" t="s">
@@ -6386,9 +6299,6 @@
       </c>
       <c r="J46" s="2" t="s">
         <v>186</v>
-      </c>
-      <c r="K46" t="b">
-        <v>0</v>
       </c>
       <c r="L46" t="b">
         <v>1</v>
@@ -6426,9 +6336,6 @@
       <c r="J47" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="K47" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="48" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A48" t="s">
@@ -6458,11 +6365,8 @@
       <c r="J48" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="K48" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.45">
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A49" t="s">
         <v>271</v>
       </c>
@@ -6490,11 +6394,8 @@
       <c r="J49" s="2" t="s">
         <v>274</v>
       </c>
-      <c r="K49" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.45">
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A50" t="s">
         <v>476</v>
       </c>
@@ -6519,11 +6420,8 @@
       <c r="J50" s="2" t="s">
         <v>558</v>
       </c>
-      <c r="K50" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.45">
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A51" t="s">
         <v>477</v>
       </c>
@@ -6548,11 +6446,8 @@
       <c r="J51" s="2" t="s">
         <v>560</v>
       </c>
-      <c r="K51" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.45">
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A52" t="s">
         <v>478</v>
       </c>
@@ -6580,11 +6475,8 @@
       <c r="J52" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="K52" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.45">
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A53" t="s">
         <v>479</v>
       </c>
@@ -6609,11 +6501,8 @@
       <c r="J53" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="K53" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.45">
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A54" t="s">
         <v>480</v>
       </c>
@@ -6641,11 +6530,8 @@
       <c r="J54" s="2" t="s">
         <v>200</v>
       </c>
-      <c r="K54" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.45">
+    </row>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A55" t="s">
         <v>481</v>
       </c>
@@ -6673,11 +6559,8 @@
       <c r="J55" s="2" t="s">
         <v>564</v>
       </c>
-      <c r="K55" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.45">
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A56" t="s">
         <v>482</v>
       </c>
@@ -6705,11 +6588,8 @@
       <c r="J56" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="K56" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.45">
+    </row>
+    <row r="57" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A57" t="s">
         <v>483</v>
       </c>
@@ -6734,11 +6614,8 @@
       <c r="J57" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="K57" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.45">
+    </row>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A58" t="s">
         <v>484</v>
       </c>
@@ -6766,11 +6643,8 @@
       <c r="J58" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="K58" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.45">
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A59" t="s">
         <v>485</v>
       </c>
@@ -6795,11 +6669,8 @@
       <c r="J59" s="2" t="s">
         <v>200</v>
       </c>
-      <c r="K59" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.45">
+    </row>
+    <row r="60" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A60" t="s">
         <v>486</v>
       </c>
@@ -6824,11 +6695,8 @@
       <c r="J60" s="2" t="s">
         <v>200</v>
       </c>
-      <c r="K60" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.45">
+    </row>
+    <row r="61" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A61" t="s">
         <v>487</v>
       </c>
@@ -6856,11 +6724,8 @@
       <c r="J61" s="2" t="s">
         <v>200</v>
       </c>
-      <c r="K61" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.45">
+    </row>
+    <row r="62" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A62" t="s">
         <v>488</v>
       </c>
@@ -6888,11 +6753,8 @@
       <c r="J62" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="K62" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.45">
+    </row>
+    <row r="63" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A63" t="s">
         <v>489</v>
       </c>
@@ -6920,11 +6782,8 @@
       <c r="J63" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="K63" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.45">
+    </row>
+    <row r="64" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A64" t="s">
         <v>490</v>
       </c>
@@ -6951,9 +6810,6 @@
       </c>
       <c r="J64" s="2" t="s">
         <v>564</v>
-      </c>
-      <c r="K64" t="b">
-        <v>0</v>
       </c>
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.45">
@@ -6984,9 +6840,6 @@
       <c r="J65" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="K65" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A66" t="s">
@@ -7013,9 +6866,6 @@
       <c r="J66" s="2" t="s">
         <v>200</v>
       </c>
-      <c r="K66" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="67" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A67" t="s">
@@ -7042,9 +6892,6 @@
       <c r="J67" s="2" t="s">
         <v>570</v>
       </c>
-      <c r="K67" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A68" t="s">
@@ -7074,9 +6921,6 @@
       <c r="J68" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="K68" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="69" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A69" t="s">
@@ -7106,9 +6950,6 @@
       <c r="J69" s="2" t="s">
         <v>200</v>
       </c>
-      <c r="K69" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="70" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A70" t="s">
@@ -7167,9 +7008,6 @@
       <c r="J71" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="K71" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="72" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A72" t="s">
@@ -7199,9 +7037,6 @@
       <c r="J72" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="K72" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="73" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A73" t="s">
@@ -7231,9 +7066,6 @@
       <c r="J73" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="K73" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="74" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A74" t="s">
@@ -7260,9 +7092,6 @@
       <c r="J74" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="K74" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="75" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A75" t="s">
@@ -7289,9 +7118,6 @@
       <c r="J75" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="K75" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="76" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A76" t="s">
@@ -7318,9 +7144,6 @@
       <c r="J76" s="2" t="s">
         <v>649</v>
       </c>
-      <c r="K76" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="77" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A77" t="s">
@@ -7347,9 +7170,6 @@
       <c r="J77" s="2" t="s">
         <v>650</v>
       </c>
-      <c r="K77" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="78" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A78" t="s">
@@ -7379,9 +7199,6 @@
       <c r="J78" s="2" t="s">
         <v>436</v>
       </c>
-      <c r="K78" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="79" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A79" t="s">
@@ -7411,9 +7228,6 @@
       <c r="J79" s="2" t="s">
         <v>651</v>
       </c>
-      <c r="K79" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="80" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A80" t="s">
@@ -7443,11 +7257,8 @@
       <c r="J80" s="2" t="s">
         <v>653</v>
       </c>
-      <c r="K80" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="81" spans="1:11" x14ac:dyDescent="0.45">
+    </row>
+    <row r="81" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A81" t="s">
         <v>544</v>
       </c>
@@ -7475,11 +7286,8 @@
       <c r="J81" s="2" t="s">
         <v>200</v>
       </c>
-      <c r="K81" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="82" spans="1:11" x14ac:dyDescent="0.45">
+    </row>
+    <row r="82" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A82" t="s">
         <v>545</v>
       </c>
@@ -7504,11 +7312,8 @@
       <c r="J82" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="K82" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="83" spans="1:11" x14ac:dyDescent="0.45">
+    </row>
+    <row r="83" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A83" t="s">
         <v>546</v>
       </c>
@@ -7533,11 +7338,8 @@
       <c r="J83" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="K83" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" spans="1:11" x14ac:dyDescent="0.45">
+    </row>
+    <row r="84" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A84" t="s">
         <v>547</v>
       </c>
@@ -7565,11 +7367,8 @@
       <c r="J84" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="K84" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="85" spans="1:11" x14ac:dyDescent="0.45">
+    </row>
+    <row r="85" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A85" t="s">
         <v>548</v>
       </c>
@@ -7597,11 +7396,8 @@
       <c r="J85" s="2" t="s">
         <v>200</v>
       </c>
-      <c r="K85" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="86" spans="1:11" x14ac:dyDescent="0.45">
+    </row>
+    <row r="86" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A86" t="s">
         <v>549</v>
       </c>
@@ -7626,11 +7422,8 @@
       <c r="J86" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="K86" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="87" spans="1:11" x14ac:dyDescent="0.45">
+    </row>
+    <row r="87" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A87" t="s">
         <v>550</v>
       </c>
@@ -7655,11 +7448,8 @@
       <c r="J87" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="K87" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="88" spans="1:11" x14ac:dyDescent="0.45">
+    </row>
+    <row r="88" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A88" t="s">
         <v>551</v>
       </c>
@@ -7687,11 +7477,8 @@
       <c r="J88" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="K88" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="89" spans="1:11" x14ac:dyDescent="0.45">
+    </row>
+    <row r="89" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A89" t="s">
         <v>552</v>
       </c>
@@ -7719,11 +7506,8 @@
       <c r="J89" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="K89" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90" spans="1:11" x14ac:dyDescent="0.45">
+    </row>
+    <row r="90" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A90" t="s">
         <v>553</v>
       </c>
@@ -7751,11 +7535,8 @@
       <c r="J90" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="K90" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="91" spans="1:11" x14ac:dyDescent="0.45">
+    </row>
+    <row r="91" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A91" t="s">
         <v>554</v>
       </c>
@@ -7783,11 +7564,8 @@
       <c r="J91" s="2" t="s">
         <v>663</v>
       </c>
-      <c r="K91" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92" spans="1:11" x14ac:dyDescent="0.45">
+    </row>
+    <row r="92" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A92" t="s">
         <v>555</v>
       </c>
@@ -7815,11 +7593,8 @@
       <c r="J92" s="2" t="s">
         <v>665</v>
       </c>
-      <c r="K92" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="93" spans="1:11" x14ac:dyDescent="0.45">
+    </row>
+    <row r="93" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A93" t="s">
         <v>556</v>
       </c>
@@ -7847,11 +7622,8 @@
       <c r="J93" s="2" t="s">
         <v>194</v>
       </c>
-      <c r="K93" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="94" spans="1:11" x14ac:dyDescent="0.45">
+    </row>
+    <row r="94" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A94" t="s">
         <v>281</v>
       </c>
@@ -7876,11 +7648,8 @@
       <c r="J94" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="K94" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="1:11" x14ac:dyDescent="0.45">
+    </row>
+    <row r="95" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A95" t="s">
         <v>738</v>
       </c>
@@ -7902,11 +7671,8 @@
       <c r="J95" s="2" t="s">
         <v>744</v>
       </c>
-      <c r="K95" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="96" spans="1:11" x14ac:dyDescent="0.45">
+    </row>
+    <row r="96" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A96" t="s">
         <v>739</v>
       </c>
@@ -7933,9 +7699,6 @@
       </c>
       <c r="J96" s="2" t="s">
         <v>183</v>
-      </c>
-      <c r="K96" t="b">
-        <v>0</v>
       </c>
     </row>
     <row r="97" spans="1:12" x14ac:dyDescent="0.45">
@@ -7958,13 +7721,10 @@
         <v>100</v>
       </c>
       <c r="I97" s="2" t="s">
-        <v>1466</v>
+        <v>1465</v>
       </c>
       <c r="J97" s="2" t="s">
         <v>558</v>
-      </c>
-      <c r="K97" t="b">
-        <v>0</v>
       </c>
     </row>
     <row r="98" spans="1:12" x14ac:dyDescent="0.45">
@@ -8021,9 +7781,6 @@
       <c r="J99" s="2" t="s">
         <v>762</v>
       </c>
-      <c r="K99" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="100" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A100" t="s">
@@ -8053,9 +7810,6 @@
       <c r="J100" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="K100" t="b">
-        <v>0</v>
-      </c>
       <c r="L100" t="b">
         <v>1</v>
       </c>
@@ -8085,9 +7839,6 @@
       <c r="J101" s="2" t="s">
         <v>436</v>
       </c>
-      <c r="K101" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="102" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A102" t="s">
@@ -8140,9 +7891,6 @@
       <c r="J103" s="2" t="s">
         <v>564</v>
       </c>
-      <c r="K103" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="104" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A104" t="s">
@@ -8169,9 +7917,6 @@
       <c r="J104" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="K104" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="105" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A105" t="s">
@@ -8198,9 +7943,6 @@
       <c r="J105" s="2" t="s">
         <v>558</v>
       </c>
-      <c r="K105" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="106" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A106" t="s">
@@ -8227,9 +7969,6 @@
       <c r="J106" s="2" t="s">
         <v>194</v>
       </c>
-      <c r="K106" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="107" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A107" t="s">
@@ -8259,9 +7998,6 @@
       <c r="J107" s="2" t="s">
         <v>194</v>
       </c>
-      <c r="K107" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="108" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A108" t="s">
@@ -8291,9 +8027,6 @@
       <c r="J108" s="2" t="s">
         <v>194</v>
       </c>
-      <c r="K108" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="109" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A109" t="s">
@@ -8349,9 +8082,6 @@
       <c r="J110" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="K110" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="111" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A111" t="s">
@@ -8378,9 +8108,6 @@
       <c r="J111" s="2" t="s">
         <v>436</v>
       </c>
-      <c r="K111" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="112" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A112" t="s">
@@ -8410,11 +8137,8 @@
       <c r="J112" s="2" t="s">
         <v>837</v>
       </c>
-      <c r="K112" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="113" spans="1:11" x14ac:dyDescent="0.45">
+    </row>
+    <row r="113" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A113" t="s">
         <v>810</v>
       </c>
@@ -8439,11 +8163,8 @@
       <c r="J113" s="2" t="s">
         <v>744</v>
       </c>
-      <c r="K113" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="114" spans="1:11" x14ac:dyDescent="0.45">
+    </row>
+    <row r="114" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A114" t="s">
         <v>811</v>
       </c>
@@ -8468,11 +8189,8 @@
       <c r="J114" s="2" t="s">
         <v>564</v>
       </c>
-      <c r="K114" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="115" spans="1:11" x14ac:dyDescent="0.45">
+    </row>
+    <row r="115" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A115" t="s">
         <v>812</v>
       </c>
@@ -8500,11 +8218,8 @@
       <c r="J115" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="K115" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="116" spans="1:11" x14ac:dyDescent="0.45">
+    </row>
+    <row r="116" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A116" t="s">
         <v>813</v>
       </c>
@@ -8532,11 +8247,8 @@
       <c r="J116" s="2" t="s">
         <v>194</v>
       </c>
-      <c r="K116" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="117" spans="1:11" x14ac:dyDescent="0.45">
+    </row>
+    <row r="117" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A117" t="s">
         <v>814</v>
       </c>
@@ -8561,11 +8273,8 @@
       <c r="J117" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="K117" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="118" spans="1:11" x14ac:dyDescent="0.45">
+    </row>
+    <row r="118" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A118" t="s">
         <v>815</v>
       </c>
@@ -8593,11 +8302,8 @@
       <c r="J118" s="2" t="s">
         <v>564</v>
       </c>
-      <c r="K118" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="119" spans="1:11" x14ac:dyDescent="0.45">
+    </row>
+    <row r="119" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A119" t="s">
         <v>816</v>
       </c>
@@ -8625,11 +8331,8 @@
       <c r="J119" s="2" t="s">
         <v>866</v>
       </c>
-      <c r="K119" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="120" spans="1:11" x14ac:dyDescent="0.45">
+    </row>
+    <row r="120" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A120" t="s">
         <v>817</v>
       </c>
@@ -8657,11 +8360,8 @@
       <c r="J120" s="2" t="s">
         <v>200</v>
       </c>
-      <c r="K120" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="121" spans="1:11" x14ac:dyDescent="0.45">
+    </row>
+    <row r="121" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A121" t="s">
         <v>818</v>
       </c>
@@ -8689,11 +8389,8 @@
       <c r="J121" s="2" t="s">
         <v>837</v>
       </c>
-      <c r="K121" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="122" spans="1:11" x14ac:dyDescent="0.45">
+    </row>
+    <row r="122" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A122" t="s">
         <v>314</v>
       </c>
@@ -8718,11 +8415,8 @@
       <c r="J122" s="2" t="s">
         <v>319</v>
       </c>
-      <c r="K122" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="123" spans="1:11" x14ac:dyDescent="0.45">
+    </row>
+    <row r="123" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A123" t="s">
         <v>879</v>
       </c>
@@ -8730,7 +8424,7 @@
         <v>467</v>
       </c>
       <c r="C123" t="s">
-        <v>1465</v>
+        <v>1464</v>
       </c>
       <c r="D123" t="s">
         <v>317</v>
@@ -8750,11 +8444,8 @@
       <c r="J123" s="2" t="s">
         <v>564</v>
       </c>
-      <c r="K123" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="124" spans="1:11" x14ac:dyDescent="0.45">
+    </row>
+    <row r="124" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A124" t="s">
         <v>880</v>
       </c>
@@ -8782,11 +8473,8 @@
       <c r="J124" s="2" t="s">
         <v>936</v>
       </c>
-      <c r="K124" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="125" spans="1:11" x14ac:dyDescent="0.45">
+    </row>
+    <row r="125" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A125" t="s">
         <v>881</v>
       </c>
@@ -8811,11 +8499,8 @@
       <c r="J125" s="2" t="s">
         <v>270</v>
       </c>
-      <c r="K125" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="126" spans="1:11" x14ac:dyDescent="0.45">
+    </row>
+    <row r="126" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A126" t="s">
         <v>882</v>
       </c>
@@ -8843,11 +8528,8 @@
       <c r="J126" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="K126" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="127" spans="1:11" x14ac:dyDescent="0.45">
+    </row>
+    <row r="127" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A127" t="s">
         <v>883</v>
       </c>
@@ -8872,11 +8554,8 @@
       <c r="J127" s="2" t="s">
         <v>938</v>
       </c>
-      <c r="K127" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="128" spans="1:11" x14ac:dyDescent="0.45">
+    </row>
+    <row r="128" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A128" t="s">
         <v>884</v>
       </c>
@@ -8900,9 +8579,6 @@
       </c>
       <c r="J128" s="2" t="s">
         <v>940</v>
-      </c>
-      <c r="K128" t="b">
-        <v>0</v>
       </c>
     </row>
     <row r="129" spans="1:11" x14ac:dyDescent="0.45">
@@ -8930,9 +8606,6 @@
       <c r="J129" s="2" t="s">
         <v>436</v>
       </c>
-      <c r="K129" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="130" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A130" t="s">
@@ -8994,9 +8667,6 @@
       <c r="J131" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="K131" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="132" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A132" t="s">
@@ -9026,9 +8696,6 @@
       <c r="J132" s="2" t="s">
         <v>941</v>
       </c>
-      <c r="K132" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="133" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A133" t="s">
@@ -9058,9 +8725,6 @@
       <c r="J133" s="2" t="s">
         <v>564</v>
       </c>
-      <c r="K133" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="134" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A134" t="s">
@@ -9090,9 +8754,6 @@
       <c r="J134" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="K134" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="135" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A135" t="s">
@@ -9119,9 +8780,6 @@
       <c r="J135" s="2" t="s">
         <v>270</v>
       </c>
-      <c r="K135" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="136" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A136" t="s">
@@ -9151,9 +8809,6 @@
       <c r="J136" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="K136" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="137" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A137" t="s">
@@ -9180,9 +8835,6 @@
       <c r="J137" s="2" t="s">
         <v>944</v>
       </c>
-      <c r="K137" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="138" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A138" t="s">
@@ -9212,9 +8864,6 @@
       <c r="J138" s="2" t="s">
         <v>744</v>
       </c>
-      <c r="K138" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="139" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A139" t="s">
@@ -9244,9 +8893,6 @@
       <c r="J139" s="2" t="s">
         <v>948</v>
       </c>
-      <c r="K139" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="140" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A140" t="s">
@@ -9273,9 +8919,6 @@
       <c r="J140" s="2" t="s">
         <v>1056</v>
       </c>
-      <c r="K140" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="141" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A141" t="s">
@@ -9302,9 +8945,6 @@
       <c r="J141" s="2" t="s">
         <v>1057</v>
       </c>
-      <c r="K141" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="142" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A142" t="s">
@@ -9334,9 +8974,6 @@
       <c r="J142" s="2" t="s">
         <v>1058</v>
       </c>
-      <c r="K142" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="143" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A143" t="s">
@@ -9363,9 +9000,6 @@
       <c r="J143" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="K143" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="144" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A144" t="s">
@@ -9392,11 +9026,8 @@
       <c r="J144" s="2" t="s">
         <v>1061</v>
       </c>
-      <c r="K144" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="145" spans="1:11" x14ac:dyDescent="0.45">
+    </row>
+    <row r="145" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A145" t="s">
         <v>901</v>
       </c>
@@ -9421,11 +9052,8 @@
       <c r="J145" s="2" t="s">
         <v>1062</v>
       </c>
-      <c r="K145" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="146" spans="1:11" x14ac:dyDescent="0.45">
+    </row>
+    <row r="146" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A146" t="s">
         <v>902</v>
       </c>
@@ -9450,11 +9078,8 @@
       <c r="J146" s="2" t="s">
         <v>1064</v>
       </c>
-      <c r="K146" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="147" spans="1:11" x14ac:dyDescent="0.45">
+    </row>
+    <row r="147" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A147" t="s">
         <v>903</v>
       </c>
@@ -9479,11 +9104,8 @@
       <c r="J147" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="K147" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="148" spans="1:11" x14ac:dyDescent="0.45">
+    </row>
+    <row r="148" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A148" t="s">
         <v>76</v>
       </c>
@@ -9511,11 +9133,8 @@
       <c r="J148" s="2" t="s">
         <v>322</v>
       </c>
-      <c r="K148" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="149" spans="1:11" x14ac:dyDescent="0.45">
+    </row>
+    <row r="149" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A149" t="s">
         <v>995</v>
       </c>
@@ -9543,11 +9162,8 @@
       <c r="J149" s="2" t="s">
         <v>1066</v>
       </c>
-      <c r="K149" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="150" spans="1:11" x14ac:dyDescent="0.45">
+    </row>
+    <row r="150" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A150" t="s">
         <v>996</v>
       </c>
@@ -9575,16 +9191,13 @@
       <c r="J150" s="2" t="s">
         <v>1067</v>
       </c>
-      <c r="K150" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="151" spans="1:11" x14ac:dyDescent="0.45">
+    </row>
+    <row r="151" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A151" t="s">
         <v>997</v>
       </c>
       <c r="B151" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
       <c r="C151" t="s">
         <v>1036</v>
@@ -9604,11 +9217,8 @@
       <c r="J151" s="2" t="s">
         <v>1068</v>
       </c>
-      <c r="K151" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="152" spans="1:11" x14ac:dyDescent="0.45">
+    </row>
+    <row r="152" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A152" t="s">
         <v>998</v>
       </c>
@@ -9633,11 +9243,8 @@
       <c r="J152" s="2" t="s">
         <v>1069</v>
       </c>
-      <c r="K152" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="153" spans="1:11" x14ac:dyDescent="0.45">
+    </row>
+    <row r="153" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A153" t="s">
         <v>999</v>
       </c>
@@ -9665,11 +9272,8 @@
       <c r="J153" s="2" t="s">
         <v>837</v>
       </c>
-      <c r="K153" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="154" spans="1:11" x14ac:dyDescent="0.45">
+    </row>
+    <row r="154" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A154" t="s">
         <v>1000</v>
       </c>
@@ -9694,16 +9298,13 @@
       <c r="J154" s="2" t="s">
         <v>1066</v>
       </c>
-      <c r="K154" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="155" spans="1:11" x14ac:dyDescent="0.45">
+    </row>
+    <row r="155" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A155" t="s">
         <v>1001</v>
       </c>
       <c r="B155" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="C155" t="s">
         <v>1042</v>
@@ -9726,11 +9327,8 @@
       <c r="J155" s="2" t="s">
         <v>1071</v>
       </c>
-      <c r="K155" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="156" spans="1:11" x14ac:dyDescent="0.45">
+    </row>
+    <row r="156" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A156" t="s">
         <v>1002</v>
       </c>
@@ -9755,11 +9353,8 @@
       <c r="J156" s="2" t="s">
         <v>1072</v>
       </c>
-      <c r="K156" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="157" spans="1:11" x14ac:dyDescent="0.45">
+    </row>
+    <row r="157" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A157" t="s">
         <v>1003</v>
       </c>
@@ -9787,11 +9382,8 @@
       <c r="J157" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="K157" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="158" spans="1:11" x14ac:dyDescent="0.45">
+    </row>
+    <row r="158" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A158" t="s">
         <v>1004</v>
       </c>
@@ -9819,11 +9411,8 @@
       <c r="J158" s="2" t="s">
         <v>744</v>
       </c>
-      <c r="K158" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="159" spans="1:11" x14ac:dyDescent="0.45">
+    </row>
+    <row r="159" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A159" t="s">
         <v>1005</v>
       </c>
@@ -9848,11 +9437,8 @@
       <c r="J159" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="K159" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="160" spans="1:11" x14ac:dyDescent="0.45">
+    </row>
+    <row r="160" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A160" t="s">
         <v>1006</v>
       </c>
@@ -9878,13 +9464,10 @@
         <v>15</v>
       </c>
       <c r="J160" s="2" t="s">
-        <v>1073</v>
-      </c>
-      <c r="K160" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="161" spans="1:11" x14ac:dyDescent="0.45">
+        <v>1507</v>
+      </c>
+    </row>
+    <row r="161" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A161" t="s">
         <v>1007</v>
       </c>
@@ -9907,13 +9490,10 @@
         <v>27</v>
       </c>
       <c r="J161" s="2" t="s">
-        <v>1074</v>
-      </c>
-      <c r="K161" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="162" spans="1:11" x14ac:dyDescent="0.45">
+        <v>1073</v>
+      </c>
+    </row>
+    <row r="162" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A162" t="s">
         <v>1008</v>
       </c>
@@ -9936,21 +9516,18 @@
         <v>100</v>
       </c>
       <c r="J162" s="2" t="s">
-        <v>1075</v>
-      </c>
-      <c r="K162" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="163" spans="1:11" x14ac:dyDescent="0.45">
+        <v>1074</v>
+      </c>
+    </row>
+    <row r="163" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A163" t="s">
         <v>1009</v>
       </c>
       <c r="B163" t="s">
+        <v>1154</v>
+      </c>
+      <c r="C163" t="s">
         <v>1155</v>
-      </c>
-      <c r="C163" t="s">
-        <v>1156</v>
       </c>
       <c r="D163" t="s">
         <v>26</v>
@@ -9968,21 +9545,18 @@
         <v>15</v>
       </c>
       <c r="J163" s="2" t="s">
-        <v>1197</v>
-      </c>
-      <c r="K163" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="164" spans="1:11" x14ac:dyDescent="0.45">
+        <v>1196</v>
+      </c>
+    </row>
+    <row r="164" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A164" t="s">
         <v>1010</v>
       </c>
       <c r="B164" t="s">
+        <v>1157</v>
+      </c>
+      <c r="C164" t="s">
         <v>1158</v>
-      </c>
-      <c r="C164" t="s">
-        <v>1159</v>
       </c>
       <c r="D164" t="s">
         <v>26</v>
@@ -10000,21 +9574,18 @@
         <v>451</v>
       </c>
       <c r="J164" s="2" t="s">
-        <v>1198</v>
-      </c>
-      <c r="K164" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="165" spans="1:11" x14ac:dyDescent="0.45">
+        <v>1197</v>
+      </c>
+    </row>
+    <row r="165" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A165" t="s">
         <v>1011</v>
       </c>
       <c r="B165" t="s">
+        <v>1159</v>
+      </c>
+      <c r="C165" t="s">
         <v>1160</v>
-      </c>
-      <c r="C165" t="s">
-        <v>1161</v>
       </c>
       <c r="D165" t="s">
         <v>26</v>
@@ -10029,21 +9600,18 @@
         <v>431</v>
       </c>
       <c r="J165" s="2" t="s">
-        <v>1199</v>
-      </c>
-      <c r="K165" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="166" spans="1:11" x14ac:dyDescent="0.45">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="166" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A166" t="s">
         <v>1012</v>
       </c>
       <c r="B166" t="s">
+        <v>1161</v>
+      </c>
+      <c r="C166" t="s">
         <v>1162</v>
-      </c>
-      <c r="C166" t="s">
-        <v>1163</v>
       </c>
       <c r="D166" t="s">
         <v>26</v>
@@ -10061,21 +9629,18 @@
         <v>190</v>
       </c>
       <c r="J166" s="2" t="s">
-        <v>1197</v>
-      </c>
-      <c r="K166" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="167" spans="1:11" x14ac:dyDescent="0.45">
+        <v>1196</v>
+      </c>
+    </row>
+    <row r="167" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A167" t="s">
         <v>1013</v>
       </c>
       <c r="B167" t="s">
+        <v>1163</v>
+      </c>
+      <c r="C167" t="s">
         <v>1164</v>
-      </c>
-      <c r="C167" t="s">
-        <v>1165</v>
       </c>
       <c r="D167" t="s">
         <v>26</v>
@@ -10087,19 +9652,16 @@
         <v>947</v>
       </c>
       <c r="H167" s="2" t="s">
-        <v>1200</v>
+        <v>1199</v>
       </c>
       <c r="I167" s="2" t="s">
         <v>191</v>
       </c>
       <c r="J167" s="2" t="s">
-        <v>1201</v>
-      </c>
-      <c r="K167" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="168" spans="1:11" x14ac:dyDescent="0.45">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="168" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A168" t="s">
         <v>23</v>
       </c>
@@ -10124,19 +9686,16 @@
       <c r="J168" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="K168" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="169" spans="1:11" x14ac:dyDescent="0.45">
+    </row>
+    <row r="169" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A169" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="B169" t="s">
+        <v>1165</v>
+      </c>
+      <c r="C169" t="s">
         <v>1166</v>
-      </c>
-      <c r="C169" t="s">
-        <v>1167</v>
       </c>
       <c r="D169" t="s">
         <v>26</v>
@@ -10154,24 +9713,21 @@
         <v>196</v>
       </c>
       <c r="J169" s="2" t="s">
-        <v>1197</v>
-      </c>
-      <c r="K169" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="170" spans="1:11" x14ac:dyDescent="0.45">
+        <v>1196</v>
+      </c>
+    </row>
+    <row r="170" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A170" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="B170" t="s">
+        <v>1167</v>
+      </c>
+      <c r="C170" t="s">
         <v>1168</v>
       </c>
-      <c r="C170" t="s">
+      <c r="D170" t="s">
         <v>1169</v>
-      </c>
-      <c r="D170" t="s">
-        <v>1170</v>
       </c>
       <c r="E170" t="s">
         <v>40</v>
@@ -10186,24 +9742,24 @@
         <v>81</v>
       </c>
       <c r="J170" s="2" t="s">
-        <v>1202</v>
-      </c>
-      <c r="K170" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="171" spans="1:11" x14ac:dyDescent="0.45">
+        <v>1201</v>
+      </c>
+      <c r="L170" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="171" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A171" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
       <c r="B171" t="s">
+        <v>1170</v>
+      </c>
+      <c r="C171" t="s">
         <v>1171</v>
       </c>
-      <c r="C171" t="s">
-        <v>1172</v>
-      </c>
       <c r="D171" t="s">
-        <v>1170</v>
+        <v>1169</v>
       </c>
       <c r="E171" t="s">
         <v>40</v>
@@ -10220,22 +9776,22 @@
       <c r="J171" s="2" t="s">
         <v>436</v>
       </c>
-      <c r="K171" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="172" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L171" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="172" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A172" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="B172" t="s">
+        <v>1172</v>
+      </c>
+      <c r="C172" t="s">
         <v>1173</v>
       </c>
-      <c r="C172" t="s">
-        <v>1174</v>
-      </c>
       <c r="D172" t="s">
-        <v>1170</v>
+        <v>1169</v>
       </c>
       <c r="E172" t="s">
         <v>89</v>
@@ -10247,24 +9803,21 @@
         <v>176</v>
       </c>
       <c r="J172" s="2" t="s">
-        <v>1203</v>
-      </c>
-      <c r="K172" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="173" spans="1:11" x14ac:dyDescent="0.45">
+        <v>1202</v>
+      </c>
+    </row>
+    <row r="173" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A173" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="B173" t="s">
+        <v>1174</v>
+      </c>
+      <c r="C173" t="s">
         <v>1175</v>
       </c>
-      <c r="C173" t="s">
-        <v>1176</v>
-      </c>
       <c r="D173" t="s">
-        <v>1170</v>
+        <v>1169</v>
       </c>
       <c r="E173" t="s">
         <v>40</v>
@@ -10281,19 +9834,16 @@
       <c r="J173" s="2" t="s">
         <v>436</v>
       </c>
-      <c r="K173" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="174" spans="1:11" x14ac:dyDescent="0.45">
+    </row>
+    <row r="174" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A174" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
       <c r="B174" t="s">
+        <v>1176</v>
+      </c>
+      <c r="C174" t="s">
         <v>1177</v>
-      </c>
-      <c r="C174" t="s">
-        <v>1178</v>
       </c>
       <c r="D174" t="s">
         <v>646</v>
@@ -10311,24 +9861,24 @@
         <v>451</v>
       </c>
       <c r="J174" s="2" t="s">
-        <v>1204</v>
-      </c>
-      <c r="K174" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="175" spans="1:11" x14ac:dyDescent="0.45">
+        <v>1203</v>
+      </c>
+      <c r="L174" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="175" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A175" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
       <c r="B175" t="s">
+        <v>1178</v>
+      </c>
+      <c r="C175" t="s">
         <v>1179</v>
       </c>
-      <c r="C175" t="s">
-        <v>1180</v>
-      </c>
       <c r="D175" t="s">
-        <v>1170</v>
+        <v>1169</v>
       </c>
       <c r="E175" t="s">
         <v>99</v>
@@ -10343,24 +9893,24 @@
         <v>187</v>
       </c>
       <c r="J175" s="2" t="s">
-        <v>1205</v>
-      </c>
-      <c r="K175" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="176" spans="1:11" x14ac:dyDescent="0.45">
+        <v>1204</v>
+      </c>
+      <c r="L175" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="176" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A176" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
       <c r="B176" t="s">
+        <v>1180</v>
+      </c>
+      <c r="C176" t="s">
         <v>1181</v>
       </c>
-      <c r="C176" t="s">
-        <v>1182</v>
-      </c>
       <c r="D176" t="s">
-        <v>1170</v>
+        <v>1169</v>
       </c>
       <c r="E176" t="s">
         <v>99</v>
@@ -10377,22 +9927,22 @@
       <c r="J176" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="K176" t="b">
-        <v>0</v>
+      <c r="L176" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="177" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A177" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="B177" t="s">
+        <v>1182</v>
+      </c>
+      <c r="C177" t="s">
         <v>1183</v>
       </c>
-      <c r="C177" t="s">
-        <v>1184</v>
-      </c>
       <c r="D177" t="s">
-        <v>1170</v>
+        <v>1169</v>
       </c>
       <c r="E177" t="s">
         <v>40</v>
@@ -10409,19 +9959,16 @@
       <c r="J177" s="2" t="s">
         <v>436</v>
       </c>
-      <c r="K177" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="178" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A178" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
       <c r="B178" t="s">
+        <v>1184</v>
+      </c>
+      <c r="C178" t="s">
         <v>1185</v>
-      </c>
-      <c r="C178" t="s">
-        <v>1186</v>
       </c>
       <c r="D178" t="s">
         <v>32</v>
@@ -10430,7 +9977,7 @@
         <v>99</v>
       </c>
       <c r="G178" s="2" t="s">
-        <v>1206</v>
+        <v>1205</v>
       </c>
       <c r="H178" s="2" t="s">
         <v>15</v>
@@ -10439,10 +9986,7 @@
         <v>196</v>
       </c>
       <c r="J178" s="2" t="s">
-        <v>1207</v>
-      </c>
-      <c r="K178" t="b">
-        <v>0</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="179" spans="1:11" x14ac:dyDescent="0.45">
@@ -10473,22 +10017,19 @@
       <c r="J179" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="K179" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="180" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A180" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
       <c r="B180" t="s">
+        <v>1186</v>
+      </c>
+      <c r="C180" t="s">
         <v>1187</v>
       </c>
-      <c r="C180" t="s">
+      <c r="D180" t="s">
         <v>1188</v>
-      </c>
-      <c r="D180" t="s">
-        <v>1189</v>
       </c>
       <c r="E180" t="s">
         <v>8</v>
@@ -10500,24 +10041,21 @@
         <v>204</v>
       </c>
       <c r="J180" s="2" t="s">
-        <v>1208</v>
-      </c>
-      <c r="K180" t="b">
-        <v>0</v>
+        <v>1207</v>
       </c>
     </row>
     <row r="181" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A181" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="B181" t="s">
+        <v>1189</v>
+      </c>
+      <c r="C181" t="s">
         <v>1190</v>
       </c>
-      <c r="C181" t="s">
-        <v>1191</v>
-      </c>
       <c r="D181" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="E181" t="s">
         <v>89</v>
@@ -10532,30 +10070,27 @@
         <v>176</v>
       </c>
       <c r="J181" s="2" t="s">
-        <v>1209</v>
-      </c>
-      <c r="K181" t="b">
-        <v>0</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="182" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A182" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
       <c r="B182" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="C182" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="D182" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="E182" t="s">
         <v>33</v>
       </c>
       <c r="H182" s="2" t="s">
-        <v>1200</v>
+        <v>1199</v>
       </c>
       <c r="I182" s="2" t="s">
         <v>189</v>
@@ -10563,22 +10098,19 @@
       <c r="J182" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="K182" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="183" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A183" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
       <c r="B183" t="s">
+        <v>1192</v>
+      </c>
+      <c r="C183" t="s">
         <v>1193</v>
       </c>
-      <c r="C183" t="s">
-        <v>1194</v>
-      </c>
       <c r="D183" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="E183" t="s">
         <v>89</v>
@@ -10595,22 +10127,19 @@
       <c r="J183" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="K183" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="184" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A184" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="B184" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
       <c r="C184" t="s">
-        <v>1196</v>
+        <v>1195</v>
       </c>
       <c r="D184" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="E184" t="s">
         <v>8</v>
@@ -10626,9 +10155,6 @@
       </c>
       <c r="J184" s="2" t="s">
         <v>179</v>
-      </c>
-      <c r="K184" t="b">
-        <v>0</v>
       </c>
     </row>
     <row r="185" spans="1:11" x14ac:dyDescent="0.45">
@@ -11131,7 +10657,7 @@
         <v>51</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>1260</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.45">
@@ -18186,7 +17712,7 @@
         <v>0</v>
       </c>
       <c r="E416" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="417" spans="1:5" x14ac:dyDescent="0.45">
@@ -18203,7 +17729,7 @@
         <v>0</v>
       </c>
       <c r="E417" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="418" spans="1:5" x14ac:dyDescent="0.45">
@@ -18220,7 +17746,7 @@
         <v>0</v>
       </c>
       <c r="E418" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="419" spans="1:5" x14ac:dyDescent="0.45">
@@ -18237,7 +17763,7 @@
         <v>0</v>
       </c>
       <c r="E419" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="420" spans="1:5" x14ac:dyDescent="0.45">
@@ -18254,7 +17780,7 @@
         <v>0</v>
       </c>
       <c r="E420" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="421" spans="1:5" x14ac:dyDescent="0.45">
@@ -18271,7 +17797,7 @@
         <v>0</v>
       </c>
       <c r="E421" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="422" spans="1:5" x14ac:dyDescent="0.45">
@@ -18288,7 +17814,7 @@
         <v>0</v>
       </c>
       <c r="E422" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="423" spans="1:5" x14ac:dyDescent="0.45">
@@ -18305,7 +17831,7 @@
         <v>0</v>
       </c>
       <c r="E423" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="424" spans="1:5" x14ac:dyDescent="0.45">
@@ -18322,7 +17848,7 @@
         <v>0</v>
       </c>
       <c r="E424" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="425" spans="1:5" x14ac:dyDescent="0.45">
@@ -18339,7 +17865,7 @@
         <v>0</v>
       </c>
       <c r="E425" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="426" spans="1:5" x14ac:dyDescent="0.45">
@@ -18356,7 +17882,7 @@
         <v>0</v>
       </c>
       <c r="E426" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="427" spans="1:5" x14ac:dyDescent="0.45">
@@ -18373,7 +17899,7 @@
         <v>0</v>
       </c>
       <c r="E427" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="428" spans="1:5" x14ac:dyDescent="0.45">
@@ -18390,7 +17916,7 @@
         <v>0</v>
       </c>
       <c r="E428" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="429" spans="1:5" x14ac:dyDescent="0.45">
@@ -18407,7 +17933,7 @@
         <v>0</v>
       </c>
       <c r="E429" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="430" spans="1:5" x14ac:dyDescent="0.45">
@@ -18424,7 +17950,7 @@
         <v>0</v>
       </c>
       <c r="E430" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="431" spans="1:5" x14ac:dyDescent="0.45">
@@ -18441,7 +17967,7 @@
         <v>0</v>
       </c>
       <c r="E431" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="432" spans="1:5" x14ac:dyDescent="0.45">
@@ -18458,7 +17984,7 @@
         <v>0</v>
       </c>
       <c r="E432" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="433" spans="1:5" x14ac:dyDescent="0.45">
@@ -18475,7 +18001,7 @@
         <v>0</v>
       </c>
       <c r="E433" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="434" spans="1:5" x14ac:dyDescent="0.45">
@@ -18492,7 +18018,7 @@
         <v>0</v>
       </c>
       <c r="E434" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="435" spans="1:5" x14ac:dyDescent="0.45">
@@ -18509,7 +18035,7 @@
         <v>0</v>
       </c>
       <c r="E435" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="436" spans="1:5" x14ac:dyDescent="0.45">
@@ -18526,7 +18052,7 @@
         <v>0</v>
       </c>
       <c r="E436" t="s">
-        <v>1094</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="437" spans="1:5" x14ac:dyDescent="0.45">
@@ -18543,7 +18069,7 @@
         <v>0</v>
       </c>
       <c r="E437" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="438" spans="1:5" x14ac:dyDescent="0.45">
@@ -18560,7 +18086,7 @@
         <v>0</v>
       </c>
       <c r="E438" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="439" spans="1:5" x14ac:dyDescent="0.45">
@@ -18577,7 +18103,7 @@
         <v>0</v>
       </c>
       <c r="E439" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="440" spans="1:5" x14ac:dyDescent="0.45">
@@ -18645,7 +18171,7 @@
         <v>0</v>
       </c>
       <c r="E443" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="444" spans="1:5" x14ac:dyDescent="0.45">
@@ -18662,7 +18188,7 @@
         <v>0</v>
       </c>
       <c r="E444" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="445" spans="1:5" x14ac:dyDescent="0.45">
@@ -18679,7 +18205,7 @@
         <v>0</v>
       </c>
       <c r="E445" t="s">
-        <v>1099</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="446" spans="1:5" x14ac:dyDescent="0.45">
@@ -18696,7 +18222,7 @@
         <v>0</v>
       </c>
       <c r="E446" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="447" spans="1:5" x14ac:dyDescent="0.45">
@@ -18713,7 +18239,7 @@
         <v>0</v>
       </c>
       <c r="E447" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="448" spans="1:5" x14ac:dyDescent="0.45">
@@ -18730,7 +18256,7 @@
         <v>0</v>
       </c>
       <c r="E448" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="449" spans="1:5" x14ac:dyDescent="0.45">
@@ -18738,16 +18264,16 @@
         <v>997</v>
       </c>
       <c r="B449" t="s">
+        <v>1102</v>
+      </c>
+      <c r="C449">
+        <v>1</v>
+      </c>
+      <c r="D449" t="b">
+        <v>0</v>
+      </c>
+      <c r="E449" t="s">
         <v>1103</v>
-      </c>
-      <c r="C449">
-        <v>1</v>
-      </c>
-      <c r="D449" t="b">
-        <v>0</v>
-      </c>
-      <c r="E449" t="s">
-        <v>1104</v>
       </c>
     </row>
     <row r="450" spans="1:5" x14ac:dyDescent="0.45">
@@ -18755,7 +18281,7 @@
         <v>997</v>
       </c>
       <c r="B450" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
       <c r="C450">
         <v>2</v>
@@ -18764,7 +18290,7 @@
         <v>0</v>
       </c>
       <c r="E450" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="451" spans="1:5" x14ac:dyDescent="0.45">
@@ -18772,7 +18298,7 @@
         <v>997</v>
       </c>
       <c r="B451" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
       <c r="C451">
         <v>3</v>
@@ -18781,7 +18307,7 @@
         <v>0</v>
       </c>
       <c r="E451" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="452" spans="1:5" x14ac:dyDescent="0.45">
@@ -18798,7 +18324,7 @@
         <v>0</v>
       </c>
       <c r="E452" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="453" spans="1:5" x14ac:dyDescent="0.45">
@@ -18815,7 +18341,7 @@
         <v>0</v>
       </c>
       <c r="E453" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="454" spans="1:5" x14ac:dyDescent="0.45">
@@ -18832,7 +18358,7 @@
         <v>0</v>
       </c>
       <c r="E454" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="455" spans="1:5" x14ac:dyDescent="0.45">
@@ -18849,7 +18375,7 @@
         <v>0</v>
       </c>
       <c r="E455" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="456" spans="1:5" x14ac:dyDescent="0.45">
@@ -18866,7 +18392,7 @@
         <v>0</v>
       </c>
       <c r="E456" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="457" spans="1:5" x14ac:dyDescent="0.45">
@@ -18883,7 +18409,7 @@
         <v>0</v>
       </c>
       <c r="E457" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="458" spans="1:5" x14ac:dyDescent="0.45">
@@ -18900,7 +18426,7 @@
         <v>0</v>
       </c>
       <c r="E458" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="459" spans="1:5" x14ac:dyDescent="0.45">
@@ -18917,7 +18443,7 @@
         <v>0</v>
       </c>
       <c r="E459" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="460" spans="1:5" x14ac:dyDescent="0.45">
@@ -18934,7 +18460,7 @@
         <v>0</v>
       </c>
       <c r="E460" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="461" spans="1:5" x14ac:dyDescent="0.45">
@@ -18942,16 +18468,16 @@
         <v>1001</v>
       </c>
       <c r="B461" t="s">
+        <v>1115</v>
+      </c>
+      <c r="C461">
+        <v>1</v>
+      </c>
+      <c r="D461" t="b">
+        <v>0</v>
+      </c>
+      <c r="E461" t="s">
         <v>1116</v>
-      </c>
-      <c r="C461">
-        <v>1</v>
-      </c>
-      <c r="D461" t="b">
-        <v>0</v>
-      </c>
-      <c r="E461" t="s">
-        <v>1117</v>
       </c>
     </row>
     <row r="462" spans="1:5" x14ac:dyDescent="0.45">
@@ -18959,7 +18485,7 @@
         <v>1001</v>
       </c>
       <c r="B462" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="C462">
         <v>2</v>
@@ -18968,7 +18494,7 @@
         <v>0</v>
       </c>
       <c r="E462" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="463" spans="1:5" x14ac:dyDescent="0.45">
@@ -18976,7 +18502,7 @@
         <v>1001</v>
       </c>
       <c r="B463" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="C463">
         <v>3</v>
@@ -18985,7 +18511,7 @@
         <v>0</v>
       </c>
       <c r="E463" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="464" spans="1:5" x14ac:dyDescent="0.45">
@@ -19002,7 +18528,7 @@
         <v>0</v>
       </c>
       <c r="E464" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="465" spans="1:5" x14ac:dyDescent="0.45">
@@ -19019,7 +18545,7 @@
         <v>0</v>
       </c>
       <c r="E465" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="466" spans="1:5" x14ac:dyDescent="0.45">
@@ -19036,7 +18562,7 @@
         <v>0</v>
       </c>
       <c r="E466" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="467" spans="1:5" x14ac:dyDescent="0.45">
@@ -19053,7 +18579,7 @@
         <v>0</v>
       </c>
       <c r="E467" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="468" spans="1:5" x14ac:dyDescent="0.45">
@@ -19070,7 +18596,7 @@
         <v>0</v>
       </c>
       <c r="E468" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="469" spans="1:5" x14ac:dyDescent="0.45">
@@ -19087,7 +18613,7 @@
         <v>0</v>
       </c>
       <c r="E469" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="470" spans="1:5" x14ac:dyDescent="0.45">
@@ -19104,7 +18630,7 @@
         <v>0</v>
       </c>
       <c r="E470" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="471" spans="1:5" x14ac:dyDescent="0.45">
@@ -19121,7 +18647,7 @@
         <v>0</v>
       </c>
       <c r="E471" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="472" spans="1:5" x14ac:dyDescent="0.45">
@@ -19138,7 +18664,7 @@
         <v>0</v>
       </c>
       <c r="E472" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="473" spans="1:5" x14ac:dyDescent="0.45">
@@ -19155,7 +18681,7 @@
         <v>0</v>
       </c>
       <c r="E473" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="474" spans="1:5" x14ac:dyDescent="0.45">
@@ -19189,7 +18715,7 @@
         <v>0</v>
       </c>
       <c r="E475" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="476" spans="1:5" x14ac:dyDescent="0.45">
@@ -19206,7 +18732,7 @@
         <v>0</v>
       </c>
       <c r="E476" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="477" spans="1:5" x14ac:dyDescent="0.45">
@@ -19223,7 +18749,7 @@
         <v>0</v>
       </c>
       <c r="E477" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="478" spans="1:5" x14ac:dyDescent="0.45">
@@ -19240,7 +18766,7 @@
         <v>0</v>
       </c>
       <c r="E478" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="479" spans="1:5" x14ac:dyDescent="0.45">
@@ -19257,7 +18783,7 @@
         <v>0</v>
       </c>
       <c r="E479" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="480" spans="1:5" x14ac:dyDescent="0.45">
@@ -19274,7 +18800,7 @@
         <v>0</v>
       </c>
       <c r="E480" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="481" spans="1:5" x14ac:dyDescent="0.45">
@@ -19291,7 +18817,7 @@
         <v>0</v>
       </c>
       <c r="E481" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="482" spans="1:5" x14ac:dyDescent="0.45">
@@ -19308,7 +18834,7 @@
         <v>0</v>
       </c>
       <c r="E482" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="483" spans="1:5" x14ac:dyDescent="0.45">
@@ -19325,7 +18851,7 @@
         <v>0</v>
       </c>
       <c r="E483" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="484" spans="1:5" x14ac:dyDescent="0.45">
@@ -19342,7 +18868,7 @@
         <v>0</v>
       </c>
       <c r="E484" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="485" spans="1:5" x14ac:dyDescent="0.45">
@@ -19350,7 +18876,7 @@
         <v>1009</v>
       </c>
       <c r="B485" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
       <c r="C485">
         <v>1</v>
@@ -19359,7 +18885,7 @@
         <v>0</v>
       </c>
       <c r="E485" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
     </row>
     <row r="486" spans="1:5" x14ac:dyDescent="0.45">
@@ -19367,7 +18893,7 @@
         <v>1009</v>
       </c>
       <c r="B486" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
       <c r="C486">
         <v>2</v>
@@ -19376,7 +18902,7 @@
         <v>0</v>
       </c>
       <c r="E486" t="s">
-        <v>1211</v>
+        <v>1210</v>
       </c>
     </row>
     <row r="487" spans="1:5" x14ac:dyDescent="0.45">
@@ -19384,7 +18910,7 @@
         <v>1009</v>
       </c>
       <c r="B487" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
       <c r="C487">
         <v>3</v>
@@ -19393,7 +18919,7 @@
         <v>0</v>
       </c>
       <c r="E487" t="s">
-        <v>1212</v>
+        <v>1211</v>
       </c>
     </row>
     <row r="488" spans="1:5" x14ac:dyDescent="0.45">
@@ -19401,7 +18927,7 @@
         <v>1010</v>
       </c>
       <c r="B488" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="C488">
         <v>1</v>
@@ -19410,7 +18936,7 @@
         <v>0</v>
       </c>
       <c r="E488" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="489" spans="1:5" x14ac:dyDescent="0.45">
@@ -19418,7 +18944,7 @@
         <v>1010</v>
       </c>
       <c r="B489" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="C489">
         <v>2</v>
@@ -19427,7 +18953,7 @@
         <v>0</v>
       </c>
       <c r="E489" t="s">
-        <v>1214</v>
+        <v>1213</v>
       </c>
     </row>
     <row r="490" spans="1:5" x14ac:dyDescent="0.45">
@@ -19435,7 +18961,7 @@
         <v>1010</v>
       </c>
       <c r="B490" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="C490">
         <v>3</v>
@@ -19444,7 +18970,7 @@
         <v>0</v>
       </c>
       <c r="E490" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="491" spans="1:5" x14ac:dyDescent="0.45">
@@ -19452,7 +18978,7 @@
         <v>1011</v>
       </c>
       <c r="B491" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="C491">
         <v>1</v>
@@ -19461,7 +18987,7 @@
         <v>0</v>
       </c>
       <c r="E491" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="492" spans="1:5" x14ac:dyDescent="0.45">
@@ -19469,7 +18995,7 @@
         <v>1011</v>
       </c>
       <c r="B492" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="C492">
         <v>2</v>
@@ -19478,7 +19004,7 @@
         <v>0</v>
       </c>
       <c r="E492" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="493" spans="1:5" x14ac:dyDescent="0.45">
@@ -19486,7 +19012,7 @@
         <v>1011</v>
       </c>
       <c r="B493" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="C493">
         <v>3</v>
@@ -19503,7 +19029,7 @@
         <v>1012</v>
       </c>
       <c r="B494" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
       <c r="C494">
         <v>1</v>
@@ -19512,7 +19038,7 @@
         <v>0</v>
       </c>
       <c r="E494" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
     </row>
     <row r="495" spans="1:5" x14ac:dyDescent="0.45">
@@ -19520,7 +19046,7 @@
         <v>1012</v>
       </c>
       <c r="B495" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
       <c r="C495">
         <v>2</v>
@@ -19529,7 +19055,7 @@
         <v>0</v>
       </c>
       <c r="E495" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="496" spans="1:5" x14ac:dyDescent="0.45">
@@ -19537,7 +19063,7 @@
         <v>1012</v>
       </c>
       <c r="B496" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
       <c r="C496">
         <v>3</v>
@@ -19554,7 +19080,7 @@
         <v>1013</v>
       </c>
       <c r="B497" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
       <c r="C497">
         <v>1</v>
@@ -19563,7 +19089,7 @@
         <v>0</v>
       </c>
       <c r="E497" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
     </row>
     <row r="498" spans="1:5" x14ac:dyDescent="0.45">
@@ -19571,7 +19097,7 @@
         <v>1013</v>
       </c>
       <c r="B498" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
       <c r="C498">
         <v>2</v>
@@ -19580,7 +19106,7 @@
         <v>0</v>
       </c>
       <c r="E498" t="s">
-        <v>1221</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="499" spans="1:5" x14ac:dyDescent="0.45">
@@ -19588,7 +19114,7 @@
         <v>1013</v>
       </c>
       <c r="B499" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
       <c r="C499">
         <v>3</v>
@@ -19653,10 +19179,10 @@
     </row>
     <row r="503" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A503" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="B503" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="C503">
         <v>1</v>
@@ -19665,15 +19191,15 @@
         <v>0</v>
       </c>
       <c r="E503" t="s">
-        <v>1222</v>
+        <v>1221</v>
       </c>
     </row>
     <row r="504" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A504" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="B504" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="C504">
         <v>2</v>
@@ -19682,15 +19208,15 @@
         <v>0</v>
       </c>
       <c r="E504" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="505" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A505" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="B505" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="C505">
         <v>3</v>
@@ -19704,10 +19230,10 @@
     </row>
     <row r="506" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A506" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="B506" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
       <c r="C506">
         <v>1</v>
@@ -19716,15 +19242,15 @@
         <v>1</v>
       </c>
       <c r="E506" t="s">
-        <v>1226</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="507" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A507" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="B507" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
       <c r="C507">
         <v>2</v>
@@ -19733,15 +19259,15 @@
         <v>0</v>
       </c>
       <c r="E507" t="s">
-        <v>1224</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="508" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A508" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="B508" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
       <c r="C508">
         <v>3</v>
@@ -19750,15 +19276,15 @@
         <v>0</v>
       </c>
       <c r="E508" t="s">
-        <v>1225</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="509" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A509" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
       <c r="B509" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
       <c r="C509">
         <v>1</v>
@@ -19767,15 +19293,15 @@
         <v>1</v>
       </c>
       <c r="E509" t="s">
-        <v>1226</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="510" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A510" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
       <c r="B510" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
       <c r="C510">
         <v>2</v>
@@ -19784,15 +19310,15 @@
         <v>0</v>
       </c>
       <c r="E510" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="511" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A511" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
       <c r="B511" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
       <c r="C511">
         <v>3</v>
@@ -19801,15 +19327,15 @@
         <v>0</v>
       </c>
       <c r="E511" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="512" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A512" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="B512" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="C512">
         <v>1</v>
@@ -19818,15 +19344,15 @@
         <v>0</v>
       </c>
       <c r="E512" t="s">
-        <v>1229</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="513" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A513" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="B513" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="C513">
         <v>2</v>
@@ -19835,15 +19361,15 @@
         <v>0</v>
       </c>
       <c r="E513" t="s">
-        <v>1230</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="514" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A514" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="B514" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="C514">
         <v>3</v>
@@ -19852,15 +19378,15 @@
         <v>0</v>
       </c>
       <c r="E514" t="s">
-        <v>1231</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="515" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A515" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="B515" t="s">
-        <v>1175</v>
+        <v>1174</v>
       </c>
       <c r="C515">
         <v>1</v>
@@ -19869,15 +19395,15 @@
         <v>0</v>
       </c>
       <c r="E515" t="s">
-        <v>1232</v>
+        <v>1231</v>
       </c>
     </row>
     <row r="516" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A516" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="B516" t="s">
-        <v>1175</v>
+        <v>1174</v>
       </c>
       <c r="C516">
         <v>2</v>
@@ -19886,15 +19412,15 @@
         <v>0</v>
       </c>
       <c r="E516" t="s">
-        <v>1233</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="517" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A517" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="B517" t="s">
-        <v>1175</v>
+        <v>1174</v>
       </c>
       <c r="C517">
         <v>3</v>
@@ -19903,15 +19429,15 @@
         <v>0</v>
       </c>
       <c r="E517" t="s">
-        <v>1234</v>
+        <v>1233</v>
       </c>
     </row>
     <row r="518" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A518" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
       <c r="B518" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="C518">
         <v>1</v>
@@ -19925,10 +19451,10 @@
     </row>
     <row r="519" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A519" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
       <c r="B519" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="C519">
         <v>2</v>
@@ -19937,15 +19463,15 @@
         <v>1</v>
       </c>
       <c r="E519" t="s">
-        <v>1226</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="520" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A520" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
       <c r="B520" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="C520">
         <v>3</v>
@@ -19954,15 +19480,15 @@
         <v>0</v>
       </c>
       <c r="E520" t="s">
-        <v>1235</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="521" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A521" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
       <c r="B521" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="C521">
         <v>1</v>
@@ -19971,15 +19497,15 @@
         <v>1</v>
       </c>
       <c r="E521" t="s">
-        <v>1226</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="522" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A522" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
       <c r="B522" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="C522">
         <v>2</v>
@@ -19993,10 +19519,10 @@
     </row>
     <row r="523" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A523" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
       <c r="B523" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="C523">
         <v>3</v>
@@ -20005,15 +19531,15 @@
         <v>0</v>
       </c>
       <c r="E523" t="s">
-        <v>1236</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="524" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A524" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
       <c r="B524" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="C524">
         <v>1</v>
@@ -20022,15 +19548,15 @@
         <v>1</v>
       </c>
       <c r="E524" t="s">
-        <v>1226</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="525" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A525" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
       <c r="B525" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="C525">
         <v>2</v>
@@ -20039,15 +19565,15 @@
         <v>0</v>
       </c>
       <c r="E525" t="s">
-        <v>1237</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="526" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A526" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
       <c r="B526" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="C526">
         <v>3</v>
@@ -20056,15 +19582,15 @@
         <v>0</v>
       </c>
       <c r="E526" t="s">
-        <v>1238</v>
+        <v>1237</v>
       </c>
     </row>
     <row r="527" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A527" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="B527" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="C527">
         <v>1</v>
@@ -20073,15 +19599,15 @@
         <v>0</v>
       </c>
       <c r="E527" t="s">
-        <v>1239</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="528" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A528" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="B528" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="C528">
         <v>2</v>
@@ -20090,15 +19616,15 @@
         <v>0</v>
       </c>
       <c r="E528" t="s">
-        <v>1240</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="529" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A529" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="B529" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="C529">
         <v>3</v>
@@ -20107,15 +19633,15 @@
         <v>0</v>
       </c>
       <c r="E529" t="s">
-        <v>1241</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="530" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A530" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
       <c r="B530" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
       <c r="C530">
         <v>1</v>
@@ -20124,15 +19650,15 @@
         <v>0</v>
       </c>
       <c r="E530" t="s">
-        <v>1242</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="531" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A531" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
       <c r="B531" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
       <c r="C531">
         <v>2</v>
@@ -20141,15 +19667,15 @@
         <v>0</v>
       </c>
       <c r="E531" t="s">
-        <v>1243</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="532" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A532" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
       <c r="B532" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
       <c r="C532">
         <v>3</v>
@@ -20158,7 +19684,7 @@
         <v>0</v>
       </c>
       <c r="E532" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="533" spans="1:5" x14ac:dyDescent="0.45">
@@ -20214,10 +19740,10 @@
     </row>
     <row r="536" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A536" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
       <c r="B536" t="s">
-        <v>1187</v>
+        <v>1186</v>
       </c>
       <c r="C536">
         <v>1</v>
@@ -20226,15 +19752,15 @@
         <v>0</v>
       </c>
       <c r="E536" t="s">
-        <v>1245</v>
+        <v>1244</v>
       </c>
     </row>
     <row r="537" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A537" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
       <c r="B537" t="s">
-        <v>1187</v>
+        <v>1186</v>
       </c>
       <c r="C537">
         <v>2</v>
@@ -20243,15 +19769,15 @@
         <v>0</v>
       </c>
       <c r="E537" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="538" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A538" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
       <c r="B538" t="s">
-        <v>1187</v>
+        <v>1186</v>
       </c>
       <c r="C538">
         <v>3</v>
@@ -20260,15 +19786,15 @@
         <v>0</v>
       </c>
       <c r="E538" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="539" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A539" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="B539" t="s">
-        <v>1190</v>
+        <v>1189</v>
       </c>
       <c r="C539">
         <v>1</v>
@@ -20277,15 +19803,15 @@
         <v>0</v>
       </c>
       <c r="E539" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="540" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A540" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="B540" t="s">
-        <v>1190</v>
+        <v>1189</v>
       </c>
       <c r="C540">
         <v>2</v>
@@ -20294,15 +19820,15 @@
         <v>0</v>
       </c>
       <c r="E540" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="541" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A541" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="B541" t="s">
-        <v>1190</v>
+        <v>1189</v>
       </c>
       <c r="C541">
         <v>3</v>
@@ -20311,15 +19837,15 @@
         <v>0</v>
       </c>
       <c r="E541" t="s">
-        <v>1250</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="542" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A542" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
       <c r="B542" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="C542">
         <v>1</v>
@@ -20328,15 +19854,15 @@
         <v>0</v>
       </c>
       <c r="E542" t="s">
-        <v>1251</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="543" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A543" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
       <c r="B543" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="C543">
         <v>2</v>
@@ -20345,15 +19871,15 @@
         <v>0</v>
       </c>
       <c r="E543" t="s">
-        <v>1252</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="544" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A544" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
       <c r="B544" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="C544">
         <v>3</v>
@@ -20362,15 +19888,15 @@
         <v>0</v>
       </c>
       <c r="E544" t="s">
-        <v>1253</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="545" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A545" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
       <c r="B545" t="s">
-        <v>1193</v>
+        <v>1192</v>
       </c>
       <c r="C545">
         <v>1</v>
@@ -20379,15 +19905,15 @@
         <v>0</v>
       </c>
       <c r="E545" t="s">
-        <v>1254</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="546" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A546" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
       <c r="B546" t="s">
-        <v>1193</v>
+        <v>1192</v>
       </c>
       <c r="C546">
         <v>2</v>
@@ -20396,15 +19922,15 @@
         <v>0</v>
       </c>
       <c r="E546" t="s">
-        <v>1255</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="547" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A547" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
       <c r="B547" t="s">
-        <v>1193</v>
+        <v>1192</v>
       </c>
       <c r="C547">
         <v>3</v>
@@ -20413,15 +19939,15 @@
         <v>0</v>
       </c>
       <c r="E547" t="s">
-        <v>1256</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="548" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A548" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="B548" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
       <c r="C548">
         <v>1</v>
@@ -20430,15 +19956,15 @@
         <v>0</v>
       </c>
       <c r="E548" t="s">
-        <v>1257</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="549" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A549" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="B549" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
       <c r="C549">
         <v>2</v>
@@ -20447,15 +19973,15 @@
         <v>0</v>
       </c>
       <c r="E549" t="s">
-        <v>1258</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="550" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A550" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="B550" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
       <c r="C550">
         <v>3</v>
@@ -20464,7 +19990,7 @@
         <v>0</v>
       </c>
       <c r="E550" t="s">
-        <v>1259</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="551" spans="1:5" x14ac:dyDescent="0.45">
@@ -20526,13 +20052,13 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{494C60D6-2426-4CE0-9CA4-43EAAA3DD51B}">
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="11.73046875" customWidth="1"/>
-    <col min="2" max="2" width="18.1328125" customWidth="1"/>
+    <col min="2" max="2" width="22.19921875" customWidth="1"/>
     <col min="3" max="3" width="18.265625" customWidth="1"/>
-    <col min="4" max="4" width="17.1328125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18" customWidth="1"/>
     <col min="5" max="5" width="11.86328125" customWidth="1"/>
     <col min="6" max="6" width="14.59765625" customWidth="1"/>
   </cols>
@@ -20551,7 +20077,7 @@
         <v>45</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>1468</v>
+        <v>1467</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>75</v>
@@ -20559,19 +20085,19 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
-        <v>348</v>
+        <v>113</v>
       </c>
       <c r="B2" t="s">
-        <v>462</v>
+        <v>136</v>
       </c>
       <c r="C2" t="s">
-        <v>1261</v>
+        <v>1497</v>
       </c>
       <c r="D2" t="s">
-        <v>1472</v>
+        <v>1500</v>
       </c>
       <c r="E2" t="s">
-        <v>1260</v>
+        <v>1503</v>
       </c>
       <c r="F2">
         <v>1</v>
@@ -20579,19 +20105,19 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>348</v>
+        <v>113</v>
       </c>
       <c r="B3" t="s">
-        <v>462</v>
+        <v>136</v>
       </c>
       <c r="C3" t="s">
-        <v>1262</v>
+        <v>1498</v>
       </c>
       <c r="D3" t="s">
-        <v>1473</v>
+        <v>1502</v>
       </c>
       <c r="E3" t="s">
-        <v>1469</v>
+        <v>1503</v>
       </c>
       <c r="F3">
         <v>1</v>
@@ -20599,19 +20125,19 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
-        <v>348</v>
+        <v>113</v>
       </c>
       <c r="B4" t="s">
-        <v>462</v>
+        <v>136</v>
       </c>
       <c r="C4" t="s">
-        <v>463</v>
+        <v>1499</v>
       </c>
       <c r="D4" t="s">
-        <v>1474</v>
+        <v>1501</v>
       </c>
       <c r="E4" t="s">
-        <v>1469</v>
+        <v>1503</v>
       </c>
       <c r="F4">
         <v>1</v>
@@ -20625,13 +20151,13 @@
         <v>462</v>
       </c>
       <c r="C5" t="s">
-        <v>1263</v>
+        <v>1260</v>
       </c>
       <c r="D5" t="s">
-        <v>1475</v>
+        <v>1508</v>
       </c>
       <c r="E5" t="s">
-        <v>1469</v>
+        <v>1259</v>
       </c>
       <c r="F5">
         <v>1</v>
@@ -20639,62 +20165,62 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>757</v>
+        <v>348</v>
       </c>
       <c r="B6" t="s">
-        <v>765</v>
+        <v>462</v>
       </c>
       <c r="C6" t="s">
-        <v>1470</v>
+        <v>1261</v>
       </c>
       <c r="D6" t="s">
         <v>1471</v>
       </c>
       <c r="E6" t="s">
-        <v>1476</v>
+        <v>1468</v>
       </c>
       <c r="F6">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
-        <v>757</v>
+        <v>348</v>
       </c>
       <c r="B7" t="s">
-        <v>765</v>
+        <v>462</v>
       </c>
       <c r="C7" t="s">
-        <v>1477</v>
+        <v>463</v>
       </c>
       <c r="D7" t="s">
-        <v>1478</v>
+        <v>1472</v>
       </c>
       <c r="E7" t="s">
-        <v>1476</v>
+        <v>1468</v>
       </c>
       <c r="F7">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
-        <v>757</v>
+        <v>348</v>
       </c>
       <c r="B8" t="s">
-        <v>765</v>
+        <v>462</v>
       </c>
       <c r="C8" t="s">
-        <v>1479</v>
+        <v>1262</v>
       </c>
       <c r="D8" t="s">
-        <v>1481</v>
+        <v>1473</v>
       </c>
       <c r="E8" t="s">
-        <v>1476</v>
+        <v>1468</v>
       </c>
       <c r="F8">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.45">
@@ -20705,16 +20231,16 @@
         <v>765</v>
       </c>
       <c r="C9" t="s">
-        <v>1480</v>
+        <v>1469</v>
       </c>
       <c r="D9" t="s">
-        <v>1482</v>
+        <v>1470</v>
       </c>
       <c r="E9" t="s">
-        <v>1476</v>
+        <v>1474</v>
       </c>
       <c r="F9">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.45">
@@ -20725,16 +20251,16 @@
         <v>765</v>
       </c>
       <c r="C10" t="s">
-        <v>1483</v>
+        <v>1475</v>
       </c>
       <c r="D10" t="s">
-        <v>1484</v>
+        <v>1476</v>
       </c>
       <c r="E10" t="s">
-        <v>1476</v>
+        <v>1474</v>
       </c>
       <c r="F10">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.45">
@@ -20745,13 +20271,13 @@
         <v>765</v>
       </c>
       <c r="C11" t="s">
-        <v>1485</v>
+        <v>1477</v>
       </c>
       <c r="D11" t="s">
-        <v>1485</v>
+        <v>1479</v>
       </c>
       <c r="E11" t="s">
-        <v>1476</v>
+        <v>1474</v>
       </c>
       <c r="F11">
         <v>2</v>
@@ -20765,16 +20291,16 @@
         <v>765</v>
       </c>
       <c r="C12" t="s">
-        <v>1487</v>
+        <v>1478</v>
       </c>
       <c r="D12" t="s">
-        <v>1486</v>
+        <v>1480</v>
       </c>
       <c r="E12" t="s">
-        <v>1476</v>
+        <v>1474</v>
       </c>
       <c r="F12">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.45">
@@ -20785,13 +20311,13 @@
         <v>765</v>
       </c>
       <c r="C13" t="s">
-        <v>1488</v>
+        <v>1481</v>
       </c>
       <c r="D13" t="s">
-        <v>1494</v>
+        <v>1482</v>
       </c>
       <c r="E13" t="s">
-        <v>1476</v>
+        <v>1474</v>
       </c>
       <c r="F13">
         <v>1</v>
@@ -20805,16 +20331,16 @@
         <v>765</v>
       </c>
       <c r="C14" t="s">
-        <v>1489</v>
+        <v>1483</v>
       </c>
       <c r="D14" t="s">
-        <v>1489</v>
+        <v>1483</v>
       </c>
       <c r="E14" t="s">
-        <v>1476</v>
+        <v>1474</v>
       </c>
       <c r="F14">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.45">
@@ -20825,13 +20351,13 @@
         <v>765</v>
       </c>
       <c r="C15" t="s">
-        <v>1490</v>
+        <v>1485</v>
       </c>
       <c r="D15" t="s">
-        <v>1495</v>
+        <v>1484</v>
       </c>
       <c r="E15" t="s">
-        <v>1476</v>
+        <v>1474</v>
       </c>
       <c r="F15">
         <v>1</v>
@@ -20845,16 +20371,16 @@
         <v>765</v>
       </c>
       <c r="C16" t="s">
-        <v>1491</v>
+        <v>1486</v>
       </c>
       <c r="D16" t="s">
-        <v>1496</v>
+        <v>1492</v>
       </c>
       <c r="E16" t="s">
-        <v>1476</v>
+        <v>1474</v>
       </c>
       <c r="F16">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.45">
@@ -20865,13 +20391,13 @@
         <v>765</v>
       </c>
       <c r="C17" t="s">
-        <v>1492</v>
+        <v>1487</v>
       </c>
       <c r="D17" t="s">
-        <v>1497</v>
+        <v>1487</v>
       </c>
       <c r="E17" t="s">
-        <v>1476</v>
+        <v>1474</v>
       </c>
       <c r="F17">
         <v>1</v>
@@ -20885,15 +20411,175 @@
         <v>765</v>
       </c>
       <c r="C18" t="s">
+        <v>1488</v>
+      </c>
+      <c r="D18" t="s">
         <v>1493</v>
       </c>
-      <c r="D18" t="s">
-        <v>1498</v>
-      </c>
       <c r="E18" t="s">
-        <v>1476</v>
+        <v>1474</v>
       </c>
       <c r="F18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A19" t="s">
+        <v>757</v>
+      </c>
+      <c r="B19" t="s">
+        <v>765</v>
+      </c>
+      <c r="C19" t="s">
+        <v>1489</v>
+      </c>
+      <c r="D19" t="s">
+        <v>1494</v>
+      </c>
+      <c r="E19" t="s">
+        <v>1474</v>
+      </c>
+      <c r="F19">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A20" t="s">
+        <v>757</v>
+      </c>
+      <c r="B20" t="s">
+        <v>765</v>
+      </c>
+      <c r="C20" t="s">
+        <v>1490</v>
+      </c>
+      <c r="D20" t="s">
+        <v>1495</v>
+      </c>
+      <c r="E20" t="s">
+        <v>1474</v>
+      </c>
+      <c r="F20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A21" t="s">
+        <v>757</v>
+      </c>
+      <c r="B21" t="s">
+        <v>765</v>
+      </c>
+      <c r="C21" t="s">
+        <v>1491</v>
+      </c>
+      <c r="D21" t="s">
+        <v>1496</v>
+      </c>
+      <c r="E21" t="s">
+        <v>1474</v>
+      </c>
+      <c r="F21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A22" t="s">
+        <v>1140</v>
+      </c>
+      <c r="B22" t="s">
+        <v>1167</v>
+      </c>
+      <c r="C22" t="s">
+        <v>1504</v>
+      </c>
+      <c r="D22" t="s">
+        <v>1505</v>
+      </c>
+      <c r="E22" t="s">
+        <v>1506</v>
+      </c>
+      <c r="F22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A23" t="s">
+        <v>1141</v>
+      </c>
+      <c r="B23" t="s">
+        <v>1170</v>
+      </c>
+      <c r="C23" t="s">
+        <v>1504</v>
+      </c>
+      <c r="D23" t="s">
+        <v>1505</v>
+      </c>
+      <c r="E23" t="s">
+        <v>1506</v>
+      </c>
+      <c r="F23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A24" t="s">
+        <v>1144</v>
+      </c>
+      <c r="B24" t="s">
+        <v>1176</v>
+      </c>
+      <c r="C24" t="s">
+        <v>1504</v>
+      </c>
+      <c r="D24" t="s">
+        <v>1505</v>
+      </c>
+      <c r="E24" t="s">
+        <v>1506</v>
+      </c>
+      <c r="F24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A25" t="s">
+        <v>1145</v>
+      </c>
+      <c r="B25" t="s">
+        <v>1178</v>
+      </c>
+      <c r="C25" t="s">
+        <v>1504</v>
+      </c>
+      <c r="D25" t="s">
+        <v>1505</v>
+      </c>
+      <c r="E25" t="s">
+        <v>1506</v>
+      </c>
+      <c r="F25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A26" t="s">
+        <v>1146</v>
+      </c>
+      <c r="B26" t="s">
+        <v>1180</v>
+      </c>
+      <c r="C26" t="s">
+        <v>1504</v>
+      </c>
+      <c r="D26" t="s">
+        <v>1505</v>
+      </c>
+      <c r="E26" t="s">
+        <v>1506</v>
+      </c>
+      <c r="F26">
         <v>1</v>
       </c>
     </row>
@@ -20916,176 +20602,176 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
-        <v>1264</v>
+        <v>1263</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>1330</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>1331</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>1401</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>1332</v>
       </c>
       <c r="E1" s="1"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
-        <v>1265</v>
+        <v>1264</v>
       </c>
       <c r="B2" t="s">
         <v>510</v>
       </c>
       <c r="C2" t="s">
-        <v>1402</v>
+        <v>1401</v>
       </c>
       <c r="D2" t="s">
-        <v>1334</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>1266</v>
+        <v>1265</v>
       </c>
       <c r="B3" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
       <c r="C3" t="s">
-        <v>1403</v>
+        <v>1402</v>
       </c>
       <c r="D3" t="s">
-        <v>1335</v>
+        <v>1334</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
-        <v>1267</v>
+        <v>1266</v>
       </c>
       <c r="B4" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
       <c r="C4" t="s">
-        <v>1404</v>
+        <v>1403</v>
       </c>
       <c r="D4" t="s">
-        <v>1336</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>1268</v>
+        <v>1267</v>
       </c>
       <c r="B5" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="C5" t="s">
-        <v>1405</v>
+        <v>1404</v>
       </c>
       <c r="D5" t="s">
-        <v>1337</v>
+        <v>1336</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>1269</v>
+        <v>1268</v>
       </c>
       <c r="B6" t="s">
-        <v>1341</v>
+        <v>1340</v>
       </c>
       <c r="C6" t="s">
         <v>286</v>
       </c>
       <c r="D6" t="s">
-        <v>1336</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
-        <v>1270</v>
+        <v>1269</v>
       </c>
       <c r="B7" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="C7" t="s">
-        <v>1406</v>
+        <v>1405</v>
       </c>
       <c r="D7" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
-        <v>1271</v>
+        <v>1270</v>
       </c>
       <c r="B8" t="s">
-        <v>1343</v>
+        <v>1342</v>
       </c>
       <c r="C8" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="D8" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
-        <v>1272</v>
+        <v>1271</v>
       </c>
       <c r="B9" t="s">
-        <v>1344</v>
+        <v>1343</v>
       </c>
       <c r="C9" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="D9" t="s">
-        <v>1336</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
-        <v>1273</v>
+        <v>1272</v>
       </c>
       <c r="B10" t="s">
-        <v>1345</v>
+        <v>1344</v>
       </c>
       <c r="C10" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
       <c r="D10" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
-        <v>1274</v>
+        <v>1273</v>
       </c>
       <c r="B11" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
       <c r="C11" t="s">
-        <v>1446</v>
+        <v>1445</v>
       </c>
       <c r="D11" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
-        <v>1275</v>
+        <v>1274</v>
       </c>
       <c r="B12" t="s">
-        <v>1347</v>
+        <v>1346</v>
       </c>
       <c r="C12" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="D12" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
-        <v>1276</v>
+        <v>1275</v>
       </c>
       <c r="B13" t="s">
         <v>5</v>
@@ -21094,614 +20780,614 @@
         <v>6</v>
       </c>
       <c r="D13" t="s">
-        <v>1334</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
-        <v>1277</v>
+        <v>1276</v>
       </c>
       <c r="B14" t="s">
-        <v>1348</v>
+        <v>1347</v>
       </c>
       <c r="C14" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D14" t="s">
-        <v>1334</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
-        <v>1278</v>
+        <v>1277</v>
       </c>
       <c r="B15" t="s">
-        <v>1349</v>
+        <v>1348</v>
       </c>
       <c r="C15" t="s">
-        <v>1447</v>
+        <v>1446</v>
       </c>
       <c r="D15" t="s">
-        <v>1336</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
-        <v>1279</v>
+        <v>1278</v>
       </c>
       <c r="B16" t="s">
-        <v>1350</v>
+        <v>1349</v>
       </c>
       <c r="C16" t="s">
-        <v>1412</v>
+        <v>1411</v>
       </c>
       <c r="D16" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
-        <v>1280</v>
+        <v>1279</v>
       </c>
       <c r="B17" t="s">
-        <v>1351</v>
+        <v>1350</v>
       </c>
       <c r="C17" t="s">
-        <v>1413</v>
+        <v>1412</v>
       </c>
       <c r="D17" t="s">
-        <v>1336</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="B18" t="s">
-        <v>1352</v>
+        <v>1351</v>
       </c>
       <c r="C18" t="s">
-        <v>1414</v>
+        <v>1413</v>
       </c>
       <c r="D18" t="s">
-        <v>1335</v>
+        <v>1334</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
-        <v>1282</v>
+        <v>1281</v>
       </c>
       <c r="B19" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="C19" t="s">
-        <v>1415</v>
+        <v>1414</v>
       </c>
       <c r="D19" t="s">
-        <v>1334</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
-        <v>1283</v>
+        <v>1282</v>
       </c>
       <c r="B20" t="s">
-        <v>1354</v>
+        <v>1353</v>
       </c>
       <c r="C20" t="s">
-        <v>1416</v>
+        <v>1415</v>
       </c>
       <c r="D20" t="s">
-        <v>1336</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
-        <v>1284</v>
+        <v>1283</v>
       </c>
       <c r="B21" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="C21" t="s">
-        <v>1453</v>
+        <v>1452</v>
       </c>
       <c r="D21" t="s">
-        <v>1334</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="B22" t="s">
-        <v>1356</v>
+        <v>1355</v>
       </c>
       <c r="C22" t="s">
-        <v>1454</v>
+        <v>1453</v>
       </c>
       <c r="D22" t="s">
-        <v>1335</v>
+        <v>1334</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
-        <v>1286</v>
+        <v>1285</v>
       </c>
       <c r="B23" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="C23" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="D23" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="B24" t="s">
-        <v>1358</v>
+        <v>1357</v>
       </c>
       <c r="C24" t="s">
-        <v>1418</v>
+        <v>1417</v>
       </c>
       <c r="D24" t="s">
-        <v>1334</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
-        <v>1288</v>
+        <v>1287</v>
       </c>
       <c r="B25" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="C25" t="s">
-        <v>1419</v>
+        <v>1418</v>
       </c>
       <c r="D25" t="s">
-        <v>1334</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
-        <v>1289</v>
+        <v>1288</v>
       </c>
       <c r="B26" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="C26" t="s">
-        <v>1460</v>
+        <v>1459</v>
       </c>
       <c r="D26" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
-        <v>1290</v>
+        <v>1289</v>
       </c>
       <c r="B27" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="C27" t="s">
-        <v>1448</v>
+        <v>1447</v>
       </c>
       <c r="D27" t="s">
-        <v>1335</v>
+        <v>1334</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
-        <v>1291</v>
+        <v>1290</v>
       </c>
       <c r="B28" t="s">
-        <v>1362</v>
+        <v>1361</v>
       </c>
       <c r="C28" t="s">
-        <v>1449</v>
+        <v>1448</v>
       </c>
       <c r="D28" t="s">
-        <v>1334</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
-        <v>1292</v>
+        <v>1291</v>
       </c>
       <c r="B29" t="s">
-        <v>1363</v>
+        <v>1362</v>
       </c>
       <c r="C29" t="s">
-        <v>1420</v>
+        <v>1419</v>
       </c>
       <c r="D29" t="s">
-        <v>1337</v>
+        <v>1336</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
-        <v>1293</v>
+        <v>1292</v>
       </c>
       <c r="B30" t="s">
-        <v>1364</v>
+        <v>1363</v>
       </c>
       <c r="C30" t="s">
-        <v>1450</v>
+        <v>1449</v>
       </c>
       <c r="D30" t="s">
-        <v>1335</v>
+        <v>1334</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
-        <v>1294</v>
+        <v>1293</v>
       </c>
       <c r="B31" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
       <c r="C31" t="s">
-        <v>1421</v>
+        <v>1420</v>
       </c>
       <c r="D31" t="s">
-        <v>1336</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
-        <v>1295</v>
+        <v>1294</v>
       </c>
       <c r="B32" t="s">
-        <v>1366</v>
+        <v>1365</v>
       </c>
       <c r="C32" t="s">
-        <v>1422</v>
+        <v>1421</v>
       </c>
       <c r="D32" t="s">
-        <v>1334</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
-        <v>1296</v>
+        <v>1295</v>
       </c>
       <c r="B33" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="C33" t="s">
-        <v>1423</v>
+        <v>1422</v>
       </c>
       <c r="D33" t="s">
-        <v>1334</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
-        <v>1297</v>
+        <v>1296</v>
       </c>
       <c r="B34" t="s">
-        <v>1368</v>
+        <v>1367</v>
       </c>
       <c r="C34" t="s">
-        <v>1424</v>
+        <v>1423</v>
       </c>
       <c r="D34" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A35" t="s">
-        <v>1298</v>
+        <v>1297</v>
       </c>
       <c r="B35" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
       <c r="C35" t="s">
-        <v>1425</v>
+        <v>1424</v>
       </c>
       <c r="D35" t="s">
-        <v>1336</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A36" t="s">
-        <v>1299</v>
+        <v>1298</v>
       </c>
       <c r="B36" t="s">
-        <v>1370</v>
+        <v>1369</v>
       </c>
       <c r="C36" t="s">
-        <v>1459</v>
+        <v>1458</v>
       </c>
       <c r="D36" t="s">
-        <v>1334</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A37" t="s">
-        <v>1300</v>
+        <v>1299</v>
       </c>
       <c r="B37" t="s">
-        <v>1371</v>
+        <v>1370</v>
       </c>
       <c r="C37" t="s">
-        <v>1426</v>
+        <v>1425</v>
       </c>
       <c r="D37" t="s">
-        <v>1335</v>
+        <v>1334</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A38" t="s">
-        <v>1301</v>
+        <v>1300</v>
       </c>
       <c r="B38" t="s">
-        <v>1372</v>
+        <v>1371</v>
       </c>
       <c r="C38" t="s">
-        <v>1427</v>
+        <v>1426</v>
       </c>
       <c r="D38" t="s">
-        <v>1334</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A39" t="s">
-        <v>1302</v>
+        <v>1301</v>
       </c>
       <c r="B39" t="s">
+        <v>1372</v>
+      </c>
+      <c r="C39" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D39" t="s">
         <v>1373</v>
-      </c>
-      <c r="C39" t="s">
-        <v>1455</v>
-      </c>
-      <c r="D39" t="s">
-        <v>1374</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A40" t="s">
-        <v>1303</v>
+        <v>1302</v>
       </c>
       <c r="B40" t="s">
-        <v>1375</v>
+        <v>1374</v>
       </c>
       <c r="C40" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="D40" t="s">
-        <v>1335</v>
+        <v>1334</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A41" t="s">
-        <v>1304</v>
+        <v>1303</v>
       </c>
       <c r="B41" t="s">
-        <v>1376</v>
+        <v>1375</v>
       </c>
       <c r="C41" t="s">
-        <v>1428</v>
+        <v>1427</v>
       </c>
       <c r="D41" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A42" t="s">
-        <v>1305</v>
+        <v>1304</v>
       </c>
       <c r="B42" t="s">
-        <v>1377</v>
+        <v>1376</v>
       </c>
       <c r="C42" t="s">
-        <v>1429</v>
+        <v>1428</v>
       </c>
       <c r="D42" t="s">
-        <v>1374</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A43" t="s">
-        <v>1306</v>
+        <v>1305</v>
       </c>
       <c r="B43" t="s">
-        <v>1378</v>
+        <v>1377</v>
       </c>
       <c r="C43" t="s">
-        <v>1461</v>
+        <v>1460</v>
       </c>
       <c r="D43" t="s">
-        <v>1336</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A44" t="s">
-        <v>1307</v>
+        <v>1306</v>
       </c>
       <c r="B44" t="s">
-        <v>1379</v>
+        <v>1378</v>
       </c>
       <c r="C44" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="D44" t="s">
-        <v>1335</v>
+        <v>1334</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A45" t="s">
-        <v>1308</v>
+        <v>1307</v>
       </c>
       <c r="B45" t="s">
-        <v>1380</v>
+        <v>1379</v>
       </c>
       <c r="C45" t="s">
-        <v>1431</v>
+        <v>1430</v>
       </c>
       <c r="D45" t="s">
-        <v>1334</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A46" t="s">
-        <v>1309</v>
+        <v>1308</v>
       </c>
       <c r="B46" t="s">
-        <v>1381</v>
+        <v>1380</v>
       </c>
       <c r="C46" t="s">
-        <v>1432</v>
+        <v>1431</v>
       </c>
       <c r="D46" t="s">
-        <v>1334</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A47" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="B47" t="s">
-        <v>1382</v>
+        <v>1381</v>
       </c>
       <c r="C47" t="s">
-        <v>1433</v>
+        <v>1432</v>
       </c>
       <c r="D47" t="s">
-        <v>1334</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A48" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="B48" t="s">
-        <v>1383</v>
+        <v>1382</v>
       </c>
       <c r="C48" t="s">
-        <v>1434</v>
+        <v>1433</v>
       </c>
       <c r="D48" t="s">
-        <v>1334</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A49" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="B49" t="s">
-        <v>1384</v>
+        <v>1383</v>
       </c>
       <c r="C49" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="D49" t="s">
-        <v>1334</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A50" t="s">
-        <v>1313</v>
+        <v>1312</v>
       </c>
       <c r="B50" t="s">
-        <v>1385</v>
+        <v>1384</v>
       </c>
       <c r="C50" t="s">
-        <v>1462</v>
+        <v>1461</v>
       </c>
       <c r="D50" t="s">
-        <v>1337</v>
+        <v>1336</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A51" t="s">
-        <v>1314</v>
+        <v>1313</v>
       </c>
       <c r="B51" t="s">
         <v>510</v>
       </c>
       <c r="C51" t="s">
-        <v>1464</v>
+        <v>1463</v>
       </c>
       <c r="D51" t="s">
-        <v>1336</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A52" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="B52" t="s">
-        <v>1386</v>
+        <v>1385</v>
       </c>
       <c r="C52" t="s">
-        <v>1435</v>
+        <v>1434</v>
       </c>
       <c r="D52" t="s">
-        <v>1335</v>
+        <v>1334</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A53" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="B53" t="s">
-        <v>1387</v>
+        <v>1386</v>
       </c>
       <c r="C53" t="s">
-        <v>1436</v>
+        <v>1435</v>
       </c>
       <c r="D53" t="s">
-        <v>1335</v>
+        <v>1334</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A54" t="s">
-        <v>1317</v>
+        <v>1316</v>
       </c>
       <c r="B54" t="s">
-        <v>1388</v>
+        <v>1387</v>
       </c>
       <c r="C54" t="s">
-        <v>1437</v>
+        <v>1436</v>
       </c>
       <c r="D54" t="s">
-        <v>1374</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A55" t="s">
-        <v>1318</v>
+        <v>1317</v>
       </c>
       <c r="B55" t="s">
-        <v>1389</v>
+        <v>1388</v>
       </c>
       <c r="C55" t="s">
-        <v>1438</v>
+        <v>1437</v>
       </c>
       <c r="D55" t="s">
-        <v>1334</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A56" t="s">
-        <v>1319</v>
+        <v>1318</v>
       </c>
       <c r="B56" t="s">
-        <v>1390</v>
+        <v>1389</v>
       </c>
       <c r="C56" t="s">
-        <v>1439</v>
+        <v>1438</v>
       </c>
       <c r="D56" t="s">
-        <v>1334</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A57" t="s">
-        <v>1320</v>
+        <v>1319</v>
       </c>
       <c r="B57" t="s">
         <v>1020</v>
@@ -21710,147 +21396,147 @@
         <v>1021</v>
       </c>
       <c r="D57" t="s">
-        <v>1334</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A58" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="B58" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="C58" t="s">
-        <v>1463</v>
+        <v>1462</v>
       </c>
       <c r="D58" t="s">
-        <v>1335</v>
+        <v>1334</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A59" t="s">
-        <v>1322</v>
+        <v>1321</v>
       </c>
       <c r="B59" t="s">
-        <v>1392</v>
+        <v>1391</v>
       </c>
       <c r="C59" t="s">
-        <v>1440</v>
+        <v>1439</v>
       </c>
       <c r="D59" t="s">
-        <v>1335</v>
+        <v>1334</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A60" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="B60" t="s">
-        <v>1393</v>
+        <v>1392</v>
       </c>
       <c r="C60" t="s">
-        <v>1452</v>
+        <v>1451</v>
       </c>
       <c r="D60" t="s">
-        <v>1335</v>
+        <v>1334</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A61" t="s">
-        <v>1324</v>
+        <v>1323</v>
       </c>
       <c r="B61" t="s">
-        <v>1394</v>
+        <v>1393</v>
       </c>
       <c r="C61" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
       <c r="D61" t="s">
-        <v>1335</v>
+        <v>1334</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A62" t="s">
-        <v>1325</v>
+        <v>1324</v>
       </c>
       <c r="B62" t="s">
-        <v>1395</v>
+        <v>1394</v>
       </c>
       <c r="C62" t="s">
-        <v>1457</v>
+        <v>1456</v>
       </c>
       <c r="D62" t="s">
-        <v>1334</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A63" t="s">
-        <v>1326</v>
+        <v>1325</v>
       </c>
       <c r="B63" t="s">
-        <v>1396</v>
+        <v>1395</v>
       </c>
       <c r="C63" t="s">
-        <v>1442</v>
+        <v>1441</v>
       </c>
       <c r="D63" t="s">
-        <v>1334</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A64" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
       <c r="B64" t="s">
-        <v>1397</v>
+        <v>1396</v>
       </c>
       <c r="C64" t="s">
-        <v>1458</v>
+        <v>1457</v>
       </c>
       <c r="D64" t="s">
-        <v>1334</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A65" t="s">
-        <v>1328</v>
+        <v>1327</v>
       </c>
       <c r="B65" t="s">
-        <v>1398</v>
+        <v>1397</v>
       </c>
       <c r="C65" t="s">
-        <v>1443</v>
+        <v>1442</v>
       </c>
       <c r="D65" t="s">
-        <v>1334</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A66" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="B66" t="s">
-        <v>1399</v>
+        <v>1398</v>
       </c>
       <c r="C66" t="s">
-        <v>1444</v>
+        <v>1443</v>
       </c>
       <c r="D66" t="s">
-        <v>1336</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A67" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="B67" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
       <c r="C67" t="s">
-        <v>1445</v>
+        <v>1444</v>
       </c>
       <c r="D67" t="s">
-        <v>1336</v>
+        <v>1335</v>
       </c>
     </row>
   </sheetData>

--- a/data/Fate-Spreadsheet.xlsx
+++ b/data/Fate-Spreadsheet.xlsx
@@ -8,17 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pixel\Documents\Projects\Fate-Wiki\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A8AEC5F-F014-4DE0-B160-E5C74668FC87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6975E217-4937-4962-9F68-2043D1A69F68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="3" xr2:uid="{B05E798F-9EF6-4508-A0A4-311D06661AED}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{B05E798F-9EF6-4508-A0A4-311D06661AED}"/>
   </bookViews>
   <sheets>
     <sheet name="Servants" sheetId="1" r:id="rId1"/>
-    <sheet name="Unique Deck Cards" sheetId="4" r:id="rId2"/>
-    <sheet name="Servant Skills" sheetId="3" r:id="rId3"/>
-    <sheet name="Servant Misc Cards" sheetId="7" r:id="rId4"/>
-    <sheet name="Masters" sheetId="5" r:id="rId5"/>
-    <sheet name="Master Cards" sheetId="6" r:id="rId6"/>
+    <sheet name="Servant Traits List" sheetId="8" r:id="rId2"/>
+    <sheet name="Unique Deck Cards" sheetId="4" r:id="rId3"/>
+    <sheet name="Servant Skills" sheetId="3" r:id="rId4"/>
+    <sheet name="Servant Misc Cards" sheetId="7" r:id="rId5"/>
+    <sheet name="Masters" sheetId="5" r:id="rId6"/>
+    <sheet name="Master Cards" sheetId="6" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -44,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3752" uniqueCount="1509">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4216" uniqueCount="1884">
   <si>
     <t>servant_id</t>
   </si>
@@ -4571,6 +4572,1131 @@
   </si>
   <si>
     <t>Albions-Remnant</t>
+  </si>
+  <si>
+    <t>Power Negation,High Power,VP Negation</t>
+  </si>
+  <si>
+    <t>NP Reliant</t>
+  </si>
+  <si>
+    <t>Win Streak VP Gain,Turn Order Manipulation</t>
+  </si>
+  <si>
+    <t>High Risk,Setup Reliant,NP Reliant</t>
+  </si>
+  <si>
+    <t>traits_pros</t>
+  </si>
+  <si>
+    <t>traits_cons</t>
+  </si>
+  <si>
+    <t>servant_pros</t>
+  </si>
+  <si>
+    <t>servant_cons</t>
+  </si>
+  <si>
+    <t>High Power,Combat Plays</t>
+  </si>
+  <si>
+    <t>Mana Hungry,NP Reliant</t>
+  </si>
+  <si>
+    <t>Power Negation</t>
+  </si>
+  <si>
+    <t>High Power</t>
+  </si>
+  <si>
+    <t>VP Negation</t>
+  </si>
+  <si>
+    <t>Win Streak VP Gain</t>
+  </si>
+  <si>
+    <t>Turn Order Manipulation</t>
+  </si>
+  <si>
+    <t>Combat Plays</t>
+  </si>
+  <si>
+    <t>High Risk</t>
+  </si>
+  <si>
+    <t>Setup Reliant</t>
+  </si>
+  <si>
+    <t>Mana Hungry</t>
+  </si>
+  <si>
+    <t>High Power,Objective Manipulation</t>
+  </si>
+  <si>
+    <t>Objective Manipulation</t>
+  </si>
+  <si>
+    <t>High Power,VP Gain</t>
+  </si>
+  <si>
+    <t>High Power,Cheap Power,Ability Negation</t>
+  </si>
+  <si>
+    <t>Cheap Power</t>
+  </si>
+  <si>
+    <t>Ability Negation</t>
+  </si>
+  <si>
+    <t>Deck Destruction</t>
+  </si>
+  <si>
+    <t>Fading Power</t>
+  </si>
+  <si>
+    <t>Deck Destruction,Fading Power</t>
+  </si>
+  <si>
+    <t>Good Scaling,Cheap Power</t>
+  </si>
+  <si>
+    <t>Chance Reliant</t>
+  </si>
+  <si>
+    <t>Good Scaling</t>
+  </si>
+  <si>
+    <t>Good Scaling,Cheap Power,High Power</t>
+  </si>
+  <si>
+    <t>VP Loss</t>
+  </si>
+  <si>
+    <t>NP Reliant,VP Loss,Card Reliant</t>
+  </si>
+  <si>
+    <t>Card Reliant</t>
+  </si>
+  <si>
+    <t>Prediction Reliant</t>
+  </si>
+  <si>
+    <t>Cheap Power,Card Negation</t>
+  </si>
+  <si>
+    <t>Card Reliant,Prediction Reliant</t>
+  </si>
+  <si>
+    <t>Card Negation</t>
+  </si>
+  <si>
+    <t>Combat Plays,Cheap Power</t>
+  </si>
+  <si>
+    <t>Card Reliant,Setup Reliant,Limited Use</t>
+  </si>
+  <si>
+    <t>Limited Use</t>
+  </si>
+  <si>
+    <t>Growing Power</t>
+  </si>
+  <si>
+    <t>Low Power</t>
+  </si>
+  <si>
+    <t>Needs Combat Wins</t>
+  </si>
+  <si>
+    <t>Growing Power,Cheap Power</t>
+  </si>
+  <si>
+    <t>Low Power,Needs Combat Wins</t>
+  </si>
+  <si>
+    <t>Control,High Power</t>
+  </si>
+  <si>
+    <t>Setup Reliant,Mana Hungry</t>
+  </si>
+  <si>
+    <t>Control</t>
+  </si>
+  <si>
+    <t>Objective Recycling</t>
+  </si>
+  <si>
+    <t>Good Scaling,High Power,Objective Recycling</t>
+  </si>
+  <si>
+    <t>Mana Hungry,Card Reliant</t>
+  </si>
+  <si>
+    <t>High Power,Foreigner Transform,Special Hate</t>
+  </si>
+  <si>
+    <t>Foreigner Transform</t>
+  </si>
+  <si>
+    <t>Special Hate</t>
+  </si>
+  <si>
+    <t>High Risk,Mana Hungry,Setup Reliant</t>
+  </si>
+  <si>
+    <t>Adaptable</t>
+  </si>
+  <si>
+    <t>Power Negation,High Power,Adaptable</t>
+  </si>
+  <si>
+    <t>Cheap Power,Good Scaling,Free Card Plays</t>
+  </si>
+  <si>
+    <t>Free Card Plays</t>
+  </si>
+  <si>
+    <t>Setup Reliant,Card Reliant,Chance Reliant</t>
+  </si>
+  <si>
+    <t>High Power,Cheap Power,Power Negation</t>
+  </si>
+  <si>
+    <t>Immobile</t>
+  </si>
+  <si>
+    <t>Chance Reliant,Immobile,Card Reliant</t>
+  </si>
+  <si>
+    <t>Power Negation,Good Scaling</t>
+  </si>
+  <si>
+    <t>Low Power,NP Reliant,Buff Reliant</t>
+  </si>
+  <si>
+    <t>Buff Reliant</t>
+  </si>
+  <si>
+    <t>Buff Reliant,Mana Hungry,Card Reliant</t>
+  </si>
+  <si>
+    <t>Gank Protection,VP Negation,Good Scaling</t>
+  </si>
+  <si>
+    <t>Gank Protection</t>
+  </si>
+  <si>
+    <t>Reactive</t>
+  </si>
+  <si>
+    <t>Positioning Reliant</t>
+  </si>
+  <si>
+    <t>No Luck</t>
+  </si>
+  <si>
+    <t>Reactive,Positioning Reliant,No Luck</t>
+  </si>
+  <si>
+    <t>Luck Reliant,Setup Reliant</t>
+  </si>
+  <si>
+    <t>Luck Reliant</t>
+  </si>
+  <si>
+    <t>Card Reliant,Setup Reliant</t>
+  </si>
+  <si>
+    <t>Target Defeat,VP Theft</t>
+  </si>
+  <si>
+    <t>Target Defeat</t>
+  </si>
+  <si>
+    <t>VP Theft</t>
+  </si>
+  <si>
+    <t>NP Reliant,Low Power,No Luck</t>
+  </si>
+  <si>
+    <t>Power Negation,Skill Removal,Combat Plays</t>
+  </si>
+  <si>
+    <t>Low Power,No Luck</t>
+  </si>
+  <si>
+    <t>Skill Removal</t>
+  </si>
+  <si>
+    <t>Player Removal</t>
+  </si>
+  <si>
+    <t>Power Negation,High Power,Player Removal</t>
+  </si>
+  <si>
+    <t>Mana Hungry,VP Loss</t>
+  </si>
+  <si>
+    <t>Cheap Power,Gank Protection,Good Scaling</t>
+  </si>
+  <si>
+    <t>Growing Power,VP Gain</t>
+  </si>
+  <si>
+    <t>Immobile,NP Reliant,Mana Hungry</t>
+  </si>
+  <si>
+    <t>Adaptable,Group Defeat,High Power</t>
+  </si>
+  <si>
+    <t>Group Defeat</t>
+  </si>
+  <si>
+    <t>High Mobility</t>
+  </si>
+  <si>
+    <t>Difficult Mechanics</t>
+  </si>
+  <si>
+    <t>High Mobility,Cheap Power,High Power</t>
+  </si>
+  <si>
+    <t>High Risk,Card Reliant,Difficult Mechanics</t>
+  </si>
+  <si>
+    <t>Objective Inversion</t>
+  </si>
+  <si>
+    <t>Buff Reliant,Setup Reliant</t>
+  </si>
+  <si>
+    <t>Good Scaling,Adaptable,Control</t>
+  </si>
+  <si>
+    <t>Setup Reliant,Card Reliant,Difficult Mechanics</t>
+  </si>
+  <si>
+    <t>Power Negation,Skill Theft,Control</t>
+  </si>
+  <si>
+    <t>Skill Theft</t>
+  </si>
+  <si>
+    <t>Setup Reliant,Chance Reliant</t>
+  </si>
+  <si>
+    <t>Adaptable,VP Gain,Cheap Power</t>
+  </si>
+  <si>
+    <t>Positioning Reliant,Setup Reliant,NP Reliant</t>
+  </si>
+  <si>
+    <t>Adaptable,High Mobility,Cheap Power</t>
+  </si>
+  <si>
+    <t>Control,Combat Plays,Gank Protection</t>
+  </si>
+  <si>
+    <t>Immobile,Low Power</t>
+  </si>
+  <si>
+    <t>Gank Protection,VP Gain,High Power</t>
+  </si>
+  <si>
+    <t>Good Scaling,Cheap Power,High Mobility</t>
+  </si>
+  <si>
+    <t>Buff Reliant,Positioning Reliant,Setup Reliant</t>
+  </si>
+  <si>
+    <t>Control,Skill Theft,Growing Power</t>
+  </si>
+  <si>
+    <t>Low Power,Setup Reliant</t>
+  </si>
+  <si>
+    <t>VP Gain,Growing Power</t>
+  </si>
+  <si>
+    <t>Low Power,NP Reliant</t>
+  </si>
+  <si>
+    <t>Alternate Win Con</t>
+  </si>
+  <si>
+    <t>High Power,Alternate Win Con,Cheap Power</t>
+  </si>
+  <si>
+    <t>NP Reliant,Mana Hungry,VP Loss</t>
+  </si>
+  <si>
+    <t>Ability Negation,Buff Negation,Combat Plays</t>
+  </si>
+  <si>
+    <t>Buff Negation</t>
+  </si>
+  <si>
+    <t>NP Reliant,Low Power</t>
+  </si>
+  <si>
+    <t>Low Power,Card Reliant,Setup Reliant</t>
+  </si>
+  <si>
+    <t>Cheap Power,VP Gain,Good Scaling</t>
+  </si>
+  <si>
+    <t>Control Loss,Gives VP</t>
+  </si>
+  <si>
+    <t>Control Loss</t>
+  </si>
+  <si>
+    <t>Gives VP</t>
+  </si>
+  <si>
+    <t>Transform,Cheap Power,Good Scaling</t>
+  </si>
+  <si>
+    <t>VP Loss,NP Reliant</t>
+  </si>
+  <si>
+    <t>Transform</t>
+  </si>
+  <si>
+    <t>Good Scaling,Target Defeat,Card Draw</t>
+  </si>
+  <si>
+    <t>Card Draw</t>
+  </si>
+  <si>
+    <t>Good Scaling,Agility Negation,VP Gain</t>
+  </si>
+  <si>
+    <t>Setup Reliant,Positioning Reliant,No Luck</t>
+  </si>
+  <si>
+    <t>Agility Negation</t>
+  </si>
+  <si>
+    <t>Growing Power,Power Reduction,Group Defeat</t>
+  </si>
+  <si>
+    <t>Power Reduction</t>
+  </si>
+  <si>
+    <t>Low Power,High Risk,No Luck</t>
+  </si>
+  <si>
+    <t>VP Gain,Good Scaling,Adaptable</t>
+  </si>
+  <si>
+    <t>NP Reliant,Positioning Reliant,No Luck</t>
+  </si>
+  <si>
+    <t>Combat Plays,VP Gain</t>
+  </si>
+  <si>
+    <t>VP Gain,Group Defeat</t>
+  </si>
+  <si>
+    <t>Low Power,Setup Reliant,No Luck</t>
+  </si>
+  <si>
+    <t>Cheap Power,High Power,Control</t>
+  </si>
+  <si>
+    <t>Combat Plays,VP Gain,High Mobility</t>
+  </si>
+  <si>
+    <t>High Power,Gank Protection,Enemy Displacement</t>
+  </si>
+  <si>
+    <t>Enemy Displacement</t>
+  </si>
+  <si>
+    <t>Positioning Reliant,Setup Reliant</t>
+  </si>
+  <si>
+    <t>High Power,Cheap Power,VP Gain</t>
+  </si>
+  <si>
+    <t>High Risk,Dies</t>
+  </si>
+  <si>
+    <t>Dies</t>
+  </si>
+  <si>
+    <t>High Power,Mana Gain</t>
+  </si>
+  <si>
+    <t>Donates Mana</t>
+  </si>
+  <si>
+    <t>Donates Mana,Setup Reliant,Difficult Mechanics</t>
+  </si>
+  <si>
+    <t>Good Scaling,Combat Plays</t>
+  </si>
+  <si>
+    <t>VP Gain,Combat Negation</t>
+  </si>
+  <si>
+    <t>Combat Negation</t>
+  </si>
+  <si>
+    <t>Card Reliant,Limited Use</t>
+  </si>
+  <si>
+    <t>Cheap Power,Good Scaling</t>
+  </si>
+  <si>
+    <t>VP Gain,Power Negation</t>
+  </si>
+  <si>
+    <t>Event Manipulation,Cheap Power,Good Scaling</t>
+  </si>
+  <si>
+    <t>Setup Reliant,Positioning Reliant,Card Reliant</t>
+  </si>
+  <si>
+    <t>Event Manipulation</t>
+  </si>
+  <si>
+    <t>Cheap Power,VP Gain,Target Defeat</t>
+  </si>
+  <si>
+    <t>Setup Reliant,Card Reliant,No Luck</t>
+  </si>
+  <si>
+    <t>Target Defeat,VP Gain</t>
+  </si>
+  <si>
+    <t>Setup Reliant,Low Power,No Luck</t>
+  </si>
+  <si>
+    <t>VP Gain,Control</t>
+  </si>
+  <si>
+    <t>Positioning Reliant,Mana Hungry</t>
+  </si>
+  <si>
+    <t>High Power,Cheap Power</t>
+  </si>
+  <si>
+    <t>Card Reliant,Chance Reliant,Mana Hungry</t>
+  </si>
+  <si>
+    <t>Cheap Power,Skill Theft,VP Theft</t>
+  </si>
+  <si>
+    <t>NP Reliant,Limited Use,No Luck</t>
+  </si>
+  <si>
+    <t>VP Gain,Cheap Power,Good Scaling</t>
+  </si>
+  <si>
+    <t>NP Reliant,Setup Reliant,Card Reliant</t>
+  </si>
+  <si>
+    <t>VP Gain,Cheap Power</t>
+  </si>
+  <si>
+    <t>High Risk,Card Reliant</t>
+  </si>
+  <si>
+    <t>High Power,Group Defeat</t>
+  </si>
+  <si>
+    <t>Mana Hungry,No Luck</t>
+  </si>
+  <si>
+    <t>High Power,Good Scaling,Objective Manipulation</t>
+  </si>
+  <si>
+    <t>Mana Hungry,Buff Reliant,NP Reliant</t>
+  </si>
+  <si>
+    <t>Power Negation,Control,Gank Protection</t>
+  </si>
+  <si>
+    <t>High Risk,Low Power,NP Reliant</t>
+  </si>
+  <si>
+    <t>VP Denial</t>
+  </si>
+  <si>
+    <t>VP Denial,VP Gain,Enemy Displacement</t>
+  </si>
+  <si>
+    <t>Immobile,Card Reliant</t>
+  </si>
+  <si>
+    <t>High Mobility,High Power,VP Gain</t>
+  </si>
+  <si>
+    <t>Good Scaling,Enemy Displacement,High Mobility</t>
+  </si>
+  <si>
+    <t>Buff Reliant,Card Reliant,No Luck</t>
+  </si>
+  <si>
+    <t>Control,Gank Protection</t>
+  </si>
+  <si>
+    <t>Setup Reliant,NP Reliant</t>
+  </si>
+  <si>
+    <t>Cheap Power,VP Gain,Control</t>
+  </si>
+  <si>
+    <t>Card Reliant,Buff Reliant,Setup Reliant</t>
+  </si>
+  <si>
+    <t>Enemy Displacement,VP Theft,High Mobility</t>
+  </si>
+  <si>
+    <t>Setup Reliant,Mana Hungry,Low Power</t>
+  </si>
+  <si>
+    <t>Weak Duelist,NP Reliant</t>
+  </si>
+  <si>
+    <t>Weak Duelist</t>
+  </si>
+  <si>
+    <t>High Mobility,Cheap Power,VP Gain</t>
+  </si>
+  <si>
+    <t>Weak Duelist,Buff Reliant,NP Reliant</t>
+  </si>
+  <si>
+    <t>Cheap Power,High Mobility</t>
+  </si>
+  <si>
+    <t>NP Reliant,High Risk</t>
+  </si>
+  <si>
+    <t>High Power,Good Scaling,High Mobility</t>
+  </si>
+  <si>
+    <t>Setup Reliant,Difficult Mechanics</t>
+  </si>
+  <si>
+    <t>VP Gain,Card Negation,Good Scaling</t>
+  </si>
+  <si>
+    <t>Limited Early Game,NP Reliant,Mana Hungry</t>
+  </si>
+  <si>
+    <t>Limited Early Game</t>
+  </si>
+  <si>
+    <t>No Utility,Buff Reliant</t>
+  </si>
+  <si>
+    <t>No Utility</t>
+  </si>
+  <si>
+    <t>Growing Power,VP Gain,Deck Destruction</t>
+  </si>
+  <si>
+    <t>NP Reliant,Needs Combat Wins</t>
+  </si>
+  <si>
+    <t>Cheap Power,VP Gain,Combat Plays</t>
+  </si>
+  <si>
+    <t>Limited Use,Weak Climax</t>
+  </si>
+  <si>
+    <t>Weak Climax</t>
+  </si>
+  <si>
+    <t>High Power,Enemy Displacement,VP Gain</t>
+  </si>
+  <si>
+    <t>High Power,High Mobility,Cheap Power</t>
+  </si>
+  <si>
+    <t>Mana Hungry,Card Reliant,Setup Reliant</t>
+  </si>
+  <si>
+    <t>High Mobility,Adaptable,Cheap Power</t>
+  </si>
+  <si>
+    <t>Setup Reliant,Low Power,Card Reliant</t>
+  </si>
+  <si>
+    <t>Group Defeat,Cheap Power,VP Theft</t>
+  </si>
+  <si>
+    <t>Poor Matchups</t>
+  </si>
+  <si>
+    <t>Setup Reliant,Weak Climax,Poor Matchups</t>
+  </si>
+  <si>
+    <t>Cheap Power,VP Gain</t>
+  </si>
+  <si>
+    <t>VP Gain,Target Defeat</t>
+  </si>
+  <si>
+    <t>VP Gain,Good Scaling,High Power</t>
+  </si>
+  <si>
+    <t>High Risk,Setup Reliant,No Luck</t>
+  </si>
+  <si>
+    <t>Growing Power,Good Scaling,Magic Penetration</t>
+  </si>
+  <si>
+    <t>Magic Penetration</t>
+  </si>
+  <si>
+    <t>NP Reliant,Mana Hungry,Card Reliant</t>
+  </si>
+  <si>
+    <t>VP Gain,Kingmaking</t>
+  </si>
+  <si>
+    <t>Low Power,Prediction Reliant,Setup Reliant</t>
+  </si>
+  <si>
+    <t>Kingmaking</t>
+  </si>
+  <si>
+    <t>VP Gain,Growing Power,High Power</t>
+  </si>
+  <si>
+    <t>Setup Reliant,High Risk,Mana Hungry,No Luck</t>
+  </si>
+  <si>
+    <t>VP Gain,Unlocks Master Ascension</t>
+  </si>
+  <si>
+    <t>Unlocks Master Ascension</t>
+  </si>
+  <si>
+    <t>NP Theft</t>
+  </si>
+  <si>
+    <t>NP Theft,Adaptable,VP Gain,Growing Power</t>
+  </si>
+  <si>
+    <t>Matchup Reliant,Low Power,Setup Reliant</t>
+  </si>
+  <si>
+    <t>Matchup Reliant</t>
+  </si>
+  <si>
+    <t>VP Gain,VP Loss,Gank Protection</t>
+  </si>
+  <si>
+    <t>Low Power,High Risk,Setup Reliant</t>
+  </si>
+  <si>
+    <t>VP Theft,VP Gain</t>
+  </si>
+  <si>
+    <t>Setup Reliant,No Luck</t>
+  </si>
+  <si>
+    <t>Power Negation,VP Denial,High Mobility</t>
+  </si>
+  <si>
+    <t>Low Power,Recon Reliant</t>
+  </si>
+  <si>
+    <t>Recon Reliant</t>
+  </si>
+  <si>
+    <t>VP Gain,Mana Gain,Power Negation</t>
+  </si>
+  <si>
+    <t>Donates Mana,Setup Reliant,No Luck</t>
+  </si>
+  <si>
+    <t>VP Gain,Type Negation,Special Negation</t>
+  </si>
+  <si>
+    <t>Type Negation</t>
+  </si>
+  <si>
+    <t>Special Negation</t>
+  </si>
+  <si>
+    <t>VP Gain,High Power,Group Defeat</t>
+  </si>
+  <si>
+    <t>Setup Reliant,Donates Mana</t>
+  </si>
+  <si>
+    <t>VP Gain,High Power</t>
+  </si>
+  <si>
+    <t>Growing Power,Adaptable,VP Gain</t>
+  </si>
+  <si>
+    <t>Needs Combat Wins,Card Reliant,Setup Reliant</t>
+  </si>
+  <si>
+    <t>VP Gain,Reliable Defeat</t>
+  </si>
+  <si>
+    <t>Reliable Defeat</t>
+  </si>
+  <si>
+    <t>Buffs Opponents</t>
+  </si>
+  <si>
+    <t>Cheap Power,Adaptable,Target Defeat</t>
+  </si>
+  <si>
+    <t>Card Reliant,Buffs Opponents</t>
+  </si>
+  <si>
+    <t>Free Command Spells,Cheap Power</t>
+  </si>
+  <si>
+    <t>Free Command Spells</t>
+  </si>
+  <si>
+    <t>Group Defeat,VP Gain,Cheap Power</t>
+  </si>
+  <si>
+    <t>Positioning Reliant,Immobile,Mana Hungry</t>
+  </si>
+  <si>
+    <t>High Risk,Weak Duelist,NP Reliant</t>
+  </si>
+  <si>
+    <t>Control,Cheap Power,VP Gain</t>
+  </si>
+  <si>
+    <t>High Risk,Setup Reliant,Limited Use</t>
+  </si>
+  <si>
+    <t>VP Gain,Skill Negation</t>
+  </si>
+  <si>
+    <t>Low Power,Card Reliant</t>
+  </si>
+  <si>
+    <t>Skill Negation</t>
+  </si>
+  <si>
+    <t>Good Scaling,Ability Negation</t>
+  </si>
+  <si>
+    <t>VP Gain,Assassination,Target Defeat</t>
+  </si>
+  <si>
+    <t>Low Power,Limited Use,No Luck</t>
+  </si>
+  <si>
+    <t>Assassination</t>
+  </si>
+  <si>
+    <t>VP Gain,Assassination,High Mobility</t>
+  </si>
+  <si>
+    <t>Low Power,Buff Reliant,No Luck</t>
+  </si>
+  <si>
+    <t>Assassination,Basic Negation,High Mobility</t>
+  </si>
+  <si>
+    <t>Low Power,Weak Duelist</t>
+  </si>
+  <si>
+    <t>Basic Negation</t>
+  </si>
+  <si>
+    <t>Servant Removal,Group Defeat,High Power</t>
+  </si>
+  <si>
+    <t>Servant Removal</t>
+  </si>
+  <si>
+    <t>VP Gain,Assassination,Group Defeat</t>
+  </si>
+  <si>
+    <t>Low Power,Positioning Reliant</t>
+  </si>
+  <si>
+    <t>Combat Negation,Control,Assassination</t>
+  </si>
+  <si>
+    <t>Low Power,NP Reliant,No Luck</t>
+  </si>
+  <si>
+    <t>Target Defeat,Obscure Objectives,High Mobility</t>
+  </si>
+  <si>
+    <t>Obscure Objectives</t>
+  </si>
+  <si>
+    <t>Target Defeat,Combat Plays,High Mobility</t>
+  </si>
+  <si>
+    <t>Target Defeat,Deck Destruction,Control,VP Gain</t>
+  </si>
+  <si>
+    <t>Low Power,Setup Reliant,Immobile</t>
+  </si>
+  <si>
+    <t>Assassination,VP Gain</t>
+  </si>
+  <si>
+    <t>Alternating Abilities</t>
+  </si>
+  <si>
+    <t>Target Defeat,Assassination,VP Gain</t>
+  </si>
+  <si>
+    <t>Prediction Reliant,Positioning Reliant,Card Reliant</t>
+  </si>
+  <si>
+    <t>Target Defeat,Cheap Power,VP Gain</t>
+  </si>
+  <si>
+    <t>Requires Negotiation</t>
+  </si>
+  <si>
+    <t>Card Reliant,Setup Reliant,Chance Reliant</t>
+  </si>
+  <si>
+    <t>VP Gain,Assassination,Good Scaling</t>
+  </si>
+  <si>
+    <t>Assassination,Card Negation,VP Gain</t>
+  </si>
+  <si>
+    <t>Low Power,Card Reliant,Requires Negotiation</t>
+  </si>
+  <si>
+    <t>VP Theft,Assassination,Combat Plays</t>
+  </si>
+  <si>
+    <t>Good Scaling,Target Defeat,Assassination</t>
+  </si>
+  <si>
+    <t>Mana Hungry,Setup Reliant,High Risk</t>
+  </si>
+  <si>
+    <t>Assassination,VP Loss,Cheap Power</t>
+  </si>
+  <si>
+    <t>Setup Reliant,Reactive,No Luck</t>
+  </si>
+  <si>
+    <t>High Power,Cheap Power,Target Defeat</t>
+  </si>
+  <si>
+    <t>Mana Hungry,Limited Use,NP Reliant</t>
+  </si>
+  <si>
+    <t>VP Theft,Target Defeat,High Mobility</t>
+  </si>
+  <si>
+    <t>Positioning Reliant,Low Power,No Luck</t>
+  </si>
+  <si>
+    <t>VP Theft,Mana Theft,Control</t>
+  </si>
+  <si>
+    <t>Mana Theft</t>
+  </si>
+  <si>
+    <t>Low Power,Mana Hungry,Requires Negotiation</t>
+  </si>
+  <si>
+    <t>Cheap Power,Group Defeat,VP Theft</t>
+  </si>
+  <si>
+    <t>Limited Use,Card Reliant</t>
+  </si>
+  <si>
+    <t>Attack Theft,Skill Theft,Gank Protection</t>
+  </si>
+  <si>
+    <t>Attack Theft</t>
+  </si>
+  <si>
+    <t>VP Denial,Target Defeat,Gank Protection</t>
+  </si>
+  <si>
+    <t>VP Gain,Command Seal Hate</t>
+  </si>
+  <si>
+    <t>Command Seal Hate</t>
+  </si>
+  <si>
+    <t>VP Gain,Cheap Power,Gank Protection</t>
+  </si>
+  <si>
+    <t>Poor Matchups,Prediction Reliant</t>
+  </si>
+  <si>
+    <t>Cheap Power,High Power</t>
+  </si>
+  <si>
+    <t>Power Negation,VP Gain</t>
+  </si>
+  <si>
+    <t>Growing Power,High Power</t>
+  </si>
+  <si>
+    <t>Mana Hungry,Setup Reliant</t>
+  </si>
+  <si>
+    <t>Cheap Power,High Power,VP Gain</t>
+  </si>
+  <si>
+    <t>VP Loss,Limited Use</t>
+  </si>
+  <si>
+    <t>High Mobility,High Power</t>
+  </si>
+  <si>
+    <t>Cheap Power,High Power,Objective Manipulation</t>
+  </si>
+  <si>
+    <t>High Risk,Mana Hungry,NP Reliant</t>
+  </si>
+  <si>
+    <t>VP Gain,Cheap Power,Adapatable</t>
+  </si>
+  <si>
+    <t>VP Theft,Good Scaling</t>
+  </si>
+  <si>
+    <t>VP Gain,Cheap Power,VP Loss</t>
+  </si>
+  <si>
+    <t>Buffs Opponents,VP Loss</t>
+  </si>
+  <si>
+    <t>Mana Hungry,Card Reliant,Immobile</t>
+  </si>
+  <si>
+    <t>Enemy Displacement,VP Loss,High Power</t>
+  </si>
+  <si>
+    <t>Mana Hungry,Buffs Opponents,Card Reliant</t>
+  </si>
+  <si>
+    <t>Cheap Power,Control,Combat Plays</t>
+  </si>
+  <si>
+    <t>Setup Reliant,Card Reliant,Matchup Reliant</t>
+  </si>
+  <si>
+    <t>Gank Protection,Mana Loss,High Power</t>
+  </si>
+  <si>
+    <t>Mana Loss</t>
+  </si>
+  <si>
+    <t>Card Reliant,Setup Reliant,No Luck</t>
+  </si>
+  <si>
+    <t>Chance Reliant,Setup Reliant</t>
+  </si>
+  <si>
+    <t>Reactive,Setup Reliant,No Luck</t>
+  </si>
+  <si>
+    <t>Good Scaling,VP Loss,Group Defeat</t>
+  </si>
+  <si>
+    <t>Setup Reliant,High Risk,No Luck</t>
+  </si>
+  <si>
+    <t>Target Defeat,High Mobility,VP Loss</t>
+  </si>
+  <si>
+    <t>Reactive,Card Reliant,No Luck</t>
+  </si>
+  <si>
+    <t>Group Defeat,Control,Gank Protection</t>
+  </si>
+  <si>
+    <t>Enemy Displacement,VP Gain,Group Defeat</t>
+  </si>
+  <si>
+    <t>Enemy Displacement,VP Gain,VP Denial</t>
+  </si>
+  <si>
+    <t>Chance Reliant,Matchup Reliant</t>
+  </si>
+  <si>
+    <t>Prediction Reliant,High Risk</t>
+  </si>
+  <si>
+    <t>Enemy Displacement,High Power</t>
+  </si>
+  <si>
+    <t>Limited Use,NP Reliant,Mana Hungry</t>
+  </si>
+  <si>
+    <t>Alternate Win Con,Cheap Power,Adaptable</t>
+  </si>
+  <si>
+    <t>Poor Matchups,NP Reliant,Card Reliant</t>
+  </si>
+  <si>
+    <t>Low Power,NP Reliant,Mana Hungry</t>
+  </si>
+  <si>
+    <t>Power Reduction,Control</t>
+  </si>
+  <si>
+    <t>Low Power,Setup Reliant,NP Reliant</t>
+  </si>
+  <si>
+    <t>VP Gain,World Manipulation</t>
+  </si>
+  <si>
+    <t>World Manipulation</t>
+  </si>
+  <si>
+    <t>Chance Reliant,Card Reliant,Mana Hungry</t>
+  </si>
+  <si>
+    <t>Objective Manipulation,VP Denial,Mana Gain</t>
+  </si>
+  <si>
+    <t>Low Power,Mana Hungry</t>
+  </si>
+  <si>
+    <t>Setup Reliant,Chance Reliant,Mana Hungry</t>
+  </si>
+  <si>
+    <t>Card Negation,Type Manipulation</t>
+  </si>
+  <si>
+    <t>Type Manipulation</t>
+  </si>
+  <si>
+    <t>Cheap Power,Power Reduction,VP Gain</t>
+  </si>
+  <si>
+    <t>Setup Reliant,NP Reliant,Low Power</t>
+  </si>
+  <si>
+    <t>Setup Reliant,VP Loss,No Luck</t>
+  </si>
+  <si>
+    <t>High Power,Cheap Power,Combat Plays,Alternate Win Con</t>
+  </si>
+  <si>
+    <t>Limited Use,Mana Hungry</t>
+  </si>
+  <si>
+    <t>Kingmaking,VP Gain,Power Reduction</t>
   </si>
 </sst>
 </file>
@@ -4972,8 +6098,8 @@
     <col min="10" max="10" width="97" style="2" customWidth="1"/>
     <col min="11" max="11" width="12.59765625" customWidth="1"/>
     <col min="12" max="12" width="10.9296875" customWidth="1"/>
-    <col min="13" max="13" width="12" customWidth="1"/>
-    <col min="14" max="14" width="11.53125" customWidth="1"/>
+    <col min="13" max="13" width="45.6640625" customWidth="1"/>
+    <col min="14" max="14" width="41.33203125" customWidth="1"/>
     <col min="15" max="15" width="11.796875" customWidth="1"/>
     <col min="16" max="16" width="18.19921875" customWidth="1"/>
   </cols>
@@ -5015,8 +6141,12 @@
       <c r="L1" s="3" t="s">
         <v>1466</v>
       </c>
-      <c r="M1" s="3"/>
-      <c r="N1" s="3"/>
+      <c r="M1" s="3" t="s">
+        <v>1515</v>
+      </c>
+      <c r="N1" s="3" t="s">
+        <v>1516</v>
+      </c>
       <c r="O1" s="3"/>
       <c r="P1" s="3"/>
     </row>
@@ -5048,6 +6178,12 @@
       <c r="J2" s="2" t="s">
         <v>16</v>
       </c>
+      <c r="M2" s="2" t="s">
+        <v>1509</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>1510</v>
+      </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
@@ -5077,6 +6213,12 @@
       <c r="J3" s="2" t="s">
         <v>177</v>
       </c>
+      <c r="M3" s="2" t="s">
+        <v>1511</v>
+      </c>
+      <c r="N3" s="2" t="s">
+        <v>1512</v>
+      </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
@@ -5103,6 +6245,12 @@
       <c r="J4" s="2" t="s">
         <v>179</v>
       </c>
+      <c r="M4" t="s">
+        <v>1517</v>
+      </c>
+      <c r="N4" t="s">
+        <v>1518</v>
+      </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
@@ -5132,6 +6280,12 @@
       <c r="L5" t="b">
         <v>1</v>
       </c>
+      <c r="M5" t="s">
+        <v>1528</v>
+      </c>
+      <c r="N5" t="s">
+        <v>1527</v>
+      </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
@@ -5161,6 +6315,12 @@
       <c r="J6" s="2" t="s">
         <v>183</v>
       </c>
+      <c r="M6" s="2" t="s">
+        <v>1530</v>
+      </c>
+      <c r="N6" s="2" t="s">
+        <v>1525</v>
+      </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
@@ -5190,6 +6350,12 @@
       <c r="J7" s="2" t="s">
         <v>186</v>
       </c>
+      <c r="M7" s="2" t="s">
+        <v>1531</v>
+      </c>
+      <c r="N7" s="2" t="s">
+        <v>1536</v>
+      </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
@@ -5219,6 +6385,12 @@
       <c r="K8" t="b">
         <v>1</v>
       </c>
+      <c r="M8" s="2" t="s">
+        <v>1537</v>
+      </c>
+      <c r="N8" s="2" t="s">
+        <v>1538</v>
+      </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
@@ -5245,6 +6417,12 @@
       <c r="J9" s="2" t="s">
         <v>186</v>
       </c>
+      <c r="M9" s="2" t="s">
+        <v>1540</v>
+      </c>
+      <c r="N9" s="2" t="s">
+        <v>1541</v>
+      </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
@@ -5274,6 +6452,12 @@
       <c r="J10" s="2" t="s">
         <v>188</v>
       </c>
+      <c r="M10" s="2" t="s">
+        <v>1531</v>
+      </c>
+      <c r="N10" s="2" t="s">
+        <v>1542</v>
+      </c>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
@@ -5303,6 +6487,12 @@
       <c r="J11" s="2" t="s">
         <v>188</v>
       </c>
+      <c r="M11" s="2" t="s">
+        <v>1545</v>
+      </c>
+      <c r="N11" s="2" t="s">
+        <v>1546</v>
+      </c>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
@@ -5332,6 +6522,12 @@
       <c r="J12" s="2" t="s">
         <v>194</v>
       </c>
+      <c r="M12" s="2" t="s">
+        <v>1548</v>
+      </c>
+      <c r="N12" s="2" t="s">
+        <v>1549</v>
+      </c>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
@@ -5358,6 +6554,12 @@
       <c r="J13" s="2" t="s">
         <v>188</v>
       </c>
+      <c r="M13" s="2" t="s">
+        <v>1554</v>
+      </c>
+      <c r="N13" s="2" t="s">
+        <v>1555</v>
+      </c>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
@@ -5387,6 +6589,12 @@
       <c r="J14" s="2" t="s">
         <v>188</v>
       </c>
+      <c r="M14" s="2" t="s">
+        <v>1556</v>
+      </c>
+      <c r="N14" s="2" t="s">
+        <v>1557</v>
+      </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
@@ -5416,6 +6624,12 @@
       <c r="J15" s="2" t="s">
         <v>197</v>
       </c>
+      <c r="M15" s="2" t="s">
+        <v>1560</v>
+      </c>
+      <c r="N15" s="2" t="s">
+        <v>1561</v>
+      </c>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
@@ -5445,8 +6659,14 @@
       <c r="J16" s="2" t="s">
         <v>200</v>
       </c>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="M16" s="2" t="s">
+        <v>1562</v>
+      </c>
+      <c r="N16" s="2" t="s">
+        <v>1565</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>125</v>
       </c>
@@ -5474,8 +6694,14 @@
       <c r="J17" s="2" t="s">
         <v>186</v>
       </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="M17" s="2" t="s">
+        <v>1567</v>
+      </c>
+      <c r="N17" s="2" t="s">
+        <v>1510</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>126</v>
       </c>
@@ -5506,8 +6732,14 @@
       <c r="K18" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="M18" s="2" t="s">
+        <v>1568</v>
+      </c>
+      <c r="N18" s="2" t="s">
+        <v>1570</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
         <v>127</v>
       </c>
@@ -5535,8 +6767,14 @@
       <c r="J19" s="2" t="s">
         <v>186</v>
       </c>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="M19" s="2" t="s">
+        <v>1571</v>
+      </c>
+      <c r="N19" s="2" t="s">
+        <v>1573</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>128</v>
       </c>
@@ -5561,8 +6799,14 @@
       <c r="J20" s="2" t="s">
         <v>186</v>
       </c>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="M20" s="2" t="s">
+        <v>1574</v>
+      </c>
+      <c r="N20" s="2" t="s">
+        <v>1575</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
         <v>129</v>
       </c>
@@ -5590,8 +6834,14 @@
       <c r="J21" s="2" t="s">
         <v>205</v>
       </c>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="M21" s="2" t="s">
+        <v>1537</v>
+      </c>
+      <c r="N21" s="2" t="s">
+        <v>1577</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
         <v>130</v>
       </c>
@@ -5622,8 +6872,14 @@
       <c r="K22" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="M22" s="2" t="s">
+        <v>1578</v>
+      </c>
+      <c r="N22" s="2" t="s">
+        <v>1583</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
         <v>131</v>
       </c>
@@ -5651,8 +6907,14 @@
       <c r="J23" s="2" t="s">
         <v>188</v>
       </c>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="M23" s="2" t="s">
+        <v>1537</v>
+      </c>
+      <c r="N23" s="2" t="s">
+        <v>1584</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
         <v>132</v>
       </c>
@@ -5680,8 +6942,14 @@
       <c r="J24" s="2" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="M24" s="2" t="s">
+        <v>1537</v>
+      </c>
+      <c r="N24" s="2" t="s">
+        <v>1586</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
         <v>264</v>
       </c>
@@ -5709,8 +6977,14 @@
       <c r="J25" s="2" t="s">
         <v>270</v>
       </c>
-    </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="M25" s="2" t="s">
+        <v>1587</v>
+      </c>
+      <c r="N25" s="2" t="s">
+        <v>1590</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
         <v>323</v>
       </c>
@@ -5735,8 +7009,14 @@
       <c r="J26" s="2" t="s">
         <v>328</v>
       </c>
-    </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="M26" s="2" t="s">
+        <v>1591</v>
+      </c>
+      <c r="N26" s="2" t="s">
+        <v>1592</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
         <v>329</v>
       </c>
@@ -5764,8 +7044,14 @@
       <c r="J27" s="2" t="s">
         <v>200</v>
       </c>
-    </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="M27" s="2" t="s">
+        <v>1595</v>
+      </c>
+      <c r="N27" s="2" t="s">
+        <v>1596</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
         <v>330</v>
       </c>
@@ -5790,8 +7076,14 @@
       <c r="J28" s="2" t="s">
         <v>396</v>
       </c>
-    </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="M28" s="2" t="s">
+        <v>1597</v>
+      </c>
+      <c r="N28" s="2" t="s">
+        <v>1581</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
         <v>331</v>
       </c>
@@ -5819,8 +7111,14 @@
       <c r="J29" s="2" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="M29" s="2" t="s">
+        <v>1598</v>
+      </c>
+      <c r="N29" s="2" t="s">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
         <v>332</v>
       </c>
@@ -5845,8 +7143,14 @@
       <c r="J30" s="2" t="s">
         <v>200</v>
       </c>
-    </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="M30" s="2" t="s">
+        <v>1600</v>
+      </c>
+      <c r="N30" s="2" t="s">
+        <v>1518</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
         <v>333</v>
       </c>
@@ -5877,8 +7181,14 @@
       <c r="K31" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="M31" s="2" t="s">
+        <v>1604</v>
+      </c>
+      <c r="N31" s="2" t="s">
+        <v>1605</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
         <v>334</v>
       </c>
@@ -5905,6 +7215,12 @@
       </c>
       <c r="J32" s="2" t="s">
         <v>194</v>
+      </c>
+      <c r="M32" s="2" t="s">
+        <v>1606</v>
+      </c>
+      <c r="N32" s="2" t="s">
+        <v>1607</v>
       </c>
     </row>
     <row r="33" spans="1:16" x14ac:dyDescent="0.45">
@@ -5935,6 +7251,12 @@
       <c r="J33" s="2" t="s">
         <v>200</v>
       </c>
+      <c r="M33" s="2" t="s">
+        <v>1608</v>
+      </c>
+      <c r="N33" s="2" t="s">
+        <v>1609</v>
+      </c>
     </row>
     <row r="34" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
@@ -5964,6 +7286,12 @@
       <c r="J34" s="2" t="s">
         <v>186</v>
       </c>
+      <c r="M34" s="2" t="s">
+        <v>1610</v>
+      </c>
+      <c r="N34" s="2" t="s">
+        <v>1612</v>
+      </c>
     </row>
     <row r="35" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A35" t="s">
@@ -5993,6 +7321,12 @@
       <c r="J35" s="2" t="s">
         <v>188</v>
       </c>
+      <c r="M35" s="2" t="s">
+        <v>1613</v>
+      </c>
+      <c r="N35" s="2" t="s">
+        <v>1614</v>
+      </c>
     </row>
     <row r="36" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A36" t="s">
@@ -6019,6 +7353,12 @@
       <c r="J36" s="2" t="s">
         <v>179</v>
       </c>
+      <c r="M36" s="2" t="s">
+        <v>1615</v>
+      </c>
+      <c r="N36" s="2" t="s">
+        <v>1526</v>
+      </c>
     </row>
     <row r="37" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A37" t="s">
@@ -6045,6 +7385,12 @@
       <c r="J37" s="2" t="s">
         <v>432</v>
       </c>
+      <c r="M37" s="2" t="s">
+        <v>1616</v>
+      </c>
+      <c r="N37" s="2" t="s">
+        <v>1617</v>
+      </c>
     </row>
     <row r="38" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A38" t="s">
@@ -6074,6 +7420,12 @@
       <c r="J38" s="2" t="s">
         <v>436</v>
       </c>
+      <c r="M38" s="2" t="s">
+        <v>1618</v>
+      </c>
+      <c r="N38" s="2" t="s">
+        <v>1518</v>
+      </c>
     </row>
     <row r="39" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A39" t="s">
@@ -6100,6 +7452,12 @@
       <c r="J39" s="2" t="s">
         <v>186</v>
       </c>
+      <c r="M39" s="2" t="s">
+        <v>1619</v>
+      </c>
+      <c r="N39" s="2" t="s">
+        <v>1620</v>
+      </c>
     </row>
     <row r="40" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A40" t="s">
@@ -6129,6 +7487,12 @@
       <c r="J40" s="2" t="s">
         <v>194</v>
       </c>
+      <c r="M40" s="2" t="s">
+        <v>1621</v>
+      </c>
+      <c r="N40" s="2" t="s">
+        <v>1622</v>
+      </c>
     </row>
     <row r="41" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A41" t="s">
@@ -6155,6 +7519,12 @@
       <c r="J41" s="2" t="s">
         <v>186</v>
       </c>
+      <c r="M41" s="2" t="s">
+        <v>1623</v>
+      </c>
+      <c r="N41" s="2" t="s">
+        <v>1624</v>
+      </c>
     </row>
     <row r="42" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A42" t="s">
@@ -6184,6 +7554,12 @@
       <c r="J42" s="2" t="s">
         <v>179</v>
       </c>
+      <c r="M42" s="2" t="s">
+        <v>1626</v>
+      </c>
+      <c r="N42" s="2" t="s">
+        <v>1627</v>
+      </c>
     </row>
     <row r="43" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A43" t="s">
@@ -6213,6 +7589,12 @@
       <c r="J43" s="2" t="s">
         <v>200</v>
       </c>
+      <c r="M43" s="2" t="s">
+        <v>1628</v>
+      </c>
+      <c r="N43" s="2" t="s">
+        <v>1630</v>
+      </c>
     </row>
     <row r="44" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A44" t="s">
@@ -6242,6 +7624,12 @@
       <c r="J44" s="2" t="s">
         <v>197</v>
       </c>
+      <c r="M44" s="2" t="s">
+        <v>1619</v>
+      </c>
+      <c r="N44" s="2" t="s">
+        <v>1631</v>
+      </c>
     </row>
     <row r="45" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A45" t="s">
@@ -6271,6 +7659,12 @@
       <c r="J45" s="2" t="s">
         <v>179</v>
       </c>
+      <c r="M45" s="2" t="s">
+        <v>1632</v>
+      </c>
+      <c r="N45" s="2" t="s">
+        <v>1633</v>
+      </c>
     </row>
     <row r="46" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A46" t="s">
@@ -6303,8 +7697,12 @@
       <c r="L46" t="b">
         <v>1</v>
       </c>
-      <c r="M46" s="2"/>
-      <c r="N46" s="2"/>
+      <c r="M46" s="2" t="s">
+        <v>1636</v>
+      </c>
+      <c r="N46" s="2" t="s">
+        <v>1637</v>
+      </c>
       <c r="O46" s="2"/>
       <c r="P46" s="2"/>
     </row>
@@ -6336,6 +7734,12 @@
       <c r="J47" s="2" t="s">
         <v>179</v>
       </c>
+      <c r="M47" s="2" t="s">
+        <v>1639</v>
+      </c>
+      <c r="N47" s="2" t="s">
+        <v>1561</v>
+      </c>
     </row>
     <row r="48" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A48" t="s">
@@ -6365,8 +7769,14 @@
       <c r="J48" s="2" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="M48" s="2" t="s">
+        <v>1641</v>
+      </c>
+      <c r="N48" s="2" t="s">
+        <v>1642</v>
+      </c>
+    </row>
+    <row r="49" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A49" t="s">
         <v>271</v>
       </c>
@@ -6394,8 +7804,14 @@
       <c r="J49" s="2" t="s">
         <v>274</v>
       </c>
-    </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="M49" s="2" t="s">
+        <v>1530</v>
+      </c>
+      <c r="N49" s="2" t="s">
+        <v>1510</v>
+      </c>
+    </row>
+    <row r="50" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A50" t="s">
         <v>476</v>
       </c>
@@ -6420,8 +7836,14 @@
       <c r="J50" s="2" t="s">
         <v>558</v>
       </c>
-    </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="M50" s="2" t="s">
+        <v>1644</v>
+      </c>
+      <c r="N50" s="2" t="s">
+        <v>1646</v>
+      </c>
+    </row>
+    <row r="51" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A51" t="s">
         <v>477</v>
       </c>
@@ -6446,8 +7868,14 @@
       <c r="J51" s="2" t="s">
         <v>560</v>
       </c>
-    </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="M51" s="2" t="s">
+        <v>1647</v>
+      </c>
+      <c r="N51" s="2" t="s">
+        <v>1648</v>
+      </c>
+    </row>
+    <row r="52" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A52" t="s">
         <v>478</v>
       </c>
@@ -6475,8 +7903,14 @@
       <c r="J52" s="2" t="s">
         <v>188</v>
       </c>
-    </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="M52" s="2" t="s">
+        <v>1649</v>
+      </c>
+      <c r="N52" s="2" t="s">
+        <v>1510</v>
+      </c>
+    </row>
+    <row r="53" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A53" t="s">
         <v>479</v>
       </c>
@@ -6501,8 +7935,14 @@
       <c r="J53" s="2" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="M53" s="2" t="s">
+        <v>1650</v>
+      </c>
+      <c r="N53" s="2" t="s">
+        <v>1651</v>
+      </c>
+    </row>
+    <row r="54" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A54" t="s">
         <v>480</v>
       </c>
@@ -6530,8 +7970,14 @@
       <c r="J54" s="2" t="s">
         <v>200</v>
       </c>
-    </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="M54" s="2" t="s">
+        <v>1652</v>
+      </c>
+      <c r="N54" s="2" t="s">
+        <v>1550</v>
+      </c>
+    </row>
+    <row r="55" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A55" t="s">
         <v>481</v>
       </c>
@@ -6559,8 +8005,14 @@
       <c r="J55" s="2" t="s">
         <v>564</v>
       </c>
-    </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="M55" s="2" t="s">
+        <v>1653</v>
+      </c>
+      <c r="N55" s="2" t="s">
+        <v>1543</v>
+      </c>
+    </row>
+    <row r="56" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A56" t="s">
         <v>482</v>
       </c>
@@ -6588,8 +8040,14 @@
       <c r="J56" s="2" t="s">
         <v>186</v>
       </c>
-    </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="M56" s="2" t="s">
+        <v>1654</v>
+      </c>
+      <c r="N56" s="2" t="s">
+        <v>1656</v>
+      </c>
+    </row>
+    <row r="57" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A57" t="s">
         <v>483</v>
       </c>
@@ -6614,8 +8072,14 @@
       <c r="J57" s="2" t="s">
         <v>186</v>
       </c>
-    </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="M57" s="2" t="s">
+        <v>1657</v>
+      </c>
+      <c r="N57" s="2" t="s">
+        <v>1658</v>
+      </c>
+    </row>
+    <row r="58" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A58" t="s">
         <v>484</v>
       </c>
@@ -6643,8 +8107,14 @@
       <c r="J58" s="2" t="s">
         <v>183</v>
       </c>
-    </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="M58" s="2" t="s">
+        <v>1660</v>
+      </c>
+      <c r="N58" s="2" t="s">
+        <v>1662</v>
+      </c>
+    </row>
+    <row r="59" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A59" t="s">
         <v>485</v>
       </c>
@@ -6669,8 +8139,14 @@
       <c r="J59" s="2" t="s">
         <v>200</v>
       </c>
-    </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="M59" s="2" t="s">
+        <v>1663</v>
+      </c>
+      <c r="N59" s="2" t="s">
+        <v>1543</v>
+      </c>
+    </row>
+    <row r="60" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A60" t="s">
         <v>486</v>
       </c>
@@ -6695,8 +8171,14 @@
       <c r="J60" s="2" t="s">
         <v>200</v>
       </c>
-    </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="M60" s="2" t="s">
+        <v>1664</v>
+      </c>
+      <c r="N60" s="2" t="s">
+        <v>1666</v>
+      </c>
+    </row>
+    <row r="61" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A61" t="s">
         <v>487</v>
       </c>
@@ -6724,8 +8206,14 @@
       <c r="J61" s="2" t="s">
         <v>200</v>
       </c>
-    </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="M61" s="2" t="s">
+        <v>1667</v>
+      </c>
+      <c r="N61" s="2" t="s">
+        <v>1609</v>
+      </c>
+    </row>
+    <row r="62" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A62" t="s">
         <v>488</v>
       </c>
@@ -6753,8 +8241,14 @@
       <c r="J62" s="2" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="M62" s="2" t="s">
+        <v>1668</v>
+      </c>
+      <c r="N62" s="2" t="s">
+        <v>1651</v>
+      </c>
+    </row>
+    <row r="63" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A63" t="s">
         <v>489</v>
       </c>
@@ -6782,8 +8276,14 @@
       <c r="J63" s="2" t="s">
         <v>188</v>
       </c>
-    </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="M63" s="2" t="s">
+        <v>1669</v>
+      </c>
+      <c r="N63" s="2" t="s">
+        <v>1670</v>
+      </c>
+    </row>
+    <row r="64" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A64" t="s">
         <v>490</v>
       </c>
@@ -6811,8 +8311,14 @@
       <c r="J64" s="2" t="s">
         <v>564</v>
       </c>
-    </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="M64" s="2" t="s">
+        <v>1672</v>
+      </c>
+      <c r="N64" s="2" t="s">
+        <v>1673</v>
+      </c>
+    </row>
+    <row r="65" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A65" t="s">
         <v>491</v>
       </c>
@@ -6840,8 +8346,14 @@
       <c r="J65" s="2" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="M65" s="2" t="s">
+        <v>1674</v>
+      </c>
+      <c r="N65" s="2" t="s">
+        <v>1675</v>
+      </c>
+    </row>
+    <row r="66" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A66" t="s">
         <v>492</v>
       </c>
@@ -6866,8 +8378,14 @@
       <c r="J66" s="2" t="s">
         <v>200</v>
       </c>
-    </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="M66" s="2" t="s">
+        <v>1676</v>
+      </c>
+      <c r="N66" s="2" t="s">
+        <v>1677</v>
+      </c>
+    </row>
+    <row r="67" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A67" t="s">
         <v>493</v>
       </c>
@@ -6892,8 +8410,14 @@
       <c r="J67" s="2" t="s">
         <v>570</v>
       </c>
-    </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="M67" s="2" t="s">
+        <v>1678</v>
+      </c>
+      <c r="N67" s="2" t="s">
+        <v>1679</v>
+      </c>
+    </row>
+    <row r="68" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A68" t="s">
         <v>494</v>
       </c>
@@ -6921,8 +8445,14 @@
       <c r="J68" s="2" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="M68" s="2" t="s">
+        <v>1680</v>
+      </c>
+      <c r="N68" s="2" t="s">
+        <v>1681</v>
+      </c>
+    </row>
+    <row r="69" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A69" t="s">
         <v>495</v>
       </c>
@@ -6950,8 +8480,14 @@
       <c r="J69" s="2" t="s">
         <v>200</v>
       </c>
-    </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="M69" s="2" t="s">
+        <v>1682</v>
+      </c>
+      <c r="N69" s="2" t="s">
+        <v>1683</v>
+      </c>
+    </row>
+    <row r="70" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A70" t="s">
         <v>85</v>
       </c>
@@ -6979,8 +8515,14 @@
       <c r="K70" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="M70" s="2" t="s">
+        <v>1684</v>
+      </c>
+      <c r="N70" s="2" t="s">
+        <v>1685</v>
+      </c>
+    </row>
+    <row r="71" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A71" t="s">
         <v>275</v>
       </c>
@@ -7008,8 +8550,14 @@
       <c r="J71" s="2" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="M71" s="2" t="s">
+        <v>1686</v>
+      </c>
+      <c r="N71" s="2" t="s">
+        <v>1687</v>
+      </c>
+    </row>
+    <row r="72" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A72" t="s">
         <v>535</v>
       </c>
@@ -7037,8 +8585,14 @@
       <c r="J72" s="2" t="s">
         <v>181</v>
       </c>
-    </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="M72" s="2" t="s">
+        <v>1688</v>
+      </c>
+      <c r="N72" s="2" t="s">
+        <v>1689</v>
+      </c>
+    </row>
+    <row r="73" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A73" t="s">
         <v>536</v>
       </c>
@@ -7066,8 +8620,14 @@
       <c r="J73" s="2" t="s">
         <v>188</v>
       </c>
-    </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="M73" s="2" t="s">
+        <v>1547</v>
+      </c>
+      <c r="N73" s="2" t="s">
+        <v>1552</v>
+      </c>
+    </row>
+    <row r="74" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A74" t="s">
         <v>537</v>
       </c>
@@ -7092,8 +8652,14 @@
       <c r="J74" s="2" t="s">
         <v>186</v>
       </c>
-    </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="M74" s="2" t="s">
+        <v>1690</v>
+      </c>
+      <c r="N74" s="2" t="s">
+        <v>1691</v>
+      </c>
+    </row>
+    <row r="75" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A75" t="s">
         <v>538</v>
       </c>
@@ -7118,8 +8684,14 @@
       <c r="J75" s="2" t="s">
         <v>183</v>
       </c>
-    </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="M75" s="2" t="s">
+        <v>1693</v>
+      </c>
+      <c r="N75" s="2" t="s">
+        <v>1694</v>
+      </c>
+    </row>
+    <row r="76" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A76" t="s">
         <v>539</v>
       </c>
@@ -7144,8 +8716,14 @@
       <c r="J76" s="2" t="s">
         <v>649</v>
       </c>
-    </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="M76" s="2" t="s">
+        <v>1695</v>
+      </c>
+      <c r="N76" s="2" t="s">
+        <v>1561</v>
+      </c>
+    </row>
+    <row r="77" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A77" t="s">
         <v>540</v>
       </c>
@@ -7170,8 +8748,14 @@
       <c r="J77" s="2" t="s">
         <v>650</v>
       </c>
-    </row>
-    <row r="78" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="M77" s="2" t="s">
+        <v>1696</v>
+      </c>
+      <c r="N77" s="2" t="s">
+        <v>1697</v>
+      </c>
+    </row>
+    <row r="78" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A78" t="s">
         <v>541</v>
       </c>
@@ -7199,8 +8783,14 @@
       <c r="J78" s="2" t="s">
         <v>436</v>
       </c>
-    </row>
-    <row r="79" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="M78" s="2" t="s">
+        <v>1698</v>
+      </c>
+      <c r="N78" s="2" t="s">
+        <v>1699</v>
+      </c>
+    </row>
+    <row r="79" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A79" t="s">
         <v>542</v>
       </c>
@@ -7228,8 +8818,14 @@
       <c r="J79" s="2" t="s">
         <v>651</v>
       </c>
-    </row>
-    <row r="80" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="M79" s="2" t="s">
+        <v>1700</v>
+      </c>
+      <c r="N79" s="2" t="s">
+        <v>1701</v>
+      </c>
+    </row>
+    <row r="80" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A80" t="s">
         <v>543</v>
       </c>
@@ -7257,8 +8853,14 @@
       <c r="J80" s="2" t="s">
         <v>653</v>
       </c>
-    </row>
-    <row r="81" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="M80" s="2" t="s">
+        <v>1702</v>
+      </c>
+      <c r="N80" s="2" t="s">
+        <v>1703</v>
+      </c>
+    </row>
+    <row r="81" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A81" t="s">
         <v>544</v>
       </c>
@@ -7286,8 +8888,14 @@
       <c r="J81" s="2" t="s">
         <v>200</v>
       </c>
-    </row>
-    <row r="82" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="M81" s="2" t="s">
+        <v>1700</v>
+      </c>
+      <c r="N81" s="2" t="s">
+        <v>1704</v>
+      </c>
+    </row>
+    <row r="82" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A82" t="s">
         <v>545</v>
       </c>
@@ -7312,8 +8920,14 @@
       <c r="J82" s="2" t="s">
         <v>186</v>
       </c>
-    </row>
-    <row r="83" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="M82" s="2" t="s">
+        <v>1706</v>
+      </c>
+      <c r="N82" s="2" t="s">
+        <v>1707</v>
+      </c>
+    </row>
+    <row r="83" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A83" t="s">
         <v>546</v>
       </c>
@@ -7338,8 +8952,14 @@
       <c r="J83" s="2" t="s">
         <v>179</v>
       </c>
-    </row>
-    <row r="84" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="M83" s="2" t="s">
+        <v>1708</v>
+      </c>
+      <c r="N83" s="2" t="s">
+        <v>1709</v>
+      </c>
+    </row>
+    <row r="84" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A84" t="s">
         <v>547</v>
       </c>
@@ -7367,8 +8987,14 @@
       <c r="J84" s="2" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="85" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="M84" s="2" t="s">
+        <v>1710</v>
+      </c>
+      <c r="N84" s="2" t="s">
+        <v>1711</v>
+      </c>
+    </row>
+    <row r="85" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A85" t="s">
         <v>548</v>
       </c>
@@ -7396,8 +9022,14 @@
       <c r="J85" s="2" t="s">
         <v>200</v>
       </c>
-    </row>
-    <row r="86" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="M85" s="2" t="s">
+        <v>1712</v>
+      </c>
+      <c r="N85" s="2" t="s">
+        <v>1713</v>
+      </c>
+    </row>
+    <row r="86" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A86" t="s">
         <v>549</v>
       </c>
@@ -7422,8 +9054,14 @@
       <c r="J86" s="2" t="s">
         <v>188</v>
       </c>
-    </row>
-    <row r="87" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="M86" s="2" t="s">
+        <v>1667</v>
+      </c>
+      <c r="N86" s="2" t="s">
+        <v>1715</v>
+      </c>
+    </row>
+    <row r="87" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A87" t="s">
         <v>550</v>
       </c>
@@ -7448,8 +9086,14 @@
       <c r="J87" s="2" t="s">
         <v>188</v>
       </c>
-    </row>
-    <row r="88" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="M87" s="2" t="s">
+        <v>1717</v>
+      </c>
+      <c r="N87" s="2" t="s">
+        <v>1718</v>
+      </c>
+    </row>
+    <row r="88" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A88" t="s">
         <v>551</v>
       </c>
@@ -7477,8 +9121,14 @@
       <c r="J88" s="2" t="s">
         <v>188</v>
       </c>
-    </row>
-    <row r="89" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="M88" s="2" t="s">
+        <v>1719</v>
+      </c>
+      <c r="N88" s="2" t="s">
+        <v>1720</v>
+      </c>
+    </row>
+    <row r="89" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A89" t="s">
         <v>552</v>
       </c>
@@ -7506,8 +9156,14 @@
       <c r="J89" s="2" t="s">
         <v>179</v>
       </c>
-    </row>
-    <row r="90" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="M89" s="2" t="s">
+        <v>1722</v>
+      </c>
+      <c r="N89" s="2" t="s">
+        <v>1527</v>
+      </c>
+    </row>
+    <row r="90" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A90" t="s">
         <v>553</v>
       </c>
@@ -7535,8 +9191,14 @@
       <c r="J90" s="2" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="91" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="M90" s="2" t="s">
+        <v>1723</v>
+      </c>
+      <c r="N90" s="2" t="s">
+        <v>1724</v>
+      </c>
+    </row>
+    <row r="91" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A91" t="s">
         <v>554</v>
       </c>
@@ -7564,8 +9226,14 @@
       <c r="J91" s="2" t="s">
         <v>663</v>
       </c>
-    </row>
-    <row r="92" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="M91" s="2" t="s">
+        <v>1725</v>
+      </c>
+      <c r="N91" s="2" t="s">
+        <v>1726</v>
+      </c>
+    </row>
+    <row r="92" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A92" t="s">
         <v>555</v>
       </c>
@@ -7593,8 +9261,14 @@
       <c r="J92" s="2" t="s">
         <v>665</v>
       </c>
-    </row>
-    <row r="93" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="M92" s="2" t="s">
+        <v>1727</v>
+      </c>
+      <c r="N92" s="2" t="s">
+        <v>1729</v>
+      </c>
+    </row>
+    <row r="93" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A93" t="s">
         <v>556</v>
       </c>
@@ -7622,8 +9296,14 @@
       <c r="J93" s="2" t="s">
         <v>194</v>
       </c>
-    </row>
-    <row r="94" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="M93" s="2" t="s">
+        <v>1730</v>
+      </c>
+      <c r="N93" s="2" t="s">
+        <v>1585</v>
+      </c>
+    </row>
+    <row r="94" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A94" t="s">
         <v>281</v>
       </c>
@@ -7648,8 +9328,14 @@
       <c r="J94" s="2" t="s">
         <v>283</v>
       </c>
-    </row>
-    <row r="95" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="M94" s="2" t="s">
+        <v>1731</v>
+      </c>
+      <c r="N94" s="2" t="s">
+        <v>1552</v>
+      </c>
+    </row>
+    <row r="95" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A95" t="s">
         <v>738</v>
       </c>
@@ -7671,8 +9357,14 @@
       <c r="J95" s="2" t="s">
         <v>744</v>
       </c>
-    </row>
-    <row r="96" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="M95" s="2" t="s">
+        <v>1732</v>
+      </c>
+      <c r="N95" s="2" t="s">
+        <v>1733</v>
+      </c>
+    </row>
+    <row r="96" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A96" t="s">
         <v>739</v>
       </c>
@@ -7700,8 +9392,14 @@
       <c r="J96" s="2" t="s">
         <v>183</v>
       </c>
-    </row>
-    <row r="97" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="M96" s="2" t="s">
+        <v>1734</v>
+      </c>
+      <c r="N96" s="2" t="s">
+        <v>1736</v>
+      </c>
+    </row>
+    <row r="97" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A97" t="s">
         <v>740</v>
       </c>
@@ -7726,8 +9424,14 @@
       <c r="J97" s="2" t="s">
         <v>558</v>
       </c>
-    </row>
-    <row r="98" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="M97" s="2" t="s">
+        <v>1737</v>
+      </c>
+      <c r="N97" s="2" t="s">
+        <v>1738</v>
+      </c>
+    </row>
+    <row r="98" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A98" t="s">
         <v>17</v>
       </c>
@@ -7752,8 +9456,14 @@
       <c r="K98" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="99" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="M98" s="2" t="s">
+        <v>1740</v>
+      </c>
+      <c r="N98" s="2" t="s">
+        <v>1741</v>
+      </c>
+    </row>
+    <row r="99" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A99" t="s">
         <v>756</v>
       </c>
@@ -7781,8 +9491,14 @@
       <c r="J99" s="2" t="s">
         <v>762</v>
       </c>
-    </row>
-    <row r="100" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="M99" s="2" t="s">
+        <v>1742</v>
+      </c>
+      <c r="N99" s="2" t="s">
+        <v>1582</v>
+      </c>
+    </row>
+    <row r="100" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A100" t="s">
         <v>757</v>
       </c>
@@ -7813,8 +9529,14 @@
       <c r="L100" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="101" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="M100" s="2" t="s">
+        <v>1745</v>
+      </c>
+      <c r="N100" s="2" t="s">
+        <v>1746</v>
+      </c>
+    </row>
+    <row r="101" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A101" t="s">
         <v>758</v>
       </c>
@@ -7839,8 +9561,14 @@
       <c r="J101" s="2" t="s">
         <v>436</v>
       </c>
-    </row>
-    <row r="102" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="M101" s="2" t="s">
+        <v>1748</v>
+      </c>
+      <c r="N101" s="2" t="s">
+        <v>1749</v>
+      </c>
+    </row>
+    <row r="102" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A102" t="s">
         <v>284</v>
       </c>
@@ -7865,8 +9593,14 @@
       <c r="K102" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="103" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="M102" s="2" t="s">
+        <v>1566</v>
+      </c>
+      <c r="N102" s="2" t="s">
+        <v>1666</v>
+      </c>
+    </row>
+    <row r="103" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A103" t="s">
         <v>774</v>
       </c>
@@ -7891,8 +9625,14 @@
       <c r="J103" s="2" t="s">
         <v>564</v>
       </c>
-    </row>
-    <row r="104" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="M103" s="2" t="s">
+        <v>1750</v>
+      </c>
+      <c r="N103" s="2" t="s">
+        <v>1751</v>
+      </c>
+    </row>
+    <row r="104" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A104" t="s">
         <v>775</v>
       </c>
@@ -7917,8 +9657,14 @@
       <c r="J104" s="2" t="s">
         <v>186</v>
       </c>
-    </row>
-    <row r="105" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="M104" s="2" t="s">
+        <v>1752</v>
+      </c>
+      <c r="N104" s="2" t="s">
+        <v>1753</v>
+      </c>
+    </row>
+    <row r="105" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A105" t="s">
         <v>776</v>
       </c>
@@ -7943,8 +9689,14 @@
       <c r="J105" s="2" t="s">
         <v>558</v>
       </c>
-    </row>
-    <row r="106" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="M105" s="2" t="s">
+        <v>1755</v>
+      </c>
+      <c r="N105" s="2" t="s">
+        <v>1756</v>
+      </c>
+    </row>
+    <row r="106" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A106" t="s">
         <v>777</v>
       </c>
@@ -7969,8 +9721,14 @@
       <c r="J106" s="2" t="s">
         <v>194</v>
       </c>
-    </row>
-    <row r="107" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="M106" s="2" t="s">
+        <v>1757</v>
+      </c>
+      <c r="N106" s="2" t="s">
+        <v>1622</v>
+      </c>
+    </row>
+    <row r="107" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A107" t="s">
         <v>778</v>
       </c>
@@ -7998,8 +9756,14 @@
       <c r="J107" s="2" t="s">
         <v>194</v>
       </c>
-    </row>
-    <row r="108" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="M107" s="2" t="s">
+        <v>1760</v>
+      </c>
+      <c r="N107" s="2" t="s">
+        <v>1761</v>
+      </c>
+    </row>
+    <row r="108" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A108" t="s">
         <v>779</v>
       </c>
@@ -8027,8 +9791,14 @@
       <c r="J108" s="2" t="s">
         <v>194</v>
       </c>
-    </row>
-    <row r="109" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="M108" s="2" t="s">
+        <v>1762</v>
+      </c>
+      <c r="N108" s="2" t="s">
+        <v>1586</v>
+      </c>
+    </row>
+    <row r="109" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A109" t="s">
         <v>96</v>
       </c>
@@ -8053,8 +9823,14 @@
       <c r="K109" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="110" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="M109" s="2" t="s">
+        <v>1763</v>
+      </c>
+      <c r="N109" s="2" t="s">
+        <v>1764</v>
+      </c>
+    </row>
+    <row r="110" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A110" t="s">
         <v>807</v>
       </c>
@@ -8082,8 +9858,14 @@
       <c r="J110" s="2" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="111" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="M110" s="2" t="s">
+        <v>1765</v>
+      </c>
+      <c r="N110" s="2" t="s">
+        <v>1592</v>
+      </c>
+    </row>
+    <row r="111" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A111" t="s">
         <v>808</v>
       </c>
@@ -8108,8 +9890,14 @@
       <c r="J111" s="2" t="s">
         <v>436</v>
       </c>
-    </row>
-    <row r="112" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="M111" s="2" t="s">
+        <v>1768</v>
+      </c>
+      <c r="N111" s="2" t="s">
+        <v>1769</v>
+      </c>
+    </row>
+    <row r="112" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A112" t="s">
         <v>809</v>
       </c>
@@ -8137,8 +9925,14 @@
       <c r="J112" s="2" t="s">
         <v>837</v>
       </c>
-    </row>
-    <row r="113" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="M112" s="2" t="s">
+        <v>1770</v>
+      </c>
+      <c r="N112" s="2" t="s">
+        <v>1586</v>
+      </c>
+    </row>
+    <row r="113" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A113" t="s">
         <v>810</v>
       </c>
@@ -8163,8 +9957,14 @@
       <c r="J113" s="2" t="s">
         <v>744</v>
       </c>
-    </row>
-    <row r="114" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="M113" s="2" t="s">
+        <v>1772</v>
+      </c>
+      <c r="N113" s="2" t="s">
+        <v>1773</v>
+      </c>
+    </row>
+    <row r="114" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A114" t="s">
         <v>811</v>
       </c>
@@ -8189,8 +9989,14 @@
       <c r="J114" s="2" t="s">
         <v>564</v>
       </c>
-    </row>
-    <row r="115" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="M114" s="2" t="s">
+        <v>1712</v>
+      </c>
+      <c r="N114" s="2" t="s">
+        <v>1774</v>
+      </c>
+    </row>
+    <row r="115" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A115" t="s">
         <v>812</v>
       </c>
@@ -8218,8 +10024,14 @@
       <c r="J115" s="2" t="s">
         <v>186</v>
       </c>
-    </row>
-    <row r="116" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="M115" s="2" t="s">
+        <v>1775</v>
+      </c>
+      <c r="N115" s="2" t="s">
+        <v>1776</v>
+      </c>
+    </row>
+    <row r="116" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A116" t="s">
         <v>813</v>
       </c>
@@ -8247,8 +10059,14 @@
       <c r="J116" s="2" t="s">
         <v>194</v>
       </c>
-    </row>
-    <row r="117" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="M116" s="2" t="s">
+        <v>1777</v>
+      </c>
+      <c r="N116" s="2" t="s">
+        <v>1778</v>
+      </c>
+    </row>
+    <row r="117" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A117" t="s">
         <v>814</v>
       </c>
@@ -8273,8 +10091,11 @@
       <c r="J117" s="2" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="118" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="M117" s="2" t="s">
+        <v>1780</v>
+      </c>
+    </row>
+    <row r="118" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A118" t="s">
         <v>815</v>
       </c>
@@ -8302,8 +10123,14 @@
       <c r="J118" s="2" t="s">
         <v>564</v>
       </c>
-    </row>
-    <row r="119" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="M118" s="2" t="s">
+        <v>1781</v>
+      </c>
+      <c r="N118" s="2" t="s">
+        <v>1782</v>
+      </c>
+    </row>
+    <row r="119" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A119" t="s">
         <v>816</v>
       </c>
@@ -8331,8 +10158,14 @@
       <c r="J119" s="2" t="s">
         <v>866</v>
       </c>
-    </row>
-    <row r="120" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="M119" s="2" t="s">
+        <v>1784</v>
+      </c>
+      <c r="N119" s="2" t="s">
+        <v>1785</v>
+      </c>
+    </row>
+    <row r="120" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A120" t="s">
         <v>817</v>
       </c>
@@ -8360,8 +10193,14 @@
       <c r="J120" s="2" t="s">
         <v>200</v>
       </c>
-    </row>
-    <row r="121" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="M120" s="2" t="s">
+        <v>1786</v>
+      </c>
+      <c r="N120" s="2" t="s">
+        <v>1787</v>
+      </c>
+    </row>
+    <row r="121" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A121" t="s">
         <v>818</v>
       </c>
@@ -8389,8 +10228,14 @@
       <c r="J121" s="2" t="s">
         <v>837</v>
       </c>
-    </row>
-    <row r="122" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="M121" s="2" t="s">
+        <v>1789</v>
+      </c>
+      <c r="N121" s="2" t="s">
+        <v>1679</v>
+      </c>
+    </row>
+    <row r="122" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A122" t="s">
         <v>314</v>
       </c>
@@ -8415,8 +10260,14 @@
       <c r="J122" s="2" t="s">
         <v>319</v>
       </c>
-    </row>
-    <row r="123" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="M122" s="2" t="s">
+        <v>1791</v>
+      </c>
+      <c r="N122" s="2" t="s">
+        <v>1792</v>
+      </c>
+    </row>
+    <row r="123" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A123" t="s">
         <v>879</v>
       </c>
@@ -8444,8 +10295,14 @@
       <c r="J123" s="2" t="s">
         <v>564</v>
       </c>
-    </row>
-    <row r="124" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="M123" s="2" t="s">
+        <v>1793</v>
+      </c>
+      <c r="N123" s="2" t="s">
+        <v>1794</v>
+      </c>
+    </row>
+    <row r="124" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A124" t="s">
         <v>880</v>
       </c>
@@ -8473,8 +10330,14 @@
       <c r="J124" s="2" t="s">
         <v>936</v>
       </c>
-    </row>
-    <row r="125" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="M124" s="2" t="s">
+        <v>1795</v>
+      </c>
+      <c r="N124" s="2" t="s">
+        <v>1675</v>
+      </c>
+    </row>
+    <row r="125" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A125" t="s">
         <v>881</v>
       </c>
@@ -8499,8 +10362,14 @@
       <c r="J125" s="2" t="s">
         <v>270</v>
       </c>
-    </row>
-    <row r="126" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="M125" s="2" t="s">
+        <v>1797</v>
+      </c>
+      <c r="N125" s="2" t="s">
+        <v>1592</v>
+      </c>
+    </row>
+    <row r="126" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A126" t="s">
         <v>882</v>
       </c>
@@ -8528,8 +10397,14 @@
       <c r="J126" s="2" t="s">
         <v>179</v>
       </c>
-    </row>
-    <row r="127" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="M126" s="2" t="s">
+        <v>1798</v>
+      </c>
+      <c r="N126" s="2" t="s">
+        <v>1799</v>
+      </c>
+    </row>
+    <row r="127" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A127" t="s">
         <v>883</v>
       </c>
@@ -8554,8 +10429,14 @@
       <c r="J127" s="2" t="s">
         <v>938</v>
       </c>
-    </row>
-    <row r="128" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="M127" s="2" t="s">
+        <v>1800</v>
+      </c>
+      <c r="N127" s="2" t="s">
+        <v>1801</v>
+      </c>
+    </row>
+    <row r="128" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A128" t="s">
         <v>884</v>
       </c>
@@ -8580,8 +10461,14 @@
       <c r="J128" s="2" t="s">
         <v>940</v>
       </c>
-    </row>
-    <row r="129" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="M128" s="2" t="s">
+        <v>1802</v>
+      </c>
+      <c r="N128" s="2" t="s">
+        <v>1803</v>
+      </c>
+    </row>
+    <row r="129" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A129" t="s">
         <v>885</v>
       </c>
@@ -8606,8 +10493,14 @@
       <c r="J129" s="2" t="s">
         <v>436</v>
       </c>
-    </row>
-    <row r="130" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="M129" s="2" t="s">
+        <v>1804</v>
+      </c>
+      <c r="N129" s="2" t="s">
+        <v>1805</v>
+      </c>
+    </row>
+    <row r="130" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A130" t="s">
         <v>886</v>
       </c>
@@ -8638,8 +10531,14 @@
       <c r="K130" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="131" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="M130" s="2" t="s">
+        <v>1730</v>
+      </c>
+      <c r="N130" s="2" t="s">
+        <v>1806</v>
+      </c>
+    </row>
+    <row r="131" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A131" t="s">
         <v>887</v>
       </c>
@@ -8667,8 +10566,14 @@
       <c r="J131" s="2" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="132" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="M131" s="2" t="s">
+        <v>1807</v>
+      </c>
+      <c r="N131" s="2" t="s">
+        <v>1526</v>
+      </c>
+    </row>
+    <row r="132" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A132" t="s">
         <v>888</v>
       </c>
@@ -8696,8 +10601,14 @@
       <c r="J132" s="2" t="s">
         <v>941</v>
       </c>
-    </row>
-    <row r="133" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="M132" s="2" t="s">
+        <v>1808</v>
+      </c>
+      <c r="N132" s="2" t="s">
+        <v>1809</v>
+      </c>
+    </row>
+    <row r="133" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A133" t="s">
         <v>889</v>
       </c>
@@ -8725,8 +10636,14 @@
       <c r="J133" s="2" t="s">
         <v>564</v>
       </c>
-    </row>
-    <row r="134" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="M133" s="2" t="s">
+        <v>1810</v>
+      </c>
+      <c r="N133" s="2" t="s">
+        <v>1552</v>
+      </c>
+    </row>
+    <row r="134" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A134" t="s">
         <v>890</v>
       </c>
@@ -8754,8 +10671,14 @@
       <c r="J134" s="2" t="s">
         <v>188</v>
       </c>
-    </row>
-    <row r="135" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="M134" s="2" t="s">
+        <v>1811</v>
+      </c>
+      <c r="N134" s="2" t="s">
+        <v>1812</v>
+      </c>
+    </row>
+    <row r="135" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A135" t="s">
         <v>891</v>
       </c>
@@ -8780,8 +10703,14 @@
       <c r="J135" s="2" t="s">
         <v>270</v>
       </c>
-    </row>
-    <row r="136" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="M135" s="2" t="s">
+        <v>1813</v>
+      </c>
+      <c r="N135" s="2" t="s">
+        <v>1814</v>
+      </c>
+    </row>
+    <row r="136" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A136" t="s">
         <v>892</v>
       </c>
@@ -8809,8 +10738,14 @@
       <c r="J136" s="2" t="s">
         <v>179</v>
       </c>
-    </row>
-    <row r="137" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="M136" s="2" t="s">
+        <v>1815</v>
+      </c>
+      <c r="N136" s="2" t="s">
+        <v>1816</v>
+      </c>
+    </row>
+    <row r="137" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A137" t="s">
         <v>893</v>
       </c>
@@ -8835,8 +10770,14 @@
       <c r="J137" s="2" t="s">
         <v>944</v>
       </c>
-    </row>
-    <row r="138" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="M137" s="2" t="s">
+        <v>1817</v>
+      </c>
+      <c r="N137" s="2" t="s">
+        <v>1818</v>
+      </c>
+    </row>
+    <row r="138" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A138" t="s">
         <v>894</v>
       </c>
@@ -8864,8 +10805,14 @@
       <c r="J138" s="2" t="s">
         <v>744</v>
       </c>
-    </row>
-    <row r="139" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="M138" s="2" t="s">
+        <v>1819</v>
+      </c>
+      <c r="N138" s="2" t="s">
+        <v>1821</v>
+      </c>
+    </row>
+    <row r="139" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A139" t="s">
         <v>895</v>
       </c>
@@ -8893,8 +10840,14 @@
       <c r="J139" s="2" t="s">
         <v>948</v>
       </c>
-    </row>
-    <row r="140" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="M139" s="2" t="s">
+        <v>1822</v>
+      </c>
+      <c r="N139" s="2" t="s">
+        <v>1525</v>
+      </c>
+    </row>
+    <row r="140" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A140" t="s">
         <v>896</v>
       </c>
@@ -8919,8 +10872,14 @@
       <c r="J140" s="2" t="s">
         <v>1056</v>
       </c>
-    </row>
-    <row r="141" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="M140" s="2" t="s">
+        <v>1589</v>
+      </c>
+      <c r="N140" s="2" t="s">
+        <v>1823</v>
+      </c>
+    </row>
+    <row r="141" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A141" t="s">
         <v>897</v>
       </c>
@@ -8945,8 +10904,14 @@
       <c r="J141" s="2" t="s">
         <v>1057</v>
       </c>
-    </row>
-    <row r="142" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="M141" s="2" t="s">
+        <v>1824</v>
+      </c>
+      <c r="N141" s="2" t="s">
+        <v>1550</v>
+      </c>
+    </row>
+    <row r="142" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A142" t="s">
         <v>898</v>
       </c>
@@ -8974,8 +10939,14 @@
       <c r="J142" s="2" t="s">
         <v>1058</v>
       </c>
-    </row>
-    <row r="143" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="M142" s="2" t="s">
+        <v>1826</v>
+      </c>
+      <c r="N142" s="2" t="s">
+        <v>1823</v>
+      </c>
+    </row>
+    <row r="143" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A143" t="s">
         <v>899</v>
       </c>
@@ -9000,8 +10971,14 @@
       <c r="J143" s="2" t="s">
         <v>188</v>
       </c>
-    </row>
-    <row r="144" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="M143" s="2" t="s">
+        <v>1660</v>
+      </c>
+      <c r="N143" s="2" t="s">
+        <v>1510</v>
+      </c>
+    </row>
+    <row r="144" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A144" t="s">
         <v>900</v>
       </c>
@@ -9026,8 +11003,14 @@
       <c r="J144" s="2" t="s">
         <v>1061</v>
       </c>
-    </row>
-    <row r="145" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="M144" s="2" t="s">
+        <v>1827</v>
+      </c>
+      <c r="N144" s="2" t="s">
+        <v>1828</v>
+      </c>
+    </row>
+    <row r="145" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A145" t="s">
         <v>901</v>
       </c>
@@ -9052,8 +11035,14 @@
       <c r="J145" s="2" t="s">
         <v>1062</v>
       </c>
-    </row>
-    <row r="146" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="M145" s="2" t="s">
+        <v>1829</v>
+      </c>
+      <c r="N145" s="2" t="s">
+        <v>1830</v>
+      </c>
+    </row>
+    <row r="146" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A146" t="s">
         <v>902</v>
       </c>
@@ -9078,8 +11067,14 @@
       <c r="J146" s="2" t="s">
         <v>1064</v>
       </c>
-    </row>
-    <row r="147" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="M146" s="2" t="s">
+        <v>1520</v>
+      </c>
+      <c r="N146" s="2" t="s">
+        <v>1561</v>
+      </c>
+    </row>
+    <row r="147" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A147" t="s">
         <v>903</v>
       </c>
@@ -9104,8 +11099,11 @@
       <c r="J147" s="2" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="148" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="M147" s="2" t="s">
+        <v>1831</v>
+      </c>
+    </row>
+    <row r="148" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A148" t="s">
         <v>76</v>
       </c>
@@ -9133,8 +11131,14 @@
       <c r="J148" s="2" t="s">
         <v>322</v>
       </c>
-    </row>
-    <row r="149" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="M148" s="2" t="s">
+        <v>1832</v>
+      </c>
+      <c r="N148" s="2" t="s">
+        <v>1526</v>
+      </c>
+    </row>
+    <row r="149" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A149" t="s">
         <v>995</v>
       </c>
@@ -9162,8 +11166,14 @@
       <c r="J149" s="2" t="s">
         <v>1066</v>
       </c>
-    </row>
-    <row r="150" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="M149" s="2" t="s">
+        <v>1831</v>
+      </c>
+      <c r="N149" s="2" t="s">
+        <v>1550</v>
+      </c>
+    </row>
+    <row r="150" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A150" t="s">
         <v>996</v>
       </c>
@@ -9191,8 +11201,14 @@
       <c r="J150" s="2" t="s">
         <v>1067</v>
       </c>
-    </row>
-    <row r="151" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="M150" s="2" t="s">
+        <v>1833</v>
+      </c>
+      <c r="N150" s="2" t="s">
+        <v>1834</v>
+      </c>
+    </row>
+    <row r="151" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A151" t="s">
         <v>997</v>
       </c>
@@ -9217,8 +11233,14 @@
       <c r="J151" s="2" t="s">
         <v>1068</v>
       </c>
-    </row>
-    <row r="152" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="M151" s="2" t="s">
+        <v>1835</v>
+      </c>
+      <c r="N151" s="2" t="s">
+        <v>1836</v>
+      </c>
+    </row>
+    <row r="152" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A152" t="s">
         <v>998</v>
       </c>
@@ -9243,8 +11265,14 @@
       <c r="J152" s="2" t="s">
         <v>1069</v>
       </c>
-    </row>
-    <row r="153" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="M152" s="2" t="s">
+        <v>1837</v>
+      </c>
+      <c r="N152" s="2" t="s">
+        <v>1580</v>
+      </c>
+    </row>
+    <row r="153" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A153" t="s">
         <v>999</v>
       </c>
@@ -9272,8 +11300,14 @@
       <c r="J153" s="2" t="s">
         <v>837</v>
       </c>
-    </row>
-    <row r="154" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="M153" s="2" t="s">
+        <v>1838</v>
+      </c>
+      <c r="N153" s="2" t="s">
+        <v>1839</v>
+      </c>
+    </row>
+    <row r="154" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A154" t="s">
         <v>1000</v>
       </c>
@@ -9298,8 +11332,14 @@
       <c r="J154" s="2" t="s">
         <v>1066</v>
       </c>
-    </row>
-    <row r="155" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="M154" s="2" t="s">
+        <v>1840</v>
+      </c>
+      <c r="N154" s="2" t="s">
+        <v>1544</v>
+      </c>
+    </row>
+    <row r="155" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A155" t="s">
         <v>1001</v>
       </c>
@@ -9327,8 +11367,14 @@
       <c r="J155" s="2" t="s">
         <v>1071</v>
       </c>
-    </row>
-    <row r="156" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="M155" s="2" t="s">
+        <v>1841</v>
+      </c>
+      <c r="N155" s="2" t="s">
+        <v>1550</v>
+      </c>
+    </row>
+    <row r="156" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A156" t="s">
         <v>1002</v>
       </c>
@@ -9353,8 +11399,14 @@
       <c r="J156" s="2" t="s">
         <v>1072</v>
       </c>
-    </row>
-    <row r="157" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="M156" s="2" t="s">
+        <v>1551</v>
+      </c>
+      <c r="N156" s="2" t="s">
+        <v>1526</v>
+      </c>
+    </row>
+    <row r="157" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A157" t="s">
         <v>1003</v>
       </c>
@@ -9382,8 +11434,14 @@
       <c r="J157" s="2" t="s">
         <v>183</v>
       </c>
-    </row>
-    <row r="158" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="M157" s="2" t="s">
+        <v>1831</v>
+      </c>
+      <c r="N157" s="2" t="s">
+        <v>1586</v>
+      </c>
+    </row>
+    <row r="158" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A158" t="s">
         <v>1004</v>
       </c>
@@ -9411,8 +11469,14 @@
       <c r="J158" s="2" t="s">
         <v>744</v>
       </c>
-    </row>
-    <row r="159" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="M158" s="2" t="s">
+        <v>1842</v>
+      </c>
+      <c r="N158" s="2" t="s">
+        <v>1843</v>
+      </c>
+    </row>
+    <row r="159" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A159" t="s">
         <v>1005</v>
       </c>
@@ -9437,8 +11501,14 @@
       <c r="J159" s="2" t="s">
         <v>179</v>
       </c>
-    </row>
-    <row r="160" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="M159" s="2" t="s">
+        <v>1831</v>
+      </c>
+      <c r="N159" s="2" t="s">
+        <v>1844</v>
+      </c>
+    </row>
+    <row r="160" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A160" t="s">
         <v>1006</v>
       </c>
@@ -9466,8 +11536,14 @@
       <c r="J160" s="2" t="s">
         <v>1507</v>
       </c>
-    </row>
-    <row r="161" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="M160" s="2" t="s">
+        <v>1845</v>
+      </c>
+      <c r="N160" s="2" t="s">
+        <v>1846</v>
+      </c>
+    </row>
+    <row r="161" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A161" t="s">
         <v>1007</v>
       </c>
@@ -9492,8 +11568,14 @@
       <c r="J161" s="2" t="s">
         <v>1073</v>
       </c>
-    </row>
-    <row r="162" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="M161" s="2" t="s">
+        <v>1847</v>
+      </c>
+      <c r="N161" s="2" t="s">
+        <v>1848</v>
+      </c>
+    </row>
+    <row r="162" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A162" t="s">
         <v>1008</v>
       </c>
@@ -9518,8 +11600,14 @@
       <c r="J162" s="2" t="s">
         <v>1074</v>
       </c>
-    </row>
-    <row r="163" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="M162" s="2" t="s">
+        <v>1849</v>
+      </c>
+      <c r="N162" s="2" t="s">
+        <v>1561</v>
+      </c>
+    </row>
+    <row r="163" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A163" t="s">
         <v>1009</v>
       </c>
@@ -9547,8 +11635,14 @@
       <c r="J163" s="2" t="s">
         <v>1196</v>
       </c>
-    </row>
-    <row r="164" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="M163" s="2" t="s">
+        <v>1589</v>
+      </c>
+      <c r="N163" s="2" t="s">
+        <v>1851</v>
+      </c>
+    </row>
+    <row r="164" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A164" t="s">
         <v>1010</v>
       </c>
@@ -9576,8 +11670,14 @@
       <c r="J164" s="2" t="s">
         <v>1197</v>
       </c>
-    </row>
-    <row r="165" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="M164" s="2" t="s">
+        <v>1731</v>
+      </c>
+      <c r="N164" s="2" t="s">
+        <v>1852</v>
+      </c>
+    </row>
+    <row r="165" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A165" t="s">
         <v>1011</v>
       </c>
@@ -9602,8 +11702,14 @@
       <c r="J165" s="2" t="s">
         <v>1198</v>
       </c>
-    </row>
-    <row r="166" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="M165" s="2" t="s">
+        <v>1762</v>
+      </c>
+      <c r="N165" s="2" t="s">
+        <v>1853</v>
+      </c>
+    </row>
+    <row r="166" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A166" t="s">
         <v>1012</v>
       </c>
@@ -9631,8 +11737,14 @@
       <c r="J166" s="2" t="s">
         <v>1196</v>
       </c>
-    </row>
-    <row r="167" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="M166" s="2" t="s">
+        <v>1854</v>
+      </c>
+      <c r="N166" s="2" t="s">
+        <v>1855</v>
+      </c>
+    </row>
+    <row r="167" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A167" t="s">
         <v>1013</v>
       </c>
@@ -9660,8 +11772,14 @@
       <c r="J167" s="2" t="s">
         <v>1200</v>
       </c>
-    </row>
-    <row r="168" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="M167" s="2" t="s">
+        <v>1856</v>
+      </c>
+      <c r="N167" s="2" t="s">
+        <v>1857</v>
+      </c>
+    </row>
+    <row r="168" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A168" t="s">
         <v>23</v>
       </c>
@@ -9686,8 +11804,14 @@
       <c r="J168" s="2" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="169" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="M168" s="2" t="s">
+        <v>1663</v>
+      </c>
+      <c r="N168" s="2" t="s">
+        <v>1526</v>
+      </c>
+    </row>
+    <row r="169" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A169" t="s">
         <v>1139</v>
       </c>
@@ -9715,8 +11839,14 @@
       <c r="J169" s="2" t="s">
         <v>1196</v>
       </c>
-    </row>
-    <row r="170" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="M169" s="2" t="s">
+        <v>1858</v>
+      </c>
+      <c r="N169" s="2" t="s">
+        <v>1834</v>
+      </c>
+    </row>
+    <row r="170" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A170" t="s">
         <v>1140</v>
       </c>
@@ -9747,8 +11877,14 @@
       <c r="L170" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="171" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="M170" s="2" t="s">
+        <v>1859</v>
+      </c>
+      <c r="N170" s="2" t="s">
+        <v>1543</v>
+      </c>
+    </row>
+    <row r="171" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A171" t="s">
         <v>1141</v>
       </c>
@@ -9779,8 +11915,14 @@
       <c r="L171" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="172" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="M171" s="2" t="s">
+        <v>1860</v>
+      </c>
+      <c r="N171" s="2" t="s">
+        <v>1861</v>
+      </c>
+    </row>
+    <row r="172" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A172" t="s">
         <v>1142</v>
       </c>
@@ -9805,8 +11947,14 @@
       <c r="J172" s="2" t="s">
         <v>1202</v>
       </c>
-    </row>
-    <row r="173" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="M172" s="2" t="s">
+        <v>1731</v>
+      </c>
+      <c r="N172" s="2" t="s">
+        <v>1862</v>
+      </c>
+    </row>
+    <row r="173" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A173" t="s">
         <v>1143</v>
       </c>
@@ -9834,8 +11982,14 @@
       <c r="J173" s="2" t="s">
         <v>436</v>
       </c>
-    </row>
-    <row r="174" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="M173" s="2" t="s">
+        <v>1556</v>
+      </c>
+      <c r="N173" s="2" t="s">
+        <v>1543</v>
+      </c>
+    </row>
+    <row r="174" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A174" t="s">
         <v>1144</v>
       </c>
@@ -9866,8 +12020,14 @@
       <c r="L174" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="175" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="M174" s="2" t="s">
+        <v>1863</v>
+      </c>
+      <c r="N174" s="2" t="s">
+        <v>1864</v>
+      </c>
+    </row>
+    <row r="175" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A175" t="s">
         <v>1145</v>
       </c>
@@ -9898,8 +12058,14 @@
       <c r="L175" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="176" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="M175" s="2" t="s">
+        <v>1865</v>
+      </c>
+      <c r="N175" s="2" t="s">
+        <v>1866</v>
+      </c>
+    </row>
+    <row r="176" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A176" t="s">
         <v>1146</v>
       </c>
@@ -9930,8 +12096,14 @@
       <c r="L176" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="177" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="M176" s="2" t="s">
+        <v>1832</v>
+      </c>
+      <c r="N176" s="2" t="s">
+        <v>1867</v>
+      </c>
+    </row>
+    <row r="177" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A177" t="s">
         <v>1147</v>
       </c>
@@ -9959,8 +12131,14 @@
       <c r="J177" s="2" t="s">
         <v>436</v>
       </c>
-    </row>
-    <row r="178" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="M177" s="2" t="s">
+        <v>1868</v>
+      </c>
+      <c r="N177" s="2" t="s">
+        <v>1869</v>
+      </c>
+    </row>
+    <row r="178" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A178" t="s">
         <v>1148</v>
       </c>
@@ -9988,8 +12166,14 @@
       <c r="J178" s="2" t="s">
         <v>1206</v>
       </c>
-    </row>
-    <row r="179" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="M178" s="2" t="s">
+        <v>1870</v>
+      </c>
+      <c r="N178" s="2" t="s">
+        <v>1872</v>
+      </c>
+    </row>
+    <row r="179" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A179" t="s">
         <v>29</v>
       </c>
@@ -10017,8 +12201,14 @@
       <c r="J179" s="2" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="180" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="M179" s="2" t="s">
+        <v>1873</v>
+      </c>
+      <c r="N179" s="2" t="s">
+        <v>1874</v>
+      </c>
+    </row>
+    <row r="180" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A180" t="s">
         <v>1149</v>
       </c>
@@ -10043,8 +12233,14 @@
       <c r="J180" s="2" t="s">
         <v>1207</v>
       </c>
-    </row>
-    <row r="181" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="M180" s="2" t="s">
+        <v>1686</v>
+      </c>
+      <c r="N180" s="2" t="s">
+        <v>1875</v>
+      </c>
+    </row>
+    <row r="181" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A181" t="s">
         <v>1150</v>
       </c>
@@ -10072,8 +12268,14 @@
       <c r="J181" s="2" t="s">
         <v>1208</v>
       </c>
-    </row>
-    <row r="182" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="M181" s="2" t="s">
+        <v>1876</v>
+      </c>
+      <c r="N181" s="2" t="s">
+        <v>1543</v>
+      </c>
+    </row>
+    <row r="182" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A182" t="s">
         <v>1151</v>
       </c>
@@ -10098,8 +12300,14 @@
       <c r="J182" s="2" t="s">
         <v>186</v>
       </c>
-    </row>
-    <row r="183" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="M182" s="2" t="s">
+        <v>1878</v>
+      </c>
+      <c r="N182" s="2" t="s">
+        <v>1879</v>
+      </c>
+    </row>
+    <row r="183" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A183" t="s">
         <v>1152</v>
       </c>
@@ -10127,8 +12335,14 @@
       <c r="J183" s="2" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="184" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="M183" s="2" t="s">
+        <v>1667</v>
+      </c>
+      <c r="N183" s="2" t="s">
+        <v>1880</v>
+      </c>
+    </row>
+    <row r="184" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A184" t="s">
         <v>1153</v>
       </c>
@@ -10156,8 +12370,14 @@
       <c r="J184" s="2" t="s">
         <v>179</v>
       </c>
-    </row>
-    <row r="185" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="M184" s="2" t="s">
+        <v>1881</v>
+      </c>
+      <c r="N184" s="2" t="s">
+        <v>1882</v>
+      </c>
+    </row>
+    <row r="185" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A185" t="s">
         <v>36</v>
       </c>
@@ -10184,6 +12404,12 @@
       </c>
       <c r="K185" t="b">
         <v>1</v>
+      </c>
+      <c r="M185" s="2" t="s">
+        <v>1883</v>
+      </c>
+      <c r="N185" s="2" t="s">
+        <v>1543</v>
       </c>
     </row>
   </sheetData>
@@ -10196,6 +12422,428 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{445C98DF-AF88-42FF-A8A5-2AB8831F51CC}">
+  <dimension ref="A1:B60"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="22.1328125" customWidth="1"/>
+    <col min="2" max="2" width="16.9296875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A1" s="1" t="s">
+        <v>1513</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1514</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A2" t="s">
+        <v>1519</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1510</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A3" t="s">
+        <v>1520</v>
+      </c>
+      <c r="B3" t="s">
+        <v>1525</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A4" t="s">
+        <v>1521</v>
+      </c>
+      <c r="B4" t="s">
+        <v>1526</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A5" t="s">
+        <v>1522</v>
+      </c>
+      <c r="B5" t="s">
+        <v>1527</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A6" t="s">
+        <v>1523</v>
+      </c>
+      <c r="B6" t="s">
+        <v>1534</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A7" t="s">
+        <v>1524</v>
+      </c>
+      <c r="B7" t="s">
+        <v>1535</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A8" t="s">
+        <v>1529</v>
+      </c>
+      <c r="B8" t="s">
+        <v>1538</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A9" t="s">
+        <v>1337</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>1541</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A10" t="s">
+        <v>1532</v>
+      </c>
+      <c r="B10" t="s">
+        <v>1543</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A11" t="s">
+        <v>1533</v>
+      </c>
+      <c r="B11" t="s">
+        <v>1544</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A12" t="s">
+        <v>1539</v>
+      </c>
+      <c r="B12" t="s">
+        <v>1550</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A13" t="s">
+        <v>1547</v>
+      </c>
+      <c r="B13" t="s">
+        <v>1552</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A14" t="s">
+        <v>1551</v>
+      </c>
+      <c r="B14" t="s">
+        <v>1553</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A15" t="s">
+        <v>1558</v>
+      </c>
+      <c r="B15" t="s">
+        <v>1572</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A16" t="s">
+        <v>1559</v>
+      </c>
+      <c r="B16" t="s">
+        <v>1576</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A17" t="s">
+        <v>1563</v>
+      </c>
+      <c r="B17" t="s">
+        <v>1580</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A18" t="s">
+        <v>1564</v>
+      </c>
+      <c r="B18" t="s">
+        <v>1581</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A19" t="s">
+        <v>1566</v>
+      </c>
+      <c r="B19" t="s">
+        <v>1582</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A20" t="s">
+        <v>1569</v>
+      </c>
+      <c r="B20" t="s">
+        <v>1585</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A21" t="s">
+        <v>1579</v>
+      </c>
+      <c r="B21" t="s">
+        <v>1603</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A22" t="s">
+        <v>1588</v>
+      </c>
+      <c r="B22" t="s">
+        <v>1634</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A23" t="s">
+        <v>1589</v>
+      </c>
+      <c r="B23" t="s">
+        <v>1635</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A24" t="s">
+        <v>1593</v>
+      </c>
+      <c r="B24" t="s">
+        <v>1659</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A25" t="s">
+        <v>1594</v>
+      </c>
+      <c r="B25" t="s">
+        <v>1661</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A26" t="s">
+        <v>1601</v>
+      </c>
+      <c r="B26" t="s">
+        <v>1705</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A27" t="s">
+        <v>1602</v>
+      </c>
+      <c r="B27" t="s">
+        <v>1714</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A28" t="s">
+        <v>1606</v>
+      </c>
+      <c r="B28" t="s">
+        <v>1716</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A29" t="s">
+        <v>1611</v>
+      </c>
+      <c r="B29" t="s">
+        <v>1721</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A30" t="s">
+        <v>1625</v>
+      </c>
+      <c r="B30" t="s">
+        <v>1728</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A31" t="s">
+        <v>1629</v>
+      </c>
+      <c r="B31" t="s">
+        <v>1747</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A32" t="s">
+        <v>1638</v>
+      </c>
+      <c r="B32" t="s">
+        <v>1754</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A33" t="s">
+        <v>1640</v>
+      </c>
+      <c r="B33" t="s">
+        <v>1767</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A34" t="s">
+        <v>1643</v>
+      </c>
+      <c r="B34" t="s">
+        <v>1801</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A35" t="s">
+        <v>1645</v>
+      </c>
+      <c r="B35" t="s">
+        <v>1805</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A36" t="s">
+        <v>1655</v>
+      </c>
+      <c r="B36" t="s">
+        <v>1828</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A37" t="s">
+        <v>1335</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A38" t="s">
+        <v>1665</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A39" t="s">
+        <v>1671</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A40" t="s">
+        <v>1692</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A41" t="s">
+        <v>1735</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A42" t="s">
+        <v>1739</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A43" t="s">
+        <v>1743</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A44" t="s">
+        <v>1744</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A45" t="s">
+        <v>1541</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A46" t="s">
+        <v>1758</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A47" t="s">
+        <v>1759</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A48" t="s">
+        <v>1766</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A49" t="s">
+        <v>1771</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A50" t="s">
+        <v>1779</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A51" t="s">
+        <v>1783</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A52" t="s">
+        <v>1788</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A53" t="s">
+        <v>1790</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A54" t="s">
+        <v>1796</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A55" t="s">
+        <v>1820</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A56" t="s">
+        <v>1825</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A57" t="s">
+        <v>1828</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A58" t="s">
+        <v>1850</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A59" t="s">
+        <v>1871</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A60" t="s">
+        <v>1877</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D1BC60D8-44F3-478D-BCC0-4752624457AE}">
   <dimension ref="A1:F24"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
@@ -10625,7 +13273,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84E3BB0D-5578-4069-B1C9-C3864EB2A429}">
   <dimension ref="A1:G553"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
@@ -20050,7 +22698,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{494C60D6-2426-4CE0-9CA4-43EAAA3DD51B}">
   <dimension ref="A1:F26"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
@@ -20589,7 +23237,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32F3CD10-C054-4484-ABE2-D426F834FC22}">
   <dimension ref="A1:E67"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
@@ -21545,7 +24193,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{931309AC-3B5D-4169-8BD3-83BC320E154C}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>

--- a/data/Fate-Spreadsheet.xlsx
+++ b/data/Fate-Spreadsheet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pixel\Documents\Projects\Fate-Wiki\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6975E217-4937-4962-9F68-2043D1A69F68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B248AF4-BF86-482E-9932-96EE6A1D4728}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{B05E798F-9EF6-4508-A0A4-311D06661AED}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" firstSheet="2" activeTab="5" xr2:uid="{B05E798F-9EF6-4508-A0A4-311D06661AED}"/>
   </bookViews>
   <sheets>
     <sheet name="Servants" sheetId="1" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4216" uniqueCount="1884">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4219" uniqueCount="1886">
   <si>
     <t>servant_id</t>
   </si>
@@ -5697,6 +5697,12 @@
   </si>
   <si>
     <t>Kingmaking,VP Gain,Power Reduction</t>
+  </si>
+  <si>
+    <t>has_attack_cards</t>
+  </si>
+  <si>
+    <t>has_abilities</t>
   </si>
 </sst>
 </file>
@@ -23239,16 +23245,17 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32F3CD10-C054-4484-ABE2-D426F834FC22}">
-  <dimension ref="A1:E67"/>
+  <dimension ref="A1:G67"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="13.3984375" customWidth="1"/>
     <col min="2" max="3" width="26" customWidth="1"/>
-    <col min="4" max="4" width="20.46484375" customWidth="1"/>
-    <col min="5" max="5" width="14.6640625" customWidth="1"/>
+    <col min="4" max="5" width="20.46484375" customWidth="1"/>
+    <col min="6" max="6" width="14.6640625" customWidth="1"/>
+    <col min="7" max="7" width="11.46484375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>1263</v>
       </c>
@@ -23261,9 +23268,17 @@
       <c r="D1" s="1" t="s">
         <v>1331</v>
       </c>
-      <c r="E1" s="1"/>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="E1" s="1" t="s">
+        <v>1885</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>1884</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>1466</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>1264</v>
       </c>
@@ -23276,8 +23291,11 @@
       <c r="D2" t="s">
         <v>1333</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>1265</v>
       </c>
@@ -23290,8 +23308,14 @@
       <c r="D3" t="s">
         <v>1334</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="E3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>1266</v>
       </c>
@@ -23304,8 +23328,11 @@
       <c r="D4" t="s">
         <v>1335</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="E4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>1267</v>
       </c>
@@ -23318,8 +23345,11 @@
       <c r="D5" t="s">
         <v>1336</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="E5" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>1268</v>
       </c>
@@ -23332,8 +23362,11 @@
       <c r="D6" t="s">
         <v>1335</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="E6" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>1269</v>
       </c>
@@ -23346,8 +23379,11 @@
       <c r="D7" t="s">
         <v>1337</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F7" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>1270</v>
       </c>
@@ -23360,8 +23396,11 @@
       <c r="D8" t="s">
         <v>1337</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="E8" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>1271</v>
       </c>
@@ -23374,8 +23413,11 @@
       <c r="D9" t="s">
         <v>1335</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="E9" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>1272</v>
       </c>
@@ -23389,7 +23431,7 @@
         <v>1337</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>1273</v>
       </c>
@@ -23402,8 +23444,14 @@
       <c r="D11" t="s">
         <v>1337</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="E11" t="b">
+        <v>1</v>
+      </c>
+      <c r="F11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>1274</v>
       </c>
@@ -23416,8 +23464,11 @@
       <c r="D12" t="s">
         <v>1337</v>
       </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="E12" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>1275</v>
       </c>
@@ -23431,7 +23482,7 @@
         <v>1333</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>1276</v>
       </c>
@@ -23444,8 +23495,11 @@
       <c r="D14" t="s">
         <v>1333</v>
       </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F14" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>1277</v>
       </c>
@@ -23459,7 +23513,7 @@
         <v>1335</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>1278</v>
       </c>
@@ -23472,8 +23526,14 @@
       <c r="D16" t="s">
         <v>1337</v>
       </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E16" t="b">
+        <v>1</v>
+      </c>
+      <c r="F16" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>1279</v>
       </c>
@@ -23486,8 +23546,11 @@
       <c r="D17" t="s">
         <v>1335</v>
       </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E17" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>1280</v>
       </c>
@@ -23501,7 +23564,7 @@
         <v>1334</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
         <v>1281</v>
       </c>
@@ -23514,8 +23577,11 @@
       <c r="D19" t="s">
         <v>1333</v>
       </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="F19" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>1282</v>
       </c>
@@ -23528,8 +23594,11 @@
       <c r="D20" t="s">
         <v>1335</v>
       </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E20" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
         <v>1283</v>
       </c>
@@ -23542,8 +23611,11 @@
       <c r="D21" t="s">
         <v>1333</v>
       </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E21" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
         <v>1284</v>
       </c>
@@ -23556,8 +23628,11 @@
       <c r="D22" t="s">
         <v>1334</v>
       </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="F22" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
         <v>1285</v>
       </c>
@@ -23570,8 +23645,11 @@
       <c r="D23" t="s">
         <v>1337</v>
       </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E23" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
         <v>1286</v>
       </c>
@@ -23584,8 +23662,11 @@
       <c r="D24" t="s">
         <v>1333</v>
       </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E24" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
         <v>1287</v>
       </c>
@@ -23599,7 +23680,7 @@
         <v>1333</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
         <v>1288</v>
       </c>
@@ -23612,8 +23693,11 @@
       <c r="D26" t="s">
         <v>1337</v>
       </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E26" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
         <v>1289</v>
       </c>
@@ -23627,7 +23711,7 @@
         <v>1334</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
         <v>1290</v>
       </c>
@@ -23640,8 +23724,17 @@
       <c r="D28" t="s">
         <v>1333</v>
       </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E28" t="b">
+        <v>1</v>
+      </c>
+      <c r="F28" t="b">
+        <v>1</v>
+      </c>
+      <c r="G28" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
         <v>1291</v>
       </c>
@@ -23655,7 +23748,7 @@
         <v>1336</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
         <v>1292</v>
       </c>
@@ -23669,7 +23762,7 @@
         <v>1334</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
         <v>1293</v>
       </c>
@@ -23683,7 +23776,7 @@
         <v>1335</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
         <v>1294</v>
       </c>
@@ -24190,6 +24283,7 @@
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/data/Fate-Spreadsheet.xlsx
+++ b/data/Fate-Spreadsheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pixel\Documents\Projects\Fate-Wiki\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B248AF4-BF86-482E-9932-96EE6A1D4728}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21F92DEF-E213-4986-8D7C-584A7B922464}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" firstSheet="2" activeTab="5" xr2:uid="{B05E798F-9EF6-4508-A0A4-311D06661AED}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4219" uniqueCount="1886">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4220" uniqueCount="1887">
   <si>
     <t>servant_id</t>
   </si>
@@ -5703,6 +5703,9 @@
   </si>
   <si>
     <t>has_abilities</t>
+  </si>
+  <si>
+    <t>NOT FINISHED</t>
   </si>
 </sst>
 </file>
@@ -23747,6 +23750,12 @@
       <c r="D29" t="s">
         <v>1336</v>
       </c>
+      <c r="E29" t="b">
+        <v>1</v>
+      </c>
+      <c r="F29" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
@@ -23789,8 +23798,11 @@
       <c r="D32" t="s">
         <v>1333</v>
       </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E32" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
         <v>1295</v>
       </c>
@@ -23803,8 +23815,14 @@
       <c r="D33" t="s">
         <v>1333</v>
       </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E33" t="b">
+        <v>1</v>
+      </c>
+      <c r="F33" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
         <v>1296</v>
       </c>
@@ -23817,8 +23835,11 @@
       <c r="D34" t="s">
         <v>1337</v>
       </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="F34" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A35" t="s">
         <v>1297</v>
       </c>
@@ -23832,7 +23853,7 @@
         <v>1335</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A36" t="s">
         <v>1298</v>
       </c>
@@ -23845,8 +23866,11 @@
       <c r="D36" t="s">
         <v>1333</v>
       </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="F36" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A37" t="s">
         <v>1299</v>
       </c>
@@ -23859,8 +23883,11 @@
       <c r="D37" t="s">
         <v>1334</v>
       </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E37" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A38" t="s">
         <v>1300</v>
       </c>
@@ -23873,8 +23900,11 @@
       <c r="D38" t="s">
         <v>1333</v>
       </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E38" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A39" t="s">
         <v>1301</v>
       </c>
@@ -23888,7 +23918,7 @@
         <v>1373</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A40" t="s">
         <v>1302</v>
       </c>
@@ -23901,8 +23931,11 @@
       <c r="D40" t="s">
         <v>1334</v>
       </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="G40" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A41" t="s">
         <v>1303</v>
       </c>
@@ -23915,8 +23948,11 @@
       <c r="D41" t="s">
         <v>1337</v>
       </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="F41" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A42" t="s">
         <v>1304</v>
       </c>
@@ -23929,8 +23965,14 @@
       <c r="D42" t="s">
         <v>1373</v>
       </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E42" t="b">
+        <v>1</v>
+      </c>
+      <c r="G42" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A43" t="s">
         <v>1305</v>
       </c>
@@ -23944,7 +23986,7 @@
         <v>1335</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A44" t="s">
         <v>1306</v>
       </c>
@@ -23957,8 +23999,14 @@
       <c r="D44" t="s">
         <v>1334</v>
       </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E44" t="b">
+        <v>1</v>
+      </c>
+      <c r="G44" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A45" t="s">
         <v>1307</v>
       </c>
@@ -23971,8 +24019,14 @@
       <c r="D45" t="s">
         <v>1333</v>
       </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E45" t="b">
+        <v>1</v>
+      </c>
+      <c r="G45" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A46" t="s">
         <v>1308</v>
       </c>
@@ -23985,8 +24039,17 @@
       <c r="D46" t="s">
         <v>1333</v>
       </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E46" t="b">
+        <v>1</v>
+      </c>
+      <c r="F46" t="b">
+        <v>1</v>
+      </c>
+      <c r="G46" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A47" t="s">
         <v>1309</v>
       </c>
@@ -23999,8 +24062,11 @@
       <c r="D47" t="s">
         <v>1333</v>
       </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E47" t="s">
+        <v>1886</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A48" t="s">
         <v>1310</v>
       </c>
@@ -24013,8 +24079,17 @@
       <c r="D48" t="s">
         <v>1333</v>
       </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E48" t="b">
+        <v>1</v>
+      </c>
+      <c r="F48" t="b">
+        <v>1</v>
+      </c>
+      <c r="G48" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A49" t="s">
         <v>1311</v>
       </c>
@@ -24027,8 +24102,11 @@
       <c r="D49" t="s">
         <v>1333</v>
       </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="F49" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A50" t="s">
         <v>1312</v>
       </c>
@@ -24041,8 +24119,11 @@
       <c r="D50" t="s">
         <v>1336</v>
       </c>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="F50" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A51" t="s">
         <v>1313</v>
       </c>
@@ -24055,8 +24136,11 @@
       <c r="D51" t="s">
         <v>1335</v>
       </c>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E51" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A52" t="s">
         <v>1314</v>
       </c>
@@ -24069,8 +24153,11 @@
       <c r="D52" t="s">
         <v>1334</v>
       </c>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="F52" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A53" t="s">
         <v>1315</v>
       </c>
@@ -24084,7 +24171,7 @@
         <v>1334</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A54" t="s">
         <v>1316</v>
       </c>
@@ -24098,7 +24185,7 @@
         <v>1373</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A55" t="s">
         <v>1317</v>
       </c>
@@ -24112,7 +24199,7 @@
         <v>1333</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A56" t="s">
         <v>1318</v>
       </c>
@@ -24126,7 +24213,7 @@
         <v>1333</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A57" t="s">
         <v>1319</v>
       </c>
@@ -24140,7 +24227,7 @@
         <v>1333</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A58" t="s">
         <v>1320</v>
       </c>
@@ -24154,7 +24241,7 @@
         <v>1334</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A59" t="s">
         <v>1321</v>
       </c>
@@ -24168,7 +24255,7 @@
         <v>1334</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A60" t="s">
         <v>1322</v>
       </c>
@@ -24182,7 +24269,7 @@
         <v>1334</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A61" t="s">
         <v>1323</v>
       </c>
@@ -24196,7 +24283,7 @@
         <v>1334</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A62" t="s">
         <v>1324</v>
       </c>
@@ -24210,7 +24297,7 @@
         <v>1333</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A63" t="s">
         <v>1325</v>
       </c>
@@ -24224,7 +24311,7 @@
         <v>1333</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A64" t="s">
         <v>1326</v>
       </c>

--- a/data/Fate-Spreadsheet.xlsx
+++ b/data/Fate-Spreadsheet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pixel\Documents\Projects\Fate-Wiki\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21F92DEF-E213-4986-8D7C-584A7B922464}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FEAF3F0-9A7B-4665-AFC7-7E30F826BAAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" firstSheet="2" activeTab="5" xr2:uid="{B05E798F-9EF6-4508-A0A4-311D06661AED}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" firstSheet="2" activeTab="2" xr2:uid="{B05E798F-9EF6-4508-A0A4-311D06661AED}"/>
   </bookViews>
   <sheets>
     <sheet name="Servants" sheetId="1" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4220" uniqueCount="1887">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4218" uniqueCount="1885">
   <si>
     <t>servant_id</t>
   </si>
@@ -5699,13 +5699,7 @@
     <t>Kingmaking,VP Gain,Power Reduction</t>
   </si>
   <si>
-    <t>has_attack_cards</t>
-  </si>
-  <si>
     <t>has_abilities</t>
-  </si>
-  <si>
-    <t>NOT FINISHED</t>
   </si>
 </sst>
 </file>
@@ -23248,17 +23242,16 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32F3CD10-C054-4484-ABE2-D426F834FC22}">
-  <dimension ref="A1:G67"/>
+  <dimension ref="A1:F67"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="13.3984375" customWidth="1"/>
     <col min="2" max="3" width="26" customWidth="1"/>
     <col min="4" max="5" width="20.46484375" customWidth="1"/>
-    <col min="6" max="6" width="14.6640625" customWidth="1"/>
-    <col min="7" max="7" width="11.46484375" customWidth="1"/>
+    <col min="6" max="6" width="11.46484375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>1263</v>
       </c>
@@ -23272,16 +23265,13 @@
         <v>1331</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>1885</v>
+        <v>1884</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>1884</v>
-      </c>
-      <c r="G1" s="1" t="s">
         <v>1466</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>1264</v>
       </c>
@@ -23294,11 +23284,11 @@
       <c r="D2" t="s">
         <v>1333</v>
       </c>
-      <c r="F2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="E2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>1265</v>
       </c>
@@ -23314,11 +23304,8 @@
       <c r="E3" t="b">
         <v>1</v>
       </c>
-      <c r="F3" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.45">
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>1266</v>
       </c>
@@ -23335,7 +23322,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>1267</v>
       </c>
@@ -23352,7 +23339,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>1268</v>
       </c>
@@ -23369,7 +23356,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>1269</v>
       </c>
@@ -23382,11 +23369,11 @@
       <c r="D7" t="s">
         <v>1337</v>
       </c>
-      <c r="F7" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="E7" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>1270</v>
       </c>
@@ -23403,7 +23390,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>1271</v>
       </c>
@@ -23420,7 +23407,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>1272</v>
       </c>
@@ -23434,7 +23421,7 @@
         <v>1337</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>1273</v>
       </c>
@@ -23450,11 +23437,8 @@
       <c r="E11" t="b">
         <v>1</v>
       </c>
-      <c r="F11" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.45">
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>1274</v>
       </c>
@@ -23471,7 +23455,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>1275</v>
       </c>
@@ -23485,7 +23469,7 @@
         <v>1333</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>1276</v>
       </c>
@@ -23498,11 +23482,11 @@
       <c r="D14" t="s">
         <v>1333</v>
       </c>
-      <c r="F14" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="E14" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>1277</v>
       </c>
@@ -23516,7 +23500,7 @@
         <v>1335</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>1278</v>
       </c>
@@ -23532,11 +23516,8 @@
       <c r="E16" t="b">
         <v>1</v>
       </c>
-      <c r="F16" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.45">
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>1279</v>
       </c>
@@ -23553,7 +23534,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>1280</v>
       </c>
@@ -23567,7 +23548,7 @@
         <v>1334</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
         <v>1281</v>
       </c>
@@ -23580,11 +23561,11 @@
       <c r="D19" t="s">
         <v>1333</v>
       </c>
-      <c r="F19" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="E19" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>1282</v>
       </c>
@@ -23601,7 +23582,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
         <v>1283</v>
       </c>
@@ -23618,7 +23599,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
         <v>1284</v>
       </c>
@@ -23631,11 +23612,11 @@
       <c r="D22" t="s">
         <v>1334</v>
       </c>
-      <c r="F22" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="E22" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
         <v>1285</v>
       </c>
@@ -23652,7 +23633,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
         <v>1286</v>
       </c>
@@ -23669,7 +23650,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
         <v>1287</v>
       </c>
@@ -23683,7 +23664,7 @@
         <v>1333</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
         <v>1288</v>
       </c>
@@ -23700,7 +23681,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
         <v>1289</v>
       </c>
@@ -23714,7 +23695,7 @@
         <v>1334</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
         <v>1290</v>
       </c>
@@ -23730,14 +23711,8 @@
       <c r="E28" t="b">
         <v>1</v>
       </c>
-      <c r="F28" t="b">
-        <v>1</v>
-      </c>
-      <c r="G28" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.45">
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
         <v>1291</v>
       </c>
@@ -23753,11 +23728,8 @@
       <c r="E29" t="b">
         <v>1</v>
       </c>
-      <c r="F29" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.45">
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
         <v>1292</v>
       </c>
@@ -23771,7 +23743,7 @@
         <v>1334</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
         <v>1293</v>
       </c>
@@ -23785,7 +23757,7 @@
         <v>1335</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
         <v>1294</v>
       </c>
@@ -23802,7 +23774,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
         <v>1295</v>
       </c>
@@ -23818,11 +23790,8 @@
       <c r="E33" t="b">
         <v>1</v>
       </c>
-      <c r="F33" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.45">
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
         <v>1296</v>
       </c>
@@ -23835,11 +23804,11 @@
       <c r="D34" t="s">
         <v>1337</v>
       </c>
-      <c r="F34" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="E34" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A35" t="s">
         <v>1297</v>
       </c>
@@ -23853,7 +23822,7 @@
         <v>1335</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A36" t="s">
         <v>1298</v>
       </c>
@@ -23866,11 +23835,11 @@
       <c r="D36" t="s">
         <v>1333</v>
       </c>
-      <c r="F36" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="E36" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A37" t="s">
         <v>1299</v>
       </c>
@@ -23887,7 +23856,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A38" t="s">
         <v>1300</v>
       </c>
@@ -23904,7 +23873,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A39" t="s">
         <v>1301</v>
       </c>
@@ -23918,7 +23887,7 @@
         <v>1373</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A40" t="s">
         <v>1302</v>
       </c>
@@ -23931,11 +23900,8 @@
       <c r="D40" t="s">
         <v>1334</v>
       </c>
-      <c r="G40" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.45">
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A41" t="s">
         <v>1303</v>
       </c>
@@ -23948,11 +23914,11 @@
       <c r="D41" t="s">
         <v>1337</v>
       </c>
-      <c r="F41" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="E41" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A42" t="s">
         <v>1304</v>
       </c>
@@ -23968,11 +23934,8 @@
       <c r="E42" t="b">
         <v>1</v>
       </c>
-      <c r="G42" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.45">
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A43" t="s">
         <v>1305</v>
       </c>
@@ -23986,7 +23949,7 @@
         <v>1335</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A44" t="s">
         <v>1306</v>
       </c>
@@ -24002,11 +23965,8 @@
       <c r="E44" t="b">
         <v>1</v>
       </c>
-      <c r="G44" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.45">
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A45" t="s">
         <v>1307</v>
       </c>
@@ -24022,11 +23982,8 @@
       <c r="E45" t="b">
         <v>1</v>
       </c>
-      <c r="G45" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.45">
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A46" t="s">
         <v>1308</v>
       </c>
@@ -24042,14 +23999,8 @@
       <c r="E46" t="b">
         <v>1</v>
       </c>
-      <c r="F46" t="b">
-        <v>1</v>
-      </c>
-      <c r="G46" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.45">
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A47" t="s">
         <v>1309</v>
       </c>
@@ -24062,11 +24013,11 @@
       <c r="D47" t="s">
         <v>1333</v>
       </c>
-      <c r="E47" t="s">
-        <v>1886</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="E47" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A48" t="s">
         <v>1310</v>
       </c>
@@ -24082,14 +24033,8 @@
       <c r="E48" t="b">
         <v>1</v>
       </c>
-      <c r="F48" t="b">
-        <v>1</v>
-      </c>
-      <c r="G48" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.45">
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A49" t="s">
         <v>1311</v>
       </c>
@@ -24102,11 +24047,11 @@
       <c r="D49" t="s">
         <v>1333</v>
       </c>
-      <c r="F49" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="E49" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A50" t="s">
         <v>1312</v>
       </c>
@@ -24119,11 +24064,11 @@
       <c r="D50" t="s">
         <v>1336</v>
       </c>
-      <c r="F50" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="E50" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A51" t="s">
         <v>1313</v>
       </c>
@@ -24140,7 +24085,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A52" t="s">
         <v>1314</v>
       </c>
@@ -24153,11 +24098,11 @@
       <c r="D52" t="s">
         <v>1334</v>
       </c>
-      <c r="F52" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="E52" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A53" t="s">
         <v>1315</v>
       </c>
@@ -24171,7 +24116,7 @@
         <v>1334</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A54" t="s">
         <v>1316</v>
       </c>
@@ -24185,7 +24130,7 @@
         <v>1373</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A55" t="s">
         <v>1317</v>
       </c>
@@ -24199,7 +24144,7 @@
         <v>1333</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A56" t="s">
         <v>1318</v>
       </c>
@@ -24213,7 +24158,7 @@
         <v>1333</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A57" t="s">
         <v>1319</v>
       </c>
@@ -24227,7 +24172,7 @@
         <v>1333</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A58" t="s">
         <v>1320</v>
       </c>
@@ -24241,7 +24186,7 @@
         <v>1334</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A59" t="s">
         <v>1321</v>
       </c>
@@ -24255,7 +24200,7 @@
         <v>1334</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A60" t="s">
         <v>1322</v>
       </c>
@@ -24269,7 +24214,7 @@
         <v>1334</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A61" t="s">
         <v>1323</v>
       </c>
@@ -24283,7 +24228,7 @@
         <v>1334</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A62" t="s">
         <v>1324</v>
       </c>
@@ -24297,7 +24242,7 @@
         <v>1333</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A63" t="s">
         <v>1325</v>
       </c>
@@ -24311,7 +24256,7 @@
         <v>1333</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A64" t="s">
         <v>1326</v>
       </c>

--- a/data/Fate-Spreadsheet.xlsx
+++ b/data/Fate-Spreadsheet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pixel\Documents\Projects\Fate-Wiki\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FEAF3F0-9A7B-4665-AFC7-7E30F826BAAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E5DAD16-3B98-4A73-8020-619EA4DDD7CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" firstSheet="2" activeTab="2" xr2:uid="{B05E798F-9EF6-4508-A0A4-311D06661AED}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" firstSheet="1" activeTab="1" xr2:uid="{B05E798F-9EF6-4508-A0A4-311D06661AED}"/>
   </bookViews>
   <sheets>
     <sheet name="Servants" sheetId="1" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4218" uniqueCount="1885">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4219" uniqueCount="1885">
   <si>
     <t>servant_id</t>
   </si>
@@ -12426,7 +12426,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{445C98DF-AF88-42FF-A8A5-2AB8831F51CC}">
-  <dimension ref="A1:B60"/>
+  <dimension ref="A1:B61"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="22.1328125" customWidth="1"/>
@@ -12839,6 +12839,11 @@
     <row r="60" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A60" t="s">
         <v>1877</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A61" t="s">
+        <v>1534</v>
       </c>
     </row>
   </sheetData>

--- a/data/Fate-Spreadsheet.xlsx
+++ b/data/Fate-Spreadsheet.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pixel\Documents\Projects\Fate-Wiki\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Important\Python\Fate-Wiki\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E5DAD16-3B98-4A73-8020-619EA4DDD7CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{001A512E-D5B4-4085-BE1C-40AEE1E14FDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" firstSheet="1" activeTab="1" xr2:uid="{B05E798F-9EF6-4508-A0A4-311D06661AED}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="1" activeTab="5" xr2:uid="{B05E798F-9EF6-4508-A0A4-311D06661AED}"/>
   </bookViews>
   <sheets>
     <sheet name="Servants" sheetId="1" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4219" uniqueCount="1885">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4226" uniqueCount="1886">
   <si>
     <t>servant_id</t>
   </si>
@@ -5700,6 +5700,9 @@
   </si>
   <si>
     <t>has_abilities</t>
+  </si>
+  <si>
+    <t>NEED TO FIX PICS</t>
   </si>
 </sst>
 </file>
@@ -6089,25 +6092,25 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E33D7ECC-1EAA-4A40-B4DA-A93E54CBC8B5}">
   <dimension ref="A1:P185"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="3" width="22" customWidth="1"/>
-    <col min="4" max="4" width="12.59765625" customWidth="1"/>
-    <col min="5" max="5" width="11.265625" customWidth="1"/>
-    <col min="6" max="6" width="15.59765625" customWidth="1"/>
-    <col min="7" max="7" width="13.73046875" style="2" customWidth="1"/>
-    <col min="8" max="8" width="16.59765625" style="2" customWidth="1"/>
-    <col min="9" max="9" width="17.59765625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="12.5703125" customWidth="1"/>
+    <col min="5" max="5" width="11.28515625" customWidth="1"/>
+    <col min="6" max="6" width="15.5703125" customWidth="1"/>
+    <col min="7" max="7" width="13.7109375" style="2" customWidth="1"/>
+    <col min="8" max="8" width="16.5703125" style="2" customWidth="1"/>
+    <col min="9" max="9" width="17.5703125" style="2" customWidth="1"/>
     <col min="10" max="10" width="97" style="2" customWidth="1"/>
-    <col min="11" max="11" width="12.59765625" customWidth="1"/>
-    <col min="12" max="12" width="10.9296875" customWidth="1"/>
-    <col min="13" max="13" width="45.6640625" customWidth="1"/>
-    <col min="14" max="14" width="41.33203125" customWidth="1"/>
-    <col min="15" max="15" width="11.796875" customWidth="1"/>
-    <col min="16" max="16" width="18.19921875" customWidth="1"/>
+    <col min="11" max="11" width="12.5703125" customWidth="1"/>
+    <col min="12" max="12" width="11" customWidth="1"/>
+    <col min="13" max="13" width="45.7109375" customWidth="1"/>
+    <col min="14" max="14" width="41.28515625" customWidth="1"/>
+    <col min="15" max="15" width="11.85546875" customWidth="1"/>
+    <col min="16" max="16" width="18.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -6153,7 +6156,7 @@
       <c r="O1" s="3"/>
       <c r="P1" s="3"/>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -6188,7 +6191,7 @@
         <v>1510</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>111</v>
       </c>
@@ -6223,7 +6226,7 @@
         <v>1512</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>112</v>
       </c>
@@ -6255,7 +6258,7 @@
         <v>1518</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>113</v>
       </c>
@@ -6290,7 +6293,7 @@
         <v>1527</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>114</v>
       </c>
@@ -6325,7 +6328,7 @@
         <v>1525</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>115</v>
       </c>
@@ -6360,7 +6363,7 @@
         <v>1536</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>116</v>
       </c>
@@ -6395,7 +6398,7 @@
         <v>1538</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>117</v>
       </c>
@@ -6427,7 +6430,7 @@
         <v>1541</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>118</v>
       </c>
@@ -6462,7 +6465,7 @@
         <v>1542</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>119</v>
       </c>
@@ -6497,7 +6500,7 @@
         <v>1546</v>
       </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>120</v>
       </c>
@@ -6532,7 +6535,7 @@
         <v>1549</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>121</v>
       </c>
@@ -6564,7 +6567,7 @@
         <v>1555</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>122</v>
       </c>
@@ -6599,7 +6602,7 @@
         <v>1557</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>123</v>
       </c>
@@ -6634,7 +6637,7 @@
         <v>1561</v>
       </c>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>124</v>
       </c>
@@ -6669,7 +6672,7 @@
         <v>1565</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>125</v>
       </c>
@@ -6704,7 +6707,7 @@
         <v>1510</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>126</v>
       </c>
@@ -6742,7 +6745,7 @@
         <v>1570</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>127</v>
       </c>
@@ -6777,7 +6780,7 @@
         <v>1573</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>128</v>
       </c>
@@ -6809,7 +6812,7 @@
         <v>1575</v>
       </c>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>129</v>
       </c>
@@ -6844,7 +6847,7 @@
         <v>1577</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>130</v>
       </c>
@@ -6882,7 +6885,7 @@
         <v>1583</v>
       </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>131</v>
       </c>
@@ -6917,7 +6920,7 @@
         <v>1584</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>132</v>
       </c>
@@ -6952,7 +6955,7 @@
         <v>1586</v>
       </c>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>264</v>
       </c>
@@ -6987,7 +6990,7 @@
         <v>1590</v>
       </c>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>323</v>
       </c>
@@ -7019,7 +7022,7 @@
         <v>1592</v>
       </c>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>329</v>
       </c>
@@ -7054,7 +7057,7 @@
         <v>1596</v>
       </c>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>330</v>
       </c>
@@ -7086,7 +7089,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>331</v>
       </c>
@@ -7121,7 +7124,7 @@
         <v>1599</v>
       </c>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>332</v>
       </c>
@@ -7153,7 +7156,7 @@
         <v>1518</v>
       </c>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>333</v>
       </c>
@@ -7191,7 +7194,7 @@
         <v>1605</v>
       </c>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>334</v>
       </c>
@@ -7226,7 +7229,7 @@
         <v>1607</v>
       </c>
     </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>335</v>
       </c>
@@ -7261,7 +7264,7 @@
         <v>1609</v>
       </c>
     </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>336</v>
       </c>
@@ -7296,7 +7299,7 @@
         <v>1612</v>
       </c>
     </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>337</v>
       </c>
@@ -7331,7 +7334,7 @@
         <v>1614</v>
       </c>
     </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>338</v>
       </c>
@@ -7363,7 +7366,7 @@
         <v>1526</v>
       </c>
     </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>339</v>
       </c>
@@ -7395,7 +7398,7 @@
         <v>1617</v>
       </c>
     </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>340</v>
       </c>
@@ -7430,7 +7433,7 @@
         <v>1518</v>
       </c>
     </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>341</v>
       </c>
@@ -7462,7 +7465,7 @@
         <v>1620</v>
       </c>
     </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>342</v>
       </c>
@@ -7497,7 +7500,7 @@
         <v>1622</v>
       </c>
     </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>343</v>
       </c>
@@ -7529,7 +7532,7 @@
         <v>1624</v>
       </c>
     </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>344</v>
       </c>
@@ -7564,7 +7567,7 @@
         <v>1627</v>
       </c>
     </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>345</v>
       </c>
@@ -7599,7 +7602,7 @@
         <v>1630</v>
       </c>
     </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>346</v>
       </c>
@@ -7634,7 +7637,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>347</v>
       </c>
@@ -7669,7 +7672,7 @@
         <v>1633</v>
       </c>
     </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>348</v>
       </c>
@@ -7709,7 +7712,7 @@
       <c r="O46" s="2"/>
       <c r="P46" s="2"/>
     </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>349</v>
       </c>
@@ -7744,7 +7747,7 @@
         <v>1561</v>
       </c>
     </row>
-    <row r="48" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>466</v>
       </c>
@@ -7779,7 +7782,7 @@
         <v>1642</v>
       </c>
     </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>271</v>
       </c>
@@ -7814,7 +7817,7 @@
         <v>1510</v>
       </c>
     </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>476</v>
       </c>
@@ -7846,7 +7849,7 @@
         <v>1646</v>
       </c>
     </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>477</v>
       </c>
@@ -7878,7 +7881,7 @@
         <v>1648</v>
       </c>
     </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>478</v>
       </c>
@@ -7913,7 +7916,7 @@
         <v>1510</v>
       </c>
     </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>479</v>
       </c>
@@ -7945,7 +7948,7 @@
         <v>1651</v>
       </c>
     </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>480</v>
       </c>
@@ -7980,7 +7983,7 @@
         <v>1550</v>
       </c>
     </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="55" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>481</v>
       </c>
@@ -8015,7 +8018,7 @@
         <v>1543</v>
       </c>
     </row>
-    <row r="56" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>482</v>
       </c>
@@ -8050,7 +8053,7 @@
         <v>1656</v>
       </c>
     </row>
-    <row r="57" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>483</v>
       </c>
@@ -8082,7 +8085,7 @@
         <v>1658</v>
       </c>
     </row>
-    <row r="58" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="58" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>484</v>
       </c>
@@ -8117,7 +8120,7 @@
         <v>1662</v>
       </c>
     </row>
-    <row r="59" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="59" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>485</v>
       </c>
@@ -8149,7 +8152,7 @@
         <v>1543</v>
       </c>
     </row>
-    <row r="60" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="60" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>486</v>
       </c>
@@ -8181,7 +8184,7 @@
         <v>1666</v>
       </c>
     </row>
-    <row r="61" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>487</v>
       </c>
@@ -8216,7 +8219,7 @@
         <v>1609</v>
       </c>
     </row>
-    <row r="62" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="62" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>488</v>
       </c>
@@ -8251,7 +8254,7 @@
         <v>1651</v>
       </c>
     </row>
-    <row r="63" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="63" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>489</v>
       </c>
@@ -8286,7 +8289,7 @@
         <v>1670</v>
       </c>
     </row>
-    <row r="64" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="64" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>490</v>
       </c>
@@ -8321,7 +8324,7 @@
         <v>1673</v>
       </c>
     </row>
-    <row r="65" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="65" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>491</v>
       </c>
@@ -8356,7 +8359,7 @@
         <v>1675</v>
       </c>
     </row>
-    <row r="66" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="66" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>492</v>
       </c>
@@ -8388,7 +8391,7 @@
         <v>1677</v>
       </c>
     </row>
-    <row r="67" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="67" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>493</v>
       </c>
@@ -8420,7 +8423,7 @@
         <v>1679</v>
       </c>
     </row>
-    <row r="68" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="68" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>494</v>
       </c>
@@ -8455,7 +8458,7 @@
         <v>1681</v>
       </c>
     </row>
-    <row r="69" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="69" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>495</v>
       </c>
@@ -8490,7 +8493,7 @@
         <v>1683</v>
       </c>
     </row>
-    <row r="70" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="70" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>85</v>
       </c>
@@ -8525,7 +8528,7 @@
         <v>1685</v>
       </c>
     </row>
-    <row r="71" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="71" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>275</v>
       </c>
@@ -8560,7 +8563,7 @@
         <v>1687</v>
       </c>
     </row>
-    <row r="72" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="72" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>535</v>
       </c>
@@ -8595,7 +8598,7 @@
         <v>1689</v>
       </c>
     </row>
-    <row r="73" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="73" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>536</v>
       </c>
@@ -8630,7 +8633,7 @@
         <v>1552</v>
       </c>
     </row>
-    <row r="74" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="74" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>537</v>
       </c>
@@ -8662,7 +8665,7 @@
         <v>1691</v>
       </c>
     </row>
-    <row r="75" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="75" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>538</v>
       </c>
@@ -8694,7 +8697,7 @@
         <v>1694</v>
       </c>
     </row>
-    <row r="76" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="76" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>539</v>
       </c>
@@ -8726,7 +8729,7 @@
         <v>1561</v>
       </c>
     </row>
-    <row r="77" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="77" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>540</v>
       </c>
@@ -8758,7 +8761,7 @@
         <v>1697</v>
       </c>
     </row>
-    <row r="78" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="78" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>541</v>
       </c>
@@ -8793,7 +8796,7 @@
         <v>1699</v>
       </c>
     </row>
-    <row r="79" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="79" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>542</v>
       </c>
@@ -8828,7 +8831,7 @@
         <v>1701</v>
       </c>
     </row>
-    <row r="80" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="80" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>543</v>
       </c>
@@ -8863,7 +8866,7 @@
         <v>1703</v>
       </c>
     </row>
-    <row r="81" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="81" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>544</v>
       </c>
@@ -8898,7 +8901,7 @@
         <v>1704</v>
       </c>
     </row>
-    <row r="82" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="82" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>545</v>
       </c>
@@ -8930,7 +8933,7 @@
         <v>1707</v>
       </c>
     </row>
-    <row r="83" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="83" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>546</v>
       </c>
@@ -8962,7 +8965,7 @@
         <v>1709</v>
       </c>
     </row>
-    <row r="84" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="84" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>547</v>
       </c>
@@ -8997,7 +9000,7 @@
         <v>1711</v>
       </c>
     </row>
-    <row r="85" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="85" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>548</v>
       </c>
@@ -9032,7 +9035,7 @@
         <v>1713</v>
       </c>
     </row>
-    <row r="86" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="86" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>549</v>
       </c>
@@ -9064,7 +9067,7 @@
         <v>1715</v>
       </c>
     </row>
-    <row r="87" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="87" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>550</v>
       </c>
@@ -9096,7 +9099,7 @@
         <v>1718</v>
       </c>
     </row>
-    <row r="88" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="88" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>551</v>
       </c>
@@ -9131,7 +9134,7 @@
         <v>1720</v>
       </c>
     </row>
-    <row r="89" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="89" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>552</v>
       </c>
@@ -9166,7 +9169,7 @@
         <v>1527</v>
       </c>
     </row>
-    <row r="90" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="90" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>553</v>
       </c>
@@ -9201,7 +9204,7 @@
         <v>1724</v>
       </c>
     </row>
-    <row r="91" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="91" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>554</v>
       </c>
@@ -9236,7 +9239,7 @@
         <v>1726</v>
       </c>
     </row>
-    <row r="92" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="92" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>555</v>
       </c>
@@ -9271,7 +9274,7 @@
         <v>1729</v>
       </c>
     </row>
-    <row r="93" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="93" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>556</v>
       </c>
@@ -9306,7 +9309,7 @@
         <v>1585</v>
       </c>
     </row>
-    <row r="94" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="94" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>281</v>
       </c>
@@ -9338,7 +9341,7 @@
         <v>1552</v>
       </c>
     </row>
-    <row r="95" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="95" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>738</v>
       </c>
@@ -9367,7 +9370,7 @@
         <v>1733</v>
       </c>
     </row>
-    <row r="96" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="96" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>739</v>
       </c>
@@ -9402,7 +9405,7 @@
         <v>1736</v>
       </c>
     </row>
-    <row r="97" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="97" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>740</v>
       </c>
@@ -9434,7 +9437,7 @@
         <v>1738</v>
       </c>
     </row>
-    <row r="98" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="98" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>17</v>
       </c>
@@ -9466,7 +9469,7 @@
         <v>1741</v>
       </c>
     </row>
-    <row r="99" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="99" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>756</v>
       </c>
@@ -9501,7 +9504,7 @@
         <v>1582</v>
       </c>
     </row>
-    <row r="100" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="100" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>757</v>
       </c>
@@ -9539,7 +9542,7 @@
         <v>1746</v>
       </c>
     </row>
-    <row r="101" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="101" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>758</v>
       </c>
@@ -9571,7 +9574,7 @@
         <v>1749</v>
       </c>
     </row>
-    <row r="102" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="102" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>284</v>
       </c>
@@ -9603,7 +9606,7 @@
         <v>1666</v>
       </c>
     </row>
-    <row r="103" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="103" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>774</v>
       </c>
@@ -9635,7 +9638,7 @@
         <v>1751</v>
       </c>
     </row>
-    <row r="104" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="104" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>775</v>
       </c>
@@ -9667,7 +9670,7 @@
         <v>1753</v>
       </c>
     </row>
-    <row r="105" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="105" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>776</v>
       </c>
@@ -9699,7 +9702,7 @@
         <v>1756</v>
       </c>
     </row>
-    <row r="106" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="106" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>777</v>
       </c>
@@ -9731,7 +9734,7 @@
         <v>1622</v>
       </c>
     </row>
-    <row r="107" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="107" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>778</v>
       </c>
@@ -9766,7 +9769,7 @@
         <v>1761</v>
       </c>
     </row>
-    <row r="108" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="108" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>779</v>
       </c>
@@ -9801,7 +9804,7 @@
         <v>1586</v>
       </c>
     </row>
-    <row r="109" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="109" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>96</v>
       </c>
@@ -9833,7 +9836,7 @@
         <v>1764</v>
       </c>
     </row>
-    <row r="110" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="110" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>807</v>
       </c>
@@ -9868,7 +9871,7 @@
         <v>1592</v>
       </c>
     </row>
-    <row r="111" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="111" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>808</v>
       </c>
@@ -9900,7 +9903,7 @@
         <v>1769</v>
       </c>
     </row>
-    <row r="112" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="112" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>809</v>
       </c>
@@ -9935,7 +9938,7 @@
         <v>1586</v>
       </c>
     </row>
-    <row r="113" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="113" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>810</v>
       </c>
@@ -9967,7 +9970,7 @@
         <v>1773</v>
       </c>
     </row>
-    <row r="114" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="114" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>811</v>
       </c>
@@ -9999,7 +10002,7 @@
         <v>1774</v>
       </c>
     </row>
-    <row r="115" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="115" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>812</v>
       </c>
@@ -10034,7 +10037,7 @@
         <v>1776</v>
       </c>
     </row>
-    <row r="116" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="116" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>813</v>
       </c>
@@ -10069,7 +10072,7 @@
         <v>1778</v>
       </c>
     </row>
-    <row r="117" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="117" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>814</v>
       </c>
@@ -10098,7 +10101,7 @@
         <v>1780</v>
       </c>
     </row>
-    <row r="118" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="118" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>815</v>
       </c>
@@ -10133,7 +10136,7 @@
         <v>1782</v>
       </c>
     </row>
-    <row r="119" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="119" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>816</v>
       </c>
@@ -10168,7 +10171,7 @@
         <v>1785</v>
       </c>
     </row>
-    <row r="120" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="120" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>817</v>
       </c>
@@ -10203,7 +10206,7 @@
         <v>1787</v>
       </c>
     </row>
-    <row r="121" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="121" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>818</v>
       </c>
@@ -10238,7 +10241,7 @@
         <v>1679</v>
       </c>
     </row>
-    <row r="122" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="122" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>314</v>
       </c>
@@ -10270,7 +10273,7 @@
         <v>1792</v>
       </c>
     </row>
-    <row r="123" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="123" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>879</v>
       </c>
@@ -10305,7 +10308,7 @@
         <v>1794</v>
       </c>
     </row>
-    <row r="124" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="124" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>880</v>
       </c>
@@ -10340,7 +10343,7 @@
         <v>1675</v>
       </c>
     </row>
-    <row r="125" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="125" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>881</v>
       </c>
@@ -10372,7 +10375,7 @@
         <v>1592</v>
       </c>
     </row>
-    <row r="126" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="126" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>882</v>
       </c>
@@ -10407,7 +10410,7 @@
         <v>1799</v>
       </c>
     </row>
-    <row r="127" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="127" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>883</v>
       </c>
@@ -10439,7 +10442,7 @@
         <v>1801</v>
       </c>
     </row>
-    <row r="128" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="128" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>884</v>
       </c>
@@ -10471,7 +10474,7 @@
         <v>1803</v>
       </c>
     </row>
-    <row r="129" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="129" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>885</v>
       </c>
@@ -10503,7 +10506,7 @@
         <v>1805</v>
       </c>
     </row>
-    <row r="130" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="130" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>886</v>
       </c>
@@ -10541,7 +10544,7 @@
         <v>1806</v>
       </c>
     </row>
-    <row r="131" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="131" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>887</v>
       </c>
@@ -10576,7 +10579,7 @@
         <v>1526</v>
       </c>
     </row>
-    <row r="132" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="132" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>888</v>
       </c>
@@ -10611,7 +10614,7 @@
         <v>1809</v>
       </c>
     </row>
-    <row r="133" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="133" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>889</v>
       </c>
@@ -10646,7 +10649,7 @@
         <v>1552</v>
       </c>
     </row>
-    <row r="134" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="134" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>890</v>
       </c>
@@ -10681,7 +10684,7 @@
         <v>1812</v>
       </c>
     </row>
-    <row r="135" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="135" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>891</v>
       </c>
@@ -10713,7 +10716,7 @@
         <v>1814</v>
       </c>
     </row>
-    <row r="136" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="136" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>892</v>
       </c>
@@ -10748,7 +10751,7 @@
         <v>1816</v>
       </c>
     </row>
-    <row r="137" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="137" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>893</v>
       </c>
@@ -10780,7 +10783,7 @@
         <v>1818</v>
       </c>
     </row>
-    <row r="138" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="138" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>894</v>
       </c>
@@ -10815,7 +10818,7 @@
         <v>1821</v>
       </c>
     </row>
-    <row r="139" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="139" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>895</v>
       </c>
@@ -10850,7 +10853,7 @@
         <v>1525</v>
       </c>
     </row>
-    <row r="140" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="140" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>896</v>
       </c>
@@ -10882,7 +10885,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="141" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="141" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>897</v>
       </c>
@@ -10914,7 +10917,7 @@
         <v>1550</v>
       </c>
     </row>
-    <row r="142" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="142" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>898</v>
       </c>
@@ -10949,7 +10952,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="143" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="143" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>899</v>
       </c>
@@ -10981,7 +10984,7 @@
         <v>1510</v>
       </c>
     </row>
-    <row r="144" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="144" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>900</v>
       </c>
@@ -11013,7 +11016,7 @@
         <v>1828</v>
       </c>
     </row>
-    <row r="145" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="145" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>901</v>
       </c>
@@ -11045,7 +11048,7 @@
         <v>1830</v>
       </c>
     </row>
-    <row r="146" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="146" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>902</v>
       </c>
@@ -11077,7 +11080,7 @@
         <v>1561</v>
       </c>
     </row>
-    <row r="147" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="147" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>903</v>
       </c>
@@ -11106,7 +11109,7 @@
         <v>1831</v>
       </c>
     </row>
-    <row r="148" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="148" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>76</v>
       </c>
@@ -11141,7 +11144,7 @@
         <v>1526</v>
       </c>
     </row>
-    <row r="149" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="149" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>995</v>
       </c>
@@ -11176,7 +11179,7 @@
         <v>1550</v>
       </c>
     </row>
-    <row r="150" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="150" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>996</v>
       </c>
@@ -11211,7 +11214,7 @@
         <v>1834</v>
       </c>
     </row>
-    <row r="151" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="151" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>997</v>
       </c>
@@ -11243,7 +11246,7 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="152" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="152" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>998</v>
       </c>
@@ -11275,7 +11278,7 @@
         <v>1580</v>
       </c>
     </row>
-    <row r="153" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="153" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>999</v>
       </c>
@@ -11310,7 +11313,7 @@
         <v>1839</v>
       </c>
     </row>
-    <row r="154" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="154" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>1000</v>
       </c>
@@ -11342,7 +11345,7 @@
         <v>1544</v>
       </c>
     </row>
-    <row r="155" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="155" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>1001</v>
       </c>
@@ -11377,7 +11380,7 @@
         <v>1550</v>
       </c>
     </row>
-    <row r="156" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="156" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>1002</v>
       </c>
@@ -11409,7 +11412,7 @@
         <v>1526</v>
       </c>
     </row>
-    <row r="157" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="157" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>1003</v>
       </c>
@@ -11444,7 +11447,7 @@
         <v>1586</v>
       </c>
     </row>
-    <row r="158" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="158" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>1004</v>
       </c>
@@ -11479,7 +11482,7 @@
         <v>1843</v>
       </c>
     </row>
-    <row r="159" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="159" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>1005</v>
       </c>
@@ -11511,7 +11514,7 @@
         <v>1844</v>
       </c>
     </row>
-    <row r="160" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="160" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>1006</v>
       </c>
@@ -11546,7 +11549,7 @@
         <v>1846</v>
       </c>
     </row>
-    <row r="161" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="161" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>1007</v>
       </c>
@@ -11578,7 +11581,7 @@
         <v>1848</v>
       </c>
     </row>
-    <row r="162" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="162" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>1008</v>
       </c>
@@ -11610,7 +11613,7 @@
         <v>1561</v>
       </c>
     </row>
-    <row r="163" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="163" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>1009</v>
       </c>
@@ -11645,7 +11648,7 @@
         <v>1851</v>
       </c>
     </row>
-    <row r="164" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="164" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>1010</v>
       </c>
@@ -11680,7 +11683,7 @@
         <v>1852</v>
       </c>
     </row>
-    <row r="165" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="165" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>1011</v>
       </c>
@@ -11712,7 +11715,7 @@
         <v>1853</v>
       </c>
     </row>
-    <row r="166" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="166" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>1012</v>
       </c>
@@ -11747,7 +11750,7 @@
         <v>1855</v>
       </c>
     </row>
-    <row r="167" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="167" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>1013</v>
       </c>
@@ -11782,7 +11785,7 @@
         <v>1857</v>
       </c>
     </row>
-    <row r="168" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="168" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>23</v>
       </c>
@@ -11814,7 +11817,7 @@
         <v>1526</v>
       </c>
     </row>
-    <row r="169" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="169" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>1139</v>
       </c>
@@ -11849,7 +11852,7 @@
         <v>1834</v>
       </c>
     </row>
-    <row r="170" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="170" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>1140</v>
       </c>
@@ -11887,7 +11890,7 @@
         <v>1543</v>
       </c>
     </row>
-    <row r="171" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="171" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>1141</v>
       </c>
@@ -11925,7 +11928,7 @@
         <v>1861</v>
       </c>
     </row>
-    <row r="172" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="172" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>1142</v>
       </c>
@@ -11957,7 +11960,7 @@
         <v>1862</v>
       </c>
     </row>
-    <row r="173" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="173" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>1143</v>
       </c>
@@ -11992,7 +11995,7 @@
         <v>1543</v>
       </c>
     </row>
-    <row r="174" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="174" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>1144</v>
       </c>
@@ -12030,7 +12033,7 @@
         <v>1864</v>
       </c>
     </row>
-    <row r="175" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="175" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>1145</v>
       </c>
@@ -12068,7 +12071,7 @@
         <v>1866</v>
       </c>
     </row>
-    <row r="176" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="176" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>1146</v>
       </c>
@@ -12106,7 +12109,7 @@
         <v>1867</v>
       </c>
     </row>
-    <row r="177" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="177" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>1147</v>
       </c>
@@ -12141,7 +12144,7 @@
         <v>1869</v>
       </c>
     </row>
-    <row r="178" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="178" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>1148</v>
       </c>
@@ -12176,7 +12179,7 @@
         <v>1872</v>
       </c>
     </row>
-    <row r="179" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="179" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>29</v>
       </c>
@@ -12211,7 +12214,7 @@
         <v>1874</v>
       </c>
     </row>
-    <row r="180" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="180" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
         <v>1149</v>
       </c>
@@ -12243,7 +12246,7 @@
         <v>1875</v>
       </c>
     </row>
-    <row r="181" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="181" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>1150</v>
       </c>
@@ -12278,7 +12281,7 @@
         <v>1543</v>
       </c>
     </row>
-    <row r="182" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="182" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>1151</v>
       </c>
@@ -12310,7 +12313,7 @@
         <v>1879</v>
       </c>
     </row>
-    <row r="183" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="183" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>1152</v>
       </c>
@@ -12345,7 +12348,7 @@
         <v>1880</v>
       </c>
     </row>
-    <row r="184" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="184" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
         <v>1153</v>
       </c>
@@ -12380,7 +12383,7 @@
         <v>1882</v>
       </c>
     </row>
-    <row r="185" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="185" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
         <v>36</v>
       </c>
@@ -12427,13 +12430,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{445C98DF-AF88-42FF-A8A5-2AB8831F51CC}">
   <dimension ref="A1:B61"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.1328125" customWidth="1"/>
-    <col min="2" max="2" width="16.9296875" customWidth="1"/>
+    <col min="1" max="1" width="22.140625" customWidth="1"/>
+    <col min="2" max="2" width="17" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>1513</v>
       </c>
@@ -12441,7 +12444,7 @@
         <v>1514</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1519</v>
       </c>
@@ -12449,7 +12452,7 @@
         <v>1510</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>1520</v>
       </c>
@@ -12457,7 +12460,7 @@
         <v>1525</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>1521</v>
       </c>
@@ -12465,7 +12468,7 @@
         <v>1526</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>1522</v>
       </c>
@@ -12473,7 +12476,7 @@
         <v>1527</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>1523</v>
       </c>
@@ -12481,7 +12484,7 @@
         <v>1534</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>1524</v>
       </c>
@@ -12489,7 +12492,7 @@
         <v>1535</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>1529</v>
       </c>
@@ -12497,7 +12500,7 @@
         <v>1538</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>1337</v>
       </c>
@@ -12505,7 +12508,7 @@
         <v>1541</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>1532</v>
       </c>
@@ -12513,7 +12516,7 @@
         <v>1543</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>1533</v>
       </c>
@@ -12521,7 +12524,7 @@
         <v>1544</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>1539</v>
       </c>
@@ -12529,7 +12532,7 @@
         <v>1550</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>1547</v>
       </c>
@@ -12537,7 +12540,7 @@
         <v>1552</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>1551</v>
       </c>
@@ -12545,7 +12548,7 @@
         <v>1553</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>1558</v>
       </c>
@@ -12553,7 +12556,7 @@
         <v>1572</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>1559</v>
       </c>
@@ -12561,7 +12564,7 @@
         <v>1576</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>1563</v>
       </c>
@@ -12569,7 +12572,7 @@
         <v>1580</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>1564</v>
       </c>
@@ -12577,7 +12580,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>1566</v>
       </c>
@@ -12585,7 +12588,7 @@
         <v>1582</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>1569</v>
       </c>
@@ -12593,7 +12596,7 @@
         <v>1585</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>1579</v>
       </c>
@@ -12601,7 +12604,7 @@
         <v>1603</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>1588</v>
       </c>
@@ -12609,7 +12612,7 @@
         <v>1634</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>1589</v>
       </c>
@@ -12617,7 +12620,7 @@
         <v>1635</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>1593</v>
       </c>
@@ -12625,7 +12628,7 @@
         <v>1659</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>1594</v>
       </c>
@@ -12633,7 +12636,7 @@
         <v>1661</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>1601</v>
       </c>
@@ -12641,7 +12644,7 @@
         <v>1705</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>1602</v>
       </c>
@@ -12649,7 +12652,7 @@
         <v>1714</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>1606</v>
       </c>
@@ -12657,7 +12660,7 @@
         <v>1716</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>1611</v>
       </c>
@@ -12665,7 +12668,7 @@
         <v>1721</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>1625</v>
       </c>
@@ -12673,7 +12676,7 @@
         <v>1728</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>1629</v>
       </c>
@@ -12681,7 +12684,7 @@
         <v>1747</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>1638</v>
       </c>
@@ -12689,7 +12692,7 @@
         <v>1754</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>1640</v>
       </c>
@@ -12697,7 +12700,7 @@
         <v>1767</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>1643</v>
       </c>
@@ -12705,7 +12708,7 @@
         <v>1801</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>1645</v>
       </c>
@@ -12713,7 +12716,7 @@
         <v>1805</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>1655</v>
       </c>
@@ -12721,127 +12724,127 @@
         <v>1828</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>1335</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>1665</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>1671</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>1692</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>1735</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>1739</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>1743</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>1744</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>1541</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>1758</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>1759</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>1766</v>
       </c>
     </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>1771</v>
       </c>
     </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>1779</v>
       </c>
     </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>1783</v>
       </c>
     </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>1788</v>
       </c>
     </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>1790</v>
       </c>
     </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>1796</v>
       </c>
     </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>1820</v>
       </c>
     </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>1825</v>
       </c>
     </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>1828</v>
       </c>
     </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>1850</v>
       </c>
     </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>1871</v>
       </c>
     </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>1877</v>
       </c>
     </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>1534</v>
       </c>
@@ -12854,16 +12857,16 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D1BC60D8-44F3-478D-BCC0-4752624457AE}">
   <dimension ref="A1:F24"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="19" customWidth="1"/>
-    <col min="3" max="3" width="25.59765625" customWidth="1"/>
-    <col min="4" max="4" width="23.3984375" customWidth="1"/>
-    <col min="5" max="5" width="16.3984375" customWidth="1"/>
-    <col min="6" max="6" width="13.59765625" customWidth="1"/>
+    <col min="3" max="3" width="25.5703125" customWidth="1"/>
+    <col min="4" max="4" width="23.42578125" customWidth="1"/>
+    <col min="5" max="5" width="16.42578125" customWidth="1"/>
+    <col min="6" max="6" width="13.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -12883,7 +12886,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>116</v>
       </c>
@@ -12900,7 +12903,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>126</v>
       </c>
@@ -12917,7 +12920,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>130</v>
       </c>
@@ -12934,7 +12937,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>333</v>
       </c>
@@ -12951,7 +12954,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>333</v>
       </c>
@@ -12968,7 +12971,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>333</v>
       </c>
@@ -12985,7 +12988,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>85</v>
       </c>
@@ -13002,7 +13005,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>17</v>
       </c>
@@ -13019,7 +13022,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>17</v>
       </c>
@@ -13036,7 +13039,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>284</v>
       </c>
@@ -13053,7 +13056,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>284</v>
       </c>
@@ -13070,7 +13073,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>284</v>
       </c>
@@ -13087,7 +13090,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>284</v>
       </c>
@@ -13104,7 +13107,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>284</v>
       </c>
@@ -13121,7 +13124,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>284</v>
       </c>
@@ -13138,7 +13141,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>284</v>
       </c>
@@ -13155,7 +13158,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>96</v>
       </c>
@@ -13172,7 +13175,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>96</v>
       </c>
@@ -13189,7 +13192,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>96</v>
       </c>
@@ -13206,7 +13209,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>886</v>
       </c>
@@ -13223,7 +13226,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>886</v>
       </c>
@@ -13240,7 +13243,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>886</v>
       </c>
@@ -13257,7 +13260,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>36</v>
       </c>
@@ -13284,16 +13287,16 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84E3BB0D-5578-4069-B1C9-C3864EB2A429}">
   <dimension ref="A1:G553"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="26.33203125" customWidth="1"/>
-    <col min="3" max="3" width="12.73046875" customWidth="1"/>
+    <col min="2" max="2" width="26.28515625" customWidth="1"/>
+    <col min="3" max="3" width="12.7109375" customWidth="1"/>
     <col min="4" max="4" width="17" customWidth="1"/>
-    <col min="5" max="5" width="29.59765625" customWidth="1"/>
-    <col min="6" max="6" width="15.73046875" customWidth="1"/>
+    <col min="5" max="5" width="29.5703125" customWidth="1"/>
+    <col min="6" max="6" width="15.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -13316,7 +13319,7 @@
         <v>1259</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -13333,7 +13336,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -13350,7 +13353,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -13367,7 +13370,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>111</v>
       </c>
@@ -13384,7 +13387,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>111</v>
       </c>
@@ -13401,7 +13404,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>111</v>
       </c>
@@ -13418,7 +13421,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>112</v>
       </c>
@@ -13435,7 +13438,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>112</v>
       </c>
@@ -13452,7 +13455,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>112</v>
       </c>
@@ -13469,7 +13472,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>113</v>
       </c>
@@ -13486,7 +13489,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>113</v>
       </c>
@@ -13503,7 +13506,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>113</v>
       </c>
@@ -13520,7 +13523,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>114</v>
       </c>
@@ -13537,7 +13540,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>114</v>
       </c>
@@ -13554,7 +13557,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>114</v>
       </c>
@@ -13571,7 +13574,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>115</v>
       </c>
@@ -13588,7 +13591,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>115</v>
       </c>
@@ -13605,7 +13608,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>115</v>
       </c>
@@ -13622,7 +13625,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>116</v>
       </c>
@@ -13639,7 +13642,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>116</v>
       </c>
@@ -13656,7 +13659,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>116</v>
       </c>
@@ -13673,7 +13676,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>117</v>
       </c>
@@ -13690,7 +13693,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>117</v>
       </c>
@@ -13707,7 +13710,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>117</v>
       </c>
@@ -13724,7 +13727,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>118</v>
       </c>
@@ -13741,7 +13744,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>118</v>
       </c>
@@ -13758,7 +13761,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>118</v>
       </c>
@@ -13775,7 +13778,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>119</v>
       </c>
@@ -13792,7 +13795,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>119</v>
       </c>
@@ -13809,7 +13812,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>119</v>
       </c>
@@ -13826,7 +13829,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>120</v>
       </c>
@@ -13843,7 +13846,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>120</v>
       </c>
@@ -13860,7 +13863,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>120</v>
       </c>
@@ -13877,7 +13880,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>121</v>
       </c>
@@ -13894,7 +13897,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>121</v>
       </c>
@@ -13911,7 +13914,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>121</v>
       </c>
@@ -13928,7 +13931,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>122</v>
       </c>
@@ -13945,7 +13948,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>122</v>
       </c>
@@ -13962,7 +13965,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>122</v>
       </c>
@@ -13979,7 +13982,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>123</v>
       </c>
@@ -13996,7 +13999,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>123</v>
       </c>
@@ -14013,7 +14016,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>123</v>
       </c>
@@ -14030,7 +14033,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>124</v>
       </c>
@@ -14047,7 +14050,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>124</v>
       </c>
@@ -14064,7 +14067,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>124</v>
       </c>
@@ -14081,7 +14084,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>125</v>
       </c>
@@ -14098,7 +14101,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>125</v>
       </c>
@@ -14115,7 +14118,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>125</v>
       </c>
@@ -14132,7 +14135,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>126</v>
       </c>
@@ -14149,7 +14152,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>126</v>
       </c>
@@ -14166,7 +14169,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>126</v>
       </c>
@@ -14183,7 +14186,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>127</v>
       </c>
@@ -14200,7 +14203,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>127</v>
       </c>
@@ -14217,7 +14220,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>127</v>
       </c>
@@ -14234,7 +14237,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>128</v>
       </c>
@@ -14251,7 +14254,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>128</v>
       </c>
@@ -14268,7 +14271,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>128</v>
       </c>
@@ -14285,7 +14288,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>129</v>
       </c>
@@ -14302,7 +14305,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>129</v>
       </c>
@@ -14319,7 +14322,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>129</v>
       </c>
@@ -14336,7 +14339,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>130</v>
       </c>
@@ -14353,7 +14356,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>130</v>
       </c>
@@ -14370,7 +14373,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>130</v>
       </c>
@@ -14387,7 +14390,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>131</v>
       </c>
@@ -14404,7 +14407,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>131</v>
       </c>
@@ -14421,7 +14424,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>131</v>
       </c>
@@ -14438,7 +14441,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>132</v>
       </c>
@@ -14455,7 +14458,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>132</v>
       </c>
@@ -14472,7 +14475,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>132</v>
       </c>
@@ -14489,7 +14492,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>264</v>
       </c>
@@ -14506,7 +14509,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>264</v>
       </c>
@@ -14523,7 +14526,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>264</v>
       </c>
@@ -14540,7 +14543,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>323</v>
       </c>
@@ -14557,7 +14560,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>323</v>
       </c>
@@ -14574,7 +14577,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>323</v>
       </c>
@@ -14591,7 +14594,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>329</v>
       </c>
@@ -14608,7 +14611,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>329</v>
       </c>
@@ -14625,7 +14628,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>329</v>
       </c>
@@ -14642,7 +14645,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>330</v>
       </c>
@@ -14659,7 +14662,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>330</v>
       </c>
@@ -14676,7 +14679,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>330</v>
       </c>
@@ -14693,7 +14696,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>331</v>
       </c>
@@ -14710,7 +14713,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>331</v>
       </c>
@@ -14727,7 +14730,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>331</v>
       </c>
@@ -14744,7 +14747,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>332</v>
       </c>
@@ -14761,7 +14764,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>332</v>
       </c>
@@ -14778,7 +14781,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>332</v>
       </c>
@@ -14795,7 +14798,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>333</v>
       </c>
@@ -14812,7 +14815,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>333</v>
       </c>
@@ -14829,7 +14832,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>333</v>
       </c>
@@ -14846,7 +14849,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>334</v>
       </c>
@@ -14863,7 +14866,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>334</v>
       </c>
@@ -14880,7 +14883,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>334</v>
       </c>
@@ -14897,7 +14900,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>335</v>
       </c>
@@ -14914,7 +14917,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>335</v>
       </c>
@@ -14931,7 +14934,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>335</v>
       </c>
@@ -14948,7 +14951,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>336</v>
       </c>
@@ -14965,7 +14968,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>336</v>
       </c>
@@ -14982,7 +14985,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>336</v>
       </c>
@@ -14999,7 +15002,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>337</v>
       </c>
@@ -15016,7 +15019,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>337</v>
       </c>
@@ -15033,7 +15036,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>337</v>
       </c>
@@ -15050,7 +15053,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>338</v>
       </c>
@@ -15067,7 +15070,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>338</v>
       </c>
@@ -15084,7 +15087,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>338</v>
       </c>
@@ -15101,7 +15104,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>339</v>
       </c>
@@ -15118,7 +15121,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>339</v>
       </c>
@@ -15135,7 +15138,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>339</v>
       </c>
@@ -15152,7 +15155,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>340</v>
       </c>
@@ -15169,7 +15172,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>340</v>
       </c>
@@ -15186,7 +15189,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>340</v>
       </c>
@@ -15203,7 +15206,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>341</v>
       </c>
@@ -15220,7 +15223,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>341</v>
       </c>
@@ -15237,7 +15240,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>341</v>
       </c>
@@ -15254,7 +15257,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>342</v>
       </c>
@@ -15271,7 +15274,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>342</v>
       </c>
@@ -15288,7 +15291,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>342</v>
       </c>
@@ -15305,7 +15308,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>343</v>
       </c>
@@ -15322,7 +15325,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>343</v>
       </c>
@@ -15339,7 +15342,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>343</v>
       </c>
@@ -15356,7 +15359,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="122" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>344</v>
       </c>
@@ -15373,7 +15376,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="123" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="123" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>344</v>
       </c>
@@ -15390,7 +15393,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>344</v>
       </c>
@@ -15407,7 +15410,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="125" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="125" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>345</v>
       </c>
@@ -15424,7 +15427,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="126" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="126" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>345</v>
       </c>
@@ -15441,7 +15444,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="127" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>345</v>
       </c>
@@ -15458,7 +15461,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="128" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="128" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>346</v>
       </c>
@@ -15475,7 +15478,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="129" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="129" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>346</v>
       </c>
@@ -15492,7 +15495,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="130" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="130" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>346</v>
       </c>
@@ -15509,7 +15512,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="131" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="131" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>347</v>
       </c>
@@ -15526,7 +15529,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="132" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="132" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>347</v>
       </c>
@@ -15543,7 +15546,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="133" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="133" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>347</v>
       </c>
@@ -15560,7 +15563,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="134" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="134" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>348</v>
       </c>
@@ -15577,7 +15580,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="135" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="135" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>348</v>
       </c>
@@ -15594,7 +15597,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="136" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="136" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>348</v>
       </c>
@@ -15611,7 +15614,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="137" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="137" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>349</v>
       </c>
@@ -15628,7 +15631,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="138" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="138" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>349</v>
       </c>
@@ -15645,7 +15648,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="139" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="139" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>349</v>
       </c>
@@ -15662,7 +15665,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="140" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="140" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>466</v>
       </c>
@@ -15679,7 +15682,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="141" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="141" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>466</v>
       </c>
@@ -15696,7 +15699,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="142" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="142" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>466</v>
       </c>
@@ -15713,7 +15716,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="143" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="143" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>271</v>
       </c>
@@ -15730,7 +15733,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="144" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="144" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>271</v>
       </c>
@@ -15747,7 +15750,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="145" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="145" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>271</v>
       </c>
@@ -15764,7 +15767,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="146" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="146" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>476</v>
       </c>
@@ -15781,7 +15784,7 @@
         <v>571</v>
       </c>
     </row>
-    <row r="147" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="147" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>476</v>
       </c>
@@ -15798,7 +15801,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="148" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="148" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>476</v>
       </c>
@@ -15815,7 +15818,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="149" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="149" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>477</v>
       </c>
@@ -15832,7 +15835,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="150" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="150" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>477</v>
       </c>
@@ -15849,7 +15852,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="151" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="151" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>477</v>
       </c>
@@ -15866,7 +15869,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="152" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="152" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>478</v>
       </c>
@@ -15883,7 +15886,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="153" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="153" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>478</v>
       </c>
@@ -15900,7 +15903,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="154" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="154" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>478</v>
       </c>
@@ -15917,7 +15920,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="155" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="155" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>479</v>
       </c>
@@ -15934,7 +15937,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="156" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="156" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>479</v>
       </c>
@@ -15951,7 +15954,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="157" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="157" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>479</v>
       </c>
@@ -15968,7 +15971,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="158" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="158" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>480</v>
       </c>
@@ -15985,7 +15988,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="159" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="159" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>480</v>
       </c>
@@ -16002,7 +16005,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="160" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="160" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>480</v>
       </c>
@@ -16019,7 +16022,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="161" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="161" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>481</v>
       </c>
@@ -16036,7 +16039,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="162" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="162" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>481</v>
       </c>
@@ -16053,7 +16056,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="163" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="163" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>481</v>
       </c>
@@ -16070,7 +16073,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="164" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="164" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>482</v>
       </c>
@@ -16087,7 +16090,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="165" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="165" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>482</v>
       </c>
@@ -16104,7 +16107,7 @@
         <v>585</v>
       </c>
     </row>
-    <row r="166" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="166" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>482</v>
       </c>
@@ -16121,7 +16124,7 @@
         <v>586</v>
       </c>
     </row>
-    <row r="167" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="167" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>483</v>
       </c>
@@ -16138,7 +16141,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="168" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="168" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>483</v>
       </c>
@@ -16155,7 +16158,7 @@
         <v>588</v>
       </c>
     </row>
-    <row r="169" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="169" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>483</v>
       </c>
@@ -16172,7 +16175,7 @@
         <v>589</v>
       </c>
     </row>
-    <row r="170" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="170" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>484</v>
       </c>
@@ -16189,7 +16192,7 @@
         <v>590</v>
       </c>
     </row>
-    <row r="171" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="171" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>484</v>
       </c>
@@ -16206,7 +16209,7 @@
         <v>591</v>
       </c>
     </row>
-    <row r="172" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="172" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>484</v>
       </c>
@@ -16223,7 +16226,7 @@
         <v>592</v>
       </c>
     </row>
-    <row r="173" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="173" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>485</v>
       </c>
@@ -16240,7 +16243,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="174" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="174" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>485</v>
       </c>
@@ -16257,7 +16260,7 @@
         <v>594</v>
       </c>
     </row>
-    <row r="175" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="175" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>485</v>
       </c>
@@ -16274,7 +16277,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="176" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="176" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>486</v>
       </c>
@@ -16291,7 +16294,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="177" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="177" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>486</v>
       </c>
@@ -16308,7 +16311,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="178" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="178" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>486</v>
       </c>
@@ -16325,7 +16328,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="179" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="179" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>487</v>
       </c>
@@ -16342,7 +16345,7 @@
         <v>598</v>
       </c>
     </row>
-    <row r="180" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="180" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
         <v>487</v>
       </c>
@@ -16359,7 +16362,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="181" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="181" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>487</v>
       </c>
@@ -16376,7 +16379,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="182" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="182" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>488</v>
       </c>
@@ -16393,7 +16396,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="183" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="183" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>488</v>
       </c>
@@ -16410,7 +16413,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="184" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="184" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
         <v>488</v>
       </c>
@@ -16427,7 +16430,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="185" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="185" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
         <v>489</v>
       </c>
@@ -16444,7 +16447,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="186" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="186" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
         <v>489</v>
       </c>
@@ -16461,7 +16464,7 @@
         <v>605</v>
       </c>
     </row>
-    <row r="187" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="187" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
         <v>489</v>
       </c>
@@ -16478,7 +16481,7 @@
         <v>606</v>
       </c>
     </row>
-    <row r="188" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="188" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
         <v>490</v>
       </c>
@@ -16495,7 +16498,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="189" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="189" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
         <v>490</v>
       </c>
@@ -16512,7 +16515,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="190" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="190" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
         <v>490</v>
       </c>
@@ -16529,7 +16532,7 @@
         <v>608</v>
       </c>
     </row>
-    <row r="191" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="191" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
         <v>491</v>
       </c>
@@ -16546,7 +16549,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="192" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="192" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
         <v>491</v>
       </c>
@@ -16563,7 +16566,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="193" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="193" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
         <v>491</v>
       </c>
@@ -16580,7 +16583,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="194" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="194" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
         <v>492</v>
       </c>
@@ -16597,7 +16600,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="195" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="195" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
         <v>492</v>
       </c>
@@ -16614,7 +16617,7 @@
         <v>611</v>
       </c>
     </row>
-    <row r="196" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="196" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
         <v>492</v>
       </c>
@@ -16631,7 +16634,7 @@
         <v>612</v>
       </c>
     </row>
-    <row r="197" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="197" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
         <v>493</v>
       </c>
@@ -16648,7 +16651,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="198" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="198" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
         <v>493</v>
       </c>
@@ -16665,7 +16668,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="199" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="199" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
         <v>493</v>
       </c>
@@ -16682,7 +16685,7 @@
         <v>615</v>
       </c>
     </row>
-    <row r="200" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="200" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
         <v>494</v>
       </c>
@@ -16699,7 +16702,7 @@
         <v>616</v>
       </c>
     </row>
-    <row r="201" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="201" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
         <v>494</v>
       </c>
@@ -16716,7 +16719,7 @@
         <v>617</v>
       </c>
     </row>
-    <row r="202" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="202" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
         <v>494</v>
       </c>
@@ -16733,7 +16736,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="203" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="203" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
         <v>495</v>
       </c>
@@ -16750,7 +16753,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="204" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="204" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
         <v>495</v>
       </c>
@@ -16767,7 +16770,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="205" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="205" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
         <v>495</v>
       </c>
@@ -16784,7 +16787,7 @@
         <v>621</v>
       </c>
     </row>
-    <row r="206" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="206" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
         <v>85</v>
       </c>
@@ -16801,7 +16804,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="207" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="207" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
         <v>85</v>
       </c>
@@ -16818,7 +16821,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="208" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="208" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
         <v>85</v>
       </c>
@@ -16835,7 +16838,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="209" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="209" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
         <v>275</v>
       </c>
@@ -16852,7 +16855,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="210" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="210" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
         <v>275</v>
       </c>
@@ -16869,7 +16872,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="211" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="211" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
         <v>275</v>
       </c>
@@ -16886,7 +16889,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="212" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="212" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
         <v>535</v>
       </c>
@@ -16903,7 +16906,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="213" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="213" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
         <v>535</v>
       </c>
@@ -16920,7 +16923,7 @@
         <v>666</v>
       </c>
     </row>
-    <row r="214" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="214" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
         <v>535</v>
       </c>
@@ -16937,7 +16940,7 @@
         <v>667</v>
       </c>
     </row>
-    <row r="215" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="215" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
         <v>536</v>
       </c>
@@ -16954,7 +16957,7 @@
         <v>668</v>
       </c>
     </row>
-    <row r="216" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="216" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
         <v>536</v>
       </c>
@@ -16971,7 +16974,7 @@
         <v>669</v>
       </c>
     </row>
-    <row r="217" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="217" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
         <v>536</v>
       </c>
@@ -16988,7 +16991,7 @@
         <v>670</v>
       </c>
     </row>
-    <row r="218" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="218" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
         <v>537</v>
       </c>
@@ -17005,7 +17008,7 @@
         <v>671</v>
       </c>
     </row>
-    <row r="219" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="219" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
         <v>537</v>
       </c>
@@ -17022,7 +17025,7 @@
         <v>672</v>
       </c>
     </row>
-    <row r="220" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="220" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
         <v>537</v>
       </c>
@@ -17039,7 +17042,7 @@
         <v>673</v>
       </c>
     </row>
-    <row r="221" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="221" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
         <v>538</v>
       </c>
@@ -17056,7 +17059,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="222" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="222" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
         <v>538</v>
       </c>
@@ -17073,7 +17076,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="223" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="223" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
         <v>538</v>
       </c>
@@ -17090,7 +17093,7 @@
         <v>675</v>
       </c>
     </row>
-    <row r="224" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="224" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
         <v>539</v>
       </c>
@@ -17107,7 +17110,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="225" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="225" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
         <v>539</v>
       </c>
@@ -17124,7 +17127,7 @@
         <v>676</v>
       </c>
     </row>
-    <row r="226" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="226" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
         <v>539</v>
       </c>
@@ -17141,7 +17144,7 @@
         <v>677</v>
       </c>
     </row>
-    <row r="227" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="227" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
         <v>540</v>
       </c>
@@ -17158,7 +17161,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="228" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="228" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
         <v>540</v>
       </c>
@@ -17175,7 +17178,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="229" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="229" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
         <v>540</v>
       </c>
@@ -17192,7 +17195,7 @@
         <v>679</v>
       </c>
     </row>
-    <row r="230" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="230" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
         <v>541</v>
       </c>
@@ -17209,7 +17212,7 @@
         <v>680</v>
       </c>
     </row>
-    <row r="231" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="231" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
         <v>541</v>
       </c>
@@ -17226,7 +17229,7 @@
         <v>681</v>
       </c>
     </row>
-    <row r="232" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="232" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
         <v>541</v>
       </c>
@@ -17243,7 +17246,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="233" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="233" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
         <v>542</v>
       </c>
@@ -17260,7 +17263,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="234" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="234" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
         <v>542</v>
       </c>
@@ -17277,7 +17280,7 @@
         <v>683</v>
       </c>
     </row>
-    <row r="235" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="235" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
         <v>542</v>
       </c>
@@ -17294,7 +17297,7 @@
         <v>684</v>
       </c>
     </row>
-    <row r="236" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="236" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
         <v>543</v>
       </c>
@@ -17311,7 +17314,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="237" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="237" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
         <v>543</v>
       </c>
@@ -17328,7 +17331,7 @@
         <v>685</v>
       </c>
     </row>
-    <row r="238" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="238" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
         <v>543</v>
       </c>
@@ -17345,7 +17348,7 @@
         <v>686</v>
       </c>
     </row>
-    <row r="239" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="239" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
         <v>544</v>
       </c>
@@ -17362,7 +17365,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="240" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="240" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
         <v>544</v>
       </c>
@@ -17379,7 +17382,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="241" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="241" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
         <v>544</v>
       </c>
@@ -17396,7 +17399,7 @@
         <v>688</v>
       </c>
     </row>
-    <row r="242" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="242" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
         <v>545</v>
       </c>
@@ -17413,7 +17416,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="243" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="243" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
         <v>545</v>
       </c>
@@ -17430,7 +17433,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="244" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="244" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
         <v>545</v>
       </c>
@@ -17447,7 +17450,7 @@
         <v>690</v>
       </c>
     </row>
-    <row r="245" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="245" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
         <v>546</v>
       </c>
@@ -17464,7 +17467,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="246" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="246" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
         <v>546</v>
       </c>
@@ -17481,7 +17484,7 @@
         <v>691</v>
       </c>
     </row>
-    <row r="247" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="247" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
         <v>546</v>
       </c>
@@ -17498,7 +17501,7 @@
         <v>692</v>
       </c>
     </row>
-    <row r="248" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="248" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
         <v>547</v>
       </c>
@@ -17515,7 +17518,7 @@
         <v>693</v>
       </c>
     </row>
-    <row r="249" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="249" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
         <v>547</v>
       </c>
@@ -17532,7 +17535,7 @@
         <v>694</v>
       </c>
     </row>
-    <row r="250" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="250" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
         <v>547</v>
       </c>
@@ -17549,7 +17552,7 @@
         <v>695</v>
       </c>
     </row>
-    <row r="251" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="251" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
         <v>548</v>
       </c>
@@ -17566,7 +17569,7 @@
         <v>696</v>
       </c>
     </row>
-    <row r="252" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="252" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
         <v>548</v>
       </c>
@@ -17583,7 +17586,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="253" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="253" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
         <v>548</v>
       </c>
@@ -17600,7 +17603,7 @@
         <v>697</v>
       </c>
     </row>
-    <row r="254" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="254" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
         <v>549</v>
       </c>
@@ -17617,7 +17620,7 @@
         <v>698</v>
       </c>
     </row>
-    <row r="255" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="255" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
         <v>549</v>
       </c>
@@ -17634,7 +17637,7 @@
         <v>699</v>
       </c>
     </row>
-    <row r="256" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="256" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
         <v>549</v>
       </c>
@@ -17651,7 +17654,7 @@
         <v>700</v>
       </c>
     </row>
-    <row r="257" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="257" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
         <v>550</v>
       </c>
@@ -17668,7 +17671,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="258" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="258" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
         <v>550</v>
       </c>
@@ -17685,7 +17688,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="259" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="259" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
         <v>550</v>
       </c>
@@ -17702,7 +17705,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="260" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="260" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
         <v>551</v>
       </c>
@@ -17719,7 +17722,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="261" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="261" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
         <v>551</v>
       </c>
@@ -17736,7 +17739,7 @@
         <v>703</v>
       </c>
     </row>
-    <row r="262" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="262" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
         <v>551</v>
       </c>
@@ -17753,7 +17756,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="263" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="263" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
         <v>552</v>
       </c>
@@ -17770,7 +17773,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="264" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="264" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
         <v>552</v>
       </c>
@@ -17787,7 +17790,7 @@
         <v>705</v>
       </c>
     </row>
-    <row r="265" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="265" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
         <v>552</v>
       </c>
@@ -17804,7 +17807,7 @@
         <v>706</v>
       </c>
     </row>
-    <row r="266" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="266" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
         <v>553</v>
       </c>
@@ -17821,7 +17824,7 @@
         <v>707</v>
       </c>
     </row>
-    <row r="267" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="267" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
         <v>553</v>
       </c>
@@ -17838,7 +17841,7 @@
         <v>708</v>
       </c>
     </row>
-    <row r="268" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="268" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
         <v>553</v>
       </c>
@@ -17855,7 +17858,7 @@
         <v>709</v>
       </c>
     </row>
-    <row r="269" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="269" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
         <v>554</v>
       </c>
@@ -17872,7 +17875,7 @@
         <v>710</v>
       </c>
     </row>
-    <row r="270" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="270" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
         <v>554</v>
       </c>
@@ -17889,7 +17892,7 @@
         <v>711</v>
       </c>
     </row>
-    <row r="271" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="271" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
         <v>554</v>
       </c>
@@ -17906,7 +17909,7 @@
         <v>712</v>
       </c>
     </row>
-    <row r="272" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="272" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
         <v>555</v>
       </c>
@@ -17923,7 +17926,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="273" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="273" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
         <v>555</v>
       </c>
@@ -17940,7 +17943,7 @@
         <v>713</v>
       </c>
     </row>
-    <row r="274" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="274" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
         <v>555</v>
       </c>
@@ -17957,7 +17960,7 @@
         <v>714</v>
       </c>
     </row>
-    <row r="275" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="275" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
         <v>556</v>
       </c>
@@ -17974,7 +17977,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="276" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="276" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
         <v>556</v>
       </c>
@@ -17991,7 +17994,7 @@
         <v>715</v>
       </c>
     </row>
-    <row r="277" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="277" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
         <v>556</v>
       </c>
@@ -18008,7 +18011,7 @@
         <v>716</v>
       </c>
     </row>
-    <row r="278" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="278" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
         <v>281</v>
       </c>
@@ -18025,7 +18028,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="279" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="279" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
         <v>281</v>
       </c>
@@ -18042,7 +18045,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="280" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="280" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
         <v>281</v>
       </c>
@@ -18059,7 +18062,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="281" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="281" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
         <v>738</v>
       </c>
@@ -18076,7 +18079,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="282" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="282" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
         <v>738</v>
       </c>
@@ -18093,7 +18096,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="283" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="283" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
         <v>738</v>
       </c>
@@ -18110,7 +18113,7 @@
         <v>750</v>
       </c>
     </row>
-    <row r="284" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="284" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
         <v>739</v>
       </c>
@@ -18127,7 +18130,7 @@
         <v>751</v>
       </c>
     </row>
-    <row r="285" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="285" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
         <v>739</v>
       </c>
@@ -18144,7 +18147,7 @@
         <v>752</v>
       </c>
     </row>
-    <row r="286" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="286" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
         <v>739</v>
       </c>
@@ -18161,7 +18164,7 @@
         <v>753</v>
       </c>
     </row>
-    <row r="287" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="287" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
         <v>740</v>
       </c>
@@ -18178,7 +18181,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="288" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="288" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
         <v>740</v>
       </c>
@@ -18195,7 +18198,7 @@
         <v>754</v>
       </c>
     </row>
-    <row r="289" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="289" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
         <v>740</v>
       </c>
@@ -18212,7 +18215,7 @@
         <v>755</v>
       </c>
     </row>
-    <row r="290" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="290" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
         <v>17</v>
       </c>
@@ -18229,7 +18232,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="291" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="291" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
         <v>17</v>
       </c>
@@ -18246,7 +18249,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="292" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="292" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
         <v>17</v>
       </c>
@@ -18263,7 +18266,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="293" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="293" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
         <v>756</v>
       </c>
@@ -18280,7 +18283,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="294" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="294" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
         <v>756</v>
       </c>
@@ -18297,7 +18300,7 @@
         <v>763</v>
       </c>
     </row>
-    <row r="295" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="295" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
         <v>756</v>
       </c>
@@ -18314,7 +18317,7 @@
         <v>764</v>
       </c>
     </row>
-    <row r="296" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="296" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
         <v>757</v>
       </c>
@@ -18331,7 +18334,7 @@
         <v>767</v>
       </c>
     </row>
-    <row r="297" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="297" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
         <v>757</v>
       </c>
@@ -18348,7 +18351,7 @@
         <v>768</v>
       </c>
     </row>
-    <row r="298" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="298" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
         <v>757</v>
       </c>
@@ -18365,7 +18368,7 @@
         <v>769</v>
       </c>
     </row>
-    <row r="299" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="299" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
         <v>758</v>
       </c>
@@ -18382,7 +18385,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="300" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="300" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
         <v>758</v>
       </c>
@@ -18399,7 +18402,7 @@
         <v>772</v>
       </c>
     </row>
-    <row r="301" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="301" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
         <v>758</v>
       </c>
@@ -18416,7 +18419,7 @@
         <v>773</v>
       </c>
     </row>
-    <row r="302" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="302" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
         <v>284</v>
       </c>
@@ -18433,7 +18436,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="303" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="303" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
         <v>284</v>
       </c>
@@ -18450,7 +18453,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="304" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="304" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
         <v>284</v>
       </c>
@@ -18467,7 +18470,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="305" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="305" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
         <v>774</v>
       </c>
@@ -18484,7 +18487,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="306" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="306" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
         <v>774</v>
       </c>
@@ -18501,7 +18504,7 @@
         <v>782</v>
       </c>
     </row>
-    <row r="307" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="307" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
         <v>774</v>
       </c>
@@ -18518,7 +18521,7 @@
         <v>783</v>
       </c>
     </row>
-    <row r="308" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="308" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
         <v>775</v>
       </c>
@@ -18535,7 +18538,7 @@
         <v>785</v>
       </c>
     </row>
-    <row r="309" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="309" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
         <v>775</v>
       </c>
@@ -18552,7 +18555,7 @@
         <v>786</v>
       </c>
     </row>
-    <row r="310" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="310" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
         <v>775</v>
       </c>
@@ -18569,7 +18572,7 @@
         <v>787</v>
       </c>
     </row>
-    <row r="311" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="311" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
         <v>776</v>
       </c>
@@ -18586,7 +18589,7 @@
         <v>791</v>
       </c>
     </row>
-    <row r="312" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="312" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
         <v>776</v>
       </c>
@@ -18603,7 +18606,7 @@
         <v>792</v>
       </c>
     </row>
-    <row r="313" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="313" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
         <v>776</v>
       </c>
@@ -18620,7 +18623,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="314" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="314" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
         <v>777</v>
       </c>
@@ -18637,7 +18640,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="315" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="315" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
         <v>777</v>
       </c>
@@ -18654,7 +18657,7 @@
         <v>797</v>
       </c>
     </row>
-    <row r="316" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="316" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
         <v>777</v>
       </c>
@@ -18671,7 +18674,7 @@
         <v>798</v>
       </c>
     </row>
-    <row r="317" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="317" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
         <v>778</v>
       </c>
@@ -18688,7 +18691,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="318" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="318" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
         <v>778</v>
       </c>
@@ -18705,7 +18708,7 @@
         <v>801</v>
       </c>
     </row>
-    <row r="319" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="319" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
         <v>778</v>
       </c>
@@ -18722,7 +18725,7 @@
         <v>802</v>
       </c>
     </row>
-    <row r="320" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="320" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
         <v>779</v>
       </c>
@@ -18739,7 +18742,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="321" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="321" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
         <v>779</v>
       </c>
@@ -18756,7 +18759,7 @@
         <v>805</v>
       </c>
     </row>
-    <row r="322" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="322" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
         <v>779</v>
       </c>
@@ -18773,7 +18776,7 @@
         <v>806</v>
       </c>
     </row>
-    <row r="323" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="323" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
         <v>96</v>
       </c>
@@ -18790,7 +18793,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="324" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="324" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
         <v>96</v>
       </c>
@@ -18807,7 +18810,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="325" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="325" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
         <v>96</v>
       </c>
@@ -18824,7 +18827,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="326" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="326" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A326" t="s">
         <v>807</v>
       </c>
@@ -18841,7 +18844,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="327" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="327" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
         <v>807</v>
       </c>
@@ -18858,7 +18861,7 @@
         <v>833</v>
       </c>
     </row>
-    <row r="328" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="328" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A328" t="s">
         <v>807</v>
       </c>
@@ -18875,7 +18878,7 @@
         <v>834</v>
       </c>
     </row>
-    <row r="329" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="329" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A329" t="s">
         <v>808</v>
       </c>
@@ -18892,7 +18895,7 @@
         <v>840</v>
       </c>
     </row>
-    <row r="330" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="330" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A330" t="s">
         <v>808</v>
       </c>
@@ -18909,7 +18912,7 @@
         <v>841</v>
       </c>
     </row>
-    <row r="331" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="331" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A331" t="s">
         <v>808</v>
       </c>
@@ -18926,7 +18929,7 @@
         <v>842</v>
       </c>
     </row>
-    <row r="332" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="332" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A332" t="s">
         <v>809</v>
       </c>
@@ -18943,7 +18946,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="333" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="333" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A333" t="s">
         <v>809</v>
       </c>
@@ -18960,7 +18963,7 @@
         <v>844</v>
       </c>
     </row>
-    <row r="334" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="334" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A334" t="s">
         <v>809</v>
       </c>
@@ -18977,7 +18980,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="335" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="335" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A335" t="s">
         <v>810</v>
       </c>
@@ -18994,7 +18997,7 @@
         <v>846</v>
       </c>
     </row>
-    <row r="336" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="336" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A336" t="s">
         <v>810</v>
       </c>
@@ -19011,7 +19014,7 @@
         <v>847</v>
       </c>
     </row>
-    <row r="337" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="337" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A337" t="s">
         <v>810</v>
       </c>
@@ -19028,7 +19031,7 @@
         <v>848</v>
       </c>
     </row>
-    <row r="338" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="338" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A338" t="s">
         <v>811</v>
       </c>
@@ -19045,7 +19048,7 @@
         <v>696</v>
       </c>
     </row>
-    <row r="339" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="339" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A339" t="s">
         <v>811</v>
       </c>
@@ -19062,7 +19065,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="340" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="340" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A340" t="s">
         <v>811</v>
       </c>
@@ -19079,7 +19082,7 @@
         <v>849</v>
       </c>
     </row>
-    <row r="341" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="341" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A341" t="s">
         <v>812</v>
       </c>
@@ -19096,7 +19099,7 @@
         <v>850</v>
       </c>
     </row>
-    <row r="342" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="342" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A342" t="s">
         <v>812</v>
       </c>
@@ -19113,7 +19116,7 @@
         <v>851</v>
       </c>
     </row>
-    <row r="343" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="343" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A343" t="s">
         <v>812</v>
       </c>
@@ -19130,7 +19133,7 @@
         <v>852</v>
       </c>
     </row>
-    <row r="344" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="344" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A344" t="s">
         <v>813</v>
       </c>
@@ -19147,7 +19150,7 @@
         <v>853</v>
       </c>
     </row>
-    <row r="345" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="345" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A345" t="s">
         <v>813</v>
       </c>
@@ -19164,7 +19167,7 @@
         <v>854</v>
       </c>
     </row>
-    <row r="346" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="346" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A346" t="s">
         <v>813</v>
       </c>
@@ -19181,7 +19184,7 @@
         <v>855</v>
       </c>
     </row>
-    <row r="347" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="347" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A347" t="s">
         <v>814</v>
       </c>
@@ -19198,7 +19201,7 @@
         <v>867</v>
       </c>
     </row>
-    <row r="348" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="348" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A348" t="s">
         <v>814</v>
       </c>
@@ -19215,7 +19218,7 @@
         <v>868</v>
       </c>
     </row>
-    <row r="349" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="349" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A349" t="s">
         <v>814</v>
       </c>
@@ -19232,7 +19235,7 @@
         <v>869</v>
       </c>
     </row>
-    <row r="350" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="350" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A350" t="s">
         <v>815</v>
       </c>
@@ -19249,7 +19252,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="351" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="351" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A351" t="s">
         <v>815</v>
       </c>
@@ -19266,7 +19269,7 @@
         <v>870</v>
       </c>
     </row>
-    <row r="352" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="352" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A352" t="s">
         <v>815</v>
       </c>
@@ -19283,7 +19286,7 @@
         <v>871</v>
       </c>
     </row>
-    <row r="353" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="353" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A353" t="s">
         <v>816</v>
       </c>
@@ -19300,7 +19303,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="354" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="354" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A354" t="s">
         <v>816</v>
       </c>
@@ -19317,7 +19320,7 @@
         <v>872</v>
       </c>
     </row>
-    <row r="355" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="355" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A355" t="s">
         <v>816</v>
       </c>
@@ -19334,7 +19337,7 @@
         <v>873</v>
       </c>
     </row>
-    <row r="356" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="356" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A356" t="s">
         <v>817</v>
       </c>
@@ -19351,7 +19354,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="357" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="357" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A357" t="s">
         <v>817</v>
       </c>
@@ -19368,7 +19371,7 @@
         <v>874</v>
       </c>
     </row>
-    <row r="358" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="358" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A358" t="s">
         <v>817</v>
       </c>
@@ -19385,7 +19388,7 @@
         <v>875</v>
       </c>
     </row>
-    <row r="359" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="359" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A359" t="s">
         <v>818</v>
       </c>
@@ -19402,7 +19405,7 @@
         <v>876</v>
       </c>
     </row>
-    <row r="360" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="360" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A360" t="s">
         <v>818</v>
       </c>
@@ -19419,7 +19422,7 @@
         <v>877</v>
       </c>
     </row>
-    <row r="361" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="361" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A361" t="s">
         <v>818</v>
       </c>
@@ -19436,7 +19439,7 @@
         <v>878</v>
       </c>
     </row>
-    <row r="362" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="362" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A362" t="s">
         <v>314</v>
       </c>
@@ -19453,7 +19456,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="363" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="363" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A363" t="s">
         <v>314</v>
       </c>
@@ -19470,7 +19473,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="364" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="364" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A364" t="s">
         <v>314</v>
       </c>
@@ -19487,7 +19490,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="365" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="365" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A365" t="s">
         <v>879</v>
       </c>
@@ -19504,7 +19507,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="366" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="366" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A366" t="s">
         <v>879</v>
       </c>
@@ -19521,7 +19524,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="367" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="367" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A367" t="s">
         <v>879</v>
       </c>
@@ -19538,7 +19541,7 @@
         <v>950</v>
       </c>
     </row>
-    <row r="368" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="368" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A368" t="s">
         <v>880</v>
       </c>
@@ -19555,7 +19558,7 @@
         <v>951</v>
       </c>
     </row>
-    <row r="369" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="369" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A369" t="s">
         <v>880</v>
       </c>
@@ -19572,7 +19575,7 @@
         <v>952</v>
       </c>
     </row>
-    <row r="370" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="370" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A370" t="s">
         <v>880</v>
       </c>
@@ -19589,7 +19592,7 @@
         <v>953</v>
       </c>
     </row>
-    <row r="371" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="371" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A371" t="s">
         <v>881</v>
       </c>
@@ -19606,7 +19609,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="372" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="372" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A372" t="s">
         <v>881</v>
       </c>
@@ -19623,7 +19626,7 @@
         <v>954</v>
       </c>
     </row>
-    <row r="373" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="373" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A373" t="s">
         <v>881</v>
       </c>
@@ -19640,7 +19643,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="374" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="374" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A374" t="s">
         <v>882</v>
       </c>
@@ -19657,7 +19660,7 @@
         <v>956</v>
       </c>
     </row>
-    <row r="375" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="375" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A375" t="s">
         <v>882</v>
       </c>
@@ -19674,7 +19677,7 @@
         <v>957</v>
       </c>
     </row>
-    <row r="376" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="376" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A376" t="s">
         <v>882</v>
       </c>
@@ -19691,7 +19694,7 @@
         <v>958</v>
       </c>
     </row>
-    <row r="377" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="377" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A377" t="s">
         <v>883</v>
       </c>
@@ -19708,7 +19711,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="378" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="378" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A378" t="s">
         <v>883</v>
       </c>
@@ -19725,7 +19728,7 @@
         <v>959</v>
       </c>
     </row>
-    <row r="379" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="379" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A379" t="s">
         <v>883</v>
       </c>
@@ -19742,7 +19745,7 @@
         <v>960</v>
       </c>
     </row>
-    <row r="380" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="380" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A380" t="s">
         <v>884</v>
       </c>
@@ -19759,7 +19762,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="381" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="381" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A381" t="s">
         <v>884</v>
       </c>
@@ -19776,7 +19779,7 @@
         <v>961</v>
       </c>
     </row>
-    <row r="382" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="382" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A382" t="s">
         <v>884</v>
       </c>
@@ -19793,7 +19796,7 @@
         <v>962</v>
       </c>
     </row>
-    <row r="383" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="383" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A383" t="s">
         <v>885</v>
       </c>
@@ -19810,7 +19813,7 @@
         <v>963</v>
       </c>
     </row>
-    <row r="384" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="384" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A384" t="s">
         <v>885</v>
       </c>
@@ -19827,7 +19830,7 @@
         <v>965</v>
       </c>
     </row>
-    <row r="385" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="385" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A385" t="s">
         <v>885</v>
       </c>
@@ -19844,7 +19847,7 @@
         <v>964</v>
       </c>
     </row>
-    <row r="386" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="386" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A386" t="s">
         <v>886</v>
       </c>
@@ -19861,7 +19864,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="387" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="387" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A387" t="s">
         <v>886</v>
       </c>
@@ -19878,7 +19881,7 @@
         <v>966</v>
       </c>
     </row>
-    <row r="388" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="388" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A388" t="s">
         <v>886</v>
       </c>
@@ -19895,7 +19898,7 @@
         <v>967</v>
       </c>
     </row>
-    <row r="389" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="389" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A389" t="s">
         <v>887</v>
       </c>
@@ -19912,7 +19915,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="390" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="390" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A390" t="s">
         <v>887</v>
       </c>
@@ -19929,7 +19932,7 @@
         <v>974</v>
       </c>
     </row>
-    <row r="391" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="391" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A391" t="s">
         <v>887</v>
       </c>
@@ -19946,7 +19949,7 @@
         <v>975</v>
       </c>
     </row>
-    <row r="392" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="392" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A392" t="s">
         <v>888</v>
       </c>
@@ -19963,7 +19966,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="393" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="393" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A393" t="s">
         <v>888</v>
       </c>
@@ -19980,7 +19983,7 @@
         <v>976</v>
       </c>
     </row>
-    <row r="394" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="394" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A394" t="s">
         <v>888</v>
       </c>
@@ -19997,7 +20000,7 @@
         <v>977</v>
       </c>
     </row>
-    <row r="395" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="395" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A395" t="s">
         <v>889</v>
       </c>
@@ -20014,7 +20017,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="396" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="396" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A396" t="s">
         <v>889</v>
       </c>
@@ -20031,7 +20034,7 @@
         <v>978</v>
       </c>
     </row>
-    <row r="397" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="397" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A397" t="s">
         <v>889</v>
       </c>
@@ -20048,7 +20051,7 @@
         <v>979</v>
       </c>
     </row>
-    <row r="398" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="398" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A398" t="s">
         <v>890</v>
       </c>
@@ -20065,7 +20068,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="399" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="399" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A399" t="s">
         <v>890</v>
       </c>
@@ -20082,7 +20085,7 @@
         <v>980</v>
       </c>
     </row>
-    <row r="400" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="400" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A400" t="s">
         <v>890</v>
       </c>
@@ -20099,7 +20102,7 @@
         <v>981</v>
       </c>
     </row>
-    <row r="401" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="401" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A401" t="s">
         <v>891</v>
       </c>
@@ -20116,7 +20119,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="402" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="402" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A402" t="s">
         <v>891</v>
       </c>
@@ -20133,7 +20136,7 @@
         <v>982</v>
       </c>
     </row>
-    <row r="403" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="403" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A403" t="s">
         <v>891</v>
       </c>
@@ -20150,7 +20153,7 @@
         <v>983</v>
       </c>
     </row>
-    <row r="404" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="404" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A404" t="s">
         <v>892</v>
       </c>
@@ -20167,7 +20170,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="405" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="405" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A405" t="s">
         <v>892</v>
       </c>
@@ -20184,7 +20187,7 @@
         <v>984</v>
       </c>
     </row>
-    <row r="406" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="406" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A406" t="s">
         <v>892</v>
       </c>
@@ -20201,7 +20204,7 @@
         <v>985</v>
       </c>
     </row>
-    <row r="407" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="407" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A407" t="s">
         <v>893</v>
       </c>
@@ -20218,7 +20221,7 @@
         <v>986</v>
       </c>
     </row>
-    <row r="408" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="408" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A408" t="s">
         <v>893</v>
       </c>
@@ -20235,7 +20238,7 @@
         <v>987</v>
       </c>
     </row>
-    <row r="409" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="409" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A409" t="s">
         <v>893</v>
       </c>
@@ -20252,7 +20255,7 @@
         <v>988</v>
       </c>
     </row>
-    <row r="410" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="410" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A410" t="s">
         <v>894</v>
       </c>
@@ -20269,7 +20272,7 @@
         <v>989</v>
       </c>
     </row>
-    <row r="411" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="411" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A411" t="s">
         <v>894</v>
       </c>
@@ -20286,7 +20289,7 @@
         <v>990</v>
       </c>
     </row>
-    <row r="412" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="412" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A412" t="s">
         <v>894</v>
       </c>
@@ -20303,7 +20306,7 @@
         <v>991</v>
       </c>
     </row>
-    <row r="413" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="413" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A413" t="s">
         <v>895</v>
       </c>
@@ -20320,7 +20323,7 @@
         <v>992</v>
       </c>
     </row>
-    <row r="414" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="414" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A414" t="s">
         <v>895</v>
       </c>
@@ -20337,7 +20340,7 @@
         <v>993</v>
       </c>
     </row>
-    <row r="415" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="415" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A415" t="s">
         <v>895</v>
       </c>
@@ -20354,7 +20357,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="416" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="416" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A416" t="s">
         <v>896</v>
       </c>
@@ -20371,7 +20374,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="417" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="417" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A417" t="s">
         <v>896</v>
       </c>
@@ -20388,7 +20391,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="418" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="418" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A418" t="s">
         <v>896</v>
       </c>
@@ -20405,7 +20408,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="419" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="419" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A419" t="s">
         <v>897</v>
       </c>
@@ -20422,7 +20425,7 @@
         <v>1076</v>
       </c>
     </row>
-    <row r="420" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="420" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A420" t="s">
         <v>897</v>
       </c>
@@ -20439,7 +20442,7 @@
         <v>1077</v>
       </c>
     </row>
-    <row r="421" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="421" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A421" t="s">
         <v>897</v>
       </c>
@@ -20456,7 +20459,7 @@
         <v>1078</v>
       </c>
     </row>
-    <row r="422" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="422" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A422" t="s">
         <v>898</v>
       </c>
@@ -20473,7 +20476,7 @@
         <v>1079</v>
       </c>
     </row>
-    <row r="423" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="423" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A423" t="s">
         <v>898</v>
       </c>
@@ -20490,7 +20493,7 @@
         <v>1080</v>
       </c>
     </row>
-    <row r="424" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="424" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A424" t="s">
         <v>898</v>
       </c>
@@ -20507,7 +20510,7 @@
         <v>1081</v>
       </c>
     </row>
-    <row r="425" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="425" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A425" t="s">
         <v>899</v>
       </c>
@@ -20524,7 +20527,7 @@
         <v>1082</v>
       </c>
     </row>
-    <row r="426" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="426" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A426" t="s">
         <v>899</v>
       </c>
@@ -20541,7 +20544,7 @@
         <v>1083</v>
       </c>
     </row>
-    <row r="427" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="427" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A427" t="s">
         <v>899</v>
       </c>
@@ -20558,7 +20561,7 @@
         <v>1084</v>
       </c>
     </row>
-    <row r="428" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="428" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A428" t="s">
         <v>900</v>
       </c>
@@ -20575,7 +20578,7 @@
         <v>1085</v>
       </c>
     </row>
-    <row r="429" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="429" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A429" t="s">
         <v>900</v>
       </c>
@@ -20592,7 +20595,7 @@
         <v>1086</v>
       </c>
     </row>
-    <row r="430" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="430" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A430" t="s">
         <v>900</v>
       </c>
@@ -20609,7 +20612,7 @@
         <v>1087</v>
       </c>
     </row>
-    <row r="431" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="431" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A431" t="s">
         <v>901</v>
       </c>
@@ -20626,7 +20629,7 @@
         <v>1088</v>
       </c>
     </row>
-    <row r="432" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="432" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A432" t="s">
         <v>901</v>
       </c>
@@ -20643,7 +20646,7 @@
         <v>1089</v>
       </c>
     </row>
-    <row r="433" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="433" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A433" t="s">
         <v>901</v>
       </c>
@@ -20660,7 +20663,7 @@
         <v>1090</v>
       </c>
     </row>
-    <row r="434" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="434" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A434" t="s">
         <v>902</v>
       </c>
@@ -20677,7 +20680,7 @@
         <v>1091</v>
       </c>
     </row>
-    <row r="435" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="435" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A435" t="s">
         <v>902</v>
       </c>
@@ -20694,7 +20697,7 @@
         <v>1092</v>
       </c>
     </row>
-    <row r="436" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="436" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A436" t="s">
         <v>902</v>
       </c>
@@ -20711,7 +20714,7 @@
         <v>1093</v>
       </c>
     </row>
-    <row r="437" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="437" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A437" t="s">
         <v>903</v>
       </c>
@@ -20728,7 +20731,7 @@
         <v>1094</v>
       </c>
     </row>
-    <row r="438" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="438" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A438" t="s">
         <v>903</v>
       </c>
@@ -20745,7 +20748,7 @@
         <v>1094</v>
       </c>
     </row>
-    <row r="439" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="439" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A439" t="s">
         <v>903</v>
       </c>
@@ -20762,7 +20765,7 @@
         <v>1095</v>
       </c>
     </row>
-    <row r="440" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="440" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A440" t="s">
         <v>76</v>
       </c>
@@ -20779,7 +20782,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="441" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="441" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A441" t="s">
         <v>76</v>
       </c>
@@ -20796,7 +20799,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="442" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="442" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A442" t="s">
         <v>76</v>
       </c>
@@ -20813,7 +20816,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="443" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="443" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A443" t="s">
         <v>995</v>
       </c>
@@ -20830,7 +20833,7 @@
         <v>1096</v>
       </c>
     </row>
-    <row r="444" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="444" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A444" t="s">
         <v>995</v>
       </c>
@@ -20847,7 +20850,7 @@
         <v>1097</v>
       </c>
     </row>
-    <row r="445" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="445" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A445" t="s">
         <v>995</v>
       </c>
@@ -20864,7 +20867,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="446" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="446" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A446" t="s">
         <v>996</v>
       </c>
@@ -20881,7 +20884,7 @@
         <v>1099</v>
       </c>
     </row>
-    <row r="447" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="447" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A447" t="s">
         <v>996</v>
       </c>
@@ -20898,7 +20901,7 @@
         <v>1101</v>
       </c>
     </row>
-    <row r="448" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="448" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A448" t="s">
         <v>996</v>
       </c>
@@ -20915,7 +20918,7 @@
         <v>1100</v>
       </c>
     </row>
-    <row r="449" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="449" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A449" t="s">
         <v>997</v>
       </c>
@@ -20932,7 +20935,7 @@
         <v>1103</v>
       </c>
     </row>
-    <row r="450" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="450" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A450" t="s">
         <v>997</v>
       </c>
@@ -20949,7 +20952,7 @@
         <v>1104</v>
       </c>
     </row>
-    <row r="451" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="451" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A451" t="s">
         <v>997</v>
       </c>
@@ -20966,7 +20969,7 @@
         <v>1105</v>
       </c>
     </row>
-    <row r="452" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="452" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A452" t="s">
         <v>998</v>
       </c>
@@ -20983,7 +20986,7 @@
         <v>1106</v>
       </c>
     </row>
-    <row r="453" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="453" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A453" t="s">
         <v>998</v>
       </c>
@@ -21000,7 +21003,7 @@
         <v>1107</v>
       </c>
     </row>
-    <row r="454" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="454" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A454" t="s">
         <v>998</v>
       </c>
@@ -21017,7 +21020,7 @@
         <v>1108</v>
       </c>
     </row>
-    <row r="455" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="455" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A455" t="s">
         <v>999</v>
       </c>
@@ -21034,7 +21037,7 @@
         <v>1109</v>
       </c>
     </row>
-    <row r="456" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="456" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A456" t="s">
         <v>999</v>
       </c>
@@ -21051,7 +21054,7 @@
         <v>1110</v>
       </c>
     </row>
-    <row r="457" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="457" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A457" t="s">
         <v>999</v>
       </c>
@@ -21068,7 +21071,7 @@
         <v>1111</v>
       </c>
     </row>
-    <row r="458" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="458" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A458" t="s">
         <v>1000</v>
       </c>
@@ -21085,7 +21088,7 @@
         <v>1112</v>
       </c>
     </row>
-    <row r="459" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="459" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A459" t="s">
         <v>1000</v>
       </c>
@@ -21102,7 +21105,7 @@
         <v>1113</v>
       </c>
     </row>
-    <row r="460" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="460" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A460" t="s">
         <v>1000</v>
       </c>
@@ -21119,7 +21122,7 @@
         <v>1114</v>
       </c>
     </row>
-    <row r="461" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="461" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A461" t="s">
         <v>1001</v>
       </c>
@@ -21136,7 +21139,7 @@
         <v>1116</v>
       </c>
     </row>
-    <row r="462" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="462" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A462" t="s">
         <v>1001</v>
       </c>
@@ -21153,7 +21156,7 @@
         <v>1117</v>
       </c>
     </row>
-    <row r="463" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="463" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A463" t="s">
         <v>1001</v>
       </c>
@@ -21170,7 +21173,7 @@
         <v>1118</v>
       </c>
     </row>
-    <row r="464" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="464" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A464" t="s">
         <v>1002</v>
       </c>
@@ -21187,7 +21190,7 @@
         <v>1122</v>
       </c>
     </row>
-    <row r="465" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="465" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A465" t="s">
         <v>1002</v>
       </c>
@@ -21204,7 +21207,7 @@
         <v>1123</v>
       </c>
     </row>
-    <row r="466" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="466" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A466" t="s">
         <v>1002</v>
       </c>
@@ -21221,7 +21224,7 @@
         <v>1124</v>
       </c>
     </row>
-    <row r="467" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="467" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A467" t="s">
         <v>1003</v>
       </c>
@@ -21238,7 +21241,7 @@
         <v>1125</v>
       </c>
     </row>
-    <row r="468" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="468" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A468" t="s">
         <v>1003</v>
       </c>
@@ -21255,7 +21258,7 @@
         <v>1126</v>
       </c>
     </row>
-    <row r="469" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="469" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A469" t="s">
         <v>1003</v>
       </c>
@@ -21272,7 +21275,7 @@
         <v>1127</v>
       </c>
     </row>
-    <row r="470" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="470" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A470" t="s">
         <v>1004</v>
       </c>
@@ -21289,7 +21292,7 @@
         <v>1119</v>
       </c>
     </row>
-    <row r="471" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="471" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A471" t="s">
         <v>1004</v>
       </c>
@@ -21306,7 +21309,7 @@
         <v>1120</v>
       </c>
     </row>
-    <row r="472" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="472" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A472" t="s">
         <v>1004</v>
       </c>
@@ -21323,7 +21326,7 @@
         <v>1121</v>
       </c>
     </row>
-    <row r="473" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="473" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A473" t="s">
         <v>1005</v>
       </c>
@@ -21340,7 +21343,7 @@
         <v>1128</v>
       </c>
     </row>
-    <row r="474" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="474" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A474" t="s">
         <v>1005</v>
       </c>
@@ -21357,7 +21360,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="475" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="475" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A475" t="s">
         <v>1005</v>
       </c>
@@ -21374,7 +21377,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="476" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="476" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A476" t="s">
         <v>1006</v>
       </c>
@@ -21391,7 +21394,7 @@
         <v>1130</v>
       </c>
     </row>
-    <row r="477" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="477" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A477" t="s">
         <v>1006</v>
       </c>
@@ -21408,7 +21411,7 @@
         <v>1131</v>
       </c>
     </row>
-    <row r="478" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="478" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A478" t="s">
         <v>1006</v>
       </c>
@@ -21425,7 +21428,7 @@
         <v>1132</v>
       </c>
     </row>
-    <row r="479" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="479" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A479" t="s">
         <v>1007</v>
       </c>
@@ -21442,7 +21445,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="480" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="480" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A480" t="s">
         <v>1007</v>
       </c>
@@ -21459,7 +21462,7 @@
         <v>1134</v>
       </c>
     </row>
-    <row r="481" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="481" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A481" t="s">
         <v>1007</v>
       </c>
@@ -21476,7 +21479,7 @@
         <v>1135</v>
       </c>
     </row>
-    <row r="482" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="482" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A482" t="s">
         <v>1008</v>
       </c>
@@ -21493,7 +21496,7 @@
         <v>1136</v>
       </c>
     </row>
-    <row r="483" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="483" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A483" t="s">
         <v>1008</v>
       </c>
@@ -21510,7 +21513,7 @@
         <v>1137</v>
       </c>
     </row>
-    <row r="484" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="484" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A484" t="s">
         <v>1008</v>
       </c>
@@ -21527,7 +21530,7 @@
         <v>1138</v>
       </c>
     </row>
-    <row r="485" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="485" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A485" t="s">
         <v>1009</v>
       </c>
@@ -21544,7 +21547,7 @@
         <v>1209</v>
       </c>
     </row>
-    <row r="486" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="486" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A486" t="s">
         <v>1009</v>
       </c>
@@ -21561,7 +21564,7 @@
         <v>1210</v>
       </c>
     </row>
-    <row r="487" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="487" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A487" t="s">
         <v>1009</v>
       </c>
@@ -21578,7 +21581,7 @@
         <v>1211</v>
       </c>
     </row>
-    <row r="488" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="488" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A488" t="s">
         <v>1010</v>
       </c>
@@ -21595,7 +21598,7 @@
         <v>1212</v>
       </c>
     </row>
-    <row r="489" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="489" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A489" t="s">
         <v>1010</v>
       </c>
@@ -21612,7 +21615,7 @@
         <v>1213</v>
       </c>
     </row>
-    <row r="490" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="490" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A490" t="s">
         <v>1010</v>
       </c>
@@ -21629,7 +21632,7 @@
         <v>1214</v>
       </c>
     </row>
-    <row r="491" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="491" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A491" t="s">
         <v>1011</v>
       </c>
@@ -21646,7 +21649,7 @@
         <v>1215</v>
       </c>
     </row>
-    <row r="492" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="492" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A492" t="s">
         <v>1011</v>
       </c>
@@ -21663,7 +21666,7 @@
         <v>1216</v>
       </c>
     </row>
-    <row r="493" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="493" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A493" t="s">
         <v>1011</v>
       </c>
@@ -21680,7 +21683,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="494" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="494" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A494" t="s">
         <v>1012</v>
       </c>
@@ -21697,7 +21700,7 @@
         <v>1217</v>
       </c>
     </row>
-    <row r="495" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="495" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A495" t="s">
         <v>1012</v>
       </c>
@@ -21714,7 +21717,7 @@
         <v>1218</v>
       </c>
     </row>
-    <row r="496" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="496" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A496" t="s">
         <v>1012</v>
       </c>
@@ -21731,7 +21734,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="497" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="497" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A497" t="s">
         <v>1013</v>
       </c>
@@ -21748,7 +21751,7 @@
         <v>1219</v>
       </c>
     </row>
-    <row r="498" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="498" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A498" t="s">
         <v>1013</v>
       </c>
@@ -21765,7 +21768,7 @@
         <v>1220</v>
       </c>
     </row>
-    <row r="499" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="499" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A499" t="s">
         <v>1013</v>
       </c>
@@ -21782,7 +21785,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="500" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="500" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A500" t="s">
         <v>23</v>
       </c>
@@ -21799,7 +21802,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="501" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="501" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A501" t="s">
         <v>23</v>
       </c>
@@ -21816,7 +21819,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="502" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="502" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A502" t="s">
         <v>23</v>
       </c>
@@ -21833,7 +21836,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="503" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="503" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A503" t="s">
         <v>1139</v>
       </c>
@@ -21850,7 +21853,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="504" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="504" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A504" t="s">
         <v>1139</v>
       </c>
@@ -21867,7 +21870,7 @@
         <v>1222</v>
       </c>
     </row>
-    <row r="505" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="505" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A505" t="s">
         <v>1139</v>
       </c>
@@ -21884,7 +21887,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="506" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="506" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A506" t="s">
         <v>1140</v>
       </c>
@@ -21901,7 +21904,7 @@
         <v>1225</v>
       </c>
     </row>
-    <row r="507" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="507" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A507" t="s">
         <v>1140</v>
       </c>
@@ -21918,7 +21921,7 @@
         <v>1223</v>
       </c>
     </row>
-    <row r="508" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="508" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A508" t="s">
         <v>1140</v>
       </c>
@@ -21935,7 +21938,7 @@
         <v>1224</v>
       </c>
     </row>
-    <row r="509" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="509" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A509" t="s">
         <v>1141</v>
       </c>
@@ -21952,7 +21955,7 @@
         <v>1225</v>
       </c>
     </row>
-    <row r="510" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="510" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A510" t="s">
         <v>1141</v>
       </c>
@@ -21969,7 +21972,7 @@
         <v>1226</v>
       </c>
     </row>
-    <row r="511" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="511" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A511" t="s">
         <v>1141</v>
       </c>
@@ -21986,7 +21989,7 @@
         <v>1227</v>
       </c>
     </row>
-    <row r="512" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="512" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A512" t="s">
         <v>1142</v>
       </c>
@@ -22003,7 +22006,7 @@
         <v>1228</v>
       </c>
     </row>
-    <row r="513" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="513" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A513" t="s">
         <v>1142</v>
       </c>
@@ -22020,7 +22023,7 @@
         <v>1229</v>
       </c>
     </row>
-    <row r="514" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="514" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A514" t="s">
         <v>1142</v>
       </c>
@@ -22037,7 +22040,7 @@
         <v>1230</v>
       </c>
     </row>
-    <row r="515" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="515" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A515" t="s">
         <v>1143</v>
       </c>
@@ -22054,7 +22057,7 @@
         <v>1231</v>
       </c>
     </row>
-    <row r="516" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="516" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A516" t="s">
         <v>1143</v>
       </c>
@@ -22071,7 +22074,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="517" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="517" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A517" t="s">
         <v>1143</v>
       </c>
@@ -22088,7 +22091,7 @@
         <v>1233</v>
       </c>
     </row>
-    <row r="518" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="518" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A518" t="s">
         <v>1144</v>
       </c>
@@ -22105,7 +22108,7 @@
         <v>696</v>
       </c>
     </row>
-    <row r="519" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="519" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A519" t="s">
         <v>1144</v>
       </c>
@@ -22122,7 +22125,7 @@
         <v>1225</v>
       </c>
     </row>
-    <row r="520" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="520" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A520" t="s">
         <v>1144</v>
       </c>
@@ -22139,7 +22142,7 @@
         <v>1234</v>
       </c>
     </row>
-    <row r="521" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="521" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A521" t="s">
         <v>1145</v>
       </c>
@@ -22156,7 +22159,7 @@
         <v>1225</v>
       </c>
     </row>
-    <row r="522" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="522" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A522" t="s">
         <v>1145</v>
       </c>
@@ -22173,7 +22176,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="523" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="523" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A523" t="s">
         <v>1145</v>
       </c>
@@ -22190,7 +22193,7 @@
         <v>1235</v>
       </c>
     </row>
-    <row r="524" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="524" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A524" t="s">
         <v>1146</v>
       </c>
@@ -22207,7 +22210,7 @@
         <v>1225</v>
       </c>
     </row>
-    <row r="525" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="525" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A525" t="s">
         <v>1146</v>
       </c>
@@ -22224,7 +22227,7 @@
         <v>1236</v>
       </c>
     </row>
-    <row r="526" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="526" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A526" t="s">
         <v>1146</v>
       </c>
@@ -22241,7 +22244,7 @@
         <v>1237</v>
       </c>
     </row>
-    <row r="527" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="527" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A527" t="s">
         <v>1147</v>
       </c>
@@ -22258,7 +22261,7 @@
         <v>1238</v>
       </c>
     </row>
-    <row r="528" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="528" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A528" t="s">
         <v>1147</v>
       </c>
@@ -22275,7 +22278,7 @@
         <v>1239</v>
       </c>
     </row>
-    <row r="529" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="529" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A529" t="s">
         <v>1147</v>
       </c>
@@ -22292,7 +22295,7 @@
         <v>1240</v>
       </c>
     </row>
-    <row r="530" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="530" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A530" t="s">
         <v>1148</v>
       </c>
@@ -22309,7 +22312,7 @@
         <v>1241</v>
       </c>
     </row>
-    <row r="531" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="531" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A531" t="s">
         <v>1148</v>
       </c>
@@ -22326,7 +22329,7 @@
         <v>1242</v>
       </c>
     </row>
-    <row r="532" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="532" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A532" t="s">
         <v>1148</v>
       </c>
@@ -22343,7 +22346,7 @@
         <v>1243</v>
       </c>
     </row>
-    <row r="533" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="533" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A533" t="s">
         <v>29</v>
       </c>
@@ -22360,7 +22363,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="534" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="534" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A534" t="s">
         <v>29</v>
       </c>
@@ -22377,7 +22380,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="535" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="535" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A535" t="s">
         <v>29</v>
       </c>
@@ -22394,7 +22397,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="536" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="536" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A536" t="s">
         <v>1149</v>
       </c>
@@ -22411,7 +22414,7 @@
         <v>1244</v>
       </c>
     </row>
-    <row r="537" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="537" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A537" t="s">
         <v>1149</v>
       </c>
@@ -22428,7 +22431,7 @@
         <v>1245</v>
       </c>
     </row>
-    <row r="538" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="538" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A538" t="s">
         <v>1149</v>
       </c>
@@ -22445,7 +22448,7 @@
         <v>1246</v>
       </c>
     </row>
-    <row r="539" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="539" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A539" t="s">
         <v>1150</v>
       </c>
@@ -22462,7 +22465,7 @@
         <v>1247</v>
       </c>
     </row>
-    <row r="540" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="540" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A540" t="s">
         <v>1150</v>
       </c>
@@ -22479,7 +22482,7 @@
         <v>1248</v>
       </c>
     </row>
-    <row r="541" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="541" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A541" t="s">
         <v>1150</v>
       </c>
@@ -22496,7 +22499,7 @@
         <v>1249</v>
       </c>
     </row>
-    <row r="542" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="542" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A542" t="s">
         <v>1151</v>
       </c>
@@ -22513,7 +22516,7 @@
         <v>1250</v>
       </c>
     </row>
-    <row r="543" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="543" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A543" t="s">
         <v>1151</v>
       </c>
@@ -22530,7 +22533,7 @@
         <v>1251</v>
       </c>
     </row>
-    <row r="544" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="544" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A544" t="s">
         <v>1151</v>
       </c>
@@ -22547,7 +22550,7 @@
         <v>1252</v>
       </c>
     </row>
-    <row r="545" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="545" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A545" t="s">
         <v>1152</v>
       </c>
@@ -22564,7 +22567,7 @@
         <v>1253</v>
       </c>
     </row>
-    <row r="546" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="546" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A546" t="s">
         <v>1152</v>
       </c>
@@ -22581,7 +22584,7 @@
         <v>1254</v>
       </c>
     </row>
-    <row r="547" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="547" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A547" t="s">
         <v>1152</v>
       </c>
@@ -22598,7 +22601,7 @@
         <v>1255</v>
       </c>
     </row>
-    <row r="548" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="548" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A548" t="s">
         <v>1153</v>
       </c>
@@ -22615,7 +22618,7 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="549" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="549" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A549" t="s">
         <v>1153</v>
       </c>
@@ -22632,7 +22635,7 @@
         <v>1257</v>
       </c>
     </row>
-    <row r="550" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="550" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A550" t="s">
         <v>1153</v>
       </c>
@@ -22649,7 +22652,7 @@
         <v>1258</v>
       </c>
     </row>
-    <row r="551" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="551" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A551" t="s">
         <v>36</v>
       </c>
@@ -22666,7 +22669,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="552" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="552" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A552" t="s">
         <v>36</v>
       </c>
@@ -22683,7 +22686,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="553" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="553" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A553" t="s">
         <v>36</v>
       </c>
@@ -22709,17 +22712,17 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{494C60D6-2426-4CE0-9CA4-43EAAA3DD51B}">
   <dimension ref="A1:F26"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.73046875" customWidth="1"/>
-    <col min="2" max="2" width="22.19921875" customWidth="1"/>
-    <col min="3" max="3" width="18.265625" customWidth="1"/>
+    <col min="1" max="1" width="11.7109375" customWidth="1"/>
+    <col min="2" max="2" width="22.140625" customWidth="1"/>
+    <col min="3" max="3" width="18.28515625" customWidth="1"/>
     <col min="4" max="4" width="18" customWidth="1"/>
-    <col min="5" max="5" width="11.86328125" customWidth="1"/>
-    <col min="6" max="6" width="14.59765625" customWidth="1"/>
+    <col min="5" max="5" width="11.85546875" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -22739,7 +22742,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>113</v>
       </c>
@@ -22759,7 +22762,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>113</v>
       </c>
@@ -22779,7 +22782,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>113</v>
       </c>
@@ -22799,7 +22802,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>348</v>
       </c>
@@ -22819,7 +22822,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>348</v>
       </c>
@@ -22839,7 +22842,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>348</v>
       </c>
@@ -22859,7 +22862,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>348</v>
       </c>
@@ -22879,7 +22882,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>757</v>
       </c>
@@ -22899,7 +22902,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>757</v>
       </c>
@@ -22919,7 +22922,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>757</v>
       </c>
@@ -22939,7 +22942,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>757</v>
       </c>
@@ -22959,7 +22962,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>757</v>
       </c>
@@ -22979,7 +22982,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>757</v>
       </c>
@@ -22999,7 +23002,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>757</v>
       </c>
@@ -23019,7 +23022,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>757</v>
       </c>
@@ -23039,7 +23042,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>757</v>
       </c>
@@ -23059,7 +23062,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>757</v>
       </c>
@@ -23079,7 +23082,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>757</v>
       </c>
@@ -23099,7 +23102,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>757</v>
       </c>
@@ -23119,7 +23122,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>757</v>
       </c>
@@ -23139,7 +23142,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>1140</v>
       </c>
@@ -23159,7 +23162,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>1141</v>
       </c>
@@ -23179,7 +23182,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>1144</v>
       </c>
@@ -23199,7 +23202,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>1145</v>
       </c>
@@ -23219,7 +23222,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>1146</v>
       </c>
@@ -23247,16 +23250,17 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32F3CD10-C054-4484-ABE2-D426F834FC22}">
-  <dimension ref="A1:F67"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:G67"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.3984375" customWidth="1"/>
+    <col min="1" max="1" width="13.42578125" customWidth="1"/>
     <col min="2" max="3" width="26" customWidth="1"/>
-    <col min="4" max="5" width="20.46484375" customWidth="1"/>
-    <col min="6" max="6" width="11.46484375" customWidth="1"/>
+    <col min="4" max="5" width="20.42578125" customWidth="1"/>
+    <col min="6" max="6" width="11.42578125" customWidth="1"/>
+    <col min="7" max="7" width="15.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>1263</v>
       </c>
@@ -23276,7 +23280,7 @@
         <v>1466</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1264</v>
       </c>
@@ -23293,7 +23297,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>1265</v>
       </c>
@@ -23310,7 +23314,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>1266</v>
       </c>
@@ -23327,7 +23331,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>1267</v>
       </c>
@@ -23344,7 +23348,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>1268</v>
       </c>
@@ -23361,7 +23365,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>1269</v>
       </c>
@@ -23378,7 +23382,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>1270</v>
       </c>
@@ -23395,7 +23399,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>1271</v>
       </c>
@@ -23412,7 +23416,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>1272</v>
       </c>
@@ -23426,7 +23430,7 @@
         <v>1337</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>1273</v>
       </c>
@@ -23443,7 +23447,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>1274</v>
       </c>
@@ -23460,7 +23464,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>1275</v>
       </c>
@@ -23474,7 +23478,7 @@
         <v>1333</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>1276</v>
       </c>
@@ -23491,7 +23495,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>1277</v>
       </c>
@@ -23505,7 +23509,7 @@
         <v>1335</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>1278</v>
       </c>
@@ -23522,7 +23526,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>1279</v>
       </c>
@@ -23539,7 +23543,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>1280</v>
       </c>
@@ -23553,7 +23557,7 @@
         <v>1334</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>1281</v>
       </c>
@@ -23570,7 +23574,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>1282</v>
       </c>
@@ -23587,7 +23591,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>1283</v>
       </c>
@@ -23604,7 +23608,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>1284</v>
       </c>
@@ -23621,7 +23625,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>1285</v>
       </c>
@@ -23638,7 +23642,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>1286</v>
       </c>
@@ -23655,7 +23659,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>1287</v>
       </c>
@@ -23669,7 +23673,7 @@
         <v>1333</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>1288</v>
       </c>
@@ -23686,7 +23690,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>1289</v>
       </c>
@@ -23700,7 +23704,7 @@
         <v>1334</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>1290</v>
       </c>
@@ -23713,11 +23717,8 @@
       <c r="D28" t="s">
         <v>1333</v>
       </c>
-      <c r="E28" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.45">
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>1291</v>
       </c>
@@ -23733,8 +23734,11 @@
       <c r="E29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F29" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>1292</v>
       </c>
@@ -23748,7 +23752,7 @@
         <v>1334</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>1293</v>
       </c>
@@ -23762,7 +23766,7 @@
         <v>1335</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>1294</v>
       </c>
@@ -23779,7 +23783,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>1295</v>
       </c>
@@ -23796,7 +23800,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>1296</v>
       </c>
@@ -23813,7 +23817,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>1297</v>
       </c>
@@ -23827,7 +23831,7 @@
         <v>1335</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>1298</v>
       </c>
@@ -23844,7 +23848,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>1299</v>
       </c>
@@ -23861,7 +23865,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>1300</v>
       </c>
@@ -23878,7 +23882,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>1301</v>
       </c>
@@ -23892,7 +23896,7 @@
         <v>1373</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>1302</v>
       </c>
@@ -23905,8 +23909,11 @@
       <c r="D40" t="s">
         <v>1334</v>
       </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F40" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>1303</v>
       </c>
@@ -23923,7 +23930,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>1304</v>
       </c>
@@ -23939,8 +23946,11 @@
       <c r="E42" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F42" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>1305</v>
       </c>
@@ -23954,7 +23964,7 @@
         <v>1335</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>1306</v>
       </c>
@@ -23970,8 +23980,11 @@
       <c r="E44" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F44" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>1307</v>
       </c>
@@ -23987,8 +24000,11 @@
       <c r="E45" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F45" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>1308</v>
       </c>
@@ -24004,8 +24020,11 @@
       <c r="E46" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F46" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>1309</v>
       </c>
@@ -24021,8 +24040,11 @@
       <c r="E47" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F47" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>1310</v>
       </c>
@@ -24038,8 +24060,11 @@
       <c r="E48" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F48" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>1311</v>
       </c>
@@ -24056,7 +24081,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>1312</v>
       </c>
@@ -24073,7 +24098,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>1313</v>
       </c>
@@ -24090,7 +24115,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>1314</v>
       </c>
@@ -24107,7 +24132,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>1315</v>
       </c>
@@ -24121,7 +24146,7 @@
         <v>1334</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>1316</v>
       </c>
@@ -24134,8 +24159,11 @@
       <c r="D54" t="s">
         <v>1373</v>
       </c>
-    </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="E54" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>1317</v>
       </c>
@@ -24148,8 +24176,11 @@
       <c r="D55" t="s">
         <v>1333</v>
       </c>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="G55" t="s">
+        <v>1885</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>1318</v>
       </c>
@@ -24162,8 +24193,11 @@
       <c r="D56" t="s">
         <v>1333</v>
       </c>
-    </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="G56" t="s">
+        <v>1885</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>1319</v>
       </c>
@@ -24176,8 +24210,11 @@
       <c r="D57" t="s">
         <v>1333</v>
       </c>
-    </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="G57" t="s">
+        <v>1885</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>1320</v>
       </c>
@@ -24190,8 +24227,11 @@
       <c r="D58" t="s">
         <v>1334</v>
       </c>
-    </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="G58" t="s">
+        <v>1885</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>1321</v>
       </c>
@@ -24204,8 +24244,11 @@
       <c r="D59" t="s">
         <v>1334</v>
       </c>
-    </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="E59" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>1322</v>
       </c>
@@ -24218,8 +24261,11 @@
       <c r="D60" t="s">
         <v>1334</v>
       </c>
-    </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="G60" t="s">
+        <v>1885</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>1323</v>
       </c>
@@ -24232,8 +24278,11 @@
       <c r="D61" t="s">
         <v>1334</v>
       </c>
-    </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="G61" t="s">
+        <v>1885</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>1324</v>
       </c>
@@ -24246,8 +24295,11 @@
       <c r="D62" t="s">
         <v>1333</v>
       </c>
-    </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="G62" t="s">
+        <v>1885</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>1325</v>
       </c>
@@ -24260,8 +24312,11 @@
       <c r="D63" t="s">
         <v>1333</v>
       </c>
-    </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="E63" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>1326</v>
       </c>
@@ -24274,8 +24329,14 @@
       <c r="D64" t="s">
         <v>1333</v>
       </c>
-    </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E64" t="b">
+        <v>1</v>
+      </c>
+      <c r="F64" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>1327</v>
       </c>
@@ -24288,8 +24349,11 @@
       <c r="D65" t="s">
         <v>1333</v>
       </c>
-    </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E65" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>1328</v>
       </c>
@@ -24302,8 +24366,11 @@
       <c r="D66" t="s">
         <v>1335</v>
       </c>
-    </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E66" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>1329</v>
       </c>
@@ -24327,7 +24394,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{931309AC-3B5D-4169-8BD3-83BC320E154C}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/Fate-Spreadsheet.xlsx
+++ b/data/Fate-Spreadsheet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Important\Python\Fate-Wiki\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{001A512E-D5B4-4085-BE1C-40AEE1E14FDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC913088-FB2B-4D96-888D-BB83772D4FE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="1" activeTab="5" xr2:uid="{B05E798F-9EF6-4508-A0A4-311D06661AED}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="5" xr2:uid="{B05E798F-9EF6-4508-A0A4-311D06661AED}"/>
   </bookViews>
   <sheets>
     <sheet name="Servants" sheetId="1" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4226" uniqueCount="1886">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4230" uniqueCount="1891">
   <si>
     <t>servant_id</t>
   </si>
@@ -5702,7 +5702,22 @@
     <t>has_abilities</t>
   </si>
   <si>
-    <t>NEED TO FIX PICS</t>
+    <t>is_beta_servant</t>
+  </si>
+  <si>
+    <t>is_custom_servant</t>
+  </si>
+  <si>
+    <t>servant_maker</t>
+  </si>
+  <si>
+    <t>webp fix</t>
+  </si>
+  <si>
+    <t>is_ability</t>
+  </si>
+  <si>
+    <t>is_asset</t>
   </si>
 </sst>
 </file>
@@ -6091,7 +6106,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E33D7ECC-1EAA-4A40-B4DA-A93E54CBC8B5}">
-  <dimension ref="A1:P185"/>
+  <dimension ref="A1:Q185"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="3" width="22" customWidth="1"/>
@@ -6106,11 +6121,12 @@
     <col min="12" max="12" width="11" customWidth="1"/>
     <col min="13" max="13" width="45.7109375" customWidth="1"/>
     <col min="14" max="14" width="41.28515625" customWidth="1"/>
-    <col min="15" max="15" width="11.85546875" customWidth="1"/>
+    <col min="15" max="15" width="17.140625" customWidth="1"/>
     <col min="16" max="16" width="18.140625" customWidth="1"/>
+    <col min="17" max="17" width="16.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -6153,10 +6169,17 @@
       <c r="N1" s="3" t="s">
         <v>1516</v>
       </c>
-      <c r="O1" s="3"/>
-      <c r="P1" s="3"/>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="O1" s="3" t="s">
+        <v>1885</v>
+      </c>
+      <c r="P1" s="3" t="s">
+        <v>1886</v>
+      </c>
+      <c r="Q1" s="3" t="s">
+        <v>1887</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -6191,7 +6214,7 @@
         <v>1510</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>111</v>
       </c>
@@ -6226,7 +6249,7 @@
         <v>1512</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>112</v>
       </c>
@@ -6258,7 +6281,7 @@
         <v>1518</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>113</v>
       </c>
@@ -6293,7 +6316,7 @@
         <v>1527</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>114</v>
       </c>
@@ -6328,7 +6351,7 @@
         <v>1525</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>115</v>
       </c>
@@ -6363,7 +6386,7 @@
         <v>1536</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>116</v>
       </c>
@@ -6398,7 +6421,7 @@
         <v>1538</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>117</v>
       </c>
@@ -6430,7 +6453,7 @@
         <v>1541</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>118</v>
       </c>
@@ -6465,7 +6488,7 @@
         <v>1542</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>119</v>
       </c>
@@ -6500,7 +6523,7 @@
         <v>1546</v>
       </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>120</v>
       </c>
@@ -6535,7 +6558,7 @@
         <v>1549</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>121</v>
       </c>
@@ -6567,7 +6590,7 @@
         <v>1555</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>122</v>
       </c>
@@ -6602,7 +6625,7 @@
         <v>1557</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>123</v>
       </c>
@@ -6637,7 +6660,7 @@
         <v>1561</v>
       </c>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>124</v>
       </c>
@@ -13315,9 +13338,7 @@
       <c r="F1" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>1259</v>
-      </c>
+      <c r="G1" s="1"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
@@ -24176,8 +24197,8 @@
       <c r="D55" t="s">
         <v>1333</v>
       </c>
-      <c r="G55" t="s">
-        <v>1885</v>
+      <c r="E55" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
@@ -24193,8 +24214,8 @@
       <c r="D56" t="s">
         <v>1333</v>
       </c>
-      <c r="G56" t="s">
-        <v>1885</v>
+      <c r="E56" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
@@ -24210,8 +24231,8 @@
       <c r="D57" t="s">
         <v>1333</v>
       </c>
-      <c r="G57" t="s">
-        <v>1885</v>
+      <c r="E57" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
@@ -24227,8 +24248,8 @@
       <c r="D58" t="s">
         <v>1334</v>
       </c>
-      <c r="G58" t="s">
-        <v>1885</v>
+      <c r="E58" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
@@ -24261,8 +24282,8 @@
       <c r="D60" t="s">
         <v>1334</v>
       </c>
-      <c r="G60" t="s">
-        <v>1885</v>
+      <c r="E60" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
@@ -24278,8 +24299,14 @@
       <c r="D61" t="s">
         <v>1334</v>
       </c>
+      <c r="E61" t="b">
+        <v>1</v>
+      </c>
+      <c r="F61" t="b">
+        <v>1</v>
+      </c>
       <c r="G61" t="s">
-        <v>1885</v>
+        <v>1888</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
@@ -24295,8 +24322,11 @@
       <c r="D62" t="s">
         <v>1333</v>
       </c>
+      <c r="E62" t="b">
+        <v>1</v>
+      </c>
       <c r="G62" t="s">
-        <v>1885</v>
+        <v>1888</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
@@ -24393,9 +24423,42 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{931309AC-3B5D-4169-8BD3-83BC320E154C}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="13.7109375" customWidth="1"/>
+    <col min="2" max="2" width="17.85546875" customWidth="1"/>
+    <col min="3" max="3" width="14.5703125" customWidth="1"/>
+    <col min="4" max="4" width="12.42578125" customWidth="1"/>
+    <col min="5" max="5" width="11.5703125" customWidth="1"/>
+    <col min="6" max="6" width="10.5703125" customWidth="1"/>
+    <col min="7" max="7" width="11.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>1263</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1330</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>1467</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>1889</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>1890</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/data/Fate-Spreadsheet.xlsx
+++ b/data/Fate-Spreadsheet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Important\Python\Fate-Wiki\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC913088-FB2B-4D96-888D-BB83772D4FE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{467A7EFF-9F84-4DAE-8E3D-19F96EF57D69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="5" xr2:uid="{B05E798F-9EF6-4508-A0A4-311D06661AED}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{B05E798F-9EF6-4508-A0A4-311D06661AED}"/>
   </bookViews>
   <sheets>
     <sheet name="Servants" sheetId="1" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4230" uniqueCount="1891">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4360" uniqueCount="1945">
   <si>
     <t>servant_id</t>
   </si>
@@ -5708,9 +5708,6 @@
     <t>is_custom_servant</t>
   </si>
   <si>
-    <t>servant_maker</t>
-  </si>
-  <si>
     <t>webp fix</t>
   </si>
   <si>
@@ -5718,6 +5715,171 @@
   </si>
   <si>
     <t>is_asset</t>
+  </si>
+  <si>
+    <t>servant_creator</t>
+  </si>
+  <si>
+    <t>profile_artist</t>
+  </si>
+  <si>
+    <t>card-artist</t>
+  </si>
+  <si>
+    <t>card_artist</t>
+  </si>
+  <si>
+    <t>is_beta_master</t>
+  </si>
+  <si>
+    <t>is_custom_master</t>
+  </si>
+  <si>
+    <t>master_maker</t>
+  </si>
+  <si>
+    <t>archetype_artist</t>
+  </si>
+  <si>
+    <t>S0185</t>
+  </si>
+  <si>
+    <t>Ibuki Douji</t>
+  </si>
+  <si>
+    <t>ibuki-douji</t>
+  </si>
+  <si>
+    <t>S0186</t>
+  </si>
+  <si>
+    <t>S0187</t>
+  </si>
+  <si>
+    <t>Demon God</t>
+  </si>
+  <si>
+    <t>Kusanagi</t>
+  </si>
+  <si>
+    <t>No Abilities</t>
+  </si>
+  <si>
+    <t>Minamoto no Tametomo</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>Luck,Luck,Luck,Surveil,Surveil,Surveil,Preparation,Preparation,Preparation</t>
+  </si>
+  <si>
+    <t>minamoto-no-tametomo</t>
+  </si>
+  <si>
+    <t>Quickshot</t>
+  </si>
+  <si>
+    <t>Mechanical Archery</t>
+  </si>
+  <si>
+    <t>Gouchin</t>
+  </si>
+  <si>
+    <t>Player Elimination</t>
+  </si>
+  <si>
+    <t>Gray</t>
+  </si>
+  <si>
+    <t>gray</t>
+  </si>
+  <si>
+    <t>Player Elimination,VP Gain,Assassination</t>
+  </si>
+  <si>
+    <t>Low Power,Mana Hungry,No Luck</t>
+  </si>
+  <si>
+    <t>Anti-Spirit Arts</t>
+  </si>
+  <si>
+    <t>S0188</t>
+  </si>
+  <si>
+    <t>Queen Draco</t>
+  </si>
+  <si>
+    <t>queen-draco</t>
+  </si>
+  <si>
+    <t>Beast</t>
+  </si>
+  <si>
+    <t>High Power,Adaptable</t>
+  </si>
+  <si>
+    <t>No Luck,Mana Hungry</t>
+  </si>
+  <si>
+    <t>Beast Class</t>
+  </si>
+  <si>
+    <t>is_shared_asset</t>
+  </si>
+  <si>
+    <t>Bestia Coccinea</t>
+  </si>
+  <si>
+    <t>Laus Tyranno Claudius</t>
+  </si>
+  <si>
+    <t>Saber's Pride</t>
+  </si>
+  <si>
+    <t>Sabers-Pride</t>
+  </si>
+  <si>
+    <t>Lancer's Lust</t>
+  </si>
+  <si>
+    <t>Archer's Cowardice</t>
+  </si>
+  <si>
+    <t>Rider's Avarice</t>
+  </si>
+  <si>
+    <t>Caster's Apathy</t>
+  </si>
+  <si>
+    <t>Assassin's Envy</t>
+  </si>
+  <si>
+    <t>Berserker's Wrath</t>
+  </si>
+  <si>
+    <t>Another's Blasphemy</t>
+  </si>
+  <si>
+    <t>Lancers-Lust</t>
+  </si>
+  <si>
+    <t>Archers-Cowardice</t>
+  </si>
+  <si>
+    <t>Riders-Avarice</t>
+  </si>
+  <si>
+    <t>Casters-Apathy</t>
+  </si>
+  <si>
+    <t>Assassins-Envy</t>
+  </si>
+  <si>
+    <t>Berserkers-Wrath</t>
+  </si>
+  <si>
+    <t>Anothers-Blasphemy</t>
   </si>
 </sst>
 </file>
@@ -6106,7 +6268,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E33D7ECC-1EAA-4A40-B4DA-A93E54CBC8B5}">
-  <dimension ref="A1:Q185"/>
+  <dimension ref="A1:R189"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="3" width="22" customWidth="1"/>
@@ -6124,9 +6286,10 @@
     <col min="15" max="15" width="17.140625" customWidth="1"/>
     <col min="16" max="16" width="18.140625" customWidth="1"/>
     <col min="17" max="17" width="16.7109375" customWidth="1"/>
+    <col min="18" max="18" width="16.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -6176,10 +6339,13 @@
         <v>1886</v>
       </c>
       <c r="Q1" s="3" t="s">
-        <v>1887</v>
-      </c>
-    </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+        <v>1890</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>1897</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -6214,7 +6380,7 @@
         <v>1510</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>111</v>
       </c>
@@ -6249,7 +6415,7 @@
         <v>1512</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>112</v>
       </c>
@@ -6281,7 +6447,7 @@
         <v>1518</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>113</v>
       </c>
@@ -6316,7 +6482,7 @@
         <v>1527</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>114</v>
       </c>
@@ -6351,7 +6517,7 @@
         <v>1525</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>115</v>
       </c>
@@ -6386,7 +6552,7 @@
         <v>1536</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>116</v>
       </c>
@@ -6421,7 +6587,7 @@
         <v>1538</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>117</v>
       </c>
@@ -6453,7 +6619,7 @@
         <v>1541</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>118</v>
       </c>
@@ -6488,7 +6654,7 @@
         <v>1542</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>119</v>
       </c>
@@ -6523,7 +6689,7 @@
         <v>1546</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>120</v>
       </c>
@@ -6558,7 +6724,7 @@
         <v>1549</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>121</v>
       </c>
@@ -6590,7 +6756,7 @@
         <v>1555</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>122</v>
       </c>
@@ -6625,7 +6791,7 @@
         <v>1557</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>123</v>
       </c>
@@ -6660,7 +6826,7 @@
         <v>1561</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>124</v>
       </c>
@@ -12132,7 +12298,7 @@
         <v>1867</v>
       </c>
     </row>
-    <row r="177" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>1147</v>
       </c>
@@ -12167,7 +12333,7 @@
         <v>1869</v>
       </c>
     </row>
-    <row r="178" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>1148</v>
       </c>
@@ -12202,7 +12368,7 @@
         <v>1872</v>
       </c>
     </row>
-    <row r="179" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>29</v>
       </c>
@@ -12237,7 +12403,7 @@
         <v>1874</v>
       </c>
     </row>
-    <row r="180" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
         <v>1149</v>
       </c>
@@ -12269,7 +12435,7 @@
         <v>1875</v>
       </c>
     </row>
-    <row r="181" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>1150</v>
       </c>
@@ -12304,7 +12470,7 @@
         <v>1543</v>
       </c>
     </row>
-    <row r="182" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>1151</v>
       </c>
@@ -12336,7 +12502,7 @@
         <v>1879</v>
       </c>
     </row>
-    <row r="183" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>1152</v>
       </c>
@@ -12371,7 +12537,7 @@
         <v>1880</v>
       </c>
     </row>
-    <row r="184" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
         <v>1153</v>
       </c>
@@ -12406,7 +12572,7 @@
         <v>1882</v>
       </c>
     </row>
-    <row r="185" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
         <v>36</v>
       </c>
@@ -12439,20 +12605,169 @@
       </c>
       <c r="N185" s="2" t="s">
         <v>1543</v>
+      </c>
+    </row>
+    <row r="186" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A186" t="s">
+        <v>1898</v>
+      </c>
+      <c r="B186" t="s">
+        <v>1899</v>
+      </c>
+      <c r="C186" t="s">
+        <v>1900</v>
+      </c>
+      <c r="D186" t="s">
+        <v>7</v>
+      </c>
+      <c r="E186" t="s">
+        <v>40</v>
+      </c>
+      <c r="G186" s="2" t="s">
+        <v>567</v>
+      </c>
+      <c r="H186" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="I186" s="2" t="s">
+        <v>397</v>
+      </c>
+      <c r="J186" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="M186" s="2" t="s">
+        <v>1545</v>
+      </c>
+      <c r="N186" s="2" t="s">
+        <v>1699</v>
+      </c>
+      <c r="O186" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="187" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A187" t="s">
+        <v>1901</v>
+      </c>
+      <c r="B187" t="s">
+        <v>1906</v>
+      </c>
+      <c r="C187" t="s">
+        <v>1909</v>
+      </c>
+      <c r="D187" t="s">
+        <v>7</v>
+      </c>
+      <c r="E187" t="s">
+        <v>8</v>
+      </c>
+      <c r="G187" s="2" t="s">
+        <v>1907</v>
+      </c>
+      <c r="H187" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="I187" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="J187" s="2" t="s">
+        <v>1908</v>
+      </c>
+      <c r="M187" s="2" t="s">
+        <v>1520</v>
+      </c>
+      <c r="N187" s="2" t="s">
+        <v>1905</v>
+      </c>
+      <c r="O187" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="188" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A188" t="s">
+        <v>1902</v>
+      </c>
+      <c r="B188" t="s">
+        <v>1914</v>
+      </c>
+      <c r="C188" t="s">
+        <v>1915</v>
+      </c>
+      <c r="D188" t="s">
+        <v>317</v>
+      </c>
+      <c r="E188" t="s">
+        <v>99</v>
+      </c>
+      <c r="G188" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="H188" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="I188" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="J188" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="M188" s="2" t="s">
+        <v>1916</v>
+      </c>
+      <c r="N188" s="2" t="s">
+        <v>1917</v>
+      </c>
+      <c r="O188" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="189" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A189" t="s">
+        <v>1919</v>
+      </c>
+      <c r="B189" t="s">
+        <v>1920</v>
+      </c>
+      <c r="C189" t="s">
+        <v>1921</v>
+      </c>
+      <c r="D189" t="s">
+        <v>1922</v>
+      </c>
+      <c r="E189" t="s">
+        <v>8</v>
+      </c>
+      <c r="G189" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="H189" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="I189" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="M189" s="2" t="s">
+        <v>1923</v>
+      </c>
+      <c r="N189" s="2" t="s">
+        <v>1924</v>
+      </c>
+      <c r="O189" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="H2 I6:I7 I10 I12 H14 I18 I22 I24 I27 G34 I40 I42 I45 I52 I62 I72 H79 I80 I84 I88 I90 G91 H100 I119 I124 I121:I123 G130:I139 G142:I148 G164:I186" numberStoredAsText="1"/>
+    <ignoredError sqref="H2 I6:I7 I10 I12 H14 I18 I22 I24 I27 G34 I40 I42 I45 I52 I62 I72 H79 I80 I84 I88 I90 G91 H100 I119 I124 I121:I123 G130:I139 G142:I148 G164:I185 G187:I187" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{445C98DF-AF88-42FF-A8A5-2AB8831F51CC}">
-  <dimension ref="A1:B61"/>
+  <dimension ref="A1:B62"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.140625" customWidth="1"/>
@@ -12751,6 +13066,9 @@
       <c r="A37" t="s">
         <v>1335</v>
       </c>
+      <c r="B37" t="s">
+        <v>1905</v>
+      </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
@@ -12870,6 +13188,11 @@
     <row r="61" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>1534</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>1913</v>
       </c>
     </row>
   </sheetData>
@@ -12879,7 +13202,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D1BC60D8-44F3-478D-BCC0-4752624457AE}">
-  <dimension ref="A1:F24"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="19" customWidth="1"/>
@@ -12887,9 +13210,10 @@
     <col min="4" max="4" width="23.42578125" customWidth="1"/>
     <col min="5" max="5" width="16.42578125" customWidth="1"/>
     <col min="6" max="6" width="13.5703125" customWidth="1"/>
+    <col min="7" max="7" width="12.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -12908,8 +13232,11 @@
       <c r="F1" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G1" s="1" t="s">
+        <v>1892</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>116</v>
       </c>
@@ -12926,7 +13253,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>126</v>
       </c>
@@ -12943,7 +13270,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>130</v>
       </c>
@@ -12960,7 +13287,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>333</v>
       </c>
@@ -12977,7 +13304,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>333</v>
       </c>
@@ -12994,7 +13321,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>333</v>
       </c>
@@ -13011,7 +13338,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>85</v>
       </c>
@@ -13028,7 +13355,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>17</v>
       </c>
@@ -13045,7 +13372,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>17</v>
       </c>
@@ -13062,7 +13389,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>284</v>
       </c>
@@ -13079,7 +13406,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>284</v>
       </c>
@@ -13096,7 +13423,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>284</v>
       </c>
@@ -13113,7 +13440,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>284</v>
       </c>
@@ -13130,7 +13457,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>284</v>
       </c>
@@ -13147,7 +13474,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>284</v>
       </c>
@@ -13309,7 +13636,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84E3BB0D-5578-4069-B1C9-C3864EB2A429}">
-  <dimension ref="A1:G553"/>
+  <dimension ref="A1:G565"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="26.28515625" customWidth="1"/>
@@ -13317,6 +13644,7 @@
     <col min="4" max="4" width="17" customWidth="1"/>
     <col min="5" max="5" width="29.5703125" customWidth="1"/>
     <col min="6" max="6" width="15.7109375" customWidth="1"/>
+    <col min="7" max="7" width="11.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -13338,7 +13666,9 @@
       <c r="F1" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="G1" s="1"/>
+      <c r="G1" s="1" t="s">
+        <v>1893</v>
+      </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
@@ -22722,6 +23052,210 @@
       </c>
       <c r="E553" t="s">
         <v>69</v>
+      </c>
+    </row>
+    <row r="554" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A554" t="s">
+        <v>1898</v>
+      </c>
+      <c r="B554" t="s">
+        <v>1899</v>
+      </c>
+      <c r="C554">
+        <v>1</v>
+      </c>
+      <c r="D554" t="b">
+        <v>0</v>
+      </c>
+      <c r="E554" t="s">
+        <v>1903</v>
+      </c>
+    </row>
+    <row r="555" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A555" t="s">
+        <v>1898</v>
+      </c>
+      <c r="B555" t="s">
+        <v>1899</v>
+      </c>
+      <c r="C555">
+        <v>2</v>
+      </c>
+      <c r="D555" t="b">
+        <v>0</v>
+      </c>
+      <c r="E555" t="s">
+        <v>1904</v>
+      </c>
+    </row>
+    <row r="556" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A556" t="s">
+        <v>1898</v>
+      </c>
+      <c r="B556" t="s">
+        <v>1899</v>
+      </c>
+      <c r="C556">
+        <v>3</v>
+      </c>
+      <c r="D556" t="b">
+        <v>0</v>
+      </c>
+      <c r="E556" t="s">
+        <v>1904</v>
+      </c>
+    </row>
+    <row r="557" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A557" t="s">
+        <v>1901</v>
+      </c>
+      <c r="B557" t="s">
+        <v>1906</v>
+      </c>
+      <c r="C557">
+        <v>1</v>
+      </c>
+      <c r="D557" t="b">
+        <v>0</v>
+      </c>
+      <c r="E557" t="s">
+        <v>1910</v>
+      </c>
+    </row>
+    <row r="558" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A558" t="s">
+        <v>1901</v>
+      </c>
+      <c r="B558" t="s">
+        <v>1906</v>
+      </c>
+      <c r="C558">
+        <v>2</v>
+      </c>
+      <c r="D558" t="b">
+        <v>0</v>
+      </c>
+      <c r="E558" t="s">
+        <v>1911</v>
+      </c>
+    </row>
+    <row r="559" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A559" t="s">
+        <v>1901</v>
+      </c>
+      <c r="B559" t="s">
+        <v>1906</v>
+      </c>
+      <c r="C559">
+        <v>3</v>
+      </c>
+      <c r="D559" t="b">
+        <v>0</v>
+      </c>
+      <c r="E559" t="s">
+        <v>1912</v>
+      </c>
+    </row>
+    <row r="560" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A560" t="s">
+        <v>1902</v>
+      </c>
+      <c r="B560" t="s">
+        <v>1914</v>
+      </c>
+      <c r="C560">
+        <v>1</v>
+      </c>
+      <c r="D560" t="b">
+        <v>1</v>
+      </c>
+      <c r="E560" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="561" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A561" t="s">
+        <v>1902</v>
+      </c>
+      <c r="B561" t="s">
+        <v>1914</v>
+      </c>
+      <c r="C561">
+        <v>2</v>
+      </c>
+      <c r="D561" t="b">
+        <v>0</v>
+      </c>
+      <c r="E561" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="562" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A562" t="s">
+        <v>1902</v>
+      </c>
+      <c r="B562" t="s">
+        <v>1914</v>
+      </c>
+      <c r="C562">
+        <v>3</v>
+      </c>
+      <c r="D562" t="b">
+        <v>0</v>
+      </c>
+      <c r="E562" t="s">
+        <v>1918</v>
+      </c>
+    </row>
+    <row r="563" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A563" t="s">
+        <v>1919</v>
+      </c>
+      <c r="B563" t="s">
+        <v>1920</v>
+      </c>
+      <c r="C563">
+        <v>1</v>
+      </c>
+      <c r="D563" t="b">
+        <v>1</v>
+      </c>
+      <c r="E563" t="s">
+        <v>1925</v>
+      </c>
+    </row>
+    <row r="564" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A564" t="s">
+        <v>1919</v>
+      </c>
+      <c r="B564" t="s">
+        <v>1920</v>
+      </c>
+      <c r="C564">
+        <v>2</v>
+      </c>
+      <c r="D564" t="b">
+        <v>0</v>
+      </c>
+      <c r="E564" t="s">
+        <v>1927</v>
+      </c>
+    </row>
+    <row r="565" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A565" t="s">
+        <v>1919</v>
+      </c>
+      <c r="B565" t="s">
+        <v>1920</v>
+      </c>
+      <c r="C565">
+        <v>3</v>
+      </c>
+      <c r="D565" t="b">
+        <v>0</v>
+      </c>
+      <c r="E565" t="s">
+        <v>1928</v>
       </c>
     </row>
   </sheetData>
@@ -22732,18 +23266,20 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{494C60D6-2426-4CE0-9CA4-43EAAA3DD51B}">
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:H34"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.7109375" customWidth="1"/>
     <col min="2" max="2" width="22.140625" customWidth="1"/>
-    <col min="3" max="3" width="18.28515625" customWidth="1"/>
-    <col min="4" max="4" width="18" customWidth="1"/>
+    <col min="3" max="3" width="20.42578125" customWidth="1"/>
+    <col min="4" max="4" width="22.42578125" customWidth="1"/>
     <col min="5" max="5" width="11.85546875" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" customWidth="1"/>
+    <col min="6" max="6" width="19.28515625" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" customWidth="1"/>
+    <col min="8" max="8" width="13.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -22760,10 +23296,16 @@
         <v>1467</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>1926</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H1" s="1" t="s">
+        <v>1892</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>113</v>
       </c>
@@ -22779,11 +23321,11 @@
       <c r="E2" t="s">
         <v>1503</v>
       </c>
-      <c r="F2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>113</v>
       </c>
@@ -22799,11 +23341,11 @@
       <c r="E3" t="s">
         <v>1503</v>
       </c>
-      <c r="F3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>113</v>
       </c>
@@ -22819,11 +23361,11 @@
       <c r="E4" t="s">
         <v>1503</v>
       </c>
-      <c r="F4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>348</v>
       </c>
@@ -22839,11 +23381,11 @@
       <c r="E5" t="s">
         <v>1259</v>
       </c>
-      <c r="F5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>348</v>
       </c>
@@ -22859,11 +23401,11 @@
       <c r="E6" t="s">
         <v>1468</v>
       </c>
-      <c r="F6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>348</v>
       </c>
@@ -22879,11 +23421,11 @@
       <c r="E7" t="s">
         <v>1468</v>
       </c>
-      <c r="F7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>348</v>
       </c>
@@ -22899,11 +23441,11 @@
       <c r="E8" t="s">
         <v>1468</v>
       </c>
-      <c r="F8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>757</v>
       </c>
@@ -22919,11 +23461,11 @@
       <c r="E9" t="s">
         <v>1474</v>
       </c>
-      <c r="F9">
+      <c r="G9">
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>757</v>
       </c>
@@ -22939,11 +23481,11 @@
       <c r="E10" t="s">
         <v>1474</v>
       </c>
-      <c r="F10">
+      <c r="G10">
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>757</v>
       </c>
@@ -22959,11 +23501,11 @@
       <c r="E11" t="s">
         <v>1474</v>
       </c>
-      <c r="F11">
+      <c r="G11">
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>757</v>
       </c>
@@ -22979,11 +23521,11 @@
       <c r="E12" t="s">
         <v>1474</v>
       </c>
-      <c r="F12">
+      <c r="G12">
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>757</v>
       </c>
@@ -22999,11 +23541,11 @@
       <c r="E13" t="s">
         <v>1474</v>
       </c>
-      <c r="F13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>757</v>
       </c>
@@ -23019,11 +23561,11 @@
       <c r="E14" t="s">
         <v>1474</v>
       </c>
-      <c r="F14">
+      <c r="G14">
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>757</v>
       </c>
@@ -23039,11 +23581,11 @@
       <c r="E15" t="s">
         <v>1474</v>
       </c>
-      <c r="F15">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>757</v>
       </c>
@@ -23059,11 +23601,11 @@
       <c r="E16" t="s">
         <v>1474</v>
       </c>
-      <c r="F16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>757</v>
       </c>
@@ -23079,11 +23621,11 @@
       <c r="E17" t="s">
         <v>1474</v>
       </c>
-      <c r="F17">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>757</v>
       </c>
@@ -23099,11 +23641,11 @@
       <c r="E18" t="s">
         <v>1474</v>
       </c>
-      <c r="F18">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>757</v>
       </c>
@@ -23119,11 +23661,11 @@
       <c r="E19" t="s">
         <v>1474</v>
       </c>
-      <c r="F19">
+      <c r="G19">
         <v>2</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>757</v>
       </c>
@@ -23139,11 +23681,11 @@
       <c r="E20" t="s">
         <v>1474</v>
       </c>
-      <c r="F20">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>757</v>
       </c>
@@ -23159,11 +23701,11 @@
       <c r="E21" t="s">
         <v>1474</v>
       </c>
-      <c r="F21">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>1140</v>
       </c>
@@ -23179,11 +23721,14 @@
       <c r="E22" t="s">
         <v>1506</v>
       </c>
-      <c r="F22">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F22" t="b">
+        <v>1</v>
+      </c>
+      <c r="G22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>1141</v>
       </c>
@@ -23199,11 +23744,14 @@
       <c r="E23" t="s">
         <v>1506</v>
       </c>
-      <c r="F23">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F23" t="b">
+        <v>1</v>
+      </c>
+      <c r="G23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>1144</v>
       </c>
@@ -23219,11 +23767,14 @@
       <c r="E24" t="s">
         <v>1506</v>
       </c>
-      <c r="F24">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F24" t="b">
+        <v>1</v>
+      </c>
+      <c r="G24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>1145</v>
       </c>
@@ -23239,11 +23790,14 @@
       <c r="E25" t="s">
         <v>1506</v>
       </c>
-      <c r="F25">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F25" t="b">
+        <v>1</v>
+      </c>
+      <c r="G25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>1146</v>
       </c>
@@ -23259,7 +23813,194 @@
       <c r="E26" t="s">
         <v>1506</v>
       </c>
-      <c r="F26">
+      <c r="F26" t="b">
+        <v>1</v>
+      </c>
+      <c r="G26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>1919</v>
+      </c>
+      <c r="B27" t="s">
+        <v>1920</v>
+      </c>
+      <c r="C27" t="s">
+        <v>1929</v>
+      </c>
+      <c r="D27" t="s">
+        <v>1930</v>
+      </c>
+      <c r="E27" t="s">
+        <v>1468</v>
+      </c>
+      <c r="F27" t="b">
+        <v>1</v>
+      </c>
+      <c r="G27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>1919</v>
+      </c>
+      <c r="B28" t="s">
+        <v>1920</v>
+      </c>
+      <c r="C28" t="s">
+        <v>1931</v>
+      </c>
+      <c r="D28" t="s">
+        <v>1938</v>
+      </c>
+      <c r="E28" t="s">
+        <v>1468</v>
+      </c>
+      <c r="F28" t="b">
+        <v>1</v>
+      </c>
+      <c r="G28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>1919</v>
+      </c>
+      <c r="B29" t="s">
+        <v>1920</v>
+      </c>
+      <c r="C29" t="s">
+        <v>1932</v>
+      </c>
+      <c r="D29" t="s">
+        <v>1939</v>
+      </c>
+      <c r="E29" t="s">
+        <v>1468</v>
+      </c>
+      <c r="F29" t="b">
+        <v>1</v>
+      </c>
+      <c r="G29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>1919</v>
+      </c>
+      <c r="B30" t="s">
+        <v>1920</v>
+      </c>
+      <c r="C30" t="s">
+        <v>1933</v>
+      </c>
+      <c r="D30" t="s">
+        <v>1940</v>
+      </c>
+      <c r="E30" t="s">
+        <v>1468</v>
+      </c>
+      <c r="F30" t="b">
+        <v>1</v>
+      </c>
+      <c r="G30">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>1919</v>
+      </c>
+      <c r="B31" t="s">
+        <v>1920</v>
+      </c>
+      <c r="C31" t="s">
+        <v>1934</v>
+      </c>
+      <c r="D31" t="s">
+        <v>1941</v>
+      </c>
+      <c r="E31" t="s">
+        <v>1468</v>
+      </c>
+      <c r="F31" t="b">
+        <v>1</v>
+      </c>
+      <c r="G31">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>1919</v>
+      </c>
+      <c r="B32" t="s">
+        <v>1920</v>
+      </c>
+      <c r="C32" t="s">
+        <v>1935</v>
+      </c>
+      <c r="D32" t="s">
+        <v>1942</v>
+      </c>
+      <c r="E32" t="s">
+        <v>1468</v>
+      </c>
+      <c r="F32" t="b">
+        <v>1</v>
+      </c>
+      <c r="G32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>1919</v>
+      </c>
+      <c r="B33" t="s">
+        <v>1920</v>
+      </c>
+      <c r="C33" t="s">
+        <v>1936</v>
+      </c>
+      <c r="D33" t="s">
+        <v>1943</v>
+      </c>
+      <c r="E33" t="s">
+        <v>1468</v>
+      </c>
+      <c r="F33" t="b">
+        <v>1</v>
+      </c>
+      <c r="G33">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>1919</v>
+      </c>
+      <c r="B34" t="s">
+        <v>1920</v>
+      </c>
+      <c r="C34" t="s">
+        <v>1937</v>
+      </c>
+      <c r="D34" t="s">
+        <v>1944</v>
+      </c>
+      <c r="E34" t="s">
+        <v>1468</v>
+      </c>
+      <c r="F34" t="b">
+        <v>1</v>
+      </c>
+      <c r="G34">
         <v>1</v>
       </c>
     </row>
@@ -23271,7 +24012,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32F3CD10-C054-4484-ABE2-D426F834FC22}">
-  <dimension ref="A1:G67"/>
+  <dimension ref="A1:J67"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.42578125" customWidth="1"/>
@@ -23279,9 +24020,12 @@
     <col min="4" max="5" width="20.42578125" customWidth="1"/>
     <col min="6" max="6" width="11.42578125" customWidth="1"/>
     <col min="7" max="7" width="15.85546875" customWidth="1"/>
+    <col min="8" max="8" width="19.85546875" customWidth="1"/>
+    <col min="9" max="9" width="16" customWidth="1"/>
+    <col min="10" max="10" width="13.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>1263</v>
       </c>
@@ -23300,8 +24044,20 @@
       <c r="F1" s="1" t="s">
         <v>1466</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G1" s="1" t="s">
+        <v>1894</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>1895</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>1896</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>1891</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1264</v>
       </c>
@@ -23318,7 +24074,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>1265</v>
       </c>
@@ -23335,7 +24091,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>1266</v>
       </c>
@@ -23352,7 +24108,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>1267</v>
       </c>
@@ -23369,7 +24125,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>1268</v>
       </c>
@@ -23386,7 +24142,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>1269</v>
       </c>
@@ -23403,7 +24159,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>1270</v>
       </c>
@@ -23420,7 +24176,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>1271</v>
       </c>
@@ -23437,7 +24193,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>1272</v>
       </c>
@@ -23451,7 +24207,7 @@
         <v>1337</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>1273</v>
       </c>
@@ -23468,7 +24224,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>1274</v>
       </c>
@@ -23485,7 +24241,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>1275</v>
       </c>
@@ -23499,7 +24255,7 @@
         <v>1333</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>1276</v>
       </c>
@@ -23516,7 +24272,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>1277</v>
       </c>
@@ -23530,7 +24286,7 @@
         <v>1335</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>1278</v>
       </c>
@@ -24306,7 +25062,7 @@
         <v>1</v>
       </c>
       <c r="G61" t="s">
-        <v>1888</v>
+        <v>1887</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
@@ -24326,7 +25082,7 @@
         <v>1</v>
       </c>
       <c r="G62" t="s">
-        <v>1888</v>
+        <v>1887</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
@@ -24452,10 +25208,10 @@
         <v>1467</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>1888</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>1889</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>1890</v>
       </c>
     </row>
   </sheetData>

--- a/data/Fate-Spreadsheet.xlsx
+++ b/data/Fate-Spreadsheet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Important\Python\Fate-Wiki\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{467A7EFF-9F84-4DAE-8E3D-19F96EF57D69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE9E610C-D5D3-4347-8319-DA44D04AEDD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{B05E798F-9EF6-4508-A0A4-311D06661AED}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="7" xr2:uid="{B05E798F-9EF6-4508-A0A4-311D06661AED}"/>
   </bookViews>
   <sheets>
     <sheet name="Servants" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,9 @@
     <sheet name="Servant Skills" sheetId="3" r:id="rId4"/>
     <sheet name="Servant Misc Cards" sheetId="7" r:id="rId5"/>
     <sheet name="Masters" sheetId="5" r:id="rId6"/>
-    <sheet name="Master Cards" sheetId="6" r:id="rId7"/>
+    <sheet name="Master Abilities" sheetId="6" r:id="rId7"/>
+    <sheet name="Master Ascensions" sheetId="10" r:id="rId8"/>
+    <sheet name="Master Assets" sheetId="9" r:id="rId9"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -45,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4360" uniqueCount="1945">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5761" uniqueCount="2507">
   <si>
     <t>servant_id</t>
   </si>
@@ -5567,9 +5569,6 @@
     <t>High Risk,Mana Hungry,NP Reliant</t>
   </si>
   <si>
-    <t>VP Gain,Cheap Power,Adapatable</t>
-  </si>
-  <si>
     <t>VP Theft,Good Scaling</t>
   </si>
   <si>
@@ -5708,24 +5707,12 @@
     <t>is_custom_servant</t>
   </si>
   <si>
-    <t>webp fix</t>
-  </si>
-  <si>
-    <t>is_ability</t>
-  </si>
-  <si>
-    <t>is_asset</t>
-  </si>
-  <si>
     <t>servant_creator</t>
   </si>
   <si>
     <t>profile_artist</t>
   </si>
   <si>
-    <t>card-artist</t>
-  </si>
-  <si>
     <t>card_artist</t>
   </si>
   <si>
@@ -5880,6 +5867,1707 @@
   </si>
   <si>
     <t>Anothers-Blasphemy</t>
+  </si>
+  <si>
+    <t>Kanshou &amp; Bakuya</t>
+  </si>
+  <si>
+    <t>kanshou-and-bakuya</t>
+  </si>
+  <si>
+    <t>Caliburn</t>
+  </si>
+  <si>
+    <t>caliburn</t>
+  </si>
+  <si>
+    <t>Gem</t>
+  </si>
+  <si>
+    <t>gem</t>
+  </si>
+  <si>
+    <t>Gandr Shot</t>
+  </si>
+  <si>
+    <t>gandr-shot</t>
+  </si>
+  <si>
+    <t>attack</t>
+  </si>
+  <si>
+    <t>passive</t>
+  </si>
+  <si>
+    <t>Jewel Sword Zelretch</t>
+  </si>
+  <si>
+    <t>jewel-sword-zelretch</t>
+  </si>
+  <si>
+    <t>Book of the False Attendant</t>
+  </si>
+  <si>
+    <t>ability_order</t>
+  </si>
+  <si>
+    <t>book-of-the-false-attendant-1</t>
+  </si>
+  <si>
+    <t>book-of-the-false-attendant-2</t>
+  </si>
+  <si>
+    <t>Cancerous Vessel</t>
+  </si>
+  <si>
+    <t>cancerous-vessel</t>
+  </si>
+  <si>
+    <t>Black Shadow</t>
+  </si>
+  <si>
+    <t>The Tainted Grail</t>
+  </si>
+  <si>
+    <t>black-shadow</t>
+  </si>
+  <si>
+    <t>the-tainted-grail</t>
+  </si>
+  <si>
+    <t>Corruptuon</t>
+  </si>
+  <si>
+    <t>corruption</t>
+  </si>
+  <si>
+    <t>Dress of Heaven</t>
+  </si>
+  <si>
+    <t>dress-of-heaven</t>
+  </si>
+  <si>
+    <t>The Third Magic</t>
+  </si>
+  <si>
+    <t>the-third-magic</t>
+  </si>
+  <si>
+    <t>Snake</t>
+  </si>
+  <si>
+    <t>snake</t>
+  </si>
+  <si>
+    <t>Perfect Breathing</t>
+  </si>
+  <si>
+    <t>perfect-breathing</t>
+  </si>
+  <si>
+    <t>Supervisor</t>
+  </si>
+  <si>
+    <t>Executor</t>
+  </si>
+  <si>
+    <t>supervisor</t>
+  </si>
+  <si>
+    <t>executor</t>
+  </si>
+  <si>
+    <t>Patron of Evil</t>
+  </si>
+  <si>
+    <t>patron-of-evil</t>
+  </si>
+  <si>
+    <t>Founder</t>
+  </si>
+  <si>
+    <t>Pseudo Vampire</t>
+  </si>
+  <si>
+    <t>founder</t>
+  </si>
+  <si>
+    <t>pseudo-vampire</t>
+  </si>
+  <si>
+    <t>Illusive Mastermind</t>
+  </si>
+  <si>
+    <t>illusive-mastermind</t>
+  </si>
+  <si>
+    <t>Wrath of the Tiger</t>
+  </si>
+  <si>
+    <t>wrath-of-the-tiger</t>
+  </si>
+  <si>
+    <t>Flawless Defense</t>
+  </si>
+  <si>
+    <t>flawless-defense</t>
+  </si>
+  <si>
+    <t>Reset</t>
+  </si>
+  <si>
+    <t>Awake</t>
+  </si>
+  <si>
+    <t>Day 1</t>
+  </si>
+  <si>
+    <t>Day 2</t>
+  </si>
+  <si>
+    <t>Day 3</t>
+  </si>
+  <si>
+    <t>Day 4</t>
+  </si>
+  <si>
+    <t>Fragarach</t>
+  </si>
+  <si>
+    <t>reset</t>
+  </si>
+  <si>
+    <t>awake</t>
+  </si>
+  <si>
+    <t>fragarach</t>
+  </si>
+  <si>
+    <t>Spiritual Masochism</t>
+  </si>
+  <si>
+    <t>Shroud of Magdalene</t>
+  </si>
+  <si>
+    <t>spiritual-masochism</t>
+  </si>
+  <si>
+    <t>shroud-of-magdalene</t>
+  </si>
+  <si>
+    <t>Shroud of Valentinus</t>
+  </si>
+  <si>
+    <t>shroud-of-valentinus</t>
+  </si>
+  <si>
+    <t>Excalibur (Wood)</t>
+  </si>
+  <si>
+    <t>excalibur-wood</t>
+  </si>
+  <si>
+    <t>Origin-Bullet</t>
+  </si>
+  <si>
+    <t>origin-bullet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Callous Assassin </t>
+  </si>
+  <si>
+    <t>callous-assassin</t>
+  </si>
+  <si>
+    <t>Life Weaving</t>
+  </si>
+  <si>
+    <t>life-weaving</t>
+  </si>
+  <si>
+    <t>Azoth Blade</t>
+  </si>
+  <si>
+    <t>Grimoir</t>
+  </si>
+  <si>
+    <t>Magic Meter</t>
+  </si>
+  <si>
+    <t>Mana Reserve</t>
+  </si>
+  <si>
+    <t>Einascherung</t>
+  </si>
+  <si>
+    <t>einascherung</t>
+  </si>
+  <si>
+    <t>mana-reserve</t>
+  </si>
+  <si>
+    <t>magic-meter</t>
+  </si>
+  <si>
+    <t>grimoir</t>
+  </si>
+  <si>
+    <t>azoth-blade</t>
+  </si>
+  <si>
+    <t>Advanced Pyromancy</t>
+  </si>
+  <si>
+    <t>advanced-pyromancy</t>
+  </si>
+  <si>
+    <t>Nemesis</t>
+  </si>
+  <si>
+    <t>nemesis</t>
+  </si>
+  <si>
+    <t>Broken</t>
+  </si>
+  <si>
+    <t>broken</t>
+  </si>
+  <si>
+    <t>Human Battery</t>
+  </si>
+  <si>
+    <t>human-battery</t>
+  </si>
+  <si>
+    <t>Master Detective</t>
+  </si>
+  <si>
+    <t>master-detective</t>
+  </si>
+  <si>
+    <t>Volumen Hydrargyrum</t>
+  </si>
+  <si>
+    <t>volumen-hydrargyrum-1</t>
+  </si>
+  <si>
+    <t>volumen-hydrargyrum-2</t>
+  </si>
+  <si>
+    <t>volumen-hydrargyrum-3</t>
+  </si>
+  <si>
+    <t>Fluid Dynamics</t>
+  </si>
+  <si>
+    <t>fluid-dynamics</t>
+  </si>
+  <si>
+    <t>Art of Death</t>
+  </si>
+  <si>
+    <t>art-of-death</t>
+  </si>
+  <si>
+    <t>Defile</t>
+  </si>
+  <si>
+    <t>defile</t>
+  </si>
+  <si>
+    <t>Challenge Results</t>
+  </si>
+  <si>
+    <t>challenge-results</t>
+  </si>
+  <si>
+    <t>Analysis</t>
+  </si>
+  <si>
+    <t>analysis</t>
+  </si>
+  <si>
+    <t>Dead Face</t>
+  </si>
+  <si>
+    <t>dead-face</t>
+  </si>
+  <si>
+    <t>Mystic Code: CCC</t>
+  </si>
+  <si>
+    <t>Mystic Code: Extella</t>
+  </si>
+  <si>
+    <t>Mystic Code: Extra</t>
+  </si>
+  <si>
+    <t>Mystic Code: Link</t>
+  </si>
+  <si>
+    <t>mystic-code-ccc</t>
+  </si>
+  <si>
+    <t>mystic-code-extella</t>
+  </si>
+  <si>
+    <t>mystic-code-extra</t>
+  </si>
+  <si>
+    <t>mystic-code-link</t>
+  </si>
+  <si>
+    <t>Moon Cell Regalia</t>
+  </si>
+  <si>
+    <t>moon-cell-regalia</t>
+  </si>
+  <si>
+    <t>Prophecy of Doom</t>
+  </si>
+  <si>
+    <t>Prophecy of Triumph</t>
+  </si>
+  <si>
+    <t>prophecy-of-triumph</t>
+  </si>
+  <si>
+    <t>prophecy-of-doom</t>
+  </si>
+  <si>
+    <t>Atlas Researcher</t>
+  </si>
+  <si>
+    <t>atlas-researcher</t>
+  </si>
+  <si>
+    <t>Cheat Code Cast</t>
+  </si>
+  <si>
+    <t>cheat-code-cast</t>
+  </si>
+  <si>
+    <t>Time Out</t>
+  </si>
+  <si>
+    <t>time-out</t>
+  </si>
+  <si>
+    <t>Beltane Knight</t>
+  </si>
+  <si>
+    <t>beltane-knight</t>
+  </si>
+  <si>
+    <t>Phantom Alice</t>
+  </si>
+  <si>
+    <t>phantom-alice</t>
+  </si>
+  <si>
+    <t>Queenside Castle</t>
+  </si>
+  <si>
+    <t>queenside-castle</t>
+  </si>
+  <si>
+    <t>Black Scorpion</t>
+  </si>
+  <si>
+    <t>black-scorpion</t>
+  </si>
+  <si>
+    <t>Final Reckoning</t>
+  </si>
+  <si>
+    <t>final-reckoning</t>
+  </si>
+  <si>
+    <t>Heaven's Hole</t>
+  </si>
+  <si>
+    <t>heavens-hole</t>
+  </si>
+  <si>
+    <t>All the World's Desire</t>
+  </si>
+  <si>
+    <t>all-the-worlds-desire</t>
+  </si>
+  <si>
+    <t>Diamond Realm</t>
+  </si>
+  <si>
+    <t>diamond-realm</t>
+  </si>
+  <si>
+    <t>Womb Realm</t>
+  </si>
+  <si>
+    <t>womb-realm</t>
+  </si>
+  <si>
+    <t>Desire for Control</t>
+  </si>
+  <si>
+    <t>desire-for-control</t>
+  </si>
+  <si>
+    <t>Desire for Subjugation</t>
+  </si>
+  <si>
+    <t>desire-for-subjugation</t>
+  </si>
+  <si>
+    <t>Escape from Reality</t>
+  </si>
+  <si>
+    <t>escape-from-reality</t>
+  </si>
+  <si>
+    <t>Fear for the Future</t>
+  </si>
+  <si>
+    <t>fear-for-the-future</t>
+  </si>
+  <si>
+    <t>Fear of the Infinite</t>
+  </si>
+  <si>
+    <t>Regrets of the Past</t>
+  </si>
+  <si>
+    <t>fear-of-the-infinite</t>
+  </si>
+  <si>
+    <t>regrets-of-the-past</t>
+  </si>
+  <si>
+    <t>The Devil's Bodhisattva</t>
+  </si>
+  <si>
+    <t>the-devils-bodhisattva</t>
+  </si>
+  <si>
+    <t>Saver</t>
+  </si>
+  <si>
+    <t>saver</t>
+  </si>
+  <si>
+    <t>Old Acquaintances</t>
+  </si>
+  <si>
+    <t>Paraplegic</t>
+  </si>
+  <si>
+    <t>Cybernetics</t>
+  </si>
+  <si>
+    <t>Meek</t>
+  </si>
+  <si>
+    <t>Resolute</t>
+  </si>
+  <si>
+    <t>Bad Circuits</t>
+  </si>
+  <si>
+    <t>Brilliant Mind</t>
+  </si>
+  <si>
+    <t>paraplegic</t>
+  </si>
+  <si>
+    <t>cybernetics</t>
+  </si>
+  <si>
+    <t>meek</t>
+  </si>
+  <si>
+    <t>resolute</t>
+  </si>
+  <si>
+    <t>bad-circuits</t>
+  </si>
+  <si>
+    <t>brilliant-mind</t>
+  </si>
+  <si>
+    <t>Full Recovery</t>
+  </si>
+  <si>
+    <t>full-recovery</t>
+  </si>
+  <si>
+    <t>Primeval Battery</t>
+  </si>
+  <si>
+    <t>primeval-battery</t>
+  </si>
+  <si>
+    <t>Crafted Tree</t>
+  </si>
+  <si>
+    <t>crafted-tree-agility</t>
+  </si>
+  <si>
+    <t>crafted-tree-magic</t>
+  </si>
+  <si>
+    <t>crafted-tree-special</t>
+  </si>
+  <si>
+    <t>crafted-tree-strength</t>
+  </si>
+  <si>
+    <t>crafted-tree-typeless</t>
+  </si>
+  <si>
+    <t>Enhanced Circuits</t>
+  </si>
+  <si>
+    <t>enhanced-circuits</t>
+  </si>
+  <si>
+    <t>Treachery</t>
+  </si>
+  <si>
+    <t>treachery</t>
+  </si>
+  <si>
+    <t>Willing Sacrifice</t>
+  </si>
+  <si>
+    <t>willing-sacrifice</t>
+  </si>
+  <si>
+    <t>Wailing Stakes</t>
+  </si>
+  <si>
+    <t>wailing-stakes</t>
+  </si>
+  <si>
+    <t>balmung</t>
+  </si>
+  <si>
+    <t>Galvanism</t>
+  </si>
+  <si>
+    <t>galvanism</t>
+  </si>
+  <si>
+    <t>Faction Leader</t>
+  </si>
+  <si>
+    <t>Kotomine's Vassal</t>
+  </si>
+  <si>
+    <t>faction-leader</t>
+  </si>
+  <si>
+    <t>kotomines-vassal</t>
+  </si>
+  <si>
+    <t>Past Ruler</t>
+  </si>
+  <si>
+    <t>past-ruler</t>
+  </si>
+  <si>
+    <t>Necromantic Rites I</t>
+  </si>
+  <si>
+    <t>necromantic-rites-i</t>
+  </si>
+  <si>
+    <t>Necromantic Rites II</t>
+  </si>
+  <si>
+    <t>necromantic-rites-ii</t>
+  </si>
+  <si>
+    <t>Macabre Mastery</t>
+  </si>
+  <si>
+    <t>macabre-mastery</t>
+  </si>
+  <si>
+    <t>Command Chain</t>
+  </si>
+  <si>
+    <t>command-chain</t>
+  </si>
+  <si>
+    <t>asset_order</t>
+  </si>
+  <si>
+    <t>Barrier</t>
+  </si>
+  <si>
+    <t>Concentration</t>
+  </si>
+  <si>
+    <t>Deception</t>
+  </si>
+  <si>
+    <t>Destruction</t>
+  </si>
+  <si>
+    <t>Flash</t>
+  </si>
+  <si>
+    <t>Gloom</t>
+  </si>
+  <si>
+    <t>Ley Line</t>
+  </si>
+  <si>
+    <t>Linkage</t>
+  </si>
+  <si>
+    <t>Mapo Tofu</t>
+  </si>
+  <si>
+    <t>Meditation</t>
+  </si>
+  <si>
+    <t>Opportunity</t>
+  </si>
+  <si>
+    <t>Preemption</t>
+  </si>
+  <si>
+    <t>Technique</t>
+  </si>
+  <si>
+    <t>Tenacity</t>
+  </si>
+  <si>
+    <t>barrier</t>
+  </si>
+  <si>
+    <t>combat</t>
+  </si>
+  <si>
+    <t>concentration</t>
+  </si>
+  <si>
+    <t>deception</t>
+  </si>
+  <si>
+    <t>destruction</t>
+  </si>
+  <si>
+    <t>flash</t>
+  </si>
+  <si>
+    <t>gloom</t>
+  </si>
+  <si>
+    <t>linkage</t>
+  </si>
+  <si>
+    <t>meditation</t>
+  </si>
+  <si>
+    <t>opportunity</t>
+  </si>
+  <si>
+    <t>preemption</t>
+  </si>
+  <si>
+    <t>technique</t>
+  </si>
+  <si>
+    <t>tenacity</t>
+  </si>
+  <si>
+    <t>mapo-tofu</t>
+  </si>
+  <si>
+    <t>ley-line</t>
+  </si>
+  <si>
+    <t>The Priest's Blessing</t>
+  </si>
+  <si>
+    <t>the-priests-blessing</t>
+  </si>
+  <si>
+    <t>Goff Punch</t>
+  </si>
+  <si>
+    <t>goff-punch</t>
+  </si>
+  <si>
+    <t>Can you keep up?</t>
+  </si>
+  <si>
+    <t>can-you-keep-up</t>
+  </si>
+  <si>
+    <t>Chaldea Library</t>
+  </si>
+  <si>
+    <t>Chaldea Gym</t>
+  </si>
+  <si>
+    <t>Chaldea Cafeteria</t>
+  </si>
+  <si>
+    <t>chaldea-library</t>
+  </si>
+  <si>
+    <t>chaldea-gym</t>
+  </si>
+  <si>
+    <t>chaldea-cafeteria</t>
+  </si>
+  <si>
+    <t>Wandering Sea</t>
+  </si>
+  <si>
+    <t>wandering-sea</t>
+  </si>
+  <si>
+    <t>EX Saber</t>
+  </si>
+  <si>
+    <t>EX Lancer</t>
+  </si>
+  <si>
+    <t>EX Archer</t>
+  </si>
+  <si>
+    <t>EX Rider</t>
+  </si>
+  <si>
+    <t>EX Alter Ego</t>
+  </si>
+  <si>
+    <t>EX Assassin</t>
+  </si>
+  <si>
+    <t>EX Caster</t>
+  </si>
+  <si>
+    <t>EX Berserker</t>
+  </si>
+  <si>
+    <t>EX Ruler</t>
+  </si>
+  <si>
+    <t>EX Avenger</t>
+  </si>
+  <si>
+    <t>EX Foreigner</t>
+  </si>
+  <si>
+    <t>EX Moon Cancer</t>
+  </si>
+  <si>
+    <t>Black Barrel</t>
+  </si>
+  <si>
+    <t>ex-saber</t>
+  </si>
+  <si>
+    <t>ex-lancer</t>
+  </si>
+  <si>
+    <t>ex-archer</t>
+  </si>
+  <si>
+    <t>ex-rider</t>
+  </si>
+  <si>
+    <t>ex-assassin</t>
+  </si>
+  <si>
+    <t>ex-caster</t>
+  </si>
+  <si>
+    <t>ex-berserker</t>
+  </si>
+  <si>
+    <t>ex-ruler</t>
+  </si>
+  <si>
+    <t>ex-avenger</t>
+  </si>
+  <si>
+    <t>ex-foreigner</t>
+  </si>
+  <si>
+    <t>black-barrel</t>
+  </si>
+  <si>
+    <t>ex-alter-ego</t>
+  </si>
+  <si>
+    <t>ex-moon-cancer</t>
+  </si>
+  <si>
+    <t>Force-of Providence</t>
+  </si>
+  <si>
+    <t>force-of-providence</t>
+  </si>
+  <si>
+    <t>Russian Lostbelt</t>
+  </si>
+  <si>
+    <t>russian-lostbelt</t>
+  </si>
+  <si>
+    <t>Fast Expansion</t>
+  </si>
+  <si>
+    <t>fast-expansion</t>
+  </si>
+  <si>
+    <t>Frozen Wastes</t>
+  </si>
+  <si>
+    <t>Royal Decree</t>
+  </si>
+  <si>
+    <t>Survival of the Fittest</t>
+  </si>
+  <si>
+    <t>frozen-wastes</t>
+  </si>
+  <si>
+    <t>royal-decree</t>
+  </si>
+  <si>
+    <t>survival-of-the-fittest</t>
+  </si>
+  <si>
+    <t>Scandinavian Lostbelt</t>
+  </si>
+  <si>
+    <t>scandinavian-lostbelt</t>
+  </si>
+  <si>
+    <t>Prolongation</t>
+  </si>
+  <si>
+    <t>prolongation</t>
+  </si>
+  <si>
+    <t>World Eater</t>
+  </si>
+  <si>
+    <t>world-eater</t>
+  </si>
+  <si>
+    <t>A Day of Peace</t>
+  </si>
+  <si>
+    <t>a-day-of-peace</t>
+  </si>
+  <si>
+    <t>Skadi's Domain</t>
+  </si>
+  <si>
+    <t>Surtr's Domain</t>
+  </si>
+  <si>
+    <t>The Envoys' Domain</t>
+  </si>
+  <si>
+    <t>the-envoys-domain</t>
+  </si>
+  <si>
+    <t>surtrs-domain</t>
+  </si>
+  <si>
+    <t>skadis-domain</t>
+  </si>
+  <si>
+    <t>Chinese Lostbelt</t>
+  </si>
+  <si>
+    <t>chinese-lostbelt</t>
+  </si>
+  <si>
+    <t>Qin Shi Huang</t>
+  </si>
+  <si>
+    <t>qin-shi-huang</t>
+  </si>
+  <si>
+    <t>Eternal Lament</t>
+  </si>
+  <si>
+    <t>eternal-lament</t>
+  </si>
+  <si>
+    <t>True Ancestor</t>
+  </si>
+  <si>
+    <t>true-ancestor</t>
+  </si>
+  <si>
+    <t>Deep Dive</t>
+  </si>
+  <si>
+    <t>Deep Lore</t>
+  </si>
+  <si>
+    <t>Walk under the Sun</t>
+  </si>
+  <si>
+    <t>Walk on Water</t>
+  </si>
+  <si>
+    <t>Walk on Clouds</t>
+  </si>
+  <si>
+    <t>Storm the Capital</t>
+  </si>
+  <si>
+    <t>Quest for Perfection</t>
+  </si>
+  <si>
+    <t>Quest for Immortality</t>
+  </si>
+  <si>
+    <t>Deep Tranquility</t>
+  </si>
+  <si>
+    <t>deep-dive</t>
+  </si>
+  <si>
+    <t>deep-lore</t>
+  </si>
+  <si>
+    <t>deep-tranquility</t>
+  </si>
+  <si>
+    <t>walk-under-the-sun</t>
+  </si>
+  <si>
+    <t>walk-on-water</t>
+  </si>
+  <si>
+    <t>walk-on-clouds</t>
+  </si>
+  <si>
+    <t>storm-the-capital</t>
+  </si>
+  <si>
+    <t>quest-for-perfection</t>
+  </si>
+  <si>
+    <t>quest-for-immortality</t>
+  </si>
+  <si>
+    <t>Nirvana</t>
+  </si>
+  <si>
+    <t>nirvana</t>
+  </si>
+  <si>
+    <t>Indian Lostbelt</t>
+  </si>
+  <si>
+    <t>Yuga Cycle</t>
+  </si>
+  <si>
+    <t>Sutra Yuga</t>
+  </si>
+  <si>
+    <t>Treta Yuga</t>
+  </si>
+  <si>
+    <t>Dvapara Yuga</t>
+  </si>
+  <si>
+    <t>Kali Yuga</t>
+  </si>
+  <si>
+    <t>Judgement</t>
+  </si>
+  <si>
+    <t>indian-lostbelt</t>
+  </si>
+  <si>
+    <t>yuga-cycle</t>
+  </si>
+  <si>
+    <t>sutra-yuga</t>
+  </si>
+  <si>
+    <t>treta-yuga</t>
+  </si>
+  <si>
+    <t>dvapara-yuga</t>
+  </si>
+  <si>
+    <t>kali-yuga</t>
+  </si>
+  <si>
+    <t>judgement-judgement</t>
+  </si>
+  <si>
+    <t>Field Research</t>
+  </si>
+  <si>
+    <t>Lotus Field</t>
+  </si>
+  <si>
+    <t>Hunting Grounds</t>
+  </si>
+  <si>
+    <t>Great Sky Boulder</t>
+  </si>
+  <si>
+    <t>Fading Town</t>
+  </si>
+  <si>
+    <t>Withering Plains</t>
+  </si>
+  <si>
+    <t>Ocean of Milk</t>
+  </si>
+  <si>
+    <t>field-research</t>
+  </si>
+  <si>
+    <t>lotus-field</t>
+  </si>
+  <si>
+    <t>hunting-grounds</t>
+  </si>
+  <si>
+    <t>fading-town</t>
+  </si>
+  <si>
+    <t>withering-plains</t>
+  </si>
+  <si>
+    <t>great-sky-boulder</t>
+  </si>
+  <si>
+    <t>ocean-of-milk</t>
+  </si>
+  <si>
+    <t>Theos Klironomia I</t>
+  </si>
+  <si>
+    <t>Theos Klironomia II</t>
+  </si>
+  <si>
+    <t>Atlantean Lostbelt</t>
+  </si>
+  <si>
+    <t>Olympian Lostbelt</t>
+  </si>
+  <si>
+    <t>Anima Animusphere</t>
+  </si>
+  <si>
+    <t>theos-klironomia-i</t>
+  </si>
+  <si>
+    <t>theos-klironomia-ii</t>
+  </si>
+  <si>
+    <t>atlantean-lostbelt</t>
+  </si>
+  <si>
+    <t>olympian-lostbelt</t>
+  </si>
+  <si>
+    <t>anima-animusphere</t>
+  </si>
+  <si>
+    <t>Grand Order</t>
+  </si>
+  <si>
+    <t>grand-order</t>
+  </si>
+  <si>
+    <t>Demeter's Favour</t>
+  </si>
+  <si>
+    <t>Aphrodite's Favour</t>
+  </si>
+  <si>
+    <t>Zeus' Favour</t>
+  </si>
+  <si>
+    <t>Hephaistos Terminal</t>
+  </si>
+  <si>
+    <t>demeters-favour</t>
+  </si>
+  <si>
+    <t>aphrodites-favour</t>
+  </si>
+  <si>
+    <t>zeus-favour</t>
+  </si>
+  <si>
+    <t>hephaistos-terminal</t>
+  </si>
+  <si>
+    <t>Demon God Baal</t>
+  </si>
+  <si>
+    <t>Demon God Phenex</t>
+  </si>
+  <si>
+    <t>Demon God Barbatos</t>
+  </si>
+  <si>
+    <t>Demon God Zepar</t>
+  </si>
+  <si>
+    <t>Demon God Flauros</t>
+  </si>
+  <si>
+    <t>Demon God Forneus</t>
+  </si>
+  <si>
+    <t>Demon God Raum</t>
+  </si>
+  <si>
+    <t>demon-god-baal</t>
+  </si>
+  <si>
+    <t>demon-god-phenex</t>
+  </si>
+  <si>
+    <t>demon-god-barbatos</t>
+  </si>
+  <si>
+    <t>demon-god-zepar</t>
+  </si>
+  <si>
+    <t>demon-god-flauros</t>
+  </si>
+  <si>
+    <t>demon-god-forneus</t>
+  </si>
+  <si>
+    <t>demon-god-raum</t>
+  </si>
+  <si>
+    <t>Temple of Time</t>
+  </si>
+  <si>
+    <t>temple-of-time</t>
+  </si>
+  <si>
+    <t>Beast of Billows</t>
+  </si>
+  <si>
+    <t>Demon Boar</t>
+  </si>
+  <si>
+    <t>Primal Dragon</t>
+  </si>
+  <si>
+    <t>Sea of Life</t>
+  </si>
+  <si>
+    <t>beast-of-billows</t>
+  </si>
+  <si>
+    <t>demon-boar</t>
+  </si>
+  <si>
+    <t>primal-dragon</t>
+  </si>
+  <si>
+    <t>sea-of-life</t>
+  </si>
+  <si>
+    <t>Titan Form</t>
+  </si>
+  <si>
+    <t>titan-form</t>
+  </si>
+  <si>
+    <t>Lion Feeding</t>
+  </si>
+  <si>
+    <t>lion-feeding</t>
+  </si>
+  <si>
+    <t>The Hungry King</t>
+  </si>
+  <si>
+    <t>the-hungry-king</t>
+  </si>
+  <si>
+    <t>Trimmau</t>
+  </si>
+  <si>
+    <t>trimmau-1</t>
+  </si>
+  <si>
+    <t>trimmau-2</t>
+  </si>
+  <si>
+    <t>trimmau-3</t>
+  </si>
+  <si>
+    <t>trimmau-4</t>
+  </si>
+  <si>
+    <t>Doppelganger</t>
+  </si>
+  <si>
+    <t>doppelganger</t>
+  </si>
+  <si>
+    <t>magical-sapphire-servant</t>
+  </si>
+  <si>
+    <t>Card Selection</t>
+  </si>
+  <si>
+    <t>card-selection</t>
+  </si>
+  <si>
+    <t>saber-install</t>
+  </si>
+  <si>
+    <t>lancer-install</t>
+  </si>
+  <si>
+    <t>archer-install</t>
+  </si>
+  <si>
+    <t>rider-install</t>
+  </si>
+  <si>
+    <t>caster-install</t>
+  </si>
+  <si>
+    <t>assassin-install</t>
+  </si>
+  <si>
+    <t>Spoilt for Choice</t>
+  </si>
+  <si>
+    <t>spoilt-for-choice</t>
+  </si>
+  <si>
+    <t>Death Perception</t>
+  </si>
+  <si>
+    <t>Flash Step</t>
+  </si>
+  <si>
+    <t>Flash Draw</t>
+  </si>
+  <si>
+    <t>death-perception</t>
+  </si>
+  <si>
+    <t>flash-step</t>
+  </si>
+  <si>
+    <t>flash-draw</t>
+  </si>
+  <si>
+    <t>Dark Compulsion</t>
+  </si>
+  <si>
+    <t>dark-compulsion</t>
+  </si>
+  <si>
+    <t>Bloodlust</t>
+  </si>
+  <si>
+    <t>Crimson Red Vermillion</t>
+  </si>
+  <si>
+    <t>bloodlust</t>
+  </si>
+  <si>
+    <t>crimson-red-vermillion</t>
+  </si>
+  <si>
+    <t>Brilliant Phantasm</t>
+  </si>
+  <si>
+    <t>brilliant-phantasm</t>
+  </si>
+  <si>
+    <t>Vampiric Impulse</t>
+  </si>
+  <si>
+    <t>marble-phantasm</t>
+  </si>
+  <si>
+    <t>vampiric-impulse</t>
+  </si>
+  <si>
+    <t>Castle Brunestud</t>
+  </si>
+  <si>
+    <t>castle-brunestud</t>
+  </si>
+  <si>
+    <t>Cremation Rites</t>
+  </si>
+  <si>
+    <t>cremation-rites</t>
+  </si>
+  <si>
+    <t>7th Holy Scripture</t>
+  </si>
+  <si>
+    <t>7th-holy-scripture</t>
+  </si>
+  <si>
+    <t>Powered Mode</t>
+  </si>
+  <si>
+    <t>powered-mode</t>
+  </si>
+  <si>
+    <t>Burned Workshop</t>
+  </si>
+  <si>
+    <t>burned-workshop</t>
+  </si>
+  <si>
+    <t>"Magical" Onslaught</t>
+  </si>
+  <si>
+    <t>magical-onslaught</t>
+  </si>
+  <si>
+    <t>Mech-Hisui</t>
+  </si>
+  <si>
+    <t>mech-hisui</t>
+  </si>
+  <si>
+    <t>Clue</t>
+  </si>
+  <si>
+    <t>clue</t>
+  </si>
+  <si>
+    <t>Confrontation</t>
+  </si>
+  <si>
+    <t>confrontation</t>
+  </si>
+  <si>
+    <t>Deduction Mode</t>
+  </si>
+  <si>
+    <t>deduction-mode</t>
+  </si>
+  <si>
+    <t>The Stalker</t>
+  </si>
+  <si>
+    <t>The Devourer</t>
+  </si>
+  <si>
+    <t>The Watcher</t>
+  </si>
+  <si>
+    <t>The Lurker</t>
+  </si>
+  <si>
+    <t>The Colossus</t>
+  </si>
+  <si>
+    <t>The Violator</t>
+  </si>
+  <si>
+    <t>The Hunter</t>
+  </si>
+  <si>
+    <t>The Horror</t>
+  </si>
+  <si>
+    <t>The Sentinels</t>
+  </si>
+  <si>
+    <t>The Emperor</t>
+  </si>
+  <si>
+    <t>The Breaker</t>
+  </si>
+  <si>
+    <t>The Scourge</t>
+  </si>
+  <si>
+    <t>The Phantasm</t>
+  </si>
+  <si>
+    <t>The Primordial</t>
+  </si>
+  <si>
+    <t>The 999th</t>
+  </si>
+  <si>
+    <t>the-stalker</t>
+  </si>
+  <si>
+    <t>the-devourer</t>
+  </si>
+  <si>
+    <t>the-watcher</t>
+  </si>
+  <si>
+    <t>the-lurker</t>
+  </si>
+  <si>
+    <t>the-colossus</t>
+  </si>
+  <si>
+    <t>the-violator</t>
+  </si>
+  <si>
+    <t>the-hunter</t>
+  </si>
+  <si>
+    <t>the-horror</t>
+  </si>
+  <si>
+    <t>the-sentinels</t>
+  </si>
+  <si>
+    <t>the-emperor</t>
+  </si>
+  <si>
+    <t>the-breaker</t>
+  </si>
+  <si>
+    <t>the-scourge</t>
+  </si>
+  <si>
+    <t>the-phantasm</t>
+  </si>
+  <si>
+    <t>the-primordial</t>
+  </si>
+  <si>
+    <t>the-999th</t>
+  </si>
+  <si>
+    <t>Army of One</t>
+  </si>
+  <si>
+    <t>army-of-one</t>
+  </si>
+  <si>
+    <t>Scrambled Seal</t>
+  </si>
+  <si>
+    <t>scrambled-seal</t>
+  </si>
+  <si>
+    <t>Michael Roa Valdamjong</t>
+  </si>
+  <si>
+    <t>Elesia</t>
+  </si>
+  <si>
+    <t>Reincarnation</t>
+  </si>
+  <si>
+    <t>Overload</t>
+  </si>
+  <si>
+    <t>michael-roa-valdamjong</t>
+  </si>
+  <si>
+    <t>elesia</t>
+  </si>
+  <si>
+    <t>reincarnation</t>
+  </si>
+  <si>
+    <t>overload</t>
+  </si>
+  <si>
+    <t>Ultimate Form</t>
+  </si>
+  <si>
+    <t>ultimate-form</t>
+  </si>
+  <si>
+    <t>Eroding Detachment</t>
+  </si>
+  <si>
+    <t>The Demon</t>
+  </si>
+  <si>
+    <t>The Serpent</t>
+  </si>
+  <si>
+    <t>eroding-detachment</t>
+  </si>
+  <si>
+    <t>the-demon</t>
+  </si>
+  <si>
+    <t>the-serpent</t>
+  </si>
+  <si>
+    <t>Sobering Lucidity</t>
+  </si>
+  <si>
+    <t>sobering-lucidity</t>
+  </si>
+  <si>
+    <t>Fear</t>
+  </si>
+  <si>
+    <t>Madness</t>
+  </si>
+  <si>
+    <t>Drama</t>
+  </si>
+  <si>
+    <t>Darkness</t>
+  </si>
+  <si>
+    <t>Phobia</t>
+  </si>
+  <si>
+    <t>Malice</t>
+  </si>
+  <si>
+    <t>fear</t>
+  </si>
+  <si>
+    <t>madness</t>
+  </si>
+  <si>
+    <t>drama</t>
+  </si>
+  <si>
+    <t>darkness</t>
+  </si>
+  <si>
+    <t>phobia</t>
+  </si>
+  <si>
+    <t>malice</t>
+  </si>
+  <si>
+    <t>Malignant Replicator</t>
+  </si>
+  <si>
+    <t>malignant-replicator</t>
+  </si>
+  <si>
+    <t>TATARI</t>
+  </si>
+  <si>
+    <t>tatari</t>
+  </si>
+  <si>
+    <t>Phantom Grasp</t>
+  </si>
+  <si>
+    <t>Sever Life</t>
+  </si>
+  <si>
+    <t>phantom-grasp</t>
+  </si>
+  <si>
+    <t>sever-life</t>
+  </si>
+  <si>
+    <t>Boundary of Emptiness</t>
+  </si>
+  <si>
+    <t>boundary-of-emptiness</t>
+  </si>
+  <si>
+    <t>Warp Space</t>
+  </si>
+  <si>
+    <t>Stomach Injury</t>
+  </si>
+  <si>
+    <t>Leg Injury</t>
+  </si>
+  <si>
+    <t>Wrist Injury</t>
+  </si>
+  <si>
+    <t>Shoulder Injury</t>
+  </si>
+  <si>
+    <t>Head Injury</t>
+  </si>
+  <si>
+    <t>Spinal Injury</t>
+  </si>
+  <si>
+    <t>Distortion</t>
+  </si>
+  <si>
+    <t>warp-space</t>
+  </si>
+  <si>
+    <t>stomach-injury</t>
+  </si>
+  <si>
+    <t>leg-injury</t>
+  </si>
+  <si>
+    <t>wrist-injury</t>
+  </si>
+  <si>
+    <t>shoulder-injury</t>
+  </si>
+  <si>
+    <t>head-injury</t>
+  </si>
+  <si>
+    <t>spinal-injury</t>
+  </si>
+  <si>
+    <t>distortion</t>
+  </si>
+  <si>
+    <t>A Remaining Sense of Pain</t>
+  </si>
+  <si>
+    <t>a-remaining-sense-of-pain</t>
+  </si>
+  <si>
+    <t>Paradox Spiral</t>
+  </si>
+  <si>
+    <t>paradox-spiral</t>
+  </si>
+  <si>
+    <t>VP Gain,Cheap Power,Adaptable</t>
+  </si>
+  <si>
+    <t>day-1</t>
+  </si>
+  <si>
+    <t>day-2</t>
+  </si>
+  <si>
+    <t>day-3</t>
+  </si>
+  <si>
+    <t>day-4</t>
+  </si>
+  <si>
+    <t>old-acquaintances</t>
   </si>
 </sst>
 </file>
@@ -6333,16 +8021,16 @@
         <v>1516</v>
       </c>
       <c r="O1" s="3" t="s">
+        <v>1884</v>
+      </c>
+      <c r="P1" s="3" t="s">
         <v>1885</v>
       </c>
-      <c r="P1" s="3" t="s">
+      <c r="Q1" s="3" t="s">
         <v>1886</v>
       </c>
-      <c r="Q1" s="3" t="s">
-        <v>1890</v>
-      </c>
       <c r="R1" s="1" t="s">
-        <v>1897</v>
+        <v>1892</v>
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.25">
@@ -11528,7 +13216,7 @@
         <v>1066</v>
       </c>
       <c r="M154" s="2" t="s">
-        <v>1840</v>
+        <v>2501</v>
       </c>
       <c r="N154" s="2" t="s">
         <v>1544</v>
@@ -11563,7 +13251,7 @@
         <v>1071</v>
       </c>
       <c r="M155" s="2" t="s">
-        <v>1841</v>
+        <v>1840</v>
       </c>
       <c r="N155" s="2" t="s">
         <v>1550</v>
@@ -11665,10 +13353,10 @@
         <v>744</v>
       </c>
       <c r="M158" s="2" t="s">
+        <v>1841</v>
+      </c>
+      <c r="N158" s="2" t="s">
         <v>1842</v>
-      </c>
-      <c r="N158" s="2" t="s">
-        <v>1843</v>
       </c>
     </row>
     <row r="159" spans="1:14" x14ac:dyDescent="0.25">
@@ -11700,7 +13388,7 @@
         <v>1831</v>
       </c>
       <c r="N159" s="2" t="s">
-        <v>1844</v>
+        <v>1843</v>
       </c>
     </row>
     <row r="160" spans="1:14" x14ac:dyDescent="0.25">
@@ -11732,10 +13420,10 @@
         <v>1507</v>
       </c>
       <c r="M160" s="2" t="s">
+        <v>1844</v>
+      </c>
+      <c r="N160" s="2" t="s">
         <v>1845</v>
-      </c>
-      <c r="N160" s="2" t="s">
-        <v>1846</v>
       </c>
     </row>
     <row r="161" spans="1:14" x14ac:dyDescent="0.25">
@@ -11764,10 +13452,10 @@
         <v>1073</v>
       </c>
       <c r="M161" s="2" t="s">
+        <v>1846</v>
+      </c>
+      <c r="N161" s="2" t="s">
         <v>1847</v>
-      </c>
-      <c r="N161" s="2" t="s">
-        <v>1848</v>
       </c>
     </row>
     <row r="162" spans="1:14" x14ac:dyDescent="0.25">
@@ -11796,7 +13484,7 @@
         <v>1074</v>
       </c>
       <c r="M162" s="2" t="s">
-        <v>1849</v>
+        <v>1848</v>
       </c>
       <c r="N162" s="2" t="s">
         <v>1561</v>
@@ -11834,7 +13522,7 @@
         <v>1589</v>
       </c>
       <c r="N163" s="2" t="s">
-        <v>1851</v>
+        <v>1850</v>
       </c>
     </row>
     <row r="164" spans="1:14" x14ac:dyDescent="0.25">
@@ -11869,7 +13557,7 @@
         <v>1731</v>
       </c>
       <c r="N164" s="2" t="s">
-        <v>1852</v>
+        <v>1851</v>
       </c>
     </row>
     <row r="165" spans="1:14" x14ac:dyDescent="0.25">
@@ -11901,7 +13589,7 @@
         <v>1762</v>
       </c>
       <c r="N165" s="2" t="s">
-        <v>1853</v>
+        <v>1852</v>
       </c>
     </row>
     <row r="166" spans="1:14" x14ac:dyDescent="0.25">
@@ -11933,10 +13621,10 @@
         <v>1196</v>
       </c>
       <c r="M166" s="2" t="s">
+        <v>1853</v>
+      </c>
+      <c r="N166" s="2" t="s">
         <v>1854</v>
-      </c>
-      <c r="N166" s="2" t="s">
-        <v>1855</v>
       </c>
     </row>
     <row r="167" spans="1:14" x14ac:dyDescent="0.25">
@@ -11968,10 +13656,10 @@
         <v>1200</v>
       </c>
       <c r="M167" s="2" t="s">
+        <v>1855</v>
+      </c>
+      <c r="N167" s="2" t="s">
         <v>1856</v>
-      </c>
-      <c r="N167" s="2" t="s">
-        <v>1857</v>
       </c>
     </row>
     <row r="168" spans="1:14" x14ac:dyDescent="0.25">
@@ -12035,7 +13723,7 @@
         <v>1196</v>
       </c>
       <c r="M169" s="2" t="s">
-        <v>1858</v>
+        <v>1857</v>
       </c>
       <c r="N169" s="2" t="s">
         <v>1834</v>
@@ -12073,7 +13761,7 @@
         <v>1</v>
       </c>
       <c r="M170" s="2" t="s">
-        <v>1859</v>
+        <v>1858</v>
       </c>
       <c r="N170" s="2" t="s">
         <v>1543</v>
@@ -12111,10 +13799,10 @@
         <v>1</v>
       </c>
       <c r="M171" s="2" t="s">
+        <v>1859</v>
+      </c>
+      <c r="N171" s="2" t="s">
         <v>1860</v>
-      </c>
-      <c r="N171" s="2" t="s">
-        <v>1861</v>
       </c>
     </row>
     <row r="172" spans="1:14" x14ac:dyDescent="0.25">
@@ -12146,7 +13834,7 @@
         <v>1731</v>
       </c>
       <c r="N172" s="2" t="s">
-        <v>1862</v>
+        <v>1861</v>
       </c>
     </row>
     <row r="173" spans="1:14" x14ac:dyDescent="0.25">
@@ -12216,10 +13904,10 @@
         <v>1</v>
       </c>
       <c r="M174" s="2" t="s">
+        <v>1862</v>
+      </c>
+      <c r="N174" s="2" t="s">
         <v>1863</v>
-      </c>
-      <c r="N174" s="2" t="s">
-        <v>1864</v>
       </c>
     </row>
     <row r="175" spans="1:14" x14ac:dyDescent="0.25">
@@ -12254,10 +13942,10 @@
         <v>1</v>
       </c>
       <c r="M175" s="2" t="s">
+        <v>1864</v>
+      </c>
+      <c r="N175" s="2" t="s">
         <v>1865</v>
-      </c>
-      <c r="N175" s="2" t="s">
-        <v>1866</v>
       </c>
     </row>
     <row r="176" spans="1:14" x14ac:dyDescent="0.25">
@@ -12295,7 +13983,7 @@
         <v>1832</v>
       </c>
       <c r="N176" s="2" t="s">
-        <v>1867</v>
+        <v>1866</v>
       </c>
     </row>
     <row r="177" spans="1:15" x14ac:dyDescent="0.25">
@@ -12327,10 +14015,10 @@
         <v>436</v>
       </c>
       <c r="M177" s="2" t="s">
+        <v>1867</v>
+      </c>
+      <c r="N177" s="2" t="s">
         <v>1868</v>
-      </c>
-      <c r="N177" s="2" t="s">
-        <v>1869</v>
       </c>
     </row>
     <row r="178" spans="1:15" x14ac:dyDescent="0.25">
@@ -12362,10 +14050,10 @@
         <v>1206</v>
       </c>
       <c r="M178" s="2" t="s">
-        <v>1870</v>
+        <v>1869</v>
       </c>
       <c r="N178" s="2" t="s">
-        <v>1872</v>
+        <v>1871</v>
       </c>
     </row>
     <row r="179" spans="1:15" x14ac:dyDescent="0.25">
@@ -12397,10 +14085,10 @@
         <v>35</v>
       </c>
       <c r="M179" s="2" t="s">
+        <v>1872</v>
+      </c>
+      <c r="N179" s="2" t="s">
         <v>1873</v>
-      </c>
-      <c r="N179" s="2" t="s">
-        <v>1874</v>
       </c>
     </row>
     <row r="180" spans="1:15" x14ac:dyDescent="0.25">
@@ -12432,7 +14120,7 @@
         <v>1686</v>
       </c>
       <c r="N180" s="2" t="s">
-        <v>1875</v>
+        <v>1874</v>
       </c>
     </row>
     <row r="181" spans="1:15" x14ac:dyDescent="0.25">
@@ -12464,7 +14152,7 @@
         <v>1208</v>
       </c>
       <c r="M181" s="2" t="s">
-        <v>1876</v>
+        <v>1875</v>
       </c>
       <c r="N181" s="2" t="s">
         <v>1543</v>
@@ -12496,10 +14184,10 @@
         <v>186</v>
       </c>
       <c r="M182" s="2" t="s">
+        <v>1877</v>
+      </c>
+      <c r="N182" s="2" t="s">
         <v>1878</v>
-      </c>
-      <c r="N182" s="2" t="s">
-        <v>1879</v>
       </c>
     </row>
     <row r="183" spans="1:15" x14ac:dyDescent="0.25">
@@ -12534,7 +14222,7 @@
         <v>1667</v>
       </c>
       <c r="N183" s="2" t="s">
-        <v>1880</v>
+        <v>1879</v>
       </c>
     </row>
     <row r="184" spans="1:15" x14ac:dyDescent="0.25">
@@ -12566,10 +14254,10 @@
         <v>179</v>
       </c>
       <c r="M184" s="2" t="s">
+        <v>1880</v>
+      </c>
+      <c r="N184" s="2" t="s">
         <v>1881</v>
-      </c>
-      <c r="N184" s="2" t="s">
-        <v>1882</v>
       </c>
     </row>
     <row r="185" spans="1:15" x14ac:dyDescent="0.25">
@@ -12601,7 +14289,7 @@
         <v>1</v>
       </c>
       <c r="M185" s="2" t="s">
-        <v>1883</v>
+        <v>1882</v>
       </c>
       <c r="N185" s="2" t="s">
         <v>1543</v>
@@ -12609,13 +14297,13 @@
     </row>
     <row r="186" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>1898</v>
+        <v>1893</v>
       </c>
       <c r="B186" t="s">
-        <v>1899</v>
+        <v>1894</v>
       </c>
       <c r="C186" t="s">
-        <v>1900</v>
+        <v>1895</v>
       </c>
       <c r="D186" t="s">
         <v>7</v>
@@ -12647,13 +14335,13 @@
     </row>
     <row r="187" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
+        <v>1896</v>
+      </c>
+      <c r="B187" t="s">
         <v>1901</v>
       </c>
-      <c r="B187" t="s">
-        <v>1906</v>
-      </c>
       <c r="C187" t="s">
-        <v>1909</v>
+        <v>1904</v>
       </c>
       <c r="D187" t="s">
         <v>7</v>
@@ -12662,7 +14350,7 @@
         <v>8</v>
       </c>
       <c r="G187" s="2" t="s">
-        <v>1907</v>
+        <v>1902</v>
       </c>
       <c r="H187" s="2" t="s">
         <v>395</v>
@@ -12671,13 +14359,13 @@
         <v>81</v>
       </c>
       <c r="J187" s="2" t="s">
-        <v>1908</v>
+        <v>1903</v>
       </c>
       <c r="M187" s="2" t="s">
         <v>1520</v>
       </c>
       <c r="N187" s="2" t="s">
-        <v>1905</v>
+        <v>1900</v>
       </c>
       <c r="O187" t="b">
         <v>1</v>
@@ -12685,13 +14373,13 @@
     </row>
     <row r="188" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>1902</v>
+        <v>1897</v>
       </c>
       <c r="B188" t="s">
-        <v>1914</v>
+        <v>1909</v>
       </c>
       <c r="C188" t="s">
-        <v>1915</v>
+        <v>1910</v>
       </c>
       <c r="D188" t="s">
         <v>317</v>
@@ -12712,10 +14400,10 @@
         <v>270</v>
       </c>
       <c r="M188" s="2" t="s">
-        <v>1916</v>
+        <v>1911</v>
       </c>
       <c r="N188" s="2" t="s">
-        <v>1917</v>
+        <v>1912</v>
       </c>
       <c r="O188" t="b">
         <v>1</v>
@@ -12723,16 +14411,16 @@
     </row>
     <row r="189" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>1919</v>
+        <v>1914</v>
       </c>
       <c r="B189" t="s">
-        <v>1920</v>
+        <v>1915</v>
       </c>
       <c r="C189" t="s">
-        <v>1921</v>
+        <v>1916</v>
       </c>
       <c r="D189" t="s">
-        <v>1922</v>
+        <v>1917</v>
       </c>
       <c r="E189" t="s">
         <v>8</v>
@@ -12747,10 +14435,10 @@
         <v>192</v>
       </c>
       <c r="M189" s="2" t="s">
-        <v>1923</v>
+        <v>1918</v>
       </c>
       <c r="N189" s="2" t="s">
-        <v>1924</v>
+        <v>1919</v>
       </c>
       <c r="O189" t="b">
         <v>1</v>
@@ -12770,8 +14458,8 @@
   <dimension ref="A1:B62"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.140625" customWidth="1"/>
-    <col min="2" max="2" width="17" customWidth="1"/>
+    <col min="1" max="1" width="31.140625" customWidth="1"/>
+    <col min="2" max="2" width="26" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -13067,7 +14755,7 @@
         <v>1335</v>
       </c>
       <c r="B37" t="s">
-        <v>1905</v>
+        <v>1900</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
@@ -13172,17 +14860,17 @@
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>1850</v>
+        <v>1849</v>
       </c>
     </row>
     <row r="59" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>1871</v>
+        <v>1870</v>
       </c>
     </row>
     <row r="60" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>1877</v>
+        <v>1876</v>
       </c>
     </row>
     <row r="61" spans="1:1" x14ac:dyDescent="0.25">
@@ -13192,7 +14880,7 @@
     </row>
     <row r="62" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>1913</v>
+        <v>1908</v>
       </c>
     </row>
   </sheetData>
@@ -13233,7 +14921,7 @@
         <v>3</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>1892</v>
+        <v>1888</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
@@ -13667,7 +15355,7 @@
         <v>51</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>1893</v>
+        <v>1888</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
@@ -23056,27 +24744,27 @@
     </row>
     <row r="554" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A554" t="s">
+        <v>1893</v>
+      </c>
+      <c r="B554" t="s">
+        <v>1894</v>
+      </c>
+      <c r="C554">
+        <v>1</v>
+      </c>
+      <c r="D554" t="b">
+        <v>0</v>
+      </c>
+      <c r="E554" t="s">
         <v>1898</v>
-      </c>
-      <c r="B554" t="s">
-        <v>1899</v>
-      </c>
-      <c r="C554">
-        <v>1</v>
-      </c>
-      <c r="D554" t="b">
-        <v>0</v>
-      </c>
-      <c r="E554" t="s">
-        <v>1903</v>
       </c>
     </row>
     <row r="555" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A555" t="s">
-        <v>1898</v>
+        <v>1893</v>
       </c>
       <c r="B555" t="s">
-        <v>1899</v>
+        <v>1894</v>
       </c>
       <c r="C555">
         <v>2</v>
@@ -23085,15 +24773,15 @@
         <v>0</v>
       </c>
       <c r="E555" t="s">
-        <v>1904</v>
+        <v>1899</v>
       </c>
     </row>
     <row r="556" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A556" t="s">
-        <v>1898</v>
+        <v>1893</v>
       </c>
       <c r="B556" t="s">
-        <v>1899</v>
+        <v>1894</v>
       </c>
       <c r="C556">
         <v>3</v>
@@ -23102,16 +24790,16 @@
         <v>0</v>
       </c>
       <c r="E556" t="s">
-        <v>1904</v>
+        <v>1899</v>
       </c>
     </row>
     <row r="557" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A557" t="s">
+        <v>1896</v>
+      </c>
+      <c r="B557" t="s">
         <v>1901</v>
       </c>
-      <c r="B557" t="s">
-        <v>1906</v>
-      </c>
       <c r="C557">
         <v>1</v>
       </c>
@@ -23119,15 +24807,15 @@
         <v>0</v>
       </c>
       <c r="E557" t="s">
-        <v>1910</v>
+        <v>1905</v>
       </c>
     </row>
     <row r="558" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A558" t="s">
+        <v>1896</v>
+      </c>
+      <c r="B558" t="s">
         <v>1901</v>
-      </c>
-      <c r="B558" t="s">
-        <v>1906</v>
       </c>
       <c r="C558">
         <v>2</v>
@@ -23136,15 +24824,15 @@
         <v>0</v>
       </c>
       <c r="E558" t="s">
-        <v>1911</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="559" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A559" t="s">
+        <v>1896</v>
+      </c>
+      <c r="B559" t="s">
         <v>1901</v>
-      </c>
-      <c r="B559" t="s">
-        <v>1906</v>
       </c>
       <c r="C559">
         <v>3</v>
@@ -23153,15 +24841,15 @@
         <v>0</v>
       </c>
       <c r="E559" t="s">
-        <v>1912</v>
+        <v>1907</v>
       </c>
     </row>
     <row r="560" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A560" t="s">
-        <v>1902</v>
+        <v>1897</v>
       </c>
       <c r="B560" t="s">
-        <v>1914</v>
+        <v>1909</v>
       </c>
       <c r="C560">
         <v>1</v>
@@ -23175,10 +24863,10 @@
     </row>
     <row r="561" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A561" t="s">
-        <v>1902</v>
+        <v>1897</v>
       </c>
       <c r="B561" t="s">
-        <v>1914</v>
+        <v>1909</v>
       </c>
       <c r="C561">
         <v>2</v>
@@ -23192,10 +24880,10 @@
     </row>
     <row r="562" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A562" t="s">
-        <v>1902</v>
+        <v>1897</v>
       </c>
       <c r="B562" t="s">
-        <v>1914</v>
+        <v>1909</v>
       </c>
       <c r="C562">
         <v>3</v>
@@ -23204,32 +24892,32 @@
         <v>0</v>
       </c>
       <c r="E562" t="s">
-        <v>1918</v>
+        <v>1913</v>
       </c>
     </row>
     <row r="563" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A563" t="s">
-        <v>1919</v>
+        <v>1914</v>
       </c>
       <c r="B563" t="s">
+        <v>1915</v>
+      </c>
+      <c r="C563">
+        <v>1</v>
+      </c>
+      <c r="D563" t="b">
+        <v>1</v>
+      </c>
+      <c r="E563" t="s">
         <v>1920</v>
-      </c>
-      <c r="C563">
-        <v>1</v>
-      </c>
-      <c r="D563" t="b">
-        <v>1</v>
-      </c>
-      <c r="E563" t="s">
-        <v>1925</v>
       </c>
     </row>
     <row r="564" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A564" t="s">
-        <v>1919</v>
+        <v>1914</v>
       </c>
       <c r="B564" t="s">
-        <v>1920</v>
+        <v>1915</v>
       </c>
       <c r="C564">
         <v>2</v>
@@ -23238,15 +24926,15 @@
         <v>0</v>
       </c>
       <c r="E564" t="s">
-        <v>1927</v>
+        <v>1922</v>
       </c>
     </row>
     <row r="565" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A565" t="s">
-        <v>1919</v>
+        <v>1914</v>
       </c>
       <c r="B565" t="s">
-        <v>1920</v>
+        <v>1915</v>
       </c>
       <c r="C565">
         <v>3</v>
@@ -23255,7 +24943,7 @@
         <v>0</v>
       </c>
       <c r="E565" t="s">
-        <v>1928</v>
+        <v>1923</v>
       </c>
     </row>
   </sheetData>
@@ -23296,13 +24984,13 @@
         <v>1467</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>1926</v>
+        <v>1921</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>75</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>1892</v>
+        <v>1888</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
@@ -23822,16 +25510,16 @@
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>1919</v>
+        <v>1914</v>
       </c>
       <c r="B27" t="s">
-        <v>1920</v>
+        <v>1915</v>
       </c>
       <c r="C27" t="s">
-        <v>1929</v>
+        <v>1924</v>
       </c>
       <c r="D27" t="s">
-        <v>1930</v>
+        <v>1925</v>
       </c>
       <c r="E27" t="s">
         <v>1468</v>
@@ -23845,16 +25533,16 @@
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>1919</v>
+        <v>1914</v>
       </c>
       <c r="B28" t="s">
-        <v>1920</v>
+        <v>1915</v>
       </c>
       <c r="C28" t="s">
-        <v>1931</v>
+        <v>1926</v>
       </c>
       <c r="D28" t="s">
-        <v>1938</v>
+        <v>1933</v>
       </c>
       <c r="E28" t="s">
         <v>1468</v>
@@ -23868,16 +25556,16 @@
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>1919</v>
+        <v>1914</v>
       </c>
       <c r="B29" t="s">
-        <v>1920</v>
+        <v>1915</v>
       </c>
       <c r="C29" t="s">
-        <v>1932</v>
+        <v>1927</v>
       </c>
       <c r="D29" t="s">
-        <v>1939</v>
+        <v>1934</v>
       </c>
       <c r="E29" t="s">
         <v>1468</v>
@@ -23891,16 +25579,16 @@
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>1919</v>
+        <v>1914</v>
       </c>
       <c r="B30" t="s">
-        <v>1920</v>
+        <v>1915</v>
       </c>
       <c r="C30" t="s">
-        <v>1933</v>
+        <v>1928</v>
       </c>
       <c r="D30" t="s">
-        <v>1940</v>
+        <v>1935</v>
       </c>
       <c r="E30" t="s">
         <v>1468</v>
@@ -23914,16 +25602,16 @@
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>1919</v>
+        <v>1914</v>
       </c>
       <c r="B31" t="s">
-        <v>1920</v>
+        <v>1915</v>
       </c>
       <c r="C31" t="s">
-        <v>1934</v>
+        <v>1929</v>
       </c>
       <c r="D31" t="s">
-        <v>1941</v>
+        <v>1936</v>
       </c>
       <c r="E31" t="s">
         <v>1468</v>
@@ -23937,16 +25625,16 @@
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>1919</v>
+        <v>1914</v>
       </c>
       <c r="B32" t="s">
-        <v>1920</v>
+        <v>1915</v>
       </c>
       <c r="C32" t="s">
-        <v>1935</v>
+        <v>1930</v>
       </c>
       <c r="D32" t="s">
-        <v>1942</v>
+        <v>1937</v>
       </c>
       <c r="E32" t="s">
         <v>1468</v>
@@ -23960,16 +25648,16 @@
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>1919</v>
+        <v>1914</v>
       </c>
       <c r="B33" t="s">
-        <v>1920</v>
+        <v>1915</v>
       </c>
       <c r="C33" t="s">
-        <v>1936</v>
+        <v>1931</v>
       </c>
       <c r="D33" t="s">
-        <v>1943</v>
+        <v>1938</v>
       </c>
       <c r="E33" t="s">
         <v>1468</v>
@@ -23983,16 +25671,16 @@
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>1919</v>
+        <v>1914</v>
       </c>
       <c r="B34" t="s">
-        <v>1920</v>
+        <v>1915</v>
       </c>
       <c r="C34" t="s">
-        <v>1937</v>
+        <v>1932</v>
       </c>
       <c r="D34" t="s">
-        <v>1944</v>
+        <v>1939</v>
       </c>
       <c r="E34" t="s">
         <v>1468</v>
@@ -24039,22 +25727,22 @@
         <v>1331</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>1884</v>
+        <v>1883</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>1466</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>1894</v>
+        <v>1889</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>1895</v>
+        <v>1890</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>1896</v>
+        <v>1891</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>1891</v>
+        <v>1887</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
@@ -24841,7 +26529,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>1311</v>
       </c>
@@ -24858,7 +26546,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>1312</v>
       </c>
@@ -24875,7 +26563,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>1313</v>
       </c>
@@ -24892,7 +26580,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>1314</v>
       </c>
@@ -24909,7 +26597,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>1315</v>
       </c>
@@ -24923,7 +26611,7 @@
         <v>1334</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>1316</v>
       </c>
@@ -24940,7 +26628,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>1317</v>
       </c>
@@ -24957,7 +26645,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>1318</v>
       </c>
@@ -24974,7 +26662,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>1319</v>
       </c>
@@ -24991,7 +26679,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>1320</v>
       </c>
@@ -25008,7 +26696,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>1321</v>
       </c>
@@ -25025,7 +26713,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>1322</v>
       </c>
@@ -25042,7 +26730,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>1323</v>
       </c>
@@ -25061,11 +26749,8 @@
       <c r="F61" t="b">
         <v>1</v>
       </c>
-      <c r="G61" t="s">
-        <v>1887</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>1324</v>
       </c>
@@ -25081,11 +26766,8 @@
       <c r="E62" t="b">
         <v>1</v>
       </c>
-      <c r="G62" t="s">
-        <v>1887</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>1325</v>
       </c>
@@ -25102,7 +26784,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>1326</v>
       </c>
@@ -25179,19 +26861,20 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{931309AC-3B5D-4169-8BD3-83BC320E154C}">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:H164"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.7109375" customWidth="1"/>
-    <col min="2" max="2" width="17.85546875" customWidth="1"/>
-    <col min="3" max="3" width="14.5703125" customWidth="1"/>
-    <col min="4" max="4" width="12.42578125" customWidth="1"/>
-    <col min="5" max="5" width="11.5703125" customWidth="1"/>
-    <col min="6" max="6" width="10.5703125" customWidth="1"/>
-    <col min="7" max="7" width="11.7109375" customWidth="1"/>
+    <col min="1" max="1" width="18" customWidth="1"/>
+    <col min="2" max="2" width="33.28515625" customWidth="1"/>
+    <col min="3" max="3" width="25.85546875" customWidth="1"/>
+    <col min="4" max="4" width="29.140625" customWidth="1"/>
+    <col min="5" max="5" width="24.140625" customWidth="1"/>
+    <col min="6" max="6" width="14.28515625" customWidth="1"/>
+    <col min="7" max="7" width="15.140625" customWidth="1"/>
+    <col min="8" max="8" width="11.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>1263</v>
       </c>
@@ -25205,13 +26888,5523 @@
         <v>45</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>1953</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>1467</v>
       </c>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>1264</v>
+      </c>
+      <c r="B2" t="s">
+        <v>510</v>
+      </c>
+      <c r="C2" t="s">
+        <v>1940</v>
+      </c>
+      <c r="D2" t="s">
+        <v>1941</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2" t="s">
+        <v>1468</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>1265</v>
+      </c>
+      <c r="B3" t="s">
+        <v>1332</v>
+      </c>
+      <c r="C3" t="s">
+        <v>1944</v>
+      </c>
+      <c r="D3" t="s">
+        <v>1945</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="F3" t="s">
+        <v>1949</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>1265</v>
+      </c>
+      <c r="B4" t="s">
+        <v>1332</v>
+      </c>
+      <c r="C4" t="s">
+        <v>1946</v>
+      </c>
+      <c r="D4" t="s">
+        <v>1947</v>
+      </c>
+      <c r="E4">
+        <v>2</v>
+      </c>
+      <c r="F4" t="s">
+        <v>1948</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>1266</v>
+      </c>
+      <c r="B5" t="s">
+        <v>1338</v>
+      </c>
+      <c r="C5" t="s">
+        <v>1952</v>
+      </c>
+      <c r="D5" t="s">
+        <v>1954</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5" t="s">
+        <v>1949</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>1266</v>
+      </c>
+      <c r="B6" t="s">
+        <v>1338</v>
+      </c>
+      <c r="C6" t="s">
+        <v>1952</v>
+      </c>
+      <c r="D6" t="s">
+        <v>1955</v>
+      </c>
+      <c r="E6">
+        <v>2</v>
+      </c>
+      <c r="F6" t="s">
+        <v>1949</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>1267</v>
+      </c>
+      <c r="B7" t="s">
+        <v>1339</v>
+      </c>
+      <c r="C7" t="s">
+        <v>1958</v>
+      </c>
+      <c r="D7" t="s">
+        <v>1960</v>
+      </c>
+      <c r="E7">
+        <v>1</v>
+      </c>
+      <c r="F7" t="s">
+        <v>1949</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>1267</v>
+      </c>
+      <c r="B8" t="s">
+        <v>1339</v>
+      </c>
+      <c r="C8" t="s">
+        <v>1959</v>
+      </c>
+      <c r="D8" t="s">
+        <v>1961</v>
+      </c>
+      <c r="E8">
+        <v>2</v>
+      </c>
+      <c r="F8" t="s">
+        <v>1949</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>1268</v>
+      </c>
+      <c r="B9" t="s">
+        <v>1340</v>
+      </c>
+      <c r="C9" t="s">
+        <v>1964</v>
+      </c>
+      <c r="D9" t="s">
+        <v>1965</v>
+      </c>
+      <c r="E9">
+        <v>1</v>
+      </c>
+      <c r="F9" t="s">
+        <v>1949</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>1269</v>
+      </c>
+      <c r="B10" t="s">
+        <v>1341</v>
+      </c>
+      <c r="C10" t="s">
+        <v>1968</v>
+      </c>
+      <c r="D10" t="s">
+        <v>1969</v>
+      </c>
+      <c r="E10">
+        <v>1</v>
+      </c>
+      <c r="F10" t="s">
+        <v>1948</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>1270</v>
+      </c>
+      <c r="B11" t="s">
+        <v>1342</v>
+      </c>
+      <c r="C11" t="s">
+        <v>1972</v>
+      </c>
+      <c r="D11" t="s">
+        <v>1974</v>
+      </c>
+      <c r="E11">
+        <v>1</v>
+      </c>
+      <c r="F11" t="s">
+        <v>1949</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>1270</v>
+      </c>
+      <c r="B12" t="s">
+        <v>1342</v>
+      </c>
+      <c r="C12" t="s">
+        <v>1973</v>
+      </c>
+      <c r="D12" t="s">
+        <v>1975</v>
+      </c>
+      <c r="E12">
+        <v>2</v>
+      </c>
+      <c r="F12" t="s">
+        <v>1949</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>1271</v>
+      </c>
+      <c r="B13" t="s">
+        <v>1343</v>
+      </c>
+      <c r="C13" t="s">
+        <v>1978</v>
+      </c>
+      <c r="D13" t="s">
+        <v>1980</v>
+      </c>
+      <c r="E13">
+        <v>1</v>
+      </c>
+      <c r="F13" t="s">
+        <v>1949</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>1271</v>
+      </c>
+      <c r="B14" t="s">
+        <v>1343</v>
+      </c>
+      <c r="C14" t="s">
+        <v>1979</v>
+      </c>
+      <c r="D14" t="s">
+        <v>1981</v>
+      </c>
+      <c r="E14">
+        <v>2</v>
+      </c>
+      <c r="F14" t="s">
+        <v>1949</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>1273</v>
+      </c>
+      <c r="B15" t="s">
+        <v>1345</v>
+      </c>
+      <c r="C15" t="s">
+        <v>1988</v>
+      </c>
+      <c r="D15" t="s">
+        <v>1995</v>
+      </c>
+      <c r="E15">
+        <v>1</v>
+      </c>
+      <c r="F15" t="s">
+        <v>1949</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>1273</v>
+      </c>
+      <c r="B16" t="s">
+        <v>1345</v>
+      </c>
+      <c r="C16" t="s">
+        <v>1989</v>
+      </c>
+      <c r="D16" t="s">
+        <v>1996</v>
+      </c>
+      <c r="E16">
+        <v>2</v>
+      </c>
+      <c r="F16" t="s">
+        <v>1949</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>1273</v>
+      </c>
+      <c r="B17" t="s">
+        <v>1345</v>
+      </c>
+      <c r="C17" t="s">
+        <v>1990</v>
+      </c>
+      <c r="D17" t="s">
+        <v>2502</v>
+      </c>
+      <c r="E17">
+        <v>3</v>
+      </c>
+      <c r="F17" t="s">
+        <v>1949</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>1273</v>
+      </c>
+      <c r="B18" t="s">
+        <v>1345</v>
+      </c>
+      <c r="C18" t="s">
+        <v>1991</v>
+      </c>
+      <c r="D18" t="s">
+        <v>2503</v>
+      </c>
+      <c r="E18">
+        <v>4</v>
+      </c>
+      <c r="F18" t="s">
+        <v>1949</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>1273</v>
+      </c>
+      <c r="B19" t="s">
+        <v>1345</v>
+      </c>
+      <c r="C19" t="s">
+        <v>1992</v>
+      </c>
+      <c r="D19" t="s">
+        <v>2504</v>
+      </c>
+      <c r="E19">
+        <v>5</v>
+      </c>
+      <c r="F19" t="s">
+        <v>1468</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>1273</v>
+      </c>
+      <c r="B20" t="s">
+        <v>1345</v>
+      </c>
+      <c r="C20" t="s">
+        <v>1993</v>
+      </c>
+      <c r="D20" t="s">
+        <v>2505</v>
+      </c>
+      <c r="E20">
+        <v>6</v>
+      </c>
+      <c r="F20" t="s">
+        <v>1949</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>1273</v>
+      </c>
+      <c r="B21" t="s">
+        <v>1345</v>
+      </c>
+      <c r="C21" t="s">
+        <v>1994</v>
+      </c>
+      <c r="D21" t="s">
+        <v>1997</v>
+      </c>
+      <c r="E21">
+        <v>7</v>
+      </c>
+      <c r="F21" t="s">
+        <v>1468</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>1274</v>
+      </c>
+      <c r="B22" t="s">
+        <v>1346</v>
+      </c>
+      <c r="C22" t="s">
+        <v>1998</v>
+      </c>
+      <c r="D22" t="s">
+        <v>2000</v>
+      </c>
+      <c r="E22">
+        <v>1</v>
+      </c>
+      <c r="F22" t="s">
+        <v>1949</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>1274</v>
+      </c>
+      <c r="B23" t="s">
+        <v>1346</v>
+      </c>
+      <c r="C23" t="s">
+        <v>1999</v>
+      </c>
+      <c r="D23" t="s">
+        <v>2001</v>
+      </c>
+      <c r="E23">
+        <v>2</v>
+      </c>
+      <c r="F23" t="s">
+        <v>1949</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>1276</v>
+      </c>
+      <c r="B24" t="s">
+        <v>1347</v>
+      </c>
+      <c r="C24" t="s">
+        <v>2006</v>
+      </c>
+      <c r="D24" t="s">
+        <v>2007</v>
+      </c>
+      <c r="E24">
+        <v>1</v>
+      </c>
+      <c r="F24" t="s">
+        <v>1948</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>1278</v>
+      </c>
+      <c r="B25" t="s">
+        <v>1349</v>
+      </c>
+      <c r="C25" t="s">
+        <v>2012</v>
+      </c>
+      <c r="D25" t="s">
+        <v>2021</v>
+      </c>
+      <c r="E25">
+        <v>1</v>
+      </c>
+      <c r="F25" t="s">
+        <v>1949</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>1278</v>
+      </c>
+      <c r="B26" t="s">
+        <v>1349</v>
+      </c>
+      <c r="C26" t="s">
+        <v>2013</v>
+      </c>
+      <c r="D26" t="s">
+        <v>2020</v>
+      </c>
+      <c r="E26">
+        <v>2</v>
+      </c>
+      <c r="F26" t="s">
+        <v>1949</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>1278</v>
+      </c>
+      <c r="B27" t="s">
+        <v>1349</v>
+      </c>
+      <c r="C27" t="s">
+        <v>2014</v>
+      </c>
+      <c r="D27" t="s">
+        <v>2019</v>
+      </c>
+      <c r="E27">
+        <v>3</v>
+      </c>
+      <c r="F27" t="s">
+        <v>1949</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>1278</v>
+      </c>
+      <c r="B28" t="s">
+        <v>1349</v>
+      </c>
+      <c r="C28" t="s">
+        <v>2015</v>
+      </c>
+      <c r="D28" t="s">
+        <v>2018</v>
+      </c>
+      <c r="E28">
+        <v>4</v>
+      </c>
+      <c r="F28" t="s">
+        <v>1949</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>1278</v>
+      </c>
+      <c r="B29" t="s">
+        <v>1349</v>
+      </c>
+      <c r="C29" t="s">
+        <v>2016</v>
+      </c>
+      <c r="D29" t="s">
+        <v>2017</v>
+      </c>
+      <c r="E29">
+        <v>5</v>
+      </c>
+      <c r="F29" t="s">
+        <v>1468</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>1279</v>
+      </c>
+      <c r="B30" t="s">
+        <v>1350</v>
+      </c>
+      <c r="C30" t="s">
+        <v>2024</v>
+      </c>
+      <c r="D30" t="s">
+        <v>2025</v>
+      </c>
+      <c r="E30">
+        <v>1</v>
+      </c>
+      <c r="F30" t="s">
+        <v>1949</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>1279</v>
+      </c>
+      <c r="B31" t="s">
+        <v>1350</v>
+      </c>
+      <c r="C31" t="s">
+        <v>2026</v>
+      </c>
+      <c r="D31" t="s">
+        <v>2027</v>
+      </c>
+      <c r="E31">
+        <v>2</v>
+      </c>
+      <c r="F31" t="s">
+        <v>1949</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>1281</v>
+      </c>
+      <c r="B32" t="s">
+        <v>1352</v>
+      </c>
+      <c r="C32" t="s">
+        <v>2032</v>
+      </c>
+      <c r="D32" t="s">
+        <v>2033</v>
+      </c>
+      <c r="E32">
+        <v>1</v>
+      </c>
+      <c r="F32" t="s">
+        <v>1948</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>1281</v>
+      </c>
+      <c r="B33" t="s">
+        <v>1352</v>
+      </c>
+      <c r="C33" t="s">
+        <v>2032</v>
+      </c>
+      <c r="D33" t="s">
+        <v>2034</v>
+      </c>
+      <c r="E33">
+        <v>2</v>
+      </c>
+      <c r="F33" t="s">
+        <v>1948</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>1281</v>
+      </c>
+      <c r="B34" t="s">
+        <v>1352</v>
+      </c>
+      <c r="C34" t="s">
+        <v>2032</v>
+      </c>
+      <c r="D34" t="s">
+        <v>2035</v>
+      </c>
+      <c r="E34">
+        <v>3</v>
+      </c>
+      <c r="F34" t="s">
+        <v>1948</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>1282</v>
+      </c>
+      <c r="B35" t="s">
+        <v>1353</v>
+      </c>
+      <c r="C35" t="s">
+        <v>2038</v>
+      </c>
+      <c r="D35" t="s">
+        <v>2039</v>
+      </c>
+      <c r="E35">
+        <v>1</v>
+      </c>
+      <c r="F35" t="s">
+        <v>1949</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>1283</v>
+      </c>
+      <c r="B36" t="s">
+        <v>1354</v>
+      </c>
+      <c r="C36" t="s">
+        <v>2042</v>
+      </c>
+      <c r="D36" t="s">
+        <v>2043</v>
+      </c>
+      <c r="E36">
+        <v>1</v>
+      </c>
+      <c r="F36" t="s">
+        <v>1949</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>1283</v>
+      </c>
+      <c r="B37" t="s">
+        <v>1354</v>
+      </c>
+      <c r="C37" t="s">
+        <v>2044</v>
+      </c>
+      <c r="D37" t="s">
+        <v>2045</v>
+      </c>
+      <c r="E37">
+        <v>2</v>
+      </c>
+      <c r="F37" t="s">
+        <v>1949</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>1284</v>
+      </c>
+      <c r="B38" t="s">
+        <v>1355</v>
+      </c>
+      <c r="C38" t="s">
+        <v>2048</v>
+      </c>
+      <c r="D38" t="s">
+        <v>2052</v>
+      </c>
+      <c r="E38">
+        <v>1</v>
+      </c>
+      <c r="F38" t="s">
+        <v>1468</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>1284</v>
+      </c>
+      <c r="B39" t="s">
+        <v>1355</v>
+      </c>
+      <c r="C39" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D39" t="s">
+        <v>2053</v>
+      </c>
+      <c r="E39">
+        <v>2</v>
+      </c>
+      <c r="F39" t="s">
+        <v>1468</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>1284</v>
+      </c>
+      <c r="B40" t="s">
+        <v>1355</v>
+      </c>
+      <c r="C40" t="s">
+        <v>2050</v>
+      </c>
+      <c r="D40" t="s">
+        <v>2054</v>
+      </c>
+      <c r="E40">
+        <v>3</v>
+      </c>
+      <c r="F40" t="s">
+        <v>1468</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>1284</v>
+      </c>
+      <c r="B41" t="s">
+        <v>1355</v>
+      </c>
+      <c r="C41" t="s">
+        <v>2051</v>
+      </c>
+      <c r="D41" t="s">
+        <v>2055</v>
+      </c>
+      <c r="E41">
+        <v>4</v>
+      </c>
+      <c r="F41" t="s">
+        <v>1468</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>1285</v>
+      </c>
+      <c r="B42" t="s">
+        <v>1356</v>
+      </c>
+      <c r="C42" t="s">
+        <v>2059</v>
+      </c>
+      <c r="D42" t="s">
+        <v>2060</v>
+      </c>
+      <c r="E42">
+        <v>1</v>
+      </c>
+      <c r="F42" t="s">
+        <v>1949</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>1285</v>
+      </c>
+      <c r="B43" t="s">
+        <v>1356</v>
+      </c>
+      <c r="C43" t="s">
+        <v>2058</v>
+      </c>
+      <c r="D43" t="s">
+        <v>2061</v>
+      </c>
+      <c r="E43">
+        <v>2</v>
+      </c>
+      <c r="F43" t="s">
+        <v>1949</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>1286</v>
+      </c>
+      <c r="B44" t="s">
+        <v>1357</v>
+      </c>
+      <c r="C44" t="s">
+        <v>2064</v>
+      </c>
+      <c r="D44" t="s">
+        <v>2065</v>
+      </c>
+      <c r="E44">
+        <v>1</v>
+      </c>
+      <c r="F44" t="s">
+        <v>1949</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>1288</v>
+      </c>
+      <c r="B45" t="s">
+        <v>1359</v>
+      </c>
+      <c r="C45" t="s">
+        <v>2070</v>
+      </c>
+      <c r="D45" t="s">
+        <v>2071</v>
+      </c>
+      <c r="E45">
+        <v>1</v>
+      </c>
+      <c r="F45" t="s">
+        <v>1949</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>1291</v>
+      </c>
+      <c r="B46" t="s">
+        <v>1362</v>
+      </c>
+      <c r="C46" t="s">
+        <v>2078</v>
+      </c>
+      <c r="D46" t="s">
+        <v>2079</v>
+      </c>
+      <c r="E46">
+        <v>1</v>
+      </c>
+      <c r="F46" t="s">
+        <v>1949</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>1291</v>
+      </c>
+      <c r="B47" t="s">
+        <v>1362</v>
+      </c>
+      <c r="C47" t="s">
+        <v>2080</v>
+      </c>
+      <c r="D47" t="s">
+        <v>2081</v>
+      </c>
+      <c r="E47">
+        <v>2</v>
+      </c>
+      <c r="F47" t="s">
+        <v>1468</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>1291</v>
+      </c>
+      <c r="B48" t="s">
+        <v>1362</v>
+      </c>
+      <c r="C48" t="s">
+        <v>2082</v>
+      </c>
+      <c r="D48" t="s">
+        <v>2083</v>
+      </c>
+      <c r="E48">
+        <v>3</v>
+      </c>
+      <c r="F48" t="s">
+        <v>1468</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>1291</v>
+      </c>
+      <c r="B49" t="s">
+        <v>1362</v>
+      </c>
+      <c r="C49" t="s">
+        <v>2084</v>
+      </c>
+      <c r="D49" t="s">
+        <v>2085</v>
+      </c>
+      <c r="E49">
+        <v>4</v>
+      </c>
+      <c r="F49" t="s">
+        <v>1468</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>1294</v>
+      </c>
+      <c r="B50" t="s">
+        <v>1365</v>
+      </c>
+      <c r="C50" t="s">
+        <v>2103</v>
+      </c>
+      <c r="D50" t="s">
+        <v>2109</v>
+      </c>
+      <c r="E50">
+        <v>1</v>
+      </c>
+      <c r="F50" t="s">
+        <v>1949</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>1294</v>
+      </c>
+      <c r="B51" t="s">
+        <v>1365</v>
+      </c>
+      <c r="C51" t="s">
+        <v>2104</v>
+      </c>
+      <c r="D51" t="s">
+        <v>2110</v>
+      </c>
+      <c r="E51">
+        <v>2</v>
+      </c>
+      <c r="F51" t="s">
+        <v>1468</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>1294</v>
+      </c>
+      <c r="B52" t="s">
+        <v>1365</v>
+      </c>
+      <c r="C52" t="s">
+        <v>2105</v>
+      </c>
+      <c r="D52" t="s">
+        <v>2111</v>
+      </c>
+      <c r="E52">
+        <v>3</v>
+      </c>
+      <c r="F52" t="s">
+        <v>1949</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>1294</v>
+      </c>
+      <c r="B53" t="s">
+        <v>1365</v>
+      </c>
+      <c r="C53" t="s">
+        <v>2106</v>
+      </c>
+      <c r="D53" t="s">
+        <v>2112</v>
+      </c>
+      <c r="E53">
+        <v>4</v>
+      </c>
+      <c r="F53" t="s">
+        <v>1949</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>1294</v>
+      </c>
+      <c r="B54" t="s">
+        <v>1365</v>
+      </c>
+      <c r="C54" t="s">
+        <v>2107</v>
+      </c>
+      <c r="D54" t="s">
+        <v>2113</v>
+      </c>
+      <c r="E54">
+        <v>5</v>
+      </c>
+      <c r="F54" t="s">
+        <v>1949</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>1294</v>
+      </c>
+      <c r="B55" t="s">
+        <v>1365</v>
+      </c>
+      <c r="C55" t="s">
+        <v>2108</v>
+      </c>
+      <c r="D55" t="s">
+        <v>2114</v>
+      </c>
+      <c r="E55">
+        <v>6</v>
+      </c>
+      <c r="F55" t="s">
+        <v>1468</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>1295</v>
+      </c>
+      <c r="B56" t="s">
+        <v>1366</v>
+      </c>
+      <c r="C56" t="s">
+        <v>2117</v>
+      </c>
+      <c r="D56" t="s">
+        <v>2118</v>
+      </c>
+      <c r="E56">
+        <v>1</v>
+      </c>
+      <c r="F56" t="s">
+        <v>1949</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>1295</v>
+      </c>
+      <c r="B57" t="s">
+        <v>1366</v>
+      </c>
+      <c r="C57" t="s">
+        <v>2119</v>
+      </c>
+      <c r="D57" t="s">
+        <v>2120</v>
+      </c>
+      <c r="E57">
+        <v>2</v>
+      </c>
+      <c r="F57" t="s">
+        <v>1468</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>1295</v>
+      </c>
+      <c r="B58" t="s">
+        <v>1366</v>
+      </c>
+      <c r="C58" t="s">
+        <v>2119</v>
+      </c>
+      <c r="D58" t="s">
+        <v>2121</v>
+      </c>
+      <c r="E58">
+        <v>3</v>
+      </c>
+      <c r="F58" t="s">
+        <v>1468</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>1295</v>
+      </c>
+      <c r="B59" t="s">
+        <v>1366</v>
+      </c>
+      <c r="C59" t="s">
+        <v>2119</v>
+      </c>
+      <c r="D59" t="s">
+        <v>2122</v>
+      </c>
+      <c r="E59">
+        <v>4</v>
+      </c>
+      <c r="F59" t="s">
+        <v>1468</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>1295</v>
+      </c>
+      <c r="B60" t="s">
+        <v>1366</v>
+      </c>
+      <c r="C60" t="s">
+        <v>2119</v>
+      </c>
+      <c r="D60" t="s">
+        <v>2123</v>
+      </c>
+      <c r="E60">
+        <v>5</v>
+      </c>
+      <c r="F60" t="s">
+        <v>1468</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>1295</v>
+      </c>
+      <c r="B61" t="s">
+        <v>1366</v>
+      </c>
+      <c r="C61" t="s">
+        <v>2119</v>
+      </c>
+      <c r="D61" t="s">
+        <v>2124</v>
+      </c>
+      <c r="E61">
+        <v>6</v>
+      </c>
+      <c r="F61" t="s">
+        <v>1468</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>1296</v>
+      </c>
+      <c r="B62" t="s">
+        <v>1367</v>
+      </c>
+      <c r="C62" t="s">
+        <v>2127</v>
+      </c>
+      <c r="D62" t="s">
+        <v>2128</v>
+      </c>
+      <c r="E62">
+        <v>1</v>
+      </c>
+      <c r="F62" t="s">
+        <v>1948</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>1298</v>
+      </c>
+      <c r="B63" t="s">
+        <v>1369</v>
+      </c>
+      <c r="C63" t="s">
+        <v>229</v>
+      </c>
+      <c r="D63" t="s">
+        <v>2133</v>
+      </c>
+      <c r="E63">
+        <v>1</v>
+      </c>
+      <c r="F63" t="s">
+        <v>1468</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>1299</v>
+      </c>
+      <c r="B64" t="s">
+        <v>1370</v>
+      </c>
+      <c r="C64" t="s">
+        <v>2136</v>
+      </c>
+      <c r="D64" t="s">
+        <v>2138</v>
+      </c>
+      <c r="E64">
+        <v>1</v>
+      </c>
+      <c r="F64" t="s">
+        <v>1949</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>1299</v>
+      </c>
+      <c r="B65" t="s">
+        <v>1370</v>
+      </c>
+      <c r="C65" t="s">
+        <v>2137</v>
+      </c>
+      <c r="D65" t="s">
+        <v>2139</v>
+      </c>
+      <c r="E65">
+        <v>2</v>
+      </c>
+      <c r="F65" t="s">
+        <v>1949</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>1300</v>
+      </c>
+      <c r="B66" t="s">
+        <v>1371</v>
+      </c>
+      <c r="C66" t="s">
+        <v>2142</v>
+      </c>
+      <c r="D66" t="s">
+        <v>2143</v>
+      </c>
+      <c r="E66">
+        <v>1</v>
+      </c>
+      <c r="F66" t="s">
+        <v>1949</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>1300</v>
+      </c>
+      <c r="B67" t="s">
+        <v>1371</v>
+      </c>
+      <c r="C67" t="s">
+        <v>2144</v>
+      </c>
+      <c r="D67" t="s">
+        <v>2145</v>
+      </c>
+      <c r="E67">
+        <v>2</v>
+      </c>
+      <c r="F67" t="s">
+        <v>1949</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>1303</v>
+      </c>
+      <c r="B68" t="s">
+        <v>1375</v>
+      </c>
+      <c r="C68" t="s">
+        <v>2182</v>
+      </c>
+      <c r="D68" t="s">
+        <v>2183</v>
+      </c>
+      <c r="E68">
+        <v>1</v>
+      </c>
+      <c r="F68" t="s">
+        <v>1948</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>1304</v>
+      </c>
+      <c r="B69" t="s">
+        <v>1376</v>
+      </c>
+      <c r="C69" t="s">
+        <v>2186</v>
+      </c>
+      <c r="D69" t="s">
+        <v>2189</v>
+      </c>
+      <c r="E69">
+        <v>1</v>
+      </c>
+      <c r="F69" t="s">
+        <v>1949</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>1304</v>
+      </c>
+      <c r="B70" t="s">
+        <v>1376</v>
+      </c>
+      <c r="C70" t="s">
+        <v>2187</v>
+      </c>
+      <c r="D70" t="s">
+        <v>2190</v>
+      </c>
+      <c r="E70">
+        <v>2</v>
+      </c>
+      <c r="F70" t="s">
+        <v>1949</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>1304</v>
+      </c>
+      <c r="B71" t="s">
+        <v>1376</v>
+      </c>
+      <c r="C71" t="s">
+        <v>2188</v>
+      </c>
+      <c r="D71" t="s">
+        <v>2191</v>
+      </c>
+      <c r="E71">
+        <v>3</v>
+      </c>
+      <c r="F71" t="s">
+        <v>1949</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>1306</v>
+      </c>
+      <c r="B72" t="s">
+        <v>1378</v>
+      </c>
+      <c r="C72" t="s">
+        <v>2222</v>
+      </c>
+      <c r="D72" t="s">
+        <v>2223</v>
+      </c>
+      <c r="E72">
+        <v>1</v>
+      </c>
+      <c r="F72" t="s">
+        <v>1949</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>1307</v>
+      </c>
+      <c r="B73" t="s">
+        <v>1379</v>
+      </c>
+      <c r="C73" t="s">
+        <v>2232</v>
+      </c>
+      <c r="D73" t="s">
+        <v>2233</v>
+      </c>
+      <c r="E73">
+        <v>1</v>
+      </c>
+      <c r="F73" t="s">
+        <v>1949</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>1307</v>
+      </c>
+      <c r="B74" t="s">
+        <v>1379</v>
+      </c>
+      <c r="C74" t="s">
+        <v>2234</v>
+      </c>
+      <c r="D74" t="s">
+        <v>2235</v>
+      </c>
+      <c r="E74">
+        <v>2</v>
+      </c>
+      <c r="F74" t="s">
+        <v>1949</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>1308</v>
+      </c>
+      <c r="B75" t="s">
+        <v>1380</v>
+      </c>
+      <c r="C75" t="s">
+        <v>2246</v>
+      </c>
+      <c r="D75" t="s">
+        <v>2247</v>
+      </c>
+      <c r="E75">
+        <v>1</v>
+      </c>
+      <c r="F75" t="s">
+        <v>1949</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>1308</v>
+      </c>
+      <c r="B76" t="s">
+        <v>1380</v>
+      </c>
+      <c r="C76" t="s">
+        <v>2248</v>
+      </c>
+      <c r="D76" t="s">
+        <v>2249</v>
+      </c>
+      <c r="E76">
+        <v>2</v>
+      </c>
+      <c r="F76" t="s">
+        <v>1949</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>1308</v>
+      </c>
+      <c r="B77" t="s">
+        <v>1380</v>
+      </c>
+      <c r="C77" t="s">
+        <v>2250</v>
+      </c>
+      <c r="D77" t="s">
+        <v>2251</v>
+      </c>
+      <c r="E77">
+        <v>3</v>
+      </c>
+      <c r="F77" t="s">
+        <v>1468</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>1309</v>
+      </c>
+      <c r="B78" t="s">
+        <v>1381</v>
+      </c>
+      <c r="C78" t="s">
+        <v>2274</v>
+      </c>
+      <c r="D78" t="s">
+        <v>2281</v>
+      </c>
+      <c r="E78">
+        <v>1</v>
+      </c>
+      <c r="F78" t="s">
+        <v>1949</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>1309</v>
+      </c>
+      <c r="B79" t="s">
+        <v>1381</v>
+      </c>
+      <c r="C79" t="s">
+        <v>2275</v>
+      </c>
+      <c r="D79" t="s">
+        <v>2282</v>
+      </c>
+      <c r="E79">
+        <v>2</v>
+      </c>
+      <c r="F79" t="s">
+        <v>1949</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>1309</v>
+      </c>
+      <c r="B80" t="s">
+        <v>1381</v>
+      </c>
+      <c r="C80" t="s">
+        <v>2276</v>
+      </c>
+      <c r="D80" t="s">
+        <v>2283</v>
+      </c>
+      <c r="E80">
+        <v>3</v>
+      </c>
+      <c r="F80" t="s">
+        <v>1949</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>1309</v>
+      </c>
+      <c r="B81" t="s">
+        <v>1381</v>
+      </c>
+      <c r="C81" t="s">
+        <v>2277</v>
+      </c>
+      <c r="D81" t="s">
+        <v>2284</v>
+      </c>
+      <c r="E81">
+        <v>4</v>
+      </c>
+      <c r="F81" t="s">
+        <v>1949</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>1309</v>
+      </c>
+      <c r="B82" t="s">
+        <v>1381</v>
+      </c>
+      <c r="C82" t="s">
+        <v>2278</v>
+      </c>
+      <c r="D82" t="s">
+        <v>2285</v>
+      </c>
+      <c r="E82">
+        <v>5</v>
+      </c>
+      <c r="F82" t="s">
+        <v>1949</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>1309</v>
+      </c>
+      <c r="B83" t="s">
+        <v>1381</v>
+      </c>
+      <c r="C83" t="s">
+        <v>2279</v>
+      </c>
+      <c r="D83" t="s">
+        <v>2286</v>
+      </c>
+      <c r="E83">
+        <v>6</v>
+      </c>
+      <c r="F83" t="s">
+        <v>1949</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>1309</v>
+      </c>
+      <c r="B84" t="s">
+        <v>1381</v>
+      </c>
+      <c r="C84" t="s">
+        <v>2280</v>
+      </c>
+      <c r="D84" t="s">
+        <v>2287</v>
+      </c>
+      <c r="E84">
+        <v>7</v>
+      </c>
+      <c r="F84" t="s">
+        <v>1949</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>1310</v>
+      </c>
+      <c r="B85" t="s">
+        <v>1382</v>
+      </c>
+      <c r="C85" t="s">
+        <v>2302</v>
+      </c>
+      <c r="D85" t="s">
+        <v>2307</v>
+      </c>
+      <c r="E85">
+        <v>1</v>
+      </c>
+      <c r="F85" t="s">
+        <v>1949</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>1310</v>
+      </c>
+      <c r="B86" t="s">
+        <v>1382</v>
+      </c>
+      <c r="C86" t="s">
+        <v>2303</v>
+      </c>
+      <c r="D86" t="s">
+        <v>2308</v>
+      </c>
+      <c r="E86">
+        <v>2</v>
+      </c>
+      <c r="F86" t="s">
+        <v>1949</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>1310</v>
+      </c>
+      <c r="B87" t="s">
+        <v>1382</v>
+      </c>
+      <c r="C87" t="s">
+        <v>2304</v>
+      </c>
+      <c r="D87" t="s">
+        <v>2309</v>
+      </c>
+      <c r="E87">
+        <v>3</v>
+      </c>
+      <c r="F87" t="s">
+        <v>1949</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>1310</v>
+      </c>
+      <c r="B88" t="s">
+        <v>1382</v>
+      </c>
+      <c r="C88" t="s">
+        <v>2305</v>
+      </c>
+      <c r="D88" t="s">
+        <v>2310</v>
+      </c>
+      <c r="E88">
+        <v>4</v>
+      </c>
+      <c r="F88" t="s">
+        <v>1949</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>1310</v>
+      </c>
+      <c r="B89" t="s">
+        <v>1382</v>
+      </c>
+      <c r="C89" t="s">
+        <v>2306</v>
+      </c>
+      <c r="D89" t="s">
+        <v>2311</v>
+      </c>
+      <c r="E89">
+        <v>5</v>
+      </c>
+      <c r="F89" t="s">
+        <v>1468</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>1311</v>
+      </c>
+      <c r="B90" t="s">
+        <v>1383</v>
+      </c>
+      <c r="C90" t="s">
+        <v>2322</v>
+      </c>
+      <c r="D90" t="s">
+        <v>2329</v>
+      </c>
+      <c r="E90">
+        <v>1</v>
+      </c>
+      <c r="F90" t="s">
+        <v>1468</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>1311</v>
+      </c>
+      <c r="B91" t="s">
+        <v>1383</v>
+      </c>
+      <c r="C91" t="s">
+        <v>2323</v>
+      </c>
+      <c r="D91" t="s">
+        <v>2330</v>
+      </c>
+      <c r="E91">
+        <v>2</v>
+      </c>
+      <c r="F91" t="s">
+        <v>1468</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>1311</v>
+      </c>
+      <c r="B92" t="s">
+        <v>1383</v>
+      </c>
+      <c r="C92" t="s">
+        <v>2324</v>
+      </c>
+      <c r="D92" t="s">
+        <v>2331</v>
+      </c>
+      <c r="E92">
+        <v>3</v>
+      </c>
+      <c r="F92" t="s">
+        <v>1468</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>1311</v>
+      </c>
+      <c r="B93" t="s">
+        <v>1383</v>
+      </c>
+      <c r="C93" t="s">
+        <v>2325</v>
+      </c>
+      <c r="D93" t="s">
+        <v>2332</v>
+      </c>
+      <c r="E93">
+        <v>4</v>
+      </c>
+      <c r="F93" t="s">
+        <v>1468</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>1311</v>
+      </c>
+      <c r="B94" t="s">
+        <v>1383</v>
+      </c>
+      <c r="C94" t="s">
+        <v>2326</v>
+      </c>
+      <c r="D94" t="s">
+        <v>2333</v>
+      </c>
+      <c r="E94">
+        <v>5</v>
+      </c>
+      <c r="F94" t="s">
+        <v>1468</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>1311</v>
+      </c>
+      <c r="B95" t="s">
+        <v>1383</v>
+      </c>
+      <c r="C95" t="s">
+        <v>2327</v>
+      </c>
+      <c r="D95" t="s">
+        <v>2334</v>
+      </c>
+      <c r="E95">
+        <v>6</v>
+      </c>
+      <c r="F95" t="s">
+        <v>1468</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>1311</v>
+      </c>
+      <c r="B96" t="s">
+        <v>1383</v>
+      </c>
+      <c r="C96" t="s">
+        <v>2328</v>
+      </c>
+      <c r="D96" t="s">
+        <v>2335</v>
+      </c>
+      <c r="E96">
+        <v>7</v>
+      </c>
+      <c r="F96" t="s">
+        <v>1468</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>1312</v>
+      </c>
+      <c r="B97" t="s">
+        <v>1384</v>
+      </c>
+      <c r="C97" t="s">
+        <v>2338</v>
+      </c>
+      <c r="D97" t="s">
+        <v>2342</v>
+      </c>
+      <c r="E97">
+        <v>1</v>
+      </c>
+      <c r="F97" t="s">
+        <v>1468</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>1312</v>
+      </c>
+      <c r="B98" t="s">
+        <v>1384</v>
+      </c>
+      <c r="C98" t="s">
+        <v>2339</v>
+      </c>
+      <c r="D98" t="s">
+        <v>2343</v>
+      </c>
+      <c r="E98">
+        <v>2</v>
+      </c>
+      <c r="F98" t="s">
+        <v>1468</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>1312</v>
+      </c>
+      <c r="B99" t="s">
+        <v>1384</v>
+      </c>
+      <c r="C99" t="s">
+        <v>2340</v>
+      </c>
+      <c r="D99" t="s">
+        <v>2344</v>
+      </c>
+      <c r="E99">
+        <v>3</v>
+      </c>
+      <c r="F99" t="s">
+        <v>1468</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>1312</v>
+      </c>
+      <c r="B100" t="s">
+        <v>1384</v>
+      </c>
+      <c r="C100" t="s">
+        <v>2341</v>
+      </c>
+      <c r="D100" t="s">
+        <v>2345</v>
+      </c>
+      <c r="E100">
+        <v>4</v>
+      </c>
+      <c r="F100" t="s">
+        <v>1468</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>1313</v>
+      </c>
+      <c r="B101" t="s">
+        <v>510</v>
+      </c>
+      <c r="C101" t="s">
+        <v>2348</v>
+      </c>
+      <c r="D101" t="s">
+        <v>2349</v>
+      </c>
+      <c r="E101">
+        <v>1</v>
+      </c>
+      <c r="F101" t="s">
+        <v>1949</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>1314</v>
+      </c>
+      <c r="B102" t="s">
+        <v>1385</v>
+      </c>
+      <c r="C102" t="s">
+        <v>2352</v>
+      </c>
+      <c r="D102" t="s">
+        <v>2353</v>
+      </c>
+      <c r="E102">
+        <v>1</v>
+      </c>
+      <c r="F102" t="s">
+        <v>1948</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>1314</v>
+      </c>
+      <c r="B103" t="s">
+        <v>1385</v>
+      </c>
+      <c r="C103" t="s">
+        <v>2352</v>
+      </c>
+      <c r="D103" t="s">
+        <v>2354</v>
+      </c>
+      <c r="E103">
+        <v>2</v>
+      </c>
+      <c r="F103" t="s">
+        <v>1948</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>1314</v>
+      </c>
+      <c r="B104" t="s">
+        <v>1385</v>
+      </c>
+      <c r="C104" t="s">
+        <v>2352</v>
+      </c>
+      <c r="D104" t="s">
+        <v>2355</v>
+      </c>
+      <c r="E104">
+        <v>3</v>
+      </c>
+      <c r="F104" t="s">
+        <v>1948</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>1316</v>
+      </c>
+      <c r="B105" t="s">
+        <v>1387</v>
+      </c>
+      <c r="C105" t="s">
+        <v>1387</v>
+      </c>
+      <c r="D105" t="s">
+        <v>2359</v>
+      </c>
+      <c r="E105">
+        <v>1</v>
+      </c>
+      <c r="F105" t="s">
+        <v>1949</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>1316</v>
+      </c>
+      <c r="B106" t="s">
+        <v>1387</v>
+      </c>
+      <c r="C106" t="s">
+        <v>2360</v>
+      </c>
+      <c r="D106" t="s">
+        <v>2361</v>
+      </c>
+      <c r="E106">
+        <v>2</v>
+      </c>
+      <c r="F106" t="s">
+        <v>1948</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>1316</v>
+      </c>
+      <c r="B107" t="s">
+        <v>1387</v>
+      </c>
+      <c r="C107" t="s">
+        <v>288</v>
+      </c>
+      <c r="D107" t="s">
+        <v>2362</v>
+      </c>
+      <c r="E107">
+        <v>3</v>
+      </c>
+      <c r="F107" t="s">
+        <v>1948</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>1316</v>
+      </c>
+      <c r="B108" t="s">
+        <v>1387</v>
+      </c>
+      <c r="C108" t="s">
+        <v>292</v>
+      </c>
+      <c r="D108" t="s">
+        <v>2363</v>
+      </c>
+      <c r="E108">
+        <v>4</v>
+      </c>
+      <c r="F108" t="s">
+        <v>1948</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>1316</v>
+      </c>
+      <c r="B109" t="s">
+        <v>1387</v>
+      </c>
+      <c r="C109" t="s">
+        <v>290</v>
+      </c>
+      <c r="D109" t="s">
+        <v>2364</v>
+      </c>
+      <c r="E109">
+        <v>5</v>
+      </c>
+      <c r="F109" t="s">
+        <v>1948</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>1316</v>
+      </c>
+      <c r="B110" t="s">
+        <v>1387</v>
+      </c>
+      <c r="C110" t="s">
+        <v>294</v>
+      </c>
+      <c r="D110" t="s">
+        <v>2365</v>
+      </c>
+      <c r="E110">
+        <v>6</v>
+      </c>
+      <c r="F110" t="s">
+        <v>1948</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>1316</v>
+      </c>
+      <c r="B111" t="s">
+        <v>1387</v>
+      </c>
+      <c r="C111" t="s">
+        <v>293</v>
+      </c>
+      <c r="D111" t="s">
+        <v>2366</v>
+      </c>
+      <c r="E111">
+        <v>7</v>
+      </c>
+      <c r="F111" t="s">
+        <v>1948</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>1316</v>
+      </c>
+      <c r="B112" t="s">
+        <v>1387</v>
+      </c>
+      <c r="C112" t="s">
+        <v>291</v>
+      </c>
+      <c r="D112" t="s">
+        <v>2367</v>
+      </c>
+      <c r="E112">
+        <v>8</v>
+      </c>
+      <c r="F112" t="s">
+        <v>1948</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>1317</v>
+      </c>
+      <c r="B113" t="s">
+        <v>1388</v>
+      </c>
+      <c r="C113" t="s">
+        <v>2370</v>
+      </c>
+      <c r="D113" t="s">
+        <v>2373</v>
+      </c>
+      <c r="E113">
+        <v>1</v>
+      </c>
+      <c r="F113" t="s">
+        <v>1949</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>1317</v>
+      </c>
+      <c r="B114" t="s">
+        <v>1388</v>
+      </c>
+      <c r="C114" t="s">
+        <v>2371</v>
+      </c>
+      <c r="D114" t="s">
+        <v>2374</v>
+      </c>
+      <c r="E114">
+        <v>2</v>
+      </c>
+      <c r="F114" t="s">
+        <v>1468</v>
+      </c>
+    </row>
+    <row r="115" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>1317</v>
+      </c>
+      <c r="B115" t="s">
+        <v>1388</v>
+      </c>
+      <c r="C115" t="s">
+        <v>2372</v>
+      </c>
+      <c r="D115" t="s">
+        <v>2375</v>
+      </c>
+      <c r="E115">
+        <v>3</v>
+      </c>
+      <c r="F115" t="s">
+        <v>1468</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>1318</v>
+      </c>
+      <c r="B116" t="s">
+        <v>1389</v>
+      </c>
+      <c r="C116" t="s">
+        <v>2378</v>
+      </c>
+      <c r="D116" t="s">
+        <v>2380</v>
+      </c>
+      <c r="E116">
+        <v>1</v>
+      </c>
+      <c r="F116" t="s">
+        <v>1949</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>1318</v>
+      </c>
+      <c r="B117" t="s">
+        <v>1389</v>
+      </c>
+      <c r="C117" t="s">
+        <v>2379</v>
+      </c>
+      <c r="D117" t="s">
+        <v>2381</v>
+      </c>
+      <c r="E117">
+        <v>2</v>
+      </c>
+      <c r="F117" t="s">
+        <v>1949</v>
+      </c>
+    </row>
+    <row r="118" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>1319</v>
+      </c>
+      <c r="B118" t="s">
+        <v>1020</v>
+      </c>
+      <c r="C118" t="s">
+        <v>1081</v>
+      </c>
+      <c r="D118" t="s">
+        <v>2385</v>
+      </c>
+      <c r="E118">
+        <v>1</v>
+      </c>
+      <c r="F118" t="s">
+        <v>1949</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>1319</v>
+      </c>
+      <c r="B119" t="s">
+        <v>1020</v>
+      </c>
+      <c r="C119" t="s">
+        <v>2384</v>
+      </c>
+      <c r="D119" t="s">
+        <v>2386</v>
+      </c>
+      <c r="E119">
+        <v>2</v>
+      </c>
+      <c r="F119" t="s">
+        <v>1949</v>
+      </c>
+    </row>
+    <row r="120" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>1320</v>
+      </c>
+      <c r="B120" t="s">
+        <v>1390</v>
+      </c>
+      <c r="C120" t="s">
+        <v>2389</v>
+      </c>
+      <c r="D120" t="s">
+        <v>2390</v>
+      </c>
+      <c r="E120">
+        <v>1</v>
+      </c>
+      <c r="F120" t="s">
+        <v>1468</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>1320</v>
+      </c>
+      <c r="B121" t="s">
+        <v>1390</v>
+      </c>
+      <c r="C121" t="s">
+        <v>2391</v>
+      </c>
+      <c r="D121" t="s">
+        <v>2392</v>
+      </c>
+      <c r="E121">
+        <v>2</v>
+      </c>
+      <c r="F121" t="s">
+        <v>1468</v>
+      </c>
+    </row>
+    <row r="122" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>1321</v>
+      </c>
+      <c r="B122" t="s">
+        <v>1391</v>
+      </c>
+      <c r="C122" t="s">
+        <v>2395</v>
+      </c>
+      <c r="D122" t="s">
+        <v>2396</v>
+      </c>
+      <c r="E122">
+        <v>1</v>
+      </c>
+      <c r="F122" t="s">
+        <v>1949</v>
+      </c>
+    </row>
+    <row r="123" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>1321</v>
+      </c>
+      <c r="B123" t="s">
+        <v>1391</v>
+      </c>
+      <c r="C123" t="s">
+        <v>2397</v>
+      </c>
+      <c r="D123" t="s">
+        <v>2398</v>
+      </c>
+      <c r="E123">
+        <v>2</v>
+      </c>
+      <c r="F123" t="s">
+        <v>1468</v>
+      </c>
+    </row>
+    <row r="124" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>1322</v>
+      </c>
+      <c r="B124" t="s">
+        <v>1392</v>
+      </c>
+      <c r="C124" t="s">
+        <v>2401</v>
+      </c>
+      <c r="D124" t="s">
+        <v>2402</v>
+      </c>
+      <c r="E124">
+        <v>1</v>
+      </c>
+      <c r="F124" t="s">
+        <v>1949</v>
+      </c>
+    </row>
+    <row r="125" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>1322</v>
+      </c>
+      <c r="B125" t="s">
+        <v>1392</v>
+      </c>
+      <c r="C125" t="s">
+        <v>2403</v>
+      </c>
+      <c r="D125" t="s">
+        <v>2404</v>
+      </c>
+      <c r="E125">
+        <v>2</v>
+      </c>
+      <c r="F125" t="s">
+        <v>1949</v>
+      </c>
+    </row>
+    <row r="126" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>1323</v>
+      </c>
+      <c r="B126" t="s">
+        <v>1393</v>
+      </c>
+      <c r="C126" t="s">
+        <v>2407</v>
+      </c>
+      <c r="D126" t="s">
+        <v>2422</v>
+      </c>
+      <c r="E126">
+        <v>1</v>
+      </c>
+      <c r="F126" t="s">
+        <v>1468</v>
+      </c>
+    </row>
+    <row r="127" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>1323</v>
+      </c>
+      <c r="B127" t="s">
+        <v>1393</v>
+      </c>
+      <c r="C127" t="s">
+        <v>2408</v>
+      </c>
+      <c r="D127" t="s">
+        <v>2423</v>
+      </c>
+      <c r="E127">
+        <v>2</v>
+      </c>
+      <c r="F127" t="s">
+        <v>1468</v>
+      </c>
+    </row>
+    <row r="128" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>1323</v>
+      </c>
+      <c r="B128" t="s">
+        <v>1393</v>
+      </c>
+      <c r="C128" t="s">
+        <v>2409</v>
+      </c>
+      <c r="D128" t="s">
+        <v>2424</v>
+      </c>
+      <c r="E128">
+        <v>3</v>
+      </c>
+      <c r="F128" t="s">
+        <v>1468</v>
+      </c>
+    </row>
+    <row r="129" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>1323</v>
+      </c>
+      <c r="B129" t="s">
+        <v>1393</v>
+      </c>
+      <c r="C129" t="s">
+        <v>2410</v>
+      </c>
+      <c r="D129" t="s">
+        <v>2425</v>
+      </c>
+      <c r="E129">
+        <v>4</v>
+      </c>
+      <c r="F129" t="s">
+        <v>1468</v>
+      </c>
+    </row>
+    <row r="130" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>1323</v>
+      </c>
+      <c r="B130" t="s">
+        <v>1393</v>
+      </c>
+      <c r="C130" t="s">
+        <v>2411</v>
+      </c>
+      <c r="D130" t="s">
+        <v>2426</v>
+      </c>
+      <c r="E130">
+        <v>5</v>
+      </c>
+      <c r="F130" t="s">
+        <v>1468</v>
+      </c>
+    </row>
+    <row r="131" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
+        <v>1323</v>
+      </c>
+      <c r="B131" t="s">
+        <v>1393</v>
+      </c>
+      <c r="C131" t="s">
+        <v>2412</v>
+      </c>
+      <c r="D131" t="s">
+        <v>2427</v>
+      </c>
+      <c r="E131">
+        <v>6</v>
+      </c>
+      <c r="F131" t="s">
+        <v>1468</v>
+      </c>
+    </row>
+    <row r="132" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>1323</v>
+      </c>
+      <c r="B132" t="s">
+        <v>1393</v>
+      </c>
+      <c r="C132" t="s">
+        <v>2413</v>
+      </c>
+      <c r="D132" t="s">
+        <v>2428</v>
+      </c>
+      <c r="E132">
+        <v>7</v>
+      </c>
+      <c r="F132" t="s">
+        <v>1468</v>
+      </c>
+    </row>
+    <row r="133" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
+        <v>1323</v>
+      </c>
+      <c r="B133" t="s">
+        <v>1393</v>
+      </c>
+      <c r="C133" t="s">
+        <v>2414</v>
+      </c>
+      <c r="D133" t="s">
+        <v>2429</v>
+      </c>
+      <c r="E133">
+        <v>8</v>
+      </c>
+      <c r="F133" t="s">
+        <v>1468</v>
+      </c>
+    </row>
+    <row r="134" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
+        <v>1323</v>
+      </c>
+      <c r="B134" t="s">
+        <v>1393</v>
+      </c>
+      <c r="C134" t="s">
+        <v>2415</v>
+      </c>
+      <c r="D134" t="s">
+        <v>2430</v>
+      </c>
+      <c r="E134">
+        <v>9</v>
+      </c>
+      <c r="F134" t="s">
+        <v>1468</v>
+      </c>
+    </row>
+    <row r="135" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
+        <v>1323</v>
+      </c>
+      <c r="B135" t="s">
+        <v>1393</v>
+      </c>
+      <c r="C135" t="s">
+        <v>2416</v>
+      </c>
+      <c r="D135" t="s">
+        <v>2431</v>
+      </c>
+      <c r="E135">
+        <v>10</v>
+      </c>
+      <c r="F135" t="s">
+        <v>1468</v>
+      </c>
+    </row>
+    <row r="136" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
+        <v>1323</v>
+      </c>
+      <c r="B136" t="s">
+        <v>1393</v>
+      </c>
+      <c r="C136" t="s">
+        <v>2417</v>
+      </c>
+      <c r="D136" t="s">
+        <v>2432</v>
+      </c>
+      <c r="E136">
+        <v>11</v>
+      </c>
+      <c r="F136" t="s">
+        <v>1468</v>
+      </c>
+    </row>
+    <row r="137" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
+        <v>1323</v>
+      </c>
+      <c r="B137" t="s">
+        <v>1393</v>
+      </c>
+      <c r="C137" t="s">
+        <v>2418</v>
+      </c>
+      <c r="D137" t="s">
+        <v>2433</v>
+      </c>
+      <c r="E137">
+        <v>12</v>
+      </c>
+      <c r="F137" t="s">
+        <v>1468</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
+        <v>1323</v>
+      </c>
+      <c r="B138" t="s">
+        <v>1393</v>
+      </c>
+      <c r="C138" t="s">
+        <v>2419</v>
+      </c>
+      <c r="D138" t="s">
+        <v>2434</v>
+      </c>
+      <c r="E138">
+        <v>13</v>
+      </c>
+      <c r="F138" t="s">
+        <v>1468</v>
+      </c>
+    </row>
+    <row r="139" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A139" t="s">
+        <v>1323</v>
+      </c>
+      <c r="B139" t="s">
+        <v>1393</v>
+      </c>
+      <c r="C139" t="s">
+        <v>2420</v>
+      </c>
+      <c r="D139" t="s">
+        <v>2435</v>
+      </c>
+      <c r="E139">
+        <v>14</v>
+      </c>
+      <c r="F139" t="s">
+        <v>1468</v>
+      </c>
+    </row>
+    <row r="140" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A140" t="s">
+        <v>1323</v>
+      </c>
+      <c r="B140" t="s">
+        <v>1393</v>
+      </c>
+      <c r="C140" t="s">
+        <v>2421</v>
+      </c>
+      <c r="D140" t="s">
+        <v>2436</v>
+      </c>
+      <c r="E140">
+        <v>15</v>
+      </c>
+      <c r="F140" t="s">
+        <v>1468</v>
+      </c>
+    </row>
+    <row r="141" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A141" t="s">
+        <v>1324</v>
+      </c>
+      <c r="B141" t="s">
+        <v>1394</v>
+      </c>
+      <c r="C141" t="s">
+        <v>2441</v>
+      </c>
+      <c r="D141" t="s">
+        <v>2445</v>
+      </c>
+      <c r="E141">
+        <v>1</v>
+      </c>
+      <c r="F141" t="s">
+        <v>1949</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A142" t="s">
+        <v>1324</v>
+      </c>
+      <c r="B142" t="s">
+        <v>1394</v>
+      </c>
+      <c r="C142" t="s">
+        <v>2442</v>
+      </c>
+      <c r="D142" t="s">
+        <v>2446</v>
+      </c>
+      <c r="E142">
+        <v>2</v>
+      </c>
+      <c r="F142" t="s">
+        <v>1949</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A143" t="s">
+        <v>1324</v>
+      </c>
+      <c r="B143" t="s">
+        <v>1394</v>
+      </c>
+      <c r="C143" t="s">
+        <v>1395</v>
+      </c>
+      <c r="D143" t="s">
+        <v>1441</v>
+      </c>
+      <c r="E143">
+        <v>3</v>
+      </c>
+      <c r="F143" t="s">
+        <v>1949</v>
+      </c>
+    </row>
+    <row r="144" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A144" t="s">
+        <v>1324</v>
+      </c>
+      <c r="B144" t="s">
+        <v>1394</v>
+      </c>
+      <c r="C144" t="s">
+        <v>2443</v>
+      </c>
+      <c r="D144" t="s">
+        <v>2447</v>
+      </c>
+      <c r="E144">
+        <v>4</v>
+      </c>
+      <c r="F144" t="s">
+        <v>1949</v>
+      </c>
+    </row>
+    <row r="145" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A145" t="s">
+        <v>1324</v>
+      </c>
+      <c r="B145" t="s">
+        <v>1394</v>
+      </c>
+      <c r="C145" t="s">
+        <v>2444</v>
+      </c>
+      <c r="D145" t="s">
+        <v>2448</v>
+      </c>
+      <c r="E145">
+        <v>5</v>
+      </c>
+      <c r="F145" t="s">
+        <v>1468</v>
+      </c>
+    </row>
+    <row r="146" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A146" t="s">
+        <v>1325</v>
+      </c>
+      <c r="B146" t="s">
+        <v>1395</v>
+      </c>
+      <c r="C146" t="s">
+        <v>2451</v>
+      </c>
+      <c r="D146" t="s">
+        <v>2454</v>
+      </c>
+      <c r="E146">
+        <v>1</v>
+      </c>
+      <c r="F146" t="s">
+        <v>1468</v>
+      </c>
+    </row>
+    <row r="147" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A147" t="s">
+        <v>1325</v>
+      </c>
+      <c r="B147" t="s">
+        <v>1395</v>
+      </c>
+      <c r="C147" t="s">
+        <v>2452</v>
+      </c>
+      <c r="D147" t="s">
+        <v>2455</v>
+      </c>
+      <c r="E147">
+        <v>2</v>
+      </c>
+      <c r="F147" t="s">
+        <v>1949</v>
+      </c>
+    </row>
+    <row r="148" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A148" t="s">
+        <v>1325</v>
+      </c>
+      <c r="B148" t="s">
+        <v>1395</v>
+      </c>
+      <c r="C148" t="s">
+        <v>2453</v>
+      </c>
+      <c r="D148" t="s">
+        <v>2456</v>
+      </c>
+      <c r="E148">
+        <v>3</v>
+      </c>
+      <c r="F148" t="s">
+        <v>1949</v>
+      </c>
+    </row>
+    <row r="149" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A149" t="s">
+        <v>1326</v>
+      </c>
+      <c r="B149" t="s">
+        <v>1396</v>
+      </c>
+      <c r="C149" t="s">
+        <v>2459</v>
+      </c>
+      <c r="D149" t="s">
+        <v>2465</v>
+      </c>
+      <c r="E149">
+        <v>1</v>
+      </c>
+      <c r="F149" t="s">
+        <v>1949</v>
+      </c>
+    </row>
+    <row r="150" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A150" t="s">
+        <v>1326</v>
+      </c>
+      <c r="B150" t="s">
+        <v>1396</v>
+      </c>
+      <c r="C150" t="s">
+        <v>2460</v>
+      </c>
+      <c r="D150" t="s">
+        <v>2466</v>
+      </c>
+      <c r="E150">
+        <v>2</v>
+      </c>
+      <c r="F150" t="s">
+        <v>1949</v>
+      </c>
+    </row>
+    <row r="151" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A151" t="s">
+        <v>1326</v>
+      </c>
+      <c r="B151" t="s">
+        <v>1396</v>
+      </c>
+      <c r="C151" t="s">
+        <v>2461</v>
+      </c>
+      <c r="D151" t="s">
+        <v>2467</v>
+      </c>
+      <c r="E151">
+        <v>3</v>
+      </c>
+      <c r="F151" t="s">
+        <v>1949</v>
+      </c>
+    </row>
+    <row r="152" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A152" t="s">
+        <v>1326</v>
+      </c>
+      <c r="B152" t="s">
+        <v>1396</v>
+      </c>
+      <c r="C152" t="s">
+        <v>2462</v>
+      </c>
+      <c r="D152" t="s">
+        <v>2468</v>
+      </c>
+      <c r="E152">
+        <v>4</v>
+      </c>
+      <c r="F152" t="s">
+        <v>1949</v>
+      </c>
+    </row>
+    <row r="153" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A153" t="s">
+        <v>1326</v>
+      </c>
+      <c r="B153" t="s">
+        <v>1396</v>
+      </c>
+      <c r="C153" t="s">
+        <v>2463</v>
+      </c>
+      <c r="D153" t="s">
+        <v>2469</v>
+      </c>
+      <c r="E153">
+        <v>5</v>
+      </c>
+      <c r="F153" t="s">
+        <v>1949</v>
+      </c>
+    </row>
+    <row r="154" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A154" t="s">
+        <v>1326</v>
+      </c>
+      <c r="B154" t="s">
+        <v>1396</v>
+      </c>
+      <c r="C154" t="s">
+        <v>2464</v>
+      </c>
+      <c r="D154" t="s">
+        <v>2470</v>
+      </c>
+      <c r="E154">
+        <v>6</v>
+      </c>
+      <c r="F154" t="s">
+        <v>1949</v>
+      </c>
+    </row>
+    <row r="155" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A155" t="s">
+        <v>1327</v>
+      </c>
+      <c r="B155" t="s">
+        <v>1397</v>
+      </c>
+      <c r="C155" t="s">
+        <v>2475</v>
+      </c>
+      <c r="D155" t="s">
+        <v>2477</v>
+      </c>
+      <c r="E155">
+        <v>1</v>
+      </c>
+      <c r="F155" t="s">
+        <v>1468</v>
+      </c>
+    </row>
+    <row r="156" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A156" t="s">
+        <v>1327</v>
+      </c>
+      <c r="B156" t="s">
+        <v>1397</v>
+      </c>
+      <c r="C156" t="s">
+        <v>2476</v>
+      </c>
+      <c r="D156" t="s">
+        <v>2478</v>
+      </c>
+      <c r="E156">
+        <v>2</v>
+      </c>
+      <c r="F156" t="s">
+        <v>1468</v>
+      </c>
+    </row>
+    <row r="157" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A157" t="s">
+        <v>1328</v>
+      </c>
+      <c r="B157" t="s">
+        <v>1398</v>
+      </c>
+      <c r="C157" t="s">
+        <v>2481</v>
+      </c>
+      <c r="D157" t="s">
+        <v>2489</v>
+      </c>
+      <c r="E157">
+        <v>1</v>
+      </c>
+      <c r="F157" t="s">
+        <v>1949</v>
+      </c>
+    </row>
+    <row r="158" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A158" t="s">
+        <v>1328</v>
+      </c>
+      <c r="B158" t="s">
+        <v>1398</v>
+      </c>
+      <c r="C158" t="s">
+        <v>2482</v>
+      </c>
+      <c r="D158" t="s">
+        <v>2490</v>
+      </c>
+      <c r="E158">
+        <v>2</v>
+      </c>
+      <c r="F158" t="s">
+        <v>1949</v>
+      </c>
+    </row>
+    <row r="159" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A159" t="s">
+        <v>1328</v>
+      </c>
+      <c r="B159" t="s">
+        <v>1398</v>
+      </c>
+      <c r="C159" t="s">
+        <v>2483</v>
+      </c>
+      <c r="D159" t="s">
+        <v>2491</v>
+      </c>
+      <c r="E159">
+        <v>3</v>
+      </c>
+      <c r="F159" t="s">
+        <v>1949</v>
+      </c>
+    </row>
+    <row r="160" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A160" t="s">
+        <v>1328</v>
+      </c>
+      <c r="B160" t="s">
+        <v>1398</v>
+      </c>
+      <c r="C160" t="s">
+        <v>2484</v>
+      </c>
+      <c r="D160" t="s">
+        <v>2492</v>
+      </c>
+      <c r="E160">
+        <v>4</v>
+      </c>
+      <c r="F160" t="s">
+        <v>1949</v>
+      </c>
+    </row>
+    <row r="161" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A161" t="s">
+        <v>1328</v>
+      </c>
+      <c r="B161" t="s">
+        <v>1398</v>
+      </c>
+      <c r="C161" t="s">
+        <v>2485</v>
+      </c>
+      <c r="D161" t="s">
+        <v>2493</v>
+      </c>
+      <c r="E161">
+        <v>5</v>
+      </c>
+      <c r="F161" t="s">
+        <v>1949</v>
+      </c>
+    </row>
+    <row r="162" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A162" t="s">
+        <v>1328</v>
+      </c>
+      <c r="B162" t="s">
+        <v>1398</v>
+      </c>
+      <c r="C162" t="s">
+        <v>2486</v>
+      </c>
+      <c r="D162" t="s">
+        <v>2494</v>
+      </c>
+      <c r="E162">
+        <v>6</v>
+      </c>
+      <c r="F162" t="s">
+        <v>1949</v>
+      </c>
+    </row>
+    <row r="163" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A163" t="s">
+        <v>1328</v>
+      </c>
+      <c r="B163" t="s">
+        <v>1398</v>
+      </c>
+      <c r="C163" t="s">
+        <v>2487</v>
+      </c>
+      <c r="D163" t="s">
+        <v>2495</v>
+      </c>
+      <c r="E163">
+        <v>7</v>
+      </c>
+      <c r="F163" t="s">
+        <v>1949</v>
+      </c>
+    </row>
+    <row r="164" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A164" t="s">
+        <v>1328</v>
+      </c>
+      <c r="B164" t="s">
+        <v>1398</v>
+      </c>
+      <c r="C164" t="s">
+        <v>2488</v>
+      </c>
+      <c r="D164" t="s">
+        <v>2496</v>
+      </c>
+      <c r="E164">
+        <v>8</v>
+      </c>
+      <c r="F164" t="s">
+        <v>1468</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F134C8BE-E9AE-4B7A-9200-034BBD6B89FF}">
+  <dimension ref="A1:D67"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="15.5703125" customWidth="1"/>
+    <col min="2" max="2" width="25.85546875" customWidth="1"/>
+    <col min="3" max="3" width="29" customWidth="1"/>
+    <col min="4" max="4" width="20.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>1263</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1330</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>1264</v>
+      </c>
+      <c r="B2" t="s">
+        <v>510</v>
+      </c>
+      <c r="C2" t="s">
+        <v>1942</v>
+      </c>
+      <c r="D2" t="s">
+        <v>1943</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>1265</v>
+      </c>
+      <c r="B3" t="s">
+        <v>1332</v>
+      </c>
+      <c r="C3" t="s">
+        <v>1950</v>
+      </c>
+      <c r="D3" t="s">
+        <v>1951</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>1266</v>
+      </c>
+      <c r="B4" t="s">
+        <v>1338</v>
+      </c>
+      <c r="C4" t="s">
+        <v>1956</v>
+      </c>
+      <c r="D4" t="s">
+        <v>1957</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>1267</v>
+      </c>
+      <c r="B5" t="s">
+        <v>1339</v>
+      </c>
+      <c r="C5" t="s">
+        <v>1962</v>
+      </c>
+      <c r="D5" t="s">
+        <v>1963</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>1268</v>
+      </c>
+      <c r="B6" t="s">
+        <v>1340</v>
+      </c>
+      <c r="C6" t="s">
+        <v>1966</v>
+      </c>
+      <c r="D6" t="s">
+        <v>1967</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>1269</v>
+      </c>
+      <c r="B7" t="s">
+        <v>1341</v>
+      </c>
+      <c r="C7" t="s">
+        <v>1970</v>
+      </c>
+      <c r="D7" t="s">
+        <v>1971</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>1270</v>
+      </c>
+      <c r="B8" t="s">
+        <v>1342</v>
+      </c>
+      <c r="C8" t="s">
+        <v>1976</v>
+      </c>
+      <c r="D8" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>1271</v>
+      </c>
+      <c r="B9" t="s">
+        <v>1343</v>
+      </c>
+      <c r="C9" t="s">
+        <v>1982</v>
+      </c>
+      <c r="D9" t="s">
+        <v>1983</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>1272</v>
+      </c>
+      <c r="B10" t="s">
+        <v>1344</v>
+      </c>
+      <c r="C10" t="s">
+        <v>1984</v>
+      </c>
+      <c r="D10" t="s">
+        <v>1985</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>1273</v>
+      </c>
+      <c r="B11" t="s">
+        <v>1345</v>
+      </c>
+      <c r="C11" t="s">
+        <v>1986</v>
+      </c>
+      <c r="D11" t="s">
+        <v>1987</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>1274</v>
+      </c>
+      <c r="B12" t="s">
+        <v>1346</v>
+      </c>
+      <c r="C12" t="s">
+        <v>2002</v>
+      </c>
+      <c r="D12" t="s">
+        <v>2003</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>1275</v>
+      </c>
+      <c r="B13" t="s">
+        <v>5</v>
+      </c>
+      <c r="C13" t="s">
+        <v>2004</v>
+      </c>
+      <c r="D13" t="s">
+        <v>2005</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>1276</v>
+      </c>
+      <c r="B14" t="s">
+        <v>1347</v>
+      </c>
+      <c r="C14" t="s">
+        <v>2008</v>
+      </c>
+      <c r="D14" t="s">
+        <v>2009</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>1277</v>
+      </c>
+      <c r="B15" t="s">
+        <v>1348</v>
+      </c>
+      <c r="C15" t="s">
+        <v>2010</v>
+      </c>
+      <c r="D15" t="s">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>1278</v>
+      </c>
+      <c r="B16" t="s">
+        <v>1349</v>
+      </c>
+      <c r="C16" t="s">
+        <v>2022</v>
+      </c>
+      <c r="D16" t="s">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>1279</v>
+      </c>
+      <c r="B17" t="s">
+        <v>1350</v>
+      </c>
+      <c r="C17" t="s">
+        <v>2028</v>
+      </c>
+      <c r="D17" t="s">
+        <v>2029</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>1280</v>
+      </c>
+      <c r="B18" t="s">
+        <v>1351</v>
+      </c>
+      <c r="C18" t="s">
+        <v>2030</v>
+      </c>
+      <c r="D18" t="s">
+        <v>2031</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>1281</v>
+      </c>
+      <c r="B19" t="s">
+        <v>1352</v>
+      </c>
+      <c r="C19" t="s">
+        <v>2036</v>
+      </c>
+      <c r="D19" t="s">
+        <v>2037</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>1282</v>
+      </c>
+      <c r="B20" t="s">
+        <v>1353</v>
+      </c>
+      <c r="C20" t="s">
+        <v>2040</v>
+      </c>
+      <c r="D20" t="s">
+        <v>2041</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>1283</v>
+      </c>
+      <c r="B21" t="s">
+        <v>1354</v>
+      </c>
+      <c r="C21" t="s">
+        <v>2046</v>
+      </c>
+      <c r="D21" t="s">
+        <v>2047</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>1284</v>
+      </c>
+      <c r="B22" t="s">
+        <v>1355</v>
+      </c>
+      <c r="C22" t="s">
+        <v>2056</v>
+      </c>
+      <c r="D22" t="s">
+        <v>2057</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>1285</v>
+      </c>
+      <c r="B23" t="s">
+        <v>1356</v>
+      </c>
+      <c r="C23" t="s">
+        <v>2062</v>
+      </c>
+      <c r="D23" t="s">
+        <v>2063</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>1286</v>
+      </c>
+      <c r="B24" t="s">
+        <v>1357</v>
+      </c>
+      <c r="C24" t="s">
+        <v>2066</v>
+      </c>
+      <c r="D24" t="s">
+        <v>2067</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>1287</v>
+      </c>
+      <c r="B25" t="s">
+        <v>1358</v>
+      </c>
+      <c r="C25" t="s">
+        <v>2068</v>
+      </c>
+      <c r="D25" t="s">
+        <v>2069</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>1288</v>
+      </c>
+      <c r="B26" t="s">
+        <v>1359</v>
+      </c>
+      <c r="C26" t="s">
+        <v>2072</v>
+      </c>
+      <c r="D26" t="s">
+        <v>2073</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>1289</v>
+      </c>
+      <c r="B27" t="s">
+        <v>1360</v>
+      </c>
+      <c r="C27" t="s">
+        <v>2074</v>
+      </c>
+      <c r="D27" t="s">
+        <v>2075</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>1290</v>
+      </c>
+      <c r="B28" t="s">
+        <v>1361</v>
+      </c>
+      <c r="C28" t="s">
+        <v>2076</v>
+      </c>
+      <c r="D28" t="s">
+        <v>2077</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>1291</v>
+      </c>
+      <c r="B29" t="s">
+        <v>1362</v>
+      </c>
+      <c r="C29" t="s">
+        <v>2098</v>
+      </c>
+      <c r="D29" t="s">
+        <v>2099</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>1292</v>
+      </c>
+      <c r="B30" t="s">
+        <v>1363</v>
+      </c>
+      <c r="C30" t="s">
+        <v>2100</v>
+      </c>
+      <c r="D30" t="s">
+        <v>2101</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>1293</v>
+      </c>
+      <c r="B31" t="s">
+        <v>1364</v>
+      </c>
+      <c r="C31" t="s">
+        <v>2102</v>
+      </c>
+      <c r="D31" t="s">
+        <v>2506</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>1294</v>
+      </c>
+      <c r="B32" t="s">
+        <v>1365</v>
+      </c>
+      <c r="C32" t="s">
+        <v>2115</v>
+      </c>
+      <c r="D32" t="s">
+        <v>2116</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>1295</v>
+      </c>
+      <c r="B33" t="s">
+        <v>1366</v>
+      </c>
+      <c r="C33" t="s">
+        <v>2125</v>
+      </c>
+      <c r="D33" t="s">
+        <v>2126</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>1296</v>
+      </c>
+      <c r="B34" t="s">
+        <v>1367</v>
+      </c>
+      <c r="C34" t="s">
+        <v>2129</v>
+      </c>
+      <c r="D34" t="s">
+        <v>2130</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>1297</v>
+      </c>
+      <c r="B35" t="s">
+        <v>1368</v>
+      </c>
+      <c r="C35" t="s">
+        <v>2131</v>
+      </c>
+      <c r="D35" t="s">
+        <v>2132</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>1298</v>
+      </c>
+      <c r="B36" t="s">
+        <v>1369</v>
+      </c>
+      <c r="C36" t="s">
+        <v>2134</v>
+      </c>
+      <c r="D36" t="s">
+        <v>2135</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>1299</v>
+      </c>
+      <c r="B37" t="s">
+        <v>1370</v>
+      </c>
+      <c r="C37" t="s">
+        <v>2140</v>
+      </c>
+      <c r="D37" t="s">
+        <v>2141</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>1300</v>
+      </c>
+      <c r="B38" t="s">
+        <v>1371</v>
+      </c>
+      <c r="C38" t="s">
+        <v>2146</v>
+      </c>
+      <c r="D38" t="s">
+        <v>2147</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>1301</v>
+      </c>
+      <c r="B39" t="s">
+        <v>1372</v>
+      </c>
+      <c r="C39" t="s">
+        <v>2148</v>
+      </c>
+      <c r="D39" t="s">
+        <v>2149</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>1302</v>
+      </c>
+      <c r="B40" t="s">
+        <v>1374</v>
+      </c>
+      <c r="C40" t="s">
+        <v>2180</v>
+      </c>
+      <c r="D40" t="s">
+        <v>2181</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>1303</v>
+      </c>
+      <c r="B41" t="s">
+        <v>1375</v>
+      </c>
+      <c r="C41" t="s">
+        <v>2184</v>
+      </c>
+      <c r="D41" t="s">
+        <v>2185</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>1304</v>
+      </c>
+      <c r="B42" t="s">
+        <v>1376</v>
+      </c>
+      <c r="C42" t="s">
+        <v>2192</v>
+      </c>
+      <c r="D42" t="s">
+        <v>2193</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>1305</v>
+      </c>
+      <c r="B43" t="s">
+        <v>1377</v>
+      </c>
+      <c r="C43" t="s">
+        <v>2220</v>
+      </c>
+      <c r="D43" t="s">
+        <v>2221</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>1306</v>
+      </c>
+      <c r="B44" t="s">
+        <v>1378</v>
+      </c>
+      <c r="C44" t="s">
+        <v>2224</v>
+      </c>
+      <c r="D44" t="s">
+        <v>2225</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>1307</v>
+      </c>
+      <c r="B45" t="s">
+        <v>1379</v>
+      </c>
+      <c r="C45" t="s">
+        <v>2236</v>
+      </c>
+      <c r="D45" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>1308</v>
+      </c>
+      <c r="B46" t="s">
+        <v>1380</v>
+      </c>
+      <c r="C46" t="s">
+        <v>2252</v>
+      </c>
+      <c r="D46" t="s">
+        <v>2253</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>1309</v>
+      </c>
+      <c r="B47" t="s">
+        <v>1381</v>
+      </c>
+      <c r="C47" t="s">
+        <v>2272</v>
+      </c>
+      <c r="D47" t="s">
+        <v>2273</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>1310</v>
+      </c>
+      <c r="B48" t="s">
+        <v>1382</v>
+      </c>
+      <c r="C48" t="s">
+        <v>2312</v>
+      </c>
+      <c r="D48" t="s">
+        <v>2313</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>1311</v>
+      </c>
+      <c r="B49" t="s">
+        <v>1383</v>
+      </c>
+      <c r="C49" t="s">
+        <v>2336</v>
+      </c>
+      <c r="D49" t="s">
+        <v>2337</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>1312</v>
+      </c>
+      <c r="B50" t="s">
+        <v>1384</v>
+      </c>
+      <c r="C50" t="s">
+        <v>2346</v>
+      </c>
+      <c r="D50" t="s">
+        <v>2347</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>1313</v>
+      </c>
+      <c r="B51" t="s">
+        <v>510</v>
+      </c>
+      <c r="C51" t="s">
+        <v>2350</v>
+      </c>
+      <c r="D51" t="s">
+        <v>2351</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>1314</v>
+      </c>
+      <c r="B52" t="s">
+        <v>1385</v>
+      </c>
+      <c r="C52" t="s">
+        <v>2352</v>
+      </c>
+      <c r="D52" t="s">
+        <v>2356</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>1315</v>
+      </c>
+      <c r="B53" t="s">
+        <v>1386</v>
+      </c>
+      <c r="C53" t="s">
+        <v>2357</v>
+      </c>
+      <c r="D53" t="s">
+        <v>2358</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>1316</v>
+      </c>
+      <c r="B54" t="s">
+        <v>1387</v>
+      </c>
+      <c r="C54" t="s">
+        <v>2368</v>
+      </c>
+      <c r="D54" t="s">
+        <v>2369</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>1317</v>
+      </c>
+      <c r="B55" t="s">
+        <v>1388</v>
+      </c>
+      <c r="C55" t="s">
+        <v>2376</v>
+      </c>
+      <c r="D55" t="s">
+        <v>2377</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>1318</v>
+      </c>
+      <c r="B56" t="s">
+        <v>1389</v>
+      </c>
+      <c r="C56" t="s">
+        <v>2382</v>
+      </c>
+      <c r="D56" t="s">
+        <v>2383</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>1319</v>
+      </c>
+      <c r="B57" t="s">
+        <v>1020</v>
+      </c>
+      <c r="C57" t="s">
+        <v>2387</v>
+      </c>
+      <c r="D57" t="s">
+        <v>2388</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>1320</v>
+      </c>
+      <c r="B58" t="s">
+        <v>1390</v>
+      </c>
+      <c r="C58" t="s">
+        <v>2393</v>
+      </c>
+      <c r="D58" t="s">
+        <v>2394</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>1321</v>
+      </c>
+      <c r="B59" t="s">
+        <v>1391</v>
+      </c>
+      <c r="C59" t="s">
+        <v>2399</v>
+      </c>
+      <c r="D59" t="s">
+        <v>2400</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>1322</v>
+      </c>
+      <c r="B60" t="s">
+        <v>1392</v>
+      </c>
+      <c r="C60" t="s">
+        <v>2405</v>
+      </c>
+      <c r="D60" t="s">
+        <v>2406</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>1323</v>
+      </c>
+      <c r="B61" t="s">
+        <v>1393</v>
+      </c>
+      <c r="C61" t="s">
+        <v>2437</v>
+      </c>
+      <c r="D61" t="s">
+        <v>2438</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>1324</v>
+      </c>
+      <c r="B62" t="s">
+        <v>1394</v>
+      </c>
+      <c r="C62" t="s">
+        <v>2449</v>
+      </c>
+      <c r="D62" t="s">
+        <v>2450</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>1325</v>
+      </c>
+      <c r="B63" t="s">
+        <v>1395</v>
+      </c>
+      <c r="C63" t="s">
+        <v>2457</v>
+      </c>
+      <c r="D63" t="s">
+        <v>2458</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>1326</v>
+      </c>
+      <c r="B64" t="s">
+        <v>1396</v>
+      </c>
+      <c r="C64" t="s">
+        <v>2471</v>
+      </c>
+      <c r="D64" t="s">
+        <v>2472</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>1327</v>
+      </c>
+      <c r="B65" t="s">
+        <v>1397</v>
+      </c>
+      <c r="C65" t="s">
+        <v>2479</v>
+      </c>
+      <c r="D65" t="s">
+        <v>2480</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>1328</v>
+      </c>
+      <c r="B66" t="s">
+        <v>1398</v>
+      </c>
+      <c r="C66" t="s">
+        <v>2497</v>
+      </c>
+      <c r="D66" t="s">
+        <v>2498</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>1329</v>
+      </c>
+      <c r="B67" t="s">
+        <v>1399</v>
+      </c>
+      <c r="C67" t="s">
+        <v>2499</v>
+      </c>
+      <c r="D67" t="s">
+        <v>2500</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01AAAE8C-814F-43DB-A5DB-B841E00BE266}">
+  <dimension ref="A1:F64"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="12.5703125" customWidth="1"/>
+    <col min="2" max="2" width="24.5703125" customWidth="1"/>
+    <col min="3" max="5" width="20.28515625" customWidth="1"/>
+    <col min="6" max="6" width="11.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>1263</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1330</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>2150</v>
+      </c>
       <c r="F1" s="1" t="s">
-        <v>1888</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>1889</v>
+        <v>1467</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>1291</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1362</v>
+      </c>
+      <c r="C2" t="s">
+        <v>2086</v>
+      </c>
+      <c r="D2" t="s">
+        <v>2087</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2" t="s">
+        <v>1503</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>1291</v>
+      </c>
+      <c r="B3" t="s">
+        <v>1362</v>
+      </c>
+      <c r="C3" t="s">
+        <v>2088</v>
+      </c>
+      <c r="D3" t="s">
+        <v>2089</v>
+      </c>
+      <c r="E3">
+        <v>2</v>
+      </c>
+      <c r="F3" t="s">
+        <v>1503</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>1291</v>
+      </c>
+      <c r="B4" t="s">
+        <v>1362</v>
+      </c>
+      <c r="C4" t="s">
+        <v>2090</v>
+      </c>
+      <c r="D4" t="s">
+        <v>2091</v>
+      </c>
+      <c r="E4">
+        <v>3</v>
+      </c>
+      <c r="F4" t="s">
+        <v>1503</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>1291</v>
+      </c>
+      <c r="B5" t="s">
+        <v>1362</v>
+      </c>
+      <c r="C5" t="s">
+        <v>2092</v>
+      </c>
+      <c r="D5" t="s">
+        <v>2093</v>
+      </c>
+      <c r="E5">
+        <v>4</v>
+      </c>
+      <c r="F5" t="s">
+        <v>1503</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>1291</v>
+      </c>
+      <c r="B6" t="s">
+        <v>1362</v>
+      </c>
+      <c r="C6" t="s">
+        <v>2094</v>
+      </c>
+      <c r="D6" t="s">
+        <v>2096</v>
+      </c>
+      <c r="E6">
+        <v>5</v>
+      </c>
+      <c r="F6" t="s">
+        <v>1503</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>1291</v>
+      </c>
+      <c r="B7" t="s">
+        <v>1362</v>
+      </c>
+      <c r="C7" t="s">
+        <v>2095</v>
+      </c>
+      <c r="D7" t="s">
+        <v>2097</v>
+      </c>
+      <c r="E7">
+        <v>6</v>
+      </c>
+      <c r="F7" t="s">
+        <v>1503</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>1302</v>
+      </c>
+      <c r="B8" t="s">
+        <v>1374</v>
+      </c>
+      <c r="C8" t="s">
+        <v>2151</v>
+      </c>
+      <c r="D8" t="s">
+        <v>2165</v>
+      </c>
+      <c r="E8">
+        <v>1</v>
+      </c>
+      <c r="F8" t="s">
+        <v>1949</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>1302</v>
+      </c>
+      <c r="B9" t="s">
+        <v>1374</v>
+      </c>
+      <c r="C9" t="s">
+        <v>1333</v>
+      </c>
+      <c r="D9" t="s">
+        <v>2166</v>
+      </c>
+      <c r="E9">
+        <v>2</v>
+      </c>
+      <c r="F9" t="s">
+        <v>1949</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>1302</v>
+      </c>
+      <c r="B10" t="s">
+        <v>1374</v>
+      </c>
+      <c r="C10" t="s">
+        <v>2152</v>
+      </c>
+      <c r="D10" t="s">
+        <v>2167</v>
+      </c>
+      <c r="E10">
+        <v>3</v>
+      </c>
+      <c r="F10" t="s">
+        <v>1949</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>1302</v>
+      </c>
+      <c r="B11" t="s">
+        <v>1374</v>
+      </c>
+      <c r="C11" t="s">
+        <v>2153</v>
+      </c>
+      <c r="D11" t="s">
+        <v>2168</v>
+      </c>
+      <c r="E11">
+        <v>4</v>
+      </c>
+      <c r="F11" t="s">
+        <v>1949</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>1302</v>
+      </c>
+      <c r="B12" t="s">
+        <v>1374</v>
+      </c>
+      <c r="C12" t="s">
+        <v>2154</v>
+      </c>
+      <c r="D12" t="s">
+        <v>2169</v>
+      </c>
+      <c r="E12">
+        <v>5</v>
+      </c>
+      <c r="F12" t="s">
+        <v>1949</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>1302</v>
+      </c>
+      <c r="B13" t="s">
+        <v>1374</v>
+      </c>
+      <c r="C13" t="s">
+        <v>2155</v>
+      </c>
+      <c r="D13" t="s">
+        <v>2170</v>
+      </c>
+      <c r="E13">
+        <v>6</v>
+      </c>
+      <c r="F13" t="s">
+        <v>1949</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>1302</v>
+      </c>
+      <c r="B14" t="s">
+        <v>1374</v>
+      </c>
+      <c r="C14" t="s">
+        <v>2156</v>
+      </c>
+      <c r="D14" t="s">
+        <v>2171</v>
+      </c>
+      <c r="E14">
+        <v>7</v>
+      </c>
+      <c r="F14" t="s">
+        <v>1949</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>1302</v>
+      </c>
+      <c r="B15" t="s">
+        <v>1374</v>
+      </c>
+      <c r="C15" t="s">
+        <v>2157</v>
+      </c>
+      <c r="D15" t="s">
+        <v>2179</v>
+      </c>
+      <c r="E15">
+        <v>8</v>
+      </c>
+      <c r="F15" t="s">
+        <v>1949</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>1302</v>
+      </c>
+      <c r="B16" t="s">
+        <v>1374</v>
+      </c>
+      <c r="C16" t="s">
+        <v>2158</v>
+      </c>
+      <c r="D16" t="s">
+        <v>2172</v>
+      </c>
+      <c r="E16">
+        <v>9</v>
+      </c>
+      <c r="F16" t="s">
+        <v>1949</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>1302</v>
+      </c>
+      <c r="B17" t="s">
+        <v>1374</v>
+      </c>
+      <c r="C17" t="s">
+        <v>2159</v>
+      </c>
+      <c r="D17" t="s">
+        <v>2178</v>
+      </c>
+      <c r="E17">
+        <v>10</v>
+      </c>
+      <c r="F17" t="s">
+        <v>1949</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>1302</v>
+      </c>
+      <c r="B18" t="s">
+        <v>1374</v>
+      </c>
+      <c r="C18" t="s">
+        <v>2160</v>
+      </c>
+      <c r="D18" t="s">
+        <v>2173</v>
+      </c>
+      <c r="E18">
+        <v>11</v>
+      </c>
+      <c r="F18" t="s">
+        <v>1949</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>1302</v>
+      </c>
+      <c r="B19" t="s">
+        <v>1374</v>
+      </c>
+      <c r="C19" t="s">
+        <v>2161</v>
+      </c>
+      <c r="D19" t="s">
+        <v>2174</v>
+      </c>
+      <c r="E19">
+        <v>12</v>
+      </c>
+      <c r="F19" t="s">
+        <v>1949</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>1302</v>
+      </c>
+      <c r="B20" t="s">
+        <v>1374</v>
+      </c>
+      <c r="C20" t="s">
+        <v>2162</v>
+      </c>
+      <c r="D20" t="s">
+        <v>2175</v>
+      </c>
+      <c r="E20">
+        <v>13</v>
+      </c>
+      <c r="F20" t="s">
+        <v>1949</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>1302</v>
+      </c>
+      <c r="B21" t="s">
+        <v>1374</v>
+      </c>
+      <c r="C21" t="s">
+        <v>2163</v>
+      </c>
+      <c r="D21" t="s">
+        <v>2176</v>
+      </c>
+      <c r="E21">
+        <v>14</v>
+      </c>
+      <c r="F21" t="s">
+        <v>1949</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>1302</v>
+      </c>
+      <c r="B22" t="s">
+        <v>1374</v>
+      </c>
+      <c r="C22" t="s">
+        <v>2164</v>
+      </c>
+      <c r="D22" t="s">
+        <v>2177</v>
+      </c>
+      <c r="E22">
+        <v>15</v>
+      </c>
+      <c r="F22" t="s">
+        <v>1949</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>1304</v>
+      </c>
+      <c r="B23" t="s">
+        <v>1376</v>
+      </c>
+      <c r="C23" t="s">
+        <v>2194</v>
+      </c>
+      <c r="D23" t="s">
+        <v>2207</v>
+      </c>
+      <c r="E23">
+        <v>1</v>
+      </c>
+      <c r="F23" t="s">
+        <v>1468</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>1304</v>
+      </c>
+      <c r="B24" t="s">
+        <v>1376</v>
+      </c>
+      <c r="C24" t="s">
+        <v>2195</v>
+      </c>
+      <c r="D24" t="s">
+        <v>2208</v>
+      </c>
+      <c r="E24">
+        <v>2</v>
+      </c>
+      <c r="F24" t="s">
+        <v>1468</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>1304</v>
+      </c>
+      <c r="B25" t="s">
+        <v>1376</v>
+      </c>
+      <c r="C25" t="s">
+        <v>2196</v>
+      </c>
+      <c r="D25" t="s">
+        <v>2209</v>
+      </c>
+      <c r="E25">
+        <v>3</v>
+      </c>
+      <c r="F25" t="s">
+        <v>1468</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>1304</v>
+      </c>
+      <c r="B26" t="s">
+        <v>1376</v>
+      </c>
+      <c r="C26" t="s">
+        <v>2197</v>
+      </c>
+      <c r="D26" t="s">
+        <v>2210</v>
+      </c>
+      <c r="E26">
+        <v>4</v>
+      </c>
+      <c r="F26" t="s">
+        <v>1468</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>1304</v>
+      </c>
+      <c r="B27" t="s">
+        <v>1376</v>
+      </c>
+      <c r="C27" t="s">
+        <v>2198</v>
+      </c>
+      <c r="D27" t="s">
+        <v>2218</v>
+      </c>
+      <c r="E27">
+        <v>5</v>
+      </c>
+      <c r="F27" t="s">
+        <v>1468</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>1304</v>
+      </c>
+      <c r="B28" t="s">
+        <v>1376</v>
+      </c>
+      <c r="C28" t="s">
+        <v>2199</v>
+      </c>
+      <c r="D28" t="s">
+        <v>2211</v>
+      </c>
+      <c r="E28">
+        <v>6</v>
+      </c>
+      <c r="F28" t="s">
+        <v>1468</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>1304</v>
+      </c>
+      <c r="B29" t="s">
+        <v>1376</v>
+      </c>
+      <c r="C29" t="s">
+        <v>2200</v>
+      </c>
+      <c r="D29" t="s">
+        <v>2212</v>
+      </c>
+      <c r="E29">
+        <v>7</v>
+      </c>
+      <c r="F29" t="s">
+        <v>1468</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>1304</v>
+      </c>
+      <c r="B30" t="s">
+        <v>1376</v>
+      </c>
+      <c r="C30" t="s">
+        <v>2201</v>
+      </c>
+      <c r="D30" t="s">
+        <v>2213</v>
+      </c>
+      <c r="E30">
+        <v>8</v>
+      </c>
+      <c r="F30" t="s">
+        <v>1468</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>1304</v>
+      </c>
+      <c r="B31" t="s">
+        <v>1376</v>
+      </c>
+      <c r="C31" t="s">
+        <v>2202</v>
+      </c>
+      <c r="D31" t="s">
+        <v>2214</v>
+      </c>
+      <c r="E31">
+        <v>9</v>
+      </c>
+      <c r="F31" t="s">
+        <v>1949</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>1304</v>
+      </c>
+      <c r="B32" t="s">
+        <v>1376</v>
+      </c>
+      <c r="C32" t="s">
+        <v>2203</v>
+      </c>
+      <c r="D32" t="s">
+        <v>2215</v>
+      </c>
+      <c r="E32">
+        <v>10</v>
+      </c>
+      <c r="F32" t="s">
+        <v>1949</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>1304</v>
+      </c>
+      <c r="B33" t="s">
+        <v>1376</v>
+      </c>
+      <c r="C33" t="s">
+        <v>2204</v>
+      </c>
+      <c r="D33" t="s">
+        <v>2216</v>
+      </c>
+      <c r="E33">
+        <v>11</v>
+      </c>
+      <c r="F33" t="s">
+        <v>1468</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>1304</v>
+      </c>
+      <c r="B34" t="s">
+        <v>1376</v>
+      </c>
+      <c r="C34" t="s">
+        <v>2205</v>
+      </c>
+      <c r="D34" t="s">
+        <v>2219</v>
+      </c>
+      <c r="E34">
+        <v>12</v>
+      </c>
+      <c r="F34" t="s">
+        <v>1949</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>1304</v>
+      </c>
+      <c r="B35" t="s">
+        <v>1376</v>
+      </c>
+      <c r="C35" t="s">
+        <v>2206</v>
+      </c>
+      <c r="D35" t="s">
+        <v>2217</v>
+      </c>
+      <c r="E35">
+        <v>13</v>
+      </c>
+      <c r="F35" t="s">
+        <v>1468</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>1306</v>
+      </c>
+      <c r="B36" t="s">
+        <v>1378</v>
+      </c>
+      <c r="C36" t="s">
+        <v>2226</v>
+      </c>
+      <c r="D36" t="s">
+        <v>2229</v>
+      </c>
+      <c r="E36">
+        <v>1</v>
+      </c>
+      <c r="F36" t="s">
+        <v>1503</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>1306</v>
+      </c>
+      <c r="B37" t="s">
+        <v>1378</v>
+      </c>
+      <c r="C37" t="s">
+        <v>2227</v>
+      </c>
+      <c r="D37" t="s">
+        <v>2230</v>
+      </c>
+      <c r="E37">
+        <v>2</v>
+      </c>
+      <c r="F37" t="s">
+        <v>1503</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>1306</v>
+      </c>
+      <c r="B38" t="s">
+        <v>1378</v>
+      </c>
+      <c r="C38" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D38" t="s">
+        <v>2231</v>
+      </c>
+      <c r="E38">
+        <v>3</v>
+      </c>
+      <c r="F38" t="s">
+        <v>1503</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>1307</v>
+      </c>
+      <c r="B39" t="s">
+        <v>1379</v>
+      </c>
+      <c r="C39" t="s">
+        <v>2238</v>
+      </c>
+      <c r="D39" t="s">
+        <v>2239</v>
+      </c>
+      <c r="E39">
+        <v>1</v>
+      </c>
+      <c r="F39" t="s">
+        <v>1503</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>1307</v>
+      </c>
+      <c r="B40" t="s">
+        <v>1379</v>
+      </c>
+      <c r="C40" t="s">
+        <v>2240</v>
+      </c>
+      <c r="D40" t="s">
+        <v>2245</v>
+      </c>
+      <c r="E40">
+        <v>2</v>
+      </c>
+      <c r="F40" t="s">
+        <v>1503</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>1307</v>
+      </c>
+      <c r="B41" t="s">
+        <v>1379</v>
+      </c>
+      <c r="C41" t="s">
+        <v>2241</v>
+      </c>
+      <c r="D41" t="s">
+        <v>2244</v>
+      </c>
+      <c r="E41">
+        <v>3</v>
+      </c>
+      <c r="F41" t="s">
+        <v>1503</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>1307</v>
+      </c>
+      <c r="B42" t="s">
+        <v>1379</v>
+      </c>
+      <c r="C42" t="s">
+        <v>2242</v>
+      </c>
+      <c r="D42" t="s">
+        <v>2243</v>
+      </c>
+      <c r="E42">
+        <v>4</v>
+      </c>
+      <c r="F42" t="s">
+        <v>1503</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>1308</v>
+      </c>
+      <c r="B43" t="s">
+        <v>1380</v>
+      </c>
+      <c r="C43" t="s">
+        <v>2254</v>
+      </c>
+      <c r="D43" t="s">
+        <v>2263</v>
+      </c>
+      <c r="E43">
+        <v>1</v>
+      </c>
+      <c r="F43" t="s">
+        <v>1503</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>1308</v>
+      </c>
+      <c r="B44" t="s">
+        <v>1380</v>
+      </c>
+      <c r="C44" t="s">
+        <v>2255</v>
+      </c>
+      <c r="D44" t="s">
+        <v>2264</v>
+      </c>
+      <c r="E44">
+        <v>2</v>
+      </c>
+      <c r="F44" t="s">
+        <v>1503</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>1308</v>
+      </c>
+      <c r="B45" t="s">
+        <v>1380</v>
+      </c>
+      <c r="C45" t="s">
+        <v>2256</v>
+      </c>
+      <c r="D45" t="s">
+        <v>2266</v>
+      </c>
+      <c r="E45">
+        <v>3</v>
+      </c>
+      <c r="F45" t="s">
+        <v>1503</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>1308</v>
+      </c>
+      <c r="B46" t="s">
+        <v>1380</v>
+      </c>
+      <c r="C46" t="s">
+        <v>2257</v>
+      </c>
+      <c r="D46" t="s">
+        <v>2267</v>
+      </c>
+      <c r="E46">
+        <v>4</v>
+      </c>
+      <c r="F46" t="s">
+        <v>1503</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>1308</v>
+      </c>
+      <c r="B47" t="s">
+        <v>1380</v>
+      </c>
+      <c r="C47" t="s">
+        <v>2258</v>
+      </c>
+      <c r="D47" t="s">
+        <v>2268</v>
+      </c>
+      <c r="E47">
+        <v>5</v>
+      </c>
+      <c r="F47" t="s">
+        <v>1503</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>1308</v>
+      </c>
+      <c r="B48" t="s">
+        <v>1380</v>
+      </c>
+      <c r="C48" t="s">
+        <v>2259</v>
+      </c>
+      <c r="D48" t="s">
+        <v>2269</v>
+      </c>
+      <c r="E48">
+        <v>6</v>
+      </c>
+      <c r="F48" t="s">
+        <v>1503</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>1308</v>
+      </c>
+      <c r="B49" t="s">
+        <v>1380</v>
+      </c>
+      <c r="C49" t="s">
+        <v>2260</v>
+      </c>
+      <c r="D49" t="s">
+        <v>2270</v>
+      </c>
+      <c r="E49">
+        <v>7</v>
+      </c>
+      <c r="F49" t="s">
+        <v>1503</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>1308</v>
+      </c>
+      <c r="B50" t="s">
+        <v>1380</v>
+      </c>
+      <c r="C50" t="s">
+        <v>2261</v>
+      </c>
+      <c r="D50" t="s">
+        <v>2271</v>
+      </c>
+      <c r="E50">
+        <v>8</v>
+      </c>
+      <c r="F50" t="s">
+        <v>1503</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>1308</v>
+      </c>
+      <c r="B51" t="s">
+        <v>1380</v>
+      </c>
+      <c r="C51" t="s">
+        <v>2262</v>
+      </c>
+      <c r="D51" t="s">
+        <v>2265</v>
+      </c>
+      <c r="E51">
+        <v>9</v>
+      </c>
+      <c r="F51" t="s">
+        <v>1503</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>1309</v>
+      </c>
+      <c r="B52" t="s">
+        <v>1381</v>
+      </c>
+      <c r="C52" t="s">
+        <v>2288</v>
+      </c>
+      <c r="D52" t="s">
+        <v>2295</v>
+      </c>
+      <c r="E52">
+        <v>1</v>
+      </c>
+      <c r="F52" t="s">
+        <v>1503</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>1309</v>
+      </c>
+      <c r="B53" t="s">
+        <v>1381</v>
+      </c>
+      <c r="C53" t="s">
+        <v>2289</v>
+      </c>
+      <c r="D53" t="s">
+        <v>2296</v>
+      </c>
+      <c r="E53">
+        <v>2</v>
+      </c>
+      <c r="F53" t="s">
+        <v>1503</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>1309</v>
+      </c>
+      <c r="B54" t="s">
+        <v>1381</v>
+      </c>
+      <c r="C54" t="s">
+        <v>2290</v>
+      </c>
+      <c r="D54" t="s">
+        <v>2297</v>
+      </c>
+      <c r="E54">
+        <v>3</v>
+      </c>
+      <c r="F54" t="s">
+        <v>1503</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>1309</v>
+      </c>
+      <c r="B55" t="s">
+        <v>1381</v>
+      </c>
+      <c r="C55" t="s">
+        <v>2291</v>
+      </c>
+      <c r="D55" t="s">
+        <v>2300</v>
+      </c>
+      <c r="E55">
+        <v>4</v>
+      </c>
+      <c r="F55" t="s">
+        <v>1503</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>1309</v>
+      </c>
+      <c r="B56" t="s">
+        <v>1381</v>
+      </c>
+      <c r="C56" t="s">
+        <v>2292</v>
+      </c>
+      <c r="D56" t="s">
+        <v>2298</v>
+      </c>
+      <c r="E56">
+        <v>5</v>
+      </c>
+      <c r="F56" t="s">
+        <v>1503</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>1309</v>
+      </c>
+      <c r="B57" t="s">
+        <v>1381</v>
+      </c>
+      <c r="C57" t="s">
+        <v>2293</v>
+      </c>
+      <c r="D57" t="s">
+        <v>2299</v>
+      </c>
+      <c r="E57">
+        <v>6</v>
+      </c>
+      <c r="F57" t="s">
+        <v>1503</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>1309</v>
+      </c>
+      <c r="B58" t="s">
+        <v>1381</v>
+      </c>
+      <c r="C58" t="s">
+        <v>2294</v>
+      </c>
+      <c r="D58" t="s">
+        <v>2301</v>
+      </c>
+      <c r="E58">
+        <v>7</v>
+      </c>
+      <c r="F58" t="s">
+        <v>1503</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>1310</v>
+      </c>
+      <c r="B59" t="s">
+        <v>1382</v>
+      </c>
+      <c r="C59" t="s">
+        <v>2314</v>
+      </c>
+      <c r="D59" t="s">
+        <v>2318</v>
+      </c>
+      <c r="E59">
+        <v>1</v>
+      </c>
+      <c r="F59" t="s">
+        <v>1503</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>1310</v>
+      </c>
+      <c r="B60" t="s">
+        <v>1382</v>
+      </c>
+      <c r="C60" t="s">
+        <v>2315</v>
+      </c>
+      <c r="D60" t="s">
+        <v>2319</v>
+      </c>
+      <c r="E60">
+        <v>2</v>
+      </c>
+      <c r="F60" t="s">
+        <v>1503</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>1310</v>
+      </c>
+      <c r="B61" t="s">
+        <v>1382</v>
+      </c>
+      <c r="C61" t="s">
+        <v>2316</v>
+      </c>
+      <c r="D61" t="s">
+        <v>2320</v>
+      </c>
+      <c r="E61">
+        <v>3</v>
+      </c>
+      <c r="F61" t="s">
+        <v>1503</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>1310</v>
+      </c>
+      <c r="B62" t="s">
+        <v>1382</v>
+      </c>
+      <c r="C62" t="s">
+        <v>2317</v>
+      </c>
+      <c r="D62" t="s">
+        <v>2321</v>
+      </c>
+      <c r="E62">
+        <v>4</v>
+      </c>
+      <c r="F62" t="s">
+        <v>1503</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>1323</v>
+      </c>
+      <c r="B63" t="s">
+        <v>1393</v>
+      </c>
+      <c r="C63" t="s">
+        <v>2439</v>
+      </c>
+      <c r="D63" t="s">
+        <v>2440</v>
+      </c>
+      <c r="E63">
+        <v>1</v>
+      </c>
+      <c r="F63" t="s">
+        <v>1506</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>1326</v>
+      </c>
+      <c r="B64" t="s">
+        <v>1396</v>
+      </c>
+      <c r="C64" t="s">
+        <v>2473</v>
+      </c>
+      <c r="D64" t="s">
+        <v>2474</v>
+      </c>
+      <c r="E64">
+        <v>1</v>
+      </c>
+      <c r="F64" t="s">
+        <v>1503</v>
       </c>
     </row>
   </sheetData>

--- a/data/Fate-Spreadsheet.xlsx
+++ b/data/Fate-Spreadsheet.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Important\Python\Fate-Wiki\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE9E610C-D5D3-4347-8319-DA44D04AEDD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AECEEA88-4C6A-4D9C-BF5B-579B066E645F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="7" xr2:uid="{B05E798F-9EF6-4508-A0A4-311D06661AED}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="2" activeTab="7" xr2:uid="{B05E798F-9EF6-4508-A0A4-311D06661AED}"/>
   </bookViews>
   <sheets>
     <sheet name="Servants" sheetId="1" r:id="rId1"/>
@@ -20,8 +20,8 @@
     <sheet name="Servant Misc Cards" sheetId="7" r:id="rId5"/>
     <sheet name="Masters" sheetId="5" r:id="rId6"/>
     <sheet name="Master Abilities" sheetId="6" r:id="rId7"/>
-    <sheet name="Master Ascensions" sheetId="10" r:id="rId8"/>
-    <sheet name="Master Assets" sheetId="9" r:id="rId9"/>
+    <sheet name="Master Assets" sheetId="9" r:id="rId8"/>
+    <sheet name="Master Ascensions" sheetId="10" r:id="rId9"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5761" uniqueCount="2507">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5762" uniqueCount="2507">
   <si>
     <t>servant_id</t>
   </si>
@@ -25700,7 +25700,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32F3CD10-C054-4484-ABE2-D426F834FC22}">
-  <dimension ref="A1:J67"/>
+  <dimension ref="A1:K67"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.42578125" customWidth="1"/>
@@ -25711,9 +25711,10 @@
     <col min="8" max="8" width="19.85546875" customWidth="1"/>
     <col min="9" max="9" width="16" customWidth="1"/>
     <col min="10" max="10" width="13.140625" customWidth="1"/>
+    <col min="11" max="11" width="13.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>1263</v>
       </c>
@@ -25744,8 +25745,11 @@
       <c r="J1" s="1" t="s">
         <v>1887</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1264</v>
       </c>
@@ -25762,7 +25766,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>1265</v>
       </c>
@@ -25779,7 +25783,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>1266</v>
       </c>
@@ -25796,7 +25800,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>1267</v>
       </c>
@@ -25813,7 +25817,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>1268</v>
       </c>
@@ -25830,7 +25834,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>1269</v>
       </c>
@@ -25847,7 +25851,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>1270</v>
       </c>
@@ -25864,7 +25868,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>1271</v>
       </c>
@@ -25881,7 +25885,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>1272</v>
       </c>
@@ -25895,7 +25899,7 @@
         <v>1337</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>1273</v>
       </c>
@@ -25912,7 +25916,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>1274</v>
       </c>
@@ -25929,7 +25933,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>1275</v>
       </c>
@@ -25943,7 +25947,7 @@
         <v>1333</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>1276</v>
       </c>
@@ -25960,7 +25964,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>1277</v>
       </c>
@@ -25974,7 +25978,7 @@
         <v>1335</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>1278</v>
       </c>
@@ -30163,6 +30167,1302 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01AAAE8C-814F-43DB-A5DB-B841E00BE266}">
+  <dimension ref="A1:F64"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="12.5703125" customWidth="1"/>
+    <col min="2" max="2" width="24.5703125" customWidth="1"/>
+    <col min="3" max="5" width="20.28515625" customWidth="1"/>
+    <col min="6" max="6" width="11.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>1263</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1330</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>2150</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>1467</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>1291</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1362</v>
+      </c>
+      <c r="C2" t="s">
+        <v>2086</v>
+      </c>
+      <c r="D2" t="s">
+        <v>2087</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2" t="s">
+        <v>1503</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>1291</v>
+      </c>
+      <c r="B3" t="s">
+        <v>1362</v>
+      </c>
+      <c r="C3" t="s">
+        <v>2088</v>
+      </c>
+      <c r="D3" t="s">
+        <v>2089</v>
+      </c>
+      <c r="E3">
+        <v>2</v>
+      </c>
+      <c r="F3" t="s">
+        <v>1503</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>1291</v>
+      </c>
+      <c r="B4" t="s">
+        <v>1362</v>
+      </c>
+      <c r="C4" t="s">
+        <v>2090</v>
+      </c>
+      <c r="D4" t="s">
+        <v>2091</v>
+      </c>
+      <c r="E4">
+        <v>3</v>
+      </c>
+      <c r="F4" t="s">
+        <v>1503</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>1291</v>
+      </c>
+      <c r="B5" t="s">
+        <v>1362</v>
+      </c>
+      <c r="C5" t="s">
+        <v>2092</v>
+      </c>
+      <c r="D5" t="s">
+        <v>2093</v>
+      </c>
+      <c r="E5">
+        <v>4</v>
+      </c>
+      <c r="F5" t="s">
+        <v>1503</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>1291</v>
+      </c>
+      <c r="B6" t="s">
+        <v>1362</v>
+      </c>
+      <c r="C6" t="s">
+        <v>2094</v>
+      </c>
+      <c r="D6" t="s">
+        <v>2096</v>
+      </c>
+      <c r="E6">
+        <v>5</v>
+      </c>
+      <c r="F6" t="s">
+        <v>1503</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>1291</v>
+      </c>
+      <c r="B7" t="s">
+        <v>1362</v>
+      </c>
+      <c r="C7" t="s">
+        <v>2095</v>
+      </c>
+      <c r="D7" t="s">
+        <v>2097</v>
+      </c>
+      <c r="E7">
+        <v>6</v>
+      </c>
+      <c r="F7" t="s">
+        <v>1503</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>1302</v>
+      </c>
+      <c r="B8" t="s">
+        <v>1374</v>
+      </c>
+      <c r="C8" t="s">
+        <v>2151</v>
+      </c>
+      <c r="D8" t="s">
+        <v>2165</v>
+      </c>
+      <c r="E8">
+        <v>1</v>
+      </c>
+      <c r="F8" t="s">
+        <v>1949</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>1302</v>
+      </c>
+      <c r="B9" t="s">
+        <v>1374</v>
+      </c>
+      <c r="C9" t="s">
+        <v>1333</v>
+      </c>
+      <c r="D9" t="s">
+        <v>2166</v>
+      </c>
+      <c r="E9">
+        <v>2</v>
+      </c>
+      <c r="F9" t="s">
+        <v>1949</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>1302</v>
+      </c>
+      <c r="B10" t="s">
+        <v>1374</v>
+      </c>
+      <c r="C10" t="s">
+        <v>2152</v>
+      </c>
+      <c r="D10" t="s">
+        <v>2167</v>
+      </c>
+      <c r="E10">
+        <v>3</v>
+      </c>
+      <c r="F10" t="s">
+        <v>1949</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>1302</v>
+      </c>
+      <c r="B11" t="s">
+        <v>1374</v>
+      </c>
+      <c r="C11" t="s">
+        <v>2153</v>
+      </c>
+      <c r="D11" t="s">
+        <v>2168</v>
+      </c>
+      <c r="E11">
+        <v>4</v>
+      </c>
+      <c r="F11" t="s">
+        <v>1949</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>1302</v>
+      </c>
+      <c r="B12" t="s">
+        <v>1374</v>
+      </c>
+      <c r="C12" t="s">
+        <v>2154</v>
+      </c>
+      <c r="D12" t="s">
+        <v>2169</v>
+      </c>
+      <c r="E12">
+        <v>5</v>
+      </c>
+      <c r="F12" t="s">
+        <v>1949</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>1302</v>
+      </c>
+      <c r="B13" t="s">
+        <v>1374</v>
+      </c>
+      <c r="C13" t="s">
+        <v>2155</v>
+      </c>
+      <c r="D13" t="s">
+        <v>2170</v>
+      </c>
+      <c r="E13">
+        <v>6</v>
+      </c>
+      <c r="F13" t="s">
+        <v>1949</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>1302</v>
+      </c>
+      <c r="B14" t="s">
+        <v>1374</v>
+      </c>
+      <c r="C14" t="s">
+        <v>2156</v>
+      </c>
+      <c r="D14" t="s">
+        <v>2171</v>
+      </c>
+      <c r="E14">
+        <v>7</v>
+      </c>
+      <c r="F14" t="s">
+        <v>1949</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>1302</v>
+      </c>
+      <c r="B15" t="s">
+        <v>1374</v>
+      </c>
+      <c r="C15" t="s">
+        <v>2157</v>
+      </c>
+      <c r="D15" t="s">
+        <v>2179</v>
+      </c>
+      <c r="E15">
+        <v>8</v>
+      </c>
+      <c r="F15" t="s">
+        <v>1949</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>1302</v>
+      </c>
+      <c r="B16" t="s">
+        <v>1374</v>
+      </c>
+      <c r="C16" t="s">
+        <v>2158</v>
+      </c>
+      <c r="D16" t="s">
+        <v>2172</v>
+      </c>
+      <c r="E16">
+        <v>9</v>
+      </c>
+      <c r="F16" t="s">
+        <v>1949</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>1302</v>
+      </c>
+      <c r="B17" t="s">
+        <v>1374</v>
+      </c>
+      <c r="C17" t="s">
+        <v>2159</v>
+      </c>
+      <c r="D17" t="s">
+        <v>2178</v>
+      </c>
+      <c r="E17">
+        <v>10</v>
+      </c>
+      <c r="F17" t="s">
+        <v>1949</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>1302</v>
+      </c>
+      <c r="B18" t="s">
+        <v>1374</v>
+      </c>
+      <c r="C18" t="s">
+        <v>2160</v>
+      </c>
+      <c r="D18" t="s">
+        <v>2173</v>
+      </c>
+      <c r="E18">
+        <v>11</v>
+      </c>
+      <c r="F18" t="s">
+        <v>1949</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>1302</v>
+      </c>
+      <c r="B19" t="s">
+        <v>1374</v>
+      </c>
+      <c r="C19" t="s">
+        <v>2161</v>
+      </c>
+      <c r="D19" t="s">
+        <v>2174</v>
+      </c>
+      <c r="E19">
+        <v>12</v>
+      </c>
+      <c r="F19" t="s">
+        <v>1949</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>1302</v>
+      </c>
+      <c r="B20" t="s">
+        <v>1374</v>
+      </c>
+      <c r="C20" t="s">
+        <v>2162</v>
+      </c>
+      <c r="D20" t="s">
+        <v>2175</v>
+      </c>
+      <c r="E20">
+        <v>13</v>
+      </c>
+      <c r="F20" t="s">
+        <v>1949</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>1302</v>
+      </c>
+      <c r="B21" t="s">
+        <v>1374</v>
+      </c>
+      <c r="C21" t="s">
+        <v>2163</v>
+      </c>
+      <c r="D21" t="s">
+        <v>2176</v>
+      </c>
+      <c r="E21">
+        <v>14</v>
+      </c>
+      <c r="F21" t="s">
+        <v>1949</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>1302</v>
+      </c>
+      <c r="B22" t="s">
+        <v>1374</v>
+      </c>
+      <c r="C22" t="s">
+        <v>2164</v>
+      </c>
+      <c r="D22" t="s">
+        <v>2177</v>
+      </c>
+      <c r="E22">
+        <v>15</v>
+      </c>
+      <c r="F22" t="s">
+        <v>1949</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>1304</v>
+      </c>
+      <c r="B23" t="s">
+        <v>1376</v>
+      </c>
+      <c r="C23" t="s">
+        <v>2194</v>
+      </c>
+      <c r="D23" t="s">
+        <v>2207</v>
+      </c>
+      <c r="E23">
+        <v>1</v>
+      </c>
+      <c r="F23" t="s">
+        <v>1468</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>1304</v>
+      </c>
+      <c r="B24" t="s">
+        <v>1376</v>
+      </c>
+      <c r="C24" t="s">
+        <v>2195</v>
+      </c>
+      <c r="D24" t="s">
+        <v>2208</v>
+      </c>
+      <c r="E24">
+        <v>2</v>
+      </c>
+      <c r="F24" t="s">
+        <v>1468</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>1304</v>
+      </c>
+      <c r="B25" t="s">
+        <v>1376</v>
+      </c>
+      <c r="C25" t="s">
+        <v>2196</v>
+      </c>
+      <c r="D25" t="s">
+        <v>2209</v>
+      </c>
+      <c r="E25">
+        <v>3</v>
+      </c>
+      <c r="F25" t="s">
+        <v>1468</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>1304</v>
+      </c>
+      <c r="B26" t="s">
+        <v>1376</v>
+      </c>
+      <c r="C26" t="s">
+        <v>2197</v>
+      </c>
+      <c r="D26" t="s">
+        <v>2210</v>
+      </c>
+      <c r="E26">
+        <v>4</v>
+      </c>
+      <c r="F26" t="s">
+        <v>1468</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>1304</v>
+      </c>
+      <c r="B27" t="s">
+        <v>1376</v>
+      </c>
+      <c r="C27" t="s">
+        <v>2198</v>
+      </c>
+      <c r="D27" t="s">
+        <v>2218</v>
+      </c>
+      <c r="E27">
+        <v>5</v>
+      </c>
+      <c r="F27" t="s">
+        <v>1468</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>1304</v>
+      </c>
+      <c r="B28" t="s">
+        <v>1376</v>
+      </c>
+      <c r="C28" t="s">
+        <v>2199</v>
+      </c>
+      <c r="D28" t="s">
+        <v>2211</v>
+      </c>
+      <c r="E28">
+        <v>6</v>
+      </c>
+      <c r="F28" t="s">
+        <v>1468</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>1304</v>
+      </c>
+      <c r="B29" t="s">
+        <v>1376</v>
+      </c>
+      <c r="C29" t="s">
+        <v>2200</v>
+      </c>
+      <c r="D29" t="s">
+        <v>2212</v>
+      </c>
+      <c r="E29">
+        <v>7</v>
+      </c>
+      <c r="F29" t="s">
+        <v>1468</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>1304</v>
+      </c>
+      <c r="B30" t="s">
+        <v>1376</v>
+      </c>
+      <c r="C30" t="s">
+        <v>2201</v>
+      </c>
+      <c r="D30" t="s">
+        <v>2213</v>
+      </c>
+      <c r="E30">
+        <v>8</v>
+      </c>
+      <c r="F30" t="s">
+        <v>1468</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>1304</v>
+      </c>
+      <c r="B31" t="s">
+        <v>1376</v>
+      </c>
+      <c r="C31" t="s">
+        <v>2202</v>
+      </c>
+      <c r="D31" t="s">
+        <v>2214</v>
+      </c>
+      <c r="E31">
+        <v>9</v>
+      </c>
+      <c r="F31" t="s">
+        <v>1949</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>1304</v>
+      </c>
+      <c r="B32" t="s">
+        <v>1376</v>
+      </c>
+      <c r="C32" t="s">
+        <v>2203</v>
+      </c>
+      <c r="D32" t="s">
+        <v>2215</v>
+      </c>
+      <c r="E32">
+        <v>10</v>
+      </c>
+      <c r="F32" t="s">
+        <v>1949</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>1304</v>
+      </c>
+      <c r="B33" t="s">
+        <v>1376</v>
+      </c>
+      <c r="C33" t="s">
+        <v>2204</v>
+      </c>
+      <c r="D33" t="s">
+        <v>2216</v>
+      </c>
+      <c r="E33">
+        <v>11</v>
+      </c>
+      <c r="F33" t="s">
+        <v>1468</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>1304</v>
+      </c>
+      <c r="B34" t="s">
+        <v>1376</v>
+      </c>
+      <c r="C34" t="s">
+        <v>2205</v>
+      </c>
+      <c r="D34" t="s">
+        <v>2219</v>
+      </c>
+      <c r="E34">
+        <v>12</v>
+      </c>
+      <c r="F34" t="s">
+        <v>1949</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>1304</v>
+      </c>
+      <c r="B35" t="s">
+        <v>1376</v>
+      </c>
+      <c r="C35" t="s">
+        <v>2206</v>
+      </c>
+      <c r="D35" t="s">
+        <v>2217</v>
+      </c>
+      <c r="E35">
+        <v>13</v>
+      </c>
+      <c r="F35" t="s">
+        <v>1468</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>1306</v>
+      </c>
+      <c r="B36" t="s">
+        <v>1378</v>
+      </c>
+      <c r="C36" t="s">
+        <v>2226</v>
+      </c>
+      <c r="D36" t="s">
+        <v>2229</v>
+      </c>
+      <c r="E36">
+        <v>1</v>
+      </c>
+      <c r="F36" t="s">
+        <v>1503</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>1306</v>
+      </c>
+      <c r="B37" t="s">
+        <v>1378</v>
+      </c>
+      <c r="C37" t="s">
+        <v>2227</v>
+      </c>
+      <c r="D37" t="s">
+        <v>2230</v>
+      </c>
+      <c r="E37">
+        <v>2</v>
+      </c>
+      <c r="F37" t="s">
+        <v>1503</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>1306</v>
+      </c>
+      <c r="B38" t="s">
+        <v>1378</v>
+      </c>
+      <c r="C38" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D38" t="s">
+        <v>2231</v>
+      </c>
+      <c r="E38">
+        <v>3</v>
+      </c>
+      <c r="F38" t="s">
+        <v>1503</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>1307</v>
+      </c>
+      <c r="B39" t="s">
+        <v>1379</v>
+      </c>
+      <c r="C39" t="s">
+        <v>2238</v>
+      </c>
+      <c r="D39" t="s">
+        <v>2239</v>
+      </c>
+      <c r="E39">
+        <v>1</v>
+      </c>
+      <c r="F39" t="s">
+        <v>1503</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>1307</v>
+      </c>
+      <c r="B40" t="s">
+        <v>1379</v>
+      </c>
+      <c r="C40" t="s">
+        <v>2240</v>
+      </c>
+      <c r="D40" t="s">
+        <v>2245</v>
+      </c>
+      <c r="E40">
+        <v>2</v>
+      </c>
+      <c r="F40" t="s">
+        <v>1503</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>1307</v>
+      </c>
+      <c r="B41" t="s">
+        <v>1379</v>
+      </c>
+      <c r="C41" t="s">
+        <v>2241</v>
+      </c>
+      <c r="D41" t="s">
+        <v>2244</v>
+      </c>
+      <c r="E41">
+        <v>3</v>
+      </c>
+      <c r="F41" t="s">
+        <v>1503</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>1307</v>
+      </c>
+      <c r="B42" t="s">
+        <v>1379</v>
+      </c>
+      <c r="C42" t="s">
+        <v>2242</v>
+      </c>
+      <c r="D42" t="s">
+        <v>2243</v>
+      </c>
+      <c r="E42">
+        <v>4</v>
+      </c>
+      <c r="F42" t="s">
+        <v>1503</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>1308</v>
+      </c>
+      <c r="B43" t="s">
+        <v>1380</v>
+      </c>
+      <c r="C43" t="s">
+        <v>2254</v>
+      </c>
+      <c r="D43" t="s">
+        <v>2263</v>
+      </c>
+      <c r="E43">
+        <v>1</v>
+      </c>
+      <c r="F43" t="s">
+        <v>1503</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>1308</v>
+      </c>
+      <c r="B44" t="s">
+        <v>1380</v>
+      </c>
+      <c r="C44" t="s">
+        <v>2255</v>
+      </c>
+      <c r="D44" t="s">
+        <v>2264</v>
+      </c>
+      <c r="E44">
+        <v>2</v>
+      </c>
+      <c r="F44" t="s">
+        <v>1503</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>1308</v>
+      </c>
+      <c r="B45" t="s">
+        <v>1380</v>
+      </c>
+      <c r="C45" t="s">
+        <v>2256</v>
+      </c>
+      <c r="D45" t="s">
+        <v>2266</v>
+      </c>
+      <c r="E45">
+        <v>3</v>
+      </c>
+      <c r="F45" t="s">
+        <v>1503</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>1308</v>
+      </c>
+      <c r="B46" t="s">
+        <v>1380</v>
+      </c>
+      <c r="C46" t="s">
+        <v>2257</v>
+      </c>
+      <c r="D46" t="s">
+        <v>2267</v>
+      </c>
+      <c r="E46">
+        <v>4</v>
+      </c>
+      <c r="F46" t="s">
+        <v>1503</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>1308</v>
+      </c>
+      <c r="B47" t="s">
+        <v>1380</v>
+      </c>
+      <c r="C47" t="s">
+        <v>2258</v>
+      </c>
+      <c r="D47" t="s">
+        <v>2268</v>
+      </c>
+      <c r="E47">
+        <v>5</v>
+      </c>
+      <c r="F47" t="s">
+        <v>1503</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>1308</v>
+      </c>
+      <c r="B48" t="s">
+        <v>1380</v>
+      </c>
+      <c r="C48" t="s">
+        <v>2259</v>
+      </c>
+      <c r="D48" t="s">
+        <v>2269</v>
+      </c>
+      <c r="E48">
+        <v>6</v>
+      </c>
+      <c r="F48" t="s">
+        <v>1503</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>1308</v>
+      </c>
+      <c r="B49" t="s">
+        <v>1380</v>
+      </c>
+      <c r="C49" t="s">
+        <v>2260</v>
+      </c>
+      <c r="D49" t="s">
+        <v>2270</v>
+      </c>
+      <c r="E49">
+        <v>7</v>
+      </c>
+      <c r="F49" t="s">
+        <v>1503</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>1308</v>
+      </c>
+      <c r="B50" t="s">
+        <v>1380</v>
+      </c>
+      <c r="C50" t="s">
+        <v>2261</v>
+      </c>
+      <c r="D50" t="s">
+        <v>2271</v>
+      </c>
+      <c r="E50">
+        <v>8</v>
+      </c>
+      <c r="F50" t="s">
+        <v>1503</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>1308</v>
+      </c>
+      <c r="B51" t="s">
+        <v>1380</v>
+      </c>
+      <c r="C51" t="s">
+        <v>2262</v>
+      </c>
+      <c r="D51" t="s">
+        <v>2265</v>
+      </c>
+      <c r="E51">
+        <v>9</v>
+      </c>
+      <c r="F51" t="s">
+        <v>1503</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>1309</v>
+      </c>
+      <c r="B52" t="s">
+        <v>1381</v>
+      </c>
+      <c r="C52" t="s">
+        <v>2288</v>
+      </c>
+      <c r="D52" t="s">
+        <v>2295</v>
+      </c>
+      <c r="E52">
+        <v>1</v>
+      </c>
+      <c r="F52" t="s">
+        <v>1503</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>1309</v>
+      </c>
+      <c r="B53" t="s">
+        <v>1381</v>
+      </c>
+      <c r="C53" t="s">
+        <v>2289</v>
+      </c>
+      <c r="D53" t="s">
+        <v>2296</v>
+      </c>
+      <c r="E53">
+        <v>2</v>
+      </c>
+      <c r="F53" t="s">
+        <v>1503</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>1309</v>
+      </c>
+      <c r="B54" t="s">
+        <v>1381</v>
+      </c>
+      <c r="C54" t="s">
+        <v>2290</v>
+      </c>
+      <c r="D54" t="s">
+        <v>2297</v>
+      </c>
+      <c r="E54">
+        <v>3</v>
+      </c>
+      <c r="F54" t="s">
+        <v>1503</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>1309</v>
+      </c>
+      <c r="B55" t="s">
+        <v>1381</v>
+      </c>
+      <c r="C55" t="s">
+        <v>2291</v>
+      </c>
+      <c r="D55" t="s">
+        <v>2300</v>
+      </c>
+      <c r="E55">
+        <v>4</v>
+      </c>
+      <c r="F55" t="s">
+        <v>1503</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>1309</v>
+      </c>
+      <c r="B56" t="s">
+        <v>1381</v>
+      </c>
+      <c r="C56" t="s">
+        <v>2292</v>
+      </c>
+      <c r="D56" t="s">
+        <v>2298</v>
+      </c>
+      <c r="E56">
+        <v>5</v>
+      </c>
+      <c r="F56" t="s">
+        <v>1503</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>1309</v>
+      </c>
+      <c r="B57" t="s">
+        <v>1381</v>
+      </c>
+      <c r="C57" t="s">
+        <v>2293</v>
+      </c>
+      <c r="D57" t="s">
+        <v>2299</v>
+      </c>
+      <c r="E57">
+        <v>6</v>
+      </c>
+      <c r="F57" t="s">
+        <v>1503</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>1309</v>
+      </c>
+      <c r="B58" t="s">
+        <v>1381</v>
+      </c>
+      <c r="C58" t="s">
+        <v>2294</v>
+      </c>
+      <c r="D58" t="s">
+        <v>2301</v>
+      </c>
+      <c r="E58">
+        <v>7</v>
+      </c>
+      <c r="F58" t="s">
+        <v>1503</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>1310</v>
+      </c>
+      <c r="B59" t="s">
+        <v>1382</v>
+      </c>
+      <c r="C59" t="s">
+        <v>2314</v>
+      </c>
+      <c r="D59" t="s">
+        <v>2318</v>
+      </c>
+      <c r="E59">
+        <v>1</v>
+      </c>
+      <c r="F59" t="s">
+        <v>1503</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>1310</v>
+      </c>
+      <c r="B60" t="s">
+        <v>1382</v>
+      </c>
+      <c r="C60" t="s">
+        <v>2315</v>
+      </c>
+      <c r="D60" t="s">
+        <v>2319</v>
+      </c>
+      <c r="E60">
+        <v>2</v>
+      </c>
+      <c r="F60" t="s">
+        <v>1503</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>1310</v>
+      </c>
+      <c r="B61" t="s">
+        <v>1382</v>
+      </c>
+      <c r="C61" t="s">
+        <v>2316</v>
+      </c>
+      <c r="D61" t="s">
+        <v>2320</v>
+      </c>
+      <c r="E61">
+        <v>3</v>
+      </c>
+      <c r="F61" t="s">
+        <v>1503</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>1310</v>
+      </c>
+      <c r="B62" t="s">
+        <v>1382</v>
+      </c>
+      <c r="C62" t="s">
+        <v>2317</v>
+      </c>
+      <c r="D62" t="s">
+        <v>2321</v>
+      </c>
+      <c r="E62">
+        <v>4</v>
+      </c>
+      <c r="F62" t="s">
+        <v>1503</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>1323</v>
+      </c>
+      <c r="B63" t="s">
+        <v>1393</v>
+      </c>
+      <c r="C63" t="s">
+        <v>2439</v>
+      </c>
+      <c r="D63" t="s">
+        <v>2440</v>
+      </c>
+      <c r="E63">
+        <v>1</v>
+      </c>
+      <c r="F63" t="s">
+        <v>1506</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>1326</v>
+      </c>
+      <c r="B64" t="s">
+        <v>1396</v>
+      </c>
+      <c r="C64" t="s">
+        <v>2473</v>
+      </c>
+      <c r="D64" t="s">
+        <v>2474</v>
+      </c>
+      <c r="E64">
+        <v>1</v>
+      </c>
+      <c r="F64" t="s">
+        <v>1503</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F134C8BE-E9AE-4B7A-9200-034BBD6B89FF}">
   <dimension ref="A1:D67"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -31114,1300 +32414,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01AAAE8C-814F-43DB-A5DB-B841E00BE266}">
-  <dimension ref="A1:F64"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="12.5703125" customWidth="1"/>
-    <col min="2" max="2" width="24.5703125" customWidth="1"/>
-    <col min="3" max="5" width="20.28515625" customWidth="1"/>
-    <col min="6" max="6" width="11.140625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>1263</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1330</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>2150</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>1467</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>1291</v>
-      </c>
-      <c r="B2" t="s">
-        <v>1362</v>
-      </c>
-      <c r="C2" t="s">
-        <v>2086</v>
-      </c>
-      <c r="D2" t="s">
-        <v>2087</v>
-      </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
-      <c r="F2" t="s">
-        <v>1503</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>1291</v>
-      </c>
-      <c r="B3" t="s">
-        <v>1362</v>
-      </c>
-      <c r="C3" t="s">
-        <v>2088</v>
-      </c>
-      <c r="D3" t="s">
-        <v>2089</v>
-      </c>
-      <c r="E3">
-        <v>2</v>
-      </c>
-      <c r="F3" t="s">
-        <v>1503</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>1291</v>
-      </c>
-      <c r="B4" t="s">
-        <v>1362</v>
-      </c>
-      <c r="C4" t="s">
-        <v>2090</v>
-      </c>
-      <c r="D4" t="s">
-        <v>2091</v>
-      </c>
-      <c r="E4">
-        <v>3</v>
-      </c>
-      <c r="F4" t="s">
-        <v>1503</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>1291</v>
-      </c>
-      <c r="B5" t="s">
-        <v>1362</v>
-      </c>
-      <c r="C5" t="s">
-        <v>2092</v>
-      </c>
-      <c r="D5" t="s">
-        <v>2093</v>
-      </c>
-      <c r="E5">
-        <v>4</v>
-      </c>
-      <c r="F5" t="s">
-        <v>1503</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>1291</v>
-      </c>
-      <c r="B6" t="s">
-        <v>1362</v>
-      </c>
-      <c r="C6" t="s">
-        <v>2094</v>
-      </c>
-      <c r="D6" t="s">
-        <v>2096</v>
-      </c>
-      <c r="E6">
-        <v>5</v>
-      </c>
-      <c r="F6" t="s">
-        <v>1503</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>1291</v>
-      </c>
-      <c r="B7" t="s">
-        <v>1362</v>
-      </c>
-      <c r="C7" t="s">
-        <v>2095</v>
-      </c>
-      <c r="D7" t="s">
-        <v>2097</v>
-      </c>
-      <c r="E7">
-        <v>6</v>
-      </c>
-      <c r="F7" t="s">
-        <v>1503</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>1302</v>
-      </c>
-      <c r="B8" t="s">
-        <v>1374</v>
-      </c>
-      <c r="C8" t="s">
-        <v>2151</v>
-      </c>
-      <c r="D8" t="s">
-        <v>2165</v>
-      </c>
-      <c r="E8">
-        <v>1</v>
-      </c>
-      <c r="F8" t="s">
-        <v>1949</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>1302</v>
-      </c>
-      <c r="B9" t="s">
-        <v>1374</v>
-      </c>
-      <c r="C9" t="s">
-        <v>1333</v>
-      </c>
-      <c r="D9" t="s">
-        <v>2166</v>
-      </c>
-      <c r="E9">
-        <v>2</v>
-      </c>
-      <c r="F9" t="s">
-        <v>1949</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>1302</v>
-      </c>
-      <c r="B10" t="s">
-        <v>1374</v>
-      </c>
-      <c r="C10" t="s">
-        <v>2152</v>
-      </c>
-      <c r="D10" t="s">
-        <v>2167</v>
-      </c>
-      <c r="E10">
-        <v>3</v>
-      </c>
-      <c r="F10" t="s">
-        <v>1949</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>1302</v>
-      </c>
-      <c r="B11" t="s">
-        <v>1374</v>
-      </c>
-      <c r="C11" t="s">
-        <v>2153</v>
-      </c>
-      <c r="D11" t="s">
-        <v>2168</v>
-      </c>
-      <c r="E11">
-        <v>4</v>
-      </c>
-      <c r="F11" t="s">
-        <v>1949</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>1302</v>
-      </c>
-      <c r="B12" t="s">
-        <v>1374</v>
-      </c>
-      <c r="C12" t="s">
-        <v>2154</v>
-      </c>
-      <c r="D12" t="s">
-        <v>2169</v>
-      </c>
-      <c r="E12">
-        <v>5</v>
-      </c>
-      <c r="F12" t="s">
-        <v>1949</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>1302</v>
-      </c>
-      <c r="B13" t="s">
-        <v>1374</v>
-      </c>
-      <c r="C13" t="s">
-        <v>2155</v>
-      </c>
-      <c r="D13" t="s">
-        <v>2170</v>
-      </c>
-      <c r="E13">
-        <v>6</v>
-      </c>
-      <c r="F13" t="s">
-        <v>1949</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>1302</v>
-      </c>
-      <c r="B14" t="s">
-        <v>1374</v>
-      </c>
-      <c r="C14" t="s">
-        <v>2156</v>
-      </c>
-      <c r="D14" t="s">
-        <v>2171</v>
-      </c>
-      <c r="E14">
-        <v>7</v>
-      </c>
-      <c r="F14" t="s">
-        <v>1949</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>1302</v>
-      </c>
-      <c r="B15" t="s">
-        <v>1374</v>
-      </c>
-      <c r="C15" t="s">
-        <v>2157</v>
-      </c>
-      <c r="D15" t="s">
-        <v>2179</v>
-      </c>
-      <c r="E15">
-        <v>8</v>
-      </c>
-      <c r="F15" t="s">
-        <v>1949</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>1302</v>
-      </c>
-      <c r="B16" t="s">
-        <v>1374</v>
-      </c>
-      <c r="C16" t="s">
-        <v>2158</v>
-      </c>
-      <c r="D16" t="s">
-        <v>2172</v>
-      </c>
-      <c r="E16">
-        <v>9</v>
-      </c>
-      <c r="F16" t="s">
-        <v>1949</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>1302</v>
-      </c>
-      <c r="B17" t="s">
-        <v>1374</v>
-      </c>
-      <c r="C17" t="s">
-        <v>2159</v>
-      </c>
-      <c r="D17" t="s">
-        <v>2178</v>
-      </c>
-      <c r="E17">
-        <v>10</v>
-      </c>
-      <c r="F17" t="s">
-        <v>1949</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>1302</v>
-      </c>
-      <c r="B18" t="s">
-        <v>1374</v>
-      </c>
-      <c r="C18" t="s">
-        <v>2160</v>
-      </c>
-      <c r="D18" t="s">
-        <v>2173</v>
-      </c>
-      <c r="E18">
-        <v>11</v>
-      </c>
-      <c r="F18" t="s">
-        <v>1949</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>1302</v>
-      </c>
-      <c r="B19" t="s">
-        <v>1374</v>
-      </c>
-      <c r="C19" t="s">
-        <v>2161</v>
-      </c>
-      <c r="D19" t="s">
-        <v>2174</v>
-      </c>
-      <c r="E19">
-        <v>12</v>
-      </c>
-      <c r="F19" t="s">
-        <v>1949</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>1302</v>
-      </c>
-      <c r="B20" t="s">
-        <v>1374</v>
-      </c>
-      <c r="C20" t="s">
-        <v>2162</v>
-      </c>
-      <c r="D20" t="s">
-        <v>2175</v>
-      </c>
-      <c r="E20">
-        <v>13</v>
-      </c>
-      <c r="F20" t="s">
-        <v>1949</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>1302</v>
-      </c>
-      <c r="B21" t="s">
-        <v>1374</v>
-      </c>
-      <c r="C21" t="s">
-        <v>2163</v>
-      </c>
-      <c r="D21" t="s">
-        <v>2176</v>
-      </c>
-      <c r="E21">
-        <v>14</v>
-      </c>
-      <c r="F21" t="s">
-        <v>1949</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>1302</v>
-      </c>
-      <c r="B22" t="s">
-        <v>1374</v>
-      </c>
-      <c r="C22" t="s">
-        <v>2164</v>
-      </c>
-      <c r="D22" t="s">
-        <v>2177</v>
-      </c>
-      <c r="E22">
-        <v>15</v>
-      </c>
-      <c r="F22" t="s">
-        <v>1949</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>1304</v>
-      </c>
-      <c r="B23" t="s">
-        <v>1376</v>
-      </c>
-      <c r="C23" t="s">
-        <v>2194</v>
-      </c>
-      <c r="D23" t="s">
-        <v>2207</v>
-      </c>
-      <c r="E23">
-        <v>1</v>
-      </c>
-      <c r="F23" t="s">
-        <v>1468</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>1304</v>
-      </c>
-      <c r="B24" t="s">
-        <v>1376</v>
-      </c>
-      <c r="C24" t="s">
-        <v>2195</v>
-      </c>
-      <c r="D24" t="s">
-        <v>2208</v>
-      </c>
-      <c r="E24">
-        <v>2</v>
-      </c>
-      <c r="F24" t="s">
-        <v>1468</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>1304</v>
-      </c>
-      <c r="B25" t="s">
-        <v>1376</v>
-      </c>
-      <c r="C25" t="s">
-        <v>2196</v>
-      </c>
-      <c r="D25" t="s">
-        <v>2209</v>
-      </c>
-      <c r="E25">
-        <v>3</v>
-      </c>
-      <c r="F25" t="s">
-        <v>1468</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>1304</v>
-      </c>
-      <c r="B26" t="s">
-        <v>1376</v>
-      </c>
-      <c r="C26" t="s">
-        <v>2197</v>
-      </c>
-      <c r="D26" t="s">
-        <v>2210</v>
-      </c>
-      <c r="E26">
-        <v>4</v>
-      </c>
-      <c r="F26" t="s">
-        <v>1468</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>1304</v>
-      </c>
-      <c r="B27" t="s">
-        <v>1376</v>
-      </c>
-      <c r="C27" t="s">
-        <v>2198</v>
-      </c>
-      <c r="D27" t="s">
-        <v>2218</v>
-      </c>
-      <c r="E27">
-        <v>5</v>
-      </c>
-      <c r="F27" t="s">
-        <v>1468</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>1304</v>
-      </c>
-      <c r="B28" t="s">
-        <v>1376</v>
-      </c>
-      <c r="C28" t="s">
-        <v>2199</v>
-      </c>
-      <c r="D28" t="s">
-        <v>2211</v>
-      </c>
-      <c r="E28">
-        <v>6</v>
-      </c>
-      <c r="F28" t="s">
-        <v>1468</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>1304</v>
-      </c>
-      <c r="B29" t="s">
-        <v>1376</v>
-      </c>
-      <c r="C29" t="s">
-        <v>2200</v>
-      </c>
-      <c r="D29" t="s">
-        <v>2212</v>
-      </c>
-      <c r="E29">
-        <v>7</v>
-      </c>
-      <c r="F29" t="s">
-        <v>1468</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>1304</v>
-      </c>
-      <c r="B30" t="s">
-        <v>1376</v>
-      </c>
-      <c r="C30" t="s">
-        <v>2201</v>
-      </c>
-      <c r="D30" t="s">
-        <v>2213</v>
-      </c>
-      <c r="E30">
-        <v>8</v>
-      </c>
-      <c r="F30" t="s">
-        <v>1468</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>1304</v>
-      </c>
-      <c r="B31" t="s">
-        <v>1376</v>
-      </c>
-      <c r="C31" t="s">
-        <v>2202</v>
-      </c>
-      <c r="D31" t="s">
-        <v>2214</v>
-      </c>
-      <c r="E31">
-        <v>9</v>
-      </c>
-      <c r="F31" t="s">
-        <v>1949</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>1304</v>
-      </c>
-      <c r="B32" t="s">
-        <v>1376</v>
-      </c>
-      <c r="C32" t="s">
-        <v>2203</v>
-      </c>
-      <c r="D32" t="s">
-        <v>2215</v>
-      </c>
-      <c r="E32">
-        <v>10</v>
-      </c>
-      <c r="F32" t="s">
-        <v>1949</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>1304</v>
-      </c>
-      <c r="B33" t="s">
-        <v>1376</v>
-      </c>
-      <c r="C33" t="s">
-        <v>2204</v>
-      </c>
-      <c r="D33" t="s">
-        <v>2216</v>
-      </c>
-      <c r="E33">
-        <v>11</v>
-      </c>
-      <c r="F33" t="s">
-        <v>1468</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>1304</v>
-      </c>
-      <c r="B34" t="s">
-        <v>1376</v>
-      </c>
-      <c r="C34" t="s">
-        <v>2205</v>
-      </c>
-      <c r="D34" t="s">
-        <v>2219</v>
-      </c>
-      <c r="E34">
-        <v>12</v>
-      </c>
-      <c r="F34" t="s">
-        <v>1949</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>1304</v>
-      </c>
-      <c r="B35" t="s">
-        <v>1376</v>
-      </c>
-      <c r="C35" t="s">
-        <v>2206</v>
-      </c>
-      <c r="D35" t="s">
-        <v>2217</v>
-      </c>
-      <c r="E35">
-        <v>13</v>
-      </c>
-      <c r="F35" t="s">
-        <v>1468</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>1306</v>
-      </c>
-      <c r="B36" t="s">
-        <v>1378</v>
-      </c>
-      <c r="C36" t="s">
-        <v>2226</v>
-      </c>
-      <c r="D36" t="s">
-        <v>2229</v>
-      </c>
-      <c r="E36">
-        <v>1</v>
-      </c>
-      <c r="F36" t="s">
-        <v>1503</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>1306</v>
-      </c>
-      <c r="B37" t="s">
-        <v>1378</v>
-      </c>
-      <c r="C37" t="s">
-        <v>2227</v>
-      </c>
-      <c r="D37" t="s">
-        <v>2230</v>
-      </c>
-      <c r="E37">
-        <v>2</v>
-      </c>
-      <c r="F37" t="s">
-        <v>1503</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>1306</v>
-      </c>
-      <c r="B38" t="s">
-        <v>1378</v>
-      </c>
-      <c r="C38" t="s">
-        <v>2228</v>
-      </c>
-      <c r="D38" t="s">
-        <v>2231</v>
-      </c>
-      <c r="E38">
-        <v>3</v>
-      </c>
-      <c r="F38" t="s">
-        <v>1503</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>1307</v>
-      </c>
-      <c r="B39" t="s">
-        <v>1379</v>
-      </c>
-      <c r="C39" t="s">
-        <v>2238</v>
-      </c>
-      <c r="D39" t="s">
-        <v>2239</v>
-      </c>
-      <c r="E39">
-        <v>1</v>
-      </c>
-      <c r="F39" t="s">
-        <v>1503</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>1307</v>
-      </c>
-      <c r="B40" t="s">
-        <v>1379</v>
-      </c>
-      <c r="C40" t="s">
-        <v>2240</v>
-      </c>
-      <c r="D40" t="s">
-        <v>2245</v>
-      </c>
-      <c r="E40">
-        <v>2</v>
-      </c>
-      <c r="F40" t="s">
-        <v>1503</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>1307</v>
-      </c>
-      <c r="B41" t="s">
-        <v>1379</v>
-      </c>
-      <c r="C41" t="s">
-        <v>2241</v>
-      </c>
-      <c r="D41" t="s">
-        <v>2244</v>
-      </c>
-      <c r="E41">
-        <v>3</v>
-      </c>
-      <c r="F41" t="s">
-        <v>1503</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>1307</v>
-      </c>
-      <c r="B42" t="s">
-        <v>1379</v>
-      </c>
-      <c r="C42" t="s">
-        <v>2242</v>
-      </c>
-      <c r="D42" t="s">
-        <v>2243</v>
-      </c>
-      <c r="E42">
-        <v>4</v>
-      </c>
-      <c r="F42" t="s">
-        <v>1503</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>1308</v>
-      </c>
-      <c r="B43" t="s">
-        <v>1380</v>
-      </c>
-      <c r="C43" t="s">
-        <v>2254</v>
-      </c>
-      <c r="D43" t="s">
-        <v>2263</v>
-      </c>
-      <c r="E43">
-        <v>1</v>
-      </c>
-      <c r="F43" t="s">
-        <v>1503</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
-        <v>1308</v>
-      </c>
-      <c r="B44" t="s">
-        <v>1380</v>
-      </c>
-      <c r="C44" t="s">
-        <v>2255</v>
-      </c>
-      <c r="D44" t="s">
-        <v>2264</v>
-      </c>
-      <c r="E44">
-        <v>2</v>
-      </c>
-      <c r="F44" t="s">
-        <v>1503</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
-        <v>1308</v>
-      </c>
-      <c r="B45" t="s">
-        <v>1380</v>
-      </c>
-      <c r="C45" t="s">
-        <v>2256</v>
-      </c>
-      <c r="D45" t="s">
-        <v>2266</v>
-      </c>
-      <c r="E45">
-        <v>3</v>
-      </c>
-      <c r="F45" t="s">
-        <v>1503</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
-        <v>1308</v>
-      </c>
-      <c r="B46" t="s">
-        <v>1380</v>
-      </c>
-      <c r="C46" t="s">
-        <v>2257</v>
-      </c>
-      <c r="D46" t="s">
-        <v>2267</v>
-      </c>
-      <c r="E46">
-        <v>4</v>
-      </c>
-      <c r="F46" t="s">
-        <v>1503</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
-        <v>1308</v>
-      </c>
-      <c r="B47" t="s">
-        <v>1380</v>
-      </c>
-      <c r="C47" t="s">
-        <v>2258</v>
-      </c>
-      <c r="D47" t="s">
-        <v>2268</v>
-      </c>
-      <c r="E47">
-        <v>5</v>
-      </c>
-      <c r="F47" t="s">
-        <v>1503</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
-        <v>1308</v>
-      </c>
-      <c r="B48" t="s">
-        <v>1380</v>
-      </c>
-      <c r="C48" t="s">
-        <v>2259</v>
-      </c>
-      <c r="D48" t="s">
-        <v>2269</v>
-      </c>
-      <c r="E48">
-        <v>6</v>
-      </c>
-      <c r="F48" t="s">
-        <v>1503</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
-        <v>1308</v>
-      </c>
-      <c r="B49" t="s">
-        <v>1380</v>
-      </c>
-      <c r="C49" t="s">
-        <v>2260</v>
-      </c>
-      <c r="D49" t="s">
-        <v>2270</v>
-      </c>
-      <c r="E49">
-        <v>7</v>
-      </c>
-      <c r="F49" t="s">
-        <v>1503</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
-        <v>1308</v>
-      </c>
-      <c r="B50" t="s">
-        <v>1380</v>
-      </c>
-      <c r="C50" t="s">
-        <v>2261</v>
-      </c>
-      <c r="D50" t="s">
-        <v>2271</v>
-      </c>
-      <c r="E50">
-        <v>8</v>
-      </c>
-      <c r="F50" t="s">
-        <v>1503</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
-        <v>1308</v>
-      </c>
-      <c r="B51" t="s">
-        <v>1380</v>
-      </c>
-      <c r="C51" t="s">
-        <v>2262</v>
-      </c>
-      <c r="D51" t="s">
-        <v>2265</v>
-      </c>
-      <c r="E51">
-        <v>9</v>
-      </c>
-      <c r="F51" t="s">
-        <v>1503</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A52" t="s">
-        <v>1309</v>
-      </c>
-      <c r="B52" t="s">
-        <v>1381</v>
-      </c>
-      <c r="C52" t="s">
-        <v>2288</v>
-      </c>
-      <c r="D52" t="s">
-        <v>2295</v>
-      </c>
-      <c r="E52">
-        <v>1</v>
-      </c>
-      <c r="F52" t="s">
-        <v>1503</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A53" t="s">
-        <v>1309</v>
-      </c>
-      <c r="B53" t="s">
-        <v>1381</v>
-      </c>
-      <c r="C53" t="s">
-        <v>2289</v>
-      </c>
-      <c r="D53" t="s">
-        <v>2296</v>
-      </c>
-      <c r="E53">
-        <v>2</v>
-      </c>
-      <c r="F53" t="s">
-        <v>1503</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A54" t="s">
-        <v>1309</v>
-      </c>
-      <c r="B54" t="s">
-        <v>1381</v>
-      </c>
-      <c r="C54" t="s">
-        <v>2290</v>
-      </c>
-      <c r="D54" t="s">
-        <v>2297</v>
-      </c>
-      <c r="E54">
-        <v>3</v>
-      </c>
-      <c r="F54" t="s">
-        <v>1503</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A55" t="s">
-        <v>1309</v>
-      </c>
-      <c r="B55" t="s">
-        <v>1381</v>
-      </c>
-      <c r="C55" t="s">
-        <v>2291</v>
-      </c>
-      <c r="D55" t="s">
-        <v>2300</v>
-      </c>
-      <c r="E55">
-        <v>4</v>
-      </c>
-      <c r="F55" t="s">
-        <v>1503</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A56" t="s">
-        <v>1309</v>
-      </c>
-      <c r="B56" t="s">
-        <v>1381</v>
-      </c>
-      <c r="C56" t="s">
-        <v>2292</v>
-      </c>
-      <c r="D56" t="s">
-        <v>2298</v>
-      </c>
-      <c r="E56">
-        <v>5</v>
-      </c>
-      <c r="F56" t="s">
-        <v>1503</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A57" t="s">
-        <v>1309</v>
-      </c>
-      <c r="B57" t="s">
-        <v>1381</v>
-      </c>
-      <c r="C57" t="s">
-        <v>2293</v>
-      </c>
-      <c r="D57" t="s">
-        <v>2299</v>
-      </c>
-      <c r="E57">
-        <v>6</v>
-      </c>
-      <c r="F57" t="s">
-        <v>1503</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A58" t="s">
-        <v>1309</v>
-      </c>
-      <c r="B58" t="s">
-        <v>1381</v>
-      </c>
-      <c r="C58" t="s">
-        <v>2294</v>
-      </c>
-      <c r="D58" t="s">
-        <v>2301</v>
-      </c>
-      <c r="E58">
-        <v>7</v>
-      </c>
-      <c r="F58" t="s">
-        <v>1503</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A59" t="s">
-        <v>1310</v>
-      </c>
-      <c r="B59" t="s">
-        <v>1382</v>
-      </c>
-      <c r="C59" t="s">
-        <v>2314</v>
-      </c>
-      <c r="D59" t="s">
-        <v>2318</v>
-      </c>
-      <c r="E59">
-        <v>1</v>
-      </c>
-      <c r="F59" t="s">
-        <v>1503</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A60" t="s">
-        <v>1310</v>
-      </c>
-      <c r="B60" t="s">
-        <v>1382</v>
-      </c>
-      <c r="C60" t="s">
-        <v>2315</v>
-      </c>
-      <c r="D60" t="s">
-        <v>2319</v>
-      </c>
-      <c r="E60">
-        <v>2</v>
-      </c>
-      <c r="F60" t="s">
-        <v>1503</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A61" t="s">
-        <v>1310</v>
-      </c>
-      <c r="B61" t="s">
-        <v>1382</v>
-      </c>
-      <c r="C61" t="s">
-        <v>2316</v>
-      </c>
-      <c r="D61" t="s">
-        <v>2320</v>
-      </c>
-      <c r="E61">
-        <v>3</v>
-      </c>
-      <c r="F61" t="s">
-        <v>1503</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A62" t="s">
-        <v>1310</v>
-      </c>
-      <c r="B62" t="s">
-        <v>1382</v>
-      </c>
-      <c r="C62" t="s">
-        <v>2317</v>
-      </c>
-      <c r="D62" t="s">
-        <v>2321</v>
-      </c>
-      <c r="E62">
-        <v>4</v>
-      </c>
-      <c r="F62" t="s">
-        <v>1503</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A63" t="s">
-        <v>1323</v>
-      </c>
-      <c r="B63" t="s">
-        <v>1393</v>
-      </c>
-      <c r="C63" t="s">
-        <v>2439</v>
-      </c>
-      <c r="D63" t="s">
-        <v>2440</v>
-      </c>
-      <c r="E63">
-        <v>1</v>
-      </c>
-      <c r="F63" t="s">
-        <v>1506</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A64" t="s">
-        <v>1326</v>
-      </c>
-      <c r="B64" t="s">
-        <v>1396</v>
-      </c>
-      <c r="C64" t="s">
-        <v>2473</v>
-      </c>
-      <c r="D64" t="s">
-        <v>2474</v>
-      </c>
-      <c r="E64">
-        <v>1</v>
-      </c>
-      <c r="F64" t="s">
-        <v>1503</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/data/Fate-Spreadsheet.xlsx
+++ b/data/Fate-Spreadsheet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Important\Python\Fate-Wiki\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AECEEA88-4C6A-4D9C-BF5B-579B066E645F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C5EBDEB-3EBE-4AC4-B87C-81898D0D729E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="2" activeTab="7" xr2:uid="{B05E798F-9EF6-4508-A0A4-311D06661AED}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="1" activeTab="1" xr2:uid="{B05E798F-9EF6-4508-A0A4-311D06661AED}"/>
   </bookViews>
   <sheets>
     <sheet name="Servants" sheetId="1" r:id="rId1"/>
@@ -22,6 +22,7 @@
     <sheet name="Master Abilities" sheetId="6" r:id="rId7"/>
     <sheet name="Master Assets" sheetId="9" r:id="rId8"/>
     <sheet name="Master Ascensions" sheetId="10" r:id="rId9"/>
+    <sheet name="Master Mechanics List" sheetId="12" r:id="rId10"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -47,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5762" uniqueCount="2507">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5769" uniqueCount="2508">
   <si>
     <t>servant_id</t>
   </si>
@@ -7568,6 +7569,9 @@
   </si>
   <si>
     <t>old-acquaintances</t>
+  </si>
+  <si>
+    <t>mechanics</t>
   </si>
 </sst>
 </file>
@@ -7959,6 +7963,7 @@
   <dimension ref="A1:R189"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="1" max="1" width="14.85546875" customWidth="1"/>
     <col min="2" max="3" width="22" customWidth="1"/>
     <col min="4" max="4" width="12.5703125" customWidth="1"/>
     <col min="5" max="5" width="11.28515625" customWidth="1"/>
@@ -14450,6 +14455,55 @@
   <ignoredErrors>
     <ignoredError sqref="H2 I6:I7 I10 I12 H14 I18 I22 I24 I27 G34 I40 I42 I45 I52 I62 I72 H79 I80 I84 I88 I90 G91 H100 I119 I124 I121:I123 G130:I139 G142:I148 G164:I185 G187:I187" numberStoredAsText="1"/>
   </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{41E57DE0-A26F-4023-BFBB-B4D5A6C17F78}">
+  <dimension ref="A1:A7"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="21" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>2507</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>1333</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>1334</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>1335</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>1336</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>1337</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>1373</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
